--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -1629,550 +1629,760 @@
       <c r="H34" s="2" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>NU02-02</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="4" t="n"/>
-      <c r="H35" s="4" t="n"/>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Kinderstuhl IKEA Kritter, weiß</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>NU02-03</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="3" t="n"/>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Kindertisch rund, weiß</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>NU02-04</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="3" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n"/>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Kinderstuhl VS, grau</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>NU02-05</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="3" t="n"/>
-      <c r="G38" s="4" t="n"/>
-      <c r="H38" s="4" t="n"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Kindertisch halbrund, weiß</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>NU02-06</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="E39" s="4" t="n"/>
-      <c r="F39" s="3" t="n"/>
-      <c r="G39" s="4" t="n"/>
-      <c r="H39" s="4" t="n"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Beistelltisch Drahtkorb, Kupfer</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>NU02-07</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="3" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Ohrensessel klein, creme</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>NU02-08</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="3" t="n"/>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="n"/>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Spieltisch Kiefer mit weißen Einlagen</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>NU02-09</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="3" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="4" t="n"/>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Tisch weiß mit grauer Platte</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>NU02-10</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="3" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Pinolino Kindersitzgruppe rund, Holz</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>NU02-11</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="3" t="n"/>
-      <c r="G44" s="4" t="n"/>
-      <c r="H44" s="4" t="n"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Mammut Kindertisch mit vier Stühlen</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>NU02-12</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="3" t="n"/>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Mammut Kinderstuhl, rosa und grün</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>NU02-13</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="3" t="n"/>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n"/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Konsole Bambus mit weißer Ablagewanne</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>NU02-14</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="E47" s="4" t="n"/>
-      <c r="F47" s="3" t="n"/>
-      <c r="G47" s="4" t="n"/>
-      <c r="H47" s="4" t="n"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Wandregal beige, lang</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>NU02-15</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="3" t="n"/>
-      <c r="G48" s="4" t="n"/>
-      <c r="H48" s="4" t="n"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Wandregal weiß, kurz</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>NU02-16</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="E49" s="4" t="n"/>
-      <c r="F49" s="3" t="n"/>
-      <c r="G49" s="4" t="n"/>
-      <c r="H49" s="4" t="n"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Sitztier Elefant, weiß</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>NU02-17</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="E50" s="4" t="n"/>
-      <c r="F50" s="3" t="n"/>
-      <c r="G50" s="4" t="n"/>
-      <c r="H50" s="4" t="n"/>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Schrank weiß, zwei Türen</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>NU02-18</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="E51" s="4" t="n"/>
-      <c r="F51" s="3" t="n"/>
-      <c r="G51" s="4" t="n"/>
-      <c r="H51" s="4" t="n"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Schrank weiß mit zwei Schubladen</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>NU02-19</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="E52" s="4" t="n"/>
-      <c r="F52" s="3" t="n"/>
-      <c r="G52" s="4" t="n"/>
-      <c r="H52" s="4" t="n"/>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Regal weiß, hoch, drei Fächer</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>NU02-20</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="E53" s="4" t="n"/>
-      <c r="F53" s="3" t="n"/>
-      <c r="G53" s="4" t="n"/>
-      <c r="H53" s="4" t="n"/>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Acrylbild schwarz-weiß, abstrakt</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>NU02-21</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="E54" s="4" t="n"/>
-      <c r="F54" s="3" t="n"/>
-      <c r="G54" s="4" t="n"/>
-      <c r="H54" s="4" t="n"/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Konferenztisch weiß aus Segmenten</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>NU02-22</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="E55" s="4" t="n"/>
-      <c r="F55" s="3" t="n"/>
-      <c r="G55" s="4" t="n"/>
-      <c r="H55" s="4" t="n"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Regal weiß, niedrig, drei Fächer</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -11737,7 +11947,7 @@
         </is>
       </c>
       <c r="F412" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
@@ -11769,11 +11979,11 @@
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>Regal weiß 2x2</t>
+          <t>Regal weiß, 4 Fächer (IKEA Kallax)</t>
         </is>
       </c>
       <c r="F413" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -2011,7 +2011,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>IKEA Mammut Kinderstuhl, rosa und grün</t>
+          <t>IKEA Mammut Kinderstuhl, verschiedene Farben</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Konsole Bambus mit weißer Ablagewanne</t>
+          <t>Ablagetisch Bambus mit Wanne</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
@@ -2155,11 +2155,11 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Sitztier Elefant, weiß</t>
+          <t>Sitztier Elefant, weiß und schwarz</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Konferenztisch weiß aus Segmenten</t>
+          <t>Kindertisch weiß aus vier Segmenten</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -2889,238 +2889,328 @@
       <c r="H74" s="2" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>NU03-02</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 4</t>
         </is>
       </c>
-      <c r="E75" s="4" t="n"/>
-      <c r="F75" s="3" t="n"/>
-      <c r="G75" s="4" t="n"/>
-      <c r="H75" s="4" t="n"/>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Stockbett weiß mit Absturzsicherung</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>NU03-03</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 4</t>
         </is>
       </c>
-      <c r="E76" s="4" t="n"/>
-      <c r="F76" s="3" t="n"/>
-      <c r="G76" s="4" t="n"/>
-      <c r="H76" s="4" t="n"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Wesco Spielküche, mehrteilig</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>NU03-04</t>
         </is>
       </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 4</t>
         </is>
       </c>
-      <c r="E77" s="4" t="n"/>
-      <c r="F77" s="3" t="n"/>
-      <c r="G77" s="4" t="n"/>
-      <c r="H77" s="4" t="n"/>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Wesco Bügelbrett und Wäscheständer, Kindergröße</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>NU03-05</t>
         </is>
       </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 4</t>
         </is>
       </c>
-      <c r="E78" s="4" t="n"/>
-      <c r="F78" s="3" t="n"/>
-      <c r="G78" s="4" t="n"/>
-      <c r="H78" s="4" t="n"/>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Flumi Kindersessel, beige Bouclé</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>NU03-06</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 4</t>
         </is>
       </c>
-      <c r="E79" s="4" t="n"/>
-      <c r="F79" s="3" t="n"/>
-      <c r="G79" s="4" t="n"/>
-      <c r="H79" s="4" t="n"/>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Wandregal Kiefer mit Fächern</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>NU03-07</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 4</t>
         </is>
       </c>
-      <c r="E80" s="4" t="n"/>
-      <c r="F80" s="3" t="n"/>
-      <c r="G80" s="4" t="n"/>
-      <c r="H80" s="4" t="n"/>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Offenes Regal Kiefer, drei Fächer</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>NU03-08</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 4</t>
         </is>
       </c>
-      <c r="E81" s="4" t="n"/>
-      <c r="F81" s="3" t="n"/>
-      <c r="G81" s="4" t="n"/>
-      <c r="H81" s="4" t="n"/>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Malm Kommode, 3 Schubladen, weiß</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>NU03-09</t>
         </is>
       </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 4</t>
         </is>
       </c>
-      <c r="E82" s="4" t="n"/>
-      <c r="F82" s="3" t="n"/>
-      <c r="G82" s="4" t="n"/>
-      <c r="H82" s="4" t="n"/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Treppenregal Kiefer mit Wannen</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>NU03-10</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 4</t>
         </is>
       </c>
-      <c r="E83" s="4" t="n"/>
-      <c r="F83" s="3" t="n"/>
-      <c r="G83" s="4" t="n"/>
-      <c r="H83" s="4" t="n"/>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Kinderhochstuhl Kunststoff mit Gurt</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="F107" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
@@ -5643,186 +5643,256 @@
       <c r="H163" s="4" t="n"/>
     </row>
     <row r="164">
-      <c r="A164" s="4" t="inlineStr">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>NU07-01</t>
         </is>
       </c>
-      <c r="B164" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C164" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D164" s="4" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Garage</t>
         </is>
       </c>
-      <c r="E164" s="4" t="n"/>
-      <c r="F164" s="3" t="n"/>
-      <c r="G164" s="4" t="n"/>
-      <c r="H164" s="4" t="n"/>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Hausbett schwarz mit Dach</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="n"/>
     </row>
     <row r="165">
-      <c r="A165" s="4" t="inlineStr">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>NU07-02</t>
         </is>
       </c>
-      <c r="B165" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C165" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D165" s="4" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Garage</t>
         </is>
       </c>
-      <c r="E165" s="4" t="n"/>
-      <c r="F165" s="3" t="n"/>
-      <c r="G165" s="4" t="n"/>
-      <c r="H165" s="4" t="n"/>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Kaufladen weiß mit Aufsatz</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="4" t="inlineStr">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>NU07-03</t>
         </is>
       </c>
-      <c r="B166" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C166" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D166" s="4" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Garage</t>
         </is>
       </c>
-      <c r="E166" s="4" t="n"/>
-      <c r="F166" s="3" t="n"/>
-      <c r="G166" s="4" t="n"/>
-      <c r="H166" s="4" t="n"/>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Wesco Spielküche, mehrteilig</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="n"/>
     </row>
     <row r="167">
-      <c r="A167" s="4" t="inlineStr">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>NU07-04</t>
         </is>
       </c>
-      <c r="B167" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C167" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D167" s="4" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Garage</t>
         </is>
       </c>
-      <c r="E167" s="4" t="n"/>
-      <c r="F167" s="3" t="n"/>
-      <c r="G167" s="4" t="n"/>
-      <c r="H167" s="4" t="n"/>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>howa Kinderspielgrill</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="4" t="inlineStr">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>NU07-05</t>
         </is>
       </c>
-      <c r="B168" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C168" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D168" s="4" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Garage</t>
         </is>
       </c>
-      <c r="E168" s="4" t="n"/>
-      <c r="F168" s="3" t="n"/>
-      <c r="G168" s="4" t="n"/>
-      <c r="H168" s="4" t="n"/>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Kinderkleiderschrank Birke mit zwei Türen</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="n"/>
     </row>
     <row r="169">
-      <c r="A169" s="4" t="inlineStr">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>NU07-06</t>
         </is>
       </c>
-      <c r="B169" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C169" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D169" s="4" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Garage</t>
         </is>
       </c>
-      <c r="E169" s="4" t="n"/>
-      <c r="F169" s="3" t="n"/>
-      <c r="G169" s="4" t="n"/>
-      <c r="H169" s="4" t="n"/>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Aufbewahrungsregal weiß mit zehn Einschüben</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="4" t="inlineStr">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>NU07-07</t>
         </is>
       </c>
-      <c r="B170" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C170" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D170" s="4" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Garage</t>
         </is>
       </c>
-      <c r="E170" s="4" t="n"/>
-      <c r="F170" s="3" t="n"/>
-      <c r="G170" s="4" t="n"/>
-      <c r="H170" s="4" t="n"/>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Sitzgruppe: Tisch und zwei Truhenbänke</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -25793,108 +25793,148 @@
       <c r="H918" s="4" t="n"/>
     </row>
     <row r="919">
-      <c r="A919" s="4" t="inlineStr">
+      <c r="A919" s="2" t="inlineStr">
         <is>
           <t>BA01-01</t>
         </is>
       </c>
-      <c r="B919" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C919" s="4" t="inlineStr">
+      <c r="B919" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C919" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D919" s="4" t="inlineStr">
+      <c r="D919" s="2" t="inlineStr">
         <is>
           <t>Flur 1</t>
         </is>
       </c>
-      <c r="E919" s="4" t="n"/>
-      <c r="F919" s="3" t="n"/>
-      <c r="G919" s="4" t="n"/>
-      <c r="H919" s="4" t="n"/>
+      <c r="E919" s="2" t="inlineStr">
+        <is>
+          <t>Gemälde Mona Lisa, Pop-Art</t>
+        </is>
+      </c>
+      <c r="F919" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G919" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H919" s="2" t="n"/>
     </row>
     <row r="920">
-      <c r="A920" s="4" t="inlineStr">
+      <c r="A920" s="2" t="inlineStr">
         <is>
           <t>BA01-02</t>
         </is>
       </c>
-      <c r="B920" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C920" s="4" t="inlineStr">
+      <c r="B920" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C920" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D920" s="4" t="inlineStr">
+      <c r="D920" s="2" t="inlineStr">
         <is>
           <t>Flur 1</t>
         </is>
       </c>
-      <c r="E920" s="4" t="n"/>
-      <c r="F920" s="3" t="n"/>
-      <c r="G920" s="4" t="n"/>
-      <c r="H920" s="4" t="n"/>
+      <c r="E920" s="2" t="inlineStr">
+        <is>
+          <t>Acrylbild abstrakt, Neonfarben</t>
+        </is>
+      </c>
+      <c r="F920" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G920" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H920" s="2" t="n"/>
     </row>
     <row r="921">
-      <c r="A921" s="4" t="inlineStr">
+      <c r="A921" s="2" t="inlineStr">
         <is>
           <t>BA01-03</t>
         </is>
       </c>
-      <c r="B921" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C921" s="4" t="inlineStr">
+      <c r="B921" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C921" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D921" s="4" t="inlineStr">
+      <c r="D921" s="2" t="inlineStr">
         <is>
           <t>Flur 1</t>
         </is>
       </c>
-      <c r="E921" s="4" t="n"/>
-      <c r="F921" s="3" t="n"/>
-      <c r="G921" s="4" t="n"/>
-      <c r="H921" s="4" t="n"/>
+      <c r="E921" s="2" t="inlineStr">
+        <is>
+          <t>Tannen-Dekoration</t>
+        </is>
+      </c>
+      <c r="F921" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G921" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H921" s="2" t="n"/>
     </row>
     <row r="922">
-      <c r="A922" s="4" t="inlineStr">
+      <c r="A922" s="2" t="inlineStr">
         <is>
           <t>BA01-04</t>
         </is>
       </c>
-      <c r="B922" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C922" s="4" t="inlineStr">
+      <c r="B922" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C922" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D922" s="4" t="inlineStr">
+      <c r="D922" s="2" t="inlineStr">
         <is>
           <t>Flur 1</t>
         </is>
       </c>
-      <c r="E922" s="4" t="n"/>
-      <c r="F922" s="3" t="n"/>
-      <c r="G922" s="4" t="n"/>
-      <c r="H922" s="4" t="n"/>
+      <c r="E922" s="2" t="inlineStr">
+        <is>
+          <t>Leuchtbuchstabe K, schwarz</t>
+        </is>
+      </c>
+      <c r="F922" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G922" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H922" s="2" t="n"/>
     </row>
     <row r="923">
       <c r="A923" s="4" t="inlineStr">

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -25887,11 +25887,11 @@
       </c>
       <c r="E921" s="2" t="inlineStr">
         <is>
-          <t>Tannen-Dekoration</t>
+          <t>Deko-Tannen Metall auf Holzsockel</t>
         </is>
       </c>
       <c r="F921" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G921" s="2" t="inlineStr">
         <is>

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anleitung" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Erfassung'!$A$1:$H$1277</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Erfassung'!$A$1:$H$1280</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1277"/>
+  <dimension ref="A1:H1280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25927,7 +25927,7 @@
         </is>
       </c>
       <c r="F922" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G922" s="2" t="inlineStr">
         <is>
@@ -26223,212 +26223,292 @@
       <c r="H933" s="4" t="n"/>
     </row>
     <row r="934">
-      <c r="A934" s="4" t="inlineStr">
+      <c r="A934" s="2" t="inlineStr">
         <is>
           <t>BA02-01</t>
         </is>
       </c>
-      <c r="B934" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C934" s="4" t="inlineStr">
+      <c r="B934" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C934" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D934" s="4" t="inlineStr">
+      <c r="D934" s="2" t="inlineStr">
         <is>
           <t>Flur 2</t>
         </is>
       </c>
-      <c r="E934" s="4" t="n"/>
-      <c r="F934" s="3" t="n"/>
-      <c r="G934" s="4" t="n"/>
-      <c r="H934" s="4" t="n"/>
+      <c r="E934" s="2" t="inlineStr">
+        <is>
+          <t>Kindergarderobe weiß</t>
+        </is>
+      </c>
+      <c r="F934" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G934" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H934" s="2" t="n"/>
     </row>
     <row r="935">
-      <c r="A935" s="4" t="inlineStr">
+      <c r="A935" s="2" t="inlineStr">
         <is>
           <t>BA02-02</t>
         </is>
       </c>
-      <c r="B935" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C935" s="4" t="inlineStr">
+      <c r="B935" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C935" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D935" s="4" t="inlineStr">
+      <c r="D935" s="2" t="inlineStr">
         <is>
           <t>Flur 2</t>
         </is>
       </c>
-      <c r="E935" s="4" t="n"/>
-      <c r="F935" s="3" t="n"/>
-      <c r="G935" s="4" t="n"/>
-      <c r="H935" s="4" t="n"/>
+      <c r="E935" s="2" t="inlineStr">
+        <is>
+          <t>Rutscherauto rot</t>
+        </is>
+      </c>
+      <c r="F935" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G935" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H935" s="2" t="n"/>
     </row>
     <row r="936">
-      <c r="A936" s="4" t="inlineStr">
+      <c r="A936" s="2" t="inlineStr">
         <is>
           <t>BA02-03</t>
         </is>
       </c>
-      <c r="B936" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C936" s="4" t="inlineStr">
+      <c r="B936" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C936" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D936" s="4" t="inlineStr">
+      <c r="D936" s="2" t="inlineStr">
         <is>
           <t>Flur 2</t>
         </is>
       </c>
-      <c r="E936" s="4" t="n"/>
-      <c r="F936" s="3" t="n"/>
-      <c r="G936" s="4" t="n"/>
-      <c r="H936" s="4" t="n"/>
+      <c r="E936" s="2" t="inlineStr">
+        <is>
+          <t>Bilder Schwarzwald, gerahmt</t>
+        </is>
+      </c>
+      <c r="F936" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G936" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H936" s="2" t="n"/>
     </row>
     <row r="937">
-      <c r="A937" s="4" t="inlineStr">
+      <c r="A937" s="2" t="inlineStr">
         <is>
           <t>BA02-04</t>
         </is>
       </c>
-      <c r="B937" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C937" s="4" t="inlineStr">
+      <c r="B937" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C937" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D937" s="4" t="inlineStr">
+      <c r="D937" s="2" t="inlineStr">
         <is>
           <t>Flur 2</t>
         </is>
       </c>
-      <c r="E937" s="4" t="n"/>
-      <c r="F937" s="3" t="n"/>
-      <c r="G937" s="4" t="n"/>
-      <c r="H937" s="4" t="n"/>
+      <c r="E937" s="2" t="inlineStr">
+        <is>
+          <t>Kinder-Ohrensessel grau, Kunstleder</t>
+        </is>
+      </c>
+      <c r="F937" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G937" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H937" s="2" t="n"/>
     </row>
     <row r="938">
-      <c r="A938" s="4" t="inlineStr">
+      <c r="A938" s="2" t="inlineStr">
         <is>
           <t>BA02-05</t>
         </is>
       </c>
-      <c r="B938" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C938" s="4" t="inlineStr">
+      <c r="B938" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C938" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D938" s="4" t="inlineStr">
+      <c r="D938" s="2" t="inlineStr">
         <is>
           <t>Flur 2</t>
         </is>
       </c>
-      <c r="E938" s="4" t="n"/>
-      <c r="F938" s="3" t="n"/>
-      <c r="G938" s="4" t="n"/>
-      <c r="H938" s="4" t="n"/>
+      <c r="E938" s="2" t="inlineStr">
+        <is>
+          <t>Ablagepult Holz auf Metallgestell</t>
+        </is>
+      </c>
+      <c r="F938" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G938" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H938" s="2" t="n"/>
     </row>
     <row r="939">
-      <c r="A939" s="4" t="inlineStr">
+      <c r="A939" s="2" t="inlineStr">
         <is>
           <t>BA02-06</t>
         </is>
       </c>
-      <c r="B939" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C939" s="4" t="inlineStr">
+      <c r="B939" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C939" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D939" s="4" t="inlineStr">
+      <c r="D939" s="2" t="inlineStr">
         <is>
           <t>Flur 2</t>
         </is>
       </c>
-      <c r="E939" s="4" t="n"/>
-      <c r="F939" s="3" t="n"/>
-      <c r="G939" s="4" t="n"/>
-      <c r="H939" s="4" t="n"/>
+      <c r="E939" s="2" t="inlineStr">
+        <is>
+          <t>Truhenbank weiß mit Fellauflage</t>
+        </is>
+      </c>
+      <c r="F939" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G939" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H939" s="2" t="n"/>
     </row>
     <row r="940">
-      <c r="A940" s="4" t="inlineStr">
+      <c r="A940" s="2" t="inlineStr">
         <is>
           <t>BA02-07</t>
         </is>
       </c>
-      <c r="B940" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C940" s="4" t="inlineStr">
+      <c r="B940" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C940" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D940" s="4" t="inlineStr">
+      <c r="D940" s="2" t="inlineStr">
         <is>
           <t>Flur 2</t>
         </is>
       </c>
-      <c r="E940" s="4" t="n"/>
-      <c r="F940" s="3" t="n"/>
-      <c r="G940" s="4" t="n"/>
-      <c r="H940" s="4" t="n"/>
+      <c r="E940" s="2" t="inlineStr">
+        <is>
+          <t>Kinderschrank weiß mit Handabdrücken</t>
+        </is>
+      </c>
+      <c r="F940" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G940" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H940" s="2" t="n"/>
     </row>
     <row r="941">
-      <c r="A941" s="4" t="inlineStr">
+      <c r="A941" s="2" t="inlineStr">
         <is>
           <t>BA02-08</t>
         </is>
       </c>
-      <c r="B941" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C941" s="4" t="inlineStr">
+      <c r="B941" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C941" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D941" s="4" t="inlineStr">
+      <c r="D941" s="2" t="inlineStr">
         <is>
           <t>Flur 2</t>
         </is>
       </c>
-      <c r="E941" s="4" t="n"/>
-      <c r="F941" s="3" t="n"/>
-      <c r="G941" s="4" t="n"/>
-      <c r="H941" s="4" t="n"/>
+      <c r="E941" s="2" t="inlineStr">
+        <is>
+          <t>Deko-Häuser Keramik</t>
+        </is>
+      </c>
+      <c r="F941" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G941" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H941" s="2" t="n"/>
     </row>
     <row r="942">
       <c r="A942" s="4" t="inlineStr">
@@ -26615,7 +26695,7 @@
     <row r="949">
       <c r="A949" s="4" t="inlineStr">
         <is>
-          <t>BA03-01</t>
+          <t>BA02-16</t>
         </is>
       </c>
       <c r="B949" s="4" t="inlineStr">
@@ -26630,7 +26710,7 @@
       </c>
       <c r="D949" s="4" t="inlineStr">
         <is>
-          <t>Galerie</t>
+          <t>Flur 2</t>
         </is>
       </c>
       <c r="E949" s="4" t="n"/>
@@ -26641,7 +26721,7 @@
     <row r="950">
       <c r="A950" s="4" t="inlineStr">
         <is>
-          <t>BA03-02</t>
+          <t>BA02-17</t>
         </is>
       </c>
       <c r="B950" s="4" t="inlineStr">
@@ -26656,7 +26736,7 @@
       </c>
       <c r="D950" s="4" t="inlineStr">
         <is>
-          <t>Galerie</t>
+          <t>Flur 2</t>
         </is>
       </c>
       <c r="E950" s="4" t="n"/>
@@ -26667,7 +26747,7 @@
     <row r="951">
       <c r="A951" s="4" t="inlineStr">
         <is>
-          <t>BA03-03</t>
+          <t>BA02-18</t>
         </is>
       </c>
       <c r="B951" s="4" t="inlineStr">
@@ -26682,7 +26762,7 @@
       </c>
       <c r="D951" s="4" t="inlineStr">
         <is>
-          <t>Galerie</t>
+          <t>Flur 2</t>
         </is>
       </c>
       <c r="E951" s="4" t="n"/>
@@ -26693,7 +26773,7 @@
     <row r="952">
       <c r="A952" s="4" t="inlineStr">
         <is>
-          <t>BA03-04</t>
+          <t>BA03-01</t>
         </is>
       </c>
       <c r="B952" s="4" t="inlineStr">
@@ -26719,7 +26799,7 @@
     <row r="953">
       <c r="A953" s="4" t="inlineStr">
         <is>
-          <t>BA03-05</t>
+          <t>BA03-02</t>
         </is>
       </c>
       <c r="B953" s="4" t="inlineStr">
@@ -26745,7 +26825,7 @@
     <row r="954">
       <c r="A954" s="4" t="inlineStr">
         <is>
-          <t>BA03-06</t>
+          <t>BA03-03</t>
         </is>
       </c>
       <c r="B954" s="4" t="inlineStr">
@@ -26771,7 +26851,7 @@
     <row r="955">
       <c r="A955" s="4" t="inlineStr">
         <is>
-          <t>BA03-07</t>
+          <t>BA03-04</t>
         </is>
       </c>
       <c r="B955" s="4" t="inlineStr">
@@ -26797,7 +26877,7 @@
     <row r="956">
       <c r="A956" s="4" t="inlineStr">
         <is>
-          <t>BA03-08</t>
+          <t>BA03-05</t>
         </is>
       </c>
       <c r="B956" s="4" t="inlineStr">
@@ -26823,7 +26903,7 @@
     <row r="957">
       <c r="A957" s="4" t="inlineStr">
         <is>
-          <t>BA03-09</t>
+          <t>BA03-06</t>
         </is>
       </c>
       <c r="B957" s="4" t="inlineStr">
@@ -26849,7 +26929,7 @@
     <row r="958">
       <c r="A958" s="4" t="inlineStr">
         <is>
-          <t>BA03-10</t>
+          <t>BA03-07</t>
         </is>
       </c>
       <c r="B958" s="4" t="inlineStr">
@@ -26875,7 +26955,7 @@
     <row r="959">
       <c r="A959" s="4" t="inlineStr">
         <is>
-          <t>BA03-11</t>
+          <t>BA03-08</t>
         </is>
       </c>
       <c r="B959" s="4" t="inlineStr">
@@ -26901,7 +26981,7 @@
     <row r="960">
       <c r="A960" s="4" t="inlineStr">
         <is>
-          <t>BA03-12</t>
+          <t>BA03-09</t>
         </is>
       </c>
       <c r="B960" s="4" t="inlineStr">
@@ -26927,7 +27007,7 @@
     <row r="961">
       <c r="A961" s="4" t="inlineStr">
         <is>
-          <t>BA03-13</t>
+          <t>BA03-10</t>
         </is>
       </c>
       <c r="B961" s="4" t="inlineStr">
@@ -26953,7 +27033,7 @@
     <row r="962">
       <c r="A962" s="4" t="inlineStr">
         <is>
-          <t>BA03-14</t>
+          <t>BA03-11</t>
         </is>
       </c>
       <c r="B962" s="4" t="inlineStr">
@@ -26979,7 +27059,7 @@
     <row r="963">
       <c r="A963" s="4" t="inlineStr">
         <is>
-          <t>BA03-15</t>
+          <t>BA03-12</t>
         </is>
       </c>
       <c r="B963" s="4" t="inlineStr">
@@ -27003,81 +27083,61 @@
       <c r="H963" s="4" t="n"/>
     </row>
     <row r="964">
-      <c r="A964" s="2" t="inlineStr">
-        <is>
-          <t>BA04-01</t>
-        </is>
-      </c>
-      <c r="B964" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C964" s="2" t="inlineStr">
+      <c r="A964" s="4" t="inlineStr">
+        <is>
+          <t>BA03-13</t>
+        </is>
+      </c>
+      <c r="B964" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C964" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D964" s="2" t="inlineStr">
-        <is>
-          <t>Gruppenraum 4</t>
-        </is>
-      </c>
-      <c r="E964" s="2" t="inlineStr">
-        <is>
-          <t>Rattankörbe 8 Stück</t>
-        </is>
-      </c>
-      <c r="F964" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G964" s="2" t="inlineStr">
-        <is>
-          <t>Set</t>
-        </is>
-      </c>
-      <c r="H964" s="2" t="n"/>
+      <c r="D964" s="4" t="inlineStr">
+        <is>
+          <t>Galerie</t>
+        </is>
+      </c>
+      <c r="E964" s="4" t="n"/>
+      <c r="F964" s="3" t="n"/>
+      <c r="G964" s="4" t="n"/>
+      <c r="H964" s="4" t="n"/>
     </row>
     <row r="965">
-      <c r="A965" s="2" t="inlineStr">
-        <is>
-          <t>BA04-02</t>
-        </is>
-      </c>
-      <c r="B965" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C965" s="2" t="inlineStr">
+      <c r="A965" s="4" t="inlineStr">
+        <is>
+          <t>BA03-14</t>
+        </is>
+      </c>
+      <c r="B965" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C965" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D965" s="2" t="inlineStr">
-        <is>
-          <t>Gruppenraum 4</t>
-        </is>
-      </c>
-      <c r="E965" s="2" t="inlineStr">
-        <is>
-          <t>Holzkiste Obstkistenoptik</t>
-        </is>
-      </c>
-      <c r="F965" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G965" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H965" s="2" t="n"/>
+      <c r="D965" s="4" t="inlineStr">
+        <is>
+          <t>Galerie</t>
+        </is>
+      </c>
+      <c r="E965" s="4" t="n"/>
+      <c r="F965" s="3" t="n"/>
+      <c r="G965" s="4" t="n"/>
+      <c r="H965" s="4" t="n"/>
     </row>
     <row r="966">
       <c r="A966" s="4" t="inlineStr">
         <is>
-          <t>BA04-03</t>
+          <t>BA03-15</t>
         </is>
       </c>
       <c r="B966" s="4" t="inlineStr">
@@ -27092,7 +27152,7 @@
       </c>
       <c r="D966" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Galerie</t>
         </is>
       </c>
       <c r="E966" s="4" t="n"/>
@@ -27101,61 +27161,81 @@
       <c r="H966" s="4" t="n"/>
     </row>
     <row r="967">
-      <c r="A967" s="4" t="inlineStr">
-        <is>
-          <t>BA04-04</t>
-        </is>
-      </c>
-      <c r="B967" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C967" s="4" t="inlineStr">
+      <c r="A967" s="2" t="inlineStr">
+        <is>
+          <t>BA04-01</t>
+        </is>
+      </c>
+      <c r="B967" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C967" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D967" s="4" t="inlineStr">
+      <c r="D967" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 4</t>
         </is>
       </c>
-      <c r="E967" s="4" t="n"/>
-      <c r="F967" s="3" t="n"/>
-      <c r="G967" s="4" t="n"/>
-      <c r="H967" s="4" t="n"/>
+      <c r="E967" s="2" t="inlineStr">
+        <is>
+          <t>Rattankörbe 8 Stück</t>
+        </is>
+      </c>
+      <c r="F967" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G967" s="2" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="H967" s="2" t="n"/>
     </row>
     <row r="968">
-      <c r="A968" s="4" t="inlineStr">
-        <is>
-          <t>BA04-05</t>
-        </is>
-      </c>
-      <c r="B968" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C968" s="4" t="inlineStr">
+      <c r="A968" s="2" t="inlineStr">
+        <is>
+          <t>BA04-02</t>
+        </is>
+      </c>
+      <c r="B968" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C968" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D968" s="4" t="inlineStr">
+      <c r="D968" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 4</t>
         </is>
       </c>
-      <c r="E968" s="4" t="n"/>
-      <c r="F968" s="3" t="n"/>
-      <c r="G968" s="4" t="n"/>
-      <c r="H968" s="4" t="n"/>
+      <c r="E968" s="2" t="inlineStr">
+        <is>
+          <t>Holzkiste Obstkistenoptik</t>
+        </is>
+      </c>
+      <c r="F968" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G968" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H968" s="2" t="n"/>
     </row>
     <row r="969">
       <c r="A969" s="4" t="inlineStr">
         <is>
-          <t>BA04-06</t>
+          <t>BA04-03</t>
         </is>
       </c>
       <c r="B969" s="4" t="inlineStr">
@@ -27181,7 +27261,7 @@
     <row r="970">
       <c r="A970" s="4" t="inlineStr">
         <is>
-          <t>BA04-07</t>
+          <t>BA04-04</t>
         </is>
       </c>
       <c r="B970" s="4" t="inlineStr">
@@ -27207,7 +27287,7 @@
     <row r="971">
       <c r="A971" s="4" t="inlineStr">
         <is>
-          <t>BA04-08</t>
+          <t>BA04-05</t>
         </is>
       </c>
       <c r="B971" s="4" t="inlineStr">
@@ -27233,7 +27313,7 @@
     <row r="972">
       <c r="A972" s="4" t="inlineStr">
         <is>
-          <t>BA04-09</t>
+          <t>BA04-06</t>
         </is>
       </c>
       <c r="B972" s="4" t="inlineStr">
@@ -27259,7 +27339,7 @@
     <row r="973">
       <c r="A973" s="4" t="inlineStr">
         <is>
-          <t>BA04-10</t>
+          <t>BA04-07</t>
         </is>
       </c>
       <c r="B973" s="4" t="inlineStr">
@@ -27285,7 +27365,7 @@
     <row r="974">
       <c r="A974" s="4" t="inlineStr">
         <is>
-          <t>BA04-11</t>
+          <t>BA04-08</t>
         </is>
       </c>
       <c r="B974" s="4" t="inlineStr">
@@ -27311,7 +27391,7 @@
     <row r="975">
       <c r="A975" s="4" t="inlineStr">
         <is>
-          <t>BA04-12</t>
+          <t>BA04-09</t>
         </is>
       </c>
       <c r="B975" s="4" t="inlineStr">
@@ -27337,7 +27417,7 @@
     <row r="976">
       <c r="A976" s="4" t="inlineStr">
         <is>
-          <t>BA04-13</t>
+          <t>BA04-10</t>
         </is>
       </c>
       <c r="B976" s="4" t="inlineStr">
@@ -27363,7 +27443,7 @@
     <row r="977">
       <c r="A977" s="4" t="inlineStr">
         <is>
-          <t>BA04-14</t>
+          <t>BA04-11</t>
         </is>
       </c>
       <c r="B977" s="4" t="inlineStr">
@@ -27389,7 +27469,7 @@
     <row r="978">
       <c r="A978" s="4" t="inlineStr">
         <is>
-          <t>BA04-15</t>
+          <t>BA04-12</t>
         </is>
       </c>
       <c r="B978" s="4" t="inlineStr">
@@ -27415,7 +27495,7 @@
     <row r="979">
       <c r="A979" s="4" t="inlineStr">
         <is>
-          <t>BA04-16</t>
+          <t>BA04-13</t>
         </is>
       </c>
       <c r="B979" s="4" t="inlineStr">
@@ -27441,7 +27521,7 @@
     <row r="980">
       <c r="A980" s="4" t="inlineStr">
         <is>
-          <t>BA04-17</t>
+          <t>BA04-14</t>
         </is>
       </c>
       <c r="B980" s="4" t="inlineStr">
@@ -27467,7 +27547,7 @@
     <row r="981">
       <c r="A981" s="4" t="inlineStr">
         <is>
-          <t>BA04-18</t>
+          <t>BA04-15</t>
         </is>
       </c>
       <c r="B981" s="4" t="inlineStr">
@@ -27493,7 +27573,7 @@
     <row r="982">
       <c r="A982" s="4" t="inlineStr">
         <is>
-          <t>BA04-19</t>
+          <t>BA04-16</t>
         </is>
       </c>
       <c r="B982" s="4" t="inlineStr">
@@ -27519,7 +27599,7 @@
     <row r="983">
       <c r="A983" s="4" t="inlineStr">
         <is>
-          <t>BA04-20</t>
+          <t>BA04-17</t>
         </is>
       </c>
       <c r="B983" s="4" t="inlineStr">
@@ -27545,7 +27625,7 @@
     <row r="984">
       <c r="A984" s="4" t="inlineStr">
         <is>
-          <t>BA04-21</t>
+          <t>BA04-18</t>
         </is>
       </c>
       <c r="B984" s="4" t="inlineStr">
@@ -27571,7 +27651,7 @@
     <row r="985">
       <c r="A985" s="4" t="inlineStr">
         <is>
-          <t>BA04-22</t>
+          <t>BA04-19</t>
         </is>
       </c>
       <c r="B985" s="4" t="inlineStr">
@@ -27597,7 +27677,7 @@
     <row r="986">
       <c r="A986" s="4" t="inlineStr">
         <is>
-          <t>BA04-23</t>
+          <t>BA04-20</t>
         </is>
       </c>
       <c r="B986" s="4" t="inlineStr">
@@ -27623,7 +27703,7 @@
     <row r="987">
       <c r="A987" s="4" t="inlineStr">
         <is>
-          <t>BA04-24</t>
+          <t>BA04-21</t>
         </is>
       </c>
       <c r="B987" s="4" t="inlineStr">
@@ -27649,7 +27729,7 @@
     <row r="988">
       <c r="A988" s="4" t="inlineStr">
         <is>
-          <t>BA04-25</t>
+          <t>BA04-22</t>
         </is>
       </c>
       <c r="B988" s="4" t="inlineStr">
@@ -27675,7 +27755,7 @@
     <row r="989">
       <c r="A989" s="4" t="inlineStr">
         <is>
-          <t>BA05-01</t>
+          <t>BA04-23</t>
         </is>
       </c>
       <c r="B989" s="4" t="inlineStr">
@@ -27690,7 +27770,7 @@
       </c>
       <c r="D989" s="4" t="inlineStr">
         <is>
-          <t>Turnraum</t>
+          <t>Gruppenraum 4</t>
         </is>
       </c>
       <c r="E989" s="4" t="n"/>
@@ -27701,7 +27781,7 @@
     <row r="990">
       <c r="A990" s="4" t="inlineStr">
         <is>
-          <t>BA05-02</t>
+          <t>BA04-24</t>
         </is>
       </c>
       <c r="B990" s="4" t="inlineStr">
@@ -27716,7 +27796,7 @@
       </c>
       <c r="D990" s="4" t="inlineStr">
         <is>
-          <t>Turnraum</t>
+          <t>Gruppenraum 4</t>
         </is>
       </c>
       <c r="E990" s="4" t="n"/>
@@ -27727,7 +27807,7 @@
     <row r="991">
       <c r="A991" s="4" t="inlineStr">
         <is>
-          <t>BA05-03</t>
+          <t>BA04-25</t>
         </is>
       </c>
       <c r="B991" s="4" t="inlineStr">
@@ -27742,7 +27822,7 @@
       </c>
       <c r="D991" s="4" t="inlineStr">
         <is>
-          <t>Turnraum</t>
+          <t>Gruppenraum 4</t>
         </is>
       </c>
       <c r="E991" s="4" t="n"/>
@@ -27753,7 +27833,7 @@
     <row r="992">
       <c r="A992" s="4" t="inlineStr">
         <is>
-          <t>BA05-04</t>
+          <t>BA05-01</t>
         </is>
       </c>
       <c r="B992" s="4" t="inlineStr">
@@ -27779,7 +27859,7 @@
     <row r="993">
       <c r="A993" s="4" t="inlineStr">
         <is>
-          <t>BA05-05</t>
+          <t>BA05-02</t>
         </is>
       </c>
       <c r="B993" s="4" t="inlineStr">
@@ -27805,7 +27885,7 @@
     <row r="994">
       <c r="A994" s="4" t="inlineStr">
         <is>
-          <t>BA05-06</t>
+          <t>BA05-03</t>
         </is>
       </c>
       <c r="B994" s="4" t="inlineStr">
@@ -27831,7 +27911,7 @@
     <row r="995">
       <c r="A995" s="4" t="inlineStr">
         <is>
-          <t>BA05-07</t>
+          <t>BA05-04</t>
         </is>
       </c>
       <c r="B995" s="4" t="inlineStr">
@@ -27857,7 +27937,7 @@
     <row r="996">
       <c r="A996" s="4" t="inlineStr">
         <is>
-          <t>BA05-08</t>
+          <t>BA05-05</t>
         </is>
       </c>
       <c r="B996" s="4" t="inlineStr">
@@ -27883,7 +27963,7 @@
     <row r="997">
       <c r="A997" s="4" t="inlineStr">
         <is>
-          <t>BA05-09</t>
+          <t>BA05-06</t>
         </is>
       </c>
       <c r="B997" s="4" t="inlineStr">
@@ -27909,7 +27989,7 @@
     <row r="998">
       <c r="A998" s="4" t="inlineStr">
         <is>
-          <t>BA05-10</t>
+          <t>BA05-07</t>
         </is>
       </c>
       <c r="B998" s="4" t="inlineStr">
@@ -27935,7 +28015,7 @@
     <row r="999">
       <c r="A999" s="4" t="inlineStr">
         <is>
-          <t>BA05-11</t>
+          <t>BA05-08</t>
         </is>
       </c>
       <c r="B999" s="4" t="inlineStr">
@@ -27961,7 +28041,7 @@
     <row r="1000">
       <c r="A1000" s="4" t="inlineStr">
         <is>
-          <t>BA05-12</t>
+          <t>BA05-09</t>
         </is>
       </c>
       <c r="B1000" s="4" t="inlineStr">
@@ -27987,7 +28067,7 @@
     <row r="1001">
       <c r="A1001" s="4" t="inlineStr">
         <is>
-          <t>BA05-13</t>
+          <t>BA05-10</t>
         </is>
       </c>
       <c r="B1001" s="4" t="inlineStr">
@@ -28013,7 +28093,7 @@
     <row r="1002">
       <c r="A1002" s="4" t="inlineStr">
         <is>
-          <t>BA05-14</t>
+          <t>BA05-11</t>
         </is>
       </c>
       <c r="B1002" s="4" t="inlineStr">
@@ -28039,7 +28119,7 @@
     <row r="1003">
       <c r="A1003" s="4" t="inlineStr">
         <is>
-          <t>BA05-15</t>
+          <t>BA05-12</t>
         </is>
       </c>
       <c r="B1003" s="4" t="inlineStr">
@@ -28065,7 +28145,7 @@
     <row r="1004">
       <c r="A1004" s="4" t="inlineStr">
         <is>
-          <t>BA05-16</t>
+          <t>BA05-13</t>
         </is>
       </c>
       <c r="B1004" s="4" t="inlineStr">
@@ -28091,7 +28171,7 @@
     <row r="1005">
       <c r="A1005" s="4" t="inlineStr">
         <is>
-          <t>BA05-17</t>
+          <t>BA05-14</t>
         </is>
       </c>
       <c r="B1005" s="4" t="inlineStr">
@@ -28117,7 +28197,7 @@
     <row r="1006">
       <c r="A1006" s="4" t="inlineStr">
         <is>
-          <t>BA05-18</t>
+          <t>BA05-15</t>
         </is>
       </c>
       <c r="B1006" s="4" t="inlineStr">
@@ -28143,7 +28223,7 @@
     <row r="1007">
       <c r="A1007" s="4" t="inlineStr">
         <is>
-          <t>BA05-19</t>
+          <t>BA05-16</t>
         </is>
       </c>
       <c r="B1007" s="4" t="inlineStr">
@@ -28169,7 +28249,7 @@
     <row r="1008">
       <c r="A1008" s="4" t="inlineStr">
         <is>
-          <t>BA05-20</t>
+          <t>BA05-17</t>
         </is>
       </c>
       <c r="B1008" s="4" t="inlineStr">
@@ -28195,7 +28275,7 @@
     <row r="1009">
       <c r="A1009" s="4" t="inlineStr">
         <is>
-          <t>BA05-21</t>
+          <t>BA05-18</t>
         </is>
       </c>
       <c r="B1009" s="4" t="inlineStr">
@@ -28221,7 +28301,7 @@
     <row r="1010">
       <c r="A1010" s="4" t="inlineStr">
         <is>
-          <t>BA05-22</t>
+          <t>BA05-19</t>
         </is>
       </c>
       <c r="B1010" s="4" t="inlineStr">
@@ -28247,7 +28327,7 @@
     <row r="1011">
       <c r="A1011" s="4" t="inlineStr">
         <is>
-          <t>BA05-23</t>
+          <t>BA05-20</t>
         </is>
       </c>
       <c r="B1011" s="4" t="inlineStr">
@@ -28273,7 +28353,7 @@
     <row r="1012">
       <c r="A1012" s="4" t="inlineStr">
         <is>
-          <t>BA05-24</t>
+          <t>BA05-21</t>
         </is>
       </c>
       <c r="B1012" s="4" t="inlineStr">
@@ -28299,7 +28379,7 @@
     <row r="1013">
       <c r="A1013" s="4" t="inlineStr">
         <is>
-          <t>BA05-25</t>
+          <t>BA05-22</t>
         </is>
       </c>
       <c r="B1013" s="4" t="inlineStr">
@@ -28325,7 +28405,7 @@
     <row r="1014">
       <c r="A1014" s="4" t="inlineStr">
         <is>
-          <t>BA05-26</t>
+          <t>BA05-23</t>
         </is>
       </c>
       <c r="B1014" s="4" t="inlineStr">
@@ -28351,7 +28431,7 @@
     <row r="1015">
       <c r="A1015" s="4" t="inlineStr">
         <is>
-          <t>BA05-27</t>
+          <t>BA05-24</t>
         </is>
       </c>
       <c r="B1015" s="4" t="inlineStr">
@@ -28377,7 +28457,7 @@
     <row r="1016">
       <c r="A1016" s="4" t="inlineStr">
         <is>
-          <t>BA05-28</t>
+          <t>BA05-25</t>
         </is>
       </c>
       <c r="B1016" s="4" t="inlineStr">
@@ -28403,7 +28483,7 @@
     <row r="1017">
       <c r="A1017" s="4" t="inlineStr">
         <is>
-          <t>BA05-29</t>
+          <t>BA05-26</t>
         </is>
       </c>
       <c r="B1017" s="4" t="inlineStr">
@@ -28429,7 +28509,7 @@
     <row r="1018">
       <c r="A1018" s="4" t="inlineStr">
         <is>
-          <t>BA05-30</t>
+          <t>BA05-27</t>
         </is>
       </c>
       <c r="B1018" s="4" t="inlineStr">
@@ -28455,7 +28535,7 @@
     <row r="1019">
       <c r="A1019" s="4" t="inlineStr">
         <is>
-          <t>BA05-31</t>
+          <t>BA05-28</t>
         </is>
       </c>
       <c r="B1019" s="4" t="inlineStr">
@@ -28481,7 +28561,7 @@
     <row r="1020">
       <c r="A1020" s="4" t="inlineStr">
         <is>
-          <t>BA05-32</t>
+          <t>BA05-29</t>
         </is>
       </c>
       <c r="B1020" s="4" t="inlineStr">
@@ -28507,7 +28587,7 @@
     <row r="1021">
       <c r="A1021" s="4" t="inlineStr">
         <is>
-          <t>BA05-33</t>
+          <t>BA05-30</t>
         </is>
       </c>
       <c r="B1021" s="4" t="inlineStr">
@@ -28533,7 +28613,7 @@
     <row r="1022">
       <c r="A1022" s="4" t="inlineStr">
         <is>
-          <t>BA05-34</t>
+          <t>BA05-31</t>
         </is>
       </c>
       <c r="B1022" s="4" t="inlineStr">
@@ -28559,7 +28639,7 @@
     <row r="1023">
       <c r="A1023" s="4" t="inlineStr">
         <is>
-          <t>BA05-35</t>
+          <t>BA05-32</t>
         </is>
       </c>
       <c r="B1023" s="4" t="inlineStr">
@@ -28585,7 +28665,7 @@
     <row r="1024">
       <c r="A1024" s="4" t="inlineStr">
         <is>
-          <t>BA05-36</t>
+          <t>BA05-33</t>
         </is>
       </c>
       <c r="B1024" s="4" t="inlineStr">
@@ -28611,7 +28691,7 @@
     <row r="1025">
       <c r="A1025" s="4" t="inlineStr">
         <is>
-          <t>BA05-37</t>
+          <t>BA05-34</t>
         </is>
       </c>
       <c r="B1025" s="4" t="inlineStr">
@@ -28637,7 +28717,7 @@
     <row r="1026">
       <c r="A1026" s="4" t="inlineStr">
         <is>
-          <t>BA05-38</t>
+          <t>BA05-35</t>
         </is>
       </c>
       <c r="B1026" s="4" t="inlineStr">
@@ -28663,7 +28743,7 @@
     <row r="1027">
       <c r="A1027" s="4" t="inlineStr">
         <is>
-          <t>BA05-39</t>
+          <t>BA05-36</t>
         </is>
       </c>
       <c r="B1027" s="4" t="inlineStr">
@@ -28689,7 +28769,7 @@
     <row r="1028">
       <c r="A1028" s="4" t="inlineStr">
         <is>
-          <t>BA05-40</t>
+          <t>BA05-37</t>
         </is>
       </c>
       <c r="B1028" s="4" t="inlineStr">
@@ -28715,7 +28795,7 @@
     <row r="1029">
       <c r="A1029" s="4" t="inlineStr">
         <is>
-          <t>BA06-01</t>
+          <t>BA05-38</t>
         </is>
       </c>
       <c r="B1029" s="4" t="inlineStr">
@@ -28730,7 +28810,7 @@
       </c>
       <c r="D1029" s="4" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Turnraum</t>
         </is>
       </c>
       <c r="E1029" s="4" t="n"/>
@@ -28741,7 +28821,7 @@
     <row r="1030">
       <c r="A1030" s="4" t="inlineStr">
         <is>
-          <t>BA06-02</t>
+          <t>BA05-39</t>
         </is>
       </c>
       <c r="B1030" s="4" t="inlineStr">
@@ -28756,7 +28836,7 @@
       </c>
       <c r="D1030" s="4" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Turnraum</t>
         </is>
       </c>
       <c r="E1030" s="4" t="n"/>
@@ -28767,7 +28847,7 @@
     <row r="1031">
       <c r="A1031" s="4" t="inlineStr">
         <is>
-          <t>BA06-03</t>
+          <t>BA05-40</t>
         </is>
       </c>
       <c r="B1031" s="4" t="inlineStr">
@@ -28782,7 +28862,7 @@
       </c>
       <c r="D1031" s="4" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Turnraum</t>
         </is>
       </c>
       <c r="E1031" s="4" t="n"/>
@@ -28793,7 +28873,7 @@
     <row r="1032">
       <c r="A1032" s="4" t="inlineStr">
         <is>
-          <t>BA06-04</t>
+          <t>BA06-01</t>
         </is>
       </c>
       <c r="B1032" s="4" t="inlineStr">
@@ -28819,7 +28899,7 @@
     <row r="1033">
       <c r="A1033" s="4" t="inlineStr">
         <is>
-          <t>BA06-05</t>
+          <t>BA06-02</t>
         </is>
       </c>
       <c r="B1033" s="4" t="inlineStr">
@@ -28845,7 +28925,7 @@
     <row r="1034">
       <c r="A1034" s="4" t="inlineStr">
         <is>
-          <t>BA06-06</t>
+          <t>BA06-03</t>
         </is>
       </c>
       <c r="B1034" s="4" t="inlineStr">
@@ -28871,7 +28951,7 @@
     <row r="1035">
       <c r="A1035" s="4" t="inlineStr">
         <is>
-          <t>BA06-07</t>
+          <t>BA06-04</t>
         </is>
       </c>
       <c r="B1035" s="4" t="inlineStr">
@@ -28897,7 +28977,7 @@
     <row r="1036">
       <c r="A1036" s="4" t="inlineStr">
         <is>
-          <t>BA06-08</t>
+          <t>BA06-05</t>
         </is>
       </c>
       <c r="B1036" s="4" t="inlineStr">
@@ -28923,7 +29003,7 @@
     <row r="1037">
       <c r="A1037" s="4" t="inlineStr">
         <is>
-          <t>BA06-09</t>
+          <t>BA06-06</t>
         </is>
       </c>
       <c r="B1037" s="4" t="inlineStr">
@@ -28949,7 +29029,7 @@
     <row r="1038">
       <c r="A1038" s="4" t="inlineStr">
         <is>
-          <t>BA06-10</t>
+          <t>BA06-07</t>
         </is>
       </c>
       <c r="B1038" s="4" t="inlineStr">
@@ -28975,7 +29055,7 @@
     <row r="1039">
       <c r="A1039" s="4" t="inlineStr">
         <is>
-          <t>BA06-11</t>
+          <t>BA06-08</t>
         </is>
       </c>
       <c r="B1039" s="4" t="inlineStr">
@@ -29001,7 +29081,7 @@
     <row r="1040">
       <c r="A1040" s="4" t="inlineStr">
         <is>
-          <t>BA06-12</t>
+          <t>BA06-09</t>
         </is>
       </c>
       <c r="B1040" s="4" t="inlineStr">
@@ -29027,7 +29107,7 @@
     <row r="1041">
       <c r="A1041" s="4" t="inlineStr">
         <is>
-          <t>BA06-13</t>
+          <t>BA06-10</t>
         </is>
       </c>
       <c r="B1041" s="4" t="inlineStr">
@@ -29053,7 +29133,7 @@
     <row r="1042">
       <c r="A1042" s="4" t="inlineStr">
         <is>
-          <t>BA06-14</t>
+          <t>BA06-11</t>
         </is>
       </c>
       <c r="B1042" s="4" t="inlineStr">
@@ -29079,7 +29159,7 @@
     <row r="1043">
       <c r="A1043" s="4" t="inlineStr">
         <is>
-          <t>BA06-15</t>
+          <t>BA06-12</t>
         </is>
       </c>
       <c r="B1043" s="4" t="inlineStr">
@@ -29105,7 +29185,7 @@
     <row r="1044">
       <c r="A1044" s="4" t="inlineStr">
         <is>
-          <t>BA07-01</t>
+          <t>BA06-13</t>
         </is>
       </c>
       <c r="B1044" s="4" t="inlineStr">
@@ -29120,7 +29200,7 @@
       </c>
       <c r="D1044" s="4" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Material / Turnraum</t>
         </is>
       </c>
       <c r="E1044" s="4" t="n"/>
@@ -29131,7 +29211,7 @@
     <row r="1045">
       <c r="A1045" s="4" t="inlineStr">
         <is>
-          <t>BA07-02</t>
+          <t>BA06-14</t>
         </is>
       </c>
       <c r="B1045" s="4" t="inlineStr">
@@ -29146,7 +29226,7 @@
       </c>
       <c r="D1045" s="4" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Material / Turnraum</t>
         </is>
       </c>
       <c r="E1045" s="4" t="n"/>
@@ -29157,7 +29237,7 @@
     <row r="1046">
       <c r="A1046" s="4" t="inlineStr">
         <is>
-          <t>BA07-03</t>
+          <t>BA06-15</t>
         </is>
       </c>
       <c r="B1046" s="4" t="inlineStr">
@@ -29172,7 +29252,7 @@
       </c>
       <c r="D1046" s="4" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Material / Turnraum</t>
         </is>
       </c>
       <c r="E1046" s="4" t="n"/>
@@ -29183,7 +29263,7 @@
     <row r="1047">
       <c r="A1047" s="4" t="inlineStr">
         <is>
-          <t>BA07-04</t>
+          <t>BA07-01</t>
         </is>
       </c>
       <c r="B1047" s="4" t="inlineStr">
@@ -29209,7 +29289,7 @@
     <row r="1048">
       <c r="A1048" s="4" t="inlineStr">
         <is>
-          <t>BA07-05</t>
+          <t>BA07-02</t>
         </is>
       </c>
       <c r="B1048" s="4" t="inlineStr">
@@ -29235,7 +29315,7 @@
     <row r="1049">
       <c r="A1049" s="4" t="inlineStr">
         <is>
-          <t>BA07-06</t>
+          <t>BA07-03</t>
         </is>
       </c>
       <c r="B1049" s="4" t="inlineStr">
@@ -29261,7 +29341,7 @@
     <row r="1050">
       <c r="A1050" s="4" t="inlineStr">
         <is>
-          <t>BA07-07</t>
+          <t>BA07-04</t>
         </is>
       </c>
       <c r="B1050" s="4" t="inlineStr">
@@ -29287,7 +29367,7 @@
     <row r="1051">
       <c r="A1051" s="4" t="inlineStr">
         <is>
-          <t>BA07-08</t>
+          <t>BA07-05</t>
         </is>
       </c>
       <c r="B1051" s="4" t="inlineStr">
@@ -29313,7 +29393,7 @@
     <row r="1052">
       <c r="A1052" s="4" t="inlineStr">
         <is>
-          <t>BA07-09</t>
+          <t>BA07-06</t>
         </is>
       </c>
       <c r="B1052" s="4" t="inlineStr">
@@ -29339,7 +29419,7 @@
     <row r="1053">
       <c r="A1053" s="4" t="inlineStr">
         <is>
-          <t>BA07-10</t>
+          <t>BA07-07</t>
         </is>
       </c>
       <c r="B1053" s="4" t="inlineStr">
@@ -29365,7 +29445,7 @@
     <row r="1054">
       <c r="A1054" s="4" t="inlineStr">
         <is>
-          <t>BA07-11</t>
+          <t>BA07-08</t>
         </is>
       </c>
       <c r="B1054" s="4" t="inlineStr">
@@ -29391,7 +29471,7 @@
     <row r="1055">
       <c r="A1055" s="4" t="inlineStr">
         <is>
-          <t>BA07-12</t>
+          <t>BA07-09</t>
         </is>
       </c>
       <c r="B1055" s="4" t="inlineStr">
@@ -29417,7 +29497,7 @@
     <row r="1056">
       <c r="A1056" s="4" t="inlineStr">
         <is>
-          <t>BA07-13</t>
+          <t>BA07-10</t>
         </is>
       </c>
       <c r="B1056" s="4" t="inlineStr">
@@ -29443,7 +29523,7 @@
     <row r="1057">
       <c r="A1057" s="4" t="inlineStr">
         <is>
-          <t>BA07-14</t>
+          <t>BA07-11</t>
         </is>
       </c>
       <c r="B1057" s="4" t="inlineStr">
@@ -29469,7 +29549,7 @@
     <row r="1058">
       <c r="A1058" s="4" t="inlineStr">
         <is>
-          <t>BA07-15</t>
+          <t>BA07-12</t>
         </is>
       </c>
       <c r="B1058" s="4" t="inlineStr">
@@ -29493,117 +29573,87 @@
       <c r="H1058" s="4" t="n"/>
     </row>
     <row r="1059">
-      <c r="A1059" s="2" t="inlineStr">
-        <is>
-          <t>BA08-01</t>
-        </is>
-      </c>
-      <c r="B1059" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1059" s="2" t="inlineStr">
+      <c r="A1059" s="4" t="inlineStr">
+        <is>
+          <t>BA07-13</t>
+        </is>
+      </c>
+      <c r="B1059" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1059" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1059" s="2" t="inlineStr">
-        <is>
-          <t>Atelier</t>
-        </is>
-      </c>
-      <c r="E1059" s="2" t="inlineStr">
-        <is>
-          <t>Konvolut Mal- und Bastelfarben</t>
-        </is>
-      </c>
-      <c r="F1059" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1059" s="2" t="inlineStr">
-        <is>
-          <t>Konvolut</t>
-        </is>
-      </c>
-      <c r="H1059" s="2" t="n"/>
+      <c r="D1059" s="4" t="inlineStr">
+        <is>
+          <t>Klassenzimmer</t>
+        </is>
+      </c>
+      <c r="E1059" s="4" t="n"/>
+      <c r="F1059" s="3" t="n"/>
+      <c r="G1059" s="4" t="n"/>
+      <c r="H1059" s="4" t="n"/>
     </row>
     <row r="1060">
-      <c r="A1060" s="2" t="inlineStr">
-        <is>
-          <t>BA08-02</t>
-        </is>
-      </c>
-      <c r="B1060" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1060" s="2" t="inlineStr">
+      <c r="A1060" s="4" t="inlineStr">
+        <is>
+          <t>BA07-14</t>
+        </is>
+      </c>
+      <c r="B1060" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1060" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1060" s="2" t="inlineStr">
-        <is>
-          <t>Atelier</t>
-        </is>
-      </c>
-      <c r="E1060" s="2" t="inlineStr">
-        <is>
-          <t>Acrylfarben-Sortiment im Holzkasten</t>
-        </is>
-      </c>
-      <c r="F1060" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1060" s="2" t="inlineStr">
-        <is>
-          <t>Konvolut</t>
-        </is>
-      </c>
-      <c r="H1060" s="2" t="n"/>
+      <c r="D1060" s="4" t="inlineStr">
+        <is>
+          <t>Klassenzimmer</t>
+        </is>
+      </c>
+      <c r="E1060" s="4" t="n"/>
+      <c r="F1060" s="3" t="n"/>
+      <c r="G1060" s="4" t="n"/>
+      <c r="H1060" s="4" t="n"/>
     </row>
     <row r="1061">
-      <c r="A1061" s="2" t="inlineStr">
-        <is>
-          <t>BA08-03</t>
-        </is>
-      </c>
-      <c r="B1061" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1061" s="2" t="inlineStr">
+      <c r="A1061" s="4" t="inlineStr">
+        <is>
+          <t>BA07-15</t>
+        </is>
+      </c>
+      <c r="B1061" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1061" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1061" s="2" t="inlineStr">
-        <is>
-          <t>Atelier</t>
-        </is>
-      </c>
-      <c r="E1061" s="2" t="inlineStr">
-        <is>
-          <t>Konvolut Bastelmaterial</t>
-        </is>
-      </c>
-      <c r="F1061" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1061" s="2" t="inlineStr">
-        <is>
-          <t>Konvolut</t>
-        </is>
-      </c>
-      <c r="H1061" s="2" t="n"/>
+      <c r="D1061" s="4" t="inlineStr">
+        <is>
+          <t>Klassenzimmer</t>
+        </is>
+      </c>
+      <c r="E1061" s="4" t="n"/>
+      <c r="F1061" s="3" t="n"/>
+      <c r="G1061" s="4" t="n"/>
+      <c r="H1061" s="4" t="n"/>
     </row>
     <row r="1062">
       <c r="A1062" s="2" t="inlineStr">
         <is>
-          <t>BA08-04</t>
+          <t>BA08-01</t>
         </is>
       </c>
       <c r="B1062" s="2" t="inlineStr">
@@ -29623,7 +29673,7 @@
       </c>
       <c r="E1062" s="2" t="inlineStr">
         <is>
-          <t>buntes Papier</t>
+          <t>Konvolut Mal- und Bastelfarben</t>
         </is>
       </c>
       <c r="F1062" s="3" t="n">
@@ -29637,87 +29687,117 @@
       <c r="H1062" s="2" t="n"/>
     </row>
     <row r="1063">
-      <c r="A1063" s="4" t="inlineStr">
-        <is>
-          <t>BA08-05</t>
-        </is>
-      </c>
-      <c r="B1063" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1063" s="4" t="inlineStr">
+      <c r="A1063" s="2" t="inlineStr">
+        <is>
+          <t>BA08-02</t>
+        </is>
+      </c>
+      <c r="B1063" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1063" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1063" s="4" t="inlineStr">
+      <c r="D1063" s="2" t="inlineStr">
         <is>
           <t>Atelier</t>
         </is>
       </c>
-      <c r="E1063" s="4" t="n"/>
-      <c r="F1063" s="3" t="n"/>
-      <c r="G1063" s="4" t="n"/>
-      <c r="H1063" s="4" t="n"/>
+      <c r="E1063" s="2" t="inlineStr">
+        <is>
+          <t>Acrylfarben-Sortiment im Holzkasten</t>
+        </is>
+      </c>
+      <c r="F1063" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1063" s="2" t="inlineStr">
+        <is>
+          <t>Konvolut</t>
+        </is>
+      </c>
+      <c r="H1063" s="2" t="n"/>
     </row>
     <row r="1064">
-      <c r="A1064" s="4" t="inlineStr">
-        <is>
-          <t>BA08-06</t>
-        </is>
-      </c>
-      <c r="B1064" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1064" s="4" t="inlineStr">
+      <c r="A1064" s="2" t="inlineStr">
+        <is>
+          <t>BA08-03</t>
+        </is>
+      </c>
+      <c r="B1064" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1064" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1064" s="4" t="inlineStr">
+      <c r="D1064" s="2" t="inlineStr">
         <is>
           <t>Atelier</t>
         </is>
       </c>
-      <c r="E1064" s="4" t="n"/>
-      <c r="F1064" s="3" t="n"/>
-      <c r="G1064" s="4" t="n"/>
-      <c r="H1064" s="4" t="n"/>
+      <c r="E1064" s="2" t="inlineStr">
+        <is>
+          <t>Konvolut Bastelmaterial</t>
+        </is>
+      </c>
+      <c r="F1064" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1064" s="2" t="inlineStr">
+        <is>
+          <t>Konvolut</t>
+        </is>
+      </c>
+      <c r="H1064" s="2" t="n"/>
     </row>
     <row r="1065">
-      <c r="A1065" s="4" t="inlineStr">
-        <is>
-          <t>BA08-07</t>
-        </is>
-      </c>
-      <c r="B1065" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1065" s="4" t="inlineStr">
+      <c r="A1065" s="2" t="inlineStr">
+        <is>
+          <t>BA08-04</t>
+        </is>
+      </c>
+      <c r="B1065" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1065" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1065" s="4" t="inlineStr">
+      <c r="D1065" s="2" t="inlineStr">
         <is>
           <t>Atelier</t>
         </is>
       </c>
-      <c r="E1065" s="4" t="n"/>
-      <c r="F1065" s="3" t="n"/>
-      <c r="G1065" s="4" t="n"/>
-      <c r="H1065" s="4" t="n"/>
+      <c r="E1065" s="2" t="inlineStr">
+        <is>
+          <t>buntes Papier</t>
+        </is>
+      </c>
+      <c r="F1065" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1065" s="2" t="inlineStr">
+        <is>
+          <t>Konvolut</t>
+        </is>
+      </c>
+      <c r="H1065" s="2" t="n"/>
     </row>
     <row r="1066">
       <c r="A1066" s="4" t="inlineStr">
         <is>
-          <t>BA08-08</t>
+          <t>BA08-05</t>
         </is>
       </c>
       <c r="B1066" s="4" t="inlineStr">
@@ -29743,7 +29823,7 @@
     <row r="1067">
       <c r="A1067" s="4" t="inlineStr">
         <is>
-          <t>BA08-09</t>
+          <t>BA08-06</t>
         </is>
       </c>
       <c r="B1067" s="4" t="inlineStr">
@@ -29769,7 +29849,7 @@
     <row r="1068">
       <c r="A1068" s="4" t="inlineStr">
         <is>
-          <t>BA08-10</t>
+          <t>BA08-07</t>
         </is>
       </c>
       <c r="B1068" s="4" t="inlineStr">
@@ -29795,7 +29875,7 @@
     <row r="1069">
       <c r="A1069" s="4" t="inlineStr">
         <is>
-          <t>BA08-11</t>
+          <t>BA08-08</t>
         </is>
       </c>
       <c r="B1069" s="4" t="inlineStr">
@@ -29821,7 +29901,7 @@
     <row r="1070">
       <c r="A1070" s="4" t="inlineStr">
         <is>
-          <t>BA08-12</t>
+          <t>BA08-09</t>
         </is>
       </c>
       <c r="B1070" s="4" t="inlineStr">
@@ -29847,7 +29927,7 @@
     <row r="1071">
       <c r="A1071" s="4" t="inlineStr">
         <is>
-          <t>BA08-13</t>
+          <t>BA08-10</t>
         </is>
       </c>
       <c r="B1071" s="4" t="inlineStr">
@@ -29873,7 +29953,7 @@
     <row r="1072">
       <c r="A1072" s="4" t="inlineStr">
         <is>
-          <t>BA08-14</t>
+          <t>BA08-11</t>
         </is>
       </c>
       <c r="B1072" s="4" t="inlineStr">
@@ -29899,7 +29979,7 @@
     <row r="1073">
       <c r="A1073" s="4" t="inlineStr">
         <is>
-          <t>BA08-15</t>
+          <t>BA08-12</t>
         </is>
       </c>
       <c r="B1073" s="4" t="inlineStr">
@@ -29925,7 +30005,7 @@
     <row r="1074">
       <c r="A1074" s="4" t="inlineStr">
         <is>
-          <t>BA08-16</t>
+          <t>BA08-13</t>
         </is>
       </c>
       <c r="B1074" s="4" t="inlineStr">
@@ -29951,7 +30031,7 @@
     <row r="1075">
       <c r="A1075" s="4" t="inlineStr">
         <is>
-          <t>BA08-17</t>
+          <t>BA08-14</t>
         </is>
       </c>
       <c r="B1075" s="4" t="inlineStr">
@@ -29977,7 +30057,7 @@
     <row r="1076">
       <c r="A1076" s="4" t="inlineStr">
         <is>
-          <t>BA08-18</t>
+          <t>BA08-15</t>
         </is>
       </c>
       <c r="B1076" s="4" t="inlineStr">
@@ -30003,7 +30083,7 @@
     <row r="1077">
       <c r="A1077" s="4" t="inlineStr">
         <is>
-          <t>BA08-19</t>
+          <t>BA08-16</t>
         </is>
       </c>
       <c r="B1077" s="4" t="inlineStr">
@@ -30029,7 +30109,7 @@
     <row r="1078">
       <c r="A1078" s="4" t="inlineStr">
         <is>
-          <t>BA08-20</t>
+          <t>BA08-17</t>
         </is>
       </c>
       <c r="B1078" s="4" t="inlineStr">
@@ -30055,7 +30135,7 @@
     <row r="1079">
       <c r="A1079" s="4" t="inlineStr">
         <is>
-          <t>BA08-21</t>
+          <t>BA08-18</t>
         </is>
       </c>
       <c r="B1079" s="4" t="inlineStr">
@@ -30081,7 +30161,7 @@
     <row r="1080">
       <c r="A1080" s="4" t="inlineStr">
         <is>
-          <t>BA08-22</t>
+          <t>BA08-19</t>
         </is>
       </c>
       <c r="B1080" s="4" t="inlineStr">
@@ -30107,7 +30187,7 @@
     <row r="1081">
       <c r="A1081" s="4" t="inlineStr">
         <is>
-          <t>BA08-23</t>
+          <t>BA08-20</t>
         </is>
       </c>
       <c r="B1081" s="4" t="inlineStr">
@@ -30133,7 +30213,7 @@
     <row r="1082">
       <c r="A1082" s="4" t="inlineStr">
         <is>
-          <t>BA08-24</t>
+          <t>BA08-21</t>
         </is>
       </c>
       <c r="B1082" s="4" t="inlineStr">
@@ -30159,7 +30239,7 @@
     <row r="1083">
       <c r="A1083" s="4" t="inlineStr">
         <is>
-          <t>BA08-25</t>
+          <t>BA08-22</t>
         </is>
       </c>
       <c r="B1083" s="4" t="inlineStr">
@@ -30183,117 +30263,87 @@
       <c r="H1083" s="4" t="n"/>
     </row>
     <row r="1084">
-      <c r="A1084" s="2" t="inlineStr">
-        <is>
-          <t>BA09-01</t>
-        </is>
-      </c>
-      <c r="B1084" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1084" s="2" t="inlineStr">
+      <c r="A1084" s="4" t="inlineStr">
+        <is>
+          <t>BA08-23</t>
+        </is>
+      </c>
+      <c r="B1084" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1084" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1084" s="2" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="E1084" s="2" t="inlineStr">
-        <is>
-          <t>Deko Metallruten mit Pompons</t>
-        </is>
-      </c>
-      <c r="F1084" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1084" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1084" s="2" t="n"/>
+      <c r="D1084" s="4" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="E1084" s="4" t="n"/>
+      <c r="F1084" s="3" t="n"/>
+      <c r="G1084" s="4" t="n"/>
+      <c r="H1084" s="4" t="n"/>
     </row>
     <row r="1085">
-      <c r="A1085" s="2" t="inlineStr">
-        <is>
-          <t>BA09-02</t>
-        </is>
-      </c>
-      <c r="B1085" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1085" s="2" t="inlineStr">
+      <c r="A1085" s="4" t="inlineStr">
+        <is>
+          <t>BA08-24</t>
+        </is>
+      </c>
+      <c r="B1085" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1085" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1085" s="2" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="E1085" s="2" t="inlineStr">
-        <is>
-          <t>Elefantenfuß groß</t>
-        </is>
-      </c>
-      <c r="F1085" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1085" s="2" t="inlineStr">
-        <is>
-          <t>Set</t>
-        </is>
-      </c>
-      <c r="H1085" s="2" t="n"/>
+      <c r="D1085" s="4" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="E1085" s="4" t="n"/>
+      <c r="F1085" s="3" t="n"/>
+      <c r="G1085" s="4" t="n"/>
+      <c r="H1085" s="4" t="n"/>
     </row>
     <row r="1086">
-      <c r="A1086" s="2" t="inlineStr">
-        <is>
-          <t>BA09-03</t>
-        </is>
-      </c>
-      <c r="B1086" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1086" s="2" t="inlineStr">
+      <c r="A1086" s="4" t="inlineStr">
+        <is>
+          <t>BA08-25</t>
+        </is>
+      </c>
+      <c r="B1086" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1086" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1086" s="2" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="E1086" s="2" t="inlineStr">
-        <is>
-          <t>Werte-Rad</t>
-        </is>
-      </c>
-      <c r="F1086" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1086" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1086" s="2" t="n"/>
+      <c r="D1086" s="4" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="E1086" s="4" t="n"/>
+      <c r="F1086" s="3" t="n"/>
+      <c r="G1086" s="4" t="n"/>
+      <c r="H1086" s="4" t="n"/>
     </row>
     <row r="1087">
       <c r="A1087" s="2" t="inlineStr">
         <is>
-          <t>BA09-04</t>
+          <t>BA09-01</t>
         </is>
       </c>
       <c r="B1087" s="2" t="inlineStr">
@@ -30313,11 +30363,11 @@
       </c>
       <c r="E1087" s="2" t="inlineStr">
         <is>
-          <t>USM Haller Tisch</t>
+          <t>Deko Metallruten mit Pompons</t>
         </is>
       </c>
       <c r="F1087" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1087" s="2" t="inlineStr">
         <is>
@@ -30329,121 +30379,151 @@
     <row r="1088">
       <c r="A1088" s="2" t="inlineStr">
         <is>
+          <t>BA09-02</t>
+        </is>
+      </c>
+      <c r="B1088" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1088" s="2" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1088" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="E1088" s="2" t="inlineStr">
+        <is>
+          <t>Elefantenfuß groß</t>
+        </is>
+      </c>
+      <c r="F1088" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1088" s="2" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="H1088" s="2" t="n"/>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="2" t="inlineStr">
+        <is>
+          <t>BA09-03</t>
+        </is>
+      </c>
+      <c r="B1089" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1089" s="2" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1089" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="E1089" s="2" t="inlineStr">
+        <is>
+          <t>Werte-Rad</t>
+        </is>
+      </c>
+      <c r="F1089" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1089" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1089" s="2" t="n"/>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="2" t="inlineStr">
+        <is>
+          <t>BA09-04</t>
+        </is>
+      </c>
+      <c r="B1090" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1090" s="2" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1090" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="E1090" s="2" t="inlineStr">
+        <is>
+          <t>USM Haller Tisch</t>
+        </is>
+      </c>
+      <c r="F1090" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1090" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1090" s="2" t="n"/>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="2" t="inlineStr">
+        <is>
           <t>BA09-05</t>
         </is>
       </c>
-      <c r="B1088" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1088" s="2" t="inlineStr">
+      <c r="B1091" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1091" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1088" s="2" t="inlineStr">
+      <c r="D1091" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="E1088" s="2" t="inlineStr">
+      <c r="E1091" s="2" t="inlineStr">
         <is>
           <t>Kartell Masters Stuhl</t>
         </is>
       </c>
-      <c r="F1088" s="3" t="n">
+      <c r="F1091" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G1088" s="2" t="inlineStr">
+      <c r="G1091" s="2" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="H1088" s="2" t="n"/>
-    </row>
-    <row r="1089">
-      <c r="A1089" s="4" t="inlineStr">
-        <is>
-          <t>BA09-06</t>
-        </is>
-      </c>
-      <c r="B1089" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1089" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1089" s="4" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="E1089" s="4" t="n"/>
-      <c r="F1089" s="3" t="n"/>
-      <c r="G1089" s="4" t="n"/>
-      <c r="H1089" s="4" t="n"/>
-    </row>
-    <row r="1090">
-      <c r="A1090" s="4" t="inlineStr">
-        <is>
-          <t>BA09-07</t>
-        </is>
-      </c>
-      <c r="B1090" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1090" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1090" s="4" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="E1090" s="4" t="n"/>
-      <c r="F1090" s="3" t="n"/>
-      <c r="G1090" s="4" t="n"/>
-      <c r="H1090" s="4" t="n"/>
-    </row>
-    <row r="1091">
-      <c r="A1091" s="4" t="inlineStr">
-        <is>
-          <t>BA09-08</t>
-        </is>
-      </c>
-      <c r="B1091" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1091" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1091" s="4" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="E1091" s="4" t="n"/>
-      <c r="F1091" s="3" t="n"/>
-      <c r="G1091" s="4" t="n"/>
-      <c r="H1091" s="4" t="n"/>
+      <c r="H1091" s="2" t="n"/>
     </row>
     <row r="1092">
       <c r="A1092" s="4" t="inlineStr">
         <is>
-          <t>BA09-09</t>
+          <t>BA09-06</t>
         </is>
       </c>
       <c r="B1092" s="4" t="inlineStr">
@@ -30469,7 +30549,7 @@
     <row r="1093">
       <c r="A1093" s="4" t="inlineStr">
         <is>
-          <t>BA09-10</t>
+          <t>BA09-07</t>
         </is>
       </c>
       <c r="B1093" s="4" t="inlineStr">
@@ -30495,7 +30575,7 @@
     <row r="1094">
       <c r="A1094" s="4" t="inlineStr">
         <is>
-          <t>BA09-11</t>
+          <t>BA09-08</t>
         </is>
       </c>
       <c r="B1094" s="4" t="inlineStr">
@@ -30521,7 +30601,7 @@
     <row r="1095">
       <c r="A1095" s="4" t="inlineStr">
         <is>
-          <t>BA09-12</t>
+          <t>BA09-09</t>
         </is>
       </c>
       <c r="B1095" s="4" t="inlineStr">
@@ -30547,7 +30627,7 @@
     <row r="1096">
       <c r="A1096" s="4" t="inlineStr">
         <is>
-          <t>BA09-13</t>
+          <t>BA09-10</t>
         </is>
       </c>
       <c r="B1096" s="4" t="inlineStr">
@@ -30573,7 +30653,7 @@
     <row r="1097">
       <c r="A1097" s="4" t="inlineStr">
         <is>
-          <t>BA09-14</t>
+          <t>BA09-11</t>
         </is>
       </c>
       <c r="B1097" s="4" t="inlineStr">
@@ -30599,7 +30679,7 @@
     <row r="1098">
       <c r="A1098" s="4" t="inlineStr">
         <is>
-          <t>BA09-15</t>
+          <t>BA09-12</t>
         </is>
       </c>
       <c r="B1098" s="4" t="inlineStr">
@@ -30623,117 +30703,87 @@
       <c r="H1098" s="4" t="n"/>
     </row>
     <row r="1099">
-      <c r="A1099" s="2" t="inlineStr">
-        <is>
-          <t>BA10-01</t>
-        </is>
-      </c>
-      <c r="B1099" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1099" s="2" t="inlineStr">
+      <c r="A1099" s="4" t="inlineStr">
+        <is>
+          <t>BA09-13</t>
+        </is>
+      </c>
+      <c r="B1099" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1099" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1099" s="2" t="inlineStr">
-        <is>
-          <t>Ruhe- / Schlafraum</t>
-        </is>
-      </c>
-      <c r="E1099" s="2" t="inlineStr">
-        <is>
-          <t>Glastisch rund mit Chromgestell</t>
-        </is>
-      </c>
-      <c r="F1099" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1099" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1099" s="2" t="n"/>
+      <c r="D1099" s="4" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="E1099" s="4" t="n"/>
+      <c r="F1099" s="3" t="n"/>
+      <c r="G1099" s="4" t="n"/>
+      <c r="H1099" s="4" t="n"/>
     </row>
     <row r="1100">
-      <c r="A1100" s="2" t="inlineStr">
-        <is>
-          <t>BA10-02</t>
-        </is>
-      </c>
-      <c r="B1100" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1100" s="2" t="inlineStr">
+      <c r="A1100" s="4" t="inlineStr">
+        <is>
+          <t>BA09-14</t>
+        </is>
+      </c>
+      <c r="B1100" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1100" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1100" s="2" t="inlineStr">
-        <is>
-          <t>Ruhe- / Schlafraum</t>
-        </is>
-      </c>
-      <c r="E1100" s="2" t="inlineStr">
-        <is>
-          <t>Samtsofa bordeaux, 2-Sitzer</t>
-        </is>
-      </c>
-      <c r="F1100" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1100" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1100" s="2" t="n"/>
+      <c r="D1100" s="4" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="E1100" s="4" t="n"/>
+      <c r="F1100" s="3" t="n"/>
+      <c r="G1100" s="4" t="n"/>
+      <c r="H1100" s="4" t="n"/>
     </row>
     <row r="1101">
-      <c r="A1101" s="2" t="inlineStr">
-        <is>
-          <t>BA10-03</t>
-        </is>
-      </c>
-      <c r="B1101" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1101" s="2" t="inlineStr">
+      <c r="A1101" s="4" t="inlineStr">
+        <is>
+          <t>BA09-15</t>
+        </is>
+      </c>
+      <c r="B1101" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1101" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1101" s="2" t="inlineStr">
-        <is>
-          <t>Ruhe- / Schlafraum</t>
-        </is>
-      </c>
-      <c r="E1101" s="2" t="inlineStr">
-        <is>
-          <t>Sessel mit Bezug, weiß lackiert</t>
-        </is>
-      </c>
-      <c r="F1101" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1101" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1101" s="2" t="n"/>
+      <c r="D1101" s="4" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="E1101" s="4" t="n"/>
+      <c r="F1101" s="3" t="n"/>
+      <c r="G1101" s="4" t="n"/>
+      <c r="H1101" s="4" t="n"/>
     </row>
     <row r="1102">
       <c r="A1102" s="2" t="inlineStr">
         <is>
-          <t>BA10-04</t>
+          <t>BA10-01</t>
         </is>
       </c>
       <c r="B1102" s="2" t="inlineStr">
@@ -30753,11 +30803,11 @@
       </c>
       <c r="E1102" s="2" t="inlineStr">
         <is>
-          <t>Hocker grau mit Hairpin-Beinen</t>
+          <t>Glastisch rund mit Chromgestell</t>
         </is>
       </c>
       <c r="F1102" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1102" s="2" t="inlineStr">
         <is>
@@ -30769,7 +30819,7 @@
     <row r="1103">
       <c r="A1103" s="2" t="inlineStr">
         <is>
-          <t>BA10-05</t>
+          <t>BA10-02</t>
         </is>
       </c>
       <c r="B1103" s="2" t="inlineStr">
@@ -30789,7 +30839,7 @@
       </c>
       <c r="E1103" s="2" t="inlineStr">
         <is>
-          <t>Ohrensessel grau mit Kufengestell</t>
+          <t>Samtsofa bordeaux, 2-Sitzer</t>
         </is>
       </c>
       <c r="F1103" s="3" t="n">
@@ -30805,7 +30855,7 @@
     <row r="1104">
       <c r="A1104" s="2" t="inlineStr">
         <is>
-          <t>BA10-06</t>
+          <t>BA10-03</t>
         </is>
       </c>
       <c r="B1104" s="2" t="inlineStr">
@@ -30825,7 +30875,7 @@
       </c>
       <c r="E1104" s="2" t="inlineStr">
         <is>
-          <t>Hocker grau, passend</t>
+          <t>Sessel mit Bezug, weiß lackiert</t>
         </is>
       </c>
       <c r="F1104" s="3" t="n">
@@ -30841,7 +30891,7 @@
     <row r="1105">
       <c r="A1105" s="2" t="inlineStr">
         <is>
-          <t>BA10-07</t>
+          <t>BA10-04</t>
         </is>
       </c>
       <c r="B1105" s="2" t="inlineStr">
@@ -30861,11 +30911,11 @@
       </c>
       <c r="E1105" s="2" t="inlineStr">
         <is>
-          <t>Beistelltisch rund grau</t>
+          <t>Hocker grau mit Hairpin-Beinen</t>
         </is>
       </c>
       <c r="F1105" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1105" s="2" t="inlineStr">
         <is>
@@ -30877,7 +30927,7 @@
     <row r="1106">
       <c r="A1106" s="2" t="inlineStr">
         <is>
-          <t>BA10-08</t>
+          <t>BA10-05</t>
         </is>
       </c>
       <c r="B1106" s="2" t="inlineStr">
@@ -30897,7 +30947,7 @@
       </c>
       <c r="E1106" s="2" t="inlineStr">
         <is>
-          <t>Pendelleuchte Drahtgeflecht</t>
+          <t>Ohrensessel grau mit Kufengestell</t>
         </is>
       </c>
       <c r="F1106" s="3" t="n">
@@ -30911,87 +30961,117 @@
       <c r="H1106" s="2" t="n"/>
     </row>
     <row r="1107">
-      <c r="A1107" s="4" t="inlineStr">
-        <is>
-          <t>BA10-09</t>
-        </is>
-      </c>
-      <c r="B1107" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1107" s="4" t="inlineStr">
+      <c r="A1107" s="2" t="inlineStr">
+        <is>
+          <t>BA10-06</t>
+        </is>
+      </c>
+      <c r="B1107" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1107" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1107" s="4" t="inlineStr">
+      <c r="D1107" s="2" t="inlineStr">
         <is>
           <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
-      <c r="E1107" s="4" t="n"/>
-      <c r="F1107" s="3" t="n"/>
-      <c r="G1107" s="4" t="n"/>
-      <c r="H1107" s="4" t="n"/>
+      <c r="E1107" s="2" t="inlineStr">
+        <is>
+          <t>Hocker grau, passend</t>
+        </is>
+      </c>
+      <c r="F1107" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1107" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1107" s="2" t="n"/>
     </row>
     <row r="1108">
-      <c r="A1108" s="4" t="inlineStr">
-        <is>
-          <t>BA10-10</t>
-        </is>
-      </c>
-      <c r="B1108" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1108" s="4" t="inlineStr">
+      <c r="A1108" s="2" t="inlineStr">
+        <is>
+          <t>BA10-07</t>
+        </is>
+      </c>
+      <c r="B1108" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1108" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1108" s="4" t="inlineStr">
+      <c r="D1108" s="2" t="inlineStr">
         <is>
           <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
-      <c r="E1108" s="4" t="n"/>
-      <c r="F1108" s="3" t="n"/>
-      <c r="G1108" s="4" t="n"/>
-      <c r="H1108" s="4" t="n"/>
+      <c r="E1108" s="2" t="inlineStr">
+        <is>
+          <t>Beistelltisch rund grau</t>
+        </is>
+      </c>
+      <c r="F1108" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1108" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1108" s="2" t="n"/>
     </row>
     <row r="1109">
-      <c r="A1109" s="4" t="inlineStr">
-        <is>
-          <t>BA10-11</t>
-        </is>
-      </c>
-      <c r="B1109" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1109" s="4" t="inlineStr">
+      <c r="A1109" s="2" t="inlineStr">
+        <is>
+          <t>BA10-08</t>
+        </is>
+      </c>
+      <c r="B1109" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1109" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1109" s="4" t="inlineStr">
+      <c r="D1109" s="2" t="inlineStr">
         <is>
           <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
-      <c r="E1109" s="4" t="n"/>
-      <c r="F1109" s="3" t="n"/>
-      <c r="G1109" s="4" t="n"/>
-      <c r="H1109" s="4" t="n"/>
+      <c r="E1109" s="2" t="inlineStr">
+        <is>
+          <t>Pendelleuchte Drahtgeflecht</t>
+        </is>
+      </c>
+      <c r="F1109" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1109" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1109" s="2" t="n"/>
     </row>
     <row r="1110">
       <c r="A1110" s="4" t="inlineStr">
         <is>
-          <t>BA10-12</t>
+          <t>BA10-09</t>
         </is>
       </c>
       <c r="B1110" s="4" t="inlineStr">
@@ -31017,7 +31097,7 @@
     <row r="1111">
       <c r="A1111" s="4" t="inlineStr">
         <is>
-          <t>BA10-13</t>
+          <t>BA10-10</t>
         </is>
       </c>
       <c r="B1111" s="4" t="inlineStr">
@@ -31043,7 +31123,7 @@
     <row r="1112">
       <c r="A1112" s="4" t="inlineStr">
         <is>
-          <t>BA10-14</t>
+          <t>BA10-11</t>
         </is>
       </c>
       <c r="B1112" s="4" t="inlineStr">
@@ -31069,7 +31149,7 @@
     <row r="1113">
       <c r="A1113" s="4" t="inlineStr">
         <is>
-          <t>BA10-15</t>
+          <t>BA10-12</t>
         </is>
       </c>
       <c r="B1113" s="4" t="inlineStr">
@@ -31095,7 +31175,7 @@
     <row r="1114">
       <c r="A1114" s="4" t="inlineStr">
         <is>
-          <t>BA10-16</t>
+          <t>BA10-13</t>
         </is>
       </c>
       <c r="B1114" s="4" t="inlineStr">
@@ -31121,7 +31201,7 @@
     <row r="1115">
       <c r="A1115" s="4" t="inlineStr">
         <is>
-          <t>BA10-17</t>
+          <t>BA10-14</t>
         </is>
       </c>
       <c r="B1115" s="4" t="inlineStr">
@@ -31147,7 +31227,7 @@
     <row r="1116">
       <c r="A1116" s="4" t="inlineStr">
         <is>
-          <t>BA10-18</t>
+          <t>BA10-15</t>
         </is>
       </c>
       <c r="B1116" s="4" t="inlineStr">
@@ -31173,7 +31253,7 @@
     <row r="1117">
       <c r="A1117" s="4" t="inlineStr">
         <is>
-          <t>BA11-01</t>
+          <t>BA10-16</t>
         </is>
       </c>
       <c r="B1117" s="4" t="inlineStr">
@@ -31188,7 +31268,7 @@
       </c>
       <c r="D1117" s="4" t="inlineStr">
         <is>
-          <t>WC Kinder</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="E1117" s="4" t="n"/>
@@ -31199,7 +31279,7 @@
     <row r="1118">
       <c r="A1118" s="4" t="inlineStr">
         <is>
-          <t>BA11-02</t>
+          <t>BA10-17</t>
         </is>
       </c>
       <c r="B1118" s="4" t="inlineStr">
@@ -31214,7 +31294,7 @@
       </c>
       <c r="D1118" s="4" t="inlineStr">
         <is>
-          <t>WC Kinder</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="E1118" s="4" t="n"/>
@@ -31225,7 +31305,7 @@
     <row r="1119">
       <c r="A1119" s="4" t="inlineStr">
         <is>
-          <t>BA11-03</t>
+          <t>BA10-18</t>
         </is>
       </c>
       <c r="B1119" s="4" t="inlineStr">
@@ -31240,7 +31320,7 @@
       </c>
       <c r="D1119" s="4" t="inlineStr">
         <is>
-          <t>WC Kinder</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="E1119" s="4" t="n"/>
@@ -31251,7 +31331,7 @@
     <row r="1120">
       <c r="A1120" s="4" t="inlineStr">
         <is>
-          <t>BA11-04</t>
+          <t>BA11-01</t>
         </is>
       </c>
       <c r="B1120" s="4" t="inlineStr">
@@ -31277,7 +31357,7 @@
     <row r="1121">
       <c r="A1121" s="4" t="inlineStr">
         <is>
-          <t>BA11-05</t>
+          <t>BA11-02</t>
         </is>
       </c>
       <c r="B1121" s="4" t="inlineStr">
@@ -31303,7 +31383,7 @@
     <row r="1122">
       <c r="A1122" s="4" t="inlineStr">
         <is>
-          <t>BA11-06</t>
+          <t>BA11-03</t>
         </is>
       </c>
       <c r="B1122" s="4" t="inlineStr">
@@ -31329,7 +31409,7 @@
     <row r="1123">
       <c r="A1123" s="4" t="inlineStr">
         <is>
-          <t>BA11-07</t>
+          <t>BA11-04</t>
         </is>
       </c>
       <c r="B1123" s="4" t="inlineStr">
@@ -31355,7 +31435,7 @@
     <row r="1124">
       <c r="A1124" s="4" t="inlineStr">
         <is>
-          <t>BA11-08</t>
+          <t>BA11-05</t>
         </is>
       </c>
       <c r="B1124" s="4" t="inlineStr">
@@ -31381,7 +31461,7 @@
     <row r="1125">
       <c r="A1125" s="4" t="inlineStr">
         <is>
-          <t>BA11-09</t>
+          <t>BA11-06</t>
         </is>
       </c>
       <c r="B1125" s="4" t="inlineStr">
@@ -31407,7 +31487,7 @@
     <row r="1126">
       <c r="A1126" s="4" t="inlineStr">
         <is>
-          <t>BA11-10</t>
+          <t>BA11-07</t>
         </is>
       </c>
       <c r="B1126" s="4" t="inlineStr">
@@ -31433,7 +31513,7 @@
     <row r="1127">
       <c r="A1127" s="4" t="inlineStr">
         <is>
-          <t>BA11-11</t>
+          <t>BA11-08</t>
         </is>
       </c>
       <c r="B1127" s="4" t="inlineStr">
@@ -31459,7 +31539,7 @@
     <row r="1128">
       <c r="A1128" s="4" t="inlineStr">
         <is>
-          <t>BA11-12</t>
+          <t>BA11-09</t>
         </is>
       </c>
       <c r="B1128" s="4" t="inlineStr">
@@ -31485,7 +31565,7 @@
     <row r="1129">
       <c r="A1129" s="4" t="inlineStr">
         <is>
-          <t>BA11-13</t>
+          <t>BA11-10</t>
         </is>
       </c>
       <c r="B1129" s="4" t="inlineStr">
@@ -31511,7 +31591,7 @@
     <row r="1130">
       <c r="A1130" s="4" t="inlineStr">
         <is>
-          <t>BA11-14</t>
+          <t>BA11-11</t>
         </is>
       </c>
       <c r="B1130" s="4" t="inlineStr">
@@ -31537,7 +31617,7 @@
     <row r="1131">
       <c r="A1131" s="4" t="inlineStr">
         <is>
-          <t>BA11-15</t>
+          <t>BA11-12</t>
         </is>
       </c>
       <c r="B1131" s="4" t="inlineStr">
@@ -31561,45 +31641,35 @@
       <c r="H1131" s="4" t="n"/>
     </row>
     <row r="1132">
-      <c r="A1132" s="2" t="inlineStr">
-        <is>
-          <t>BA12-01</t>
-        </is>
-      </c>
-      <c r="B1132" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1132" s="2" t="inlineStr">
+      <c r="A1132" s="4" t="inlineStr">
+        <is>
+          <t>BA11-13</t>
+        </is>
+      </c>
+      <c r="B1132" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1132" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1132" s="2" t="inlineStr">
-        <is>
-          <t>WC Personal</t>
-        </is>
-      </c>
-      <c r="E1132" s="2" t="inlineStr">
-        <is>
-          <t>Ast-Mobile mit Papierwaben</t>
-        </is>
-      </c>
-      <c r="F1132" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1132" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1132" s="2" t="n"/>
+      <c r="D1132" s="4" t="inlineStr">
+        <is>
+          <t>WC Kinder</t>
+        </is>
+      </c>
+      <c r="E1132" s="4" t="n"/>
+      <c r="F1132" s="3" t="n"/>
+      <c r="G1132" s="4" t="n"/>
+      <c r="H1132" s="4" t="n"/>
     </row>
     <row r="1133">
       <c r="A1133" s="4" t="inlineStr">
         <is>
-          <t>BA12-02</t>
+          <t>BA11-14</t>
         </is>
       </c>
       <c r="B1133" s="4" t="inlineStr">
@@ -31614,7 +31684,7 @@
       </c>
       <c r="D1133" s="4" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>WC Kinder</t>
         </is>
       </c>
       <c r="E1133" s="4" t="n"/>
@@ -31625,7 +31695,7 @@
     <row r="1134">
       <c r="A1134" s="4" t="inlineStr">
         <is>
-          <t>BA12-03</t>
+          <t>BA11-15</t>
         </is>
       </c>
       <c r="B1134" s="4" t="inlineStr">
@@ -31640,7 +31710,7 @@
       </c>
       <c r="D1134" s="4" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>WC Kinder</t>
         </is>
       </c>
       <c r="E1134" s="4" t="n"/>
@@ -31649,35 +31719,45 @@
       <c r="H1134" s="4" t="n"/>
     </row>
     <row r="1135">
-      <c r="A1135" s="4" t="inlineStr">
-        <is>
-          <t>BA12-04</t>
-        </is>
-      </c>
-      <c r="B1135" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1135" s="4" t="inlineStr">
+      <c r="A1135" s="2" t="inlineStr">
+        <is>
+          <t>BA12-01</t>
+        </is>
+      </c>
+      <c r="B1135" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1135" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1135" s="4" t="inlineStr">
+      <c r="D1135" s="2" t="inlineStr">
         <is>
           <t>WC Personal</t>
         </is>
       </c>
-      <c r="E1135" s="4" t="n"/>
-      <c r="F1135" s="3" t="n"/>
-      <c r="G1135" s="4" t="n"/>
-      <c r="H1135" s="4" t="n"/>
+      <c r="E1135" s="2" t="inlineStr">
+        <is>
+          <t>Ast-Mobile mit Papierwaben</t>
+        </is>
+      </c>
+      <c r="F1135" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1135" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1135" s="2" t="n"/>
     </row>
     <row r="1136">
       <c r="A1136" s="4" t="inlineStr">
         <is>
-          <t>BA12-05</t>
+          <t>BA12-02</t>
         </is>
       </c>
       <c r="B1136" s="4" t="inlineStr">
@@ -31703,7 +31783,7 @@
     <row r="1137">
       <c r="A1137" s="4" t="inlineStr">
         <is>
-          <t>BA12-06</t>
+          <t>BA12-03</t>
         </is>
       </c>
       <c r="B1137" s="4" t="inlineStr">
@@ -31729,7 +31809,7 @@
     <row r="1138">
       <c r="A1138" s="4" t="inlineStr">
         <is>
-          <t>BA12-07</t>
+          <t>BA12-04</t>
         </is>
       </c>
       <c r="B1138" s="4" t="inlineStr">
@@ -31755,7 +31835,7 @@
     <row r="1139">
       <c r="A1139" s="4" t="inlineStr">
         <is>
-          <t>BA12-08</t>
+          <t>BA12-05</t>
         </is>
       </c>
       <c r="B1139" s="4" t="inlineStr">
@@ -31781,7 +31861,7 @@
     <row r="1140">
       <c r="A1140" s="4" t="inlineStr">
         <is>
-          <t>BA12-09</t>
+          <t>BA12-06</t>
         </is>
       </c>
       <c r="B1140" s="4" t="inlineStr">
@@ -31807,7 +31887,7 @@
     <row r="1141">
       <c r="A1141" s="4" t="inlineStr">
         <is>
-          <t>BA12-10</t>
+          <t>BA12-07</t>
         </is>
       </c>
       <c r="B1141" s="4" t="inlineStr">
@@ -31833,7 +31913,7 @@
     <row r="1142">
       <c r="A1142" s="4" t="inlineStr">
         <is>
-          <t>BA12-11</t>
+          <t>BA12-08</t>
         </is>
       </c>
       <c r="B1142" s="4" t="inlineStr">
@@ -31859,7 +31939,7 @@
     <row r="1143">
       <c r="A1143" s="4" t="inlineStr">
         <is>
-          <t>BA13-01</t>
+          <t>BA12-09</t>
         </is>
       </c>
       <c r="B1143" s="4" t="inlineStr">
@@ -31874,7 +31954,7 @@
       </c>
       <c r="D1143" s="4" t="inlineStr">
         <is>
-          <t>Abstellraum</t>
+          <t>WC Personal</t>
         </is>
       </c>
       <c r="E1143" s="4" t="n"/>
@@ -31885,7 +31965,7 @@
     <row r="1144">
       <c r="A1144" s="4" t="inlineStr">
         <is>
-          <t>BA13-02</t>
+          <t>BA12-10</t>
         </is>
       </c>
       <c r="B1144" s="4" t="inlineStr">
@@ -31900,7 +31980,7 @@
       </c>
       <c r="D1144" s="4" t="inlineStr">
         <is>
-          <t>Abstellraum</t>
+          <t>WC Personal</t>
         </is>
       </c>
       <c r="E1144" s="4" t="n"/>
@@ -31911,7 +31991,7 @@
     <row r="1145">
       <c r="A1145" s="4" t="inlineStr">
         <is>
-          <t>BA13-03</t>
+          <t>BA12-11</t>
         </is>
       </c>
       <c r="B1145" s="4" t="inlineStr">
@@ -31926,7 +32006,7 @@
       </c>
       <c r="D1145" s="4" t="inlineStr">
         <is>
-          <t>Abstellraum</t>
+          <t>WC Personal</t>
         </is>
       </c>
       <c r="E1145" s="4" t="n"/>
@@ -31937,7 +32017,7 @@
     <row r="1146">
       <c r="A1146" s="4" t="inlineStr">
         <is>
-          <t>BA13-04</t>
+          <t>BA13-01</t>
         </is>
       </c>
       <c r="B1146" s="4" t="inlineStr">
@@ -31963,7 +32043,7 @@
     <row r="1147">
       <c r="A1147" s="4" t="inlineStr">
         <is>
-          <t>BA13-05</t>
+          <t>BA13-02</t>
         </is>
       </c>
       <c r="B1147" s="4" t="inlineStr">
@@ -31989,7 +32069,7 @@
     <row r="1148">
       <c r="A1148" s="4" t="inlineStr">
         <is>
-          <t>BA13-06</t>
+          <t>BA13-03</t>
         </is>
       </c>
       <c r="B1148" s="4" t="inlineStr">
@@ -32015,7 +32095,7 @@
     <row r="1149">
       <c r="A1149" s="4" t="inlineStr">
         <is>
-          <t>BA13-07</t>
+          <t>BA13-04</t>
         </is>
       </c>
       <c r="B1149" s="4" t="inlineStr">
@@ -32041,7 +32121,7 @@
     <row r="1150">
       <c r="A1150" s="4" t="inlineStr">
         <is>
-          <t>BA13-08</t>
+          <t>BA13-05</t>
         </is>
       </c>
       <c r="B1150" s="4" t="inlineStr">
@@ -32067,7 +32147,7 @@
     <row r="1151">
       <c r="A1151" s="4" t="inlineStr">
         <is>
-          <t>BA13-09</t>
+          <t>BA13-06</t>
         </is>
       </c>
       <c r="B1151" s="4" t="inlineStr">
@@ -32093,7 +32173,7 @@
     <row r="1152">
       <c r="A1152" s="4" t="inlineStr">
         <is>
-          <t>BA13-10</t>
+          <t>BA13-07</t>
         </is>
       </c>
       <c r="B1152" s="4" t="inlineStr">
@@ -32119,7 +32199,7 @@
     <row r="1153">
       <c r="A1153" s="4" t="inlineStr">
         <is>
-          <t>BA13-11</t>
+          <t>BA13-08</t>
         </is>
       </c>
       <c r="B1153" s="4" t="inlineStr">
@@ -32145,7 +32225,7 @@
     <row r="1154">
       <c r="A1154" s="4" t="inlineStr">
         <is>
-          <t>BA13-12</t>
+          <t>BA13-09</t>
         </is>
       </c>
       <c r="B1154" s="4" t="inlineStr">
@@ -32171,7 +32251,7 @@
     <row r="1155">
       <c r="A1155" s="4" t="inlineStr">
         <is>
-          <t>BA13-13</t>
+          <t>BA13-10</t>
         </is>
       </c>
       <c r="B1155" s="4" t="inlineStr">
@@ -32197,7 +32277,7 @@
     <row r="1156">
       <c r="A1156" s="4" t="inlineStr">
         <is>
-          <t>BA13-14</t>
+          <t>BA13-11</t>
         </is>
       </c>
       <c r="B1156" s="4" t="inlineStr">
@@ -32223,7 +32303,7 @@
     <row r="1157">
       <c r="A1157" s="4" t="inlineStr">
         <is>
-          <t>BA13-15</t>
+          <t>BA13-12</t>
         </is>
       </c>
       <c r="B1157" s="4" t="inlineStr">
@@ -32247,117 +32327,87 @@
       <c r="H1157" s="4" t="n"/>
     </row>
     <row r="1158">
-      <c r="A1158" s="2" t="inlineStr">
-        <is>
-          <t>TE01-01</t>
-        </is>
-      </c>
-      <c r="B1158" s="2" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1158" s="2" t="inlineStr">
-        <is>
-          <t>ebenerdig</t>
-        </is>
-      </c>
-      <c r="D1158" s="2" t="inlineStr">
-        <is>
-          <t>Terrasse</t>
-        </is>
-      </c>
-      <c r="E1158" s="2" t="inlineStr">
-        <is>
-          <t>Biohort Freizeitbox weiß (Terrasse)</t>
-        </is>
-      </c>
-      <c r="F1158" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1158" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1158" s="2" t="n"/>
+      <c r="A1158" s="4" t="inlineStr">
+        <is>
+          <t>BA13-13</t>
+        </is>
+      </c>
+      <c r="B1158" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1158" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1158" s="4" t="inlineStr">
+        <is>
+          <t>Abstellraum</t>
+        </is>
+      </c>
+      <c r="E1158" s="4" t="n"/>
+      <c r="F1158" s="3" t="n"/>
+      <c r="G1158" s="4" t="n"/>
+      <c r="H1158" s="4" t="n"/>
     </row>
     <row r="1159">
-      <c r="A1159" s="2" t="inlineStr">
-        <is>
-          <t>TE01-02</t>
-        </is>
-      </c>
-      <c r="B1159" s="2" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1159" s="2" t="inlineStr">
-        <is>
-          <t>ebenerdig</t>
-        </is>
-      </c>
-      <c r="D1159" s="2" t="inlineStr">
-        <is>
-          <t>Terrasse</t>
-        </is>
-      </c>
-      <c r="E1159" s="2" t="inlineStr">
-        <is>
-          <t>Gartentisch mit Granitplatte inkl. Stühle und Schutzhülle</t>
-        </is>
-      </c>
-      <c r="F1159" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1159" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1159" s="2" t="n"/>
+      <c r="A1159" s="4" t="inlineStr">
+        <is>
+          <t>BA13-14</t>
+        </is>
+      </c>
+      <c r="B1159" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1159" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1159" s="4" t="inlineStr">
+        <is>
+          <t>Abstellraum</t>
+        </is>
+      </c>
+      <c r="E1159" s="4" t="n"/>
+      <c r="F1159" s="3" t="n"/>
+      <c r="G1159" s="4" t="n"/>
+      <c r="H1159" s="4" t="n"/>
     </row>
     <row r="1160">
-      <c r="A1160" s="2" t="inlineStr">
-        <is>
-          <t>TE01-03</t>
-        </is>
-      </c>
-      <c r="B1160" s="2" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1160" s="2" t="inlineStr">
-        <is>
-          <t>ebenerdig</t>
-        </is>
-      </c>
-      <c r="D1160" s="2" t="inlineStr">
-        <is>
-          <t>Terrasse</t>
-        </is>
-      </c>
-      <c r="E1160" s="2" t="inlineStr">
-        <is>
-          <t>Textilene-Stapelsessel anthrazit</t>
-        </is>
-      </c>
-      <c r="F1160" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G1160" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1160" s="2" t="n"/>
+      <c r="A1160" s="4" t="inlineStr">
+        <is>
+          <t>BA13-15</t>
+        </is>
+      </c>
+      <c r="B1160" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1160" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1160" s="4" t="inlineStr">
+        <is>
+          <t>Abstellraum</t>
+        </is>
+      </c>
+      <c r="E1160" s="4" t="n"/>
+      <c r="F1160" s="3" t="n"/>
+      <c r="G1160" s="4" t="n"/>
+      <c r="H1160" s="4" t="n"/>
     </row>
     <row r="1161">
       <c r="A1161" s="2" t="inlineStr">
         <is>
-          <t>TE01-04</t>
+          <t>TE01-01</t>
         </is>
       </c>
       <c r="B1161" s="2" t="inlineStr">
@@ -32377,7 +32427,7 @@
       </c>
       <c r="E1161" s="2" t="inlineStr">
         <is>
-          <t>Weber Genesis Gasgrill</t>
+          <t>Biohort Freizeitbox weiß (Terrasse)</t>
         </is>
       </c>
       <c r="F1161" s="3" t="n">
@@ -32393,7 +32443,7 @@
     <row r="1162">
       <c r="A1162" s="2" t="inlineStr">
         <is>
-          <t>TE01-05</t>
+          <t>TE01-02</t>
         </is>
       </c>
       <c r="B1162" s="2" t="inlineStr">
@@ -32413,7 +32463,7 @@
       </c>
       <c r="E1162" s="2" t="inlineStr">
         <is>
-          <t>Sonnenschirm creme</t>
+          <t>Gartentisch mit Granitplatte inkl. Stühle und Schutzhülle</t>
         </is>
       </c>
       <c r="F1162" s="3" t="n">
@@ -32427,87 +32477,117 @@
       <c r="H1162" s="2" t="n"/>
     </row>
     <row r="1163">
-      <c r="A1163" s="4" t="inlineStr">
-        <is>
-          <t>TE01-06</t>
-        </is>
-      </c>
-      <c r="B1163" s="4" t="inlineStr">
+      <c r="A1163" s="2" t="inlineStr">
+        <is>
+          <t>TE01-03</t>
+        </is>
+      </c>
+      <c r="B1163" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1163" s="4" t="inlineStr">
+      <c r="C1163" s="2" t="inlineStr">
         <is>
           <t>ebenerdig</t>
         </is>
       </c>
-      <c r="D1163" s="4" t="inlineStr">
+      <c r="D1163" s="2" t="inlineStr">
         <is>
           <t>Terrasse</t>
         </is>
       </c>
-      <c r="E1163" s="4" t="n"/>
-      <c r="F1163" s="3" t="n"/>
-      <c r="G1163" s="4" t="n"/>
-      <c r="H1163" s="4" t="n"/>
+      <c r="E1163" s="2" t="inlineStr">
+        <is>
+          <t>Textilene-Stapelsessel anthrazit</t>
+        </is>
+      </c>
+      <c r="F1163" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1163" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1163" s="2" t="n"/>
     </row>
     <row r="1164">
-      <c r="A1164" s="4" t="inlineStr">
-        <is>
-          <t>TE01-07</t>
-        </is>
-      </c>
-      <c r="B1164" s="4" t="inlineStr">
+      <c r="A1164" s="2" t="inlineStr">
+        <is>
+          <t>TE01-04</t>
+        </is>
+      </c>
+      <c r="B1164" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1164" s="4" t="inlineStr">
+      <c r="C1164" s="2" t="inlineStr">
         <is>
           <t>ebenerdig</t>
         </is>
       </c>
-      <c r="D1164" s="4" t="inlineStr">
+      <c r="D1164" s="2" t="inlineStr">
         <is>
           <t>Terrasse</t>
         </is>
       </c>
-      <c r="E1164" s="4" t="n"/>
-      <c r="F1164" s="3" t="n"/>
-      <c r="G1164" s="4" t="n"/>
-      <c r="H1164" s="4" t="n"/>
+      <c r="E1164" s="2" t="inlineStr">
+        <is>
+          <t>Weber Genesis Gasgrill</t>
+        </is>
+      </c>
+      <c r="F1164" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1164" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1164" s="2" t="n"/>
     </row>
     <row r="1165">
-      <c r="A1165" s="4" t="inlineStr">
-        <is>
-          <t>TE01-08</t>
-        </is>
-      </c>
-      <c r="B1165" s="4" t="inlineStr">
+      <c r="A1165" s="2" t="inlineStr">
+        <is>
+          <t>TE01-05</t>
+        </is>
+      </c>
+      <c r="B1165" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1165" s="4" t="inlineStr">
+      <c r="C1165" s="2" t="inlineStr">
         <is>
           <t>ebenerdig</t>
         </is>
       </c>
-      <c r="D1165" s="4" t="inlineStr">
+      <c r="D1165" s="2" t="inlineStr">
         <is>
           <t>Terrasse</t>
         </is>
       </c>
-      <c r="E1165" s="4" t="n"/>
-      <c r="F1165" s="3" t="n"/>
-      <c r="G1165" s="4" t="n"/>
-      <c r="H1165" s="4" t="n"/>
+      <c r="E1165" s="2" t="inlineStr">
+        <is>
+          <t>Sonnenschirm creme</t>
+        </is>
+      </c>
+      <c r="F1165" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1165" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1165" s="2" t="n"/>
     </row>
     <row r="1166">
       <c r="A1166" s="4" t="inlineStr">
         <is>
-          <t>TE01-09</t>
+          <t>TE01-06</t>
         </is>
       </c>
       <c r="B1166" s="4" t="inlineStr">
@@ -32533,7 +32613,7 @@
     <row r="1167">
       <c r="A1167" s="4" t="inlineStr">
         <is>
-          <t>TE01-10</t>
+          <t>TE01-07</t>
         </is>
       </c>
       <c r="B1167" s="4" t="inlineStr">
@@ -32559,7 +32639,7 @@
     <row r="1168">
       <c r="A1168" s="4" t="inlineStr">
         <is>
-          <t>TE01-11</t>
+          <t>TE01-08</t>
         </is>
       </c>
       <c r="B1168" s="4" t="inlineStr">
@@ -32585,7 +32665,7 @@
     <row r="1169">
       <c r="A1169" s="4" t="inlineStr">
         <is>
-          <t>TE01-12</t>
+          <t>TE01-09</t>
         </is>
       </c>
       <c r="B1169" s="4" t="inlineStr">
@@ -32611,7 +32691,7 @@
     <row r="1170">
       <c r="A1170" s="4" t="inlineStr">
         <is>
-          <t>TE01-13</t>
+          <t>TE01-10</t>
         </is>
       </c>
       <c r="B1170" s="4" t="inlineStr">
@@ -32637,7 +32717,7 @@
     <row r="1171">
       <c r="A1171" s="4" t="inlineStr">
         <is>
-          <t>TE01-14</t>
+          <t>TE01-11</t>
         </is>
       </c>
       <c r="B1171" s="4" t="inlineStr">
@@ -32663,7 +32743,7 @@
     <row r="1172">
       <c r="A1172" s="4" t="inlineStr">
         <is>
-          <t>TE01-15</t>
+          <t>TE01-12</t>
         </is>
       </c>
       <c r="B1172" s="4" t="inlineStr">
@@ -32689,7 +32769,7 @@
     <row r="1173">
       <c r="A1173" s="4" t="inlineStr">
         <is>
-          <t>TE01-16</t>
+          <t>TE01-13</t>
         </is>
       </c>
       <c r="B1173" s="4" t="inlineStr">
@@ -32715,7 +32795,7 @@
     <row r="1174">
       <c r="A1174" s="4" t="inlineStr">
         <is>
-          <t>TE01-17</t>
+          <t>TE01-14</t>
         </is>
       </c>
       <c r="B1174" s="4" t="inlineStr">
@@ -32741,7 +32821,7 @@
     <row r="1175">
       <c r="A1175" s="4" t="inlineStr">
         <is>
-          <t>TE01-18</t>
+          <t>TE01-15</t>
         </is>
       </c>
       <c r="B1175" s="4" t="inlineStr">
@@ -32767,7 +32847,7 @@
     <row r="1176">
       <c r="A1176" s="4" t="inlineStr">
         <is>
-          <t>TE01-19</t>
+          <t>TE01-16</t>
         </is>
       </c>
       <c r="B1176" s="4" t="inlineStr">
@@ -32793,7 +32873,7 @@
     <row r="1177">
       <c r="A1177" s="4" t="inlineStr">
         <is>
-          <t>TE01-20</t>
+          <t>TE01-17</t>
         </is>
       </c>
       <c r="B1177" s="4" t="inlineStr">
@@ -32819,7 +32899,7 @@
     <row r="1178">
       <c r="A1178" s="4" t="inlineStr">
         <is>
-          <t>TE01-21</t>
+          <t>TE01-18</t>
         </is>
       </c>
       <c r="B1178" s="4" t="inlineStr">
@@ -32845,7 +32925,7 @@
     <row r="1179">
       <c r="A1179" s="4" t="inlineStr">
         <is>
-          <t>TE01-22</t>
+          <t>TE01-19</t>
         </is>
       </c>
       <c r="B1179" s="4" t="inlineStr">
@@ -32871,7 +32951,7 @@
     <row r="1180">
       <c r="A1180" s="4" t="inlineStr">
         <is>
-          <t>TE01-23</t>
+          <t>TE01-20</t>
         </is>
       </c>
       <c r="B1180" s="4" t="inlineStr">
@@ -32897,7 +32977,7 @@
     <row r="1181">
       <c r="A1181" s="4" t="inlineStr">
         <is>
-          <t>TE01-24</t>
+          <t>TE01-21</t>
         </is>
       </c>
       <c r="B1181" s="4" t="inlineStr">
@@ -32923,7 +33003,7 @@
     <row r="1182">
       <c r="A1182" s="4" t="inlineStr">
         <is>
-          <t>TE01-25</t>
+          <t>TE01-22</t>
         </is>
       </c>
       <c r="B1182" s="4" t="inlineStr">
@@ -32949,7 +33029,7 @@
     <row r="1183">
       <c r="A1183" s="4" t="inlineStr">
         <is>
-          <t>TE01-26</t>
+          <t>TE01-23</t>
         </is>
       </c>
       <c r="B1183" s="4" t="inlineStr">
@@ -32975,7 +33055,7 @@
     <row r="1184">
       <c r="A1184" s="4" t="inlineStr">
         <is>
-          <t>TE01-27</t>
+          <t>TE01-24</t>
         </is>
       </c>
       <c r="B1184" s="4" t="inlineStr">
@@ -33001,7 +33081,7 @@
     <row r="1185">
       <c r="A1185" s="4" t="inlineStr">
         <is>
-          <t>TE01-28</t>
+          <t>TE01-25</t>
         </is>
       </c>
       <c r="B1185" s="4" t="inlineStr">
@@ -33027,7 +33107,7 @@
     <row r="1186">
       <c r="A1186" s="4" t="inlineStr">
         <is>
-          <t>TE01-29</t>
+          <t>TE01-26</t>
         </is>
       </c>
       <c r="B1186" s="4" t="inlineStr">
@@ -33053,7 +33133,7 @@
     <row r="1187">
       <c r="A1187" s="4" t="inlineStr">
         <is>
-          <t>TE01-30</t>
+          <t>TE01-27</t>
         </is>
       </c>
       <c r="B1187" s="4" t="inlineStr">
@@ -33079,7 +33159,7 @@
     <row r="1188">
       <c r="A1188" s="4" t="inlineStr">
         <is>
-          <t>TE01-31</t>
+          <t>TE01-28</t>
         </is>
       </c>
       <c r="B1188" s="4" t="inlineStr">
@@ -33105,7 +33185,7 @@
     <row r="1189">
       <c r="A1189" s="4" t="inlineStr">
         <is>
-          <t>TE01-32</t>
+          <t>TE01-29</t>
         </is>
       </c>
       <c r="B1189" s="4" t="inlineStr">
@@ -33131,7 +33211,7 @@
     <row r="1190">
       <c r="A1190" s="4" t="inlineStr">
         <is>
-          <t>TE01-33</t>
+          <t>TE01-30</t>
         </is>
       </c>
       <c r="B1190" s="4" t="inlineStr">
@@ -33157,7 +33237,7 @@
     <row r="1191">
       <c r="A1191" s="4" t="inlineStr">
         <is>
-          <t>TE01-34</t>
+          <t>TE01-31</t>
         </is>
       </c>
       <c r="B1191" s="4" t="inlineStr">
@@ -33183,7 +33263,7 @@
     <row r="1192">
       <c r="A1192" s="4" t="inlineStr">
         <is>
-          <t>TE01-35</t>
+          <t>TE01-32</t>
         </is>
       </c>
       <c r="B1192" s="4" t="inlineStr">
@@ -33209,7 +33289,7 @@
     <row r="1193">
       <c r="A1193" s="4" t="inlineStr">
         <is>
-          <t>TE01-36</t>
+          <t>TE01-33</t>
         </is>
       </c>
       <c r="B1193" s="4" t="inlineStr">
@@ -33235,7 +33315,7 @@
     <row r="1194">
       <c r="A1194" s="4" t="inlineStr">
         <is>
-          <t>TE01-37</t>
+          <t>TE01-34</t>
         </is>
       </c>
       <c r="B1194" s="4" t="inlineStr">
@@ -33261,7 +33341,7 @@
     <row r="1195">
       <c r="A1195" s="4" t="inlineStr">
         <is>
-          <t>TE01-38</t>
+          <t>TE01-35</t>
         </is>
       </c>
       <c r="B1195" s="4" t="inlineStr">
@@ -33287,7 +33367,7 @@
     <row r="1196">
       <c r="A1196" s="4" t="inlineStr">
         <is>
-          <t>TE01-39</t>
+          <t>TE01-36</t>
         </is>
       </c>
       <c r="B1196" s="4" t="inlineStr">
@@ -33313,7 +33393,7 @@
     <row r="1197">
       <c r="A1197" s="4" t="inlineStr">
         <is>
-          <t>TE01-40</t>
+          <t>TE01-37</t>
         </is>
       </c>
       <c r="B1197" s="4" t="inlineStr">
@@ -33337,117 +33417,87 @@
       <c r="H1197" s="4" t="n"/>
     </row>
     <row r="1198">
-      <c r="A1198" s="2" t="inlineStr">
-        <is>
-          <t>TE02-01</t>
-        </is>
-      </c>
-      <c r="B1198" s="2" t="inlineStr">
+      <c r="A1198" s="4" t="inlineStr">
+        <is>
+          <t>TE01-38</t>
+        </is>
+      </c>
+      <c r="B1198" s="4" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1198" s="2" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1198" s="2" t="inlineStr">
-        <is>
-          <t>Dachterrasse</t>
-        </is>
-      </c>
-      <c r="E1198" s="2" t="inlineStr">
-        <is>
-          <t>Pflanzkübel Plastik weiß</t>
-        </is>
-      </c>
-      <c r="F1198" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G1198" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1198" s="2" t="n"/>
+      <c r="C1198" s="4" t="inlineStr">
+        <is>
+          <t>ebenerdig</t>
+        </is>
+      </c>
+      <c r="D1198" s="4" t="inlineStr">
+        <is>
+          <t>Terrasse</t>
+        </is>
+      </c>
+      <c r="E1198" s="4" t="n"/>
+      <c r="F1198" s="3" t="n"/>
+      <c r="G1198" s="4" t="n"/>
+      <c r="H1198" s="4" t="n"/>
     </row>
     <row r="1199">
-      <c r="A1199" s="2" t="inlineStr">
-        <is>
-          <t>TE02-02</t>
-        </is>
-      </c>
-      <c r="B1199" s="2" t="inlineStr">
+      <c r="A1199" s="4" t="inlineStr">
+        <is>
+          <t>TE01-39</t>
+        </is>
+      </c>
+      <c r="B1199" s="4" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1199" s="2" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1199" s="2" t="inlineStr">
-        <is>
-          <t>Dachterrasse</t>
-        </is>
-      </c>
-      <c r="E1199" s="2" t="inlineStr">
-        <is>
-          <t>Gartenstuhl Kunststoff anthrazit</t>
-        </is>
-      </c>
-      <c r="F1199" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G1199" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1199" s="2" t="n"/>
+      <c r="C1199" s="4" t="inlineStr">
+        <is>
+          <t>ebenerdig</t>
+        </is>
+      </c>
+      <c r="D1199" s="4" t="inlineStr">
+        <is>
+          <t>Terrasse</t>
+        </is>
+      </c>
+      <c r="E1199" s="4" t="n"/>
+      <c r="F1199" s="3" t="n"/>
+      <c r="G1199" s="4" t="n"/>
+      <c r="H1199" s="4" t="n"/>
     </row>
     <row r="1200">
-      <c r="A1200" s="2" t="inlineStr">
-        <is>
-          <t>TE02-03</t>
-        </is>
-      </c>
-      <c r="B1200" s="2" t="inlineStr">
+      <c r="A1200" s="4" t="inlineStr">
+        <is>
+          <t>TE01-40</t>
+        </is>
+      </c>
+      <c r="B1200" s="4" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1200" s="2" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1200" s="2" t="inlineStr">
-        <is>
-          <t>Dachterrasse</t>
-        </is>
-      </c>
-      <c r="E1200" s="2" t="inlineStr">
-        <is>
-          <t>Gartentisch anthrazit</t>
-        </is>
-      </c>
-      <c r="F1200" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1200" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1200" s="2" t="n"/>
+      <c r="C1200" s="4" t="inlineStr">
+        <is>
+          <t>ebenerdig</t>
+        </is>
+      </c>
+      <c r="D1200" s="4" t="inlineStr">
+        <is>
+          <t>Terrasse</t>
+        </is>
+      </c>
+      <c r="E1200" s="4" t="n"/>
+      <c r="F1200" s="3" t="n"/>
+      <c r="G1200" s="4" t="n"/>
+      <c r="H1200" s="4" t="n"/>
     </row>
     <row r="1201">
       <c r="A1201" s="2" t="inlineStr">
         <is>
-          <t>TE02-04</t>
+          <t>TE02-01</t>
         </is>
       </c>
       <c r="B1201" s="2" t="inlineStr">
@@ -33467,15 +33517,15 @@
       </c>
       <c r="E1201" s="2" t="inlineStr">
         <is>
-          <t>Teak-Klapptisch rund</t>
+          <t>Pflanzkübel Plastik weiß</t>
         </is>
       </c>
       <c r="F1201" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1201" s="2" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Stück</t>
         </is>
       </c>
       <c r="H1201" s="2" t="n"/>
@@ -33483,7 +33533,7 @@
     <row r="1202">
       <c r="A1202" s="2" t="inlineStr">
         <is>
-          <t>TE02-05</t>
+          <t>TE02-02</t>
         </is>
       </c>
       <c r="B1202" s="2" t="inlineStr">
@@ -33503,11 +33553,11 @@
       </c>
       <c r="E1202" s="2" t="inlineStr">
         <is>
-          <t>Pflanzkübel grau, groß</t>
+          <t>Gartenstuhl Kunststoff anthrazit</t>
         </is>
       </c>
       <c r="F1202" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1202" s="2" t="inlineStr">
         <is>
@@ -33519,7 +33569,7 @@
     <row r="1203">
       <c r="A1203" s="2" t="inlineStr">
         <is>
-          <t>TE02-06</t>
+          <t>TE02-03</t>
         </is>
       </c>
       <c r="B1203" s="2" t="inlineStr">
@@ -33539,7 +33589,7 @@
       </c>
       <c r="E1203" s="2" t="inlineStr">
         <is>
-          <t>Holzstern mit Lichterkette</t>
+          <t>Gartentisch anthrazit</t>
         </is>
       </c>
       <c r="F1203" s="3" t="n">
@@ -33553,87 +33603,117 @@
       <c r="H1203" s="2" t="n"/>
     </row>
     <row r="1204">
-      <c r="A1204" s="4" t="inlineStr">
-        <is>
-          <t>TE02-07</t>
-        </is>
-      </c>
-      <c r="B1204" s="4" t="inlineStr">
+      <c r="A1204" s="2" t="inlineStr">
+        <is>
+          <t>TE02-04</t>
+        </is>
+      </c>
+      <c r="B1204" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1204" s="4" t="inlineStr">
+      <c r="C1204" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1204" s="4" t="inlineStr">
+      <c r="D1204" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1204" s="4" t="n"/>
-      <c r="F1204" s="3" t="n"/>
-      <c r="G1204" s="4" t="n"/>
-      <c r="H1204" s="4" t="n"/>
+      <c r="E1204" s="2" t="inlineStr">
+        <is>
+          <t>Teak-Klapptisch rund</t>
+        </is>
+      </c>
+      <c r="F1204" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1204" s="2" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="H1204" s="2" t="n"/>
     </row>
     <row r="1205">
-      <c r="A1205" s="4" t="inlineStr">
-        <is>
-          <t>TE02-08</t>
-        </is>
-      </c>
-      <c r="B1205" s="4" t="inlineStr">
+      <c r="A1205" s="2" t="inlineStr">
+        <is>
+          <t>TE02-05</t>
+        </is>
+      </c>
+      <c r="B1205" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1205" s="4" t="inlineStr">
+      <c r="C1205" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1205" s="4" t="inlineStr">
+      <c r="D1205" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1205" s="4" t="n"/>
-      <c r="F1205" s="3" t="n"/>
-      <c r="G1205" s="4" t="n"/>
-      <c r="H1205" s="4" t="n"/>
+      <c r="E1205" s="2" t="inlineStr">
+        <is>
+          <t>Pflanzkübel grau, groß</t>
+        </is>
+      </c>
+      <c r="F1205" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1205" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1205" s="2" t="n"/>
     </row>
     <row r="1206">
-      <c r="A1206" s="4" t="inlineStr">
-        <is>
-          <t>TE02-09</t>
-        </is>
-      </c>
-      <c r="B1206" s="4" t="inlineStr">
+      <c r="A1206" s="2" t="inlineStr">
+        <is>
+          <t>TE02-06</t>
+        </is>
+      </c>
+      <c r="B1206" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1206" s="4" t="inlineStr">
+      <c r="C1206" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1206" s="4" t="inlineStr">
+      <c r="D1206" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1206" s="4" t="n"/>
-      <c r="F1206" s="3" t="n"/>
-      <c r="G1206" s="4" t="n"/>
-      <c r="H1206" s="4" t="n"/>
+      <c r="E1206" s="2" t="inlineStr">
+        <is>
+          <t>Holzstern mit Lichterkette</t>
+        </is>
+      </c>
+      <c r="F1206" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1206" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1206" s="2" t="n"/>
     </row>
     <row r="1207">
       <c r="A1207" s="4" t="inlineStr">
         <is>
-          <t>TE02-10</t>
+          <t>TE02-07</t>
         </is>
       </c>
       <c r="B1207" s="4" t="inlineStr">
@@ -33659,7 +33739,7 @@
     <row r="1208">
       <c r="A1208" s="4" t="inlineStr">
         <is>
-          <t>TE02-11</t>
+          <t>TE02-08</t>
         </is>
       </c>
       <c r="B1208" s="4" t="inlineStr">
@@ -33685,7 +33765,7 @@
     <row r="1209">
       <c r="A1209" s="4" t="inlineStr">
         <is>
-          <t>TE02-12</t>
+          <t>TE02-09</t>
         </is>
       </c>
       <c r="B1209" s="4" t="inlineStr">
@@ -33711,7 +33791,7 @@
     <row r="1210">
       <c r="A1210" s="4" t="inlineStr">
         <is>
-          <t>TE02-13</t>
+          <t>TE02-10</t>
         </is>
       </c>
       <c r="B1210" s="4" t="inlineStr">
@@ -33737,7 +33817,7 @@
     <row r="1211">
       <c r="A1211" s="4" t="inlineStr">
         <is>
-          <t>TE02-14</t>
+          <t>TE02-11</t>
         </is>
       </c>
       <c r="B1211" s="4" t="inlineStr">
@@ -33763,7 +33843,7 @@
     <row r="1212">
       <c r="A1212" s="4" t="inlineStr">
         <is>
-          <t>TE02-15</t>
+          <t>TE02-12</t>
         </is>
       </c>
       <c r="B1212" s="4" t="inlineStr">
@@ -33789,7 +33869,7 @@
     <row r="1213">
       <c r="A1213" s="4" t="inlineStr">
         <is>
-          <t>TE02-16</t>
+          <t>TE02-13</t>
         </is>
       </c>
       <c r="B1213" s="4" t="inlineStr">
@@ -33815,7 +33895,7 @@
     <row r="1214">
       <c r="A1214" s="4" t="inlineStr">
         <is>
-          <t>TE02-17</t>
+          <t>TE02-14</t>
         </is>
       </c>
       <c r="B1214" s="4" t="inlineStr">
@@ -33841,7 +33921,7 @@
     <row r="1215">
       <c r="A1215" s="4" t="inlineStr">
         <is>
-          <t>TE02-18</t>
+          <t>TE02-15</t>
         </is>
       </c>
       <c r="B1215" s="4" t="inlineStr">
@@ -33867,7 +33947,7 @@
     <row r="1216">
       <c r="A1216" s="4" t="inlineStr">
         <is>
-          <t>TE02-19</t>
+          <t>TE02-16</t>
         </is>
       </c>
       <c r="B1216" s="4" t="inlineStr">
@@ -33893,7 +33973,7 @@
     <row r="1217">
       <c r="A1217" s="4" t="inlineStr">
         <is>
-          <t>TE02-20</t>
+          <t>TE02-17</t>
         </is>
       </c>
       <c r="B1217" s="4" t="inlineStr">
@@ -33919,7 +33999,7 @@
     <row r="1218">
       <c r="A1218" s="4" t="inlineStr">
         <is>
-          <t>TE02-21</t>
+          <t>TE02-18</t>
         </is>
       </c>
       <c r="B1218" s="4" t="inlineStr">
@@ -33945,7 +34025,7 @@
     <row r="1219">
       <c r="A1219" s="4" t="inlineStr">
         <is>
-          <t>TE02-22</t>
+          <t>TE02-19</t>
         </is>
       </c>
       <c r="B1219" s="4" t="inlineStr">
@@ -33971,7 +34051,7 @@
     <row r="1220">
       <c r="A1220" s="4" t="inlineStr">
         <is>
-          <t>TE02-23</t>
+          <t>TE02-20</t>
         </is>
       </c>
       <c r="B1220" s="4" t="inlineStr">
@@ -33997,7 +34077,7 @@
     <row r="1221">
       <c r="A1221" s="4" t="inlineStr">
         <is>
-          <t>TE02-24</t>
+          <t>TE02-21</t>
         </is>
       </c>
       <c r="B1221" s="4" t="inlineStr">
@@ -34023,7 +34103,7 @@
     <row r="1222">
       <c r="A1222" s="4" t="inlineStr">
         <is>
-          <t>TE02-25</t>
+          <t>TE02-22</t>
         </is>
       </c>
       <c r="B1222" s="4" t="inlineStr">
@@ -34049,7 +34129,7 @@
     <row r="1223">
       <c r="A1223" s="4" t="inlineStr">
         <is>
-          <t>TE02-26</t>
+          <t>TE02-23</t>
         </is>
       </c>
       <c r="B1223" s="4" t="inlineStr">
@@ -34075,7 +34155,7 @@
     <row r="1224">
       <c r="A1224" s="4" t="inlineStr">
         <is>
-          <t>TE02-27</t>
+          <t>TE02-24</t>
         </is>
       </c>
       <c r="B1224" s="4" t="inlineStr">
@@ -34101,7 +34181,7 @@
     <row r="1225">
       <c r="A1225" s="4" t="inlineStr">
         <is>
-          <t>TE02-28</t>
+          <t>TE02-25</t>
         </is>
       </c>
       <c r="B1225" s="4" t="inlineStr">
@@ -34127,7 +34207,7 @@
     <row r="1226">
       <c r="A1226" s="4" t="inlineStr">
         <is>
-          <t>TE02-29</t>
+          <t>TE02-26</t>
         </is>
       </c>
       <c r="B1226" s="4" t="inlineStr">
@@ -34153,7 +34233,7 @@
     <row r="1227">
       <c r="A1227" s="4" t="inlineStr">
         <is>
-          <t>TE02-30</t>
+          <t>TE02-27</t>
         </is>
       </c>
       <c r="B1227" s="4" t="inlineStr">
@@ -34179,7 +34259,7 @@
     <row r="1228">
       <c r="A1228" s="4" t="inlineStr">
         <is>
-          <t>TE02-31</t>
+          <t>TE02-28</t>
         </is>
       </c>
       <c r="B1228" s="4" t="inlineStr">
@@ -34205,7 +34285,7 @@
     <row r="1229">
       <c r="A1229" s="4" t="inlineStr">
         <is>
-          <t>TE02-32</t>
+          <t>TE02-29</t>
         </is>
       </c>
       <c r="B1229" s="4" t="inlineStr">
@@ -34231,7 +34311,7 @@
     <row r="1230">
       <c r="A1230" s="4" t="inlineStr">
         <is>
-          <t>TE02-33</t>
+          <t>TE02-30</t>
         </is>
       </c>
       <c r="B1230" s="4" t="inlineStr">
@@ -34257,7 +34337,7 @@
     <row r="1231">
       <c r="A1231" s="4" t="inlineStr">
         <is>
-          <t>TE02-34</t>
+          <t>TE02-31</t>
         </is>
       </c>
       <c r="B1231" s="4" t="inlineStr">
@@ -34283,7 +34363,7 @@
     <row r="1232">
       <c r="A1232" s="4" t="inlineStr">
         <is>
-          <t>TE02-35</t>
+          <t>TE02-32</t>
         </is>
       </c>
       <c r="B1232" s="4" t="inlineStr">
@@ -34309,7 +34389,7 @@
     <row r="1233">
       <c r="A1233" s="4" t="inlineStr">
         <is>
-          <t>TE02-36</t>
+          <t>TE02-33</t>
         </is>
       </c>
       <c r="B1233" s="4" t="inlineStr">
@@ -34335,7 +34415,7 @@
     <row r="1234">
       <c r="A1234" s="4" t="inlineStr">
         <is>
-          <t>TE02-37</t>
+          <t>TE02-34</t>
         </is>
       </c>
       <c r="B1234" s="4" t="inlineStr">
@@ -34361,7 +34441,7 @@
     <row r="1235">
       <c r="A1235" s="4" t="inlineStr">
         <is>
-          <t>TE02-38</t>
+          <t>TE02-35</t>
         </is>
       </c>
       <c r="B1235" s="4" t="inlineStr">
@@ -34387,7 +34467,7 @@
     <row r="1236">
       <c r="A1236" s="4" t="inlineStr">
         <is>
-          <t>TE02-39</t>
+          <t>TE02-36</t>
         </is>
       </c>
       <c r="B1236" s="4" t="inlineStr">
@@ -34413,7 +34493,7 @@
     <row r="1237">
       <c r="A1237" s="4" t="inlineStr">
         <is>
-          <t>TE02-40</t>
+          <t>TE02-37</t>
         </is>
       </c>
       <c r="B1237" s="4" t="inlineStr">
@@ -34437,41 +34517,35 @@
       <c r="H1237" s="4" t="n"/>
     </row>
     <row r="1238">
-      <c r="A1238" s="2" t="inlineStr">
-        <is>
-          <t>GA01-01</t>
-        </is>
-      </c>
-      <c r="B1238" s="2" t="inlineStr">
+      <c r="A1238" s="4" t="inlineStr">
+        <is>
+          <t>TE02-38</t>
+        </is>
+      </c>
+      <c r="B1238" s="4" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1238" s="2" t="inlineStr"/>
-      <c r="D1238" s="2" t="inlineStr">
-        <is>
-          <t>Gartenanlage</t>
-        </is>
-      </c>
-      <c r="E1238" s="2" t="inlineStr">
-        <is>
-          <t>Holz-Wellenliege, Doppelliege</t>
-        </is>
-      </c>
-      <c r="F1238" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1238" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1238" s="2" t="n"/>
+      <c r="C1238" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1238" s="4" t="inlineStr">
+        <is>
+          <t>Dachterrasse</t>
+        </is>
+      </c>
+      <c r="E1238" s="4" t="n"/>
+      <c r="F1238" s="3" t="n"/>
+      <c r="G1238" s="4" t="n"/>
+      <c r="H1238" s="4" t="n"/>
     </row>
     <row r="1239">
       <c r="A1239" s="4" t="inlineStr">
         <is>
-          <t>GA01-02</t>
+          <t>TE02-39</t>
         </is>
       </c>
       <c r="B1239" s="4" t="inlineStr">
@@ -34479,10 +34553,14 @@
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1239" s="4" t="inlineStr"/>
+      <c r="C1239" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
       <c r="D1239" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Dachterrasse</t>
         </is>
       </c>
       <c r="E1239" s="4" t="n"/>
@@ -34493,7 +34571,7 @@
     <row r="1240">
       <c r="A1240" s="4" t="inlineStr">
         <is>
-          <t>GA01-03</t>
+          <t>TE02-40</t>
         </is>
       </c>
       <c r="B1240" s="4" t="inlineStr">
@@ -34501,10 +34579,14 @@
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1240" s="4" t="inlineStr"/>
+      <c r="C1240" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
       <c r="D1240" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Dachterrasse</t>
         </is>
       </c>
       <c r="E1240" s="4" t="n"/>
@@ -34513,31 +34595,41 @@
       <c r="H1240" s="4" t="n"/>
     </row>
     <row r="1241">
-      <c r="A1241" s="4" t="inlineStr">
-        <is>
-          <t>GA01-04</t>
-        </is>
-      </c>
-      <c r="B1241" s="4" t="inlineStr">
+      <c r="A1241" s="2" t="inlineStr">
+        <is>
+          <t>GA01-01</t>
+        </is>
+      </c>
+      <c r="B1241" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1241" s="4" t="inlineStr"/>
-      <c r="D1241" s="4" t="inlineStr">
+      <c r="C1241" s="2" t="inlineStr"/>
+      <c r="D1241" s="2" t="inlineStr">
         <is>
           <t>Gartenanlage</t>
         </is>
       </c>
-      <c r="E1241" s="4" t="n"/>
-      <c r="F1241" s="3" t="n"/>
-      <c r="G1241" s="4" t="n"/>
-      <c r="H1241" s="4" t="n"/>
+      <c r="E1241" s="2" t="inlineStr">
+        <is>
+          <t>Holz-Wellenliege, Doppelliege</t>
+        </is>
+      </c>
+      <c r="F1241" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1241" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1241" s="2" t="n"/>
     </row>
     <row r="1242">
       <c r="A1242" s="4" t="inlineStr">
         <is>
-          <t>GA01-05</t>
+          <t>GA01-02</t>
         </is>
       </c>
       <c r="B1242" s="4" t="inlineStr">
@@ -34559,7 +34651,7 @@
     <row r="1243">
       <c r="A1243" s="4" t="inlineStr">
         <is>
-          <t>GA01-06</t>
+          <t>GA01-03</t>
         </is>
       </c>
       <c r="B1243" s="4" t="inlineStr">
@@ -34581,7 +34673,7 @@
     <row r="1244">
       <c r="A1244" s="4" t="inlineStr">
         <is>
-          <t>GA01-07</t>
+          <t>GA01-04</t>
         </is>
       </c>
       <c r="B1244" s="4" t="inlineStr">
@@ -34603,7 +34695,7 @@
     <row r="1245">
       <c r="A1245" s="4" t="inlineStr">
         <is>
-          <t>GA01-08</t>
+          <t>GA01-05</t>
         </is>
       </c>
       <c r="B1245" s="4" t="inlineStr">
@@ -34625,7 +34717,7 @@
     <row r="1246">
       <c r="A1246" s="4" t="inlineStr">
         <is>
-          <t>GA01-09</t>
+          <t>GA01-06</t>
         </is>
       </c>
       <c r="B1246" s="4" t="inlineStr">
@@ -34647,7 +34739,7 @@
     <row r="1247">
       <c r="A1247" s="4" t="inlineStr">
         <is>
-          <t>GA01-10</t>
+          <t>GA01-07</t>
         </is>
       </c>
       <c r="B1247" s="4" t="inlineStr">
@@ -34669,7 +34761,7 @@
     <row r="1248">
       <c r="A1248" s="4" t="inlineStr">
         <is>
-          <t>GA01-11</t>
+          <t>GA01-08</t>
         </is>
       </c>
       <c r="B1248" s="4" t="inlineStr">
@@ -34691,7 +34783,7 @@
     <row r="1249">
       <c r="A1249" s="4" t="inlineStr">
         <is>
-          <t>GA01-12</t>
+          <t>GA01-09</t>
         </is>
       </c>
       <c r="B1249" s="4" t="inlineStr">
@@ -34713,7 +34805,7 @@
     <row r="1250">
       <c r="A1250" s="4" t="inlineStr">
         <is>
-          <t>GA01-13</t>
+          <t>GA01-10</t>
         </is>
       </c>
       <c r="B1250" s="4" t="inlineStr">
@@ -34735,7 +34827,7 @@
     <row r="1251">
       <c r="A1251" s="4" t="inlineStr">
         <is>
-          <t>GA01-14</t>
+          <t>GA01-11</t>
         </is>
       </c>
       <c r="B1251" s="4" t="inlineStr">
@@ -34757,7 +34849,7 @@
     <row r="1252">
       <c r="A1252" s="4" t="inlineStr">
         <is>
-          <t>GA01-15</t>
+          <t>GA01-12</t>
         </is>
       </c>
       <c r="B1252" s="4" t="inlineStr">
@@ -34779,7 +34871,7 @@
     <row r="1253">
       <c r="A1253" s="4" t="inlineStr">
         <is>
-          <t>GA01-16</t>
+          <t>GA01-13</t>
         </is>
       </c>
       <c r="B1253" s="4" t="inlineStr">
@@ -34801,7 +34893,7 @@
     <row r="1254">
       <c r="A1254" s="4" t="inlineStr">
         <is>
-          <t>GA01-17</t>
+          <t>GA01-14</t>
         </is>
       </c>
       <c r="B1254" s="4" t="inlineStr">
@@ -34823,7 +34915,7 @@
     <row r="1255">
       <c r="A1255" s="4" t="inlineStr">
         <is>
-          <t>GA01-18</t>
+          <t>GA01-15</t>
         </is>
       </c>
       <c r="B1255" s="4" t="inlineStr">
@@ -34845,7 +34937,7 @@
     <row r="1256">
       <c r="A1256" s="4" t="inlineStr">
         <is>
-          <t>GA01-19</t>
+          <t>GA01-16</t>
         </is>
       </c>
       <c r="B1256" s="4" t="inlineStr">
@@ -34867,7 +34959,7 @@
     <row r="1257">
       <c r="A1257" s="4" t="inlineStr">
         <is>
-          <t>GA01-20</t>
+          <t>GA01-17</t>
         </is>
       </c>
       <c r="B1257" s="4" t="inlineStr">
@@ -34889,7 +34981,7 @@
     <row r="1258">
       <c r="A1258" s="4" t="inlineStr">
         <is>
-          <t>GA01-21</t>
+          <t>GA01-18</t>
         </is>
       </c>
       <c r="B1258" s="4" t="inlineStr">
@@ -34911,7 +35003,7 @@
     <row r="1259">
       <c r="A1259" s="4" t="inlineStr">
         <is>
-          <t>GA01-22</t>
+          <t>GA01-19</t>
         </is>
       </c>
       <c r="B1259" s="4" t="inlineStr">
@@ -34933,7 +35025,7 @@
     <row r="1260">
       <c r="A1260" s="4" t="inlineStr">
         <is>
-          <t>GA01-23</t>
+          <t>GA01-20</t>
         </is>
       </c>
       <c r="B1260" s="4" t="inlineStr">
@@ -34955,7 +35047,7 @@
     <row r="1261">
       <c r="A1261" s="4" t="inlineStr">
         <is>
-          <t>GA01-24</t>
+          <t>GA01-21</t>
         </is>
       </c>
       <c r="B1261" s="4" t="inlineStr">
@@ -34977,7 +35069,7 @@
     <row r="1262">
       <c r="A1262" s="4" t="inlineStr">
         <is>
-          <t>GA01-25</t>
+          <t>GA01-22</t>
         </is>
       </c>
       <c r="B1262" s="4" t="inlineStr">
@@ -34999,7 +35091,7 @@
     <row r="1263">
       <c r="A1263" s="4" t="inlineStr">
         <is>
-          <t>GA01-26</t>
+          <t>GA01-23</t>
         </is>
       </c>
       <c r="B1263" s="4" t="inlineStr">
@@ -35021,7 +35113,7 @@
     <row r="1264">
       <c r="A1264" s="4" t="inlineStr">
         <is>
-          <t>GA01-27</t>
+          <t>GA01-24</t>
         </is>
       </c>
       <c r="B1264" s="4" t="inlineStr">
@@ -35043,7 +35135,7 @@
     <row r="1265">
       <c r="A1265" s="4" t="inlineStr">
         <is>
-          <t>GA01-28</t>
+          <t>GA01-25</t>
         </is>
       </c>
       <c r="B1265" s="4" t="inlineStr">
@@ -35065,7 +35157,7 @@
     <row r="1266">
       <c r="A1266" s="4" t="inlineStr">
         <is>
-          <t>GA01-29</t>
+          <t>GA01-26</t>
         </is>
       </c>
       <c r="B1266" s="4" t="inlineStr">
@@ -35087,7 +35179,7 @@
     <row r="1267">
       <c r="A1267" s="4" t="inlineStr">
         <is>
-          <t>GA01-30</t>
+          <t>GA01-27</t>
         </is>
       </c>
       <c r="B1267" s="4" t="inlineStr">
@@ -35109,7 +35201,7 @@
     <row r="1268">
       <c r="A1268" s="4" t="inlineStr">
         <is>
-          <t>GA01-31</t>
+          <t>GA01-28</t>
         </is>
       </c>
       <c r="B1268" s="4" t="inlineStr">
@@ -35131,7 +35223,7 @@
     <row r="1269">
       <c r="A1269" s="4" t="inlineStr">
         <is>
-          <t>GA01-32</t>
+          <t>GA01-29</t>
         </is>
       </c>
       <c r="B1269" s="4" t="inlineStr">
@@ -35153,7 +35245,7 @@
     <row r="1270">
       <c r="A1270" s="4" t="inlineStr">
         <is>
-          <t>GA01-33</t>
+          <t>GA01-30</t>
         </is>
       </c>
       <c r="B1270" s="4" t="inlineStr">
@@ -35175,7 +35267,7 @@
     <row r="1271">
       <c r="A1271" s="4" t="inlineStr">
         <is>
-          <t>GA01-34</t>
+          <t>GA01-31</t>
         </is>
       </c>
       <c r="B1271" s="4" t="inlineStr">
@@ -35197,7 +35289,7 @@
     <row r="1272">
       <c r="A1272" s="4" t="inlineStr">
         <is>
-          <t>GA01-35</t>
+          <t>GA01-32</t>
         </is>
       </c>
       <c r="B1272" s="4" t="inlineStr">
@@ -35219,7 +35311,7 @@
     <row r="1273">
       <c r="A1273" s="4" t="inlineStr">
         <is>
-          <t>GA01-36</t>
+          <t>GA01-33</t>
         </is>
       </c>
       <c r="B1273" s="4" t="inlineStr">
@@ -35241,7 +35333,7 @@
     <row r="1274">
       <c r="A1274" s="4" t="inlineStr">
         <is>
-          <t>GA01-37</t>
+          <t>GA01-34</t>
         </is>
       </c>
       <c r="B1274" s="4" t="inlineStr">
@@ -35263,7 +35355,7 @@
     <row r="1275">
       <c r="A1275" s="4" t="inlineStr">
         <is>
-          <t>GA01-38</t>
+          <t>GA01-35</t>
         </is>
       </c>
       <c r="B1275" s="4" t="inlineStr">
@@ -35285,7 +35377,7 @@
     <row r="1276">
       <c r="A1276" s="4" t="inlineStr">
         <is>
-          <t>GA01-39</t>
+          <t>GA01-36</t>
         </is>
       </c>
       <c r="B1276" s="4" t="inlineStr">
@@ -35307,7 +35399,7 @@
     <row r="1277">
       <c r="A1277" s="4" t="inlineStr">
         <is>
-          <t>GA01-40</t>
+          <t>GA01-37</t>
         </is>
       </c>
       <c r="B1277" s="4" t="inlineStr">
@@ -35326,10 +35418,76 @@
       <c r="G1277" s="4" t="n"/>
       <c r="H1277" s="4" t="n"/>
     </row>
+    <row r="1278">
+      <c r="A1278" s="4" t="inlineStr">
+        <is>
+          <t>GA01-38</t>
+        </is>
+      </c>
+      <c r="B1278" s="4" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1278" s="4" t="inlineStr"/>
+      <c r="D1278" s="4" t="inlineStr">
+        <is>
+          <t>Gartenanlage</t>
+        </is>
+      </c>
+      <c r="E1278" s="4" t="n"/>
+      <c r="F1278" s="3" t="n"/>
+      <c r="G1278" s="4" t="n"/>
+      <c r="H1278" s="4" t="n"/>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="4" t="inlineStr">
+        <is>
+          <t>GA01-39</t>
+        </is>
+      </c>
+      <c r="B1279" s="4" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1279" s="4" t="inlineStr"/>
+      <c r="D1279" s="4" t="inlineStr">
+        <is>
+          <t>Gartenanlage</t>
+        </is>
+      </c>
+      <c r="E1279" s="4" t="n"/>
+      <c r="F1279" s="3" t="n"/>
+      <c r="G1279" s="4" t="n"/>
+      <c r="H1279" s="4" t="n"/>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="4" t="inlineStr">
+        <is>
+          <t>GA01-40</t>
+        </is>
+      </c>
+      <c r="B1280" s="4" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1280" s="4" t="inlineStr"/>
+      <c r="D1280" s="4" t="inlineStr">
+        <is>
+          <t>Gartenanlage</t>
+        </is>
+      </c>
+      <c r="E1280" s="4" t="n"/>
+      <c r="F1280" s="3" t="n"/>
+      <c r="G1280" s="4" t="n"/>
+      <c r="H1280" s="4" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1277"/>
+  <autoFilter ref="A1:H1280"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F1277" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen." type="whole" operator="greaterThan">
+    <dataValidation sqref="F2:F1280" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anleitung" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Erfassung'!$A$1:$H$1280</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Erfassung'!$A$1:$H$1279</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1280"/>
+  <dimension ref="A1:H1279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
@@ -26245,11 +26245,11 @@
       </c>
       <c r="E934" s="2" t="inlineStr">
         <is>
-          <t>Kindergarderobe weiß</t>
+          <t>Rutscherauto rot</t>
         </is>
       </c>
       <c r="F934" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G934" s="2" t="inlineStr">
         <is>
@@ -26281,11 +26281,11 @@
       </c>
       <c r="E935" s="2" t="inlineStr">
         <is>
-          <t>Rutscherauto rot</t>
+          <t>Bilder Schwarzwald, gerahmt</t>
         </is>
       </c>
       <c r="F935" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G935" s="2" t="inlineStr">
         <is>
@@ -26317,11 +26317,11 @@
       </c>
       <c r="E936" s="2" t="inlineStr">
         <is>
-          <t>Bilder Schwarzwald, gerahmt</t>
+          <t>Kinder-Ohrensessel grau, Kunstleder</t>
         </is>
       </c>
       <c r="F936" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G936" s="2" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
       </c>
       <c r="E937" s="2" t="inlineStr">
         <is>
-          <t>Kinder-Ohrensessel grau, Kunstleder</t>
+          <t>Ablagepult Holz auf Metallgestell</t>
         </is>
       </c>
       <c r="F937" s="3" t="n">
@@ -26389,7 +26389,7 @@
       </c>
       <c r="E938" s="2" t="inlineStr">
         <is>
-          <t>Ablagepult Holz auf Metallgestell</t>
+          <t>Truhenbank weiß mit Fellauflage</t>
         </is>
       </c>
       <c r="F938" s="3" t="n">
@@ -26425,11 +26425,11 @@
       </c>
       <c r="E939" s="2" t="inlineStr">
         <is>
-          <t>Truhenbank weiß mit Fellauflage</t>
+          <t>Kinderschrank weiß mit Handabdrücken</t>
         </is>
       </c>
       <c r="F939" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G939" s="2" t="inlineStr">
         <is>
@@ -26461,11 +26461,11 @@
       </c>
       <c r="E940" s="2" t="inlineStr">
         <is>
-          <t>Kinderschrank weiß mit Handabdrücken</t>
+          <t>Deko-Häuser Keramik</t>
         </is>
       </c>
       <c r="F940" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G940" s="2" t="inlineStr">
         <is>
@@ -26475,40 +26475,30 @@
       <c r="H940" s="2" t="n"/>
     </row>
     <row r="941">
-      <c r="A941" s="2" t="inlineStr">
+      <c r="A941" s="4" t="inlineStr">
         <is>
           <t>BA02-08</t>
         </is>
       </c>
-      <c r="B941" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C941" s="2" t="inlineStr">
+      <c r="B941" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C941" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D941" s="2" t="inlineStr">
+      <c r="D941" s="4" t="inlineStr">
         <is>
           <t>Flur 2</t>
         </is>
       </c>
-      <c r="E941" s="2" t="inlineStr">
-        <is>
-          <t>Deko-Häuser Keramik</t>
-        </is>
-      </c>
-      <c r="F941" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G941" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H941" s="2" t="n"/>
+      <c r="E941" s="4" t="n"/>
+      <c r="F941" s="3" t="n"/>
+      <c r="G941" s="4" t="n"/>
+      <c r="H941" s="4" t="n"/>
     </row>
     <row r="942">
       <c r="A942" s="4" t="inlineStr">
@@ -26747,7 +26737,7 @@
     <row r="951">
       <c r="A951" s="4" t="inlineStr">
         <is>
-          <t>BA02-18</t>
+          <t>BA03-01</t>
         </is>
       </c>
       <c r="B951" s="4" t="inlineStr">
@@ -26762,7 +26752,7 @@
       </c>
       <c r="D951" s="4" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Galerie</t>
         </is>
       </c>
       <c r="E951" s="4" t="n"/>
@@ -26773,7 +26763,7 @@
     <row r="952">
       <c r="A952" s="4" t="inlineStr">
         <is>
-          <t>BA03-01</t>
+          <t>BA03-02</t>
         </is>
       </c>
       <c r="B952" s="4" t="inlineStr">
@@ -26799,7 +26789,7 @@
     <row r="953">
       <c r="A953" s="4" t="inlineStr">
         <is>
-          <t>BA03-02</t>
+          <t>BA03-03</t>
         </is>
       </c>
       <c r="B953" s="4" t="inlineStr">
@@ -26825,7 +26815,7 @@
     <row r="954">
       <c r="A954" s="4" t="inlineStr">
         <is>
-          <t>BA03-03</t>
+          <t>BA03-04</t>
         </is>
       </c>
       <c r="B954" s="4" t="inlineStr">
@@ -26851,7 +26841,7 @@
     <row r="955">
       <c r="A955" s="4" t="inlineStr">
         <is>
-          <t>BA03-04</t>
+          <t>BA03-05</t>
         </is>
       </c>
       <c r="B955" s="4" t="inlineStr">
@@ -26877,7 +26867,7 @@
     <row r="956">
       <c r="A956" s="4" t="inlineStr">
         <is>
-          <t>BA03-05</t>
+          <t>BA03-06</t>
         </is>
       </c>
       <c r="B956" s="4" t="inlineStr">
@@ -26903,7 +26893,7 @@
     <row r="957">
       <c r="A957" s="4" t="inlineStr">
         <is>
-          <t>BA03-06</t>
+          <t>BA03-07</t>
         </is>
       </c>
       <c r="B957" s="4" t="inlineStr">
@@ -26929,7 +26919,7 @@
     <row r="958">
       <c r="A958" s="4" t="inlineStr">
         <is>
-          <t>BA03-07</t>
+          <t>BA03-08</t>
         </is>
       </c>
       <c r="B958" s="4" t="inlineStr">
@@ -26955,7 +26945,7 @@
     <row r="959">
       <c r="A959" s="4" t="inlineStr">
         <is>
-          <t>BA03-08</t>
+          <t>BA03-09</t>
         </is>
       </c>
       <c r="B959" s="4" t="inlineStr">
@@ -26981,7 +26971,7 @@
     <row r="960">
       <c r="A960" s="4" t="inlineStr">
         <is>
-          <t>BA03-09</t>
+          <t>BA03-10</t>
         </is>
       </c>
       <c r="B960" s="4" t="inlineStr">
@@ -27007,7 +26997,7 @@
     <row r="961">
       <c r="A961" s="4" t="inlineStr">
         <is>
-          <t>BA03-10</t>
+          <t>BA03-11</t>
         </is>
       </c>
       <c r="B961" s="4" t="inlineStr">
@@ -27033,7 +27023,7 @@
     <row r="962">
       <c r="A962" s="4" t="inlineStr">
         <is>
-          <t>BA03-11</t>
+          <t>BA03-12</t>
         </is>
       </c>
       <c r="B962" s="4" t="inlineStr">
@@ -27059,7 +27049,7 @@
     <row r="963">
       <c r="A963" s="4" t="inlineStr">
         <is>
-          <t>BA03-12</t>
+          <t>BA03-13</t>
         </is>
       </c>
       <c r="B963" s="4" t="inlineStr">
@@ -27085,7 +27075,7 @@
     <row r="964">
       <c r="A964" s="4" t="inlineStr">
         <is>
-          <t>BA03-13</t>
+          <t>BA03-14</t>
         </is>
       </c>
       <c r="B964" s="4" t="inlineStr">
@@ -27111,7 +27101,7 @@
     <row r="965">
       <c r="A965" s="4" t="inlineStr">
         <is>
-          <t>BA03-14</t>
+          <t>BA03-15</t>
         </is>
       </c>
       <c r="B965" s="4" t="inlineStr">
@@ -27135,35 +27125,45 @@
       <c r="H965" s="4" t="n"/>
     </row>
     <row r="966">
-      <c r="A966" s="4" t="inlineStr">
-        <is>
-          <t>BA03-15</t>
-        </is>
-      </c>
-      <c r="B966" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C966" s="4" t="inlineStr">
+      <c r="A966" s="2" t="inlineStr">
+        <is>
+          <t>BA04-01</t>
+        </is>
+      </c>
+      <c r="B966" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C966" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D966" s="4" t="inlineStr">
-        <is>
-          <t>Galerie</t>
-        </is>
-      </c>
-      <c r="E966" s="4" t="n"/>
-      <c r="F966" s="3" t="n"/>
-      <c r="G966" s="4" t="n"/>
-      <c r="H966" s="4" t="n"/>
+      <c r="D966" s="2" t="inlineStr">
+        <is>
+          <t>Gruppenraum 4</t>
+        </is>
+      </c>
+      <c r="E966" s="2" t="inlineStr">
+        <is>
+          <t>Rattankörbe 8 Stück</t>
+        </is>
+      </c>
+      <c r="F966" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G966" s="2" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="H966" s="2" t="n"/>
     </row>
     <row r="967">
       <c r="A967" s="2" t="inlineStr">
         <is>
-          <t>BA04-01</t>
+          <t>BA04-02</t>
         </is>
       </c>
       <c r="B967" s="2" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="E967" s="2" t="inlineStr">
         <is>
-          <t>Rattankörbe 8 Stück</t>
+          <t>Holzkiste Obstkistenoptik</t>
         </is>
       </c>
       <c r="F967" s="3" t="n">
@@ -27191,51 +27191,41 @@
       </c>
       <c r="G967" s="2" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Stück</t>
         </is>
       </c>
       <c r="H967" s="2" t="n"/>
     </row>
     <row r="968">
-      <c r="A968" s="2" t="inlineStr">
-        <is>
-          <t>BA04-02</t>
-        </is>
-      </c>
-      <c r="B968" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C968" s="2" t="inlineStr">
+      <c r="A968" s="4" t="inlineStr">
+        <is>
+          <t>BA04-03</t>
+        </is>
+      </c>
+      <c r="B968" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C968" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D968" s="2" t="inlineStr">
+      <c r="D968" s="4" t="inlineStr">
         <is>
           <t>Gruppenraum 4</t>
         </is>
       </c>
-      <c r="E968" s="2" t="inlineStr">
-        <is>
-          <t>Holzkiste Obstkistenoptik</t>
-        </is>
-      </c>
-      <c r="F968" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G968" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H968" s="2" t="n"/>
+      <c r="E968" s="4" t="n"/>
+      <c r="F968" s="3" t="n"/>
+      <c r="G968" s="4" t="n"/>
+      <c r="H968" s="4" t="n"/>
     </row>
     <row r="969">
       <c r="A969" s="4" t="inlineStr">
         <is>
-          <t>BA04-03</t>
+          <t>BA04-04</t>
         </is>
       </c>
       <c r="B969" s="4" t="inlineStr">
@@ -27261,7 +27251,7 @@
     <row r="970">
       <c r="A970" s="4" t="inlineStr">
         <is>
-          <t>BA04-04</t>
+          <t>BA04-05</t>
         </is>
       </c>
       <c r="B970" s="4" t="inlineStr">
@@ -27287,7 +27277,7 @@
     <row r="971">
       <c r="A971" s="4" t="inlineStr">
         <is>
-          <t>BA04-05</t>
+          <t>BA04-06</t>
         </is>
       </c>
       <c r="B971" s="4" t="inlineStr">
@@ -27313,7 +27303,7 @@
     <row r="972">
       <c r="A972" s="4" t="inlineStr">
         <is>
-          <t>BA04-06</t>
+          <t>BA04-07</t>
         </is>
       </c>
       <c r="B972" s="4" t="inlineStr">
@@ -27339,7 +27329,7 @@
     <row r="973">
       <c r="A973" s="4" t="inlineStr">
         <is>
-          <t>BA04-07</t>
+          <t>BA04-08</t>
         </is>
       </c>
       <c r="B973" s="4" t="inlineStr">
@@ -27365,7 +27355,7 @@
     <row r="974">
       <c r="A974" s="4" t="inlineStr">
         <is>
-          <t>BA04-08</t>
+          <t>BA04-09</t>
         </is>
       </c>
       <c r="B974" s="4" t="inlineStr">
@@ -27391,7 +27381,7 @@
     <row r="975">
       <c r="A975" s="4" t="inlineStr">
         <is>
-          <t>BA04-09</t>
+          <t>BA04-10</t>
         </is>
       </c>
       <c r="B975" s="4" t="inlineStr">
@@ -27417,7 +27407,7 @@
     <row r="976">
       <c r="A976" s="4" t="inlineStr">
         <is>
-          <t>BA04-10</t>
+          <t>BA04-11</t>
         </is>
       </c>
       <c r="B976" s="4" t="inlineStr">
@@ -27443,7 +27433,7 @@
     <row r="977">
       <c r="A977" s="4" t="inlineStr">
         <is>
-          <t>BA04-11</t>
+          <t>BA04-12</t>
         </is>
       </c>
       <c r="B977" s="4" t="inlineStr">
@@ -27469,7 +27459,7 @@
     <row r="978">
       <c r="A978" s="4" t="inlineStr">
         <is>
-          <t>BA04-12</t>
+          <t>BA04-13</t>
         </is>
       </c>
       <c r="B978" s="4" t="inlineStr">
@@ -27495,7 +27485,7 @@
     <row r="979">
       <c r="A979" s="4" t="inlineStr">
         <is>
-          <t>BA04-13</t>
+          <t>BA04-14</t>
         </is>
       </c>
       <c r="B979" s="4" t="inlineStr">
@@ -27521,7 +27511,7 @@
     <row r="980">
       <c r="A980" s="4" t="inlineStr">
         <is>
-          <t>BA04-14</t>
+          <t>BA04-15</t>
         </is>
       </c>
       <c r="B980" s="4" t="inlineStr">
@@ -27547,7 +27537,7 @@
     <row r="981">
       <c r="A981" s="4" t="inlineStr">
         <is>
-          <t>BA04-15</t>
+          <t>BA04-16</t>
         </is>
       </c>
       <c r="B981" s="4" t="inlineStr">
@@ -27573,7 +27563,7 @@
     <row r="982">
       <c r="A982" s="4" t="inlineStr">
         <is>
-          <t>BA04-16</t>
+          <t>BA04-17</t>
         </is>
       </c>
       <c r="B982" s="4" t="inlineStr">
@@ -27599,7 +27589,7 @@
     <row r="983">
       <c r="A983" s="4" t="inlineStr">
         <is>
-          <t>BA04-17</t>
+          <t>BA04-18</t>
         </is>
       </c>
       <c r="B983" s="4" t="inlineStr">
@@ -27625,7 +27615,7 @@
     <row r="984">
       <c r="A984" s="4" t="inlineStr">
         <is>
-          <t>BA04-18</t>
+          <t>BA04-19</t>
         </is>
       </c>
       <c r="B984" s="4" t="inlineStr">
@@ -27651,7 +27641,7 @@
     <row r="985">
       <c r="A985" s="4" t="inlineStr">
         <is>
-          <t>BA04-19</t>
+          <t>BA04-20</t>
         </is>
       </c>
       <c r="B985" s="4" t="inlineStr">
@@ -27677,7 +27667,7 @@
     <row r="986">
       <c r="A986" s="4" t="inlineStr">
         <is>
-          <t>BA04-20</t>
+          <t>BA04-21</t>
         </is>
       </c>
       <c r="B986" s="4" t="inlineStr">
@@ -27703,7 +27693,7 @@
     <row r="987">
       <c r="A987" s="4" t="inlineStr">
         <is>
-          <t>BA04-21</t>
+          <t>BA04-22</t>
         </is>
       </c>
       <c r="B987" s="4" t="inlineStr">
@@ -27729,7 +27719,7 @@
     <row r="988">
       <c r="A988" s="4" t="inlineStr">
         <is>
-          <t>BA04-22</t>
+          <t>BA04-23</t>
         </is>
       </c>
       <c r="B988" s="4" t="inlineStr">
@@ -27755,7 +27745,7 @@
     <row r="989">
       <c r="A989" s="4" t="inlineStr">
         <is>
-          <t>BA04-23</t>
+          <t>BA04-24</t>
         </is>
       </c>
       <c r="B989" s="4" t="inlineStr">
@@ -27781,7 +27771,7 @@
     <row r="990">
       <c r="A990" s="4" t="inlineStr">
         <is>
-          <t>BA04-24</t>
+          <t>BA04-25</t>
         </is>
       </c>
       <c r="B990" s="4" t="inlineStr">
@@ -27807,7 +27797,7 @@
     <row r="991">
       <c r="A991" s="4" t="inlineStr">
         <is>
-          <t>BA04-25</t>
+          <t>BA05-01</t>
         </is>
       </c>
       <c r="B991" s="4" t="inlineStr">
@@ -27822,7 +27812,7 @@
       </c>
       <c r="D991" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Turnraum</t>
         </is>
       </c>
       <c r="E991" s="4" t="n"/>
@@ -27833,7 +27823,7 @@
     <row r="992">
       <c r="A992" s="4" t="inlineStr">
         <is>
-          <t>BA05-01</t>
+          <t>BA05-02</t>
         </is>
       </c>
       <c r="B992" s="4" t="inlineStr">
@@ -27859,7 +27849,7 @@
     <row r="993">
       <c r="A993" s="4" t="inlineStr">
         <is>
-          <t>BA05-02</t>
+          <t>BA05-03</t>
         </is>
       </c>
       <c r="B993" s="4" t="inlineStr">
@@ -27885,7 +27875,7 @@
     <row r="994">
       <c r="A994" s="4" t="inlineStr">
         <is>
-          <t>BA05-03</t>
+          <t>BA05-04</t>
         </is>
       </c>
       <c r="B994" s="4" t="inlineStr">
@@ -27911,7 +27901,7 @@
     <row r="995">
       <c r="A995" s="4" t="inlineStr">
         <is>
-          <t>BA05-04</t>
+          <t>BA05-05</t>
         </is>
       </c>
       <c r="B995" s="4" t="inlineStr">
@@ -27937,7 +27927,7 @@
     <row r="996">
       <c r="A996" s="4" t="inlineStr">
         <is>
-          <t>BA05-05</t>
+          <t>BA05-06</t>
         </is>
       </c>
       <c r="B996" s="4" t="inlineStr">
@@ -27963,7 +27953,7 @@
     <row r="997">
       <c r="A997" s="4" t="inlineStr">
         <is>
-          <t>BA05-06</t>
+          <t>BA05-07</t>
         </is>
       </c>
       <c r="B997" s="4" t="inlineStr">
@@ -27989,7 +27979,7 @@
     <row r="998">
       <c r="A998" s="4" t="inlineStr">
         <is>
-          <t>BA05-07</t>
+          <t>BA05-08</t>
         </is>
       </c>
       <c r="B998" s="4" t="inlineStr">
@@ -28015,7 +28005,7 @@
     <row r="999">
       <c r="A999" s="4" t="inlineStr">
         <is>
-          <t>BA05-08</t>
+          <t>BA05-09</t>
         </is>
       </c>
       <c r="B999" s="4" t="inlineStr">
@@ -28041,7 +28031,7 @@
     <row r="1000">
       <c r="A1000" s="4" t="inlineStr">
         <is>
-          <t>BA05-09</t>
+          <t>BA05-10</t>
         </is>
       </c>
       <c r="B1000" s="4" t="inlineStr">
@@ -28067,7 +28057,7 @@
     <row r="1001">
       <c r="A1001" s="4" t="inlineStr">
         <is>
-          <t>BA05-10</t>
+          <t>BA05-11</t>
         </is>
       </c>
       <c r="B1001" s="4" t="inlineStr">
@@ -28093,7 +28083,7 @@
     <row r="1002">
       <c r="A1002" s="4" t="inlineStr">
         <is>
-          <t>BA05-11</t>
+          <t>BA05-12</t>
         </is>
       </c>
       <c r="B1002" s="4" t="inlineStr">
@@ -28119,7 +28109,7 @@
     <row r="1003">
       <c r="A1003" s="4" t="inlineStr">
         <is>
-          <t>BA05-12</t>
+          <t>BA05-13</t>
         </is>
       </c>
       <c r="B1003" s="4" t="inlineStr">
@@ -28145,7 +28135,7 @@
     <row r="1004">
       <c r="A1004" s="4" t="inlineStr">
         <is>
-          <t>BA05-13</t>
+          <t>BA05-14</t>
         </is>
       </c>
       <c r="B1004" s="4" t="inlineStr">
@@ -28171,7 +28161,7 @@
     <row r="1005">
       <c r="A1005" s="4" t="inlineStr">
         <is>
-          <t>BA05-14</t>
+          <t>BA05-15</t>
         </is>
       </c>
       <c r="B1005" s="4" t="inlineStr">
@@ -28197,7 +28187,7 @@
     <row r="1006">
       <c r="A1006" s="4" t="inlineStr">
         <is>
-          <t>BA05-15</t>
+          <t>BA05-16</t>
         </is>
       </c>
       <c r="B1006" s="4" t="inlineStr">
@@ -28223,7 +28213,7 @@
     <row r="1007">
       <c r="A1007" s="4" t="inlineStr">
         <is>
-          <t>BA05-16</t>
+          <t>BA05-17</t>
         </is>
       </c>
       <c r="B1007" s="4" t="inlineStr">
@@ -28249,7 +28239,7 @@
     <row r="1008">
       <c r="A1008" s="4" t="inlineStr">
         <is>
-          <t>BA05-17</t>
+          <t>BA05-18</t>
         </is>
       </c>
       <c r="B1008" s="4" t="inlineStr">
@@ -28275,7 +28265,7 @@
     <row r="1009">
       <c r="A1009" s="4" t="inlineStr">
         <is>
-          <t>BA05-18</t>
+          <t>BA05-19</t>
         </is>
       </c>
       <c r="B1009" s="4" t="inlineStr">
@@ -28301,7 +28291,7 @@
     <row r="1010">
       <c r="A1010" s="4" t="inlineStr">
         <is>
-          <t>BA05-19</t>
+          <t>BA05-20</t>
         </is>
       </c>
       <c r="B1010" s="4" t="inlineStr">
@@ -28327,7 +28317,7 @@
     <row r="1011">
       <c r="A1011" s="4" t="inlineStr">
         <is>
-          <t>BA05-20</t>
+          <t>BA05-21</t>
         </is>
       </c>
       <c r="B1011" s="4" t="inlineStr">
@@ -28353,7 +28343,7 @@
     <row r="1012">
       <c r="A1012" s="4" t="inlineStr">
         <is>
-          <t>BA05-21</t>
+          <t>BA05-22</t>
         </is>
       </c>
       <c r="B1012" s="4" t="inlineStr">
@@ -28379,7 +28369,7 @@
     <row r="1013">
       <c r="A1013" s="4" t="inlineStr">
         <is>
-          <t>BA05-22</t>
+          <t>BA05-23</t>
         </is>
       </c>
       <c r="B1013" s="4" t="inlineStr">
@@ -28405,7 +28395,7 @@
     <row r="1014">
       <c r="A1014" s="4" t="inlineStr">
         <is>
-          <t>BA05-23</t>
+          <t>BA05-24</t>
         </is>
       </c>
       <c r="B1014" s="4" t="inlineStr">
@@ -28431,7 +28421,7 @@
     <row r="1015">
       <c r="A1015" s="4" t="inlineStr">
         <is>
-          <t>BA05-24</t>
+          <t>BA05-25</t>
         </is>
       </c>
       <c r="B1015" s="4" t="inlineStr">
@@ -28457,7 +28447,7 @@
     <row r="1016">
       <c r="A1016" s="4" t="inlineStr">
         <is>
-          <t>BA05-25</t>
+          <t>BA05-26</t>
         </is>
       </c>
       <c r="B1016" s="4" t="inlineStr">
@@ -28483,7 +28473,7 @@
     <row r="1017">
       <c r="A1017" s="4" t="inlineStr">
         <is>
-          <t>BA05-26</t>
+          <t>BA05-27</t>
         </is>
       </c>
       <c r="B1017" s="4" t="inlineStr">
@@ -28509,7 +28499,7 @@
     <row r="1018">
       <c r="A1018" s="4" t="inlineStr">
         <is>
-          <t>BA05-27</t>
+          <t>BA05-28</t>
         </is>
       </c>
       <c r="B1018" s="4" t="inlineStr">
@@ -28535,7 +28525,7 @@
     <row r="1019">
       <c r="A1019" s="4" t="inlineStr">
         <is>
-          <t>BA05-28</t>
+          <t>BA05-29</t>
         </is>
       </c>
       <c r="B1019" s="4" t="inlineStr">
@@ -28561,7 +28551,7 @@
     <row r="1020">
       <c r="A1020" s="4" t="inlineStr">
         <is>
-          <t>BA05-29</t>
+          <t>BA05-30</t>
         </is>
       </c>
       <c r="B1020" s="4" t="inlineStr">
@@ -28587,7 +28577,7 @@
     <row r="1021">
       <c r="A1021" s="4" t="inlineStr">
         <is>
-          <t>BA05-30</t>
+          <t>BA05-31</t>
         </is>
       </c>
       <c r="B1021" s="4" t="inlineStr">
@@ -28613,7 +28603,7 @@
     <row r="1022">
       <c r="A1022" s="4" t="inlineStr">
         <is>
-          <t>BA05-31</t>
+          <t>BA05-32</t>
         </is>
       </c>
       <c r="B1022" s="4" t="inlineStr">
@@ -28639,7 +28629,7 @@
     <row r="1023">
       <c r="A1023" s="4" t="inlineStr">
         <is>
-          <t>BA05-32</t>
+          <t>BA05-33</t>
         </is>
       </c>
       <c r="B1023" s="4" t="inlineStr">
@@ -28665,7 +28655,7 @@
     <row r="1024">
       <c r="A1024" s="4" t="inlineStr">
         <is>
-          <t>BA05-33</t>
+          <t>BA05-34</t>
         </is>
       </c>
       <c r="B1024" s="4" t="inlineStr">
@@ -28691,7 +28681,7 @@
     <row r="1025">
       <c r="A1025" s="4" t="inlineStr">
         <is>
-          <t>BA05-34</t>
+          <t>BA05-35</t>
         </is>
       </c>
       <c r="B1025" s="4" t="inlineStr">
@@ -28717,7 +28707,7 @@
     <row r="1026">
       <c r="A1026" s="4" t="inlineStr">
         <is>
-          <t>BA05-35</t>
+          <t>BA05-36</t>
         </is>
       </c>
       <c r="B1026" s="4" t="inlineStr">
@@ -28743,7 +28733,7 @@
     <row r="1027">
       <c r="A1027" s="4" t="inlineStr">
         <is>
-          <t>BA05-36</t>
+          <t>BA05-37</t>
         </is>
       </c>
       <c r="B1027" s="4" t="inlineStr">
@@ -28769,7 +28759,7 @@
     <row r="1028">
       <c r="A1028" s="4" t="inlineStr">
         <is>
-          <t>BA05-37</t>
+          <t>BA05-38</t>
         </is>
       </c>
       <c r="B1028" s="4" t="inlineStr">
@@ -28795,7 +28785,7 @@
     <row r="1029">
       <c r="A1029" s="4" t="inlineStr">
         <is>
-          <t>BA05-38</t>
+          <t>BA05-39</t>
         </is>
       </c>
       <c r="B1029" s="4" t="inlineStr">
@@ -28821,7 +28811,7 @@
     <row r="1030">
       <c r="A1030" s="4" t="inlineStr">
         <is>
-          <t>BA05-39</t>
+          <t>BA05-40</t>
         </is>
       </c>
       <c r="B1030" s="4" t="inlineStr">
@@ -28847,7 +28837,7 @@
     <row r="1031">
       <c r="A1031" s="4" t="inlineStr">
         <is>
-          <t>BA05-40</t>
+          <t>BA06-01</t>
         </is>
       </c>
       <c r="B1031" s="4" t="inlineStr">
@@ -28862,7 +28852,7 @@
       </c>
       <c r="D1031" s="4" t="inlineStr">
         <is>
-          <t>Turnraum</t>
+          <t>Material / Turnraum</t>
         </is>
       </c>
       <c r="E1031" s="4" t="n"/>
@@ -28873,7 +28863,7 @@
     <row r="1032">
       <c r="A1032" s="4" t="inlineStr">
         <is>
-          <t>BA06-01</t>
+          <t>BA06-02</t>
         </is>
       </c>
       <c r="B1032" s="4" t="inlineStr">
@@ -28899,7 +28889,7 @@
     <row r="1033">
       <c r="A1033" s="4" t="inlineStr">
         <is>
-          <t>BA06-02</t>
+          <t>BA06-03</t>
         </is>
       </c>
       <c r="B1033" s="4" t="inlineStr">
@@ -28925,7 +28915,7 @@
     <row r="1034">
       <c r="A1034" s="4" t="inlineStr">
         <is>
-          <t>BA06-03</t>
+          <t>BA06-04</t>
         </is>
       </c>
       <c r="B1034" s="4" t="inlineStr">
@@ -28951,7 +28941,7 @@
     <row r="1035">
       <c r="A1035" s="4" t="inlineStr">
         <is>
-          <t>BA06-04</t>
+          <t>BA06-05</t>
         </is>
       </c>
       <c r="B1035" s="4" t="inlineStr">
@@ -28977,7 +28967,7 @@
     <row r="1036">
       <c r="A1036" s="4" t="inlineStr">
         <is>
-          <t>BA06-05</t>
+          <t>BA06-06</t>
         </is>
       </c>
       <c r="B1036" s="4" t="inlineStr">
@@ -29003,7 +28993,7 @@
     <row r="1037">
       <c r="A1037" s="4" t="inlineStr">
         <is>
-          <t>BA06-06</t>
+          <t>BA06-07</t>
         </is>
       </c>
       <c r="B1037" s="4" t="inlineStr">
@@ -29029,7 +29019,7 @@
     <row r="1038">
       <c r="A1038" s="4" t="inlineStr">
         <is>
-          <t>BA06-07</t>
+          <t>BA06-08</t>
         </is>
       </c>
       <c r="B1038" s="4" t="inlineStr">
@@ -29055,7 +29045,7 @@
     <row r="1039">
       <c r="A1039" s="4" t="inlineStr">
         <is>
-          <t>BA06-08</t>
+          <t>BA06-09</t>
         </is>
       </c>
       <c r="B1039" s="4" t="inlineStr">
@@ -29081,7 +29071,7 @@
     <row r="1040">
       <c r="A1040" s="4" t="inlineStr">
         <is>
-          <t>BA06-09</t>
+          <t>BA06-10</t>
         </is>
       </c>
       <c r="B1040" s="4" t="inlineStr">
@@ -29107,7 +29097,7 @@
     <row r="1041">
       <c r="A1041" s="4" t="inlineStr">
         <is>
-          <t>BA06-10</t>
+          <t>BA06-11</t>
         </is>
       </c>
       <c r="B1041" s="4" t="inlineStr">
@@ -29133,7 +29123,7 @@
     <row r="1042">
       <c r="A1042" s="4" t="inlineStr">
         <is>
-          <t>BA06-11</t>
+          <t>BA06-12</t>
         </is>
       </c>
       <c r="B1042" s="4" t="inlineStr">
@@ -29159,7 +29149,7 @@
     <row r="1043">
       <c r="A1043" s="4" t="inlineStr">
         <is>
-          <t>BA06-12</t>
+          <t>BA06-13</t>
         </is>
       </c>
       <c r="B1043" s="4" t="inlineStr">
@@ -29185,7 +29175,7 @@
     <row r="1044">
       <c r="A1044" s="4" t="inlineStr">
         <is>
-          <t>BA06-13</t>
+          <t>BA06-14</t>
         </is>
       </c>
       <c r="B1044" s="4" t="inlineStr">
@@ -29211,7 +29201,7 @@
     <row r="1045">
       <c r="A1045" s="4" t="inlineStr">
         <is>
-          <t>BA06-14</t>
+          <t>BA06-15</t>
         </is>
       </c>
       <c r="B1045" s="4" t="inlineStr">
@@ -29237,7 +29227,7 @@
     <row r="1046">
       <c r="A1046" s="4" t="inlineStr">
         <is>
-          <t>BA06-15</t>
+          <t>BA07-01</t>
         </is>
       </c>
       <c r="B1046" s="4" t="inlineStr">
@@ -29252,7 +29242,7 @@
       </c>
       <c r="D1046" s="4" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Klassenzimmer</t>
         </is>
       </c>
       <c r="E1046" s="4" t="n"/>
@@ -29263,7 +29253,7 @@
     <row r="1047">
       <c r="A1047" s="4" t="inlineStr">
         <is>
-          <t>BA07-01</t>
+          <t>BA07-02</t>
         </is>
       </c>
       <c r="B1047" s="4" t="inlineStr">
@@ -29289,7 +29279,7 @@
     <row r="1048">
       <c r="A1048" s="4" t="inlineStr">
         <is>
-          <t>BA07-02</t>
+          <t>BA07-03</t>
         </is>
       </c>
       <c r="B1048" s="4" t="inlineStr">
@@ -29315,7 +29305,7 @@
     <row r="1049">
       <c r="A1049" s="4" t="inlineStr">
         <is>
-          <t>BA07-03</t>
+          <t>BA07-04</t>
         </is>
       </c>
       <c r="B1049" s="4" t="inlineStr">
@@ -29341,7 +29331,7 @@
     <row r="1050">
       <c r="A1050" s="4" t="inlineStr">
         <is>
-          <t>BA07-04</t>
+          <t>BA07-05</t>
         </is>
       </c>
       <c r="B1050" s="4" t="inlineStr">
@@ -29367,7 +29357,7 @@
     <row r="1051">
       <c r="A1051" s="4" t="inlineStr">
         <is>
-          <t>BA07-05</t>
+          <t>BA07-06</t>
         </is>
       </c>
       <c r="B1051" s="4" t="inlineStr">
@@ -29393,7 +29383,7 @@
     <row r="1052">
       <c r="A1052" s="4" t="inlineStr">
         <is>
-          <t>BA07-06</t>
+          <t>BA07-07</t>
         </is>
       </c>
       <c r="B1052" s="4" t="inlineStr">
@@ -29419,7 +29409,7 @@
     <row r="1053">
       <c r="A1053" s="4" t="inlineStr">
         <is>
-          <t>BA07-07</t>
+          <t>BA07-08</t>
         </is>
       </c>
       <c r="B1053" s="4" t="inlineStr">
@@ -29445,7 +29435,7 @@
     <row r="1054">
       <c r="A1054" s="4" t="inlineStr">
         <is>
-          <t>BA07-08</t>
+          <t>BA07-09</t>
         </is>
       </c>
       <c r="B1054" s="4" t="inlineStr">
@@ -29471,7 +29461,7 @@
     <row r="1055">
       <c r="A1055" s="4" t="inlineStr">
         <is>
-          <t>BA07-09</t>
+          <t>BA07-10</t>
         </is>
       </c>
       <c r="B1055" s="4" t="inlineStr">
@@ -29497,7 +29487,7 @@
     <row r="1056">
       <c r="A1056" s="4" t="inlineStr">
         <is>
-          <t>BA07-10</t>
+          <t>BA07-11</t>
         </is>
       </c>
       <c r="B1056" s="4" t="inlineStr">
@@ -29523,7 +29513,7 @@
     <row r="1057">
       <c r="A1057" s="4" t="inlineStr">
         <is>
-          <t>BA07-11</t>
+          <t>BA07-12</t>
         </is>
       </c>
       <c r="B1057" s="4" t="inlineStr">
@@ -29549,7 +29539,7 @@
     <row r="1058">
       <c r="A1058" s="4" t="inlineStr">
         <is>
-          <t>BA07-12</t>
+          <t>BA07-13</t>
         </is>
       </c>
       <c r="B1058" s="4" t="inlineStr">
@@ -29575,7 +29565,7 @@
     <row r="1059">
       <c r="A1059" s="4" t="inlineStr">
         <is>
-          <t>BA07-13</t>
+          <t>BA07-14</t>
         </is>
       </c>
       <c r="B1059" s="4" t="inlineStr">
@@ -29601,7 +29591,7 @@
     <row r="1060">
       <c r="A1060" s="4" t="inlineStr">
         <is>
-          <t>BA07-14</t>
+          <t>BA07-15</t>
         </is>
       </c>
       <c r="B1060" s="4" t="inlineStr">
@@ -29625,35 +29615,45 @@
       <c r="H1060" s="4" t="n"/>
     </row>
     <row r="1061">
-      <c r="A1061" s="4" t="inlineStr">
-        <is>
-          <t>BA07-15</t>
-        </is>
-      </c>
-      <c r="B1061" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1061" s="4" t="inlineStr">
+      <c r="A1061" s="2" t="inlineStr">
+        <is>
+          <t>BA08-01</t>
+        </is>
+      </c>
+      <c r="B1061" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1061" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1061" s="4" t="inlineStr">
-        <is>
-          <t>Klassenzimmer</t>
-        </is>
-      </c>
-      <c r="E1061" s="4" t="n"/>
-      <c r="F1061" s="3" t="n"/>
-      <c r="G1061" s="4" t="n"/>
-      <c r="H1061" s="4" t="n"/>
+      <c r="D1061" s="2" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="E1061" s="2" t="inlineStr">
+        <is>
+          <t>Konvolut Mal- und Bastelfarben</t>
+        </is>
+      </c>
+      <c r="F1061" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1061" s="2" t="inlineStr">
+        <is>
+          <t>Konvolut</t>
+        </is>
+      </c>
+      <c r="H1061" s="2" t="n"/>
     </row>
     <row r="1062">
       <c r="A1062" s="2" t="inlineStr">
         <is>
-          <t>BA08-01</t>
+          <t>BA08-02</t>
         </is>
       </c>
       <c r="B1062" s="2" t="inlineStr">
@@ -29673,7 +29673,7 @@
       </c>
       <c r="E1062" s="2" t="inlineStr">
         <is>
-          <t>Konvolut Mal- und Bastelfarben</t>
+          <t>Acrylfarben-Sortiment im Holzkasten</t>
         </is>
       </c>
       <c r="F1062" s="3" t="n">
@@ -29689,7 +29689,7 @@
     <row r="1063">
       <c r="A1063" s="2" t="inlineStr">
         <is>
-          <t>BA08-02</t>
+          <t>BA08-03</t>
         </is>
       </c>
       <c r="B1063" s="2" t="inlineStr">
@@ -29709,7 +29709,7 @@
       </c>
       <c r="E1063" s="2" t="inlineStr">
         <is>
-          <t>Acrylfarben-Sortiment im Holzkasten</t>
+          <t>Konvolut Bastelmaterial</t>
         </is>
       </c>
       <c r="F1063" s="3" t="n">
@@ -29725,7 +29725,7 @@
     <row r="1064">
       <c r="A1064" s="2" t="inlineStr">
         <is>
-          <t>BA08-03</t>
+          <t>BA08-04</t>
         </is>
       </c>
       <c r="B1064" s="2" t="inlineStr">
@@ -29745,7 +29745,7 @@
       </c>
       <c r="E1064" s="2" t="inlineStr">
         <is>
-          <t>Konvolut Bastelmaterial</t>
+          <t>buntes Papier</t>
         </is>
       </c>
       <c r="F1064" s="3" t="n">
@@ -29759,45 +29759,35 @@
       <c r="H1064" s="2" t="n"/>
     </row>
     <row r="1065">
-      <c r="A1065" s="2" t="inlineStr">
-        <is>
-          <t>BA08-04</t>
-        </is>
-      </c>
-      <c r="B1065" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1065" s="2" t="inlineStr">
+      <c r="A1065" s="4" t="inlineStr">
+        <is>
+          <t>BA08-05</t>
+        </is>
+      </c>
+      <c r="B1065" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1065" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1065" s="2" t="inlineStr">
+      <c r="D1065" s="4" t="inlineStr">
         <is>
           <t>Atelier</t>
         </is>
       </c>
-      <c r="E1065" s="2" t="inlineStr">
-        <is>
-          <t>buntes Papier</t>
-        </is>
-      </c>
-      <c r="F1065" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1065" s="2" t="inlineStr">
-        <is>
-          <t>Konvolut</t>
-        </is>
-      </c>
-      <c r="H1065" s="2" t="n"/>
+      <c r="E1065" s="4" t="n"/>
+      <c r="F1065" s="3" t="n"/>
+      <c r="G1065" s="4" t="n"/>
+      <c r="H1065" s="4" t="n"/>
     </row>
     <row r="1066">
       <c r="A1066" s="4" t="inlineStr">
         <is>
-          <t>BA08-05</t>
+          <t>BA08-06</t>
         </is>
       </c>
       <c r="B1066" s="4" t="inlineStr">
@@ -29823,7 +29813,7 @@
     <row r="1067">
       <c r="A1067" s="4" t="inlineStr">
         <is>
-          <t>BA08-06</t>
+          <t>BA08-07</t>
         </is>
       </c>
       <c r="B1067" s="4" t="inlineStr">
@@ -29849,7 +29839,7 @@
     <row r="1068">
       <c r="A1068" s="4" t="inlineStr">
         <is>
-          <t>BA08-07</t>
+          <t>BA08-08</t>
         </is>
       </c>
       <c r="B1068" s="4" t="inlineStr">
@@ -29875,7 +29865,7 @@
     <row r="1069">
       <c r="A1069" s="4" t="inlineStr">
         <is>
-          <t>BA08-08</t>
+          <t>BA08-09</t>
         </is>
       </c>
       <c r="B1069" s="4" t="inlineStr">
@@ -29901,7 +29891,7 @@
     <row r="1070">
       <c r="A1070" s="4" t="inlineStr">
         <is>
-          <t>BA08-09</t>
+          <t>BA08-10</t>
         </is>
       </c>
       <c r="B1070" s="4" t="inlineStr">
@@ -29927,7 +29917,7 @@
     <row r="1071">
       <c r="A1071" s="4" t="inlineStr">
         <is>
-          <t>BA08-10</t>
+          <t>BA08-11</t>
         </is>
       </c>
       <c r="B1071" s="4" t="inlineStr">
@@ -29953,7 +29943,7 @@
     <row r="1072">
       <c r="A1072" s="4" t="inlineStr">
         <is>
-          <t>BA08-11</t>
+          <t>BA08-12</t>
         </is>
       </c>
       <c r="B1072" s="4" t="inlineStr">
@@ -29979,7 +29969,7 @@
     <row r="1073">
       <c r="A1073" s="4" t="inlineStr">
         <is>
-          <t>BA08-12</t>
+          <t>BA08-13</t>
         </is>
       </c>
       <c r="B1073" s="4" t="inlineStr">
@@ -30005,7 +29995,7 @@
     <row r="1074">
       <c r="A1074" s="4" t="inlineStr">
         <is>
-          <t>BA08-13</t>
+          <t>BA08-14</t>
         </is>
       </c>
       <c r="B1074" s="4" t="inlineStr">
@@ -30031,7 +30021,7 @@
     <row r="1075">
       <c r="A1075" s="4" t="inlineStr">
         <is>
-          <t>BA08-14</t>
+          <t>BA08-15</t>
         </is>
       </c>
       <c r="B1075" s="4" t="inlineStr">
@@ -30057,7 +30047,7 @@
     <row r="1076">
       <c r="A1076" s="4" t="inlineStr">
         <is>
-          <t>BA08-15</t>
+          <t>BA08-16</t>
         </is>
       </c>
       <c r="B1076" s="4" t="inlineStr">
@@ -30083,7 +30073,7 @@
     <row r="1077">
       <c r="A1077" s="4" t="inlineStr">
         <is>
-          <t>BA08-16</t>
+          <t>BA08-17</t>
         </is>
       </c>
       <c r="B1077" s="4" t="inlineStr">
@@ -30109,7 +30099,7 @@
     <row r="1078">
       <c r="A1078" s="4" t="inlineStr">
         <is>
-          <t>BA08-17</t>
+          <t>BA08-18</t>
         </is>
       </c>
       <c r="B1078" s="4" t="inlineStr">
@@ -30135,7 +30125,7 @@
     <row r="1079">
       <c r="A1079" s="4" t="inlineStr">
         <is>
-          <t>BA08-18</t>
+          <t>BA08-19</t>
         </is>
       </c>
       <c r="B1079" s="4" t="inlineStr">
@@ -30161,7 +30151,7 @@
     <row r="1080">
       <c r="A1080" s="4" t="inlineStr">
         <is>
-          <t>BA08-19</t>
+          <t>BA08-20</t>
         </is>
       </c>
       <c r="B1080" s="4" t="inlineStr">
@@ -30187,7 +30177,7 @@
     <row r="1081">
       <c r="A1081" s="4" t="inlineStr">
         <is>
-          <t>BA08-20</t>
+          <t>BA08-21</t>
         </is>
       </c>
       <c r="B1081" s="4" t="inlineStr">
@@ -30213,7 +30203,7 @@
     <row r="1082">
       <c r="A1082" s="4" t="inlineStr">
         <is>
-          <t>BA08-21</t>
+          <t>BA08-22</t>
         </is>
       </c>
       <c r="B1082" s="4" t="inlineStr">
@@ -30239,7 +30229,7 @@
     <row r="1083">
       <c r="A1083" s="4" t="inlineStr">
         <is>
-          <t>BA08-22</t>
+          <t>BA08-23</t>
         </is>
       </c>
       <c r="B1083" s="4" t="inlineStr">
@@ -30265,7 +30255,7 @@
     <row r="1084">
       <c r="A1084" s="4" t="inlineStr">
         <is>
-          <t>BA08-23</t>
+          <t>BA08-24</t>
         </is>
       </c>
       <c r="B1084" s="4" t="inlineStr">
@@ -30291,7 +30281,7 @@
     <row r="1085">
       <c r="A1085" s="4" t="inlineStr">
         <is>
-          <t>BA08-24</t>
+          <t>BA08-25</t>
         </is>
       </c>
       <c r="B1085" s="4" t="inlineStr">
@@ -30315,35 +30305,45 @@
       <c r="H1085" s="4" t="n"/>
     </row>
     <row r="1086">
-      <c r="A1086" s="4" t="inlineStr">
-        <is>
-          <t>BA08-25</t>
-        </is>
-      </c>
-      <c r="B1086" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1086" s="4" t="inlineStr">
+      <c r="A1086" s="2" t="inlineStr">
+        <is>
+          <t>BA09-01</t>
+        </is>
+      </c>
+      <c r="B1086" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1086" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1086" s="4" t="inlineStr">
-        <is>
-          <t>Atelier</t>
-        </is>
-      </c>
-      <c r="E1086" s="4" t="n"/>
-      <c r="F1086" s="3" t="n"/>
-      <c r="G1086" s="4" t="n"/>
-      <c r="H1086" s="4" t="n"/>
+      <c r="D1086" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="E1086" s="2" t="inlineStr">
+        <is>
+          <t>Deko Metallruten mit Pompons</t>
+        </is>
+      </c>
+      <c r="F1086" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1086" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1086" s="2" t="n"/>
     </row>
     <row r="1087">
       <c r="A1087" s="2" t="inlineStr">
         <is>
-          <t>BA09-01</t>
+          <t>BA09-02</t>
         </is>
       </c>
       <c r="B1087" s="2" t="inlineStr">
@@ -30363,15 +30363,15 @@
       </c>
       <c r="E1087" s="2" t="inlineStr">
         <is>
-          <t>Deko Metallruten mit Pompons</t>
+          <t>Elefantenfuß groß</t>
         </is>
       </c>
       <c r="F1087" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1087" s="2" t="inlineStr">
         <is>
-          <t>Stück</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="H1087" s="2" t="n"/>
@@ -30379,7 +30379,7 @@
     <row r="1088">
       <c r="A1088" s="2" t="inlineStr">
         <is>
-          <t>BA09-02</t>
+          <t>BA09-03</t>
         </is>
       </c>
       <c r="B1088" s="2" t="inlineStr">
@@ -30399,7 +30399,7 @@
       </c>
       <c r="E1088" s="2" t="inlineStr">
         <is>
-          <t>Elefantenfuß groß</t>
+          <t>Werte-Rad</t>
         </is>
       </c>
       <c r="F1088" s="3" t="n">
@@ -30407,7 +30407,7 @@
       </c>
       <c r="G1088" s="2" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Stück</t>
         </is>
       </c>
       <c r="H1088" s="2" t="n"/>
@@ -30415,7 +30415,7 @@
     <row r="1089">
       <c r="A1089" s="2" t="inlineStr">
         <is>
-          <t>BA09-03</t>
+          <t>BA09-04</t>
         </is>
       </c>
       <c r="B1089" s="2" t="inlineStr">
@@ -30435,7 +30435,7 @@
       </c>
       <c r="E1089" s="2" t="inlineStr">
         <is>
-          <t>Werte-Rad</t>
+          <t>USM Haller Tisch</t>
         </is>
       </c>
       <c r="F1089" s="3" t="n">
@@ -30451,7 +30451,7 @@
     <row r="1090">
       <c r="A1090" s="2" t="inlineStr">
         <is>
-          <t>BA09-04</t>
+          <t>BA09-05</t>
         </is>
       </c>
       <c r="B1090" s="2" t="inlineStr">
@@ -30471,11 +30471,11 @@
       </c>
       <c r="E1090" s="2" t="inlineStr">
         <is>
-          <t>USM Haller Tisch</t>
+          <t>Kartell Masters Stuhl</t>
         </is>
       </c>
       <c r="F1090" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1090" s="2" t="inlineStr">
         <is>
@@ -30485,45 +30485,35 @@
       <c r="H1090" s="2" t="n"/>
     </row>
     <row r="1091">
-      <c r="A1091" s="2" t="inlineStr">
-        <is>
-          <t>BA09-05</t>
-        </is>
-      </c>
-      <c r="B1091" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1091" s="2" t="inlineStr">
+      <c r="A1091" s="4" t="inlineStr">
+        <is>
+          <t>BA09-06</t>
+        </is>
+      </c>
+      <c r="B1091" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1091" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1091" s="2" t="inlineStr">
+      <c r="D1091" s="4" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="E1091" s="2" t="inlineStr">
-        <is>
-          <t>Kartell Masters Stuhl</t>
-        </is>
-      </c>
-      <c r="F1091" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G1091" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1091" s="2" t="n"/>
+      <c r="E1091" s="4" t="n"/>
+      <c r="F1091" s="3" t="n"/>
+      <c r="G1091" s="4" t="n"/>
+      <c r="H1091" s="4" t="n"/>
     </row>
     <row r="1092">
       <c r="A1092" s="4" t="inlineStr">
         <is>
-          <t>BA09-06</t>
+          <t>BA09-07</t>
         </is>
       </c>
       <c r="B1092" s="4" t="inlineStr">
@@ -30549,7 +30539,7 @@
     <row r="1093">
       <c r="A1093" s="4" t="inlineStr">
         <is>
-          <t>BA09-07</t>
+          <t>BA09-08</t>
         </is>
       </c>
       <c r="B1093" s="4" t="inlineStr">
@@ -30575,7 +30565,7 @@
     <row r="1094">
       <c r="A1094" s="4" t="inlineStr">
         <is>
-          <t>BA09-08</t>
+          <t>BA09-09</t>
         </is>
       </c>
       <c r="B1094" s="4" t="inlineStr">
@@ -30601,7 +30591,7 @@
     <row r="1095">
       <c r="A1095" s="4" t="inlineStr">
         <is>
-          <t>BA09-09</t>
+          <t>BA09-10</t>
         </is>
       </c>
       <c r="B1095" s="4" t="inlineStr">
@@ -30627,7 +30617,7 @@
     <row r="1096">
       <c r="A1096" s="4" t="inlineStr">
         <is>
-          <t>BA09-10</t>
+          <t>BA09-11</t>
         </is>
       </c>
       <c r="B1096" s="4" t="inlineStr">
@@ -30653,7 +30643,7 @@
     <row r="1097">
       <c r="A1097" s="4" t="inlineStr">
         <is>
-          <t>BA09-11</t>
+          <t>BA09-12</t>
         </is>
       </c>
       <c r="B1097" s="4" t="inlineStr">
@@ -30679,7 +30669,7 @@
     <row r="1098">
       <c r="A1098" s="4" t="inlineStr">
         <is>
-          <t>BA09-12</t>
+          <t>BA09-13</t>
         </is>
       </c>
       <c r="B1098" s="4" t="inlineStr">
@@ -30705,7 +30695,7 @@
     <row r="1099">
       <c r="A1099" s="4" t="inlineStr">
         <is>
-          <t>BA09-13</t>
+          <t>BA09-14</t>
         </is>
       </c>
       <c r="B1099" s="4" t="inlineStr">
@@ -30731,7 +30721,7 @@
     <row r="1100">
       <c r="A1100" s="4" t="inlineStr">
         <is>
-          <t>BA09-14</t>
+          <t>BA09-15</t>
         </is>
       </c>
       <c r="B1100" s="4" t="inlineStr">
@@ -30755,35 +30745,45 @@
       <c r="H1100" s="4" t="n"/>
     </row>
     <row r="1101">
-      <c r="A1101" s="4" t="inlineStr">
-        <is>
-          <t>BA09-15</t>
-        </is>
-      </c>
-      <c r="B1101" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1101" s="4" t="inlineStr">
+      <c r="A1101" s="2" t="inlineStr">
+        <is>
+          <t>BA10-01</t>
+        </is>
+      </c>
+      <c r="B1101" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1101" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1101" s="4" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="E1101" s="4" t="n"/>
-      <c r="F1101" s="3" t="n"/>
-      <c r="G1101" s="4" t="n"/>
-      <c r="H1101" s="4" t="n"/>
+      <c r="D1101" s="2" t="inlineStr">
+        <is>
+          <t>Ruhe- / Schlafraum</t>
+        </is>
+      </c>
+      <c r="E1101" s="2" t="inlineStr">
+        <is>
+          <t>Glastisch rund mit Chromgestell</t>
+        </is>
+      </c>
+      <c r="F1101" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1101" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1101" s="2" t="n"/>
     </row>
     <row r="1102">
       <c r="A1102" s="2" t="inlineStr">
         <is>
-          <t>BA10-01</t>
+          <t>BA10-02</t>
         </is>
       </c>
       <c r="B1102" s="2" t="inlineStr">
@@ -30803,11 +30803,11 @@
       </c>
       <c r="E1102" s="2" t="inlineStr">
         <is>
-          <t>Glastisch rund mit Chromgestell</t>
+          <t>Samtsofa bordeaux, 2-Sitzer</t>
         </is>
       </c>
       <c r="F1102" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1102" s="2" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
     <row r="1103">
       <c r="A1103" s="2" t="inlineStr">
         <is>
-          <t>BA10-02</t>
+          <t>BA10-03</t>
         </is>
       </c>
       <c r="B1103" s="2" t="inlineStr">
@@ -30839,7 +30839,7 @@
       </c>
       <c r="E1103" s="2" t="inlineStr">
         <is>
-          <t>Samtsofa bordeaux, 2-Sitzer</t>
+          <t>Sessel mit Bezug, weiß lackiert</t>
         </is>
       </c>
       <c r="F1103" s="3" t="n">
@@ -30855,7 +30855,7 @@
     <row r="1104">
       <c r="A1104" s="2" t="inlineStr">
         <is>
-          <t>BA10-03</t>
+          <t>BA10-04</t>
         </is>
       </c>
       <c r="B1104" s="2" t="inlineStr">
@@ -30875,7 +30875,7 @@
       </c>
       <c r="E1104" s="2" t="inlineStr">
         <is>
-          <t>Sessel mit Bezug, weiß lackiert</t>
+          <t>Hocker grau mit Hairpin-Beinen</t>
         </is>
       </c>
       <c r="F1104" s="3" t="n">
@@ -30891,7 +30891,7 @@
     <row r="1105">
       <c r="A1105" s="2" t="inlineStr">
         <is>
-          <t>BA10-04</t>
+          <t>BA10-05</t>
         </is>
       </c>
       <c r="B1105" s="2" t="inlineStr">
@@ -30911,7 +30911,7 @@
       </c>
       <c r="E1105" s="2" t="inlineStr">
         <is>
-          <t>Hocker grau mit Hairpin-Beinen</t>
+          <t>Ohrensessel grau mit Kufengestell</t>
         </is>
       </c>
       <c r="F1105" s="3" t="n">
@@ -30927,7 +30927,7 @@
     <row r="1106">
       <c r="A1106" s="2" t="inlineStr">
         <is>
-          <t>BA10-05</t>
+          <t>BA10-06</t>
         </is>
       </c>
       <c r="B1106" s="2" t="inlineStr">
@@ -30947,7 +30947,7 @@
       </c>
       <c r="E1106" s="2" t="inlineStr">
         <is>
-          <t>Ohrensessel grau mit Kufengestell</t>
+          <t>Hocker grau, passend</t>
         </is>
       </c>
       <c r="F1106" s="3" t="n">
@@ -30963,7 +30963,7 @@
     <row r="1107">
       <c r="A1107" s="2" t="inlineStr">
         <is>
-          <t>BA10-06</t>
+          <t>BA10-07</t>
         </is>
       </c>
       <c r="B1107" s="2" t="inlineStr">
@@ -30983,11 +30983,11 @@
       </c>
       <c r="E1107" s="2" t="inlineStr">
         <is>
-          <t>Hocker grau, passend</t>
+          <t>Beistelltisch rund grau</t>
         </is>
       </c>
       <c r="F1107" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1107" s="2" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
     <row r="1108">
       <c r="A1108" s="2" t="inlineStr">
         <is>
-          <t>BA10-07</t>
+          <t>BA10-08</t>
         </is>
       </c>
       <c r="B1108" s="2" t="inlineStr">
@@ -31019,11 +31019,11 @@
       </c>
       <c r="E1108" s="2" t="inlineStr">
         <is>
-          <t>Beistelltisch rund grau</t>
+          <t>Pendelleuchte Drahtgeflecht</t>
         </is>
       </c>
       <c r="F1108" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1108" s="2" t="inlineStr">
         <is>
@@ -31033,45 +31033,35 @@
       <c r="H1108" s="2" t="n"/>
     </row>
     <row r="1109">
-      <c r="A1109" s="2" t="inlineStr">
-        <is>
-          <t>BA10-08</t>
-        </is>
-      </c>
-      <c r="B1109" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1109" s="2" t="inlineStr">
+      <c r="A1109" s="4" t="inlineStr">
+        <is>
+          <t>BA10-09</t>
+        </is>
+      </c>
+      <c r="B1109" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1109" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1109" s="2" t="inlineStr">
+      <c r="D1109" s="4" t="inlineStr">
         <is>
           <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
-      <c r="E1109" s="2" t="inlineStr">
-        <is>
-          <t>Pendelleuchte Drahtgeflecht</t>
-        </is>
-      </c>
-      <c r="F1109" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1109" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1109" s="2" t="n"/>
+      <c r="E1109" s="4" t="n"/>
+      <c r="F1109" s="3" t="n"/>
+      <c r="G1109" s="4" t="n"/>
+      <c r="H1109" s="4" t="n"/>
     </row>
     <row r="1110">
       <c r="A1110" s="4" t="inlineStr">
         <is>
-          <t>BA10-09</t>
+          <t>BA10-10</t>
         </is>
       </c>
       <c r="B1110" s="4" t="inlineStr">
@@ -31097,7 +31087,7 @@
     <row r="1111">
       <c r="A1111" s="4" t="inlineStr">
         <is>
-          <t>BA10-10</t>
+          <t>BA10-11</t>
         </is>
       </c>
       <c r="B1111" s="4" t="inlineStr">
@@ -31123,7 +31113,7 @@
     <row r="1112">
       <c r="A1112" s="4" t="inlineStr">
         <is>
-          <t>BA10-11</t>
+          <t>BA10-12</t>
         </is>
       </c>
       <c r="B1112" s="4" t="inlineStr">
@@ -31149,7 +31139,7 @@
     <row r="1113">
       <c r="A1113" s="4" t="inlineStr">
         <is>
-          <t>BA10-12</t>
+          <t>BA10-13</t>
         </is>
       </c>
       <c r="B1113" s="4" t="inlineStr">
@@ -31175,7 +31165,7 @@
     <row r="1114">
       <c r="A1114" s="4" t="inlineStr">
         <is>
-          <t>BA10-13</t>
+          <t>BA10-14</t>
         </is>
       </c>
       <c r="B1114" s="4" t="inlineStr">
@@ -31201,7 +31191,7 @@
     <row r="1115">
       <c r="A1115" s="4" t="inlineStr">
         <is>
-          <t>BA10-14</t>
+          <t>BA10-15</t>
         </is>
       </c>
       <c r="B1115" s="4" t="inlineStr">
@@ -31227,7 +31217,7 @@
     <row r="1116">
       <c r="A1116" s="4" t="inlineStr">
         <is>
-          <t>BA10-15</t>
+          <t>BA10-16</t>
         </is>
       </c>
       <c r="B1116" s="4" t="inlineStr">
@@ -31253,7 +31243,7 @@
     <row r="1117">
       <c r="A1117" s="4" t="inlineStr">
         <is>
-          <t>BA10-16</t>
+          <t>BA10-17</t>
         </is>
       </c>
       <c r="B1117" s="4" t="inlineStr">
@@ -31279,7 +31269,7 @@
     <row r="1118">
       <c r="A1118" s="4" t="inlineStr">
         <is>
-          <t>BA10-17</t>
+          <t>BA10-18</t>
         </is>
       </c>
       <c r="B1118" s="4" t="inlineStr">
@@ -31305,7 +31295,7 @@
     <row r="1119">
       <c r="A1119" s="4" t="inlineStr">
         <is>
-          <t>BA10-18</t>
+          <t>BA11-01</t>
         </is>
       </c>
       <c r="B1119" s="4" t="inlineStr">
@@ -31320,7 +31310,7 @@
       </c>
       <c r="D1119" s="4" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>WC Kinder</t>
         </is>
       </c>
       <c r="E1119" s="4" t="n"/>
@@ -31331,7 +31321,7 @@
     <row r="1120">
       <c r="A1120" s="4" t="inlineStr">
         <is>
-          <t>BA11-01</t>
+          <t>BA11-02</t>
         </is>
       </c>
       <c r="B1120" s="4" t="inlineStr">
@@ -31357,7 +31347,7 @@
     <row r="1121">
       <c r="A1121" s="4" t="inlineStr">
         <is>
-          <t>BA11-02</t>
+          <t>BA11-03</t>
         </is>
       </c>
       <c r="B1121" s="4" t="inlineStr">
@@ -31383,7 +31373,7 @@
     <row r="1122">
       <c r="A1122" s="4" t="inlineStr">
         <is>
-          <t>BA11-03</t>
+          <t>BA11-04</t>
         </is>
       </c>
       <c r="B1122" s="4" t="inlineStr">
@@ -31409,7 +31399,7 @@
     <row r="1123">
       <c r="A1123" s="4" t="inlineStr">
         <is>
-          <t>BA11-04</t>
+          <t>BA11-05</t>
         </is>
       </c>
       <c r="B1123" s="4" t="inlineStr">
@@ -31435,7 +31425,7 @@
     <row r="1124">
       <c r="A1124" s="4" t="inlineStr">
         <is>
-          <t>BA11-05</t>
+          <t>BA11-06</t>
         </is>
       </c>
       <c r="B1124" s="4" t="inlineStr">
@@ -31461,7 +31451,7 @@
     <row r="1125">
       <c r="A1125" s="4" t="inlineStr">
         <is>
-          <t>BA11-06</t>
+          <t>BA11-07</t>
         </is>
       </c>
       <c r="B1125" s="4" t="inlineStr">
@@ -31487,7 +31477,7 @@
     <row r="1126">
       <c r="A1126" s="4" t="inlineStr">
         <is>
-          <t>BA11-07</t>
+          <t>BA11-08</t>
         </is>
       </c>
       <c r="B1126" s="4" t="inlineStr">
@@ -31513,7 +31503,7 @@
     <row r="1127">
       <c r="A1127" s="4" t="inlineStr">
         <is>
-          <t>BA11-08</t>
+          <t>BA11-09</t>
         </is>
       </c>
       <c r="B1127" s="4" t="inlineStr">
@@ -31539,7 +31529,7 @@
     <row r="1128">
       <c r="A1128" s="4" t="inlineStr">
         <is>
-          <t>BA11-09</t>
+          <t>BA11-10</t>
         </is>
       </c>
       <c r="B1128" s="4" t="inlineStr">
@@ -31565,7 +31555,7 @@
     <row r="1129">
       <c r="A1129" s="4" t="inlineStr">
         <is>
-          <t>BA11-10</t>
+          <t>BA11-11</t>
         </is>
       </c>
       <c r="B1129" s="4" t="inlineStr">
@@ -31591,7 +31581,7 @@
     <row r="1130">
       <c r="A1130" s="4" t="inlineStr">
         <is>
-          <t>BA11-11</t>
+          <t>BA11-12</t>
         </is>
       </c>
       <c r="B1130" s="4" t="inlineStr">
@@ -31617,7 +31607,7 @@
     <row r="1131">
       <c r="A1131" s="4" t="inlineStr">
         <is>
-          <t>BA11-12</t>
+          <t>BA11-13</t>
         </is>
       </c>
       <c r="B1131" s="4" t="inlineStr">
@@ -31643,7 +31633,7 @@
     <row r="1132">
       <c r="A1132" s="4" t="inlineStr">
         <is>
-          <t>BA11-13</t>
+          <t>BA11-14</t>
         </is>
       </c>
       <c r="B1132" s="4" t="inlineStr">
@@ -31669,7 +31659,7 @@
     <row r="1133">
       <c r="A1133" s="4" t="inlineStr">
         <is>
-          <t>BA11-14</t>
+          <t>BA11-15</t>
         </is>
       </c>
       <c r="B1133" s="4" t="inlineStr">
@@ -31693,71 +31683,71 @@
       <c r="H1133" s="4" t="n"/>
     </row>
     <row r="1134">
-      <c r="A1134" s="4" t="inlineStr">
-        <is>
-          <t>BA11-15</t>
-        </is>
-      </c>
-      <c r="B1134" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1134" s="4" t="inlineStr">
+      <c r="A1134" s="2" t="inlineStr">
+        <is>
+          <t>BA12-01</t>
+        </is>
+      </c>
+      <c r="B1134" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1134" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1134" s="4" t="inlineStr">
-        <is>
-          <t>WC Kinder</t>
-        </is>
-      </c>
-      <c r="E1134" s="4" t="n"/>
-      <c r="F1134" s="3" t="n"/>
-      <c r="G1134" s="4" t="n"/>
-      <c r="H1134" s="4" t="n"/>
+      <c r="D1134" s="2" t="inlineStr">
+        <is>
+          <t>WC Personal</t>
+        </is>
+      </c>
+      <c r="E1134" s="2" t="inlineStr">
+        <is>
+          <t>Ast-Mobile mit Papierwaben</t>
+        </is>
+      </c>
+      <c r="F1134" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1134" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1134" s="2" t="n"/>
     </row>
     <row r="1135">
-      <c r="A1135" s="2" t="inlineStr">
-        <is>
-          <t>BA12-01</t>
-        </is>
-      </c>
-      <c r="B1135" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1135" s="2" t="inlineStr">
+      <c r="A1135" s="4" t="inlineStr">
+        <is>
+          <t>BA12-02</t>
+        </is>
+      </c>
+      <c r="B1135" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1135" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1135" s="2" t="inlineStr">
+      <c r="D1135" s="4" t="inlineStr">
         <is>
           <t>WC Personal</t>
         </is>
       </c>
-      <c r="E1135" s="2" t="inlineStr">
-        <is>
-          <t>Ast-Mobile mit Papierwaben</t>
-        </is>
-      </c>
-      <c r="F1135" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1135" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1135" s="2" t="n"/>
+      <c r="E1135" s="4" t="n"/>
+      <c r="F1135" s="3" t="n"/>
+      <c r="G1135" s="4" t="n"/>
+      <c r="H1135" s="4" t="n"/>
     </row>
     <row r="1136">
       <c r="A1136" s="4" t="inlineStr">
         <is>
-          <t>BA12-02</t>
+          <t>BA12-03</t>
         </is>
       </c>
       <c r="B1136" s="4" t="inlineStr">
@@ -31783,7 +31773,7 @@
     <row r="1137">
       <c r="A1137" s="4" t="inlineStr">
         <is>
-          <t>BA12-03</t>
+          <t>BA12-04</t>
         </is>
       </c>
       <c r="B1137" s="4" t="inlineStr">
@@ -31809,7 +31799,7 @@
     <row r="1138">
       <c r="A1138" s="4" t="inlineStr">
         <is>
-          <t>BA12-04</t>
+          <t>BA12-05</t>
         </is>
       </c>
       <c r="B1138" s="4" t="inlineStr">
@@ -31835,7 +31825,7 @@
     <row r="1139">
       <c r="A1139" s="4" t="inlineStr">
         <is>
-          <t>BA12-05</t>
+          <t>BA12-06</t>
         </is>
       </c>
       <c r="B1139" s="4" t="inlineStr">
@@ -31861,7 +31851,7 @@
     <row r="1140">
       <c r="A1140" s="4" t="inlineStr">
         <is>
-          <t>BA12-06</t>
+          <t>BA12-07</t>
         </is>
       </c>
       <c r="B1140" s="4" t="inlineStr">
@@ -31887,7 +31877,7 @@
     <row r="1141">
       <c r="A1141" s="4" t="inlineStr">
         <is>
-          <t>BA12-07</t>
+          <t>BA12-08</t>
         </is>
       </c>
       <c r="B1141" s="4" t="inlineStr">
@@ -31913,7 +31903,7 @@
     <row r="1142">
       <c r="A1142" s="4" t="inlineStr">
         <is>
-          <t>BA12-08</t>
+          <t>BA12-09</t>
         </is>
       </c>
       <c r="B1142" s="4" t="inlineStr">
@@ -31939,7 +31929,7 @@
     <row r="1143">
       <c r="A1143" s="4" t="inlineStr">
         <is>
-          <t>BA12-09</t>
+          <t>BA12-10</t>
         </is>
       </c>
       <c r="B1143" s="4" t="inlineStr">
@@ -31965,7 +31955,7 @@
     <row r="1144">
       <c r="A1144" s="4" t="inlineStr">
         <is>
-          <t>BA12-10</t>
+          <t>BA12-11</t>
         </is>
       </c>
       <c r="B1144" s="4" t="inlineStr">
@@ -31991,7 +31981,7 @@
     <row r="1145">
       <c r="A1145" s="4" t="inlineStr">
         <is>
-          <t>BA12-11</t>
+          <t>BA13-01</t>
         </is>
       </c>
       <c r="B1145" s="4" t="inlineStr">
@@ -32006,7 +31996,7 @@
       </c>
       <c r="D1145" s="4" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>Abstellraum</t>
         </is>
       </c>
       <c r="E1145" s="4" t="n"/>
@@ -32017,7 +32007,7 @@
     <row r="1146">
       <c r="A1146" s="4" t="inlineStr">
         <is>
-          <t>BA13-01</t>
+          <t>BA13-02</t>
         </is>
       </c>
       <c r="B1146" s="4" t="inlineStr">
@@ -32043,7 +32033,7 @@
     <row r="1147">
       <c r="A1147" s="4" t="inlineStr">
         <is>
-          <t>BA13-02</t>
+          <t>BA13-03</t>
         </is>
       </c>
       <c r="B1147" s="4" t="inlineStr">
@@ -32069,7 +32059,7 @@
     <row r="1148">
       <c r="A1148" s="4" t="inlineStr">
         <is>
-          <t>BA13-03</t>
+          <t>BA13-04</t>
         </is>
       </c>
       <c r="B1148" s="4" t="inlineStr">
@@ -32095,7 +32085,7 @@
     <row r="1149">
       <c r="A1149" s="4" t="inlineStr">
         <is>
-          <t>BA13-04</t>
+          <t>BA13-05</t>
         </is>
       </c>
       <c r="B1149" s="4" t="inlineStr">
@@ -32121,7 +32111,7 @@
     <row r="1150">
       <c r="A1150" s="4" t="inlineStr">
         <is>
-          <t>BA13-05</t>
+          <t>BA13-06</t>
         </is>
       </c>
       <c r="B1150" s="4" t="inlineStr">
@@ -32147,7 +32137,7 @@
     <row r="1151">
       <c r="A1151" s="4" t="inlineStr">
         <is>
-          <t>BA13-06</t>
+          <t>BA13-07</t>
         </is>
       </c>
       <c r="B1151" s="4" t="inlineStr">
@@ -32173,7 +32163,7 @@
     <row r="1152">
       <c r="A1152" s="4" t="inlineStr">
         <is>
-          <t>BA13-07</t>
+          <t>BA13-08</t>
         </is>
       </c>
       <c r="B1152" s="4" t="inlineStr">
@@ -32199,7 +32189,7 @@
     <row r="1153">
       <c r="A1153" s="4" t="inlineStr">
         <is>
-          <t>BA13-08</t>
+          <t>BA13-09</t>
         </is>
       </c>
       <c r="B1153" s="4" t="inlineStr">
@@ -32225,7 +32215,7 @@
     <row r="1154">
       <c r="A1154" s="4" t="inlineStr">
         <is>
-          <t>BA13-09</t>
+          <t>BA13-10</t>
         </is>
       </c>
       <c r="B1154" s="4" t="inlineStr">
@@ -32251,7 +32241,7 @@
     <row r="1155">
       <c r="A1155" s="4" t="inlineStr">
         <is>
-          <t>BA13-10</t>
+          <t>BA13-11</t>
         </is>
       </c>
       <c r="B1155" s="4" t="inlineStr">
@@ -32277,7 +32267,7 @@
     <row r="1156">
       <c r="A1156" s="4" t="inlineStr">
         <is>
-          <t>BA13-11</t>
+          <t>BA13-12</t>
         </is>
       </c>
       <c r="B1156" s="4" t="inlineStr">
@@ -32303,7 +32293,7 @@
     <row r="1157">
       <c r="A1157" s="4" t="inlineStr">
         <is>
-          <t>BA13-12</t>
+          <t>BA13-13</t>
         </is>
       </c>
       <c r="B1157" s="4" t="inlineStr">
@@ -32329,7 +32319,7 @@
     <row r="1158">
       <c r="A1158" s="4" t="inlineStr">
         <is>
-          <t>BA13-13</t>
+          <t>BA13-14</t>
         </is>
       </c>
       <c r="B1158" s="4" t="inlineStr">
@@ -32355,7 +32345,7 @@
     <row r="1159">
       <c r="A1159" s="4" t="inlineStr">
         <is>
-          <t>BA13-14</t>
+          <t>BA13-15</t>
         </is>
       </c>
       <c r="B1159" s="4" t="inlineStr">
@@ -32379,35 +32369,45 @@
       <c r="H1159" s="4" t="n"/>
     </row>
     <row r="1160">
-      <c r="A1160" s="4" t="inlineStr">
-        <is>
-          <t>BA13-15</t>
-        </is>
-      </c>
-      <c r="B1160" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1160" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1160" s="4" t="inlineStr">
-        <is>
-          <t>Abstellraum</t>
-        </is>
-      </c>
-      <c r="E1160" s="4" t="n"/>
-      <c r="F1160" s="3" t="n"/>
-      <c r="G1160" s="4" t="n"/>
-      <c r="H1160" s="4" t="n"/>
+      <c r="A1160" s="2" t="inlineStr">
+        <is>
+          <t>TE01-01</t>
+        </is>
+      </c>
+      <c r="B1160" s="2" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1160" s="2" t="inlineStr">
+        <is>
+          <t>ebenerdig</t>
+        </is>
+      </c>
+      <c r="D1160" s="2" t="inlineStr">
+        <is>
+          <t>Terrasse</t>
+        </is>
+      </c>
+      <c r="E1160" s="2" t="inlineStr">
+        <is>
+          <t>Biohort Freizeitbox weiß (Terrasse)</t>
+        </is>
+      </c>
+      <c r="F1160" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1160" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1160" s="2" t="n"/>
     </row>
     <row r="1161">
       <c r="A1161" s="2" t="inlineStr">
         <is>
-          <t>TE01-01</t>
+          <t>TE01-02</t>
         </is>
       </c>
       <c r="B1161" s="2" t="inlineStr">
@@ -32427,7 +32427,7 @@
       </c>
       <c r="E1161" s="2" t="inlineStr">
         <is>
-          <t>Biohort Freizeitbox weiß (Terrasse)</t>
+          <t>Gartentisch mit Granitplatte inkl. Stühle und Schutzhülle</t>
         </is>
       </c>
       <c r="F1161" s="3" t="n">
@@ -32443,7 +32443,7 @@
     <row r="1162">
       <c r="A1162" s="2" t="inlineStr">
         <is>
-          <t>TE01-02</t>
+          <t>TE01-03</t>
         </is>
       </c>
       <c r="B1162" s="2" t="inlineStr">
@@ -32463,11 +32463,11 @@
       </c>
       <c r="E1162" s="2" t="inlineStr">
         <is>
-          <t>Gartentisch mit Granitplatte inkl. Stühle und Schutzhülle</t>
+          <t>Textilene-Stapelsessel anthrazit</t>
         </is>
       </c>
       <c r="F1162" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1162" s="2" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
     <row r="1163">
       <c r="A1163" s="2" t="inlineStr">
         <is>
-          <t>TE01-03</t>
+          <t>TE01-04</t>
         </is>
       </c>
       <c r="B1163" s="2" t="inlineStr">
@@ -32499,11 +32499,11 @@
       </c>
       <c r="E1163" s="2" t="inlineStr">
         <is>
-          <t>Textilene-Stapelsessel anthrazit</t>
+          <t>Weber Genesis Gasgrill</t>
         </is>
       </c>
       <c r="F1163" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1163" s="2" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
     <row r="1164">
       <c r="A1164" s="2" t="inlineStr">
         <is>
-          <t>TE01-04</t>
+          <t>TE01-05</t>
         </is>
       </c>
       <c r="B1164" s="2" t="inlineStr">
@@ -32535,7 +32535,7 @@
       </c>
       <c r="E1164" s="2" t="inlineStr">
         <is>
-          <t>Weber Genesis Gasgrill</t>
+          <t>Sonnenschirm creme</t>
         </is>
       </c>
       <c r="F1164" s="3" t="n">
@@ -32549,45 +32549,35 @@
       <c r="H1164" s="2" t="n"/>
     </row>
     <row r="1165">
-      <c r="A1165" s="2" t="inlineStr">
-        <is>
-          <t>TE01-05</t>
-        </is>
-      </c>
-      <c r="B1165" s="2" t="inlineStr">
+      <c r="A1165" s="4" t="inlineStr">
+        <is>
+          <t>TE01-06</t>
+        </is>
+      </c>
+      <c r="B1165" s="4" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1165" s="2" t="inlineStr">
+      <c r="C1165" s="4" t="inlineStr">
         <is>
           <t>ebenerdig</t>
         </is>
       </c>
-      <c r="D1165" s="2" t="inlineStr">
+      <c r="D1165" s="4" t="inlineStr">
         <is>
           <t>Terrasse</t>
         </is>
       </c>
-      <c r="E1165" s="2" t="inlineStr">
-        <is>
-          <t>Sonnenschirm creme</t>
-        </is>
-      </c>
-      <c r="F1165" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1165" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1165" s="2" t="n"/>
+      <c r="E1165" s="4" t="n"/>
+      <c r="F1165" s="3" t="n"/>
+      <c r="G1165" s="4" t="n"/>
+      <c r="H1165" s="4" t="n"/>
     </row>
     <row r="1166">
       <c r="A1166" s="4" t="inlineStr">
         <is>
-          <t>TE01-06</t>
+          <t>TE01-07</t>
         </is>
       </c>
       <c r="B1166" s="4" t="inlineStr">
@@ -32613,7 +32603,7 @@
     <row r="1167">
       <c r="A1167" s="4" t="inlineStr">
         <is>
-          <t>TE01-07</t>
+          <t>TE01-08</t>
         </is>
       </c>
       <c r="B1167" s="4" t="inlineStr">
@@ -32639,7 +32629,7 @@
     <row r="1168">
       <c r="A1168" s="4" t="inlineStr">
         <is>
-          <t>TE01-08</t>
+          <t>TE01-09</t>
         </is>
       </c>
       <c r="B1168" s="4" t="inlineStr">
@@ -32665,7 +32655,7 @@
     <row r="1169">
       <c r="A1169" s="4" t="inlineStr">
         <is>
-          <t>TE01-09</t>
+          <t>TE01-10</t>
         </is>
       </c>
       <c r="B1169" s="4" t="inlineStr">
@@ -32691,7 +32681,7 @@
     <row r="1170">
       <c r="A1170" s="4" t="inlineStr">
         <is>
-          <t>TE01-10</t>
+          <t>TE01-11</t>
         </is>
       </c>
       <c r="B1170" s="4" t="inlineStr">
@@ -32717,7 +32707,7 @@
     <row r="1171">
       <c r="A1171" s="4" t="inlineStr">
         <is>
-          <t>TE01-11</t>
+          <t>TE01-12</t>
         </is>
       </c>
       <c r="B1171" s="4" t="inlineStr">
@@ -32743,7 +32733,7 @@
     <row r="1172">
       <c r="A1172" s="4" t="inlineStr">
         <is>
-          <t>TE01-12</t>
+          <t>TE01-13</t>
         </is>
       </c>
       <c r="B1172" s="4" t="inlineStr">
@@ -32769,7 +32759,7 @@
     <row r="1173">
       <c r="A1173" s="4" t="inlineStr">
         <is>
-          <t>TE01-13</t>
+          <t>TE01-14</t>
         </is>
       </c>
       <c r="B1173" s="4" t="inlineStr">
@@ -32795,7 +32785,7 @@
     <row r="1174">
       <c r="A1174" s="4" t="inlineStr">
         <is>
-          <t>TE01-14</t>
+          <t>TE01-15</t>
         </is>
       </c>
       <c r="B1174" s="4" t="inlineStr">
@@ -32821,7 +32811,7 @@
     <row r="1175">
       <c r="A1175" s="4" t="inlineStr">
         <is>
-          <t>TE01-15</t>
+          <t>TE01-16</t>
         </is>
       </c>
       <c r="B1175" s="4" t="inlineStr">
@@ -32847,7 +32837,7 @@
     <row r="1176">
       <c r="A1176" s="4" t="inlineStr">
         <is>
-          <t>TE01-16</t>
+          <t>TE01-17</t>
         </is>
       </c>
       <c r="B1176" s="4" t="inlineStr">
@@ -32873,7 +32863,7 @@
     <row r="1177">
       <c r="A1177" s="4" t="inlineStr">
         <is>
-          <t>TE01-17</t>
+          <t>TE01-18</t>
         </is>
       </c>
       <c r="B1177" s="4" t="inlineStr">
@@ -32899,7 +32889,7 @@
     <row r="1178">
       <c r="A1178" s="4" t="inlineStr">
         <is>
-          <t>TE01-18</t>
+          <t>TE01-19</t>
         </is>
       </c>
       <c r="B1178" s="4" t="inlineStr">
@@ -32925,7 +32915,7 @@
     <row r="1179">
       <c r="A1179" s="4" t="inlineStr">
         <is>
-          <t>TE01-19</t>
+          <t>TE01-20</t>
         </is>
       </c>
       <c r="B1179" s="4" t="inlineStr">
@@ -32951,7 +32941,7 @@
     <row r="1180">
       <c r="A1180" s="4" t="inlineStr">
         <is>
-          <t>TE01-20</t>
+          <t>TE01-21</t>
         </is>
       </c>
       <c r="B1180" s="4" t="inlineStr">
@@ -32977,7 +32967,7 @@
     <row r="1181">
       <c r="A1181" s="4" t="inlineStr">
         <is>
-          <t>TE01-21</t>
+          <t>TE01-22</t>
         </is>
       </c>
       <c r="B1181" s="4" t="inlineStr">
@@ -33003,7 +32993,7 @@
     <row r="1182">
       <c r="A1182" s="4" t="inlineStr">
         <is>
-          <t>TE01-22</t>
+          <t>TE01-23</t>
         </is>
       </c>
       <c r="B1182" s="4" t="inlineStr">
@@ -33029,7 +33019,7 @@
     <row r="1183">
       <c r="A1183" s="4" t="inlineStr">
         <is>
-          <t>TE01-23</t>
+          <t>TE01-24</t>
         </is>
       </c>
       <c r="B1183" s="4" t="inlineStr">
@@ -33055,7 +33045,7 @@
     <row r="1184">
       <c r="A1184" s="4" t="inlineStr">
         <is>
-          <t>TE01-24</t>
+          <t>TE01-25</t>
         </is>
       </c>
       <c r="B1184" s="4" t="inlineStr">
@@ -33081,7 +33071,7 @@
     <row r="1185">
       <c r="A1185" s="4" t="inlineStr">
         <is>
-          <t>TE01-25</t>
+          <t>TE01-26</t>
         </is>
       </c>
       <c r="B1185" s="4" t="inlineStr">
@@ -33107,7 +33097,7 @@
     <row r="1186">
       <c r="A1186" s="4" t="inlineStr">
         <is>
-          <t>TE01-26</t>
+          <t>TE01-27</t>
         </is>
       </c>
       <c r="B1186" s="4" t="inlineStr">
@@ -33133,7 +33123,7 @@
     <row r="1187">
       <c r="A1187" s="4" t="inlineStr">
         <is>
-          <t>TE01-27</t>
+          <t>TE01-28</t>
         </is>
       </c>
       <c r="B1187" s="4" t="inlineStr">
@@ -33159,7 +33149,7 @@
     <row r="1188">
       <c r="A1188" s="4" t="inlineStr">
         <is>
-          <t>TE01-28</t>
+          <t>TE01-29</t>
         </is>
       </c>
       <c r="B1188" s="4" t="inlineStr">
@@ -33185,7 +33175,7 @@
     <row r="1189">
       <c r="A1189" s="4" t="inlineStr">
         <is>
-          <t>TE01-29</t>
+          <t>TE01-30</t>
         </is>
       </c>
       <c r="B1189" s="4" t="inlineStr">
@@ -33211,7 +33201,7 @@
     <row r="1190">
       <c r="A1190" s="4" t="inlineStr">
         <is>
-          <t>TE01-30</t>
+          <t>TE01-31</t>
         </is>
       </c>
       <c r="B1190" s="4" t="inlineStr">
@@ -33237,7 +33227,7 @@
     <row r="1191">
       <c r="A1191" s="4" t="inlineStr">
         <is>
-          <t>TE01-31</t>
+          <t>TE01-32</t>
         </is>
       </c>
       <c r="B1191" s="4" t="inlineStr">
@@ -33263,7 +33253,7 @@
     <row r="1192">
       <c r="A1192" s="4" t="inlineStr">
         <is>
-          <t>TE01-32</t>
+          <t>TE01-33</t>
         </is>
       </c>
       <c r="B1192" s="4" t="inlineStr">
@@ -33289,7 +33279,7 @@
     <row r="1193">
       <c r="A1193" s="4" t="inlineStr">
         <is>
-          <t>TE01-33</t>
+          <t>TE01-34</t>
         </is>
       </c>
       <c r="B1193" s="4" t="inlineStr">
@@ -33315,7 +33305,7 @@
     <row r="1194">
       <c r="A1194" s="4" t="inlineStr">
         <is>
-          <t>TE01-34</t>
+          <t>TE01-35</t>
         </is>
       </c>
       <c r="B1194" s="4" t="inlineStr">
@@ -33341,7 +33331,7 @@
     <row r="1195">
       <c r="A1195" s="4" t="inlineStr">
         <is>
-          <t>TE01-35</t>
+          <t>TE01-36</t>
         </is>
       </c>
       <c r="B1195" s="4" t="inlineStr">
@@ -33367,7 +33357,7 @@
     <row r="1196">
       <c r="A1196" s="4" t="inlineStr">
         <is>
-          <t>TE01-36</t>
+          <t>TE01-37</t>
         </is>
       </c>
       <c r="B1196" s="4" t="inlineStr">
@@ -33393,7 +33383,7 @@
     <row r="1197">
       <c r="A1197" s="4" t="inlineStr">
         <is>
-          <t>TE01-37</t>
+          <t>TE01-38</t>
         </is>
       </c>
       <c r="B1197" s="4" t="inlineStr">
@@ -33419,7 +33409,7 @@
     <row r="1198">
       <c r="A1198" s="4" t="inlineStr">
         <is>
-          <t>TE01-38</t>
+          <t>TE01-39</t>
         </is>
       </c>
       <c r="B1198" s="4" t="inlineStr">
@@ -33445,7 +33435,7 @@
     <row r="1199">
       <c r="A1199" s="4" t="inlineStr">
         <is>
-          <t>TE01-39</t>
+          <t>TE01-40</t>
         </is>
       </c>
       <c r="B1199" s="4" t="inlineStr">
@@ -33469,35 +33459,45 @@
       <c r="H1199" s="4" t="n"/>
     </row>
     <row r="1200">
-      <c r="A1200" s="4" t="inlineStr">
-        <is>
-          <t>TE01-40</t>
-        </is>
-      </c>
-      <c r="B1200" s="4" t="inlineStr">
+      <c r="A1200" s="2" t="inlineStr">
+        <is>
+          <t>TE02-01</t>
+        </is>
+      </c>
+      <c r="B1200" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1200" s="4" t="inlineStr">
-        <is>
-          <t>ebenerdig</t>
-        </is>
-      </c>
-      <c r="D1200" s="4" t="inlineStr">
-        <is>
-          <t>Terrasse</t>
-        </is>
-      </c>
-      <c r="E1200" s="4" t="n"/>
-      <c r="F1200" s="3" t="n"/>
-      <c r="G1200" s="4" t="n"/>
-      <c r="H1200" s="4" t="n"/>
+      <c r="C1200" s="2" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1200" s="2" t="inlineStr">
+        <is>
+          <t>Dachterrasse</t>
+        </is>
+      </c>
+      <c r="E1200" s="2" t="inlineStr">
+        <is>
+          <t>Pflanzkübel Plastik weiß</t>
+        </is>
+      </c>
+      <c r="F1200" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1200" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1200" s="2" t="n"/>
     </row>
     <row r="1201">
       <c r="A1201" s="2" t="inlineStr">
         <is>
-          <t>TE02-01</t>
+          <t>TE02-02</t>
         </is>
       </c>
       <c r="B1201" s="2" t="inlineStr">
@@ -33517,7 +33517,7 @@
       </c>
       <c r="E1201" s="2" t="inlineStr">
         <is>
-          <t>Pflanzkübel Plastik weiß</t>
+          <t>Gartenstuhl Kunststoff anthrazit</t>
         </is>
       </c>
       <c r="F1201" s="3" t="n">
@@ -33533,7 +33533,7 @@
     <row r="1202">
       <c r="A1202" s="2" t="inlineStr">
         <is>
-          <t>TE02-02</t>
+          <t>TE02-03</t>
         </is>
       </c>
       <c r="B1202" s="2" t="inlineStr">
@@ -33553,11 +33553,11 @@
       </c>
       <c r="E1202" s="2" t="inlineStr">
         <is>
-          <t>Gartenstuhl Kunststoff anthrazit</t>
+          <t>Gartentisch anthrazit</t>
         </is>
       </c>
       <c r="F1202" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1202" s="2" t="inlineStr">
         <is>
@@ -33569,7 +33569,7 @@
     <row r="1203">
       <c r="A1203" s="2" t="inlineStr">
         <is>
-          <t>TE02-03</t>
+          <t>TE02-04</t>
         </is>
       </c>
       <c r="B1203" s="2" t="inlineStr">
@@ -33589,7 +33589,7 @@
       </c>
       <c r="E1203" s="2" t="inlineStr">
         <is>
-          <t>Gartentisch anthrazit</t>
+          <t>Teak-Klapptisch rund</t>
         </is>
       </c>
       <c r="F1203" s="3" t="n">
@@ -33597,7 +33597,7 @@
       </c>
       <c r="G1203" s="2" t="inlineStr">
         <is>
-          <t>Stück</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="H1203" s="2" t="n"/>
@@ -33605,7 +33605,7 @@
     <row r="1204">
       <c r="A1204" s="2" t="inlineStr">
         <is>
-          <t>TE02-04</t>
+          <t>TE02-05</t>
         </is>
       </c>
       <c r="B1204" s="2" t="inlineStr">
@@ -33625,15 +33625,15 @@
       </c>
       <c r="E1204" s="2" t="inlineStr">
         <is>
-          <t>Teak-Klapptisch rund</t>
+          <t>Pflanzkübel grau, groß</t>
         </is>
       </c>
       <c r="F1204" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1204" s="2" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Stück</t>
         </is>
       </c>
       <c r="H1204" s="2" t="n"/>
@@ -33641,7 +33641,7 @@
     <row r="1205">
       <c r="A1205" s="2" t="inlineStr">
         <is>
-          <t>TE02-05</t>
+          <t>TE02-06</t>
         </is>
       </c>
       <c r="B1205" s="2" t="inlineStr">
@@ -33661,11 +33661,11 @@
       </c>
       <c r="E1205" s="2" t="inlineStr">
         <is>
-          <t>Pflanzkübel grau, groß</t>
+          <t>Holzstern mit Lichterkette</t>
         </is>
       </c>
       <c r="F1205" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1205" s="2" t="inlineStr">
         <is>
@@ -33675,45 +33675,35 @@
       <c r="H1205" s="2" t="n"/>
     </row>
     <row r="1206">
-      <c r="A1206" s="2" t="inlineStr">
-        <is>
-          <t>TE02-06</t>
-        </is>
-      </c>
-      <c r="B1206" s="2" t="inlineStr">
+      <c r="A1206" s="4" t="inlineStr">
+        <is>
+          <t>TE02-07</t>
+        </is>
+      </c>
+      <c r="B1206" s="4" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1206" s="2" t="inlineStr">
+      <c r="C1206" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1206" s="2" t="inlineStr">
+      <c r="D1206" s="4" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1206" s="2" t="inlineStr">
-        <is>
-          <t>Holzstern mit Lichterkette</t>
-        </is>
-      </c>
-      <c r="F1206" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1206" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1206" s="2" t="n"/>
+      <c r="E1206" s="4" t="n"/>
+      <c r="F1206" s="3" t="n"/>
+      <c r="G1206" s="4" t="n"/>
+      <c r="H1206" s="4" t="n"/>
     </row>
     <row r="1207">
       <c r="A1207" s="4" t="inlineStr">
         <is>
-          <t>TE02-07</t>
+          <t>TE02-08</t>
         </is>
       </c>
       <c r="B1207" s="4" t="inlineStr">
@@ -33739,7 +33729,7 @@
     <row r="1208">
       <c r="A1208" s="4" t="inlineStr">
         <is>
-          <t>TE02-08</t>
+          <t>TE02-09</t>
         </is>
       </c>
       <c r="B1208" s="4" t="inlineStr">
@@ -33765,7 +33755,7 @@
     <row r="1209">
       <c r="A1209" s="4" t="inlineStr">
         <is>
-          <t>TE02-09</t>
+          <t>TE02-10</t>
         </is>
       </c>
       <c r="B1209" s="4" t="inlineStr">
@@ -33791,7 +33781,7 @@
     <row r="1210">
       <c r="A1210" s="4" t="inlineStr">
         <is>
-          <t>TE02-10</t>
+          <t>TE02-11</t>
         </is>
       </c>
       <c r="B1210" s="4" t="inlineStr">
@@ -33817,7 +33807,7 @@
     <row r="1211">
       <c r="A1211" s="4" t="inlineStr">
         <is>
-          <t>TE02-11</t>
+          <t>TE02-12</t>
         </is>
       </c>
       <c r="B1211" s="4" t="inlineStr">
@@ -33843,7 +33833,7 @@
     <row r="1212">
       <c r="A1212" s="4" t="inlineStr">
         <is>
-          <t>TE02-12</t>
+          <t>TE02-13</t>
         </is>
       </c>
       <c r="B1212" s="4" t="inlineStr">
@@ -33869,7 +33859,7 @@
     <row r="1213">
       <c r="A1213" s="4" t="inlineStr">
         <is>
-          <t>TE02-13</t>
+          <t>TE02-14</t>
         </is>
       </c>
       <c r="B1213" s="4" t="inlineStr">
@@ -33895,7 +33885,7 @@
     <row r="1214">
       <c r="A1214" s="4" t="inlineStr">
         <is>
-          <t>TE02-14</t>
+          <t>TE02-15</t>
         </is>
       </c>
       <c r="B1214" s="4" t="inlineStr">
@@ -33921,7 +33911,7 @@
     <row r="1215">
       <c r="A1215" s="4" t="inlineStr">
         <is>
-          <t>TE02-15</t>
+          <t>TE02-16</t>
         </is>
       </c>
       <c r="B1215" s="4" t="inlineStr">
@@ -33947,7 +33937,7 @@
     <row r="1216">
       <c r="A1216" s="4" t="inlineStr">
         <is>
-          <t>TE02-16</t>
+          <t>TE02-17</t>
         </is>
       </c>
       <c r="B1216" s="4" t="inlineStr">
@@ -33973,7 +33963,7 @@
     <row r="1217">
       <c r="A1217" s="4" t="inlineStr">
         <is>
-          <t>TE02-17</t>
+          <t>TE02-18</t>
         </is>
       </c>
       <c r="B1217" s="4" t="inlineStr">
@@ -33999,7 +33989,7 @@
     <row r="1218">
       <c r="A1218" s="4" t="inlineStr">
         <is>
-          <t>TE02-18</t>
+          <t>TE02-19</t>
         </is>
       </c>
       <c r="B1218" s="4" t="inlineStr">
@@ -34025,7 +34015,7 @@
     <row r="1219">
       <c r="A1219" s="4" t="inlineStr">
         <is>
-          <t>TE02-19</t>
+          <t>TE02-20</t>
         </is>
       </c>
       <c r="B1219" s="4" t="inlineStr">
@@ -34051,7 +34041,7 @@
     <row r="1220">
       <c r="A1220" s="4" t="inlineStr">
         <is>
-          <t>TE02-20</t>
+          <t>TE02-21</t>
         </is>
       </c>
       <c r="B1220" s="4" t="inlineStr">
@@ -34077,7 +34067,7 @@
     <row r="1221">
       <c r="A1221" s="4" t="inlineStr">
         <is>
-          <t>TE02-21</t>
+          <t>TE02-22</t>
         </is>
       </c>
       <c r="B1221" s="4" t="inlineStr">
@@ -34103,7 +34093,7 @@
     <row r="1222">
       <c r="A1222" s="4" t="inlineStr">
         <is>
-          <t>TE02-22</t>
+          <t>TE02-23</t>
         </is>
       </c>
       <c r="B1222" s="4" t="inlineStr">
@@ -34129,7 +34119,7 @@
     <row r="1223">
       <c r="A1223" s="4" t="inlineStr">
         <is>
-          <t>TE02-23</t>
+          <t>TE02-24</t>
         </is>
       </c>
       <c r="B1223" s="4" t="inlineStr">
@@ -34155,7 +34145,7 @@
     <row r="1224">
       <c r="A1224" s="4" t="inlineStr">
         <is>
-          <t>TE02-24</t>
+          <t>TE02-25</t>
         </is>
       </c>
       <c r="B1224" s="4" t="inlineStr">
@@ -34181,7 +34171,7 @@
     <row r="1225">
       <c r="A1225" s="4" t="inlineStr">
         <is>
-          <t>TE02-25</t>
+          <t>TE02-26</t>
         </is>
       </c>
       <c r="B1225" s="4" t="inlineStr">
@@ -34207,7 +34197,7 @@
     <row r="1226">
       <c r="A1226" s="4" t="inlineStr">
         <is>
-          <t>TE02-26</t>
+          <t>TE02-27</t>
         </is>
       </c>
       <c r="B1226" s="4" t="inlineStr">
@@ -34233,7 +34223,7 @@
     <row r="1227">
       <c r="A1227" s="4" t="inlineStr">
         <is>
-          <t>TE02-27</t>
+          <t>TE02-28</t>
         </is>
       </c>
       <c r="B1227" s="4" t="inlineStr">
@@ -34259,7 +34249,7 @@
     <row r="1228">
       <c r="A1228" s="4" t="inlineStr">
         <is>
-          <t>TE02-28</t>
+          <t>TE02-29</t>
         </is>
       </c>
       <c r="B1228" s="4" t="inlineStr">
@@ -34285,7 +34275,7 @@
     <row r="1229">
       <c r="A1229" s="4" t="inlineStr">
         <is>
-          <t>TE02-29</t>
+          <t>TE02-30</t>
         </is>
       </c>
       <c r="B1229" s="4" t="inlineStr">
@@ -34311,7 +34301,7 @@
     <row r="1230">
       <c r="A1230" s="4" t="inlineStr">
         <is>
-          <t>TE02-30</t>
+          <t>TE02-31</t>
         </is>
       </c>
       <c r="B1230" s="4" t="inlineStr">
@@ -34337,7 +34327,7 @@
     <row r="1231">
       <c r="A1231" s="4" t="inlineStr">
         <is>
-          <t>TE02-31</t>
+          <t>TE02-32</t>
         </is>
       </c>
       <c r="B1231" s="4" t="inlineStr">
@@ -34363,7 +34353,7 @@
     <row r="1232">
       <c r="A1232" s="4" t="inlineStr">
         <is>
-          <t>TE02-32</t>
+          <t>TE02-33</t>
         </is>
       </c>
       <c r="B1232" s="4" t="inlineStr">
@@ -34389,7 +34379,7 @@
     <row r="1233">
       <c r="A1233" s="4" t="inlineStr">
         <is>
-          <t>TE02-33</t>
+          <t>TE02-34</t>
         </is>
       </c>
       <c r="B1233" s="4" t="inlineStr">
@@ -34415,7 +34405,7 @@
     <row r="1234">
       <c r="A1234" s="4" t="inlineStr">
         <is>
-          <t>TE02-34</t>
+          <t>TE02-35</t>
         </is>
       </c>
       <c r="B1234" s="4" t="inlineStr">
@@ -34441,7 +34431,7 @@
     <row r="1235">
       <c r="A1235" s="4" t="inlineStr">
         <is>
-          <t>TE02-35</t>
+          <t>TE02-36</t>
         </is>
       </c>
       <c r="B1235" s="4" t="inlineStr">
@@ -34467,7 +34457,7 @@
     <row r="1236">
       <c r="A1236" s="4" t="inlineStr">
         <is>
-          <t>TE02-36</t>
+          <t>TE02-37</t>
         </is>
       </c>
       <c r="B1236" s="4" t="inlineStr">
@@ -34493,7 +34483,7 @@
     <row r="1237">
       <c r="A1237" s="4" t="inlineStr">
         <is>
-          <t>TE02-37</t>
+          <t>TE02-38</t>
         </is>
       </c>
       <c r="B1237" s="4" t="inlineStr">
@@ -34519,7 +34509,7 @@
     <row r="1238">
       <c r="A1238" s="4" t="inlineStr">
         <is>
-          <t>TE02-38</t>
+          <t>TE02-39</t>
         </is>
       </c>
       <c r="B1238" s="4" t="inlineStr">
@@ -34545,7 +34535,7 @@
     <row r="1239">
       <c r="A1239" s="4" t="inlineStr">
         <is>
-          <t>TE02-39</t>
+          <t>TE02-40</t>
         </is>
       </c>
       <c r="B1239" s="4" t="inlineStr">
@@ -34569,67 +34559,63 @@
       <c r="H1239" s="4" t="n"/>
     </row>
     <row r="1240">
-      <c r="A1240" s="4" t="inlineStr">
-        <is>
-          <t>TE02-40</t>
-        </is>
-      </c>
-      <c r="B1240" s="4" t="inlineStr">
+      <c r="A1240" s="2" t="inlineStr">
+        <is>
+          <t>GA01-01</t>
+        </is>
+      </c>
+      <c r="B1240" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1240" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1240" s="4" t="inlineStr">
-        <is>
-          <t>Dachterrasse</t>
-        </is>
-      </c>
-      <c r="E1240" s="4" t="n"/>
-      <c r="F1240" s="3" t="n"/>
-      <c r="G1240" s="4" t="n"/>
-      <c r="H1240" s="4" t="n"/>
+      <c r="C1240" s="2" t="inlineStr"/>
+      <c r="D1240" s="2" t="inlineStr">
+        <is>
+          <t>Gartenanlage</t>
+        </is>
+      </c>
+      <c r="E1240" s="2" t="inlineStr">
+        <is>
+          <t>Holz-Wellenliege, Doppelliege</t>
+        </is>
+      </c>
+      <c r="F1240" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1240" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1240" s="2" t="n"/>
     </row>
     <row r="1241">
-      <c r="A1241" s="2" t="inlineStr">
-        <is>
-          <t>GA01-01</t>
-        </is>
-      </c>
-      <c r="B1241" s="2" t="inlineStr">
+      <c r="A1241" s="4" t="inlineStr">
+        <is>
+          <t>GA01-02</t>
+        </is>
+      </c>
+      <c r="B1241" s="4" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1241" s="2" t="inlineStr"/>
-      <c r="D1241" s="2" t="inlineStr">
+      <c r="C1241" s="4" t="inlineStr"/>
+      <c r="D1241" s="4" t="inlineStr">
         <is>
           <t>Gartenanlage</t>
         </is>
       </c>
-      <c r="E1241" s="2" t="inlineStr">
-        <is>
-          <t>Holz-Wellenliege, Doppelliege</t>
-        </is>
-      </c>
-      <c r="F1241" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1241" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1241" s="2" t="n"/>
+      <c r="E1241" s="4" t="n"/>
+      <c r="F1241" s="3" t="n"/>
+      <c r="G1241" s="4" t="n"/>
+      <c r="H1241" s="4" t="n"/>
     </row>
     <row r="1242">
       <c r="A1242" s="4" t="inlineStr">
         <is>
-          <t>GA01-02</t>
+          <t>GA01-03</t>
         </is>
       </c>
       <c r="B1242" s="4" t="inlineStr">
@@ -34651,7 +34637,7 @@
     <row r="1243">
       <c r="A1243" s="4" t="inlineStr">
         <is>
-          <t>GA01-03</t>
+          <t>GA01-04</t>
         </is>
       </c>
       <c r="B1243" s="4" t="inlineStr">
@@ -34673,7 +34659,7 @@
     <row r="1244">
       <c r="A1244" s="4" t="inlineStr">
         <is>
-          <t>GA01-04</t>
+          <t>GA01-05</t>
         </is>
       </c>
       <c r="B1244" s="4" t="inlineStr">
@@ -34695,7 +34681,7 @@
     <row r="1245">
       <c r="A1245" s="4" t="inlineStr">
         <is>
-          <t>GA01-05</t>
+          <t>GA01-06</t>
         </is>
       </c>
       <c r="B1245" s="4" t="inlineStr">
@@ -34717,7 +34703,7 @@
     <row r="1246">
       <c r="A1246" s="4" t="inlineStr">
         <is>
-          <t>GA01-06</t>
+          <t>GA01-07</t>
         </is>
       </c>
       <c r="B1246" s="4" t="inlineStr">
@@ -34739,7 +34725,7 @@
     <row r="1247">
       <c r="A1247" s="4" t="inlineStr">
         <is>
-          <t>GA01-07</t>
+          <t>GA01-08</t>
         </is>
       </c>
       <c r="B1247" s="4" t="inlineStr">
@@ -34761,7 +34747,7 @@
     <row r="1248">
       <c r="A1248" s="4" t="inlineStr">
         <is>
-          <t>GA01-08</t>
+          <t>GA01-09</t>
         </is>
       </c>
       <c r="B1248" s="4" t="inlineStr">
@@ -34783,7 +34769,7 @@
     <row r="1249">
       <c r="A1249" s="4" t="inlineStr">
         <is>
-          <t>GA01-09</t>
+          <t>GA01-10</t>
         </is>
       </c>
       <c r="B1249" s="4" t="inlineStr">
@@ -34805,7 +34791,7 @@
     <row r="1250">
       <c r="A1250" s="4" t="inlineStr">
         <is>
-          <t>GA01-10</t>
+          <t>GA01-11</t>
         </is>
       </c>
       <c r="B1250" s="4" t="inlineStr">
@@ -34827,7 +34813,7 @@
     <row r="1251">
       <c r="A1251" s="4" t="inlineStr">
         <is>
-          <t>GA01-11</t>
+          <t>GA01-12</t>
         </is>
       </c>
       <c r="B1251" s="4" t="inlineStr">
@@ -34849,7 +34835,7 @@
     <row r="1252">
       <c r="A1252" s="4" t="inlineStr">
         <is>
-          <t>GA01-12</t>
+          <t>GA01-13</t>
         </is>
       </c>
       <c r="B1252" s="4" t="inlineStr">
@@ -34871,7 +34857,7 @@
     <row r="1253">
       <c r="A1253" s="4" t="inlineStr">
         <is>
-          <t>GA01-13</t>
+          <t>GA01-14</t>
         </is>
       </c>
       <c r="B1253" s="4" t="inlineStr">
@@ -34893,7 +34879,7 @@
     <row r="1254">
       <c r="A1254" s="4" t="inlineStr">
         <is>
-          <t>GA01-14</t>
+          <t>GA01-15</t>
         </is>
       </c>
       <c r="B1254" s="4" t="inlineStr">
@@ -34915,7 +34901,7 @@
     <row r="1255">
       <c r="A1255" s="4" t="inlineStr">
         <is>
-          <t>GA01-15</t>
+          <t>GA01-16</t>
         </is>
       </c>
       <c r="B1255" s="4" t="inlineStr">
@@ -34937,7 +34923,7 @@
     <row r="1256">
       <c r="A1256" s="4" t="inlineStr">
         <is>
-          <t>GA01-16</t>
+          <t>GA01-17</t>
         </is>
       </c>
       <c r="B1256" s="4" t="inlineStr">
@@ -34959,7 +34945,7 @@
     <row r="1257">
       <c r="A1257" s="4" t="inlineStr">
         <is>
-          <t>GA01-17</t>
+          <t>GA01-18</t>
         </is>
       </c>
       <c r="B1257" s="4" t="inlineStr">
@@ -34981,7 +34967,7 @@
     <row r="1258">
       <c r="A1258" s="4" t="inlineStr">
         <is>
-          <t>GA01-18</t>
+          <t>GA01-19</t>
         </is>
       </c>
       <c r="B1258" s="4" t="inlineStr">
@@ -35003,7 +34989,7 @@
     <row r="1259">
       <c r="A1259" s="4" t="inlineStr">
         <is>
-          <t>GA01-19</t>
+          <t>GA01-20</t>
         </is>
       </c>
       <c r="B1259" s="4" t="inlineStr">
@@ -35025,7 +35011,7 @@
     <row r="1260">
       <c r="A1260" s="4" t="inlineStr">
         <is>
-          <t>GA01-20</t>
+          <t>GA01-21</t>
         </is>
       </c>
       <c r="B1260" s="4" t="inlineStr">
@@ -35047,7 +35033,7 @@
     <row r="1261">
       <c r="A1261" s="4" t="inlineStr">
         <is>
-          <t>GA01-21</t>
+          <t>GA01-22</t>
         </is>
       </c>
       <c r="B1261" s="4" t="inlineStr">
@@ -35069,7 +35055,7 @@
     <row r="1262">
       <c r="A1262" s="4" t="inlineStr">
         <is>
-          <t>GA01-22</t>
+          <t>GA01-23</t>
         </is>
       </c>
       <c r="B1262" s="4" t="inlineStr">
@@ -35091,7 +35077,7 @@
     <row r="1263">
       <c r="A1263" s="4" t="inlineStr">
         <is>
-          <t>GA01-23</t>
+          <t>GA01-24</t>
         </is>
       </c>
       <c r="B1263" s="4" t="inlineStr">
@@ -35113,7 +35099,7 @@
     <row r="1264">
       <c r="A1264" s="4" t="inlineStr">
         <is>
-          <t>GA01-24</t>
+          <t>GA01-25</t>
         </is>
       </c>
       <c r="B1264" s="4" t="inlineStr">
@@ -35135,7 +35121,7 @@
     <row r="1265">
       <c r="A1265" s="4" t="inlineStr">
         <is>
-          <t>GA01-25</t>
+          <t>GA01-26</t>
         </is>
       </c>
       <c r="B1265" s="4" t="inlineStr">
@@ -35157,7 +35143,7 @@
     <row r="1266">
       <c r="A1266" s="4" t="inlineStr">
         <is>
-          <t>GA01-26</t>
+          <t>GA01-27</t>
         </is>
       </c>
       <c r="B1266" s="4" t="inlineStr">
@@ -35179,7 +35165,7 @@
     <row r="1267">
       <c r="A1267" s="4" t="inlineStr">
         <is>
-          <t>GA01-27</t>
+          <t>GA01-28</t>
         </is>
       </c>
       <c r="B1267" s="4" t="inlineStr">
@@ -35201,7 +35187,7 @@
     <row r="1268">
       <c r="A1268" s="4" t="inlineStr">
         <is>
-          <t>GA01-28</t>
+          <t>GA01-29</t>
         </is>
       </c>
       <c r="B1268" s="4" t="inlineStr">
@@ -35223,7 +35209,7 @@
     <row r="1269">
       <c r="A1269" s="4" t="inlineStr">
         <is>
-          <t>GA01-29</t>
+          <t>GA01-30</t>
         </is>
       </c>
       <c r="B1269" s="4" t="inlineStr">
@@ -35245,7 +35231,7 @@
     <row r="1270">
       <c r="A1270" s="4" t="inlineStr">
         <is>
-          <t>GA01-30</t>
+          <t>GA01-31</t>
         </is>
       </c>
       <c r="B1270" s="4" t="inlineStr">
@@ -35267,7 +35253,7 @@
     <row r="1271">
       <c r="A1271" s="4" t="inlineStr">
         <is>
-          <t>GA01-31</t>
+          <t>GA01-32</t>
         </is>
       </c>
       <c r="B1271" s="4" t="inlineStr">
@@ -35289,7 +35275,7 @@
     <row r="1272">
       <c r="A1272" s="4" t="inlineStr">
         <is>
-          <t>GA01-32</t>
+          <t>GA01-33</t>
         </is>
       </c>
       <c r="B1272" s="4" t="inlineStr">
@@ -35311,7 +35297,7 @@
     <row r="1273">
       <c r="A1273" s="4" t="inlineStr">
         <is>
-          <t>GA01-33</t>
+          <t>GA01-34</t>
         </is>
       </c>
       <c r="B1273" s="4" t="inlineStr">
@@ -35333,7 +35319,7 @@
     <row r="1274">
       <c r="A1274" s="4" t="inlineStr">
         <is>
-          <t>GA01-34</t>
+          <t>GA01-35</t>
         </is>
       </c>
       <c r="B1274" s="4" t="inlineStr">
@@ -35355,7 +35341,7 @@
     <row r="1275">
       <c r="A1275" s="4" t="inlineStr">
         <is>
-          <t>GA01-35</t>
+          <t>GA01-36</t>
         </is>
       </c>
       <c r="B1275" s="4" t="inlineStr">
@@ -35377,7 +35363,7 @@
     <row r="1276">
       <c r="A1276" s="4" t="inlineStr">
         <is>
-          <t>GA01-36</t>
+          <t>GA01-37</t>
         </is>
       </c>
       <c r="B1276" s="4" t="inlineStr">
@@ -35399,7 +35385,7 @@
     <row r="1277">
       <c r="A1277" s="4" t="inlineStr">
         <is>
-          <t>GA01-37</t>
+          <t>GA01-38</t>
         </is>
       </c>
       <c r="B1277" s="4" t="inlineStr">
@@ -35421,7 +35407,7 @@
     <row r="1278">
       <c r="A1278" s="4" t="inlineStr">
         <is>
-          <t>GA01-38</t>
+          <t>GA01-39</t>
         </is>
       </c>
       <c r="B1278" s="4" t="inlineStr">
@@ -35443,7 +35429,7 @@
     <row r="1279">
       <c r="A1279" s="4" t="inlineStr">
         <is>
-          <t>GA01-39</t>
+          <t>GA01-40</t>
         </is>
       </c>
       <c r="B1279" s="4" t="inlineStr">
@@ -35462,32 +35448,10 @@
       <c r="G1279" s="4" t="n"/>
       <c r="H1279" s="4" t="n"/>
     </row>
-    <row r="1280">
-      <c r="A1280" s="4" t="inlineStr">
-        <is>
-          <t>GA01-40</t>
-        </is>
-      </c>
-      <c r="B1280" s="4" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1280" s="4" t="inlineStr"/>
-      <c r="D1280" s="4" t="inlineStr">
-        <is>
-          <t>Gartenanlage</t>
-        </is>
-      </c>
-      <c r="E1280" s="4" t="n"/>
-      <c r="F1280" s="3" t="n"/>
-      <c r="G1280" s="4" t="n"/>
-      <c r="H1280" s="4" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H1280"/>
+  <autoFilter ref="A1:H1279"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F1280" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen." type="whole" operator="greaterThan">
+    <dataValidation sqref="F2:F1279" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anleitung" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Erfassung'!$A$1:$H$1279</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Erfassung'!$A$1:$H$1280</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1279"/>
+  <dimension ref="A1:H1280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30475,7 +30475,7 @@
         </is>
       </c>
       <c r="F1090" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1090" s="2" t="inlineStr">
         <is>
@@ -30485,30 +30485,40 @@
       <c r="H1090" s="2" t="n"/>
     </row>
     <row r="1091">
-      <c r="A1091" s="4" t="inlineStr">
+      <c r="A1091" s="2" t="inlineStr">
         <is>
           <t>BA09-06</t>
         </is>
       </c>
-      <c r="B1091" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1091" s="4" t="inlineStr">
+      <c r="B1091" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1091" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1091" s="4" t="inlineStr">
+      <c r="D1091" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="E1091" s="4" t="n"/>
-      <c r="F1091" s="3" t="n"/>
-      <c r="G1091" s="4" t="n"/>
-      <c r="H1091" s="4" t="n"/>
+      <c r="E1091" s="2" t="inlineStr">
+        <is>
+          <t>Sitzhocker rund, drehbar auf Rollen</t>
+        </is>
+      </c>
+      <c r="F1091" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1091" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1091" s="2" t="n"/>
     </row>
     <row r="1092">
       <c r="A1092" s="4" t="inlineStr">
@@ -30745,45 +30755,35 @@
       <c r="H1100" s="4" t="n"/>
     </row>
     <row r="1101">
-      <c r="A1101" s="2" t="inlineStr">
-        <is>
-          <t>BA10-01</t>
-        </is>
-      </c>
-      <c r="B1101" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1101" s="2" t="inlineStr">
+      <c r="A1101" s="4" t="inlineStr">
+        <is>
+          <t>BA09-16</t>
+        </is>
+      </c>
+      <c r="B1101" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1101" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1101" s="2" t="inlineStr">
-        <is>
-          <t>Ruhe- / Schlafraum</t>
-        </is>
-      </c>
-      <c r="E1101" s="2" t="inlineStr">
-        <is>
-          <t>Glastisch rund mit Chromgestell</t>
-        </is>
-      </c>
-      <c r="F1101" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1101" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1101" s="2" t="n"/>
+      <c r="D1101" s="4" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="E1101" s="4" t="n"/>
+      <c r="F1101" s="3" t="n"/>
+      <c r="G1101" s="4" t="n"/>
+      <c r="H1101" s="4" t="n"/>
     </row>
     <row r="1102">
       <c r="A1102" s="2" t="inlineStr">
         <is>
-          <t>BA10-02</t>
+          <t>BA10-01</t>
         </is>
       </c>
       <c r="B1102" s="2" t="inlineStr">
@@ -30803,11 +30803,11 @@
       </c>
       <c r="E1102" s="2" t="inlineStr">
         <is>
-          <t>Samtsofa bordeaux, 2-Sitzer</t>
+          <t>Glastisch rund mit Chromgestell</t>
         </is>
       </c>
       <c r="F1102" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1102" s="2" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
     <row r="1103">
       <c r="A1103" s="2" t="inlineStr">
         <is>
-          <t>BA10-03</t>
+          <t>BA10-02</t>
         </is>
       </c>
       <c r="B1103" s="2" t="inlineStr">
@@ -30839,7 +30839,7 @@
       </c>
       <c r="E1103" s="2" t="inlineStr">
         <is>
-          <t>Sessel mit Bezug, weiß lackiert</t>
+          <t>Samtsofa bordeaux, 2-Sitzer</t>
         </is>
       </c>
       <c r="F1103" s="3" t="n">
@@ -30855,7 +30855,7 @@
     <row r="1104">
       <c r="A1104" s="2" t="inlineStr">
         <is>
-          <t>BA10-04</t>
+          <t>BA10-03</t>
         </is>
       </c>
       <c r="B1104" s="2" t="inlineStr">
@@ -30875,7 +30875,7 @@
       </c>
       <c r="E1104" s="2" t="inlineStr">
         <is>
-          <t>Hocker grau mit Hairpin-Beinen</t>
+          <t>Sessel mit Bezug, weiß lackiert</t>
         </is>
       </c>
       <c r="F1104" s="3" t="n">
@@ -30891,7 +30891,7 @@
     <row r="1105">
       <c r="A1105" s="2" t="inlineStr">
         <is>
-          <t>BA10-05</t>
+          <t>BA10-04</t>
         </is>
       </c>
       <c r="B1105" s="2" t="inlineStr">
@@ -30911,7 +30911,7 @@
       </c>
       <c r="E1105" s="2" t="inlineStr">
         <is>
-          <t>Ohrensessel grau mit Kufengestell</t>
+          <t>Hocker grau mit Hairpin-Beinen</t>
         </is>
       </c>
       <c r="F1105" s="3" t="n">
@@ -30927,7 +30927,7 @@
     <row r="1106">
       <c r="A1106" s="2" t="inlineStr">
         <is>
-          <t>BA10-06</t>
+          <t>BA10-05</t>
         </is>
       </c>
       <c r="B1106" s="2" t="inlineStr">
@@ -30947,7 +30947,7 @@
       </c>
       <c r="E1106" s="2" t="inlineStr">
         <is>
-          <t>Hocker grau, passend</t>
+          <t>Ohrensessel grau mit Kufengestell</t>
         </is>
       </c>
       <c r="F1106" s="3" t="n">
@@ -30963,7 +30963,7 @@
     <row r="1107">
       <c r="A1107" s="2" t="inlineStr">
         <is>
-          <t>BA10-07</t>
+          <t>BA10-06</t>
         </is>
       </c>
       <c r="B1107" s="2" t="inlineStr">
@@ -30983,11 +30983,11 @@
       </c>
       <c r="E1107" s="2" t="inlineStr">
         <is>
-          <t>Beistelltisch rund grau</t>
+          <t>Hocker grau, passend</t>
         </is>
       </c>
       <c r="F1107" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1107" s="2" t="inlineStr">
         <is>
@@ -30999,69 +30999,79 @@
     <row r="1108">
       <c r="A1108" s="2" t="inlineStr">
         <is>
+          <t>BA10-07</t>
+        </is>
+      </c>
+      <c r="B1108" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1108" s="2" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1108" s="2" t="inlineStr">
+        <is>
+          <t>Ruhe- / Schlafraum</t>
+        </is>
+      </c>
+      <c r="E1108" s="2" t="inlineStr">
+        <is>
+          <t>Beistelltisch rund grau</t>
+        </is>
+      </c>
+      <c r="F1108" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1108" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1108" s="2" t="n"/>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="2" t="inlineStr">
+        <is>
           <t>BA10-08</t>
         </is>
       </c>
-      <c r="B1108" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1108" s="2" t="inlineStr">
+      <c r="B1109" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1109" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1108" s="2" t="inlineStr">
+      <c r="D1109" s="2" t="inlineStr">
         <is>
           <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
-      <c r="E1108" s="2" t="inlineStr">
+      <c r="E1109" s="2" t="inlineStr">
         <is>
           <t>Pendelleuchte Drahtgeflecht</t>
         </is>
       </c>
-      <c r="F1108" s="3" t="n">
+      <c r="F1109" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G1108" s="2" t="inlineStr">
+      <c r="G1109" s="2" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="H1108" s="2" t="n"/>
-    </row>
-    <row r="1109">
-      <c r="A1109" s="4" t="inlineStr">
-        <is>
-          <t>BA10-09</t>
-        </is>
-      </c>
-      <c r="B1109" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1109" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1109" s="4" t="inlineStr">
-        <is>
-          <t>Ruhe- / Schlafraum</t>
-        </is>
-      </c>
-      <c r="E1109" s="4" t="n"/>
-      <c r="F1109" s="3" t="n"/>
-      <c r="G1109" s="4" t="n"/>
-      <c r="H1109" s="4" t="n"/>
+      <c r="H1109" s="2" t="n"/>
     </row>
     <row r="1110">
       <c r="A1110" s="4" t="inlineStr">
         <is>
-          <t>BA10-10</t>
+          <t>BA10-09</t>
         </is>
       </c>
       <c r="B1110" s="4" t="inlineStr">
@@ -31087,7 +31097,7 @@
     <row r="1111">
       <c r="A1111" s="4" t="inlineStr">
         <is>
-          <t>BA10-11</t>
+          <t>BA10-10</t>
         </is>
       </c>
       <c r="B1111" s="4" t="inlineStr">
@@ -31113,7 +31123,7 @@
     <row r="1112">
       <c r="A1112" s="4" t="inlineStr">
         <is>
-          <t>BA10-12</t>
+          <t>BA10-11</t>
         </is>
       </c>
       <c r="B1112" s="4" t="inlineStr">
@@ -31139,7 +31149,7 @@
     <row r="1113">
       <c r="A1113" s="4" t="inlineStr">
         <is>
-          <t>BA10-13</t>
+          <t>BA10-12</t>
         </is>
       </c>
       <c r="B1113" s="4" t="inlineStr">
@@ -31165,7 +31175,7 @@
     <row r="1114">
       <c r="A1114" s="4" t="inlineStr">
         <is>
-          <t>BA10-14</t>
+          <t>BA10-13</t>
         </is>
       </c>
       <c r="B1114" s="4" t="inlineStr">
@@ -31191,7 +31201,7 @@
     <row r="1115">
       <c r="A1115" s="4" t="inlineStr">
         <is>
-          <t>BA10-15</t>
+          <t>BA10-14</t>
         </is>
       </c>
       <c r="B1115" s="4" t="inlineStr">
@@ -31217,7 +31227,7 @@
     <row r="1116">
       <c r="A1116" s="4" t="inlineStr">
         <is>
-          <t>BA10-16</t>
+          <t>BA10-15</t>
         </is>
       </c>
       <c r="B1116" s="4" t="inlineStr">
@@ -31243,7 +31253,7 @@
     <row r="1117">
       <c r="A1117" s="4" t="inlineStr">
         <is>
-          <t>BA10-17</t>
+          <t>BA10-16</t>
         </is>
       </c>
       <c r="B1117" s="4" t="inlineStr">
@@ -31269,7 +31279,7 @@
     <row r="1118">
       <c r="A1118" s="4" t="inlineStr">
         <is>
-          <t>BA10-18</t>
+          <t>BA10-17</t>
         </is>
       </c>
       <c r="B1118" s="4" t="inlineStr">
@@ -31295,7 +31305,7 @@
     <row r="1119">
       <c r="A1119" s="4" t="inlineStr">
         <is>
-          <t>BA11-01</t>
+          <t>BA10-18</t>
         </is>
       </c>
       <c r="B1119" s="4" t="inlineStr">
@@ -31310,7 +31320,7 @@
       </c>
       <c r="D1119" s="4" t="inlineStr">
         <is>
-          <t>WC Kinder</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="E1119" s="4" t="n"/>
@@ -31321,7 +31331,7 @@
     <row r="1120">
       <c r="A1120" s="4" t="inlineStr">
         <is>
-          <t>BA11-02</t>
+          <t>BA11-01</t>
         </is>
       </c>
       <c r="B1120" s="4" t="inlineStr">
@@ -31347,7 +31357,7 @@
     <row r="1121">
       <c r="A1121" s="4" t="inlineStr">
         <is>
-          <t>BA11-03</t>
+          <t>BA11-02</t>
         </is>
       </c>
       <c r="B1121" s="4" t="inlineStr">
@@ -31373,7 +31383,7 @@
     <row r="1122">
       <c r="A1122" s="4" t="inlineStr">
         <is>
-          <t>BA11-04</t>
+          <t>BA11-03</t>
         </is>
       </c>
       <c r="B1122" s="4" t="inlineStr">
@@ -31399,7 +31409,7 @@
     <row r="1123">
       <c r="A1123" s="4" t="inlineStr">
         <is>
-          <t>BA11-05</t>
+          <t>BA11-04</t>
         </is>
       </c>
       <c r="B1123" s="4" t="inlineStr">
@@ -31425,7 +31435,7 @@
     <row r="1124">
       <c r="A1124" s="4" t="inlineStr">
         <is>
-          <t>BA11-06</t>
+          <t>BA11-05</t>
         </is>
       </c>
       <c r="B1124" s="4" t="inlineStr">
@@ -31451,7 +31461,7 @@
     <row r="1125">
       <c r="A1125" s="4" t="inlineStr">
         <is>
-          <t>BA11-07</t>
+          <t>BA11-06</t>
         </is>
       </c>
       <c r="B1125" s="4" t="inlineStr">
@@ -31477,7 +31487,7 @@
     <row r="1126">
       <c r="A1126" s="4" t="inlineStr">
         <is>
-          <t>BA11-08</t>
+          <t>BA11-07</t>
         </is>
       </c>
       <c r="B1126" s="4" t="inlineStr">
@@ -31503,7 +31513,7 @@
     <row r="1127">
       <c r="A1127" s="4" t="inlineStr">
         <is>
-          <t>BA11-09</t>
+          <t>BA11-08</t>
         </is>
       </c>
       <c r="B1127" s="4" t="inlineStr">
@@ -31529,7 +31539,7 @@
     <row r="1128">
       <c r="A1128" s="4" t="inlineStr">
         <is>
-          <t>BA11-10</t>
+          <t>BA11-09</t>
         </is>
       </c>
       <c r="B1128" s="4" t="inlineStr">
@@ -31555,7 +31565,7 @@
     <row r="1129">
       <c r="A1129" s="4" t="inlineStr">
         <is>
-          <t>BA11-11</t>
+          <t>BA11-10</t>
         </is>
       </c>
       <c r="B1129" s="4" t="inlineStr">
@@ -31581,7 +31591,7 @@
     <row r="1130">
       <c r="A1130" s="4" t="inlineStr">
         <is>
-          <t>BA11-12</t>
+          <t>BA11-11</t>
         </is>
       </c>
       <c r="B1130" s="4" t="inlineStr">
@@ -31607,7 +31617,7 @@
     <row r="1131">
       <c r="A1131" s="4" t="inlineStr">
         <is>
-          <t>BA11-13</t>
+          <t>BA11-12</t>
         </is>
       </c>
       <c r="B1131" s="4" t="inlineStr">
@@ -31633,7 +31643,7 @@
     <row r="1132">
       <c r="A1132" s="4" t="inlineStr">
         <is>
-          <t>BA11-14</t>
+          <t>BA11-13</t>
         </is>
       </c>
       <c r="B1132" s="4" t="inlineStr">
@@ -31659,7 +31669,7 @@
     <row r="1133">
       <c r="A1133" s="4" t="inlineStr">
         <is>
-          <t>BA11-15</t>
+          <t>BA11-14</t>
         </is>
       </c>
       <c r="B1133" s="4" t="inlineStr">
@@ -31683,71 +31693,71 @@
       <c r="H1133" s="4" t="n"/>
     </row>
     <row r="1134">
-      <c r="A1134" s="2" t="inlineStr">
+      <c r="A1134" s="4" t="inlineStr">
+        <is>
+          <t>BA11-15</t>
+        </is>
+      </c>
+      <c r="B1134" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1134" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1134" s="4" t="inlineStr">
+        <is>
+          <t>WC Kinder</t>
+        </is>
+      </c>
+      <c r="E1134" s="4" t="n"/>
+      <c r="F1134" s="3" t="n"/>
+      <c r="G1134" s="4" t="n"/>
+      <c r="H1134" s="4" t="n"/>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="2" t="inlineStr">
         <is>
           <t>BA12-01</t>
         </is>
       </c>
-      <c r="B1134" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1134" s="2" t="inlineStr">
+      <c r="B1135" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1135" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1134" s="2" t="inlineStr">
+      <c r="D1135" s="2" t="inlineStr">
         <is>
           <t>WC Personal</t>
         </is>
       </c>
-      <c r="E1134" s="2" t="inlineStr">
+      <c r="E1135" s="2" t="inlineStr">
         <is>
           <t>Ast-Mobile mit Papierwaben</t>
         </is>
       </c>
-      <c r="F1134" s="3" t="n">
+      <c r="F1135" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G1134" s="2" t="inlineStr">
+      <c r="G1135" s="2" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="H1134" s="2" t="n"/>
-    </row>
-    <row r="1135">
-      <c r="A1135" s="4" t="inlineStr">
-        <is>
-          <t>BA12-02</t>
-        </is>
-      </c>
-      <c r="B1135" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1135" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1135" s="4" t="inlineStr">
-        <is>
-          <t>WC Personal</t>
-        </is>
-      </c>
-      <c r="E1135" s="4" t="n"/>
-      <c r="F1135" s="3" t="n"/>
-      <c r="G1135" s="4" t="n"/>
-      <c r="H1135" s="4" t="n"/>
+      <c r="H1135" s="2" t="n"/>
     </row>
     <row r="1136">
       <c r="A1136" s="4" t="inlineStr">
         <is>
-          <t>BA12-03</t>
+          <t>BA12-02</t>
         </is>
       </c>
       <c r="B1136" s="4" t="inlineStr">
@@ -31773,7 +31783,7 @@
     <row r="1137">
       <c r="A1137" s="4" t="inlineStr">
         <is>
-          <t>BA12-04</t>
+          <t>BA12-03</t>
         </is>
       </c>
       <c r="B1137" s="4" t="inlineStr">
@@ -31799,7 +31809,7 @@
     <row r="1138">
       <c r="A1138" s="4" t="inlineStr">
         <is>
-          <t>BA12-05</t>
+          <t>BA12-04</t>
         </is>
       </c>
       <c r="B1138" s="4" t="inlineStr">
@@ -31825,7 +31835,7 @@
     <row r="1139">
       <c r="A1139" s="4" t="inlineStr">
         <is>
-          <t>BA12-06</t>
+          <t>BA12-05</t>
         </is>
       </c>
       <c r="B1139" s="4" t="inlineStr">
@@ -31851,7 +31861,7 @@
     <row r="1140">
       <c r="A1140" s="4" t="inlineStr">
         <is>
-          <t>BA12-07</t>
+          <t>BA12-06</t>
         </is>
       </c>
       <c r="B1140" s="4" t="inlineStr">
@@ -31877,7 +31887,7 @@
     <row r="1141">
       <c r="A1141" s="4" t="inlineStr">
         <is>
-          <t>BA12-08</t>
+          <t>BA12-07</t>
         </is>
       </c>
       <c r="B1141" s="4" t="inlineStr">
@@ -31903,7 +31913,7 @@
     <row r="1142">
       <c r="A1142" s="4" t="inlineStr">
         <is>
-          <t>BA12-09</t>
+          <t>BA12-08</t>
         </is>
       </c>
       <c r="B1142" s="4" t="inlineStr">
@@ -31929,7 +31939,7 @@
     <row r="1143">
       <c r="A1143" s="4" t="inlineStr">
         <is>
-          <t>BA12-10</t>
+          <t>BA12-09</t>
         </is>
       </c>
       <c r="B1143" s="4" t="inlineStr">
@@ -31955,7 +31965,7 @@
     <row r="1144">
       <c r="A1144" s="4" t="inlineStr">
         <is>
-          <t>BA12-11</t>
+          <t>BA12-10</t>
         </is>
       </c>
       <c r="B1144" s="4" t="inlineStr">
@@ -31981,7 +31991,7 @@
     <row r="1145">
       <c r="A1145" s="4" t="inlineStr">
         <is>
-          <t>BA13-01</t>
+          <t>BA12-11</t>
         </is>
       </c>
       <c r="B1145" s="4" t="inlineStr">
@@ -31996,7 +32006,7 @@
       </c>
       <c r="D1145" s="4" t="inlineStr">
         <is>
-          <t>Abstellraum</t>
+          <t>WC Personal</t>
         </is>
       </c>
       <c r="E1145" s="4" t="n"/>
@@ -32007,7 +32017,7 @@
     <row r="1146">
       <c r="A1146" s="4" t="inlineStr">
         <is>
-          <t>BA13-02</t>
+          <t>BA13-01</t>
         </is>
       </c>
       <c r="B1146" s="4" t="inlineStr">
@@ -32033,7 +32043,7 @@
     <row r="1147">
       <c r="A1147" s="4" t="inlineStr">
         <is>
-          <t>BA13-03</t>
+          <t>BA13-02</t>
         </is>
       </c>
       <c r="B1147" s="4" t="inlineStr">
@@ -32059,7 +32069,7 @@
     <row r="1148">
       <c r="A1148" s="4" t="inlineStr">
         <is>
-          <t>BA13-04</t>
+          <t>BA13-03</t>
         </is>
       </c>
       <c r="B1148" s="4" t="inlineStr">
@@ -32085,7 +32095,7 @@
     <row r="1149">
       <c r="A1149" s="4" t="inlineStr">
         <is>
-          <t>BA13-05</t>
+          <t>BA13-04</t>
         </is>
       </c>
       <c r="B1149" s="4" t="inlineStr">
@@ -32111,7 +32121,7 @@
     <row r="1150">
       <c r="A1150" s="4" t="inlineStr">
         <is>
-          <t>BA13-06</t>
+          <t>BA13-05</t>
         </is>
       </c>
       <c r="B1150" s="4" t="inlineStr">
@@ -32137,7 +32147,7 @@
     <row r="1151">
       <c r="A1151" s="4" t="inlineStr">
         <is>
-          <t>BA13-07</t>
+          <t>BA13-06</t>
         </is>
       </c>
       <c r="B1151" s="4" t="inlineStr">
@@ -32163,7 +32173,7 @@
     <row r="1152">
       <c r="A1152" s="4" t="inlineStr">
         <is>
-          <t>BA13-08</t>
+          <t>BA13-07</t>
         </is>
       </c>
       <c r="B1152" s="4" t="inlineStr">
@@ -32189,7 +32199,7 @@
     <row r="1153">
       <c r="A1153" s="4" t="inlineStr">
         <is>
-          <t>BA13-09</t>
+          <t>BA13-08</t>
         </is>
       </c>
       <c r="B1153" s="4" t="inlineStr">
@@ -32215,7 +32225,7 @@
     <row r="1154">
       <c r="A1154" s="4" t="inlineStr">
         <is>
-          <t>BA13-10</t>
+          <t>BA13-09</t>
         </is>
       </c>
       <c r="B1154" s="4" t="inlineStr">
@@ -32241,7 +32251,7 @@
     <row r="1155">
       <c r="A1155" s="4" t="inlineStr">
         <is>
-          <t>BA13-11</t>
+          <t>BA13-10</t>
         </is>
       </c>
       <c r="B1155" s="4" t="inlineStr">
@@ -32267,7 +32277,7 @@
     <row r="1156">
       <c r="A1156" s="4" t="inlineStr">
         <is>
-          <t>BA13-12</t>
+          <t>BA13-11</t>
         </is>
       </c>
       <c r="B1156" s="4" t="inlineStr">
@@ -32293,7 +32303,7 @@
     <row r="1157">
       <c r="A1157" s="4" t="inlineStr">
         <is>
-          <t>BA13-13</t>
+          <t>BA13-12</t>
         </is>
       </c>
       <c r="B1157" s="4" t="inlineStr">
@@ -32319,7 +32329,7 @@
     <row r="1158">
       <c r="A1158" s="4" t="inlineStr">
         <is>
-          <t>BA13-14</t>
+          <t>BA13-13</t>
         </is>
       </c>
       <c r="B1158" s="4" t="inlineStr">
@@ -32345,7 +32355,7 @@
     <row r="1159">
       <c r="A1159" s="4" t="inlineStr">
         <is>
-          <t>BA13-15</t>
+          <t>BA13-14</t>
         </is>
       </c>
       <c r="B1159" s="4" t="inlineStr">
@@ -32369,45 +32379,35 @@
       <c r="H1159" s="4" t="n"/>
     </row>
     <row r="1160">
-      <c r="A1160" s="2" t="inlineStr">
-        <is>
-          <t>TE01-01</t>
-        </is>
-      </c>
-      <c r="B1160" s="2" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1160" s="2" t="inlineStr">
-        <is>
-          <t>ebenerdig</t>
-        </is>
-      </c>
-      <c r="D1160" s="2" t="inlineStr">
-        <is>
-          <t>Terrasse</t>
-        </is>
-      </c>
-      <c r="E1160" s="2" t="inlineStr">
-        <is>
-          <t>Biohort Freizeitbox weiß (Terrasse)</t>
-        </is>
-      </c>
-      <c r="F1160" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1160" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1160" s="2" t="n"/>
+      <c r="A1160" s="4" t="inlineStr">
+        <is>
+          <t>BA13-15</t>
+        </is>
+      </c>
+      <c r="B1160" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1160" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1160" s="4" t="inlineStr">
+        <is>
+          <t>Abstellraum</t>
+        </is>
+      </c>
+      <c r="E1160" s="4" t="n"/>
+      <c r="F1160" s="3" t="n"/>
+      <c r="G1160" s="4" t="n"/>
+      <c r="H1160" s="4" t="n"/>
     </row>
     <row r="1161">
       <c r="A1161" s="2" t="inlineStr">
         <is>
-          <t>TE01-02</t>
+          <t>TE01-01</t>
         </is>
       </c>
       <c r="B1161" s="2" t="inlineStr">
@@ -32427,7 +32427,7 @@
       </c>
       <c r="E1161" s="2" t="inlineStr">
         <is>
-          <t>Gartentisch mit Granitplatte inkl. Stühle und Schutzhülle</t>
+          <t>Biohort Freizeitbox weiß (Terrasse)</t>
         </is>
       </c>
       <c r="F1161" s="3" t="n">
@@ -32443,7 +32443,7 @@
     <row r="1162">
       <c r="A1162" s="2" t="inlineStr">
         <is>
-          <t>TE01-03</t>
+          <t>TE01-02</t>
         </is>
       </c>
       <c r="B1162" s="2" t="inlineStr">
@@ -32463,11 +32463,11 @@
       </c>
       <c r="E1162" s="2" t="inlineStr">
         <is>
-          <t>Textilene-Stapelsessel anthrazit</t>
+          <t>Gartentisch mit Granitplatte inkl. Stühle und Schutzhülle</t>
         </is>
       </c>
       <c r="F1162" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1162" s="2" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
     <row r="1163">
       <c r="A1163" s="2" t="inlineStr">
         <is>
-          <t>TE01-04</t>
+          <t>TE01-03</t>
         </is>
       </c>
       <c r="B1163" s="2" t="inlineStr">
@@ -32499,11 +32499,11 @@
       </c>
       <c r="E1163" s="2" t="inlineStr">
         <is>
-          <t>Weber Genesis Gasgrill</t>
+          <t>Textilene-Stapelsessel anthrazit</t>
         </is>
       </c>
       <c r="F1163" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1163" s="2" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
     <row r="1164">
       <c r="A1164" s="2" t="inlineStr">
         <is>
-          <t>TE01-05</t>
+          <t>TE01-04</t>
         </is>
       </c>
       <c r="B1164" s="2" t="inlineStr">
@@ -32535,7 +32535,7 @@
       </c>
       <c r="E1164" s="2" t="inlineStr">
         <is>
-          <t>Sonnenschirm creme</t>
+          <t>Weber Genesis Gasgrill</t>
         </is>
       </c>
       <c r="F1164" s="3" t="n">
@@ -32549,35 +32549,45 @@
       <c r="H1164" s="2" t="n"/>
     </row>
     <row r="1165">
-      <c r="A1165" s="4" t="inlineStr">
-        <is>
-          <t>TE01-06</t>
-        </is>
-      </c>
-      <c r="B1165" s="4" t="inlineStr">
+      <c r="A1165" s="2" t="inlineStr">
+        <is>
+          <t>TE01-05</t>
+        </is>
+      </c>
+      <c r="B1165" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1165" s="4" t="inlineStr">
+      <c r="C1165" s="2" t="inlineStr">
         <is>
           <t>ebenerdig</t>
         </is>
       </c>
-      <c r="D1165" s="4" t="inlineStr">
+      <c r="D1165" s="2" t="inlineStr">
         <is>
           <t>Terrasse</t>
         </is>
       </c>
-      <c r="E1165" s="4" t="n"/>
-      <c r="F1165" s="3" t="n"/>
-      <c r="G1165" s="4" t="n"/>
-      <c r="H1165" s="4" t="n"/>
+      <c r="E1165" s="2" t="inlineStr">
+        <is>
+          <t>Sonnenschirm creme</t>
+        </is>
+      </c>
+      <c r="F1165" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1165" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1165" s="2" t="n"/>
     </row>
     <row r="1166">
       <c r="A1166" s="4" t="inlineStr">
         <is>
-          <t>TE01-07</t>
+          <t>TE01-06</t>
         </is>
       </c>
       <c r="B1166" s="4" t="inlineStr">
@@ -32603,7 +32613,7 @@
     <row r="1167">
       <c r="A1167" s="4" t="inlineStr">
         <is>
-          <t>TE01-08</t>
+          <t>TE01-07</t>
         </is>
       </c>
       <c r="B1167" s="4" t="inlineStr">
@@ -32629,7 +32639,7 @@
     <row r="1168">
       <c r="A1168" s="4" t="inlineStr">
         <is>
-          <t>TE01-09</t>
+          <t>TE01-08</t>
         </is>
       </c>
       <c r="B1168" s="4" t="inlineStr">
@@ -32655,7 +32665,7 @@
     <row r="1169">
       <c r="A1169" s="4" t="inlineStr">
         <is>
-          <t>TE01-10</t>
+          <t>TE01-09</t>
         </is>
       </c>
       <c r="B1169" s="4" t="inlineStr">
@@ -32681,7 +32691,7 @@
     <row r="1170">
       <c r="A1170" s="4" t="inlineStr">
         <is>
-          <t>TE01-11</t>
+          <t>TE01-10</t>
         </is>
       </c>
       <c r="B1170" s="4" t="inlineStr">
@@ -32707,7 +32717,7 @@
     <row r="1171">
       <c r="A1171" s="4" t="inlineStr">
         <is>
-          <t>TE01-12</t>
+          <t>TE01-11</t>
         </is>
       </c>
       <c r="B1171" s="4" t="inlineStr">
@@ -32733,7 +32743,7 @@
     <row r="1172">
       <c r="A1172" s="4" t="inlineStr">
         <is>
-          <t>TE01-13</t>
+          <t>TE01-12</t>
         </is>
       </c>
       <c r="B1172" s="4" t="inlineStr">
@@ -32759,7 +32769,7 @@
     <row r="1173">
       <c r="A1173" s="4" t="inlineStr">
         <is>
-          <t>TE01-14</t>
+          <t>TE01-13</t>
         </is>
       </c>
       <c r="B1173" s="4" t="inlineStr">
@@ -32785,7 +32795,7 @@
     <row r="1174">
       <c r="A1174" s="4" t="inlineStr">
         <is>
-          <t>TE01-15</t>
+          <t>TE01-14</t>
         </is>
       </c>
       <c r="B1174" s="4" t="inlineStr">
@@ -32811,7 +32821,7 @@
     <row r="1175">
       <c r="A1175" s="4" t="inlineStr">
         <is>
-          <t>TE01-16</t>
+          <t>TE01-15</t>
         </is>
       </c>
       <c r="B1175" s="4" t="inlineStr">
@@ -32837,7 +32847,7 @@
     <row r="1176">
       <c r="A1176" s="4" t="inlineStr">
         <is>
-          <t>TE01-17</t>
+          <t>TE01-16</t>
         </is>
       </c>
       <c r="B1176" s="4" t="inlineStr">
@@ -32863,7 +32873,7 @@
     <row r="1177">
       <c r="A1177" s="4" t="inlineStr">
         <is>
-          <t>TE01-18</t>
+          <t>TE01-17</t>
         </is>
       </c>
       <c r="B1177" s="4" t="inlineStr">
@@ -32889,7 +32899,7 @@
     <row r="1178">
       <c r="A1178" s="4" t="inlineStr">
         <is>
-          <t>TE01-19</t>
+          <t>TE01-18</t>
         </is>
       </c>
       <c r="B1178" s="4" t="inlineStr">
@@ -32915,7 +32925,7 @@
     <row r="1179">
       <c r="A1179" s="4" t="inlineStr">
         <is>
-          <t>TE01-20</t>
+          <t>TE01-19</t>
         </is>
       </c>
       <c r="B1179" s="4" t="inlineStr">
@@ -32941,7 +32951,7 @@
     <row r="1180">
       <c r="A1180" s="4" t="inlineStr">
         <is>
-          <t>TE01-21</t>
+          <t>TE01-20</t>
         </is>
       </c>
       <c r="B1180" s="4" t="inlineStr">
@@ -32967,7 +32977,7 @@
     <row r="1181">
       <c r="A1181" s="4" t="inlineStr">
         <is>
-          <t>TE01-22</t>
+          <t>TE01-21</t>
         </is>
       </c>
       <c r="B1181" s="4" t="inlineStr">
@@ -32993,7 +33003,7 @@
     <row r="1182">
       <c r="A1182" s="4" t="inlineStr">
         <is>
-          <t>TE01-23</t>
+          <t>TE01-22</t>
         </is>
       </c>
       <c r="B1182" s="4" t="inlineStr">
@@ -33019,7 +33029,7 @@
     <row r="1183">
       <c r="A1183" s="4" t="inlineStr">
         <is>
-          <t>TE01-24</t>
+          <t>TE01-23</t>
         </is>
       </c>
       <c r="B1183" s="4" t="inlineStr">
@@ -33045,7 +33055,7 @@
     <row r="1184">
       <c r="A1184" s="4" t="inlineStr">
         <is>
-          <t>TE01-25</t>
+          <t>TE01-24</t>
         </is>
       </c>
       <c r="B1184" s="4" t="inlineStr">
@@ -33071,7 +33081,7 @@
     <row r="1185">
       <c r="A1185" s="4" t="inlineStr">
         <is>
-          <t>TE01-26</t>
+          <t>TE01-25</t>
         </is>
       </c>
       <c r="B1185" s="4" t="inlineStr">
@@ -33097,7 +33107,7 @@
     <row r="1186">
       <c r="A1186" s="4" t="inlineStr">
         <is>
-          <t>TE01-27</t>
+          <t>TE01-26</t>
         </is>
       </c>
       <c r="B1186" s="4" t="inlineStr">
@@ -33123,7 +33133,7 @@
     <row r="1187">
       <c r="A1187" s="4" t="inlineStr">
         <is>
-          <t>TE01-28</t>
+          <t>TE01-27</t>
         </is>
       </c>
       <c r="B1187" s="4" t="inlineStr">
@@ -33149,7 +33159,7 @@
     <row r="1188">
       <c r="A1188" s="4" t="inlineStr">
         <is>
-          <t>TE01-29</t>
+          <t>TE01-28</t>
         </is>
       </c>
       <c r="B1188" s="4" t="inlineStr">
@@ -33175,7 +33185,7 @@
     <row r="1189">
       <c r="A1189" s="4" t="inlineStr">
         <is>
-          <t>TE01-30</t>
+          <t>TE01-29</t>
         </is>
       </c>
       <c r="B1189" s="4" t="inlineStr">
@@ -33201,7 +33211,7 @@
     <row r="1190">
       <c r="A1190" s="4" t="inlineStr">
         <is>
-          <t>TE01-31</t>
+          <t>TE01-30</t>
         </is>
       </c>
       <c r="B1190" s="4" t="inlineStr">
@@ -33227,7 +33237,7 @@
     <row r="1191">
       <c r="A1191" s="4" t="inlineStr">
         <is>
-          <t>TE01-32</t>
+          <t>TE01-31</t>
         </is>
       </c>
       <c r="B1191" s="4" t="inlineStr">
@@ -33253,7 +33263,7 @@
     <row r="1192">
       <c r="A1192" s="4" t="inlineStr">
         <is>
-          <t>TE01-33</t>
+          <t>TE01-32</t>
         </is>
       </c>
       <c r="B1192" s="4" t="inlineStr">
@@ -33279,7 +33289,7 @@
     <row r="1193">
       <c r="A1193" s="4" t="inlineStr">
         <is>
-          <t>TE01-34</t>
+          <t>TE01-33</t>
         </is>
       </c>
       <c r="B1193" s="4" t="inlineStr">
@@ -33305,7 +33315,7 @@
     <row r="1194">
       <c r="A1194" s="4" t="inlineStr">
         <is>
-          <t>TE01-35</t>
+          <t>TE01-34</t>
         </is>
       </c>
       <c r="B1194" s="4" t="inlineStr">
@@ -33331,7 +33341,7 @@
     <row r="1195">
       <c r="A1195" s="4" t="inlineStr">
         <is>
-          <t>TE01-36</t>
+          <t>TE01-35</t>
         </is>
       </c>
       <c r="B1195" s="4" t="inlineStr">
@@ -33357,7 +33367,7 @@
     <row r="1196">
       <c r="A1196" s="4" t="inlineStr">
         <is>
-          <t>TE01-37</t>
+          <t>TE01-36</t>
         </is>
       </c>
       <c r="B1196" s="4" t="inlineStr">
@@ -33383,7 +33393,7 @@
     <row r="1197">
       <c r="A1197" s="4" t="inlineStr">
         <is>
-          <t>TE01-38</t>
+          <t>TE01-37</t>
         </is>
       </c>
       <c r="B1197" s="4" t="inlineStr">
@@ -33409,7 +33419,7 @@
     <row r="1198">
       <c r="A1198" s="4" t="inlineStr">
         <is>
-          <t>TE01-39</t>
+          <t>TE01-38</t>
         </is>
       </c>
       <c r="B1198" s="4" t="inlineStr">
@@ -33435,7 +33445,7 @@
     <row r="1199">
       <c r="A1199" s="4" t="inlineStr">
         <is>
-          <t>TE01-40</t>
+          <t>TE01-39</t>
         </is>
       </c>
       <c r="B1199" s="4" t="inlineStr">
@@ -33459,45 +33469,35 @@
       <c r="H1199" s="4" t="n"/>
     </row>
     <row r="1200">
-      <c r="A1200" s="2" t="inlineStr">
-        <is>
-          <t>TE02-01</t>
-        </is>
-      </c>
-      <c r="B1200" s="2" t="inlineStr">
+      <c r="A1200" s="4" t="inlineStr">
+        <is>
+          <t>TE01-40</t>
+        </is>
+      </c>
+      <c r="B1200" s="4" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1200" s="2" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1200" s="2" t="inlineStr">
-        <is>
-          <t>Dachterrasse</t>
-        </is>
-      </c>
-      <c r="E1200" s="2" t="inlineStr">
-        <is>
-          <t>Pflanzkübel Plastik weiß</t>
-        </is>
-      </c>
-      <c r="F1200" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G1200" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1200" s="2" t="n"/>
+      <c r="C1200" s="4" t="inlineStr">
+        <is>
+          <t>ebenerdig</t>
+        </is>
+      </c>
+      <c r="D1200" s="4" t="inlineStr">
+        <is>
+          <t>Terrasse</t>
+        </is>
+      </c>
+      <c r="E1200" s="4" t="n"/>
+      <c r="F1200" s="3" t="n"/>
+      <c r="G1200" s="4" t="n"/>
+      <c r="H1200" s="4" t="n"/>
     </row>
     <row r="1201">
       <c r="A1201" s="2" t="inlineStr">
         <is>
-          <t>TE02-02</t>
+          <t>TE02-01</t>
         </is>
       </c>
       <c r="B1201" s="2" t="inlineStr">
@@ -33517,7 +33517,7 @@
       </c>
       <c r="E1201" s="2" t="inlineStr">
         <is>
-          <t>Gartenstuhl Kunststoff anthrazit</t>
+          <t>Pflanzkübel Plastik weiß</t>
         </is>
       </c>
       <c r="F1201" s="3" t="n">
@@ -33533,7 +33533,7 @@
     <row r="1202">
       <c r="A1202" s="2" t="inlineStr">
         <is>
-          <t>TE02-03</t>
+          <t>TE02-02</t>
         </is>
       </c>
       <c r="B1202" s="2" t="inlineStr">
@@ -33553,11 +33553,11 @@
       </c>
       <c r="E1202" s="2" t="inlineStr">
         <is>
-          <t>Gartentisch anthrazit</t>
+          <t>Gartenstuhl Kunststoff anthrazit</t>
         </is>
       </c>
       <c r="F1202" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1202" s="2" t="inlineStr">
         <is>
@@ -33569,7 +33569,7 @@
     <row r="1203">
       <c r="A1203" s="2" t="inlineStr">
         <is>
-          <t>TE02-04</t>
+          <t>TE02-03</t>
         </is>
       </c>
       <c r="B1203" s="2" t="inlineStr">
@@ -33589,7 +33589,7 @@
       </c>
       <c r="E1203" s="2" t="inlineStr">
         <is>
-          <t>Teak-Klapptisch rund</t>
+          <t>Gartentisch anthrazit</t>
         </is>
       </c>
       <c r="F1203" s="3" t="n">
@@ -33597,7 +33597,7 @@
       </c>
       <c r="G1203" s="2" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Stück</t>
         </is>
       </c>
       <c r="H1203" s="2" t="n"/>
@@ -33605,7 +33605,7 @@
     <row r="1204">
       <c r="A1204" s="2" t="inlineStr">
         <is>
-          <t>TE02-05</t>
+          <t>TE02-04</t>
         </is>
       </c>
       <c r="B1204" s="2" t="inlineStr">
@@ -33625,15 +33625,15 @@
       </c>
       <c r="E1204" s="2" t="inlineStr">
         <is>
-          <t>Pflanzkübel grau, groß</t>
+          <t>Teak-Klapptisch rund</t>
         </is>
       </c>
       <c r="F1204" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1204" s="2" t="inlineStr">
         <is>
-          <t>Stück</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="H1204" s="2" t="n"/>
@@ -33641,69 +33641,79 @@
     <row r="1205">
       <c r="A1205" s="2" t="inlineStr">
         <is>
+          <t>TE02-05</t>
+        </is>
+      </c>
+      <c r="B1205" s="2" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1205" s="2" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1205" s="2" t="inlineStr">
+        <is>
+          <t>Dachterrasse</t>
+        </is>
+      </c>
+      <c r="E1205" s="2" t="inlineStr">
+        <is>
+          <t>Pflanzkübel grau, groß</t>
+        </is>
+      </c>
+      <c r="F1205" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1205" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1205" s="2" t="n"/>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="2" t="inlineStr">
+        <is>
           <t>TE02-06</t>
         </is>
       </c>
-      <c r="B1205" s="2" t="inlineStr">
+      <c r="B1206" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1205" s="2" t="inlineStr">
+      <c r="C1206" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1205" s="2" t="inlineStr">
+      <c r="D1206" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1205" s="2" t="inlineStr">
+      <c r="E1206" s="2" t="inlineStr">
         <is>
           <t>Holzstern mit Lichterkette</t>
         </is>
       </c>
-      <c r="F1205" s="3" t="n">
+      <c r="F1206" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G1205" s="2" t="inlineStr">
+      <c r="G1206" s="2" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="H1205" s="2" t="n"/>
-    </row>
-    <row r="1206">
-      <c r="A1206" s="4" t="inlineStr">
-        <is>
-          <t>TE02-07</t>
-        </is>
-      </c>
-      <c r="B1206" s="4" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1206" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1206" s="4" t="inlineStr">
-        <is>
-          <t>Dachterrasse</t>
-        </is>
-      </c>
-      <c r="E1206" s="4" t="n"/>
-      <c r="F1206" s="3" t="n"/>
-      <c r="G1206" s="4" t="n"/>
-      <c r="H1206" s="4" t="n"/>
+      <c r="H1206" s="2" t="n"/>
     </row>
     <row r="1207">
       <c r="A1207" s="4" t="inlineStr">
         <is>
-          <t>TE02-08</t>
+          <t>TE02-07</t>
         </is>
       </c>
       <c r="B1207" s="4" t="inlineStr">
@@ -33729,7 +33739,7 @@
     <row r="1208">
       <c r="A1208" s="4" t="inlineStr">
         <is>
-          <t>TE02-09</t>
+          <t>TE02-08</t>
         </is>
       </c>
       <c r="B1208" s="4" t="inlineStr">
@@ -33755,7 +33765,7 @@
     <row r="1209">
       <c r="A1209" s="4" t="inlineStr">
         <is>
-          <t>TE02-10</t>
+          <t>TE02-09</t>
         </is>
       </c>
       <c r="B1209" s="4" t="inlineStr">
@@ -33781,7 +33791,7 @@
     <row r="1210">
       <c r="A1210" s="4" t="inlineStr">
         <is>
-          <t>TE02-11</t>
+          <t>TE02-10</t>
         </is>
       </c>
       <c r="B1210" s="4" t="inlineStr">
@@ -33807,7 +33817,7 @@
     <row r="1211">
       <c r="A1211" s="4" t="inlineStr">
         <is>
-          <t>TE02-12</t>
+          <t>TE02-11</t>
         </is>
       </c>
       <c r="B1211" s="4" t="inlineStr">
@@ -33833,7 +33843,7 @@
     <row r="1212">
       <c r="A1212" s="4" t="inlineStr">
         <is>
-          <t>TE02-13</t>
+          <t>TE02-12</t>
         </is>
       </c>
       <c r="B1212" s="4" t="inlineStr">
@@ -33859,7 +33869,7 @@
     <row r="1213">
       <c r="A1213" s="4" t="inlineStr">
         <is>
-          <t>TE02-14</t>
+          <t>TE02-13</t>
         </is>
       </c>
       <c r="B1213" s="4" t="inlineStr">
@@ -33885,7 +33895,7 @@
     <row r="1214">
       <c r="A1214" s="4" t="inlineStr">
         <is>
-          <t>TE02-15</t>
+          <t>TE02-14</t>
         </is>
       </c>
       <c r="B1214" s="4" t="inlineStr">
@@ -33911,7 +33921,7 @@
     <row r="1215">
       <c r="A1215" s="4" t="inlineStr">
         <is>
-          <t>TE02-16</t>
+          <t>TE02-15</t>
         </is>
       </c>
       <c r="B1215" s="4" t="inlineStr">
@@ -33937,7 +33947,7 @@
     <row r="1216">
       <c r="A1216" s="4" t="inlineStr">
         <is>
-          <t>TE02-17</t>
+          <t>TE02-16</t>
         </is>
       </c>
       <c r="B1216" s="4" t="inlineStr">
@@ -33963,7 +33973,7 @@
     <row r="1217">
       <c r="A1217" s="4" t="inlineStr">
         <is>
-          <t>TE02-18</t>
+          <t>TE02-17</t>
         </is>
       </c>
       <c r="B1217" s="4" t="inlineStr">
@@ -33989,7 +33999,7 @@
     <row r="1218">
       <c r="A1218" s="4" t="inlineStr">
         <is>
-          <t>TE02-19</t>
+          <t>TE02-18</t>
         </is>
       </c>
       <c r="B1218" s="4" t="inlineStr">
@@ -34015,7 +34025,7 @@
     <row r="1219">
       <c r="A1219" s="4" t="inlineStr">
         <is>
-          <t>TE02-20</t>
+          <t>TE02-19</t>
         </is>
       </c>
       <c r="B1219" s="4" t="inlineStr">
@@ -34041,7 +34051,7 @@
     <row r="1220">
       <c r="A1220" s="4" t="inlineStr">
         <is>
-          <t>TE02-21</t>
+          <t>TE02-20</t>
         </is>
       </c>
       <c r="B1220" s="4" t="inlineStr">
@@ -34067,7 +34077,7 @@
     <row r="1221">
       <c r="A1221" s="4" t="inlineStr">
         <is>
-          <t>TE02-22</t>
+          <t>TE02-21</t>
         </is>
       </c>
       <c r="B1221" s="4" t="inlineStr">
@@ -34093,7 +34103,7 @@
     <row r="1222">
       <c r="A1222" s="4" t="inlineStr">
         <is>
-          <t>TE02-23</t>
+          <t>TE02-22</t>
         </is>
       </c>
       <c r="B1222" s="4" t="inlineStr">
@@ -34119,7 +34129,7 @@
     <row r="1223">
       <c r="A1223" s="4" t="inlineStr">
         <is>
-          <t>TE02-24</t>
+          <t>TE02-23</t>
         </is>
       </c>
       <c r="B1223" s="4" t="inlineStr">
@@ -34145,7 +34155,7 @@
     <row r="1224">
       <c r="A1224" s="4" t="inlineStr">
         <is>
-          <t>TE02-25</t>
+          <t>TE02-24</t>
         </is>
       </c>
       <c r="B1224" s="4" t="inlineStr">
@@ -34171,7 +34181,7 @@
     <row r="1225">
       <c r="A1225" s="4" t="inlineStr">
         <is>
-          <t>TE02-26</t>
+          <t>TE02-25</t>
         </is>
       </c>
       <c r="B1225" s="4" t="inlineStr">
@@ -34197,7 +34207,7 @@
     <row r="1226">
       <c r="A1226" s="4" t="inlineStr">
         <is>
-          <t>TE02-27</t>
+          <t>TE02-26</t>
         </is>
       </c>
       <c r="B1226" s="4" t="inlineStr">
@@ -34223,7 +34233,7 @@
     <row r="1227">
       <c r="A1227" s="4" t="inlineStr">
         <is>
-          <t>TE02-28</t>
+          <t>TE02-27</t>
         </is>
       </c>
       <c r="B1227" s="4" t="inlineStr">
@@ -34249,7 +34259,7 @@
     <row r="1228">
       <c r="A1228" s="4" t="inlineStr">
         <is>
-          <t>TE02-29</t>
+          <t>TE02-28</t>
         </is>
       </c>
       <c r="B1228" s="4" t="inlineStr">
@@ -34275,7 +34285,7 @@
     <row r="1229">
       <c r="A1229" s="4" t="inlineStr">
         <is>
-          <t>TE02-30</t>
+          <t>TE02-29</t>
         </is>
       </c>
       <c r="B1229" s="4" t="inlineStr">
@@ -34301,7 +34311,7 @@
     <row r="1230">
       <c r="A1230" s="4" t="inlineStr">
         <is>
-          <t>TE02-31</t>
+          <t>TE02-30</t>
         </is>
       </c>
       <c r="B1230" s="4" t="inlineStr">
@@ -34327,7 +34337,7 @@
     <row r="1231">
       <c r="A1231" s="4" t="inlineStr">
         <is>
-          <t>TE02-32</t>
+          <t>TE02-31</t>
         </is>
       </c>
       <c r="B1231" s="4" t="inlineStr">
@@ -34353,7 +34363,7 @@
     <row r="1232">
       <c r="A1232" s="4" t="inlineStr">
         <is>
-          <t>TE02-33</t>
+          <t>TE02-32</t>
         </is>
       </c>
       <c r="B1232" s="4" t="inlineStr">
@@ -34379,7 +34389,7 @@
     <row r="1233">
       <c r="A1233" s="4" t="inlineStr">
         <is>
-          <t>TE02-34</t>
+          <t>TE02-33</t>
         </is>
       </c>
       <c r="B1233" s="4" t="inlineStr">
@@ -34405,7 +34415,7 @@
     <row r="1234">
       <c r="A1234" s="4" t="inlineStr">
         <is>
-          <t>TE02-35</t>
+          <t>TE02-34</t>
         </is>
       </c>
       <c r="B1234" s="4" t="inlineStr">
@@ -34431,7 +34441,7 @@
     <row r="1235">
       <c r="A1235" s="4" t="inlineStr">
         <is>
-          <t>TE02-36</t>
+          <t>TE02-35</t>
         </is>
       </c>
       <c r="B1235" s="4" t="inlineStr">
@@ -34457,7 +34467,7 @@
     <row r="1236">
       <c r="A1236" s="4" t="inlineStr">
         <is>
-          <t>TE02-37</t>
+          <t>TE02-36</t>
         </is>
       </c>
       <c r="B1236" s="4" t="inlineStr">
@@ -34483,7 +34493,7 @@
     <row r="1237">
       <c r="A1237" s="4" t="inlineStr">
         <is>
-          <t>TE02-38</t>
+          <t>TE02-37</t>
         </is>
       </c>
       <c r="B1237" s="4" t="inlineStr">
@@ -34509,7 +34519,7 @@
     <row r="1238">
       <c r="A1238" s="4" t="inlineStr">
         <is>
-          <t>TE02-39</t>
+          <t>TE02-38</t>
         </is>
       </c>
       <c r="B1238" s="4" t="inlineStr">
@@ -34535,7 +34545,7 @@
     <row r="1239">
       <c r="A1239" s="4" t="inlineStr">
         <is>
-          <t>TE02-40</t>
+          <t>TE02-39</t>
         </is>
       </c>
       <c r="B1239" s="4" t="inlineStr">
@@ -34559,63 +34569,67 @@
       <c r="H1239" s="4" t="n"/>
     </row>
     <row r="1240">
-      <c r="A1240" s="2" t="inlineStr">
+      <c r="A1240" s="4" t="inlineStr">
+        <is>
+          <t>TE02-40</t>
+        </is>
+      </c>
+      <c r="B1240" s="4" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1240" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1240" s="4" t="inlineStr">
+        <is>
+          <t>Dachterrasse</t>
+        </is>
+      </c>
+      <c r="E1240" s="4" t="n"/>
+      <c r="F1240" s="3" t="n"/>
+      <c r="G1240" s="4" t="n"/>
+      <c r="H1240" s="4" t="n"/>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="2" t="inlineStr">
         <is>
           <t>GA01-01</t>
         </is>
       </c>
-      <c r="B1240" s="2" t="inlineStr">
+      <c r="B1241" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1240" s="2" t="inlineStr"/>
-      <c r="D1240" s="2" t="inlineStr">
+      <c r="C1241" s="2" t="inlineStr"/>
+      <c r="D1241" s="2" t="inlineStr">
         <is>
           <t>Gartenanlage</t>
         </is>
       </c>
-      <c r="E1240" s="2" t="inlineStr">
+      <c r="E1241" s="2" t="inlineStr">
         <is>
           <t>Holz-Wellenliege, Doppelliege</t>
         </is>
       </c>
-      <c r="F1240" s="3" t="n">
+      <c r="F1241" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G1240" s="2" t="inlineStr">
+      <c r="G1241" s="2" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="H1240" s="2" t="n"/>
-    </row>
-    <row r="1241">
-      <c r="A1241" s="4" t="inlineStr">
-        <is>
-          <t>GA01-02</t>
-        </is>
-      </c>
-      <c r="B1241" s="4" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1241" s="4" t="inlineStr"/>
-      <c r="D1241" s="4" t="inlineStr">
-        <is>
-          <t>Gartenanlage</t>
-        </is>
-      </c>
-      <c r="E1241" s="4" t="n"/>
-      <c r="F1241" s="3" t="n"/>
-      <c r="G1241" s="4" t="n"/>
-      <c r="H1241" s="4" t="n"/>
+      <c r="H1241" s="2" t="n"/>
     </row>
     <row r="1242">
       <c r="A1242" s="4" t="inlineStr">
         <is>
-          <t>GA01-03</t>
+          <t>GA01-02</t>
         </is>
       </c>
       <c r="B1242" s="4" t="inlineStr">
@@ -34637,7 +34651,7 @@
     <row r="1243">
       <c r="A1243" s="4" t="inlineStr">
         <is>
-          <t>GA01-04</t>
+          <t>GA01-03</t>
         </is>
       </c>
       <c r="B1243" s="4" t="inlineStr">
@@ -34659,7 +34673,7 @@
     <row r="1244">
       <c r="A1244" s="4" t="inlineStr">
         <is>
-          <t>GA01-05</t>
+          <t>GA01-04</t>
         </is>
       </c>
       <c r="B1244" s="4" t="inlineStr">
@@ -34681,7 +34695,7 @@
     <row r="1245">
       <c r="A1245" s="4" t="inlineStr">
         <is>
-          <t>GA01-06</t>
+          <t>GA01-05</t>
         </is>
       </c>
       <c r="B1245" s="4" t="inlineStr">
@@ -34703,7 +34717,7 @@
     <row r="1246">
       <c r="A1246" s="4" t="inlineStr">
         <is>
-          <t>GA01-07</t>
+          <t>GA01-06</t>
         </is>
       </c>
       <c r="B1246" s="4" t="inlineStr">
@@ -34725,7 +34739,7 @@
     <row r="1247">
       <c r="A1247" s="4" t="inlineStr">
         <is>
-          <t>GA01-08</t>
+          <t>GA01-07</t>
         </is>
       </c>
       <c r="B1247" s="4" t="inlineStr">
@@ -34747,7 +34761,7 @@
     <row r="1248">
       <c r="A1248" s="4" t="inlineStr">
         <is>
-          <t>GA01-09</t>
+          <t>GA01-08</t>
         </is>
       </c>
       <c r="B1248" s="4" t="inlineStr">
@@ -34769,7 +34783,7 @@
     <row r="1249">
       <c r="A1249" s="4" t="inlineStr">
         <is>
-          <t>GA01-10</t>
+          <t>GA01-09</t>
         </is>
       </c>
       <c r="B1249" s="4" t="inlineStr">
@@ -34791,7 +34805,7 @@
     <row r="1250">
       <c r="A1250" s="4" t="inlineStr">
         <is>
-          <t>GA01-11</t>
+          <t>GA01-10</t>
         </is>
       </c>
       <c r="B1250" s="4" t="inlineStr">
@@ -34813,7 +34827,7 @@
     <row r="1251">
       <c r="A1251" s="4" t="inlineStr">
         <is>
-          <t>GA01-12</t>
+          <t>GA01-11</t>
         </is>
       </c>
       <c r="B1251" s="4" t="inlineStr">
@@ -34835,7 +34849,7 @@
     <row r="1252">
       <c r="A1252" s="4" t="inlineStr">
         <is>
-          <t>GA01-13</t>
+          <t>GA01-12</t>
         </is>
       </c>
       <c r="B1252" s="4" t="inlineStr">
@@ -34857,7 +34871,7 @@
     <row r="1253">
       <c r="A1253" s="4" t="inlineStr">
         <is>
-          <t>GA01-14</t>
+          <t>GA01-13</t>
         </is>
       </c>
       <c r="B1253" s="4" t="inlineStr">
@@ -34879,7 +34893,7 @@
     <row r="1254">
       <c r="A1254" s="4" t="inlineStr">
         <is>
-          <t>GA01-15</t>
+          <t>GA01-14</t>
         </is>
       </c>
       <c r="B1254" s="4" t="inlineStr">
@@ -34901,7 +34915,7 @@
     <row r="1255">
       <c r="A1255" s="4" t="inlineStr">
         <is>
-          <t>GA01-16</t>
+          <t>GA01-15</t>
         </is>
       </c>
       <c r="B1255" s="4" t="inlineStr">
@@ -34923,7 +34937,7 @@
     <row r="1256">
       <c r="A1256" s="4" t="inlineStr">
         <is>
-          <t>GA01-17</t>
+          <t>GA01-16</t>
         </is>
       </c>
       <c r="B1256" s="4" t="inlineStr">
@@ -34945,7 +34959,7 @@
     <row r="1257">
       <c r="A1257" s="4" t="inlineStr">
         <is>
-          <t>GA01-18</t>
+          <t>GA01-17</t>
         </is>
       </c>
       <c r="B1257" s="4" t="inlineStr">
@@ -34967,7 +34981,7 @@
     <row r="1258">
       <c r="A1258" s="4" t="inlineStr">
         <is>
-          <t>GA01-19</t>
+          <t>GA01-18</t>
         </is>
       </c>
       <c r="B1258" s="4" t="inlineStr">
@@ -34989,7 +35003,7 @@
     <row r="1259">
       <c r="A1259" s="4" t="inlineStr">
         <is>
-          <t>GA01-20</t>
+          <t>GA01-19</t>
         </is>
       </c>
       <c r="B1259" s="4" t="inlineStr">
@@ -35011,7 +35025,7 @@
     <row r="1260">
       <c r="A1260" s="4" t="inlineStr">
         <is>
-          <t>GA01-21</t>
+          <t>GA01-20</t>
         </is>
       </c>
       <c r="B1260" s="4" t="inlineStr">
@@ -35033,7 +35047,7 @@
     <row r="1261">
       <c r="A1261" s="4" t="inlineStr">
         <is>
-          <t>GA01-22</t>
+          <t>GA01-21</t>
         </is>
       </c>
       <c r="B1261" s="4" t="inlineStr">
@@ -35055,7 +35069,7 @@
     <row r="1262">
       <c r="A1262" s="4" t="inlineStr">
         <is>
-          <t>GA01-23</t>
+          <t>GA01-22</t>
         </is>
       </c>
       <c r="B1262" s="4" t="inlineStr">
@@ -35077,7 +35091,7 @@
     <row r="1263">
       <c r="A1263" s="4" t="inlineStr">
         <is>
-          <t>GA01-24</t>
+          <t>GA01-23</t>
         </is>
       </c>
       <c r="B1263" s="4" t="inlineStr">
@@ -35099,7 +35113,7 @@
     <row r="1264">
       <c r="A1264" s="4" t="inlineStr">
         <is>
-          <t>GA01-25</t>
+          <t>GA01-24</t>
         </is>
       </c>
       <c r="B1264" s="4" t="inlineStr">
@@ -35121,7 +35135,7 @@
     <row r="1265">
       <c r="A1265" s="4" t="inlineStr">
         <is>
-          <t>GA01-26</t>
+          <t>GA01-25</t>
         </is>
       </c>
       <c r="B1265" s="4" t="inlineStr">
@@ -35143,7 +35157,7 @@
     <row r="1266">
       <c r="A1266" s="4" t="inlineStr">
         <is>
-          <t>GA01-27</t>
+          <t>GA01-26</t>
         </is>
       </c>
       <c r="B1266" s="4" t="inlineStr">
@@ -35165,7 +35179,7 @@
     <row r="1267">
       <c r="A1267" s="4" t="inlineStr">
         <is>
-          <t>GA01-28</t>
+          <t>GA01-27</t>
         </is>
       </c>
       <c r="B1267" s="4" t="inlineStr">
@@ -35187,7 +35201,7 @@
     <row r="1268">
       <c r="A1268" s="4" t="inlineStr">
         <is>
-          <t>GA01-29</t>
+          <t>GA01-28</t>
         </is>
       </c>
       <c r="B1268" s="4" t="inlineStr">
@@ -35209,7 +35223,7 @@
     <row r="1269">
       <c r="A1269" s="4" t="inlineStr">
         <is>
-          <t>GA01-30</t>
+          <t>GA01-29</t>
         </is>
       </c>
       <c r="B1269" s="4" t="inlineStr">
@@ -35231,7 +35245,7 @@
     <row r="1270">
       <c r="A1270" s="4" t="inlineStr">
         <is>
-          <t>GA01-31</t>
+          <t>GA01-30</t>
         </is>
       </c>
       <c r="B1270" s="4" t="inlineStr">
@@ -35253,7 +35267,7 @@
     <row r="1271">
       <c r="A1271" s="4" t="inlineStr">
         <is>
-          <t>GA01-32</t>
+          <t>GA01-31</t>
         </is>
       </c>
       <c r="B1271" s="4" t="inlineStr">
@@ -35275,7 +35289,7 @@
     <row r="1272">
       <c r="A1272" s="4" t="inlineStr">
         <is>
-          <t>GA01-33</t>
+          <t>GA01-32</t>
         </is>
       </c>
       <c r="B1272" s="4" t="inlineStr">
@@ -35297,7 +35311,7 @@
     <row r="1273">
       <c r="A1273" s="4" t="inlineStr">
         <is>
-          <t>GA01-34</t>
+          <t>GA01-33</t>
         </is>
       </c>
       <c r="B1273" s="4" t="inlineStr">
@@ -35319,7 +35333,7 @@
     <row r="1274">
       <c r="A1274" s="4" t="inlineStr">
         <is>
-          <t>GA01-35</t>
+          <t>GA01-34</t>
         </is>
       </c>
       <c r="B1274" s="4" t="inlineStr">
@@ -35341,7 +35355,7 @@
     <row r="1275">
       <c r="A1275" s="4" t="inlineStr">
         <is>
-          <t>GA01-36</t>
+          <t>GA01-35</t>
         </is>
       </c>
       <c r="B1275" s="4" t="inlineStr">
@@ -35363,7 +35377,7 @@
     <row r="1276">
       <c r="A1276" s="4" t="inlineStr">
         <is>
-          <t>GA01-37</t>
+          <t>GA01-36</t>
         </is>
       </c>
       <c r="B1276" s="4" t="inlineStr">
@@ -35385,7 +35399,7 @@
     <row r="1277">
       <c r="A1277" s="4" t="inlineStr">
         <is>
-          <t>GA01-38</t>
+          <t>GA01-37</t>
         </is>
       </c>
       <c r="B1277" s="4" t="inlineStr">
@@ -35407,7 +35421,7 @@
     <row r="1278">
       <c r="A1278" s="4" t="inlineStr">
         <is>
-          <t>GA01-39</t>
+          <t>GA01-38</t>
         </is>
       </c>
       <c r="B1278" s="4" t="inlineStr">
@@ -35429,7 +35443,7 @@
     <row r="1279">
       <c r="A1279" s="4" t="inlineStr">
         <is>
-          <t>GA01-40</t>
+          <t>GA01-39</t>
         </is>
       </c>
       <c r="B1279" s="4" t="inlineStr">
@@ -35448,10 +35462,32 @@
       <c r="G1279" s="4" t="n"/>
       <c r="H1279" s="4" t="n"/>
     </row>
+    <row r="1280">
+      <c r="A1280" s="4" t="inlineStr">
+        <is>
+          <t>GA01-40</t>
+        </is>
+      </c>
+      <c r="B1280" s="4" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1280" s="4" t="inlineStr"/>
+      <c r="D1280" s="4" t="inlineStr">
+        <is>
+          <t>Gartenanlage</t>
+        </is>
+      </c>
+      <c r="E1280" s="4" t="n"/>
+      <c r="F1280" s="3" t="n"/>
+      <c r="G1280" s="4" t="n"/>
+      <c r="H1280" s="4" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1279"/>
+  <autoFilter ref="A1:H1280"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F1279" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen." type="whole" operator="greaterThan">
+    <dataValidation sqref="F2:F1280" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -7523,238 +7523,328 @@
       <c r="H223" s="4" t="n"/>
     </row>
     <row r="224">
-      <c r="A224" s="4" t="inlineStr">
+      <c r="A224" s="2" t="inlineStr">
         <is>
           <t>NE02-01</t>
         </is>
       </c>
-      <c r="B224" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C224" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D224" s="4" t="inlineStr">
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
         <is>
           <t>Küche</t>
         </is>
       </c>
-      <c r="E224" s="4" t="n"/>
-      <c r="F224" s="3" t="n"/>
-      <c r="G224" s="4" t="n"/>
-      <c r="H224" s="4" t="n"/>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>Hirsch Metall, stehend</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="n"/>
     </row>
     <row r="225">
-      <c r="A225" s="4" t="inlineStr">
+      <c r="A225" s="2" t="inlineStr">
         <is>
           <t>NE02-02</t>
         </is>
       </c>
-      <c r="B225" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C225" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D225" s="4" t="inlineStr">
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>Küche</t>
         </is>
       </c>
-      <c r="E225" s="4" t="n"/>
-      <c r="F225" s="3" t="n"/>
-      <c r="G225" s="4" t="n"/>
-      <c r="H225" s="4" t="n"/>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>Barhocker dunkelgrau, Erwachsenenhöhe</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="n"/>
     </row>
     <row r="226">
-      <c r="A226" s="4" t="inlineStr">
+      <c r="A226" s="2" t="inlineStr">
         <is>
           <t>NE02-03</t>
         </is>
       </c>
-      <c r="B226" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C226" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D226" s="4" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>Küche</t>
         </is>
       </c>
-      <c r="E226" s="4" t="n"/>
-      <c r="F226" s="3" t="n"/>
-      <c r="G226" s="4" t="n"/>
-      <c r="H226" s="4" t="n"/>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>Wäschekorb schwarz mit Deckel</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="n"/>
     </row>
     <row r="227">
-      <c r="A227" s="4" t="inlineStr">
+      <c r="A227" s="2" t="inlineStr">
         <is>
           <t>NE02-04</t>
         </is>
       </c>
-      <c r="B227" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C227" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D227" s="4" t="inlineStr">
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
         <is>
           <t>Küche</t>
         </is>
       </c>
-      <c r="E227" s="4" t="n"/>
-      <c r="F227" s="3" t="n"/>
-      <c r="G227" s="4" t="n"/>
-      <c r="H227" s="4" t="n"/>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>Mülleimer Kunststoff schwarz, groß</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="n"/>
     </row>
     <row r="228">
-      <c r="A228" s="4" t="inlineStr">
+      <c r="A228" s="2" t="inlineStr">
         <is>
           <t>NE02-05</t>
         </is>
       </c>
-      <c r="B228" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C228" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D228" s="4" t="inlineStr">
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>Küche</t>
         </is>
       </c>
-      <c r="E228" s="4" t="n"/>
-      <c r="F228" s="3" t="n"/>
-      <c r="G228" s="4" t="n"/>
-      <c r="H228" s="4" t="n"/>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Trinkbecher Kinder, bunt</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="n"/>
     </row>
     <row r="229">
-      <c r="A229" s="4" t="inlineStr">
+      <c r="A229" s="2" t="inlineStr">
         <is>
           <t>NE02-06</t>
         </is>
       </c>
-      <c r="B229" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C229" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D229" s="4" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>Küche</t>
         </is>
       </c>
-      <c r="E229" s="4" t="n"/>
-      <c r="F229" s="3" t="n"/>
-      <c r="G229" s="4" t="n"/>
-      <c r="H229" s="4" t="n"/>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>Trinkbecher Melamin, grün- und grautöne</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="n"/>
     </row>
     <row r="230">
-      <c r="A230" s="4" t="inlineStr">
+      <c r="A230" s="2" t="inlineStr">
         <is>
           <t>NE02-07</t>
         </is>
       </c>
-      <c r="B230" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C230" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D230" s="4" t="inlineStr">
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
         <is>
           <t>Küche</t>
         </is>
       </c>
-      <c r="E230" s="4" t="n"/>
-      <c r="F230" s="3" t="n"/>
-      <c r="G230" s="4" t="n"/>
-      <c r="H230" s="4" t="n"/>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>Teller Kunststoff, bunt</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="n"/>
     </row>
     <row r="231">
-      <c r="A231" s="4" t="inlineStr">
+      <c r="A231" s="2" t="inlineStr">
         <is>
           <t>NE02-08</t>
         </is>
       </c>
-      <c r="B231" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C231" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D231" s="4" t="inlineStr">
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
         <is>
           <t>Küche</t>
         </is>
       </c>
-      <c r="E231" s="4" t="n"/>
-      <c r="F231" s="3" t="n"/>
-      <c r="G231" s="4" t="n"/>
-      <c r="H231" s="4" t="n"/>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>Schriftzug „Sterneküche", schwarz</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="n"/>
     </row>
     <row r="232">
-      <c r="A232" s="4" t="inlineStr">
+      <c r="A232" s="2" t="inlineStr">
         <is>
           <t>NE02-09</t>
         </is>
       </c>
-      <c r="B232" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C232" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D232" s="4" t="inlineStr">
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>Küche</t>
         </is>
       </c>
-      <c r="E232" s="4" t="n"/>
-      <c r="F232" s="3" t="n"/>
-      <c r="G232" s="4" t="n"/>
-      <c r="H232" s="4" t="n"/>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>Tablett weiß mit Streifenmuster</t>
+        </is>
+      </c>
+      <c r="F232" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="4" t="inlineStr">

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anleitung" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Erfassung'!$A$1:$H$1280</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Erfassung'!$A$1:$H$1283</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1280"/>
+  <dimension ref="A1:H1283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30601,7 +30601,7 @@
         </is>
       </c>
       <c r="F1091" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1091" s="2" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         </is>
       </c>
       <c r="F1105" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1105" s="2" t="inlineStr">
         <is>
@@ -31159,82 +31159,112 @@
       <c r="H1109" s="2" t="n"/>
     </row>
     <row r="1110">
-      <c r="A1110" s="4" t="inlineStr">
+      <c r="A1110" s="2" t="inlineStr">
         <is>
           <t>BA10-09</t>
         </is>
       </c>
-      <c r="B1110" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1110" s="4" t="inlineStr">
+      <c r="B1110" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1110" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1110" s="4" t="inlineStr">
+      <c r="D1110" s="2" t="inlineStr">
         <is>
           <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
-      <c r="E1110" s="4" t="n"/>
-      <c r="F1110" s="3" t="n"/>
-      <c r="G1110" s="4" t="n"/>
-      <c r="H1110" s="4" t="n"/>
+      <c r="E1110" s="2" t="inlineStr">
+        <is>
+          <t>Beistelltisch rund, Tablettplatte Birke</t>
+        </is>
+      </c>
+      <c r="F1110" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1110" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1110" s="2" t="n"/>
     </row>
     <row r="1111">
-      <c r="A1111" s="4" t="inlineStr">
+      <c r="A1111" s="2" t="inlineStr">
         <is>
           <t>BA10-10</t>
         </is>
       </c>
-      <c r="B1111" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1111" s="4" t="inlineStr">
+      <c r="B1111" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1111" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1111" s="4" t="inlineStr">
+      <c r="D1111" s="2" t="inlineStr">
         <is>
           <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
-      <c r="E1111" s="4" t="n"/>
-      <c r="F1111" s="3" t="n"/>
-      <c r="G1111" s="4" t="n"/>
-      <c r="H1111" s="4" t="n"/>
+      <c r="E1111" s="2" t="inlineStr">
+        <is>
+          <t>Beistelltisch rund, Tablettplatte schwarz</t>
+        </is>
+      </c>
+      <c r="F1111" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1111" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1111" s="2" t="n"/>
     </row>
     <row r="1112">
-      <c r="A1112" s="4" t="inlineStr">
+      <c r="A1112" s="2" t="inlineStr">
         <is>
           <t>BA10-11</t>
         </is>
       </c>
-      <c r="B1112" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1112" s="4" t="inlineStr">
+      <c r="B1112" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1112" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1112" s="4" t="inlineStr">
+      <c r="D1112" s="2" t="inlineStr">
         <is>
           <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
-      <c r="E1112" s="4" t="n"/>
-      <c r="F1112" s="3" t="n"/>
-      <c r="G1112" s="4" t="n"/>
-      <c r="H1112" s="4" t="n"/>
+      <c r="E1112" s="2" t="inlineStr">
+        <is>
+          <t>Tisch rund, zweiteilig, weiß</t>
+        </is>
+      </c>
+      <c r="F1112" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1112" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1112" s="2" t="n"/>
     </row>
     <row r="1113">
       <c r="A1113" s="4" t="inlineStr">
@@ -31421,7 +31451,7 @@
     <row r="1120">
       <c r="A1120" s="4" t="inlineStr">
         <is>
-          <t>BA11-01</t>
+          <t>BA10-19</t>
         </is>
       </c>
       <c r="B1120" s="4" t="inlineStr">
@@ -31436,7 +31466,7 @@
       </c>
       <c r="D1120" s="4" t="inlineStr">
         <is>
-          <t>WC Kinder</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="E1120" s="4" t="n"/>
@@ -31447,7 +31477,7 @@
     <row r="1121">
       <c r="A1121" s="4" t="inlineStr">
         <is>
-          <t>BA11-02</t>
+          <t>BA10-20</t>
         </is>
       </c>
       <c r="B1121" s="4" t="inlineStr">
@@ -31462,7 +31492,7 @@
       </c>
       <c r="D1121" s="4" t="inlineStr">
         <is>
-          <t>WC Kinder</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="E1121" s="4" t="n"/>
@@ -31473,7 +31503,7 @@
     <row r="1122">
       <c r="A1122" s="4" t="inlineStr">
         <is>
-          <t>BA11-03</t>
+          <t>BA10-21</t>
         </is>
       </c>
       <c r="B1122" s="4" t="inlineStr">
@@ -31488,7 +31518,7 @@
       </c>
       <c r="D1122" s="4" t="inlineStr">
         <is>
-          <t>WC Kinder</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="E1122" s="4" t="n"/>
@@ -31499,7 +31529,7 @@
     <row r="1123">
       <c r="A1123" s="4" t="inlineStr">
         <is>
-          <t>BA11-04</t>
+          <t>BA11-01</t>
         </is>
       </c>
       <c r="B1123" s="4" t="inlineStr">
@@ -31525,7 +31555,7 @@
     <row r="1124">
       <c r="A1124" s="4" t="inlineStr">
         <is>
-          <t>BA11-05</t>
+          <t>BA11-02</t>
         </is>
       </c>
       <c r="B1124" s="4" t="inlineStr">
@@ -31551,7 +31581,7 @@
     <row r="1125">
       <c r="A1125" s="4" t="inlineStr">
         <is>
-          <t>BA11-06</t>
+          <t>BA11-03</t>
         </is>
       </c>
       <c r="B1125" s="4" t="inlineStr">
@@ -31577,7 +31607,7 @@
     <row r="1126">
       <c r="A1126" s="4" t="inlineStr">
         <is>
-          <t>BA11-07</t>
+          <t>BA11-04</t>
         </is>
       </c>
       <c r="B1126" s="4" t="inlineStr">
@@ -31603,7 +31633,7 @@
     <row r="1127">
       <c r="A1127" s="4" t="inlineStr">
         <is>
-          <t>BA11-08</t>
+          <t>BA11-05</t>
         </is>
       </c>
       <c r="B1127" s="4" t="inlineStr">
@@ -31629,7 +31659,7 @@
     <row r="1128">
       <c r="A1128" s="4" t="inlineStr">
         <is>
-          <t>BA11-09</t>
+          <t>BA11-06</t>
         </is>
       </c>
       <c r="B1128" s="4" t="inlineStr">
@@ -31655,7 +31685,7 @@
     <row r="1129">
       <c r="A1129" s="4" t="inlineStr">
         <is>
-          <t>BA11-10</t>
+          <t>BA11-07</t>
         </is>
       </c>
       <c r="B1129" s="4" t="inlineStr">
@@ -31681,7 +31711,7 @@
     <row r="1130">
       <c r="A1130" s="4" t="inlineStr">
         <is>
-          <t>BA11-11</t>
+          <t>BA11-08</t>
         </is>
       </c>
       <c r="B1130" s="4" t="inlineStr">
@@ -31707,7 +31737,7 @@
     <row r="1131">
       <c r="A1131" s="4" t="inlineStr">
         <is>
-          <t>BA11-12</t>
+          <t>BA11-09</t>
         </is>
       </c>
       <c r="B1131" s="4" t="inlineStr">
@@ -31733,7 +31763,7 @@
     <row r="1132">
       <c r="A1132" s="4" t="inlineStr">
         <is>
-          <t>BA11-13</t>
+          <t>BA11-10</t>
         </is>
       </c>
       <c r="B1132" s="4" t="inlineStr">
@@ -31759,7 +31789,7 @@
     <row r="1133">
       <c r="A1133" s="4" t="inlineStr">
         <is>
-          <t>BA11-14</t>
+          <t>BA11-11</t>
         </is>
       </c>
       <c r="B1133" s="4" t="inlineStr">
@@ -31785,7 +31815,7 @@
     <row r="1134">
       <c r="A1134" s="4" t="inlineStr">
         <is>
-          <t>BA11-15</t>
+          <t>BA11-12</t>
         </is>
       </c>
       <c r="B1134" s="4" t="inlineStr">
@@ -31809,45 +31839,35 @@
       <c r="H1134" s="4" t="n"/>
     </row>
     <row r="1135">
-      <c r="A1135" s="2" t="inlineStr">
-        <is>
-          <t>BA12-01</t>
-        </is>
-      </c>
-      <c r="B1135" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1135" s="2" t="inlineStr">
+      <c r="A1135" s="4" t="inlineStr">
+        <is>
+          <t>BA11-13</t>
+        </is>
+      </c>
+      <c r="B1135" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1135" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1135" s="2" t="inlineStr">
-        <is>
-          <t>WC Personal</t>
-        </is>
-      </c>
-      <c r="E1135" s="2" t="inlineStr">
-        <is>
-          <t>Ast-Mobile mit Papierwaben</t>
-        </is>
-      </c>
-      <c r="F1135" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1135" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1135" s="2" t="n"/>
+      <c r="D1135" s="4" t="inlineStr">
+        <is>
+          <t>WC Kinder</t>
+        </is>
+      </c>
+      <c r="E1135" s="4" t="n"/>
+      <c r="F1135" s="3" t="n"/>
+      <c r="G1135" s="4" t="n"/>
+      <c r="H1135" s="4" t="n"/>
     </row>
     <row r="1136">
       <c r="A1136" s="4" t="inlineStr">
         <is>
-          <t>BA12-02</t>
+          <t>BA11-14</t>
         </is>
       </c>
       <c r="B1136" s="4" t="inlineStr">
@@ -31862,7 +31882,7 @@
       </c>
       <c r="D1136" s="4" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>WC Kinder</t>
         </is>
       </c>
       <c r="E1136" s="4" t="n"/>
@@ -31873,7 +31893,7 @@
     <row r="1137">
       <c r="A1137" s="4" t="inlineStr">
         <is>
-          <t>BA12-03</t>
+          <t>BA11-15</t>
         </is>
       </c>
       <c r="B1137" s="4" t="inlineStr">
@@ -31888,7 +31908,7 @@
       </c>
       <c r="D1137" s="4" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>WC Kinder</t>
         </is>
       </c>
       <c r="E1137" s="4" t="n"/>
@@ -31897,35 +31917,45 @@
       <c r="H1137" s="4" t="n"/>
     </row>
     <row r="1138">
-      <c r="A1138" s="4" t="inlineStr">
-        <is>
-          <t>BA12-04</t>
-        </is>
-      </c>
-      <c r="B1138" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1138" s="4" t="inlineStr">
+      <c r="A1138" s="2" t="inlineStr">
+        <is>
+          <t>BA12-01</t>
+        </is>
+      </c>
+      <c r="B1138" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1138" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1138" s="4" t="inlineStr">
+      <c r="D1138" s="2" t="inlineStr">
         <is>
           <t>WC Personal</t>
         </is>
       </c>
-      <c r="E1138" s="4" t="n"/>
-      <c r="F1138" s="3" t="n"/>
-      <c r="G1138" s="4" t="n"/>
-      <c r="H1138" s="4" t="n"/>
+      <c r="E1138" s="2" t="inlineStr">
+        <is>
+          <t>Ast-Mobile mit Papierwaben</t>
+        </is>
+      </c>
+      <c r="F1138" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1138" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1138" s="2" t="n"/>
     </row>
     <row r="1139">
       <c r="A1139" s="4" t="inlineStr">
         <is>
-          <t>BA12-05</t>
+          <t>BA12-02</t>
         </is>
       </c>
       <c r="B1139" s="4" t="inlineStr">
@@ -31951,7 +31981,7 @@
     <row r="1140">
       <c r="A1140" s="4" t="inlineStr">
         <is>
-          <t>BA12-06</t>
+          <t>BA12-03</t>
         </is>
       </c>
       <c r="B1140" s="4" t="inlineStr">
@@ -31977,7 +32007,7 @@
     <row r="1141">
       <c r="A1141" s="4" t="inlineStr">
         <is>
-          <t>BA12-07</t>
+          <t>BA12-04</t>
         </is>
       </c>
       <c r="B1141" s="4" t="inlineStr">
@@ -32003,7 +32033,7 @@
     <row r="1142">
       <c r="A1142" s="4" t="inlineStr">
         <is>
-          <t>BA12-08</t>
+          <t>BA12-05</t>
         </is>
       </c>
       <c r="B1142" s="4" t="inlineStr">
@@ -32029,7 +32059,7 @@
     <row r="1143">
       <c r="A1143" s="4" t="inlineStr">
         <is>
-          <t>BA12-09</t>
+          <t>BA12-06</t>
         </is>
       </c>
       <c r="B1143" s="4" t="inlineStr">
@@ -32055,7 +32085,7 @@
     <row r="1144">
       <c r="A1144" s="4" t="inlineStr">
         <is>
-          <t>BA12-10</t>
+          <t>BA12-07</t>
         </is>
       </c>
       <c r="B1144" s="4" t="inlineStr">
@@ -32081,7 +32111,7 @@
     <row r="1145">
       <c r="A1145" s="4" t="inlineStr">
         <is>
-          <t>BA12-11</t>
+          <t>BA12-08</t>
         </is>
       </c>
       <c r="B1145" s="4" t="inlineStr">
@@ -32107,7 +32137,7 @@
     <row r="1146">
       <c r="A1146" s="4" t="inlineStr">
         <is>
-          <t>BA13-01</t>
+          <t>BA12-09</t>
         </is>
       </c>
       <c r="B1146" s="4" t="inlineStr">
@@ -32122,7 +32152,7 @@
       </c>
       <c r="D1146" s="4" t="inlineStr">
         <is>
-          <t>Abstellraum</t>
+          <t>WC Personal</t>
         </is>
       </c>
       <c r="E1146" s="4" t="n"/>
@@ -32133,7 +32163,7 @@
     <row r="1147">
       <c r="A1147" s="4" t="inlineStr">
         <is>
-          <t>BA13-02</t>
+          <t>BA12-10</t>
         </is>
       </c>
       <c r="B1147" s="4" t="inlineStr">
@@ -32148,7 +32178,7 @@
       </c>
       <c r="D1147" s="4" t="inlineStr">
         <is>
-          <t>Abstellraum</t>
+          <t>WC Personal</t>
         </is>
       </c>
       <c r="E1147" s="4" t="n"/>
@@ -32159,7 +32189,7 @@
     <row r="1148">
       <c r="A1148" s="4" t="inlineStr">
         <is>
-          <t>BA13-03</t>
+          <t>BA12-11</t>
         </is>
       </c>
       <c r="B1148" s="4" t="inlineStr">
@@ -32174,7 +32204,7 @@
       </c>
       <c r="D1148" s="4" t="inlineStr">
         <is>
-          <t>Abstellraum</t>
+          <t>WC Personal</t>
         </is>
       </c>
       <c r="E1148" s="4" t="n"/>
@@ -32185,7 +32215,7 @@
     <row r="1149">
       <c r="A1149" s="4" t="inlineStr">
         <is>
-          <t>BA13-04</t>
+          <t>BA13-01</t>
         </is>
       </c>
       <c r="B1149" s="4" t="inlineStr">
@@ -32211,7 +32241,7 @@
     <row r="1150">
       <c r="A1150" s="4" t="inlineStr">
         <is>
-          <t>BA13-05</t>
+          <t>BA13-02</t>
         </is>
       </c>
       <c r="B1150" s="4" t="inlineStr">
@@ -32237,7 +32267,7 @@
     <row r="1151">
       <c r="A1151" s="4" t="inlineStr">
         <is>
-          <t>BA13-06</t>
+          <t>BA13-03</t>
         </is>
       </c>
       <c r="B1151" s="4" t="inlineStr">
@@ -32263,7 +32293,7 @@
     <row r="1152">
       <c r="A1152" s="4" t="inlineStr">
         <is>
-          <t>BA13-07</t>
+          <t>BA13-04</t>
         </is>
       </c>
       <c r="B1152" s="4" t="inlineStr">
@@ -32289,7 +32319,7 @@
     <row r="1153">
       <c r="A1153" s="4" t="inlineStr">
         <is>
-          <t>BA13-08</t>
+          <t>BA13-05</t>
         </is>
       </c>
       <c r="B1153" s="4" t="inlineStr">
@@ -32315,7 +32345,7 @@
     <row r="1154">
       <c r="A1154" s="4" t="inlineStr">
         <is>
-          <t>BA13-09</t>
+          <t>BA13-06</t>
         </is>
       </c>
       <c r="B1154" s="4" t="inlineStr">
@@ -32341,7 +32371,7 @@
     <row r="1155">
       <c r="A1155" s="4" t="inlineStr">
         <is>
-          <t>BA13-10</t>
+          <t>BA13-07</t>
         </is>
       </c>
       <c r="B1155" s="4" t="inlineStr">
@@ -32367,7 +32397,7 @@
     <row r="1156">
       <c r="A1156" s="4" t="inlineStr">
         <is>
-          <t>BA13-11</t>
+          <t>BA13-08</t>
         </is>
       </c>
       <c r="B1156" s="4" t="inlineStr">
@@ -32393,7 +32423,7 @@
     <row r="1157">
       <c r="A1157" s="4" t="inlineStr">
         <is>
-          <t>BA13-12</t>
+          <t>BA13-09</t>
         </is>
       </c>
       <c r="B1157" s="4" t="inlineStr">
@@ -32419,7 +32449,7 @@
     <row r="1158">
       <c r="A1158" s="4" t="inlineStr">
         <is>
-          <t>BA13-13</t>
+          <t>BA13-10</t>
         </is>
       </c>
       <c r="B1158" s="4" t="inlineStr">
@@ -32445,7 +32475,7 @@
     <row r="1159">
       <c r="A1159" s="4" t="inlineStr">
         <is>
-          <t>BA13-14</t>
+          <t>BA13-11</t>
         </is>
       </c>
       <c r="B1159" s="4" t="inlineStr">
@@ -32471,7 +32501,7 @@
     <row r="1160">
       <c r="A1160" s="4" t="inlineStr">
         <is>
-          <t>BA13-15</t>
+          <t>BA13-12</t>
         </is>
       </c>
       <c r="B1160" s="4" t="inlineStr">
@@ -32495,117 +32525,87 @@
       <c r="H1160" s="4" t="n"/>
     </row>
     <row r="1161">
-      <c r="A1161" s="2" t="inlineStr">
-        <is>
-          <t>TE01-01</t>
-        </is>
-      </c>
-      <c r="B1161" s="2" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1161" s="2" t="inlineStr">
-        <is>
-          <t>ebenerdig</t>
-        </is>
-      </c>
-      <c r="D1161" s="2" t="inlineStr">
-        <is>
-          <t>Terrasse</t>
-        </is>
-      </c>
-      <c r="E1161" s="2" t="inlineStr">
-        <is>
-          <t>Biohort Freizeitbox weiß (Terrasse)</t>
-        </is>
-      </c>
-      <c r="F1161" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1161" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1161" s="2" t="n"/>
+      <c r="A1161" s="4" t="inlineStr">
+        <is>
+          <t>BA13-13</t>
+        </is>
+      </c>
+      <c r="B1161" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1161" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1161" s="4" t="inlineStr">
+        <is>
+          <t>Abstellraum</t>
+        </is>
+      </c>
+      <c r="E1161" s="4" t="n"/>
+      <c r="F1161" s="3" t="n"/>
+      <c r="G1161" s="4" t="n"/>
+      <c r="H1161" s="4" t="n"/>
     </row>
     <row r="1162">
-      <c r="A1162" s="2" t="inlineStr">
-        <is>
-          <t>TE01-02</t>
-        </is>
-      </c>
-      <c r="B1162" s="2" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1162" s="2" t="inlineStr">
-        <is>
-          <t>ebenerdig</t>
-        </is>
-      </c>
-      <c r="D1162" s="2" t="inlineStr">
-        <is>
-          <t>Terrasse</t>
-        </is>
-      </c>
-      <c r="E1162" s="2" t="inlineStr">
-        <is>
-          <t>Gartentisch mit Granitplatte inkl. Stühle und Schutzhülle</t>
-        </is>
-      </c>
-      <c r="F1162" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1162" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1162" s="2" t="n"/>
+      <c r="A1162" s="4" t="inlineStr">
+        <is>
+          <t>BA13-14</t>
+        </is>
+      </c>
+      <c r="B1162" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1162" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1162" s="4" t="inlineStr">
+        <is>
+          <t>Abstellraum</t>
+        </is>
+      </c>
+      <c r="E1162" s="4" t="n"/>
+      <c r="F1162" s="3" t="n"/>
+      <c r="G1162" s="4" t="n"/>
+      <c r="H1162" s="4" t="n"/>
     </row>
     <row r="1163">
-      <c r="A1163" s="2" t="inlineStr">
-        <is>
-          <t>TE01-03</t>
-        </is>
-      </c>
-      <c r="B1163" s="2" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1163" s="2" t="inlineStr">
-        <is>
-          <t>ebenerdig</t>
-        </is>
-      </c>
-      <c r="D1163" s="2" t="inlineStr">
-        <is>
-          <t>Terrasse</t>
-        </is>
-      </c>
-      <c r="E1163" s="2" t="inlineStr">
-        <is>
-          <t>Textilene-Stapelsessel anthrazit</t>
-        </is>
-      </c>
-      <c r="F1163" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G1163" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1163" s="2" t="n"/>
+      <c r="A1163" s="4" t="inlineStr">
+        <is>
+          <t>BA13-15</t>
+        </is>
+      </c>
+      <c r="B1163" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1163" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1163" s="4" t="inlineStr">
+        <is>
+          <t>Abstellraum</t>
+        </is>
+      </c>
+      <c r="E1163" s="4" t="n"/>
+      <c r="F1163" s="3" t="n"/>
+      <c r="G1163" s="4" t="n"/>
+      <c r="H1163" s="4" t="n"/>
     </row>
     <row r="1164">
       <c r="A1164" s="2" t="inlineStr">
         <is>
-          <t>TE01-04</t>
+          <t>TE01-01</t>
         </is>
       </c>
       <c r="B1164" s="2" t="inlineStr">
@@ -32625,7 +32625,7 @@
       </c>
       <c r="E1164" s="2" t="inlineStr">
         <is>
-          <t>Weber Genesis Gasgrill</t>
+          <t>Biohort Freizeitbox weiß (Terrasse)</t>
         </is>
       </c>
       <c r="F1164" s="3" t="n">
@@ -32641,7 +32641,7 @@
     <row r="1165">
       <c r="A1165" s="2" t="inlineStr">
         <is>
-          <t>TE01-05</t>
+          <t>TE01-02</t>
         </is>
       </c>
       <c r="B1165" s="2" t="inlineStr">
@@ -32661,7 +32661,7 @@
       </c>
       <c r="E1165" s="2" t="inlineStr">
         <is>
-          <t>Sonnenschirm creme</t>
+          <t>Gartentisch mit Granitplatte inkl. Stühle und Schutzhülle</t>
         </is>
       </c>
       <c r="F1165" s="3" t="n">
@@ -32675,87 +32675,117 @@
       <c r="H1165" s="2" t="n"/>
     </row>
     <row r="1166">
-      <c r="A1166" s="4" t="inlineStr">
-        <is>
-          <t>TE01-06</t>
-        </is>
-      </c>
-      <c r="B1166" s="4" t="inlineStr">
+      <c r="A1166" s="2" t="inlineStr">
+        <is>
+          <t>TE01-03</t>
+        </is>
+      </c>
+      <c r="B1166" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1166" s="4" t="inlineStr">
+      <c r="C1166" s="2" t="inlineStr">
         <is>
           <t>ebenerdig</t>
         </is>
       </c>
-      <c r="D1166" s="4" t="inlineStr">
+      <c r="D1166" s="2" t="inlineStr">
         <is>
           <t>Terrasse</t>
         </is>
       </c>
-      <c r="E1166" s="4" t="n"/>
-      <c r="F1166" s="3" t="n"/>
-      <c r="G1166" s="4" t="n"/>
-      <c r="H1166" s="4" t="n"/>
+      <c r="E1166" s="2" t="inlineStr">
+        <is>
+          <t>Textilene-Stapelsessel anthrazit</t>
+        </is>
+      </c>
+      <c r="F1166" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1166" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1166" s="2" t="n"/>
     </row>
     <row r="1167">
-      <c r="A1167" s="4" t="inlineStr">
-        <is>
-          <t>TE01-07</t>
-        </is>
-      </c>
-      <c r="B1167" s="4" t="inlineStr">
+      <c r="A1167" s="2" t="inlineStr">
+        <is>
+          <t>TE01-04</t>
+        </is>
+      </c>
+      <c r="B1167" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1167" s="4" t="inlineStr">
+      <c r="C1167" s="2" t="inlineStr">
         <is>
           <t>ebenerdig</t>
         </is>
       </c>
-      <c r="D1167" s="4" t="inlineStr">
+      <c r="D1167" s="2" t="inlineStr">
         <is>
           <t>Terrasse</t>
         </is>
       </c>
-      <c r="E1167" s="4" t="n"/>
-      <c r="F1167" s="3" t="n"/>
-      <c r="G1167" s="4" t="n"/>
-      <c r="H1167" s="4" t="n"/>
+      <c r="E1167" s="2" t="inlineStr">
+        <is>
+          <t>Weber Genesis Gasgrill</t>
+        </is>
+      </c>
+      <c r="F1167" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1167" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1167" s="2" t="n"/>
     </row>
     <row r="1168">
-      <c r="A1168" s="4" t="inlineStr">
-        <is>
-          <t>TE01-08</t>
-        </is>
-      </c>
-      <c r="B1168" s="4" t="inlineStr">
+      <c r="A1168" s="2" t="inlineStr">
+        <is>
+          <t>TE01-05</t>
+        </is>
+      </c>
+      <c r="B1168" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1168" s="4" t="inlineStr">
+      <c r="C1168" s="2" t="inlineStr">
         <is>
           <t>ebenerdig</t>
         </is>
       </c>
-      <c r="D1168" s="4" t="inlineStr">
+      <c r="D1168" s="2" t="inlineStr">
         <is>
           <t>Terrasse</t>
         </is>
       </c>
-      <c r="E1168" s="4" t="n"/>
-      <c r="F1168" s="3" t="n"/>
-      <c r="G1168" s="4" t="n"/>
-      <c r="H1168" s="4" t="n"/>
+      <c r="E1168" s="2" t="inlineStr">
+        <is>
+          <t>Sonnenschirm creme</t>
+        </is>
+      </c>
+      <c r="F1168" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1168" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1168" s="2" t="n"/>
     </row>
     <row r="1169">
       <c r="A1169" s="4" t="inlineStr">
         <is>
-          <t>TE01-09</t>
+          <t>TE01-06</t>
         </is>
       </c>
       <c r="B1169" s="4" t="inlineStr">
@@ -32781,7 +32811,7 @@
     <row r="1170">
       <c r="A1170" s="4" t="inlineStr">
         <is>
-          <t>TE01-10</t>
+          <t>TE01-07</t>
         </is>
       </c>
       <c r="B1170" s="4" t="inlineStr">
@@ -32807,7 +32837,7 @@
     <row r="1171">
       <c r="A1171" s="4" t="inlineStr">
         <is>
-          <t>TE01-11</t>
+          <t>TE01-08</t>
         </is>
       </c>
       <c r="B1171" s="4" t="inlineStr">
@@ -32833,7 +32863,7 @@
     <row r="1172">
       <c r="A1172" s="4" t="inlineStr">
         <is>
-          <t>TE01-12</t>
+          <t>TE01-09</t>
         </is>
       </c>
       <c r="B1172" s="4" t="inlineStr">
@@ -32859,7 +32889,7 @@
     <row r="1173">
       <c r="A1173" s="4" t="inlineStr">
         <is>
-          <t>TE01-13</t>
+          <t>TE01-10</t>
         </is>
       </c>
       <c r="B1173" s="4" t="inlineStr">
@@ -32885,7 +32915,7 @@
     <row r="1174">
       <c r="A1174" s="4" t="inlineStr">
         <is>
-          <t>TE01-14</t>
+          <t>TE01-11</t>
         </is>
       </c>
       <c r="B1174" s="4" t="inlineStr">
@@ -32911,7 +32941,7 @@
     <row r="1175">
       <c r="A1175" s="4" t="inlineStr">
         <is>
-          <t>TE01-15</t>
+          <t>TE01-12</t>
         </is>
       </c>
       <c r="B1175" s="4" t="inlineStr">
@@ -32937,7 +32967,7 @@
     <row r="1176">
       <c r="A1176" s="4" t="inlineStr">
         <is>
-          <t>TE01-16</t>
+          <t>TE01-13</t>
         </is>
       </c>
       <c r="B1176" s="4" t="inlineStr">
@@ -32963,7 +32993,7 @@
     <row r="1177">
       <c r="A1177" s="4" t="inlineStr">
         <is>
-          <t>TE01-17</t>
+          <t>TE01-14</t>
         </is>
       </c>
       <c r="B1177" s="4" t="inlineStr">
@@ -32989,7 +33019,7 @@
     <row r="1178">
       <c r="A1178" s="4" t="inlineStr">
         <is>
-          <t>TE01-18</t>
+          <t>TE01-15</t>
         </is>
       </c>
       <c r="B1178" s="4" t="inlineStr">
@@ -33015,7 +33045,7 @@
     <row r="1179">
       <c r="A1179" s="4" t="inlineStr">
         <is>
-          <t>TE01-19</t>
+          <t>TE01-16</t>
         </is>
       </c>
       <c r="B1179" s="4" t="inlineStr">
@@ -33041,7 +33071,7 @@
     <row r="1180">
       <c r="A1180" s="4" t="inlineStr">
         <is>
-          <t>TE01-20</t>
+          <t>TE01-17</t>
         </is>
       </c>
       <c r="B1180" s="4" t="inlineStr">
@@ -33067,7 +33097,7 @@
     <row r="1181">
       <c r="A1181" s="4" t="inlineStr">
         <is>
-          <t>TE01-21</t>
+          <t>TE01-18</t>
         </is>
       </c>
       <c r="B1181" s="4" t="inlineStr">
@@ -33093,7 +33123,7 @@
     <row r="1182">
       <c r="A1182" s="4" t="inlineStr">
         <is>
-          <t>TE01-22</t>
+          <t>TE01-19</t>
         </is>
       </c>
       <c r="B1182" s="4" t="inlineStr">
@@ -33119,7 +33149,7 @@
     <row r="1183">
       <c r="A1183" s="4" t="inlineStr">
         <is>
-          <t>TE01-23</t>
+          <t>TE01-20</t>
         </is>
       </c>
       <c r="B1183" s="4" t="inlineStr">
@@ -33145,7 +33175,7 @@
     <row r="1184">
       <c r="A1184" s="4" t="inlineStr">
         <is>
-          <t>TE01-24</t>
+          <t>TE01-21</t>
         </is>
       </c>
       <c r="B1184" s="4" t="inlineStr">
@@ -33171,7 +33201,7 @@
     <row r="1185">
       <c r="A1185" s="4" t="inlineStr">
         <is>
-          <t>TE01-25</t>
+          <t>TE01-22</t>
         </is>
       </c>
       <c r="B1185" s="4" t="inlineStr">
@@ -33197,7 +33227,7 @@
     <row r="1186">
       <c r="A1186" s="4" t="inlineStr">
         <is>
-          <t>TE01-26</t>
+          <t>TE01-23</t>
         </is>
       </c>
       <c r="B1186" s="4" t="inlineStr">
@@ -33223,7 +33253,7 @@
     <row r="1187">
       <c r="A1187" s="4" t="inlineStr">
         <is>
-          <t>TE01-27</t>
+          <t>TE01-24</t>
         </is>
       </c>
       <c r="B1187" s="4" t="inlineStr">
@@ -33249,7 +33279,7 @@
     <row r="1188">
       <c r="A1188" s="4" t="inlineStr">
         <is>
-          <t>TE01-28</t>
+          <t>TE01-25</t>
         </is>
       </c>
       <c r="B1188" s="4" t="inlineStr">
@@ -33275,7 +33305,7 @@
     <row r="1189">
       <c r="A1189" s="4" t="inlineStr">
         <is>
-          <t>TE01-29</t>
+          <t>TE01-26</t>
         </is>
       </c>
       <c r="B1189" s="4" t="inlineStr">
@@ -33301,7 +33331,7 @@
     <row r="1190">
       <c r="A1190" s="4" t="inlineStr">
         <is>
-          <t>TE01-30</t>
+          <t>TE01-27</t>
         </is>
       </c>
       <c r="B1190" s="4" t="inlineStr">
@@ -33327,7 +33357,7 @@
     <row r="1191">
       <c r="A1191" s="4" t="inlineStr">
         <is>
-          <t>TE01-31</t>
+          <t>TE01-28</t>
         </is>
       </c>
       <c r="B1191" s="4" t="inlineStr">
@@ -33353,7 +33383,7 @@
     <row r="1192">
       <c r="A1192" s="4" t="inlineStr">
         <is>
-          <t>TE01-32</t>
+          <t>TE01-29</t>
         </is>
       </c>
       <c r="B1192" s="4" t="inlineStr">
@@ -33379,7 +33409,7 @@
     <row r="1193">
       <c r="A1193" s="4" t="inlineStr">
         <is>
-          <t>TE01-33</t>
+          <t>TE01-30</t>
         </is>
       </c>
       <c r="B1193" s="4" t="inlineStr">
@@ -33405,7 +33435,7 @@
     <row r="1194">
       <c r="A1194" s="4" t="inlineStr">
         <is>
-          <t>TE01-34</t>
+          <t>TE01-31</t>
         </is>
       </c>
       <c r="B1194" s="4" t="inlineStr">
@@ -33431,7 +33461,7 @@
     <row r="1195">
       <c r="A1195" s="4" t="inlineStr">
         <is>
-          <t>TE01-35</t>
+          <t>TE01-32</t>
         </is>
       </c>
       <c r="B1195" s="4" t="inlineStr">
@@ -33457,7 +33487,7 @@
     <row r="1196">
       <c r="A1196" s="4" t="inlineStr">
         <is>
-          <t>TE01-36</t>
+          <t>TE01-33</t>
         </is>
       </c>
       <c r="B1196" s="4" t="inlineStr">
@@ -33483,7 +33513,7 @@
     <row r="1197">
       <c r="A1197" s="4" t="inlineStr">
         <is>
-          <t>TE01-37</t>
+          <t>TE01-34</t>
         </is>
       </c>
       <c r="B1197" s="4" t="inlineStr">
@@ -33509,7 +33539,7 @@
     <row r="1198">
       <c r="A1198" s="4" t="inlineStr">
         <is>
-          <t>TE01-38</t>
+          <t>TE01-35</t>
         </is>
       </c>
       <c r="B1198" s="4" t="inlineStr">
@@ -33535,7 +33565,7 @@
     <row r="1199">
       <c r="A1199" s="4" t="inlineStr">
         <is>
-          <t>TE01-39</t>
+          <t>TE01-36</t>
         </is>
       </c>
       <c r="B1199" s="4" t="inlineStr">
@@ -33561,7 +33591,7 @@
     <row r="1200">
       <c r="A1200" s="4" t="inlineStr">
         <is>
-          <t>TE01-40</t>
+          <t>TE01-37</t>
         </is>
       </c>
       <c r="B1200" s="4" t="inlineStr">
@@ -33585,117 +33615,87 @@
       <c r="H1200" s="4" t="n"/>
     </row>
     <row r="1201">
-      <c r="A1201" s="2" t="inlineStr">
-        <is>
-          <t>TE02-01</t>
-        </is>
-      </c>
-      <c r="B1201" s="2" t="inlineStr">
+      <c r="A1201" s="4" t="inlineStr">
+        <is>
+          <t>TE01-38</t>
+        </is>
+      </c>
+      <c r="B1201" s="4" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1201" s="2" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1201" s="2" t="inlineStr">
-        <is>
-          <t>Dachterrasse</t>
-        </is>
-      </c>
-      <c r="E1201" s="2" t="inlineStr">
-        <is>
-          <t>Pflanzkübel Plastik weiß</t>
-        </is>
-      </c>
-      <c r="F1201" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G1201" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1201" s="2" t="n"/>
+      <c r="C1201" s="4" t="inlineStr">
+        <is>
+          <t>ebenerdig</t>
+        </is>
+      </c>
+      <c r="D1201" s="4" t="inlineStr">
+        <is>
+          <t>Terrasse</t>
+        </is>
+      </c>
+      <c r="E1201" s="4" t="n"/>
+      <c r="F1201" s="3" t="n"/>
+      <c r="G1201" s="4" t="n"/>
+      <c r="H1201" s="4" t="n"/>
     </row>
     <row r="1202">
-      <c r="A1202" s="2" t="inlineStr">
-        <is>
-          <t>TE02-02</t>
-        </is>
-      </c>
-      <c r="B1202" s="2" t="inlineStr">
+      <c r="A1202" s="4" t="inlineStr">
+        <is>
+          <t>TE01-39</t>
+        </is>
+      </c>
+      <c r="B1202" s="4" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1202" s="2" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1202" s="2" t="inlineStr">
-        <is>
-          <t>Dachterrasse</t>
-        </is>
-      </c>
-      <c r="E1202" s="2" t="inlineStr">
-        <is>
-          <t>Gartenstuhl Kunststoff anthrazit</t>
-        </is>
-      </c>
-      <c r="F1202" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G1202" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1202" s="2" t="n"/>
+      <c r="C1202" s="4" t="inlineStr">
+        <is>
+          <t>ebenerdig</t>
+        </is>
+      </c>
+      <c r="D1202" s="4" t="inlineStr">
+        <is>
+          <t>Terrasse</t>
+        </is>
+      </c>
+      <c r="E1202" s="4" t="n"/>
+      <c r="F1202" s="3" t="n"/>
+      <c r="G1202" s="4" t="n"/>
+      <c r="H1202" s="4" t="n"/>
     </row>
     <row r="1203">
-      <c r="A1203" s="2" t="inlineStr">
-        <is>
-          <t>TE02-03</t>
-        </is>
-      </c>
-      <c r="B1203" s="2" t="inlineStr">
+      <c r="A1203" s="4" t="inlineStr">
+        <is>
+          <t>TE01-40</t>
+        </is>
+      </c>
+      <c r="B1203" s="4" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1203" s="2" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1203" s="2" t="inlineStr">
-        <is>
-          <t>Dachterrasse</t>
-        </is>
-      </c>
-      <c r="E1203" s="2" t="inlineStr">
-        <is>
-          <t>Gartentisch anthrazit</t>
-        </is>
-      </c>
-      <c r="F1203" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1203" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1203" s="2" t="n"/>
+      <c r="C1203" s="4" t="inlineStr">
+        <is>
+          <t>ebenerdig</t>
+        </is>
+      </c>
+      <c r="D1203" s="4" t="inlineStr">
+        <is>
+          <t>Terrasse</t>
+        </is>
+      </c>
+      <c r="E1203" s="4" t="n"/>
+      <c r="F1203" s="3" t="n"/>
+      <c r="G1203" s="4" t="n"/>
+      <c r="H1203" s="4" t="n"/>
     </row>
     <row r="1204">
       <c r="A1204" s="2" t="inlineStr">
         <is>
-          <t>TE02-04</t>
+          <t>TE02-01</t>
         </is>
       </c>
       <c r="B1204" s="2" t="inlineStr">
@@ -33715,15 +33715,15 @@
       </c>
       <c r="E1204" s="2" t="inlineStr">
         <is>
-          <t>Teak-Klapptisch rund</t>
+          <t>Pflanzkübel Plastik weiß</t>
         </is>
       </c>
       <c r="F1204" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1204" s="2" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Stück</t>
         </is>
       </c>
       <c r="H1204" s="2" t="n"/>
@@ -33731,7 +33731,7 @@
     <row r="1205">
       <c r="A1205" s="2" t="inlineStr">
         <is>
-          <t>TE02-05</t>
+          <t>TE02-02</t>
         </is>
       </c>
       <c r="B1205" s="2" t="inlineStr">
@@ -33751,11 +33751,11 @@
       </c>
       <c r="E1205" s="2" t="inlineStr">
         <is>
-          <t>Pflanzkübel grau, groß</t>
+          <t>Gartenstuhl Kunststoff anthrazit</t>
         </is>
       </c>
       <c r="F1205" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1205" s="2" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
     <row r="1206">
       <c r="A1206" s="2" t="inlineStr">
         <is>
-          <t>TE02-06</t>
+          <t>TE02-03</t>
         </is>
       </c>
       <c r="B1206" s="2" t="inlineStr">
@@ -33787,7 +33787,7 @@
       </c>
       <c r="E1206" s="2" t="inlineStr">
         <is>
-          <t>Holzstern mit Lichterkette</t>
+          <t>Gartentisch anthrazit</t>
         </is>
       </c>
       <c r="F1206" s="3" t="n">
@@ -33801,87 +33801,117 @@
       <c r="H1206" s="2" t="n"/>
     </row>
     <row r="1207">
-      <c r="A1207" s="4" t="inlineStr">
-        <is>
-          <t>TE02-07</t>
-        </is>
-      </c>
-      <c r="B1207" s="4" t="inlineStr">
+      <c r="A1207" s="2" t="inlineStr">
+        <is>
+          <t>TE02-04</t>
+        </is>
+      </c>
+      <c r="B1207" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1207" s="4" t="inlineStr">
+      <c r="C1207" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1207" s="4" t="inlineStr">
+      <c r="D1207" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1207" s="4" t="n"/>
-      <c r="F1207" s="3" t="n"/>
-      <c r="G1207" s="4" t="n"/>
-      <c r="H1207" s="4" t="n"/>
+      <c r="E1207" s="2" t="inlineStr">
+        <is>
+          <t>Teak-Klapptisch rund</t>
+        </is>
+      </c>
+      <c r="F1207" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1207" s="2" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="H1207" s="2" t="n"/>
     </row>
     <row r="1208">
-      <c r="A1208" s="4" t="inlineStr">
-        <is>
-          <t>TE02-08</t>
-        </is>
-      </c>
-      <c r="B1208" s="4" t="inlineStr">
+      <c r="A1208" s="2" t="inlineStr">
+        <is>
+          <t>TE02-05</t>
+        </is>
+      </c>
+      <c r="B1208" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1208" s="4" t="inlineStr">
+      <c r="C1208" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1208" s="4" t="inlineStr">
+      <c r="D1208" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1208" s="4" t="n"/>
-      <c r="F1208" s="3" t="n"/>
-      <c r="G1208" s="4" t="n"/>
-      <c r="H1208" s="4" t="n"/>
+      <c r="E1208" s="2" t="inlineStr">
+        <is>
+          <t>Pflanzkübel grau, groß</t>
+        </is>
+      </c>
+      <c r="F1208" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1208" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1208" s="2" t="n"/>
     </row>
     <row r="1209">
-      <c r="A1209" s="4" t="inlineStr">
-        <is>
-          <t>TE02-09</t>
-        </is>
-      </c>
-      <c r="B1209" s="4" t="inlineStr">
+      <c r="A1209" s="2" t="inlineStr">
+        <is>
+          <t>TE02-06</t>
+        </is>
+      </c>
+      <c r="B1209" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1209" s="4" t="inlineStr">
+      <c r="C1209" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1209" s="4" t="inlineStr">
+      <c r="D1209" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1209" s="4" t="n"/>
-      <c r="F1209" s="3" t="n"/>
-      <c r="G1209" s="4" t="n"/>
-      <c r="H1209" s="4" t="n"/>
+      <c r="E1209" s="2" t="inlineStr">
+        <is>
+          <t>Holzstern mit Lichterkette</t>
+        </is>
+      </c>
+      <c r="F1209" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1209" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1209" s="2" t="n"/>
     </row>
     <row r="1210">
       <c r="A1210" s="4" t="inlineStr">
         <is>
-          <t>TE02-10</t>
+          <t>TE02-07</t>
         </is>
       </c>
       <c r="B1210" s="4" t="inlineStr">
@@ -33907,7 +33937,7 @@
     <row r="1211">
       <c r="A1211" s="4" t="inlineStr">
         <is>
-          <t>TE02-11</t>
+          <t>TE02-08</t>
         </is>
       </c>
       <c r="B1211" s="4" t="inlineStr">
@@ -33933,7 +33963,7 @@
     <row r="1212">
       <c r="A1212" s="4" t="inlineStr">
         <is>
-          <t>TE02-12</t>
+          <t>TE02-09</t>
         </is>
       </c>
       <c r="B1212" s="4" t="inlineStr">
@@ -33959,7 +33989,7 @@
     <row r="1213">
       <c r="A1213" s="4" t="inlineStr">
         <is>
-          <t>TE02-13</t>
+          <t>TE02-10</t>
         </is>
       </c>
       <c r="B1213" s="4" t="inlineStr">
@@ -33985,7 +34015,7 @@
     <row r="1214">
       <c r="A1214" s="4" t="inlineStr">
         <is>
-          <t>TE02-14</t>
+          <t>TE02-11</t>
         </is>
       </c>
       <c r="B1214" s="4" t="inlineStr">
@@ -34011,7 +34041,7 @@
     <row r="1215">
       <c r="A1215" s="4" t="inlineStr">
         <is>
-          <t>TE02-15</t>
+          <t>TE02-12</t>
         </is>
       </c>
       <c r="B1215" s="4" t="inlineStr">
@@ -34037,7 +34067,7 @@
     <row r="1216">
       <c r="A1216" s="4" t="inlineStr">
         <is>
-          <t>TE02-16</t>
+          <t>TE02-13</t>
         </is>
       </c>
       <c r="B1216" s="4" t="inlineStr">
@@ -34063,7 +34093,7 @@
     <row r="1217">
       <c r="A1217" s="4" t="inlineStr">
         <is>
-          <t>TE02-17</t>
+          <t>TE02-14</t>
         </is>
       </c>
       <c r="B1217" s="4" t="inlineStr">
@@ -34089,7 +34119,7 @@
     <row r="1218">
       <c r="A1218" s="4" t="inlineStr">
         <is>
-          <t>TE02-18</t>
+          <t>TE02-15</t>
         </is>
       </c>
       <c r="B1218" s="4" t="inlineStr">
@@ -34115,7 +34145,7 @@
     <row r="1219">
       <c r="A1219" s="4" t="inlineStr">
         <is>
-          <t>TE02-19</t>
+          <t>TE02-16</t>
         </is>
       </c>
       <c r="B1219" s="4" t="inlineStr">
@@ -34141,7 +34171,7 @@
     <row r="1220">
       <c r="A1220" s="4" t="inlineStr">
         <is>
-          <t>TE02-20</t>
+          <t>TE02-17</t>
         </is>
       </c>
       <c r="B1220" s="4" t="inlineStr">
@@ -34167,7 +34197,7 @@
     <row r="1221">
       <c r="A1221" s="4" t="inlineStr">
         <is>
-          <t>TE02-21</t>
+          <t>TE02-18</t>
         </is>
       </c>
       <c r="B1221" s="4" t="inlineStr">
@@ -34193,7 +34223,7 @@
     <row r="1222">
       <c r="A1222" s="4" t="inlineStr">
         <is>
-          <t>TE02-22</t>
+          <t>TE02-19</t>
         </is>
       </c>
       <c r="B1222" s="4" t="inlineStr">
@@ -34219,7 +34249,7 @@
     <row r="1223">
       <c r="A1223" s="4" t="inlineStr">
         <is>
-          <t>TE02-23</t>
+          <t>TE02-20</t>
         </is>
       </c>
       <c r="B1223" s="4" t="inlineStr">
@@ -34245,7 +34275,7 @@
     <row r="1224">
       <c r="A1224" s="4" t="inlineStr">
         <is>
-          <t>TE02-24</t>
+          <t>TE02-21</t>
         </is>
       </c>
       <c r="B1224" s="4" t="inlineStr">
@@ -34271,7 +34301,7 @@
     <row r="1225">
       <c r="A1225" s="4" t="inlineStr">
         <is>
-          <t>TE02-25</t>
+          <t>TE02-22</t>
         </is>
       </c>
       <c r="B1225" s="4" t="inlineStr">
@@ -34297,7 +34327,7 @@
     <row r="1226">
       <c r="A1226" s="4" t="inlineStr">
         <is>
-          <t>TE02-26</t>
+          <t>TE02-23</t>
         </is>
       </c>
       <c r="B1226" s="4" t="inlineStr">
@@ -34323,7 +34353,7 @@
     <row r="1227">
       <c r="A1227" s="4" t="inlineStr">
         <is>
-          <t>TE02-27</t>
+          <t>TE02-24</t>
         </is>
       </c>
       <c r="B1227" s="4" t="inlineStr">
@@ -34349,7 +34379,7 @@
     <row r="1228">
       <c r="A1228" s="4" t="inlineStr">
         <is>
-          <t>TE02-28</t>
+          <t>TE02-25</t>
         </is>
       </c>
       <c r="B1228" s="4" t="inlineStr">
@@ -34375,7 +34405,7 @@
     <row r="1229">
       <c r="A1229" s="4" t="inlineStr">
         <is>
-          <t>TE02-29</t>
+          <t>TE02-26</t>
         </is>
       </c>
       <c r="B1229" s="4" t="inlineStr">
@@ -34401,7 +34431,7 @@
     <row r="1230">
       <c r="A1230" s="4" t="inlineStr">
         <is>
-          <t>TE02-30</t>
+          <t>TE02-27</t>
         </is>
       </c>
       <c r="B1230" s="4" t="inlineStr">
@@ -34427,7 +34457,7 @@
     <row r="1231">
       <c r="A1231" s="4" t="inlineStr">
         <is>
-          <t>TE02-31</t>
+          <t>TE02-28</t>
         </is>
       </c>
       <c r="B1231" s="4" t="inlineStr">
@@ -34453,7 +34483,7 @@
     <row r="1232">
       <c r="A1232" s="4" t="inlineStr">
         <is>
-          <t>TE02-32</t>
+          <t>TE02-29</t>
         </is>
       </c>
       <c r="B1232" s="4" t="inlineStr">
@@ -34479,7 +34509,7 @@
     <row r="1233">
       <c r="A1233" s="4" t="inlineStr">
         <is>
-          <t>TE02-33</t>
+          <t>TE02-30</t>
         </is>
       </c>
       <c r="B1233" s="4" t="inlineStr">
@@ -34505,7 +34535,7 @@
     <row r="1234">
       <c r="A1234" s="4" t="inlineStr">
         <is>
-          <t>TE02-34</t>
+          <t>TE02-31</t>
         </is>
       </c>
       <c r="B1234" s="4" t="inlineStr">
@@ -34531,7 +34561,7 @@
     <row r="1235">
       <c r="A1235" s="4" t="inlineStr">
         <is>
-          <t>TE02-35</t>
+          <t>TE02-32</t>
         </is>
       </c>
       <c r="B1235" s="4" t="inlineStr">
@@ -34557,7 +34587,7 @@
     <row r="1236">
       <c r="A1236" s="4" t="inlineStr">
         <is>
-          <t>TE02-36</t>
+          <t>TE02-33</t>
         </is>
       </c>
       <c r="B1236" s="4" t="inlineStr">
@@ -34583,7 +34613,7 @@
     <row r="1237">
       <c r="A1237" s="4" t="inlineStr">
         <is>
-          <t>TE02-37</t>
+          <t>TE02-34</t>
         </is>
       </c>
       <c r="B1237" s="4" t="inlineStr">
@@ -34609,7 +34639,7 @@
     <row r="1238">
       <c r="A1238" s="4" t="inlineStr">
         <is>
-          <t>TE02-38</t>
+          <t>TE02-35</t>
         </is>
       </c>
       <c r="B1238" s="4" t="inlineStr">
@@ -34635,7 +34665,7 @@
     <row r="1239">
       <c r="A1239" s="4" t="inlineStr">
         <is>
-          <t>TE02-39</t>
+          <t>TE02-36</t>
         </is>
       </c>
       <c r="B1239" s="4" t="inlineStr">
@@ -34661,7 +34691,7 @@
     <row r="1240">
       <c r="A1240" s="4" t="inlineStr">
         <is>
-          <t>TE02-40</t>
+          <t>TE02-37</t>
         </is>
       </c>
       <c r="B1240" s="4" t="inlineStr">
@@ -34685,41 +34715,35 @@
       <c r="H1240" s="4" t="n"/>
     </row>
     <row r="1241">
-      <c r="A1241" s="2" t="inlineStr">
-        <is>
-          <t>GA01-01</t>
-        </is>
-      </c>
-      <c r="B1241" s="2" t="inlineStr">
+      <c r="A1241" s="4" t="inlineStr">
+        <is>
+          <t>TE02-38</t>
+        </is>
+      </c>
+      <c r="B1241" s="4" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1241" s="2" t="inlineStr"/>
-      <c r="D1241" s="2" t="inlineStr">
-        <is>
-          <t>Gartenanlage</t>
-        </is>
-      </c>
-      <c r="E1241" s="2" t="inlineStr">
-        <is>
-          <t>Holz-Wellenliege, Doppelliege</t>
-        </is>
-      </c>
-      <c r="F1241" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1241" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1241" s="2" t="n"/>
+      <c r="C1241" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1241" s="4" t="inlineStr">
+        <is>
+          <t>Dachterrasse</t>
+        </is>
+      </c>
+      <c r="E1241" s="4" t="n"/>
+      <c r="F1241" s="3" t="n"/>
+      <c r="G1241" s="4" t="n"/>
+      <c r="H1241" s="4" t="n"/>
     </row>
     <row r="1242">
       <c r="A1242" s="4" t="inlineStr">
         <is>
-          <t>GA01-02</t>
+          <t>TE02-39</t>
         </is>
       </c>
       <c r="B1242" s="4" t="inlineStr">
@@ -34727,10 +34751,14 @@
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1242" s="4" t="inlineStr"/>
+      <c r="C1242" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
       <c r="D1242" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Dachterrasse</t>
         </is>
       </c>
       <c r="E1242" s="4" t="n"/>
@@ -34741,7 +34769,7 @@
     <row r="1243">
       <c r="A1243" s="4" t="inlineStr">
         <is>
-          <t>GA01-03</t>
+          <t>TE02-40</t>
         </is>
       </c>
       <c r="B1243" s="4" t="inlineStr">
@@ -34749,10 +34777,14 @@
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1243" s="4" t="inlineStr"/>
+      <c r="C1243" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
       <c r="D1243" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Dachterrasse</t>
         </is>
       </c>
       <c r="E1243" s="4" t="n"/>
@@ -34761,31 +34793,41 @@
       <c r="H1243" s="4" t="n"/>
     </row>
     <row r="1244">
-      <c r="A1244" s="4" t="inlineStr">
-        <is>
-          <t>GA01-04</t>
-        </is>
-      </c>
-      <c r="B1244" s="4" t="inlineStr">
+      <c r="A1244" s="2" t="inlineStr">
+        <is>
+          <t>GA01-01</t>
+        </is>
+      </c>
+      <c r="B1244" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1244" s="4" t="inlineStr"/>
-      <c r="D1244" s="4" t="inlineStr">
+      <c r="C1244" s="2" t="inlineStr"/>
+      <c r="D1244" s="2" t="inlineStr">
         <is>
           <t>Gartenanlage</t>
         </is>
       </c>
-      <c r="E1244" s="4" t="n"/>
-      <c r="F1244" s="3" t="n"/>
-      <c r="G1244" s="4" t="n"/>
-      <c r="H1244" s="4" t="n"/>
+      <c r="E1244" s="2" t="inlineStr">
+        <is>
+          <t>Holz-Wellenliege, Doppelliege</t>
+        </is>
+      </c>
+      <c r="F1244" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1244" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1244" s="2" t="n"/>
     </row>
     <row r="1245">
       <c r="A1245" s="4" t="inlineStr">
         <is>
-          <t>GA01-05</t>
+          <t>GA01-02</t>
         </is>
       </c>
       <c r="B1245" s="4" t="inlineStr">
@@ -34807,7 +34849,7 @@
     <row r="1246">
       <c r="A1246" s="4" t="inlineStr">
         <is>
-          <t>GA01-06</t>
+          <t>GA01-03</t>
         </is>
       </c>
       <c r="B1246" s="4" t="inlineStr">
@@ -34829,7 +34871,7 @@
     <row r="1247">
       <c r="A1247" s="4" t="inlineStr">
         <is>
-          <t>GA01-07</t>
+          <t>GA01-04</t>
         </is>
       </c>
       <c r="B1247" s="4" t="inlineStr">
@@ -34851,7 +34893,7 @@
     <row r="1248">
       <c r="A1248" s="4" t="inlineStr">
         <is>
-          <t>GA01-08</t>
+          <t>GA01-05</t>
         </is>
       </c>
       <c r="B1248" s="4" t="inlineStr">
@@ -34873,7 +34915,7 @@
     <row r="1249">
       <c r="A1249" s="4" t="inlineStr">
         <is>
-          <t>GA01-09</t>
+          <t>GA01-06</t>
         </is>
       </c>
       <c r="B1249" s="4" t="inlineStr">
@@ -34895,7 +34937,7 @@
     <row r="1250">
       <c r="A1250" s="4" t="inlineStr">
         <is>
-          <t>GA01-10</t>
+          <t>GA01-07</t>
         </is>
       </c>
       <c r="B1250" s="4" t="inlineStr">
@@ -34917,7 +34959,7 @@
     <row r="1251">
       <c r="A1251" s="4" t="inlineStr">
         <is>
-          <t>GA01-11</t>
+          <t>GA01-08</t>
         </is>
       </c>
       <c r="B1251" s="4" t="inlineStr">
@@ -34939,7 +34981,7 @@
     <row r="1252">
       <c r="A1252" s="4" t="inlineStr">
         <is>
-          <t>GA01-12</t>
+          <t>GA01-09</t>
         </is>
       </c>
       <c r="B1252" s="4" t="inlineStr">
@@ -34961,7 +35003,7 @@
     <row r="1253">
       <c r="A1253" s="4" t="inlineStr">
         <is>
-          <t>GA01-13</t>
+          <t>GA01-10</t>
         </is>
       </c>
       <c r="B1253" s="4" t="inlineStr">
@@ -34983,7 +35025,7 @@
     <row r="1254">
       <c r="A1254" s="4" t="inlineStr">
         <is>
-          <t>GA01-14</t>
+          <t>GA01-11</t>
         </is>
       </c>
       <c r="B1254" s="4" t="inlineStr">
@@ -35005,7 +35047,7 @@
     <row r="1255">
       <c r="A1255" s="4" t="inlineStr">
         <is>
-          <t>GA01-15</t>
+          <t>GA01-12</t>
         </is>
       </c>
       <c r="B1255" s="4" t="inlineStr">
@@ -35027,7 +35069,7 @@
     <row r="1256">
       <c r="A1256" s="4" t="inlineStr">
         <is>
-          <t>GA01-16</t>
+          <t>GA01-13</t>
         </is>
       </c>
       <c r="B1256" s="4" t="inlineStr">
@@ -35049,7 +35091,7 @@
     <row r="1257">
       <c r="A1257" s="4" t="inlineStr">
         <is>
-          <t>GA01-17</t>
+          <t>GA01-14</t>
         </is>
       </c>
       <c r="B1257" s="4" t="inlineStr">
@@ -35071,7 +35113,7 @@
     <row r="1258">
       <c r="A1258" s="4" t="inlineStr">
         <is>
-          <t>GA01-18</t>
+          <t>GA01-15</t>
         </is>
       </c>
       <c r="B1258" s="4" t="inlineStr">
@@ -35093,7 +35135,7 @@
     <row r="1259">
       <c r="A1259" s="4" t="inlineStr">
         <is>
-          <t>GA01-19</t>
+          <t>GA01-16</t>
         </is>
       </c>
       <c r="B1259" s="4" t="inlineStr">
@@ -35115,7 +35157,7 @@
     <row r="1260">
       <c r="A1260" s="4" t="inlineStr">
         <is>
-          <t>GA01-20</t>
+          <t>GA01-17</t>
         </is>
       </c>
       <c r="B1260" s="4" t="inlineStr">
@@ -35137,7 +35179,7 @@
     <row r="1261">
       <c r="A1261" s="4" t="inlineStr">
         <is>
-          <t>GA01-21</t>
+          <t>GA01-18</t>
         </is>
       </c>
       <c r="B1261" s="4" t="inlineStr">
@@ -35159,7 +35201,7 @@
     <row r="1262">
       <c r="A1262" s="4" t="inlineStr">
         <is>
-          <t>GA01-22</t>
+          <t>GA01-19</t>
         </is>
       </c>
       <c r="B1262" s="4" t="inlineStr">
@@ -35181,7 +35223,7 @@
     <row r="1263">
       <c r="A1263" s="4" t="inlineStr">
         <is>
-          <t>GA01-23</t>
+          <t>GA01-20</t>
         </is>
       </c>
       <c r="B1263" s="4" t="inlineStr">
@@ -35203,7 +35245,7 @@
     <row r="1264">
       <c r="A1264" s="4" t="inlineStr">
         <is>
-          <t>GA01-24</t>
+          <t>GA01-21</t>
         </is>
       </c>
       <c r="B1264" s="4" t="inlineStr">
@@ -35225,7 +35267,7 @@
     <row r="1265">
       <c r="A1265" s="4" t="inlineStr">
         <is>
-          <t>GA01-25</t>
+          <t>GA01-22</t>
         </is>
       </c>
       <c r="B1265" s="4" t="inlineStr">
@@ -35247,7 +35289,7 @@
     <row r="1266">
       <c r="A1266" s="4" t="inlineStr">
         <is>
-          <t>GA01-26</t>
+          <t>GA01-23</t>
         </is>
       </c>
       <c r="B1266" s="4" t="inlineStr">
@@ -35269,7 +35311,7 @@
     <row r="1267">
       <c r="A1267" s="4" t="inlineStr">
         <is>
-          <t>GA01-27</t>
+          <t>GA01-24</t>
         </is>
       </c>
       <c r="B1267" s="4" t="inlineStr">
@@ -35291,7 +35333,7 @@
     <row r="1268">
       <c r="A1268" s="4" t="inlineStr">
         <is>
-          <t>GA01-28</t>
+          <t>GA01-25</t>
         </is>
       </c>
       <c r="B1268" s="4" t="inlineStr">
@@ -35313,7 +35355,7 @@
     <row r="1269">
       <c r="A1269" s="4" t="inlineStr">
         <is>
-          <t>GA01-29</t>
+          <t>GA01-26</t>
         </is>
       </c>
       <c r="B1269" s="4" t="inlineStr">
@@ -35335,7 +35377,7 @@
     <row r="1270">
       <c r="A1270" s="4" t="inlineStr">
         <is>
-          <t>GA01-30</t>
+          <t>GA01-27</t>
         </is>
       </c>
       <c r="B1270" s="4" t="inlineStr">
@@ -35357,7 +35399,7 @@
     <row r="1271">
       <c r="A1271" s="4" t="inlineStr">
         <is>
-          <t>GA01-31</t>
+          <t>GA01-28</t>
         </is>
       </c>
       <c r="B1271" s="4" t="inlineStr">
@@ -35379,7 +35421,7 @@
     <row r="1272">
       <c r="A1272" s="4" t="inlineStr">
         <is>
-          <t>GA01-32</t>
+          <t>GA01-29</t>
         </is>
       </c>
       <c r="B1272" s="4" t="inlineStr">
@@ -35401,7 +35443,7 @@
     <row r="1273">
       <c r="A1273" s="4" t="inlineStr">
         <is>
-          <t>GA01-33</t>
+          <t>GA01-30</t>
         </is>
       </c>
       <c r="B1273" s="4" t="inlineStr">
@@ -35423,7 +35465,7 @@
     <row r="1274">
       <c r="A1274" s="4" t="inlineStr">
         <is>
-          <t>GA01-34</t>
+          <t>GA01-31</t>
         </is>
       </c>
       <c r="B1274" s="4" t="inlineStr">
@@ -35445,7 +35487,7 @@
     <row r="1275">
       <c r="A1275" s="4" t="inlineStr">
         <is>
-          <t>GA01-35</t>
+          <t>GA01-32</t>
         </is>
       </c>
       <c r="B1275" s="4" t="inlineStr">
@@ -35467,7 +35509,7 @@
     <row r="1276">
       <c r="A1276" s="4" t="inlineStr">
         <is>
-          <t>GA01-36</t>
+          <t>GA01-33</t>
         </is>
       </c>
       <c r="B1276" s="4" t="inlineStr">
@@ -35489,7 +35531,7 @@
     <row r="1277">
       <c r="A1277" s="4" t="inlineStr">
         <is>
-          <t>GA01-37</t>
+          <t>GA01-34</t>
         </is>
       </c>
       <c r="B1277" s="4" t="inlineStr">
@@ -35511,7 +35553,7 @@
     <row r="1278">
       <c r="A1278" s="4" t="inlineStr">
         <is>
-          <t>GA01-38</t>
+          <t>GA01-35</t>
         </is>
       </c>
       <c r="B1278" s="4" t="inlineStr">
@@ -35533,7 +35575,7 @@
     <row r="1279">
       <c r="A1279" s="4" t="inlineStr">
         <is>
-          <t>GA01-39</t>
+          <t>GA01-36</t>
         </is>
       </c>
       <c r="B1279" s="4" t="inlineStr">
@@ -35555,7 +35597,7 @@
     <row r="1280">
       <c r="A1280" s="4" t="inlineStr">
         <is>
-          <t>GA01-40</t>
+          <t>GA01-37</t>
         </is>
       </c>
       <c r="B1280" s="4" t="inlineStr">
@@ -35574,10 +35616,76 @@
       <c r="G1280" s="4" t="n"/>
       <c r="H1280" s="4" t="n"/>
     </row>
+    <row r="1281">
+      <c r="A1281" s="4" t="inlineStr">
+        <is>
+          <t>GA01-38</t>
+        </is>
+      </c>
+      <c r="B1281" s="4" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1281" s="4" t="inlineStr"/>
+      <c r="D1281" s="4" t="inlineStr">
+        <is>
+          <t>Gartenanlage</t>
+        </is>
+      </c>
+      <c r="E1281" s="4" t="n"/>
+      <c r="F1281" s="3" t="n"/>
+      <c r="G1281" s="4" t="n"/>
+      <c r="H1281" s="4" t="n"/>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="4" t="inlineStr">
+        <is>
+          <t>GA01-39</t>
+        </is>
+      </c>
+      <c r="B1282" s="4" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1282" s="4" t="inlineStr"/>
+      <c r="D1282" s="4" t="inlineStr">
+        <is>
+          <t>Gartenanlage</t>
+        </is>
+      </c>
+      <c r="E1282" s="4" t="n"/>
+      <c r="F1282" s="3" t="n"/>
+      <c r="G1282" s="4" t="n"/>
+      <c r="H1282" s="4" t="n"/>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="4" t="inlineStr">
+        <is>
+          <t>GA01-40</t>
+        </is>
+      </c>
+      <c r="B1283" s="4" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1283" s="4" t="inlineStr"/>
+      <c r="D1283" s="4" t="inlineStr">
+        <is>
+          <t>Gartenanlage</t>
+        </is>
+      </c>
+      <c r="E1283" s="4" t="n"/>
+      <c r="F1283" s="3" t="n"/>
+      <c r="G1283" s="4" t="n"/>
+      <c r="H1283" s="4" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1280"/>
+  <autoFilter ref="A1:H1283"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F1280" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen." type="whole" operator="greaterThan">
+    <dataValidation sqref="F2:F1283" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anleitung" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Erfassung'!$A$1:$H$1283</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Erfassung'!$A$1:$H$1285</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1283"/>
+  <dimension ref="A1:H1285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26825,186 +26825,256 @@
       <c r="H950" s="4" t="n"/>
     </row>
     <row r="951">
-      <c r="A951" s="4" t="inlineStr">
+      <c r="A951" s="2" t="inlineStr">
         <is>
           <t>BA03-01</t>
         </is>
       </c>
-      <c r="B951" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C951" s="4" t="inlineStr">
+      <c r="B951" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C951" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D951" s="4" t="inlineStr">
+      <c r="D951" s="2" t="inlineStr">
         <is>
           <t>Galerie</t>
         </is>
       </c>
-      <c r="E951" s="4" t="n"/>
-      <c r="F951" s="3" t="n"/>
-      <c r="G951" s="4" t="n"/>
-      <c r="H951" s="4" t="n"/>
+      <c r="E951" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Avsiktlig Teppich, schwarz-weiß gepunktet</t>
+        </is>
+      </c>
+      <c r="F951" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G951" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H951" s="2" t="n"/>
     </row>
     <row r="952">
-      <c r="A952" s="4" t="inlineStr">
+      <c r="A952" s="2" t="inlineStr">
         <is>
           <t>BA03-02</t>
         </is>
       </c>
-      <c r="B952" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C952" s="4" t="inlineStr">
+      <c r="B952" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C952" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D952" s="4" t="inlineStr">
+      <c r="D952" s="2" t="inlineStr">
         <is>
           <t>Galerie</t>
         </is>
       </c>
-      <c r="E952" s="4" t="n"/>
-      <c r="F952" s="3" t="n"/>
-      <c r="G952" s="4" t="n"/>
-      <c r="H952" s="4" t="n"/>
+      <c r="E952" s="2" t="inlineStr">
+        <is>
+          <t>Spielküche beige-braun, mehrteilig</t>
+        </is>
+      </c>
+      <c r="F952" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G952" s="2" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="H952" s="2" t="n"/>
     </row>
     <row r="953">
-      <c r="A953" s="4" t="inlineStr">
+      <c r="A953" s="2" t="inlineStr">
         <is>
           <t>BA03-03</t>
         </is>
       </c>
-      <c r="B953" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C953" s="4" t="inlineStr">
+      <c r="B953" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C953" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D953" s="4" t="inlineStr">
+      <c r="D953" s="2" t="inlineStr">
         <is>
           <t>Galerie</t>
         </is>
       </c>
-      <c r="E953" s="4" t="n"/>
-      <c r="F953" s="3" t="n"/>
-      <c r="G953" s="4" t="n"/>
-      <c r="H953" s="4" t="n"/>
+      <c r="E953" s="2" t="inlineStr">
+        <is>
+          <t>Sofa grau, 2-Sitzer</t>
+        </is>
+      </c>
+      <c r="F953" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G953" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H953" s="2" t="n"/>
     </row>
     <row r="954">
-      <c r="A954" s="4" t="inlineStr">
+      <c r="A954" s="2" t="inlineStr">
         <is>
           <t>BA03-04</t>
         </is>
       </c>
-      <c r="B954" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C954" s="4" t="inlineStr">
+      <c r="B954" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C954" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D954" s="4" t="inlineStr">
+      <c r="D954" s="2" t="inlineStr">
         <is>
           <t>Galerie</t>
         </is>
       </c>
-      <c r="E954" s="4" t="n"/>
-      <c r="F954" s="3" t="n"/>
-      <c r="G954" s="4" t="n"/>
-      <c r="H954" s="4" t="n"/>
+      <c r="E954" s="2" t="inlineStr">
+        <is>
+          <t>Wandregal Hausform, schwarz</t>
+        </is>
+      </c>
+      <c r="F954" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G954" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H954" s="2" t="n"/>
     </row>
     <row r="955">
-      <c r="A955" s="4" t="inlineStr">
+      <c r="A955" s="2" t="inlineStr">
         <is>
           <t>BA03-05</t>
         </is>
       </c>
-      <c r="B955" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C955" s="4" t="inlineStr">
+      <c r="B955" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C955" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D955" s="4" t="inlineStr">
+      <c r="D955" s="2" t="inlineStr">
         <is>
           <t>Galerie</t>
         </is>
       </c>
-      <c r="E955" s="4" t="n"/>
-      <c r="F955" s="3" t="n"/>
-      <c r="G955" s="4" t="n"/>
-      <c r="H955" s="4" t="n"/>
+      <c r="E955" s="2" t="inlineStr">
+        <is>
+          <t>BRIO Puppenwagen rot gepunktet</t>
+        </is>
+      </c>
+      <c r="F955" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G955" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H955" s="2" t="n"/>
     </row>
     <row r="956">
-      <c r="A956" s="4" t="inlineStr">
+      <c r="A956" s="2" t="inlineStr">
         <is>
           <t>BA03-06</t>
         </is>
       </c>
-      <c r="B956" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C956" s="4" t="inlineStr">
+      <c r="B956" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C956" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D956" s="4" t="inlineStr">
+      <c r="D956" s="2" t="inlineStr">
         <is>
           <t>Galerie</t>
         </is>
       </c>
-      <c r="E956" s="4" t="n"/>
-      <c r="F956" s="3" t="n"/>
-      <c r="G956" s="4" t="n"/>
-      <c r="H956" s="4" t="n"/>
+      <c r="E956" s="2" t="inlineStr">
+        <is>
+          <t>Kaufladen weiß mit Aufsatz</t>
+        </is>
+      </c>
+      <c r="F956" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G956" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H956" s="2" t="n"/>
     </row>
     <row r="957">
-      <c r="A957" s="4" t="inlineStr">
+      <c r="A957" s="2" t="inlineStr">
         <is>
           <t>BA03-07</t>
         </is>
       </c>
-      <c r="B957" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C957" s="4" t="inlineStr">
+      <c r="B957" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C957" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D957" s="4" t="inlineStr">
+      <c r="D957" s="2" t="inlineStr">
         <is>
           <t>Galerie</t>
         </is>
       </c>
-      <c r="E957" s="4" t="n"/>
-      <c r="F957" s="3" t="n"/>
-      <c r="G957" s="4" t="n"/>
-      <c r="H957" s="4" t="n"/>
+      <c r="E957" s="2" t="inlineStr">
+        <is>
+          <t>Schrank weiß, zwei Türen</t>
+        </is>
+      </c>
+      <c r="F957" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G957" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H957" s="2" t="n"/>
     </row>
     <row r="958">
       <c r="A958" s="4" t="inlineStr">
@@ -27215,133 +27285,133 @@
       <c r="H965" s="4" t="n"/>
     </row>
     <row r="966">
-      <c r="A966" s="2" t="inlineStr">
+      <c r="A966" s="4" t="inlineStr">
+        <is>
+          <t>BA03-16</t>
+        </is>
+      </c>
+      <c r="B966" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C966" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D966" s="4" t="inlineStr">
+        <is>
+          <t>Galerie</t>
+        </is>
+      </c>
+      <c r="E966" s="4" t="n"/>
+      <c r="F966" s="3" t="n"/>
+      <c r="G966" s="4" t="n"/>
+      <c r="H966" s="4" t="n"/>
+    </row>
+    <row r="967">
+      <c r="A967" s="4" t="inlineStr">
+        <is>
+          <t>BA03-17</t>
+        </is>
+      </c>
+      <c r="B967" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C967" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D967" s="4" t="inlineStr">
+        <is>
+          <t>Galerie</t>
+        </is>
+      </c>
+      <c r="E967" s="4" t="n"/>
+      <c r="F967" s="3" t="n"/>
+      <c r="G967" s="4" t="n"/>
+      <c r="H967" s="4" t="n"/>
+    </row>
+    <row r="968">
+      <c r="A968" s="2" t="inlineStr">
         <is>
           <t>BA04-01</t>
         </is>
       </c>
-      <c r="B966" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C966" s="2" t="inlineStr">
+      <c r="B968" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C968" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D966" s="2" t="inlineStr">
+      <c r="D968" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 4</t>
         </is>
       </c>
-      <c r="E966" s="2" t="inlineStr">
+      <c r="E968" s="2" t="inlineStr">
         <is>
           <t>Rattankörbe 8 Stück</t>
         </is>
       </c>
-      <c r="F966" s="3" t="n">
+      <c r="F968" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G966" s="2" t="inlineStr">
+      <c r="G968" s="2" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="H966" s="2" t="n"/>
-    </row>
-    <row r="967">
-      <c r="A967" s="2" t="inlineStr">
+      <c r="H968" s="2" t="n"/>
+    </row>
+    <row r="969">
+      <c r="A969" s="2" t="inlineStr">
         <is>
           <t>BA04-02</t>
         </is>
       </c>
-      <c r="B967" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C967" s="2" t="inlineStr">
+      <c r="B969" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C969" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D967" s="2" t="inlineStr">
+      <c r="D969" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 4</t>
         </is>
       </c>
-      <c r="E967" s="2" t="inlineStr">
+      <c r="E969" s="2" t="inlineStr">
         <is>
           <t>Holzkiste Obstkistenoptik</t>
         </is>
       </c>
-      <c r="F967" s="3" t="n">
+      <c r="F969" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G967" s="2" t="inlineStr">
+      <c r="G969" s="2" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="H967" s="2" t="n"/>
-    </row>
-    <row r="968">
-      <c r="A968" s="4" t="inlineStr">
-        <is>
-          <t>BA04-03</t>
-        </is>
-      </c>
-      <c r="B968" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C968" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D968" s="4" t="inlineStr">
-        <is>
-          <t>Gruppenraum 4</t>
-        </is>
-      </c>
-      <c r="E968" s="4" t="n"/>
-      <c r="F968" s="3" t="n"/>
-      <c r="G968" s="4" t="n"/>
-      <c r="H968" s="4" t="n"/>
-    </row>
-    <row r="969">
-      <c r="A969" s="4" t="inlineStr">
-        <is>
-          <t>BA04-04</t>
-        </is>
-      </c>
-      <c r="B969" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C969" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D969" s="4" t="inlineStr">
-        <is>
-          <t>Gruppenraum 4</t>
-        </is>
-      </c>
-      <c r="E969" s="4" t="n"/>
-      <c r="F969" s="3" t="n"/>
-      <c r="G969" s="4" t="n"/>
-      <c r="H969" s="4" t="n"/>
+      <c r="H969" s="2" t="n"/>
     </row>
     <row r="970">
       <c r="A970" s="4" t="inlineStr">
         <is>
-          <t>BA04-05</t>
+          <t>BA04-03</t>
         </is>
       </c>
       <c r="B970" s="4" t="inlineStr">
@@ -27367,7 +27437,7 @@
     <row r="971">
       <c r="A971" s="4" t="inlineStr">
         <is>
-          <t>BA04-06</t>
+          <t>BA04-04</t>
         </is>
       </c>
       <c r="B971" s="4" t="inlineStr">
@@ -27393,7 +27463,7 @@
     <row r="972">
       <c r="A972" s="4" t="inlineStr">
         <is>
-          <t>BA04-07</t>
+          <t>BA04-05</t>
         </is>
       </c>
       <c r="B972" s="4" t="inlineStr">
@@ -27419,7 +27489,7 @@
     <row r="973">
       <c r="A973" s="4" t="inlineStr">
         <is>
-          <t>BA04-08</t>
+          <t>BA04-06</t>
         </is>
       </c>
       <c r="B973" s="4" t="inlineStr">
@@ -27445,7 +27515,7 @@
     <row r="974">
       <c r="A974" s="4" t="inlineStr">
         <is>
-          <t>BA04-09</t>
+          <t>BA04-07</t>
         </is>
       </c>
       <c r="B974" s="4" t="inlineStr">
@@ -27471,7 +27541,7 @@
     <row r="975">
       <c r="A975" s="4" t="inlineStr">
         <is>
-          <t>BA04-10</t>
+          <t>BA04-08</t>
         </is>
       </c>
       <c r="B975" s="4" t="inlineStr">
@@ -27497,7 +27567,7 @@
     <row r="976">
       <c r="A976" s="4" t="inlineStr">
         <is>
-          <t>BA04-11</t>
+          <t>BA04-09</t>
         </is>
       </c>
       <c r="B976" s="4" t="inlineStr">
@@ -27523,7 +27593,7 @@
     <row r="977">
       <c r="A977" s="4" t="inlineStr">
         <is>
-          <t>BA04-12</t>
+          <t>BA04-10</t>
         </is>
       </c>
       <c r="B977" s="4" t="inlineStr">
@@ -27549,7 +27619,7 @@
     <row r="978">
       <c r="A978" s="4" t="inlineStr">
         <is>
-          <t>BA04-13</t>
+          <t>BA04-11</t>
         </is>
       </c>
       <c r="B978" s="4" t="inlineStr">
@@ -27575,7 +27645,7 @@
     <row r="979">
       <c r="A979" s="4" t="inlineStr">
         <is>
-          <t>BA04-14</t>
+          <t>BA04-12</t>
         </is>
       </c>
       <c r="B979" s="4" t="inlineStr">
@@ -27601,7 +27671,7 @@
     <row r="980">
       <c r="A980" s="4" t="inlineStr">
         <is>
-          <t>BA04-15</t>
+          <t>BA04-13</t>
         </is>
       </c>
       <c r="B980" s="4" t="inlineStr">
@@ -27627,7 +27697,7 @@
     <row r="981">
       <c r="A981" s="4" t="inlineStr">
         <is>
-          <t>BA04-16</t>
+          <t>BA04-14</t>
         </is>
       </c>
       <c r="B981" s="4" t="inlineStr">
@@ -27653,7 +27723,7 @@
     <row r="982">
       <c r="A982" s="4" t="inlineStr">
         <is>
-          <t>BA04-17</t>
+          <t>BA04-15</t>
         </is>
       </c>
       <c r="B982" s="4" t="inlineStr">
@@ -27679,7 +27749,7 @@
     <row r="983">
       <c r="A983" s="4" t="inlineStr">
         <is>
-          <t>BA04-18</t>
+          <t>BA04-16</t>
         </is>
       </c>
       <c r="B983" s="4" t="inlineStr">
@@ -27705,7 +27775,7 @@
     <row r="984">
       <c r="A984" s="4" t="inlineStr">
         <is>
-          <t>BA04-19</t>
+          <t>BA04-17</t>
         </is>
       </c>
       <c r="B984" s="4" t="inlineStr">
@@ -27731,7 +27801,7 @@
     <row r="985">
       <c r="A985" s="4" t="inlineStr">
         <is>
-          <t>BA04-20</t>
+          <t>BA04-18</t>
         </is>
       </c>
       <c r="B985" s="4" t="inlineStr">
@@ -27757,7 +27827,7 @@
     <row r="986">
       <c r="A986" s="4" t="inlineStr">
         <is>
-          <t>BA04-21</t>
+          <t>BA04-19</t>
         </is>
       </c>
       <c r="B986" s="4" t="inlineStr">
@@ -27783,7 +27853,7 @@
     <row r="987">
       <c r="A987" s="4" t="inlineStr">
         <is>
-          <t>BA04-22</t>
+          <t>BA04-20</t>
         </is>
       </c>
       <c r="B987" s="4" t="inlineStr">
@@ -27809,7 +27879,7 @@
     <row r="988">
       <c r="A988" s="4" t="inlineStr">
         <is>
-          <t>BA04-23</t>
+          <t>BA04-21</t>
         </is>
       </c>
       <c r="B988" s="4" t="inlineStr">
@@ -27835,7 +27905,7 @@
     <row r="989">
       <c r="A989" s="4" t="inlineStr">
         <is>
-          <t>BA04-24</t>
+          <t>BA04-22</t>
         </is>
       </c>
       <c r="B989" s="4" t="inlineStr">
@@ -27861,7 +27931,7 @@
     <row r="990">
       <c r="A990" s="4" t="inlineStr">
         <is>
-          <t>BA04-25</t>
+          <t>BA04-23</t>
         </is>
       </c>
       <c r="B990" s="4" t="inlineStr">
@@ -27887,7 +27957,7 @@
     <row r="991">
       <c r="A991" s="4" t="inlineStr">
         <is>
-          <t>BA05-01</t>
+          <t>BA04-24</t>
         </is>
       </c>
       <c r="B991" s="4" t="inlineStr">
@@ -27902,7 +27972,7 @@
       </c>
       <c r="D991" s="4" t="inlineStr">
         <is>
-          <t>Turnraum</t>
+          <t>Gruppenraum 4</t>
         </is>
       </c>
       <c r="E991" s="4" t="n"/>
@@ -27913,7 +27983,7 @@
     <row r="992">
       <c r="A992" s="4" t="inlineStr">
         <is>
-          <t>BA05-02</t>
+          <t>BA04-25</t>
         </is>
       </c>
       <c r="B992" s="4" t="inlineStr">
@@ -27928,7 +27998,7 @@
       </c>
       <c r="D992" s="4" t="inlineStr">
         <is>
-          <t>Turnraum</t>
+          <t>Gruppenraum 4</t>
         </is>
       </c>
       <c r="E992" s="4" t="n"/>
@@ -27939,7 +28009,7 @@
     <row r="993">
       <c r="A993" s="4" t="inlineStr">
         <is>
-          <t>BA05-03</t>
+          <t>BA05-01</t>
         </is>
       </c>
       <c r="B993" s="4" t="inlineStr">
@@ -27965,7 +28035,7 @@
     <row r="994">
       <c r="A994" s="4" t="inlineStr">
         <is>
-          <t>BA05-04</t>
+          <t>BA05-02</t>
         </is>
       </c>
       <c r="B994" s="4" t="inlineStr">
@@ -27991,7 +28061,7 @@
     <row r="995">
       <c r="A995" s="4" t="inlineStr">
         <is>
-          <t>BA05-05</t>
+          <t>BA05-03</t>
         </is>
       </c>
       <c r="B995" s="4" t="inlineStr">
@@ -28017,7 +28087,7 @@
     <row r="996">
       <c r="A996" s="4" t="inlineStr">
         <is>
-          <t>BA05-06</t>
+          <t>BA05-04</t>
         </is>
       </c>
       <c r="B996" s="4" t="inlineStr">
@@ -28043,7 +28113,7 @@
     <row r="997">
       <c r="A997" s="4" t="inlineStr">
         <is>
-          <t>BA05-07</t>
+          <t>BA05-05</t>
         </is>
       </c>
       <c r="B997" s="4" t="inlineStr">
@@ -28069,7 +28139,7 @@
     <row r="998">
       <c r="A998" s="4" t="inlineStr">
         <is>
-          <t>BA05-08</t>
+          <t>BA05-06</t>
         </is>
       </c>
       <c r="B998" s="4" t="inlineStr">
@@ -28095,7 +28165,7 @@
     <row r="999">
       <c r="A999" s="4" t="inlineStr">
         <is>
-          <t>BA05-09</t>
+          <t>BA05-07</t>
         </is>
       </c>
       <c r="B999" s="4" t="inlineStr">
@@ -28121,7 +28191,7 @@
     <row r="1000">
       <c r="A1000" s="4" t="inlineStr">
         <is>
-          <t>BA05-10</t>
+          <t>BA05-08</t>
         </is>
       </c>
       <c r="B1000" s="4" t="inlineStr">
@@ -28147,7 +28217,7 @@
     <row r="1001">
       <c r="A1001" s="4" t="inlineStr">
         <is>
-          <t>BA05-11</t>
+          <t>BA05-09</t>
         </is>
       </c>
       <c r="B1001" s="4" t="inlineStr">
@@ -28173,7 +28243,7 @@
     <row r="1002">
       <c r="A1002" s="4" t="inlineStr">
         <is>
-          <t>BA05-12</t>
+          <t>BA05-10</t>
         </is>
       </c>
       <c r="B1002" s="4" t="inlineStr">
@@ -28199,7 +28269,7 @@
     <row r="1003">
       <c r="A1003" s="4" t="inlineStr">
         <is>
-          <t>BA05-13</t>
+          <t>BA05-11</t>
         </is>
       </c>
       <c r="B1003" s="4" t="inlineStr">
@@ -28225,7 +28295,7 @@
     <row r="1004">
       <c r="A1004" s="4" t="inlineStr">
         <is>
-          <t>BA05-14</t>
+          <t>BA05-12</t>
         </is>
       </c>
       <c r="B1004" s="4" t="inlineStr">
@@ -28251,7 +28321,7 @@
     <row r="1005">
       <c r="A1005" s="4" t="inlineStr">
         <is>
-          <t>BA05-15</t>
+          <t>BA05-13</t>
         </is>
       </c>
       <c r="B1005" s="4" t="inlineStr">
@@ -28277,7 +28347,7 @@
     <row r="1006">
       <c r="A1006" s="4" t="inlineStr">
         <is>
-          <t>BA05-16</t>
+          <t>BA05-14</t>
         </is>
       </c>
       <c r="B1006" s="4" t="inlineStr">
@@ -28303,7 +28373,7 @@
     <row r="1007">
       <c r="A1007" s="4" t="inlineStr">
         <is>
-          <t>BA05-17</t>
+          <t>BA05-15</t>
         </is>
       </c>
       <c r="B1007" s="4" t="inlineStr">
@@ -28329,7 +28399,7 @@
     <row r="1008">
       <c r="A1008" s="4" t="inlineStr">
         <is>
-          <t>BA05-18</t>
+          <t>BA05-16</t>
         </is>
       </c>
       <c r="B1008" s="4" t="inlineStr">
@@ -28355,7 +28425,7 @@
     <row r="1009">
       <c r="A1009" s="4" t="inlineStr">
         <is>
-          <t>BA05-19</t>
+          <t>BA05-17</t>
         </is>
       </c>
       <c r="B1009" s="4" t="inlineStr">
@@ -28381,7 +28451,7 @@
     <row r="1010">
       <c r="A1010" s="4" t="inlineStr">
         <is>
-          <t>BA05-20</t>
+          <t>BA05-18</t>
         </is>
       </c>
       <c r="B1010" s="4" t="inlineStr">
@@ -28407,7 +28477,7 @@
     <row r="1011">
       <c r="A1011" s="4" t="inlineStr">
         <is>
-          <t>BA05-21</t>
+          <t>BA05-19</t>
         </is>
       </c>
       <c r="B1011" s="4" t="inlineStr">
@@ -28433,7 +28503,7 @@
     <row r="1012">
       <c r="A1012" s="4" t="inlineStr">
         <is>
-          <t>BA05-22</t>
+          <t>BA05-20</t>
         </is>
       </c>
       <c r="B1012" s="4" t="inlineStr">
@@ -28459,7 +28529,7 @@
     <row r="1013">
       <c r="A1013" s="4" t="inlineStr">
         <is>
-          <t>BA05-23</t>
+          <t>BA05-21</t>
         </is>
       </c>
       <c r="B1013" s="4" t="inlineStr">
@@ -28485,7 +28555,7 @@
     <row r="1014">
       <c r="A1014" s="4" t="inlineStr">
         <is>
-          <t>BA05-24</t>
+          <t>BA05-22</t>
         </is>
       </c>
       <c r="B1014" s="4" t="inlineStr">
@@ -28511,7 +28581,7 @@
     <row r="1015">
       <c r="A1015" s="4" t="inlineStr">
         <is>
-          <t>BA05-25</t>
+          <t>BA05-23</t>
         </is>
       </c>
       <c r="B1015" s="4" t="inlineStr">
@@ -28537,7 +28607,7 @@
     <row r="1016">
       <c r="A1016" s="4" t="inlineStr">
         <is>
-          <t>BA05-26</t>
+          <t>BA05-24</t>
         </is>
       </c>
       <c r="B1016" s="4" t="inlineStr">
@@ -28563,7 +28633,7 @@
     <row r="1017">
       <c r="A1017" s="4" t="inlineStr">
         <is>
-          <t>BA05-27</t>
+          <t>BA05-25</t>
         </is>
       </c>
       <c r="B1017" s="4" t="inlineStr">
@@ -28589,7 +28659,7 @@
     <row r="1018">
       <c r="A1018" s="4" t="inlineStr">
         <is>
-          <t>BA05-28</t>
+          <t>BA05-26</t>
         </is>
       </c>
       <c r="B1018" s="4" t="inlineStr">
@@ -28615,7 +28685,7 @@
     <row r="1019">
       <c r="A1019" s="4" t="inlineStr">
         <is>
-          <t>BA05-29</t>
+          <t>BA05-27</t>
         </is>
       </c>
       <c r="B1019" s="4" t="inlineStr">
@@ -28641,7 +28711,7 @@
     <row r="1020">
       <c r="A1020" s="4" t="inlineStr">
         <is>
-          <t>BA05-30</t>
+          <t>BA05-28</t>
         </is>
       </c>
       <c r="B1020" s="4" t="inlineStr">
@@ -28667,7 +28737,7 @@
     <row r="1021">
       <c r="A1021" s="4" t="inlineStr">
         <is>
-          <t>BA05-31</t>
+          <t>BA05-29</t>
         </is>
       </c>
       <c r="B1021" s="4" t="inlineStr">
@@ -28693,7 +28763,7 @@
     <row r="1022">
       <c r="A1022" s="4" t="inlineStr">
         <is>
-          <t>BA05-32</t>
+          <t>BA05-30</t>
         </is>
       </c>
       <c r="B1022" s="4" t="inlineStr">
@@ -28719,7 +28789,7 @@
     <row r="1023">
       <c r="A1023" s="4" t="inlineStr">
         <is>
-          <t>BA05-33</t>
+          <t>BA05-31</t>
         </is>
       </c>
       <c r="B1023" s="4" t="inlineStr">
@@ -28745,7 +28815,7 @@
     <row r="1024">
       <c r="A1024" s="4" t="inlineStr">
         <is>
-          <t>BA05-34</t>
+          <t>BA05-32</t>
         </is>
       </c>
       <c r="B1024" s="4" t="inlineStr">
@@ -28771,7 +28841,7 @@
     <row r="1025">
       <c r="A1025" s="4" t="inlineStr">
         <is>
-          <t>BA05-35</t>
+          <t>BA05-33</t>
         </is>
       </c>
       <c r="B1025" s="4" t="inlineStr">
@@ -28797,7 +28867,7 @@
     <row r="1026">
       <c r="A1026" s="4" t="inlineStr">
         <is>
-          <t>BA05-36</t>
+          <t>BA05-34</t>
         </is>
       </c>
       <c r="B1026" s="4" t="inlineStr">
@@ -28823,7 +28893,7 @@
     <row r="1027">
       <c r="A1027" s="4" t="inlineStr">
         <is>
-          <t>BA05-37</t>
+          <t>BA05-35</t>
         </is>
       </c>
       <c r="B1027" s="4" t="inlineStr">
@@ -28849,7 +28919,7 @@
     <row r="1028">
       <c r="A1028" s="4" t="inlineStr">
         <is>
-          <t>BA05-38</t>
+          <t>BA05-36</t>
         </is>
       </c>
       <c r="B1028" s="4" t="inlineStr">
@@ -28875,7 +28945,7 @@
     <row r="1029">
       <c r="A1029" s="4" t="inlineStr">
         <is>
-          <t>BA05-39</t>
+          <t>BA05-37</t>
         </is>
       </c>
       <c r="B1029" s="4" t="inlineStr">
@@ -28901,7 +28971,7 @@
     <row r="1030">
       <c r="A1030" s="4" t="inlineStr">
         <is>
-          <t>BA05-40</t>
+          <t>BA05-38</t>
         </is>
       </c>
       <c r="B1030" s="4" t="inlineStr">
@@ -28927,7 +28997,7 @@
     <row r="1031">
       <c r="A1031" s="4" t="inlineStr">
         <is>
-          <t>BA06-01</t>
+          <t>BA05-39</t>
         </is>
       </c>
       <c r="B1031" s="4" t="inlineStr">
@@ -28942,7 +29012,7 @@
       </c>
       <c r="D1031" s="4" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Turnraum</t>
         </is>
       </c>
       <c r="E1031" s="4" t="n"/>
@@ -28953,7 +29023,7 @@
     <row r="1032">
       <c r="A1032" s="4" t="inlineStr">
         <is>
-          <t>BA06-02</t>
+          <t>BA05-40</t>
         </is>
       </c>
       <c r="B1032" s="4" t="inlineStr">
@@ -28968,7 +29038,7 @@
       </c>
       <c r="D1032" s="4" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Turnraum</t>
         </is>
       </c>
       <c r="E1032" s="4" t="n"/>
@@ -28979,7 +29049,7 @@
     <row r="1033">
       <c r="A1033" s="4" t="inlineStr">
         <is>
-          <t>BA06-03</t>
+          <t>BA06-01</t>
         </is>
       </c>
       <c r="B1033" s="4" t="inlineStr">
@@ -29005,7 +29075,7 @@
     <row r="1034">
       <c r="A1034" s="4" t="inlineStr">
         <is>
-          <t>BA06-04</t>
+          <t>BA06-02</t>
         </is>
       </c>
       <c r="B1034" s="4" t="inlineStr">
@@ -29031,7 +29101,7 @@
     <row r="1035">
       <c r="A1035" s="4" t="inlineStr">
         <is>
-          <t>BA06-05</t>
+          <t>BA06-03</t>
         </is>
       </c>
       <c r="B1035" s="4" t="inlineStr">
@@ -29057,7 +29127,7 @@
     <row r="1036">
       <c r="A1036" s="4" t="inlineStr">
         <is>
-          <t>BA06-06</t>
+          <t>BA06-04</t>
         </is>
       </c>
       <c r="B1036" s="4" t="inlineStr">
@@ -29083,7 +29153,7 @@
     <row r="1037">
       <c r="A1037" s="4" t="inlineStr">
         <is>
-          <t>BA06-07</t>
+          <t>BA06-05</t>
         </is>
       </c>
       <c r="B1037" s="4" t="inlineStr">
@@ -29109,7 +29179,7 @@
     <row r="1038">
       <c r="A1038" s="4" t="inlineStr">
         <is>
-          <t>BA06-08</t>
+          <t>BA06-06</t>
         </is>
       </c>
       <c r="B1038" s="4" t="inlineStr">
@@ -29135,7 +29205,7 @@
     <row r="1039">
       <c r="A1039" s="4" t="inlineStr">
         <is>
-          <t>BA06-09</t>
+          <t>BA06-07</t>
         </is>
       </c>
       <c r="B1039" s="4" t="inlineStr">
@@ -29161,7 +29231,7 @@
     <row r="1040">
       <c r="A1040" s="4" t="inlineStr">
         <is>
-          <t>BA06-10</t>
+          <t>BA06-08</t>
         </is>
       </c>
       <c r="B1040" s="4" t="inlineStr">
@@ -29187,7 +29257,7 @@
     <row r="1041">
       <c r="A1041" s="4" t="inlineStr">
         <is>
-          <t>BA06-11</t>
+          <t>BA06-09</t>
         </is>
       </c>
       <c r="B1041" s="4" t="inlineStr">
@@ -29213,7 +29283,7 @@
     <row r="1042">
       <c r="A1042" s="4" t="inlineStr">
         <is>
-          <t>BA06-12</t>
+          <t>BA06-10</t>
         </is>
       </c>
       <c r="B1042" s="4" t="inlineStr">
@@ -29239,7 +29309,7 @@
     <row r="1043">
       <c r="A1043" s="4" t="inlineStr">
         <is>
-          <t>BA06-13</t>
+          <t>BA06-11</t>
         </is>
       </c>
       <c r="B1043" s="4" t="inlineStr">
@@ -29265,7 +29335,7 @@
     <row r="1044">
       <c r="A1044" s="4" t="inlineStr">
         <is>
-          <t>BA06-14</t>
+          <t>BA06-12</t>
         </is>
       </c>
       <c r="B1044" s="4" t="inlineStr">
@@ -29291,7 +29361,7 @@
     <row r="1045">
       <c r="A1045" s="4" t="inlineStr">
         <is>
-          <t>BA06-15</t>
+          <t>BA06-13</t>
         </is>
       </c>
       <c r="B1045" s="4" t="inlineStr">
@@ -29317,7 +29387,7 @@
     <row r="1046">
       <c r="A1046" s="4" t="inlineStr">
         <is>
-          <t>BA07-01</t>
+          <t>BA06-14</t>
         </is>
       </c>
       <c r="B1046" s="4" t="inlineStr">
@@ -29332,7 +29402,7 @@
       </c>
       <c r="D1046" s="4" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Material / Turnraum</t>
         </is>
       </c>
       <c r="E1046" s="4" t="n"/>
@@ -29343,7 +29413,7 @@
     <row r="1047">
       <c r="A1047" s="4" t="inlineStr">
         <is>
-          <t>BA07-02</t>
+          <t>BA06-15</t>
         </is>
       </c>
       <c r="B1047" s="4" t="inlineStr">
@@ -29358,7 +29428,7 @@
       </c>
       <c r="D1047" s="4" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Material / Turnraum</t>
         </is>
       </c>
       <c r="E1047" s="4" t="n"/>
@@ -29369,7 +29439,7 @@
     <row r="1048">
       <c r="A1048" s="4" t="inlineStr">
         <is>
-          <t>BA07-03</t>
+          <t>BA07-01</t>
         </is>
       </c>
       <c r="B1048" s="4" t="inlineStr">
@@ -29395,7 +29465,7 @@
     <row r="1049">
       <c r="A1049" s="4" t="inlineStr">
         <is>
-          <t>BA07-04</t>
+          <t>BA07-02</t>
         </is>
       </c>
       <c r="B1049" s="4" t="inlineStr">
@@ -29421,7 +29491,7 @@
     <row r="1050">
       <c r="A1050" s="4" t="inlineStr">
         <is>
-          <t>BA07-05</t>
+          <t>BA07-03</t>
         </is>
       </c>
       <c r="B1050" s="4" t="inlineStr">
@@ -29447,7 +29517,7 @@
     <row r="1051">
       <c r="A1051" s="4" t="inlineStr">
         <is>
-          <t>BA07-06</t>
+          <t>BA07-04</t>
         </is>
       </c>
       <c r="B1051" s="4" t="inlineStr">
@@ -29473,7 +29543,7 @@
     <row r="1052">
       <c r="A1052" s="4" t="inlineStr">
         <is>
-          <t>BA07-07</t>
+          <t>BA07-05</t>
         </is>
       </c>
       <c r="B1052" s="4" t="inlineStr">
@@ -29499,7 +29569,7 @@
     <row r="1053">
       <c r="A1053" s="4" t="inlineStr">
         <is>
-          <t>BA07-08</t>
+          <t>BA07-06</t>
         </is>
       </c>
       <c r="B1053" s="4" t="inlineStr">
@@ -29525,7 +29595,7 @@
     <row r="1054">
       <c r="A1054" s="4" t="inlineStr">
         <is>
-          <t>BA07-09</t>
+          <t>BA07-07</t>
         </is>
       </c>
       <c r="B1054" s="4" t="inlineStr">
@@ -29551,7 +29621,7 @@
     <row r="1055">
       <c r="A1055" s="4" t="inlineStr">
         <is>
-          <t>BA07-10</t>
+          <t>BA07-08</t>
         </is>
       </c>
       <c r="B1055" s="4" t="inlineStr">
@@ -29577,7 +29647,7 @@
     <row r="1056">
       <c r="A1056" s="4" t="inlineStr">
         <is>
-          <t>BA07-11</t>
+          <t>BA07-09</t>
         </is>
       </c>
       <c r="B1056" s="4" t="inlineStr">
@@ -29603,7 +29673,7 @@
     <row r="1057">
       <c r="A1057" s="4" t="inlineStr">
         <is>
-          <t>BA07-12</t>
+          <t>BA07-10</t>
         </is>
       </c>
       <c r="B1057" s="4" t="inlineStr">
@@ -29629,7 +29699,7 @@
     <row r="1058">
       <c r="A1058" s="4" t="inlineStr">
         <is>
-          <t>BA07-13</t>
+          <t>BA07-11</t>
         </is>
       </c>
       <c r="B1058" s="4" t="inlineStr">
@@ -29655,7 +29725,7 @@
     <row r="1059">
       <c r="A1059" s="4" t="inlineStr">
         <is>
-          <t>BA07-14</t>
+          <t>BA07-12</t>
         </is>
       </c>
       <c r="B1059" s="4" t="inlineStr">
@@ -29681,7 +29751,7 @@
     <row r="1060">
       <c r="A1060" s="4" t="inlineStr">
         <is>
-          <t>BA07-15</t>
+          <t>BA07-13</t>
         </is>
       </c>
       <c r="B1060" s="4" t="inlineStr">
@@ -29705,81 +29775,61 @@
       <c r="H1060" s="4" t="n"/>
     </row>
     <row r="1061">
-      <c r="A1061" s="2" t="inlineStr">
-        <is>
-          <t>BA08-01</t>
-        </is>
-      </c>
-      <c r="B1061" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1061" s="2" t="inlineStr">
+      <c r="A1061" s="4" t="inlineStr">
+        <is>
+          <t>BA07-14</t>
+        </is>
+      </c>
+      <c r="B1061" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1061" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1061" s="2" t="inlineStr">
-        <is>
-          <t>Atelier</t>
-        </is>
-      </c>
-      <c r="E1061" s="2" t="inlineStr">
-        <is>
-          <t>Konvolut Mal- und Bastelfarben</t>
-        </is>
-      </c>
-      <c r="F1061" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1061" s="2" t="inlineStr">
-        <is>
-          <t>Konvolut</t>
-        </is>
-      </c>
-      <c r="H1061" s="2" t="n"/>
+      <c r="D1061" s="4" t="inlineStr">
+        <is>
+          <t>Klassenzimmer</t>
+        </is>
+      </c>
+      <c r="E1061" s="4" t="n"/>
+      <c r="F1061" s="3" t="n"/>
+      <c r="G1061" s="4" t="n"/>
+      <c r="H1061" s="4" t="n"/>
     </row>
     <row r="1062">
-      <c r="A1062" s="2" t="inlineStr">
-        <is>
-          <t>BA08-02</t>
-        </is>
-      </c>
-      <c r="B1062" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1062" s="2" t="inlineStr">
+      <c r="A1062" s="4" t="inlineStr">
+        <is>
+          <t>BA07-15</t>
+        </is>
+      </c>
+      <c r="B1062" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1062" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1062" s="2" t="inlineStr">
-        <is>
-          <t>Atelier</t>
-        </is>
-      </c>
-      <c r="E1062" s="2" t="inlineStr">
-        <is>
-          <t>Acrylfarben-Sortiment im Holzkasten</t>
-        </is>
-      </c>
-      <c r="F1062" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1062" s="2" t="inlineStr">
-        <is>
-          <t>Konvolut</t>
-        </is>
-      </c>
-      <c r="H1062" s="2" t="n"/>
+      <c r="D1062" s="4" t="inlineStr">
+        <is>
+          <t>Klassenzimmer</t>
+        </is>
+      </c>
+      <c r="E1062" s="4" t="n"/>
+      <c r="F1062" s="3" t="n"/>
+      <c r="G1062" s="4" t="n"/>
+      <c r="H1062" s="4" t="n"/>
     </row>
     <row r="1063">
       <c r="A1063" s="2" t="inlineStr">
         <is>
-          <t>BA08-03</t>
+          <t>BA08-01</t>
         </is>
       </c>
       <c r="B1063" s="2" t="inlineStr">
@@ -29799,7 +29849,7 @@
       </c>
       <c r="E1063" s="2" t="inlineStr">
         <is>
-          <t>Konvolut Bastelmaterial</t>
+          <t>Konvolut Mal- und Bastelfarben</t>
         </is>
       </c>
       <c r="F1063" s="3" t="n">
@@ -29815,7 +29865,7 @@
     <row r="1064">
       <c r="A1064" s="2" t="inlineStr">
         <is>
-          <t>BA08-04</t>
+          <t>BA08-02</t>
         </is>
       </c>
       <c r="B1064" s="2" t="inlineStr">
@@ -29835,7 +29885,7 @@
       </c>
       <c r="E1064" s="2" t="inlineStr">
         <is>
-          <t>buntes Papier</t>
+          <t>Acrylfarben-Sortiment im Holzkasten</t>
         </is>
       </c>
       <c r="F1064" s="3" t="n">
@@ -29849,61 +29899,81 @@
       <c r="H1064" s="2" t="n"/>
     </row>
     <row r="1065">
-      <c r="A1065" s="4" t="inlineStr">
-        <is>
-          <t>BA08-05</t>
-        </is>
-      </c>
-      <c r="B1065" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1065" s="4" t="inlineStr">
+      <c r="A1065" s="2" t="inlineStr">
+        <is>
+          <t>BA08-03</t>
+        </is>
+      </c>
+      <c r="B1065" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1065" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1065" s="4" t="inlineStr">
+      <c r="D1065" s="2" t="inlineStr">
         <is>
           <t>Atelier</t>
         </is>
       </c>
-      <c r="E1065" s="4" t="n"/>
-      <c r="F1065" s="3" t="n"/>
-      <c r="G1065" s="4" t="n"/>
-      <c r="H1065" s="4" t="n"/>
+      <c r="E1065" s="2" t="inlineStr">
+        <is>
+          <t>Konvolut Bastelmaterial</t>
+        </is>
+      </c>
+      <c r="F1065" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1065" s="2" t="inlineStr">
+        <is>
+          <t>Konvolut</t>
+        </is>
+      </c>
+      <c r="H1065" s="2" t="n"/>
     </row>
     <row r="1066">
-      <c r="A1066" s="4" t="inlineStr">
-        <is>
-          <t>BA08-06</t>
-        </is>
-      </c>
-      <c r="B1066" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1066" s="4" t="inlineStr">
+      <c r="A1066" s="2" t="inlineStr">
+        <is>
+          <t>BA08-04</t>
+        </is>
+      </c>
+      <c r="B1066" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1066" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1066" s="4" t="inlineStr">
+      <c r="D1066" s="2" t="inlineStr">
         <is>
           <t>Atelier</t>
         </is>
       </c>
-      <c r="E1066" s="4" t="n"/>
-      <c r="F1066" s="3" t="n"/>
-      <c r="G1066" s="4" t="n"/>
-      <c r="H1066" s="4" t="n"/>
+      <c r="E1066" s="2" t="inlineStr">
+        <is>
+          <t>buntes Papier</t>
+        </is>
+      </c>
+      <c r="F1066" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1066" s="2" t="inlineStr">
+        <is>
+          <t>Konvolut</t>
+        </is>
+      </c>
+      <c r="H1066" s="2" t="n"/>
     </row>
     <row r="1067">
       <c r="A1067" s="4" t="inlineStr">
         <is>
-          <t>BA08-07</t>
+          <t>BA08-05</t>
         </is>
       </c>
       <c r="B1067" s="4" t="inlineStr">
@@ -29929,7 +29999,7 @@
     <row r="1068">
       <c r="A1068" s="4" t="inlineStr">
         <is>
-          <t>BA08-08</t>
+          <t>BA08-06</t>
         </is>
       </c>
       <c r="B1068" s="4" t="inlineStr">
@@ -29955,7 +30025,7 @@
     <row r="1069">
       <c r="A1069" s="4" t="inlineStr">
         <is>
-          <t>BA08-09</t>
+          <t>BA08-07</t>
         </is>
       </c>
       <c r="B1069" s="4" t="inlineStr">
@@ -29981,7 +30051,7 @@
     <row r="1070">
       <c r="A1070" s="4" t="inlineStr">
         <is>
-          <t>BA08-10</t>
+          <t>BA08-08</t>
         </is>
       </c>
       <c r="B1070" s="4" t="inlineStr">
@@ -30007,7 +30077,7 @@
     <row r="1071">
       <c r="A1071" s="4" t="inlineStr">
         <is>
-          <t>BA08-11</t>
+          <t>BA08-09</t>
         </is>
       </c>
       <c r="B1071" s="4" t="inlineStr">
@@ -30033,7 +30103,7 @@
     <row r="1072">
       <c r="A1072" s="4" t="inlineStr">
         <is>
-          <t>BA08-12</t>
+          <t>BA08-10</t>
         </is>
       </c>
       <c r="B1072" s="4" t="inlineStr">
@@ -30059,7 +30129,7 @@
     <row r="1073">
       <c r="A1073" s="4" t="inlineStr">
         <is>
-          <t>BA08-13</t>
+          <t>BA08-11</t>
         </is>
       </c>
       <c r="B1073" s="4" t="inlineStr">
@@ -30085,7 +30155,7 @@
     <row r="1074">
       <c r="A1074" s="4" t="inlineStr">
         <is>
-          <t>BA08-14</t>
+          <t>BA08-12</t>
         </is>
       </c>
       <c r="B1074" s="4" t="inlineStr">
@@ -30111,7 +30181,7 @@
     <row r="1075">
       <c r="A1075" s="4" t="inlineStr">
         <is>
-          <t>BA08-15</t>
+          <t>BA08-13</t>
         </is>
       </c>
       <c r="B1075" s="4" t="inlineStr">
@@ -30137,7 +30207,7 @@
     <row r="1076">
       <c r="A1076" s="4" t="inlineStr">
         <is>
-          <t>BA08-16</t>
+          <t>BA08-14</t>
         </is>
       </c>
       <c r="B1076" s="4" t="inlineStr">
@@ -30163,7 +30233,7 @@
     <row r="1077">
       <c r="A1077" s="4" t="inlineStr">
         <is>
-          <t>BA08-17</t>
+          <t>BA08-15</t>
         </is>
       </c>
       <c r="B1077" s="4" t="inlineStr">
@@ -30189,7 +30259,7 @@
     <row r="1078">
       <c r="A1078" s="4" t="inlineStr">
         <is>
-          <t>BA08-18</t>
+          <t>BA08-16</t>
         </is>
       </c>
       <c r="B1078" s="4" t="inlineStr">
@@ -30215,7 +30285,7 @@
     <row r="1079">
       <c r="A1079" s="4" t="inlineStr">
         <is>
-          <t>BA08-19</t>
+          <t>BA08-17</t>
         </is>
       </c>
       <c r="B1079" s="4" t="inlineStr">
@@ -30241,7 +30311,7 @@
     <row r="1080">
       <c r="A1080" s="4" t="inlineStr">
         <is>
-          <t>BA08-20</t>
+          <t>BA08-18</t>
         </is>
       </c>
       <c r="B1080" s="4" t="inlineStr">
@@ -30267,7 +30337,7 @@
     <row r="1081">
       <c r="A1081" s="4" t="inlineStr">
         <is>
-          <t>BA08-21</t>
+          <t>BA08-19</t>
         </is>
       </c>
       <c r="B1081" s="4" t="inlineStr">
@@ -30293,7 +30363,7 @@
     <row r="1082">
       <c r="A1082" s="4" t="inlineStr">
         <is>
-          <t>BA08-22</t>
+          <t>BA08-20</t>
         </is>
       </c>
       <c r="B1082" s="4" t="inlineStr">
@@ -30319,7 +30389,7 @@
     <row r="1083">
       <c r="A1083" s="4" t="inlineStr">
         <is>
-          <t>BA08-23</t>
+          <t>BA08-21</t>
         </is>
       </c>
       <c r="B1083" s="4" t="inlineStr">
@@ -30345,7 +30415,7 @@
     <row r="1084">
       <c r="A1084" s="4" t="inlineStr">
         <is>
-          <t>BA08-24</t>
+          <t>BA08-22</t>
         </is>
       </c>
       <c r="B1084" s="4" t="inlineStr">
@@ -30371,7 +30441,7 @@
     <row r="1085">
       <c r="A1085" s="4" t="inlineStr">
         <is>
-          <t>BA08-25</t>
+          <t>BA08-23</t>
         </is>
       </c>
       <c r="B1085" s="4" t="inlineStr">
@@ -30395,81 +30465,61 @@
       <c r="H1085" s="4" t="n"/>
     </row>
     <row r="1086">
-      <c r="A1086" s="2" t="inlineStr">
-        <is>
-          <t>BA09-01</t>
-        </is>
-      </c>
-      <c r="B1086" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1086" s="2" t="inlineStr">
+      <c r="A1086" s="4" t="inlineStr">
+        <is>
+          <t>BA08-24</t>
+        </is>
+      </c>
+      <c r="B1086" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1086" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1086" s="2" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="E1086" s="2" t="inlineStr">
-        <is>
-          <t>Deko Metallruten mit Pompons</t>
-        </is>
-      </c>
-      <c r="F1086" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1086" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1086" s="2" t="n"/>
+      <c r="D1086" s="4" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="E1086" s="4" t="n"/>
+      <c r="F1086" s="3" t="n"/>
+      <c r="G1086" s="4" t="n"/>
+      <c r="H1086" s="4" t="n"/>
     </row>
     <row r="1087">
-      <c r="A1087" s="2" t="inlineStr">
-        <is>
-          <t>BA09-02</t>
-        </is>
-      </c>
-      <c r="B1087" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1087" s="2" t="inlineStr">
+      <c r="A1087" s="4" t="inlineStr">
+        <is>
+          <t>BA08-25</t>
+        </is>
+      </c>
+      <c r="B1087" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1087" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1087" s="2" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="E1087" s="2" t="inlineStr">
-        <is>
-          <t>Elefantenfuß groß</t>
-        </is>
-      </c>
-      <c r="F1087" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1087" s="2" t="inlineStr">
-        <is>
-          <t>Set</t>
-        </is>
-      </c>
-      <c r="H1087" s="2" t="n"/>
+      <c r="D1087" s="4" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="E1087" s="4" t="n"/>
+      <c r="F1087" s="3" t="n"/>
+      <c r="G1087" s="4" t="n"/>
+      <c r="H1087" s="4" t="n"/>
     </row>
     <row r="1088">
       <c r="A1088" s="2" t="inlineStr">
         <is>
-          <t>BA09-03</t>
+          <t>BA09-01</t>
         </is>
       </c>
       <c r="B1088" s="2" t="inlineStr">
@@ -30489,11 +30539,11 @@
       </c>
       <c r="E1088" s="2" t="inlineStr">
         <is>
-          <t>Werte-Rad</t>
+          <t>Deko Metallruten mit Pompons</t>
         </is>
       </c>
       <c r="F1088" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1088" s="2" t="inlineStr">
         <is>
@@ -30505,7 +30555,7 @@
     <row r="1089">
       <c r="A1089" s="2" t="inlineStr">
         <is>
-          <t>BA09-04</t>
+          <t>BA09-02</t>
         </is>
       </c>
       <c r="B1089" s="2" t="inlineStr">
@@ -30525,7 +30575,7 @@
       </c>
       <c r="E1089" s="2" t="inlineStr">
         <is>
-          <t>USM Haller Tisch</t>
+          <t>Elefantenfuß groß</t>
         </is>
       </c>
       <c r="F1089" s="3" t="n">
@@ -30533,7 +30583,7 @@
       </c>
       <c r="G1089" s="2" t="inlineStr">
         <is>
-          <t>Stück</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="H1089" s="2" t="n"/>
@@ -30541,7 +30591,7 @@
     <row r="1090">
       <c r="A1090" s="2" t="inlineStr">
         <is>
-          <t>BA09-05</t>
+          <t>BA09-03</t>
         </is>
       </c>
       <c r="B1090" s="2" t="inlineStr">
@@ -30561,11 +30611,11 @@
       </c>
       <c r="E1090" s="2" t="inlineStr">
         <is>
-          <t>Kartell Masters Stuhl</t>
+          <t>Werte-Rad</t>
         </is>
       </c>
       <c r="F1090" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1090" s="2" t="inlineStr">
         <is>
@@ -30577,95 +30627,115 @@
     <row r="1091">
       <c r="A1091" s="2" t="inlineStr">
         <is>
+          <t>BA09-04</t>
+        </is>
+      </c>
+      <c r="B1091" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1091" s="2" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1091" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="E1091" s="2" t="inlineStr">
+        <is>
+          <t>USM Haller Tisch</t>
+        </is>
+      </c>
+      <c r="F1091" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1091" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1091" s="2" t="n"/>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="2" t="inlineStr">
+        <is>
+          <t>BA09-05</t>
+        </is>
+      </c>
+      <c r="B1092" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1092" s="2" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1092" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="E1092" s="2" t="inlineStr">
+        <is>
+          <t>Kartell Masters Stuhl</t>
+        </is>
+      </c>
+      <c r="F1092" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1092" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1092" s="2" t="n"/>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="2" t="inlineStr">
+        <is>
           <t>BA09-06</t>
         </is>
       </c>
-      <c r="B1091" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1091" s="2" t="inlineStr">
+      <c r="B1093" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1093" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1091" s="2" t="inlineStr">
+      <c r="D1093" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="E1091" s="2" t="inlineStr">
+      <c r="E1093" s="2" t="inlineStr">
         <is>
           <t>Sitzhocker rund, drehbar auf Rollen</t>
         </is>
       </c>
-      <c r="F1091" s="3" t="n">
+      <c r="F1093" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G1091" s="2" t="inlineStr">
+      <c r="G1093" s="2" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="H1091" s="2" t="n"/>
-    </row>
-    <row r="1092">
-      <c r="A1092" s="4" t="inlineStr">
-        <is>
-          <t>BA09-07</t>
-        </is>
-      </c>
-      <c r="B1092" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1092" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1092" s="4" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="E1092" s="4" t="n"/>
-      <c r="F1092" s="3" t="n"/>
-      <c r="G1092" s="4" t="n"/>
-      <c r="H1092" s="4" t="n"/>
-    </row>
-    <row r="1093">
-      <c r="A1093" s="4" t="inlineStr">
-        <is>
-          <t>BA09-08</t>
-        </is>
-      </c>
-      <c r="B1093" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1093" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1093" s="4" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="E1093" s="4" t="n"/>
-      <c r="F1093" s="3" t="n"/>
-      <c r="G1093" s="4" t="n"/>
-      <c r="H1093" s="4" t="n"/>
+      <c r="H1093" s="2" t="n"/>
     </row>
     <row r="1094">
       <c r="A1094" s="4" t="inlineStr">
         <is>
-          <t>BA09-09</t>
+          <t>BA09-07</t>
         </is>
       </c>
       <c r="B1094" s="4" t="inlineStr">
@@ -30691,7 +30761,7 @@
     <row r="1095">
       <c r="A1095" s="4" t="inlineStr">
         <is>
-          <t>BA09-10</t>
+          <t>BA09-08</t>
         </is>
       </c>
       <c r="B1095" s="4" t="inlineStr">
@@ -30717,7 +30787,7 @@
     <row r="1096">
       <c r="A1096" s="4" t="inlineStr">
         <is>
-          <t>BA09-11</t>
+          <t>BA09-09</t>
         </is>
       </c>
       <c r="B1096" s="4" t="inlineStr">
@@ -30743,7 +30813,7 @@
     <row r="1097">
       <c r="A1097" s="4" t="inlineStr">
         <is>
-          <t>BA09-12</t>
+          <t>BA09-10</t>
         </is>
       </c>
       <c r="B1097" s="4" t="inlineStr">
@@ -30769,7 +30839,7 @@
     <row r="1098">
       <c r="A1098" s="4" t="inlineStr">
         <is>
-          <t>BA09-13</t>
+          <t>BA09-11</t>
         </is>
       </c>
       <c r="B1098" s="4" t="inlineStr">
@@ -30795,7 +30865,7 @@
     <row r="1099">
       <c r="A1099" s="4" t="inlineStr">
         <is>
-          <t>BA09-14</t>
+          <t>BA09-12</t>
         </is>
       </c>
       <c r="B1099" s="4" t="inlineStr">
@@ -30821,7 +30891,7 @@
     <row r="1100">
       <c r="A1100" s="4" t="inlineStr">
         <is>
-          <t>BA09-15</t>
+          <t>BA09-13</t>
         </is>
       </c>
       <c r="B1100" s="4" t="inlineStr">
@@ -30847,7 +30917,7 @@
     <row r="1101">
       <c r="A1101" s="4" t="inlineStr">
         <is>
-          <t>BA09-16</t>
+          <t>BA09-14</t>
         </is>
       </c>
       <c r="B1101" s="4" t="inlineStr">
@@ -30871,81 +30941,61 @@
       <c r="H1101" s="4" t="n"/>
     </row>
     <row r="1102">
-      <c r="A1102" s="2" t="inlineStr">
-        <is>
-          <t>BA10-01</t>
-        </is>
-      </c>
-      <c r="B1102" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1102" s="2" t="inlineStr">
+      <c r="A1102" s="4" t="inlineStr">
+        <is>
+          <t>BA09-15</t>
+        </is>
+      </c>
+      <c r="B1102" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1102" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1102" s="2" t="inlineStr">
-        <is>
-          <t>Ruhe- / Schlafraum</t>
-        </is>
-      </c>
-      <c r="E1102" s="2" t="inlineStr">
-        <is>
-          <t>Glastisch rund mit Chromgestell</t>
-        </is>
-      </c>
-      <c r="F1102" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1102" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1102" s="2" t="n"/>
+      <c r="D1102" s="4" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="E1102" s="4" t="n"/>
+      <c r="F1102" s="3" t="n"/>
+      <c r="G1102" s="4" t="n"/>
+      <c r="H1102" s="4" t="n"/>
     </row>
     <row r="1103">
-      <c r="A1103" s="2" t="inlineStr">
-        <is>
-          <t>BA10-02</t>
-        </is>
-      </c>
-      <c r="B1103" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1103" s="2" t="inlineStr">
+      <c r="A1103" s="4" t="inlineStr">
+        <is>
+          <t>BA09-16</t>
+        </is>
+      </c>
+      <c r="B1103" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1103" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1103" s="2" t="inlineStr">
-        <is>
-          <t>Ruhe- / Schlafraum</t>
-        </is>
-      </c>
-      <c r="E1103" s="2" t="inlineStr">
-        <is>
-          <t>Samtsofa bordeaux, 2-Sitzer</t>
-        </is>
-      </c>
-      <c r="F1103" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1103" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1103" s="2" t="n"/>
+      <c r="D1103" s="4" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="E1103" s="4" t="n"/>
+      <c r="F1103" s="3" t="n"/>
+      <c r="G1103" s="4" t="n"/>
+      <c r="H1103" s="4" t="n"/>
     </row>
     <row r="1104">
       <c r="A1104" s="2" t="inlineStr">
         <is>
-          <t>BA10-03</t>
+          <t>BA10-01</t>
         </is>
       </c>
       <c r="B1104" s="2" t="inlineStr">
@@ -30965,11 +31015,11 @@
       </c>
       <c r="E1104" s="2" t="inlineStr">
         <is>
-          <t>Sessel mit Bezug, weiß lackiert</t>
+          <t>Glastisch rund mit Chromgestell</t>
         </is>
       </c>
       <c r="F1104" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1104" s="2" t="inlineStr">
         <is>
@@ -30981,7 +31031,7 @@
     <row r="1105">
       <c r="A1105" s="2" t="inlineStr">
         <is>
-          <t>BA10-04</t>
+          <t>BA10-02</t>
         </is>
       </c>
       <c r="B1105" s="2" t="inlineStr">
@@ -31001,11 +31051,11 @@
       </c>
       <c r="E1105" s="2" t="inlineStr">
         <is>
-          <t>Hocker grau mit Hairpin-Beinen</t>
+          <t>Samtsofa bordeaux, 2-Sitzer</t>
         </is>
       </c>
       <c r="F1105" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1105" s="2" t="inlineStr">
         <is>
@@ -31017,7 +31067,7 @@
     <row r="1106">
       <c r="A1106" s="2" t="inlineStr">
         <is>
-          <t>BA10-05</t>
+          <t>BA10-03</t>
         </is>
       </c>
       <c r="B1106" s="2" t="inlineStr">
@@ -31037,7 +31087,7 @@
       </c>
       <c r="E1106" s="2" t="inlineStr">
         <is>
-          <t>Ohrensessel grau mit Kufengestell</t>
+          <t>Sessel mit Bezug, weiß lackiert</t>
         </is>
       </c>
       <c r="F1106" s="3" t="n">
@@ -31053,7 +31103,7 @@
     <row r="1107">
       <c r="A1107" s="2" t="inlineStr">
         <is>
-          <t>BA10-06</t>
+          <t>BA10-04</t>
         </is>
       </c>
       <c r="B1107" s="2" t="inlineStr">
@@ -31073,11 +31123,11 @@
       </c>
       <c r="E1107" s="2" t="inlineStr">
         <is>
-          <t>Hocker grau, passend</t>
+          <t>Hocker grau mit Hairpin-Beinen</t>
         </is>
       </c>
       <c r="F1107" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1107" s="2" t="inlineStr">
         <is>
@@ -31089,7 +31139,7 @@
     <row r="1108">
       <c r="A1108" s="2" t="inlineStr">
         <is>
-          <t>BA10-07</t>
+          <t>BA10-05</t>
         </is>
       </c>
       <c r="B1108" s="2" t="inlineStr">
@@ -31109,11 +31159,11 @@
       </c>
       <c r="E1108" s="2" t="inlineStr">
         <is>
-          <t>Beistelltisch rund grau</t>
+          <t>Ohrensessel grau mit Kufengestell</t>
         </is>
       </c>
       <c r="F1108" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1108" s="2" t="inlineStr">
         <is>
@@ -31125,7 +31175,7 @@
     <row r="1109">
       <c r="A1109" s="2" t="inlineStr">
         <is>
-          <t>BA10-08</t>
+          <t>BA10-06</t>
         </is>
       </c>
       <c r="B1109" s="2" t="inlineStr">
@@ -31145,7 +31195,7 @@
       </c>
       <c r="E1109" s="2" t="inlineStr">
         <is>
-          <t>Pendelleuchte Drahtgeflecht</t>
+          <t>Hocker grau, passend</t>
         </is>
       </c>
       <c r="F1109" s="3" t="n">
@@ -31161,7 +31211,7 @@
     <row r="1110">
       <c r="A1110" s="2" t="inlineStr">
         <is>
-          <t>BA10-09</t>
+          <t>BA10-07</t>
         </is>
       </c>
       <c r="B1110" s="2" t="inlineStr">
@@ -31181,7 +31231,7 @@
       </c>
       <c r="E1110" s="2" t="inlineStr">
         <is>
-          <t>Beistelltisch rund, Tablettplatte Birke</t>
+          <t>Beistelltisch rund grau</t>
         </is>
       </c>
       <c r="F1110" s="3" t="n">
@@ -31197,7 +31247,7 @@
     <row r="1111">
       <c r="A1111" s="2" t="inlineStr">
         <is>
-          <t>BA10-10</t>
+          <t>BA10-08</t>
         </is>
       </c>
       <c r="B1111" s="2" t="inlineStr">
@@ -31217,11 +31267,11 @@
       </c>
       <c r="E1111" s="2" t="inlineStr">
         <is>
-          <t>Beistelltisch rund, Tablettplatte schwarz</t>
+          <t>Pendelleuchte Drahtgeflecht</t>
         </is>
       </c>
       <c r="F1111" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1111" s="2" t="inlineStr">
         <is>
@@ -31233,7 +31283,7 @@
     <row r="1112">
       <c r="A1112" s="2" t="inlineStr">
         <is>
-          <t>BA10-11</t>
+          <t>BA10-09</t>
         </is>
       </c>
       <c r="B1112" s="2" t="inlineStr">
@@ -31253,7 +31303,7 @@
       </c>
       <c r="E1112" s="2" t="inlineStr">
         <is>
-          <t>Tisch rund, zweiteilig, weiß</t>
+          <t>Beistelltisch rund, Tablettplatte Birke</t>
         </is>
       </c>
       <c r="F1112" s="3" t="n">
@@ -31267,61 +31317,81 @@
       <c r="H1112" s="2" t="n"/>
     </row>
     <row r="1113">
-      <c r="A1113" s="4" t="inlineStr">
-        <is>
-          <t>BA10-12</t>
-        </is>
-      </c>
-      <c r="B1113" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1113" s="4" t="inlineStr">
+      <c r="A1113" s="2" t="inlineStr">
+        <is>
+          <t>BA10-10</t>
+        </is>
+      </c>
+      <c r="B1113" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1113" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1113" s="4" t="inlineStr">
+      <c r="D1113" s="2" t="inlineStr">
         <is>
           <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
-      <c r="E1113" s="4" t="n"/>
-      <c r="F1113" s="3" t="n"/>
-      <c r="G1113" s="4" t="n"/>
-      <c r="H1113" s="4" t="n"/>
+      <c r="E1113" s="2" t="inlineStr">
+        <is>
+          <t>Beistelltisch rund, Tablettplatte schwarz</t>
+        </is>
+      </c>
+      <c r="F1113" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1113" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1113" s="2" t="n"/>
     </row>
     <row r="1114">
-      <c r="A1114" s="4" t="inlineStr">
-        <is>
-          <t>BA10-13</t>
-        </is>
-      </c>
-      <c r="B1114" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1114" s="4" t="inlineStr">
+      <c r="A1114" s="2" t="inlineStr">
+        <is>
+          <t>BA10-11</t>
+        </is>
+      </c>
+      <c r="B1114" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1114" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1114" s="4" t="inlineStr">
+      <c r="D1114" s="2" t="inlineStr">
         <is>
           <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
-      <c r="E1114" s="4" t="n"/>
-      <c r="F1114" s="3" t="n"/>
-      <c r="G1114" s="4" t="n"/>
-      <c r="H1114" s="4" t="n"/>
+      <c r="E1114" s="2" t="inlineStr">
+        <is>
+          <t>Tisch rund, zweiteilig, weiß</t>
+        </is>
+      </c>
+      <c r="F1114" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1114" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1114" s="2" t="n"/>
     </row>
     <row r="1115">
       <c r="A1115" s="4" t="inlineStr">
         <is>
-          <t>BA10-14</t>
+          <t>BA10-12</t>
         </is>
       </c>
       <c r="B1115" s="4" t="inlineStr">
@@ -31347,7 +31417,7 @@
     <row r="1116">
       <c r="A1116" s="4" t="inlineStr">
         <is>
-          <t>BA10-15</t>
+          <t>BA10-13</t>
         </is>
       </c>
       <c r="B1116" s="4" t="inlineStr">
@@ -31373,7 +31443,7 @@
     <row r="1117">
       <c r="A1117" s="4" t="inlineStr">
         <is>
-          <t>BA10-16</t>
+          <t>BA10-14</t>
         </is>
       </c>
       <c r="B1117" s="4" t="inlineStr">
@@ -31399,7 +31469,7 @@
     <row r="1118">
       <c r="A1118" s="4" t="inlineStr">
         <is>
-          <t>BA10-17</t>
+          <t>BA10-15</t>
         </is>
       </c>
       <c r="B1118" s="4" t="inlineStr">
@@ -31425,7 +31495,7 @@
     <row r="1119">
       <c r="A1119" s="4" t="inlineStr">
         <is>
-          <t>BA10-18</t>
+          <t>BA10-16</t>
         </is>
       </c>
       <c r="B1119" s="4" t="inlineStr">
@@ -31451,7 +31521,7 @@
     <row r="1120">
       <c r="A1120" s="4" t="inlineStr">
         <is>
-          <t>BA10-19</t>
+          <t>BA10-17</t>
         </is>
       </c>
       <c r="B1120" s="4" t="inlineStr">
@@ -31477,7 +31547,7 @@
     <row r="1121">
       <c r="A1121" s="4" t="inlineStr">
         <is>
-          <t>BA10-20</t>
+          <t>BA10-18</t>
         </is>
       </c>
       <c r="B1121" s="4" t="inlineStr">
@@ -31503,7 +31573,7 @@
     <row r="1122">
       <c r="A1122" s="4" t="inlineStr">
         <is>
-          <t>BA10-21</t>
+          <t>BA10-19</t>
         </is>
       </c>
       <c r="B1122" s="4" t="inlineStr">
@@ -31529,7 +31599,7 @@
     <row r="1123">
       <c r="A1123" s="4" t="inlineStr">
         <is>
-          <t>BA11-01</t>
+          <t>BA10-20</t>
         </is>
       </c>
       <c r="B1123" s="4" t="inlineStr">
@@ -31544,7 +31614,7 @@
       </c>
       <c r="D1123" s="4" t="inlineStr">
         <is>
-          <t>WC Kinder</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="E1123" s="4" t="n"/>
@@ -31555,7 +31625,7 @@
     <row r="1124">
       <c r="A1124" s="4" t="inlineStr">
         <is>
-          <t>BA11-02</t>
+          <t>BA10-21</t>
         </is>
       </c>
       <c r="B1124" s="4" t="inlineStr">
@@ -31570,7 +31640,7 @@
       </c>
       <c r="D1124" s="4" t="inlineStr">
         <is>
-          <t>WC Kinder</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="E1124" s="4" t="n"/>
@@ -31581,7 +31651,7 @@
     <row r="1125">
       <c r="A1125" s="4" t="inlineStr">
         <is>
-          <t>BA11-03</t>
+          <t>BA11-01</t>
         </is>
       </c>
       <c r="B1125" s="4" t="inlineStr">
@@ -31607,7 +31677,7 @@
     <row r="1126">
       <c r="A1126" s="4" t="inlineStr">
         <is>
-          <t>BA11-04</t>
+          <t>BA11-02</t>
         </is>
       </c>
       <c r="B1126" s="4" t="inlineStr">
@@ -31633,7 +31703,7 @@
     <row r="1127">
       <c r="A1127" s="4" t="inlineStr">
         <is>
-          <t>BA11-05</t>
+          <t>BA11-03</t>
         </is>
       </c>
       <c r="B1127" s="4" t="inlineStr">
@@ -31659,7 +31729,7 @@
     <row r="1128">
       <c r="A1128" s="4" t="inlineStr">
         <is>
-          <t>BA11-06</t>
+          <t>BA11-04</t>
         </is>
       </c>
       <c r="B1128" s="4" t="inlineStr">
@@ -31685,7 +31755,7 @@
     <row r="1129">
       <c r="A1129" s="4" t="inlineStr">
         <is>
-          <t>BA11-07</t>
+          <t>BA11-05</t>
         </is>
       </c>
       <c r="B1129" s="4" t="inlineStr">
@@ -31711,7 +31781,7 @@
     <row r="1130">
       <c r="A1130" s="4" t="inlineStr">
         <is>
-          <t>BA11-08</t>
+          <t>BA11-06</t>
         </is>
       </c>
       <c r="B1130" s="4" t="inlineStr">
@@ -31737,7 +31807,7 @@
     <row r="1131">
       <c r="A1131" s="4" t="inlineStr">
         <is>
-          <t>BA11-09</t>
+          <t>BA11-07</t>
         </is>
       </c>
       <c r="B1131" s="4" t="inlineStr">
@@ -31763,7 +31833,7 @@
     <row r="1132">
       <c r="A1132" s="4" t="inlineStr">
         <is>
-          <t>BA11-10</t>
+          <t>BA11-08</t>
         </is>
       </c>
       <c r="B1132" s="4" t="inlineStr">
@@ -31789,7 +31859,7 @@
     <row r="1133">
       <c r="A1133" s="4" t="inlineStr">
         <is>
-          <t>BA11-11</t>
+          <t>BA11-09</t>
         </is>
       </c>
       <c r="B1133" s="4" t="inlineStr">
@@ -31815,7 +31885,7 @@
     <row r="1134">
       <c r="A1134" s="4" t="inlineStr">
         <is>
-          <t>BA11-12</t>
+          <t>BA11-10</t>
         </is>
       </c>
       <c r="B1134" s="4" t="inlineStr">
@@ -31841,7 +31911,7 @@
     <row r="1135">
       <c r="A1135" s="4" t="inlineStr">
         <is>
-          <t>BA11-13</t>
+          <t>BA11-11</t>
         </is>
       </c>
       <c r="B1135" s="4" t="inlineStr">
@@ -31867,7 +31937,7 @@
     <row r="1136">
       <c r="A1136" s="4" t="inlineStr">
         <is>
-          <t>BA11-14</t>
+          <t>BA11-12</t>
         </is>
       </c>
       <c r="B1136" s="4" t="inlineStr">
@@ -31893,7 +31963,7 @@
     <row r="1137">
       <c r="A1137" s="4" t="inlineStr">
         <is>
-          <t>BA11-15</t>
+          <t>BA11-13</t>
         </is>
       </c>
       <c r="B1137" s="4" t="inlineStr">
@@ -31917,45 +31987,35 @@
       <c r="H1137" s="4" t="n"/>
     </row>
     <row r="1138">
-      <c r="A1138" s="2" t="inlineStr">
-        <is>
-          <t>BA12-01</t>
-        </is>
-      </c>
-      <c r="B1138" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1138" s="2" t="inlineStr">
+      <c r="A1138" s="4" t="inlineStr">
+        <is>
+          <t>BA11-14</t>
+        </is>
+      </c>
+      <c r="B1138" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1138" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1138" s="2" t="inlineStr">
-        <is>
-          <t>WC Personal</t>
-        </is>
-      </c>
-      <c r="E1138" s="2" t="inlineStr">
-        <is>
-          <t>Ast-Mobile mit Papierwaben</t>
-        </is>
-      </c>
-      <c r="F1138" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1138" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1138" s="2" t="n"/>
+      <c r="D1138" s="4" t="inlineStr">
+        <is>
+          <t>WC Kinder</t>
+        </is>
+      </c>
+      <c r="E1138" s="4" t="n"/>
+      <c r="F1138" s="3" t="n"/>
+      <c r="G1138" s="4" t="n"/>
+      <c r="H1138" s="4" t="n"/>
     </row>
     <row r="1139">
       <c r="A1139" s="4" t="inlineStr">
         <is>
-          <t>BA12-02</t>
+          <t>BA11-15</t>
         </is>
       </c>
       <c r="B1139" s="4" t="inlineStr">
@@ -31970,7 +32030,7 @@
       </c>
       <c r="D1139" s="4" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>WC Kinder</t>
         </is>
       </c>
       <c r="E1139" s="4" t="n"/>
@@ -31979,35 +32039,45 @@
       <c r="H1139" s="4" t="n"/>
     </row>
     <row r="1140">
-      <c r="A1140" s="4" t="inlineStr">
-        <is>
-          <t>BA12-03</t>
-        </is>
-      </c>
-      <c r="B1140" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1140" s="4" t="inlineStr">
+      <c r="A1140" s="2" t="inlineStr">
+        <is>
+          <t>BA12-01</t>
+        </is>
+      </c>
+      <c r="B1140" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1140" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1140" s="4" t="inlineStr">
+      <c r="D1140" s="2" t="inlineStr">
         <is>
           <t>WC Personal</t>
         </is>
       </c>
-      <c r="E1140" s="4" t="n"/>
-      <c r="F1140" s="3" t="n"/>
-      <c r="G1140" s="4" t="n"/>
-      <c r="H1140" s="4" t="n"/>
+      <c r="E1140" s="2" t="inlineStr">
+        <is>
+          <t>Ast-Mobile mit Papierwaben</t>
+        </is>
+      </c>
+      <c r="F1140" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1140" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1140" s="2" t="n"/>
     </row>
     <row r="1141">
       <c r="A1141" s="4" t="inlineStr">
         <is>
-          <t>BA12-04</t>
+          <t>BA12-02</t>
         </is>
       </c>
       <c r="B1141" s="4" t="inlineStr">
@@ -32033,7 +32103,7 @@
     <row r="1142">
       <c r="A1142" s="4" t="inlineStr">
         <is>
-          <t>BA12-05</t>
+          <t>BA12-03</t>
         </is>
       </c>
       <c r="B1142" s="4" t="inlineStr">
@@ -32059,7 +32129,7 @@
     <row r="1143">
       <c r="A1143" s="4" t="inlineStr">
         <is>
-          <t>BA12-06</t>
+          <t>BA12-04</t>
         </is>
       </c>
       <c r="B1143" s="4" t="inlineStr">
@@ -32085,7 +32155,7 @@
     <row r="1144">
       <c r="A1144" s="4" t="inlineStr">
         <is>
-          <t>BA12-07</t>
+          <t>BA12-05</t>
         </is>
       </c>
       <c r="B1144" s="4" t="inlineStr">
@@ -32111,7 +32181,7 @@
     <row r="1145">
       <c r="A1145" s="4" t="inlineStr">
         <is>
-          <t>BA12-08</t>
+          <t>BA12-06</t>
         </is>
       </c>
       <c r="B1145" s="4" t="inlineStr">
@@ -32137,7 +32207,7 @@
     <row r="1146">
       <c r="A1146" s="4" t="inlineStr">
         <is>
-          <t>BA12-09</t>
+          <t>BA12-07</t>
         </is>
       </c>
       <c r="B1146" s="4" t="inlineStr">
@@ -32163,7 +32233,7 @@
     <row r="1147">
       <c r="A1147" s="4" t="inlineStr">
         <is>
-          <t>BA12-10</t>
+          <t>BA12-08</t>
         </is>
       </c>
       <c r="B1147" s="4" t="inlineStr">
@@ -32189,7 +32259,7 @@
     <row r="1148">
       <c r="A1148" s="4" t="inlineStr">
         <is>
-          <t>BA12-11</t>
+          <t>BA12-09</t>
         </is>
       </c>
       <c r="B1148" s="4" t="inlineStr">
@@ -32215,7 +32285,7 @@
     <row r="1149">
       <c r="A1149" s="4" t="inlineStr">
         <is>
-          <t>BA13-01</t>
+          <t>BA12-10</t>
         </is>
       </c>
       <c r="B1149" s="4" t="inlineStr">
@@ -32230,7 +32300,7 @@
       </c>
       <c r="D1149" s="4" t="inlineStr">
         <is>
-          <t>Abstellraum</t>
+          <t>WC Personal</t>
         </is>
       </c>
       <c r="E1149" s="4" t="n"/>
@@ -32241,7 +32311,7 @@
     <row r="1150">
       <c r="A1150" s="4" t="inlineStr">
         <is>
-          <t>BA13-02</t>
+          <t>BA12-11</t>
         </is>
       </c>
       <c r="B1150" s="4" t="inlineStr">
@@ -32256,7 +32326,7 @@
       </c>
       <c r="D1150" s="4" t="inlineStr">
         <is>
-          <t>Abstellraum</t>
+          <t>WC Personal</t>
         </is>
       </c>
       <c r="E1150" s="4" t="n"/>
@@ -32267,7 +32337,7 @@
     <row r="1151">
       <c r="A1151" s="4" t="inlineStr">
         <is>
-          <t>BA13-03</t>
+          <t>BA13-01</t>
         </is>
       </c>
       <c r="B1151" s="4" t="inlineStr">
@@ -32293,7 +32363,7 @@
     <row r="1152">
       <c r="A1152" s="4" t="inlineStr">
         <is>
-          <t>BA13-04</t>
+          <t>BA13-02</t>
         </is>
       </c>
       <c r="B1152" s="4" t="inlineStr">
@@ -32319,7 +32389,7 @@
     <row r="1153">
       <c r="A1153" s="4" t="inlineStr">
         <is>
-          <t>BA13-05</t>
+          <t>BA13-03</t>
         </is>
       </c>
       <c r="B1153" s="4" t="inlineStr">
@@ -32345,7 +32415,7 @@
     <row r="1154">
       <c r="A1154" s="4" t="inlineStr">
         <is>
-          <t>BA13-06</t>
+          <t>BA13-04</t>
         </is>
       </c>
       <c r="B1154" s="4" t="inlineStr">
@@ -32371,7 +32441,7 @@
     <row r="1155">
       <c r="A1155" s="4" t="inlineStr">
         <is>
-          <t>BA13-07</t>
+          <t>BA13-05</t>
         </is>
       </c>
       <c r="B1155" s="4" t="inlineStr">
@@ -32397,7 +32467,7 @@
     <row r="1156">
       <c r="A1156" s="4" t="inlineStr">
         <is>
-          <t>BA13-08</t>
+          <t>BA13-06</t>
         </is>
       </c>
       <c r="B1156" s="4" t="inlineStr">
@@ -32423,7 +32493,7 @@
     <row r="1157">
       <c r="A1157" s="4" t="inlineStr">
         <is>
-          <t>BA13-09</t>
+          <t>BA13-07</t>
         </is>
       </c>
       <c r="B1157" s="4" t="inlineStr">
@@ -32449,7 +32519,7 @@
     <row r="1158">
       <c r="A1158" s="4" t="inlineStr">
         <is>
-          <t>BA13-10</t>
+          <t>BA13-08</t>
         </is>
       </c>
       <c r="B1158" s="4" t="inlineStr">
@@ -32475,7 +32545,7 @@
     <row r="1159">
       <c r="A1159" s="4" t="inlineStr">
         <is>
-          <t>BA13-11</t>
+          <t>BA13-09</t>
         </is>
       </c>
       <c r="B1159" s="4" t="inlineStr">
@@ -32501,7 +32571,7 @@
     <row r="1160">
       <c r="A1160" s="4" t="inlineStr">
         <is>
-          <t>BA13-12</t>
+          <t>BA13-10</t>
         </is>
       </c>
       <c r="B1160" s="4" t="inlineStr">
@@ -32527,7 +32597,7 @@
     <row r="1161">
       <c r="A1161" s="4" t="inlineStr">
         <is>
-          <t>BA13-13</t>
+          <t>BA13-11</t>
         </is>
       </c>
       <c r="B1161" s="4" t="inlineStr">
@@ -32553,7 +32623,7 @@
     <row r="1162">
       <c r="A1162" s="4" t="inlineStr">
         <is>
-          <t>BA13-14</t>
+          <t>BA13-12</t>
         </is>
       </c>
       <c r="B1162" s="4" t="inlineStr">
@@ -32579,7 +32649,7 @@
     <row r="1163">
       <c r="A1163" s="4" t="inlineStr">
         <is>
-          <t>BA13-15</t>
+          <t>BA13-13</t>
         </is>
       </c>
       <c r="B1163" s="4" t="inlineStr">
@@ -32603,81 +32673,61 @@
       <c r="H1163" s="4" t="n"/>
     </row>
     <row r="1164">
-      <c r="A1164" s="2" t="inlineStr">
-        <is>
-          <t>TE01-01</t>
-        </is>
-      </c>
-      <c r="B1164" s="2" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1164" s="2" t="inlineStr">
-        <is>
-          <t>ebenerdig</t>
-        </is>
-      </c>
-      <c r="D1164" s="2" t="inlineStr">
-        <is>
-          <t>Terrasse</t>
-        </is>
-      </c>
-      <c r="E1164" s="2" t="inlineStr">
-        <is>
-          <t>Biohort Freizeitbox weiß (Terrasse)</t>
-        </is>
-      </c>
-      <c r="F1164" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1164" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1164" s="2" t="n"/>
+      <c r="A1164" s="4" t="inlineStr">
+        <is>
+          <t>BA13-14</t>
+        </is>
+      </c>
+      <c r="B1164" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1164" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1164" s="4" t="inlineStr">
+        <is>
+          <t>Abstellraum</t>
+        </is>
+      </c>
+      <c r="E1164" s="4" t="n"/>
+      <c r="F1164" s="3" t="n"/>
+      <c r="G1164" s="4" t="n"/>
+      <c r="H1164" s="4" t="n"/>
     </row>
     <row r="1165">
-      <c r="A1165" s="2" t="inlineStr">
-        <is>
-          <t>TE01-02</t>
-        </is>
-      </c>
-      <c r="B1165" s="2" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1165" s="2" t="inlineStr">
-        <is>
-          <t>ebenerdig</t>
-        </is>
-      </c>
-      <c r="D1165" s="2" t="inlineStr">
-        <is>
-          <t>Terrasse</t>
-        </is>
-      </c>
-      <c r="E1165" s="2" t="inlineStr">
-        <is>
-          <t>Gartentisch mit Granitplatte inkl. Stühle und Schutzhülle</t>
-        </is>
-      </c>
-      <c r="F1165" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1165" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1165" s="2" t="n"/>
+      <c r="A1165" s="4" t="inlineStr">
+        <is>
+          <t>BA13-15</t>
+        </is>
+      </c>
+      <c r="B1165" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1165" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1165" s="4" t="inlineStr">
+        <is>
+          <t>Abstellraum</t>
+        </is>
+      </c>
+      <c r="E1165" s="4" t="n"/>
+      <c r="F1165" s="3" t="n"/>
+      <c r="G1165" s="4" t="n"/>
+      <c r="H1165" s="4" t="n"/>
     </row>
     <row r="1166">
       <c r="A1166" s="2" t="inlineStr">
         <is>
-          <t>TE01-03</t>
+          <t>TE01-01</t>
         </is>
       </c>
       <c r="B1166" s="2" t="inlineStr">
@@ -32697,11 +32747,11 @@
       </c>
       <c r="E1166" s="2" t="inlineStr">
         <is>
-          <t>Textilene-Stapelsessel anthrazit</t>
+          <t>Biohort Freizeitbox weiß (Terrasse)</t>
         </is>
       </c>
       <c r="F1166" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1166" s="2" t="inlineStr">
         <is>
@@ -32713,7 +32763,7 @@
     <row r="1167">
       <c r="A1167" s="2" t="inlineStr">
         <is>
-          <t>TE01-04</t>
+          <t>TE01-02</t>
         </is>
       </c>
       <c r="B1167" s="2" t="inlineStr">
@@ -32733,7 +32783,7 @@
       </c>
       <c r="E1167" s="2" t="inlineStr">
         <is>
-          <t>Weber Genesis Gasgrill</t>
+          <t>Gartentisch mit Granitplatte inkl. Stühle und Schutzhülle</t>
         </is>
       </c>
       <c r="F1167" s="3" t="n">
@@ -32749,95 +32799,115 @@
     <row r="1168">
       <c r="A1168" s="2" t="inlineStr">
         <is>
+          <t>TE01-03</t>
+        </is>
+      </c>
+      <c r="B1168" s="2" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1168" s="2" t="inlineStr">
+        <is>
+          <t>ebenerdig</t>
+        </is>
+      </c>
+      <c r="D1168" s="2" t="inlineStr">
+        <is>
+          <t>Terrasse</t>
+        </is>
+      </c>
+      <c r="E1168" s="2" t="inlineStr">
+        <is>
+          <t>Textilene-Stapelsessel anthrazit</t>
+        </is>
+      </c>
+      <c r="F1168" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1168" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1168" s="2" t="n"/>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="2" t="inlineStr">
+        <is>
+          <t>TE01-04</t>
+        </is>
+      </c>
+      <c r="B1169" s="2" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1169" s="2" t="inlineStr">
+        <is>
+          <t>ebenerdig</t>
+        </is>
+      </c>
+      <c r="D1169" s="2" t="inlineStr">
+        <is>
+          <t>Terrasse</t>
+        </is>
+      </c>
+      <c r="E1169" s="2" t="inlineStr">
+        <is>
+          <t>Weber Genesis Gasgrill</t>
+        </is>
+      </c>
+      <c r="F1169" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1169" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1169" s="2" t="n"/>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="2" t="inlineStr">
+        <is>
           <t>TE01-05</t>
         </is>
       </c>
-      <c r="B1168" s="2" t="inlineStr">
+      <c r="B1170" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1168" s="2" t="inlineStr">
+      <c r="C1170" s="2" t="inlineStr">
         <is>
           <t>ebenerdig</t>
         </is>
       </c>
-      <c r="D1168" s="2" t="inlineStr">
+      <c r="D1170" s="2" t="inlineStr">
         <is>
           <t>Terrasse</t>
         </is>
       </c>
-      <c r="E1168" s="2" t="inlineStr">
+      <c r="E1170" s="2" t="inlineStr">
         <is>
           <t>Sonnenschirm creme</t>
         </is>
       </c>
-      <c r="F1168" s="3" t="n">
+      <c r="F1170" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G1168" s="2" t="inlineStr">
+      <c r="G1170" s="2" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="H1168" s="2" t="n"/>
-    </row>
-    <row r="1169">
-      <c r="A1169" s="4" t="inlineStr">
-        <is>
-          <t>TE01-06</t>
-        </is>
-      </c>
-      <c r="B1169" s="4" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1169" s="4" t="inlineStr">
-        <is>
-          <t>ebenerdig</t>
-        </is>
-      </c>
-      <c r="D1169" s="4" t="inlineStr">
-        <is>
-          <t>Terrasse</t>
-        </is>
-      </c>
-      <c r="E1169" s="4" t="n"/>
-      <c r="F1169" s="3" t="n"/>
-      <c r="G1169" s="4" t="n"/>
-      <c r="H1169" s="4" t="n"/>
-    </row>
-    <row r="1170">
-      <c r="A1170" s="4" t="inlineStr">
-        <is>
-          <t>TE01-07</t>
-        </is>
-      </c>
-      <c r="B1170" s="4" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1170" s="4" t="inlineStr">
-        <is>
-          <t>ebenerdig</t>
-        </is>
-      </c>
-      <c r="D1170" s="4" t="inlineStr">
-        <is>
-          <t>Terrasse</t>
-        </is>
-      </c>
-      <c r="E1170" s="4" t="n"/>
-      <c r="F1170" s="3" t="n"/>
-      <c r="G1170" s="4" t="n"/>
-      <c r="H1170" s="4" t="n"/>
+      <c r="H1170" s="2" t="n"/>
     </row>
     <row r="1171">
       <c r="A1171" s="4" t="inlineStr">
         <is>
-          <t>TE01-08</t>
+          <t>TE01-06</t>
         </is>
       </c>
       <c r="B1171" s="4" t="inlineStr">
@@ -32863,7 +32933,7 @@
     <row r="1172">
       <c r="A1172" s="4" t="inlineStr">
         <is>
-          <t>TE01-09</t>
+          <t>TE01-07</t>
         </is>
       </c>
       <c r="B1172" s="4" t="inlineStr">
@@ -32889,7 +32959,7 @@
     <row r="1173">
       <c r="A1173" s="4" t="inlineStr">
         <is>
-          <t>TE01-10</t>
+          <t>TE01-08</t>
         </is>
       </c>
       <c r="B1173" s="4" t="inlineStr">
@@ -32915,7 +32985,7 @@
     <row r="1174">
       <c r="A1174" s="4" t="inlineStr">
         <is>
-          <t>TE01-11</t>
+          <t>TE01-09</t>
         </is>
       </c>
       <c r="B1174" s="4" t="inlineStr">
@@ -32941,7 +33011,7 @@
     <row r="1175">
       <c r="A1175" s="4" t="inlineStr">
         <is>
-          <t>TE01-12</t>
+          <t>TE01-10</t>
         </is>
       </c>
       <c r="B1175" s="4" t="inlineStr">
@@ -32967,7 +33037,7 @@
     <row r="1176">
       <c r="A1176" s="4" t="inlineStr">
         <is>
-          <t>TE01-13</t>
+          <t>TE01-11</t>
         </is>
       </c>
       <c r="B1176" s="4" t="inlineStr">
@@ -32993,7 +33063,7 @@
     <row r="1177">
       <c r="A1177" s="4" t="inlineStr">
         <is>
-          <t>TE01-14</t>
+          <t>TE01-12</t>
         </is>
       </c>
       <c r="B1177" s="4" t="inlineStr">
@@ -33019,7 +33089,7 @@
     <row r="1178">
       <c r="A1178" s="4" t="inlineStr">
         <is>
-          <t>TE01-15</t>
+          <t>TE01-13</t>
         </is>
       </c>
       <c r="B1178" s="4" t="inlineStr">
@@ -33045,7 +33115,7 @@
     <row r="1179">
       <c r="A1179" s="4" t="inlineStr">
         <is>
-          <t>TE01-16</t>
+          <t>TE01-14</t>
         </is>
       </c>
       <c r="B1179" s="4" t="inlineStr">
@@ -33071,7 +33141,7 @@
     <row r="1180">
       <c r="A1180" s="4" t="inlineStr">
         <is>
-          <t>TE01-17</t>
+          <t>TE01-15</t>
         </is>
       </c>
       <c r="B1180" s="4" t="inlineStr">
@@ -33097,7 +33167,7 @@
     <row r="1181">
       <c r="A1181" s="4" t="inlineStr">
         <is>
-          <t>TE01-18</t>
+          <t>TE01-16</t>
         </is>
       </c>
       <c r="B1181" s="4" t="inlineStr">
@@ -33123,7 +33193,7 @@
     <row r="1182">
       <c r="A1182" s="4" t="inlineStr">
         <is>
-          <t>TE01-19</t>
+          <t>TE01-17</t>
         </is>
       </c>
       <c r="B1182" s="4" t="inlineStr">
@@ -33149,7 +33219,7 @@
     <row r="1183">
       <c r="A1183" s="4" t="inlineStr">
         <is>
-          <t>TE01-20</t>
+          <t>TE01-18</t>
         </is>
       </c>
       <c r="B1183" s="4" t="inlineStr">
@@ -33175,7 +33245,7 @@
     <row r="1184">
       <c r="A1184" s="4" t="inlineStr">
         <is>
-          <t>TE01-21</t>
+          <t>TE01-19</t>
         </is>
       </c>
       <c r="B1184" s="4" t="inlineStr">
@@ -33201,7 +33271,7 @@
     <row r="1185">
       <c r="A1185" s="4" t="inlineStr">
         <is>
-          <t>TE01-22</t>
+          <t>TE01-20</t>
         </is>
       </c>
       <c r="B1185" s="4" t="inlineStr">
@@ -33227,7 +33297,7 @@
     <row r="1186">
       <c r="A1186" s="4" t="inlineStr">
         <is>
-          <t>TE01-23</t>
+          <t>TE01-21</t>
         </is>
       </c>
       <c r="B1186" s="4" t="inlineStr">
@@ -33253,7 +33323,7 @@
     <row r="1187">
       <c r="A1187" s="4" t="inlineStr">
         <is>
-          <t>TE01-24</t>
+          <t>TE01-22</t>
         </is>
       </c>
       <c r="B1187" s="4" t="inlineStr">
@@ -33279,7 +33349,7 @@
     <row r="1188">
       <c r="A1188" s="4" t="inlineStr">
         <is>
-          <t>TE01-25</t>
+          <t>TE01-23</t>
         </is>
       </c>
       <c r="B1188" s="4" t="inlineStr">
@@ -33305,7 +33375,7 @@
     <row r="1189">
       <c r="A1189" s="4" t="inlineStr">
         <is>
-          <t>TE01-26</t>
+          <t>TE01-24</t>
         </is>
       </c>
       <c r="B1189" s="4" t="inlineStr">
@@ -33331,7 +33401,7 @@
     <row r="1190">
       <c r="A1190" s="4" t="inlineStr">
         <is>
-          <t>TE01-27</t>
+          <t>TE01-25</t>
         </is>
       </c>
       <c r="B1190" s="4" t="inlineStr">
@@ -33357,7 +33427,7 @@
     <row r="1191">
       <c r="A1191" s="4" t="inlineStr">
         <is>
-          <t>TE01-28</t>
+          <t>TE01-26</t>
         </is>
       </c>
       <c r="B1191" s="4" t="inlineStr">
@@ -33383,7 +33453,7 @@
     <row r="1192">
       <c r="A1192" s="4" t="inlineStr">
         <is>
-          <t>TE01-29</t>
+          <t>TE01-27</t>
         </is>
       </c>
       <c r="B1192" s="4" t="inlineStr">
@@ -33409,7 +33479,7 @@
     <row r="1193">
       <c r="A1193" s="4" t="inlineStr">
         <is>
-          <t>TE01-30</t>
+          <t>TE01-28</t>
         </is>
       </c>
       <c r="B1193" s="4" t="inlineStr">
@@ -33435,7 +33505,7 @@
     <row r="1194">
       <c r="A1194" s="4" t="inlineStr">
         <is>
-          <t>TE01-31</t>
+          <t>TE01-29</t>
         </is>
       </c>
       <c r="B1194" s="4" t="inlineStr">
@@ -33461,7 +33531,7 @@
     <row r="1195">
       <c r="A1195" s="4" t="inlineStr">
         <is>
-          <t>TE01-32</t>
+          <t>TE01-30</t>
         </is>
       </c>
       <c r="B1195" s="4" t="inlineStr">
@@ -33487,7 +33557,7 @@
     <row r="1196">
       <c r="A1196" s="4" t="inlineStr">
         <is>
-          <t>TE01-33</t>
+          <t>TE01-31</t>
         </is>
       </c>
       <c r="B1196" s="4" t="inlineStr">
@@ -33513,7 +33583,7 @@
     <row r="1197">
       <c r="A1197" s="4" t="inlineStr">
         <is>
-          <t>TE01-34</t>
+          <t>TE01-32</t>
         </is>
       </c>
       <c r="B1197" s="4" t="inlineStr">
@@ -33539,7 +33609,7 @@
     <row r="1198">
       <c r="A1198" s="4" t="inlineStr">
         <is>
-          <t>TE01-35</t>
+          <t>TE01-33</t>
         </is>
       </c>
       <c r="B1198" s="4" t="inlineStr">
@@ -33565,7 +33635,7 @@
     <row r="1199">
       <c r="A1199" s="4" t="inlineStr">
         <is>
-          <t>TE01-36</t>
+          <t>TE01-34</t>
         </is>
       </c>
       <c r="B1199" s="4" t="inlineStr">
@@ -33591,7 +33661,7 @@
     <row r="1200">
       <c r="A1200" s="4" t="inlineStr">
         <is>
-          <t>TE01-37</t>
+          <t>TE01-35</t>
         </is>
       </c>
       <c r="B1200" s="4" t="inlineStr">
@@ -33617,7 +33687,7 @@
     <row r="1201">
       <c r="A1201" s="4" t="inlineStr">
         <is>
-          <t>TE01-38</t>
+          <t>TE01-36</t>
         </is>
       </c>
       <c r="B1201" s="4" t="inlineStr">
@@ -33643,7 +33713,7 @@
     <row r="1202">
       <c r="A1202" s="4" t="inlineStr">
         <is>
-          <t>TE01-39</t>
+          <t>TE01-37</t>
         </is>
       </c>
       <c r="B1202" s="4" t="inlineStr">
@@ -33669,7 +33739,7 @@
     <row r="1203">
       <c r="A1203" s="4" t="inlineStr">
         <is>
-          <t>TE01-40</t>
+          <t>TE01-38</t>
         </is>
       </c>
       <c r="B1203" s="4" t="inlineStr">
@@ -33693,81 +33763,61 @@
       <c r="H1203" s="4" t="n"/>
     </row>
     <row r="1204">
-      <c r="A1204" s="2" t="inlineStr">
-        <is>
-          <t>TE02-01</t>
-        </is>
-      </c>
-      <c r="B1204" s="2" t="inlineStr">
+      <c r="A1204" s="4" t="inlineStr">
+        <is>
+          <t>TE01-39</t>
+        </is>
+      </c>
+      <c r="B1204" s="4" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1204" s="2" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1204" s="2" t="inlineStr">
-        <is>
-          <t>Dachterrasse</t>
-        </is>
-      </c>
-      <c r="E1204" s="2" t="inlineStr">
-        <is>
-          <t>Pflanzkübel Plastik weiß</t>
-        </is>
-      </c>
-      <c r="F1204" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G1204" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1204" s="2" t="n"/>
+      <c r="C1204" s="4" t="inlineStr">
+        <is>
+          <t>ebenerdig</t>
+        </is>
+      </c>
+      <c r="D1204" s="4" t="inlineStr">
+        <is>
+          <t>Terrasse</t>
+        </is>
+      </c>
+      <c r="E1204" s="4" t="n"/>
+      <c r="F1204" s="3" t="n"/>
+      <c r="G1204" s="4" t="n"/>
+      <c r="H1204" s="4" t="n"/>
     </row>
     <row r="1205">
-      <c r="A1205" s="2" t="inlineStr">
-        <is>
-          <t>TE02-02</t>
-        </is>
-      </c>
-      <c r="B1205" s="2" t="inlineStr">
+      <c r="A1205" s="4" t="inlineStr">
+        <is>
+          <t>TE01-40</t>
+        </is>
+      </c>
+      <c r="B1205" s="4" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1205" s="2" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1205" s="2" t="inlineStr">
-        <is>
-          <t>Dachterrasse</t>
-        </is>
-      </c>
-      <c r="E1205" s="2" t="inlineStr">
-        <is>
-          <t>Gartenstuhl Kunststoff anthrazit</t>
-        </is>
-      </c>
-      <c r="F1205" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G1205" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1205" s="2" t="n"/>
+      <c r="C1205" s="4" t="inlineStr">
+        <is>
+          <t>ebenerdig</t>
+        </is>
+      </c>
+      <c r="D1205" s="4" t="inlineStr">
+        <is>
+          <t>Terrasse</t>
+        </is>
+      </c>
+      <c r="E1205" s="4" t="n"/>
+      <c r="F1205" s="3" t="n"/>
+      <c r="G1205" s="4" t="n"/>
+      <c r="H1205" s="4" t="n"/>
     </row>
     <row r="1206">
       <c r="A1206" s="2" t="inlineStr">
         <is>
-          <t>TE02-03</t>
+          <t>TE02-01</t>
         </is>
       </c>
       <c r="B1206" s="2" t="inlineStr">
@@ -33787,11 +33837,11 @@
       </c>
       <c r="E1206" s="2" t="inlineStr">
         <is>
-          <t>Gartentisch anthrazit</t>
+          <t>Pflanzkübel Plastik weiß</t>
         </is>
       </c>
       <c r="F1206" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1206" s="2" t="inlineStr">
         <is>
@@ -33803,7 +33853,7 @@
     <row r="1207">
       <c r="A1207" s="2" t="inlineStr">
         <is>
-          <t>TE02-04</t>
+          <t>TE02-02</t>
         </is>
       </c>
       <c r="B1207" s="2" t="inlineStr">
@@ -33823,15 +33873,15 @@
       </c>
       <c r="E1207" s="2" t="inlineStr">
         <is>
-          <t>Teak-Klapptisch rund</t>
+          <t>Gartenstuhl Kunststoff anthrazit</t>
         </is>
       </c>
       <c r="F1207" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1207" s="2" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Stück</t>
         </is>
       </c>
       <c r="H1207" s="2" t="n"/>
@@ -33839,7 +33889,7 @@
     <row r="1208">
       <c r="A1208" s="2" t="inlineStr">
         <is>
-          <t>TE02-05</t>
+          <t>TE02-03</t>
         </is>
       </c>
       <c r="B1208" s="2" t="inlineStr">
@@ -33859,11 +33909,11 @@
       </c>
       <c r="E1208" s="2" t="inlineStr">
         <is>
-          <t>Pflanzkübel grau, groß</t>
+          <t>Gartentisch anthrazit</t>
         </is>
       </c>
       <c r="F1208" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1208" s="2" t="inlineStr">
         <is>
@@ -33875,7 +33925,7 @@
     <row r="1209">
       <c r="A1209" s="2" t="inlineStr">
         <is>
-          <t>TE02-06</t>
+          <t>TE02-04</t>
         </is>
       </c>
       <c r="B1209" s="2" t="inlineStr">
@@ -33895,7 +33945,7 @@
       </c>
       <c r="E1209" s="2" t="inlineStr">
         <is>
-          <t>Holzstern mit Lichterkette</t>
+          <t>Teak-Klapptisch rund</t>
         </is>
       </c>
       <c r="F1209" s="3" t="n">
@@ -33903,67 +33953,87 @@
       </c>
       <c r="G1209" s="2" t="inlineStr">
         <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="H1209" s="2" t="n"/>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="2" t="inlineStr">
+        <is>
+          <t>TE02-05</t>
+        </is>
+      </c>
+      <c r="B1210" s="2" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1210" s="2" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1210" s="2" t="inlineStr">
+        <is>
+          <t>Dachterrasse</t>
+        </is>
+      </c>
+      <c r="E1210" s="2" t="inlineStr">
+        <is>
+          <t>Pflanzkübel grau, groß</t>
+        </is>
+      </c>
+      <c r="F1210" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1210" s="2" t="inlineStr">
+        <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="H1209" s="2" t="n"/>
-    </row>
-    <row r="1210">
-      <c r="A1210" s="4" t="inlineStr">
-        <is>
-          <t>TE02-07</t>
-        </is>
-      </c>
-      <c r="B1210" s="4" t="inlineStr">
+      <c r="H1210" s="2" t="n"/>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="2" t="inlineStr">
+        <is>
+          <t>TE02-06</t>
+        </is>
+      </c>
+      <c r="B1211" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1210" s="4" t="inlineStr">
+      <c r="C1211" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1210" s="4" t="inlineStr">
+      <c r="D1211" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1210" s="4" t="n"/>
-      <c r="F1210" s="3" t="n"/>
-      <c r="G1210" s="4" t="n"/>
-      <c r="H1210" s="4" t="n"/>
-    </row>
-    <row r="1211">
-      <c r="A1211" s="4" t="inlineStr">
-        <is>
-          <t>TE02-08</t>
-        </is>
-      </c>
-      <c r="B1211" s="4" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1211" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1211" s="4" t="inlineStr">
-        <is>
-          <t>Dachterrasse</t>
-        </is>
-      </c>
-      <c r="E1211" s="4" t="n"/>
-      <c r="F1211" s="3" t="n"/>
-      <c r="G1211" s="4" t="n"/>
-      <c r="H1211" s="4" t="n"/>
+      <c r="E1211" s="2" t="inlineStr">
+        <is>
+          <t>Holzstern mit Lichterkette</t>
+        </is>
+      </c>
+      <c r="F1211" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1211" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1211" s="2" t="n"/>
     </row>
     <row r="1212">
       <c r="A1212" s="4" t="inlineStr">
         <is>
-          <t>TE02-09</t>
+          <t>TE02-07</t>
         </is>
       </c>
       <c r="B1212" s="4" t="inlineStr">
@@ -33989,7 +34059,7 @@
     <row r="1213">
       <c r="A1213" s="4" t="inlineStr">
         <is>
-          <t>TE02-10</t>
+          <t>TE02-08</t>
         </is>
       </c>
       <c r="B1213" s="4" t="inlineStr">
@@ -34015,7 +34085,7 @@
     <row r="1214">
       <c r="A1214" s="4" t="inlineStr">
         <is>
-          <t>TE02-11</t>
+          <t>TE02-09</t>
         </is>
       </c>
       <c r="B1214" s="4" t="inlineStr">
@@ -34041,7 +34111,7 @@
     <row r="1215">
       <c r="A1215" s="4" t="inlineStr">
         <is>
-          <t>TE02-12</t>
+          <t>TE02-10</t>
         </is>
       </c>
       <c r="B1215" s="4" t="inlineStr">
@@ -34067,7 +34137,7 @@
     <row r="1216">
       <c r="A1216" s="4" t="inlineStr">
         <is>
-          <t>TE02-13</t>
+          <t>TE02-11</t>
         </is>
       </c>
       <c r="B1216" s="4" t="inlineStr">
@@ -34093,7 +34163,7 @@
     <row r="1217">
       <c r="A1217" s="4" t="inlineStr">
         <is>
-          <t>TE02-14</t>
+          <t>TE02-12</t>
         </is>
       </c>
       <c r="B1217" s="4" t="inlineStr">
@@ -34119,7 +34189,7 @@
     <row r="1218">
       <c r="A1218" s="4" t="inlineStr">
         <is>
-          <t>TE02-15</t>
+          <t>TE02-13</t>
         </is>
       </c>
       <c r="B1218" s="4" t="inlineStr">
@@ -34145,7 +34215,7 @@
     <row r="1219">
       <c r="A1219" s="4" t="inlineStr">
         <is>
-          <t>TE02-16</t>
+          <t>TE02-14</t>
         </is>
       </c>
       <c r="B1219" s="4" t="inlineStr">
@@ -34171,7 +34241,7 @@
     <row r="1220">
       <c r="A1220" s="4" t="inlineStr">
         <is>
-          <t>TE02-17</t>
+          <t>TE02-15</t>
         </is>
       </c>
       <c r="B1220" s="4" t="inlineStr">
@@ -34197,7 +34267,7 @@
     <row r="1221">
       <c r="A1221" s="4" t="inlineStr">
         <is>
-          <t>TE02-18</t>
+          <t>TE02-16</t>
         </is>
       </c>
       <c r="B1221" s="4" t="inlineStr">
@@ -34223,7 +34293,7 @@
     <row r="1222">
       <c r="A1222" s="4" t="inlineStr">
         <is>
-          <t>TE02-19</t>
+          <t>TE02-17</t>
         </is>
       </c>
       <c r="B1222" s="4" t="inlineStr">
@@ -34249,7 +34319,7 @@
     <row r="1223">
       <c r="A1223" s="4" t="inlineStr">
         <is>
-          <t>TE02-20</t>
+          <t>TE02-18</t>
         </is>
       </c>
       <c r="B1223" s="4" t="inlineStr">
@@ -34275,7 +34345,7 @@
     <row r="1224">
       <c r="A1224" s="4" t="inlineStr">
         <is>
-          <t>TE02-21</t>
+          <t>TE02-19</t>
         </is>
       </c>
       <c r="B1224" s="4" t="inlineStr">
@@ -34301,7 +34371,7 @@
     <row r="1225">
       <c r="A1225" s="4" t="inlineStr">
         <is>
-          <t>TE02-22</t>
+          <t>TE02-20</t>
         </is>
       </c>
       <c r="B1225" s="4" t="inlineStr">
@@ -34327,7 +34397,7 @@
     <row r="1226">
       <c r="A1226" s="4" t="inlineStr">
         <is>
-          <t>TE02-23</t>
+          <t>TE02-21</t>
         </is>
       </c>
       <c r="B1226" s="4" t="inlineStr">
@@ -34353,7 +34423,7 @@
     <row r="1227">
       <c r="A1227" s="4" t="inlineStr">
         <is>
-          <t>TE02-24</t>
+          <t>TE02-22</t>
         </is>
       </c>
       <c r="B1227" s="4" t="inlineStr">
@@ -34379,7 +34449,7 @@
     <row r="1228">
       <c r="A1228" s="4" t="inlineStr">
         <is>
-          <t>TE02-25</t>
+          <t>TE02-23</t>
         </is>
       </c>
       <c r="B1228" s="4" t="inlineStr">
@@ -34405,7 +34475,7 @@
     <row r="1229">
       <c r="A1229" s="4" t="inlineStr">
         <is>
-          <t>TE02-26</t>
+          <t>TE02-24</t>
         </is>
       </c>
       <c r="B1229" s="4" t="inlineStr">
@@ -34431,7 +34501,7 @@
     <row r="1230">
       <c r="A1230" s="4" t="inlineStr">
         <is>
-          <t>TE02-27</t>
+          <t>TE02-25</t>
         </is>
       </c>
       <c r="B1230" s="4" t="inlineStr">
@@ -34457,7 +34527,7 @@
     <row r="1231">
       <c r="A1231" s="4" t="inlineStr">
         <is>
-          <t>TE02-28</t>
+          <t>TE02-26</t>
         </is>
       </c>
       <c r="B1231" s="4" t="inlineStr">
@@ -34483,7 +34553,7 @@
     <row r="1232">
       <c r="A1232" s="4" t="inlineStr">
         <is>
-          <t>TE02-29</t>
+          <t>TE02-27</t>
         </is>
       </c>
       <c r="B1232" s="4" t="inlineStr">
@@ -34509,7 +34579,7 @@
     <row r="1233">
       <c r="A1233" s="4" t="inlineStr">
         <is>
-          <t>TE02-30</t>
+          <t>TE02-28</t>
         </is>
       </c>
       <c r="B1233" s="4" t="inlineStr">
@@ -34535,7 +34605,7 @@
     <row r="1234">
       <c r="A1234" s="4" t="inlineStr">
         <is>
-          <t>TE02-31</t>
+          <t>TE02-29</t>
         </is>
       </c>
       <c r="B1234" s="4" t="inlineStr">
@@ -34561,7 +34631,7 @@
     <row r="1235">
       <c r="A1235" s="4" t="inlineStr">
         <is>
-          <t>TE02-32</t>
+          <t>TE02-30</t>
         </is>
       </c>
       <c r="B1235" s="4" t="inlineStr">
@@ -34587,7 +34657,7 @@
     <row r="1236">
       <c r="A1236" s="4" t="inlineStr">
         <is>
-          <t>TE02-33</t>
+          <t>TE02-31</t>
         </is>
       </c>
       <c r="B1236" s="4" t="inlineStr">
@@ -34613,7 +34683,7 @@
     <row r="1237">
       <c r="A1237" s="4" t="inlineStr">
         <is>
-          <t>TE02-34</t>
+          <t>TE02-32</t>
         </is>
       </c>
       <c r="B1237" s="4" t="inlineStr">
@@ -34639,7 +34709,7 @@
     <row r="1238">
       <c r="A1238" s="4" t="inlineStr">
         <is>
-          <t>TE02-35</t>
+          <t>TE02-33</t>
         </is>
       </c>
       <c r="B1238" s="4" t="inlineStr">
@@ -34665,7 +34735,7 @@
     <row r="1239">
       <c r="A1239" s="4" t="inlineStr">
         <is>
-          <t>TE02-36</t>
+          <t>TE02-34</t>
         </is>
       </c>
       <c r="B1239" s="4" t="inlineStr">
@@ -34691,7 +34761,7 @@
     <row r="1240">
       <c r="A1240" s="4" t="inlineStr">
         <is>
-          <t>TE02-37</t>
+          <t>TE02-35</t>
         </is>
       </c>
       <c r="B1240" s="4" t="inlineStr">
@@ -34717,7 +34787,7 @@
     <row r="1241">
       <c r="A1241" s="4" t="inlineStr">
         <is>
-          <t>TE02-38</t>
+          <t>TE02-36</t>
         </is>
       </c>
       <c r="B1241" s="4" t="inlineStr">
@@ -34743,7 +34813,7 @@
     <row r="1242">
       <c r="A1242" s="4" t="inlineStr">
         <is>
-          <t>TE02-39</t>
+          <t>TE02-37</t>
         </is>
       </c>
       <c r="B1242" s="4" t="inlineStr">
@@ -34769,7 +34839,7 @@
     <row r="1243">
       <c r="A1243" s="4" t="inlineStr">
         <is>
-          <t>TE02-40</t>
+          <t>TE02-38</t>
         </is>
       </c>
       <c r="B1243" s="4" t="inlineStr">
@@ -34793,41 +34863,35 @@
       <c r="H1243" s="4" t="n"/>
     </row>
     <row r="1244">
-      <c r="A1244" s="2" t="inlineStr">
-        <is>
-          <t>GA01-01</t>
-        </is>
-      </c>
-      <c r="B1244" s="2" t="inlineStr">
+      <c r="A1244" s="4" t="inlineStr">
+        <is>
+          <t>TE02-39</t>
+        </is>
+      </c>
+      <c r="B1244" s="4" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1244" s="2" t="inlineStr"/>
-      <c r="D1244" s="2" t="inlineStr">
-        <is>
-          <t>Gartenanlage</t>
-        </is>
-      </c>
-      <c r="E1244" s="2" t="inlineStr">
-        <is>
-          <t>Holz-Wellenliege, Doppelliege</t>
-        </is>
-      </c>
-      <c r="F1244" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1244" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1244" s="2" t="n"/>
+      <c r="C1244" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1244" s="4" t="inlineStr">
+        <is>
+          <t>Dachterrasse</t>
+        </is>
+      </c>
+      <c r="E1244" s="4" t="n"/>
+      <c r="F1244" s="3" t="n"/>
+      <c r="G1244" s="4" t="n"/>
+      <c r="H1244" s="4" t="n"/>
     </row>
     <row r="1245">
       <c r="A1245" s="4" t="inlineStr">
         <is>
-          <t>GA01-02</t>
+          <t>TE02-40</t>
         </is>
       </c>
       <c r="B1245" s="4" t="inlineStr">
@@ -34835,10 +34899,14 @@
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1245" s="4" t="inlineStr"/>
+      <c r="C1245" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
       <c r="D1245" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Dachterrasse</t>
         </is>
       </c>
       <c r="E1245" s="4" t="n"/>
@@ -34847,31 +34915,41 @@
       <c r="H1245" s="4" t="n"/>
     </row>
     <row r="1246">
-      <c r="A1246" s="4" t="inlineStr">
-        <is>
-          <t>GA01-03</t>
-        </is>
-      </c>
-      <c r="B1246" s="4" t="inlineStr">
+      <c r="A1246" s="2" t="inlineStr">
+        <is>
+          <t>GA01-01</t>
+        </is>
+      </c>
+      <c r="B1246" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1246" s="4" t="inlineStr"/>
-      <c r="D1246" s="4" t="inlineStr">
+      <c r="C1246" s="2" t="inlineStr"/>
+      <c r="D1246" s="2" t="inlineStr">
         <is>
           <t>Gartenanlage</t>
         </is>
       </c>
-      <c r="E1246" s="4" t="n"/>
-      <c r="F1246" s="3" t="n"/>
-      <c r="G1246" s="4" t="n"/>
-      <c r="H1246" s="4" t="n"/>
+      <c r="E1246" s="2" t="inlineStr">
+        <is>
+          <t>Holz-Wellenliege, Doppelliege</t>
+        </is>
+      </c>
+      <c r="F1246" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1246" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1246" s="2" t="n"/>
     </row>
     <row r="1247">
       <c r="A1247" s="4" t="inlineStr">
         <is>
-          <t>GA01-04</t>
+          <t>GA01-02</t>
         </is>
       </c>
       <c r="B1247" s="4" t="inlineStr">
@@ -34893,7 +34971,7 @@
     <row r="1248">
       <c r="A1248" s="4" t="inlineStr">
         <is>
-          <t>GA01-05</t>
+          <t>GA01-03</t>
         </is>
       </c>
       <c r="B1248" s="4" t="inlineStr">
@@ -34915,7 +34993,7 @@
     <row r="1249">
       <c r="A1249" s="4" t="inlineStr">
         <is>
-          <t>GA01-06</t>
+          <t>GA01-04</t>
         </is>
       </c>
       <c r="B1249" s="4" t="inlineStr">
@@ -34937,7 +35015,7 @@
     <row r="1250">
       <c r="A1250" s="4" t="inlineStr">
         <is>
-          <t>GA01-07</t>
+          <t>GA01-05</t>
         </is>
       </c>
       <c r="B1250" s="4" t="inlineStr">
@@ -34959,7 +35037,7 @@
     <row r="1251">
       <c r="A1251" s="4" t="inlineStr">
         <is>
-          <t>GA01-08</t>
+          <t>GA01-06</t>
         </is>
       </c>
       <c r="B1251" s="4" t="inlineStr">
@@ -34981,7 +35059,7 @@
     <row r="1252">
       <c r="A1252" s="4" t="inlineStr">
         <is>
-          <t>GA01-09</t>
+          <t>GA01-07</t>
         </is>
       </c>
       <c r="B1252" s="4" t="inlineStr">
@@ -35003,7 +35081,7 @@
     <row r="1253">
       <c r="A1253" s="4" t="inlineStr">
         <is>
-          <t>GA01-10</t>
+          <t>GA01-08</t>
         </is>
       </c>
       <c r="B1253" s="4" t="inlineStr">
@@ -35025,7 +35103,7 @@
     <row r="1254">
       <c r="A1254" s="4" t="inlineStr">
         <is>
-          <t>GA01-11</t>
+          <t>GA01-09</t>
         </is>
       </c>
       <c r="B1254" s="4" t="inlineStr">
@@ -35047,7 +35125,7 @@
     <row r="1255">
       <c r="A1255" s="4" t="inlineStr">
         <is>
-          <t>GA01-12</t>
+          <t>GA01-10</t>
         </is>
       </c>
       <c r="B1255" s="4" t="inlineStr">
@@ -35069,7 +35147,7 @@
     <row r="1256">
       <c r="A1256" s="4" t="inlineStr">
         <is>
-          <t>GA01-13</t>
+          <t>GA01-11</t>
         </is>
       </c>
       <c r="B1256" s="4" t="inlineStr">
@@ -35091,7 +35169,7 @@
     <row r="1257">
       <c r="A1257" s="4" t="inlineStr">
         <is>
-          <t>GA01-14</t>
+          <t>GA01-12</t>
         </is>
       </c>
       <c r="B1257" s="4" t="inlineStr">
@@ -35113,7 +35191,7 @@
     <row r="1258">
       <c r="A1258" s="4" t="inlineStr">
         <is>
-          <t>GA01-15</t>
+          <t>GA01-13</t>
         </is>
       </c>
       <c r="B1258" s="4" t="inlineStr">
@@ -35135,7 +35213,7 @@
     <row r="1259">
       <c r="A1259" s="4" t="inlineStr">
         <is>
-          <t>GA01-16</t>
+          <t>GA01-14</t>
         </is>
       </c>
       <c r="B1259" s="4" t="inlineStr">
@@ -35157,7 +35235,7 @@
     <row r="1260">
       <c r="A1260" s="4" t="inlineStr">
         <is>
-          <t>GA01-17</t>
+          <t>GA01-15</t>
         </is>
       </c>
       <c r="B1260" s="4" t="inlineStr">
@@ -35179,7 +35257,7 @@
     <row r="1261">
       <c r="A1261" s="4" t="inlineStr">
         <is>
-          <t>GA01-18</t>
+          <t>GA01-16</t>
         </is>
       </c>
       <c r="B1261" s="4" t="inlineStr">
@@ -35201,7 +35279,7 @@
     <row r="1262">
       <c r="A1262" s="4" t="inlineStr">
         <is>
-          <t>GA01-19</t>
+          <t>GA01-17</t>
         </is>
       </c>
       <c r="B1262" s="4" t="inlineStr">
@@ -35223,7 +35301,7 @@
     <row r="1263">
       <c r="A1263" s="4" t="inlineStr">
         <is>
-          <t>GA01-20</t>
+          <t>GA01-18</t>
         </is>
       </c>
       <c r="B1263" s="4" t="inlineStr">
@@ -35245,7 +35323,7 @@
     <row r="1264">
       <c r="A1264" s="4" t="inlineStr">
         <is>
-          <t>GA01-21</t>
+          <t>GA01-19</t>
         </is>
       </c>
       <c r="B1264" s="4" t="inlineStr">
@@ -35267,7 +35345,7 @@
     <row r="1265">
       <c r="A1265" s="4" t="inlineStr">
         <is>
-          <t>GA01-22</t>
+          <t>GA01-20</t>
         </is>
       </c>
       <c r="B1265" s="4" t="inlineStr">
@@ -35289,7 +35367,7 @@
     <row r="1266">
       <c r="A1266" s="4" t="inlineStr">
         <is>
-          <t>GA01-23</t>
+          <t>GA01-21</t>
         </is>
       </c>
       <c r="B1266" s="4" t="inlineStr">
@@ -35311,7 +35389,7 @@
     <row r="1267">
       <c r="A1267" s="4" t="inlineStr">
         <is>
-          <t>GA01-24</t>
+          <t>GA01-22</t>
         </is>
       </c>
       <c r="B1267" s="4" t="inlineStr">
@@ -35333,7 +35411,7 @@
     <row r="1268">
       <c r="A1268" s="4" t="inlineStr">
         <is>
-          <t>GA01-25</t>
+          <t>GA01-23</t>
         </is>
       </c>
       <c r="B1268" s="4" t="inlineStr">
@@ -35355,7 +35433,7 @@
     <row r="1269">
       <c r="A1269" s="4" t="inlineStr">
         <is>
-          <t>GA01-26</t>
+          <t>GA01-24</t>
         </is>
       </c>
       <c r="B1269" s="4" t="inlineStr">
@@ -35377,7 +35455,7 @@
     <row r="1270">
       <c r="A1270" s="4" t="inlineStr">
         <is>
-          <t>GA01-27</t>
+          <t>GA01-25</t>
         </is>
       </c>
       <c r="B1270" s="4" t="inlineStr">
@@ -35399,7 +35477,7 @@
     <row r="1271">
       <c r="A1271" s="4" t="inlineStr">
         <is>
-          <t>GA01-28</t>
+          <t>GA01-26</t>
         </is>
       </c>
       <c r="B1271" s="4" t="inlineStr">
@@ -35421,7 +35499,7 @@
     <row r="1272">
       <c r="A1272" s="4" t="inlineStr">
         <is>
-          <t>GA01-29</t>
+          <t>GA01-27</t>
         </is>
       </c>
       <c r="B1272" s="4" t="inlineStr">
@@ -35443,7 +35521,7 @@
     <row r="1273">
       <c r="A1273" s="4" t="inlineStr">
         <is>
-          <t>GA01-30</t>
+          <t>GA01-28</t>
         </is>
       </c>
       <c r="B1273" s="4" t="inlineStr">
@@ -35465,7 +35543,7 @@
     <row r="1274">
       <c r="A1274" s="4" t="inlineStr">
         <is>
-          <t>GA01-31</t>
+          <t>GA01-29</t>
         </is>
       </c>
       <c r="B1274" s="4" t="inlineStr">
@@ -35487,7 +35565,7 @@
     <row r="1275">
       <c r="A1275" s="4" t="inlineStr">
         <is>
-          <t>GA01-32</t>
+          <t>GA01-30</t>
         </is>
       </c>
       <c r="B1275" s="4" t="inlineStr">
@@ -35509,7 +35587,7 @@
     <row r="1276">
       <c r="A1276" s="4" t="inlineStr">
         <is>
-          <t>GA01-33</t>
+          <t>GA01-31</t>
         </is>
       </c>
       <c r="B1276" s="4" t="inlineStr">
@@ -35531,7 +35609,7 @@
     <row r="1277">
       <c r="A1277" s="4" t="inlineStr">
         <is>
-          <t>GA01-34</t>
+          <t>GA01-32</t>
         </is>
       </c>
       <c r="B1277" s="4" t="inlineStr">
@@ -35553,7 +35631,7 @@
     <row r="1278">
       <c r="A1278" s="4" t="inlineStr">
         <is>
-          <t>GA01-35</t>
+          <t>GA01-33</t>
         </is>
       </c>
       <c r="B1278" s="4" t="inlineStr">
@@ -35575,7 +35653,7 @@
     <row r="1279">
       <c r="A1279" s="4" t="inlineStr">
         <is>
-          <t>GA01-36</t>
+          <t>GA01-34</t>
         </is>
       </c>
       <c r="B1279" s="4" t="inlineStr">
@@ -35597,7 +35675,7 @@
     <row r="1280">
       <c r="A1280" s="4" t="inlineStr">
         <is>
-          <t>GA01-37</t>
+          <t>GA01-35</t>
         </is>
       </c>
       <c r="B1280" s="4" t="inlineStr">
@@ -35619,7 +35697,7 @@
     <row r="1281">
       <c r="A1281" s="4" t="inlineStr">
         <is>
-          <t>GA01-38</t>
+          <t>GA01-36</t>
         </is>
       </c>
       <c r="B1281" s="4" t="inlineStr">
@@ -35641,7 +35719,7 @@
     <row r="1282">
       <c r="A1282" s="4" t="inlineStr">
         <is>
-          <t>GA01-39</t>
+          <t>GA01-37</t>
         </is>
       </c>
       <c r="B1282" s="4" t="inlineStr">
@@ -35663,7 +35741,7 @@
     <row r="1283">
       <c r="A1283" s="4" t="inlineStr">
         <is>
-          <t>GA01-40</t>
+          <t>GA01-38</t>
         </is>
       </c>
       <c r="B1283" s="4" t="inlineStr">
@@ -35682,10 +35760,54 @@
       <c r="G1283" s="4" t="n"/>
       <c r="H1283" s="4" t="n"/>
     </row>
+    <row r="1284">
+      <c r="A1284" s="4" t="inlineStr">
+        <is>
+          <t>GA01-39</t>
+        </is>
+      </c>
+      <c r="B1284" s="4" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1284" s="4" t="inlineStr"/>
+      <c r="D1284" s="4" t="inlineStr">
+        <is>
+          <t>Gartenanlage</t>
+        </is>
+      </c>
+      <c r="E1284" s="4" t="n"/>
+      <c r="F1284" s="3" t="n"/>
+      <c r="G1284" s="4" t="n"/>
+      <c r="H1284" s="4" t="n"/>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="4" t="inlineStr">
+        <is>
+          <t>GA01-40</t>
+        </is>
+      </c>
+      <c r="B1285" s="4" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1285" s="4" t="inlineStr"/>
+      <c r="D1285" s="4" t="inlineStr">
+        <is>
+          <t>Gartenanlage</t>
+        </is>
+      </c>
+      <c r="E1285" s="4" t="n"/>
+      <c r="F1285" s="3" t="n"/>
+      <c r="G1285" s="4" t="n"/>
+      <c r="H1285" s="4" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1283"/>
+  <autoFilter ref="A1:H1285"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F1283" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen." type="whole" operator="greaterThan">
+    <dataValidation sqref="F2:F1285" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="F107" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="F114" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
@@ -27399,144 +27399,194 @@
         </is>
       </c>
       <c r="F969" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G969" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H969" s="2" t="n"/>
+    </row>
+    <row r="970">
+      <c r="A970" s="2" t="inlineStr">
+        <is>
+          <t>BA04-03</t>
+        </is>
+      </c>
+      <c r="B970" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C970" s="2" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D970" s="2" t="inlineStr">
+        <is>
+          <t>Gruppenraum 4</t>
+        </is>
+      </c>
+      <c r="E970" s="2" t="inlineStr">
+        <is>
+          <t>Stapelstuhl Kunststoff, weiß</t>
+        </is>
+      </c>
+      <c r="F970" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G970" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H970" s="2" t="n"/>
+    </row>
+    <row r="971">
+      <c r="A971" s="2" t="inlineStr">
+        <is>
+          <t>BA04-04</t>
+        </is>
+      </c>
+      <c r="B971" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C971" s="2" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D971" s="2" t="inlineStr">
+        <is>
+          <t>Gruppenraum 4</t>
+        </is>
+      </c>
+      <c r="E971" s="2" t="inlineStr">
+        <is>
+          <t>Kinder-Sessel Bugholz mit Polster</t>
+        </is>
+      </c>
+      <c r="F971" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G969" s="2" t="inlineStr">
+      <c r="G971" s="2" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="H969" s="2" t="n"/>
-    </row>
-    <row r="970">
-      <c r="A970" s="4" t="inlineStr">
-        <is>
-          <t>BA04-03</t>
-        </is>
-      </c>
-      <c r="B970" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C970" s="4" t="inlineStr">
+      <c r="H971" s="2" t="n"/>
+    </row>
+    <row r="972">
+      <c r="A972" s="2" t="inlineStr">
+        <is>
+          <t>BA04-05</t>
+        </is>
+      </c>
+      <c r="B972" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C972" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D970" s="4" t="inlineStr">
+      <c r="D972" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 4</t>
         </is>
       </c>
-      <c r="E970" s="4" t="n"/>
-      <c r="F970" s="3" t="n"/>
-      <c r="G970" s="4" t="n"/>
-      <c r="H970" s="4" t="n"/>
-    </row>
-    <row r="971">
-      <c r="A971" s="4" t="inlineStr">
-        <is>
-          <t>BA04-04</t>
-        </is>
-      </c>
-      <c r="B971" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C971" s="4" t="inlineStr">
+      <c r="E972" s="2" t="inlineStr">
+        <is>
+          <t>Rollwagen weiß, drei Etagen</t>
+        </is>
+      </c>
+      <c r="F972" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G972" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H972" s="2" t="n"/>
+    </row>
+    <row r="973">
+      <c r="A973" s="2" t="inlineStr">
+        <is>
+          <t>BA04-06</t>
+        </is>
+      </c>
+      <c r="B973" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C973" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D971" s="4" t="inlineStr">
+      <c r="D973" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 4</t>
         </is>
       </c>
-      <c r="E971" s="4" t="n"/>
-      <c r="F971" s="3" t="n"/>
-      <c r="G971" s="4" t="n"/>
-      <c r="H971" s="4" t="n"/>
-    </row>
-    <row r="972">
-      <c r="A972" s="4" t="inlineStr">
-        <is>
-          <t>BA04-05</t>
-        </is>
-      </c>
-      <c r="B972" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C972" s="4" t="inlineStr">
+      <c r="E973" s="2" t="inlineStr">
+        <is>
+          <t>Beistelltisch Drahtkorb, weiß</t>
+        </is>
+      </c>
+      <c r="F973" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G973" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H973" s="2" t="n"/>
+    </row>
+    <row r="974">
+      <c r="A974" s="2" t="inlineStr">
+        <is>
+          <t>BA04-07</t>
+        </is>
+      </c>
+      <c r="B974" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C974" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D972" s="4" t="inlineStr">
+      <c r="D974" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 4</t>
         </is>
       </c>
-      <c r="E972" s="4" t="n"/>
-      <c r="F972" s="3" t="n"/>
-      <c r="G972" s="4" t="n"/>
-      <c r="H972" s="4" t="n"/>
-    </row>
-    <row r="973">
-      <c r="A973" s="4" t="inlineStr">
-        <is>
-          <t>BA04-06</t>
-        </is>
-      </c>
-      <c r="B973" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C973" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D973" s="4" t="inlineStr">
-        <is>
-          <t>Gruppenraum 4</t>
-        </is>
-      </c>
-      <c r="E973" s="4" t="n"/>
-      <c r="F973" s="3" t="n"/>
-      <c r="G973" s="4" t="n"/>
-      <c r="H973" s="4" t="n"/>
-    </row>
-    <row r="974">
-      <c r="A974" s="4" t="inlineStr">
-        <is>
-          <t>BA04-07</t>
-        </is>
-      </c>
-      <c r="B974" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C974" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D974" s="4" t="inlineStr">
-        <is>
-          <t>Gruppenraum 4</t>
-        </is>
-      </c>
-      <c r="E974" s="4" t="n"/>
-      <c r="F974" s="3" t="n"/>
-      <c r="G974" s="4" t="n"/>
-      <c r="H974" s="4" t="n"/>
+      <c r="E974" s="2" t="inlineStr">
+        <is>
+          <t>Kinderschrank weiß, zwei Türen mit Schublade</t>
+        </is>
+      </c>
+      <c r="F974" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G974" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H974" s="2" t="n"/>
     </row>
     <row r="975">
       <c r="A975" s="4" t="inlineStr">

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -26515,11 +26515,11 @@
       </c>
       <c r="E939" s="2" t="inlineStr">
         <is>
-          <t>Kinderschrank weiß mit Handabdrücken</t>
+          <t>IKEA Kinderschrank weiß, zwei Türen</t>
         </is>
       </c>
       <c r="F939" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G939" s="2" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
       </c>
       <c r="E970" s="2" t="inlineStr">
         <is>
-          <t>Stapelstuhl Kunststoff, weiß</t>
+          <t>Stapelstuhl Kunststoff weiß, Erwachsenengröße</t>
         </is>
       </c>
       <c r="F970" s="3" t="n">
@@ -27553,40 +27553,30 @@
       <c r="H973" s="2" t="n"/>
     </row>
     <row r="974">
-      <c r="A974" s="2" t="inlineStr">
+      <c r="A974" s="4" t="inlineStr">
         <is>
           <t>BA04-07</t>
         </is>
       </c>
-      <c r="B974" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C974" s="2" t="inlineStr">
+      <c r="B974" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C974" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D974" s="2" t="inlineStr">
+      <c r="D974" s="4" t="inlineStr">
         <is>
           <t>Gruppenraum 4</t>
         </is>
       </c>
-      <c r="E974" s="2" t="inlineStr">
-        <is>
-          <t>Kinderschrank weiß, zwei Türen mit Schublade</t>
-        </is>
-      </c>
-      <c r="F974" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G974" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H974" s="2" t="n"/>
+      <c r="E974" s="4" t="n"/>
+      <c r="F974" s="3" t="n"/>
+      <c r="G974" s="4" t="n"/>
+      <c r="H974" s="4" t="n"/>
     </row>
     <row r="975">
       <c r="A975" s="4" t="inlineStr">
@@ -28057,264 +28047,364 @@
       <c r="H992" s="4" t="n"/>
     </row>
     <row r="993">
-      <c r="A993" s="4" t="inlineStr">
+      <c r="A993" s="2" t="inlineStr">
         <is>
           <t>BA05-01</t>
         </is>
       </c>
-      <c r="B993" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C993" s="4" t="inlineStr">
+      <c r="B993" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C993" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D993" s="4" t="inlineStr">
+      <c r="D993" s="2" t="inlineStr">
         <is>
           <t>Turnraum</t>
         </is>
       </c>
-      <c r="E993" s="4" t="n"/>
-      <c r="F993" s="3" t="n"/>
-      <c r="G993" s="4" t="n"/>
-      <c r="H993" s="4" t="n"/>
+      <c r="E993" s="2" t="inlineStr">
+        <is>
+          <t>Rollkasten mit großen Kunststoff-Bausteinen</t>
+        </is>
+      </c>
+      <c r="F993" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G993" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H993" s="2" t="n"/>
     </row>
     <row r="994">
-      <c r="A994" s="4" t="inlineStr">
+      <c r="A994" s="2" t="inlineStr">
         <is>
           <t>BA05-02</t>
         </is>
       </c>
-      <c r="B994" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C994" s="4" t="inlineStr">
+      <c r="B994" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C994" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D994" s="4" t="inlineStr">
+      <c r="D994" s="2" t="inlineStr">
         <is>
           <t>Turnraum</t>
         </is>
       </c>
-      <c r="E994" s="4" t="n"/>
-      <c r="F994" s="3" t="n"/>
-      <c r="G994" s="4" t="n"/>
-      <c r="H994" s="4" t="n"/>
+      <c r="E994" s="2" t="inlineStr">
+        <is>
+          <t>BENZ Turnbank</t>
+        </is>
+      </c>
+      <c r="F994" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G994" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H994" s="2" t="n"/>
     </row>
     <row r="995">
-      <c r="A995" s="4" t="inlineStr">
+      <c r="A995" s="2" t="inlineStr">
         <is>
           <t>BA05-03</t>
         </is>
       </c>
-      <c r="B995" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C995" s="4" t="inlineStr">
+      <c r="B995" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C995" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D995" s="4" t="inlineStr">
+      <c r="D995" s="2" t="inlineStr">
         <is>
           <t>Turnraum</t>
         </is>
       </c>
-      <c r="E995" s="4" t="n"/>
-      <c r="F995" s="3" t="n"/>
-      <c r="G995" s="4" t="n"/>
-      <c r="H995" s="4" t="n"/>
+      <c r="E995" s="2" t="inlineStr">
+        <is>
+          <t>Trampolin mit Haltestange</t>
+        </is>
+      </c>
+      <c r="F995" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G995" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H995" s="2" t="n"/>
     </row>
     <row r="996">
-      <c r="A996" s="4" t="inlineStr">
+      <c r="A996" s="2" t="inlineStr">
         <is>
           <t>BA05-04</t>
         </is>
       </c>
-      <c r="B996" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C996" s="4" t="inlineStr">
+      <c r="B996" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C996" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D996" s="4" t="inlineStr">
+      <c r="D996" s="2" t="inlineStr">
         <is>
           <t>Turnraum</t>
         </is>
       </c>
-      <c r="E996" s="4" t="n"/>
-      <c r="F996" s="3" t="n"/>
-      <c r="G996" s="4" t="n"/>
-      <c r="H996" s="4" t="n"/>
+      <c r="E996" s="2" t="inlineStr">
+        <is>
+          <t>Spielhochbett mit Bällebad und Rutsche</t>
+        </is>
+      </c>
+      <c r="F996" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G996" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H996" s="2" t="n"/>
     </row>
     <row r="997">
-      <c r="A997" s="4" t="inlineStr">
+      <c r="A997" s="2" t="inlineStr">
         <is>
           <t>BA05-05</t>
         </is>
       </c>
-      <c r="B997" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C997" s="4" t="inlineStr">
+      <c r="B997" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C997" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D997" s="4" t="inlineStr">
+      <c r="D997" s="2" t="inlineStr">
         <is>
           <t>Turnraum</t>
         </is>
       </c>
-      <c r="E997" s="4" t="n"/>
-      <c r="F997" s="3" t="n"/>
-      <c r="G997" s="4" t="n"/>
-      <c r="H997" s="4" t="n"/>
+      <c r="E997" s="2" t="inlineStr">
+        <is>
+          <t>Sprossenwand einzeln</t>
+        </is>
+      </c>
+      <c r="F997" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G997" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H997" s="2" t="n"/>
     </row>
     <row r="998">
-      <c r="A998" s="4" t="inlineStr">
+      <c r="A998" s="2" t="inlineStr">
         <is>
           <t>BA05-06</t>
         </is>
       </c>
-      <c r="B998" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C998" s="4" t="inlineStr">
+      <c r="B998" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C998" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D998" s="4" t="inlineStr">
+      <c r="D998" s="2" t="inlineStr">
         <is>
           <t>Turnraum</t>
         </is>
       </c>
-      <c r="E998" s="4" t="n"/>
-      <c r="F998" s="3" t="n"/>
-      <c r="G998" s="4" t="n"/>
-      <c r="H998" s="4" t="n"/>
+      <c r="E998" s="2" t="inlineStr">
+        <is>
+          <t>Doppelsprossenwand</t>
+        </is>
+      </c>
+      <c r="F998" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G998" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H998" s="2" t="n"/>
     </row>
     <row r="999">
-      <c r="A999" s="4" t="inlineStr">
+      <c r="A999" s="2" t="inlineStr">
         <is>
           <t>BA05-07</t>
         </is>
       </c>
-      <c r="B999" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C999" s="4" t="inlineStr">
+      <c r="B999" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C999" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D999" s="4" t="inlineStr">
+      <c r="D999" s="2" t="inlineStr">
         <is>
           <t>Turnraum</t>
         </is>
       </c>
-      <c r="E999" s="4" t="n"/>
-      <c r="F999" s="3" t="n"/>
-      <c r="G999" s="4" t="n"/>
-      <c r="H999" s="4" t="n"/>
+      <c r="E999" s="2" t="inlineStr">
+        <is>
+          <t>Treppenturngerät gepolstert</t>
+        </is>
+      </c>
+      <c r="F999" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G999" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H999" s="2" t="n"/>
     </row>
     <row r="1000">
-      <c r="A1000" s="4" t="inlineStr">
+      <c r="A1000" s="2" t="inlineStr">
         <is>
           <t>BA05-08</t>
         </is>
       </c>
-      <c r="B1000" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1000" s="4" t="inlineStr">
+      <c r="B1000" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1000" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1000" s="4" t="inlineStr">
+      <c r="D1000" s="2" t="inlineStr">
         <is>
           <t>Turnraum</t>
         </is>
       </c>
-      <c r="E1000" s="4" t="n"/>
-      <c r="F1000" s="3" t="n"/>
-      <c r="G1000" s="4" t="n"/>
-      <c r="H1000" s="4" t="n"/>
+      <c r="E1000" s="2" t="inlineStr">
+        <is>
+          <t>Rody Hüpfpferd rot</t>
+        </is>
+      </c>
+      <c r="F1000" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1000" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1000" s="2" t="n"/>
     </row>
     <row r="1001">
-      <c r="A1001" s="4" t="inlineStr">
+      <c r="A1001" s="2" t="inlineStr">
         <is>
           <t>BA05-09</t>
         </is>
       </c>
-      <c r="B1001" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1001" s="4" t="inlineStr">
+      <c r="B1001" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1001" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1001" s="4" t="inlineStr">
+      <c r="D1001" s="2" t="inlineStr">
         <is>
           <t>Turnraum</t>
         </is>
       </c>
-      <c r="E1001" s="4" t="n"/>
-      <c r="F1001" s="3" t="n"/>
-      <c r="G1001" s="4" t="n"/>
-      <c r="H1001" s="4" t="n"/>
+      <c r="E1001" s="2" t="inlineStr">
+        <is>
+          <t>Softbausteine gepolstert, groß</t>
+        </is>
+      </c>
+      <c r="F1001" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1001" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1001" s="2" t="n"/>
     </row>
     <row r="1002">
-      <c r="A1002" s="4" t="inlineStr">
+      <c r="A1002" s="2" t="inlineStr">
         <is>
           <t>BA05-10</t>
         </is>
       </c>
-      <c r="B1002" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1002" s="4" t="inlineStr">
+      <c r="B1002" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1002" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1002" s="4" t="inlineStr">
+      <c r="D1002" s="2" t="inlineStr">
         <is>
           <t>Turnraum</t>
         </is>
       </c>
-      <c r="E1002" s="4" t="n"/>
-      <c r="F1002" s="3" t="n"/>
-      <c r="G1002" s="4" t="n"/>
-      <c r="H1002" s="4" t="n"/>
+      <c r="E1002" s="2" t="inlineStr">
+        <is>
+          <t>Wandschutz grün, gepolstert</t>
+        </is>
+      </c>
+      <c r="F1002" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1002" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1002" s="2" t="n"/>
     </row>
     <row r="1003">
       <c r="A1003" s="4" t="inlineStr">

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -28393,7 +28393,7 @@
       </c>
       <c r="E1002" s="2" t="inlineStr">
         <is>
-          <t>Wandschutz grün, gepolstert</t>
+          <t>Polstersäule grün, Raumteiler</t>
         </is>
       </c>
       <c r="F1002" s="3" t="n">

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anleitung" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Erfassung'!$A$1:$H$1285</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Erfassung'!$A$1:$H$1291</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1285"/>
+  <dimension ref="A1:H1291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="F111" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
@@ -28321,11 +28321,11 @@
       </c>
       <c r="E1000" s="2" t="inlineStr">
         <is>
-          <t>Rody Hüpfpferd rot</t>
+          <t>Rody Hüpfpferd, rot und grün</t>
         </is>
       </c>
       <c r="F1000" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1000" s="2" t="inlineStr">
         <is>
@@ -29187,290 +29187,400 @@
       <c r="H1032" s="4" t="n"/>
     </row>
     <row r="1033">
-      <c r="A1033" s="4" t="inlineStr">
+      <c r="A1033" s="2" t="inlineStr">
         <is>
           <t>BA06-01</t>
         </is>
       </c>
-      <c r="B1033" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1033" s="4" t="inlineStr">
+      <c r="B1033" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1033" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1033" s="4" t="inlineStr">
+      <c r="D1033" s="2" t="inlineStr">
         <is>
           <t>Material / Turnraum</t>
         </is>
       </c>
-      <c r="E1033" s="4" t="n"/>
-      <c r="F1033" s="3" t="n"/>
-      <c r="G1033" s="4" t="n"/>
-      <c r="H1033" s="4" t="n"/>
+      <c r="E1033" s="2" t="inlineStr">
+        <is>
+          <t>BMW Baby Racer Rutscherauto</t>
+        </is>
+      </c>
+      <c r="F1033" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1033" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1033" s="2" t="n"/>
     </row>
     <row r="1034">
-      <c r="A1034" s="4" t="inlineStr">
+      <c r="A1034" s="2" t="inlineStr">
         <is>
           <t>BA06-02</t>
         </is>
       </c>
-      <c r="B1034" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1034" s="4" t="inlineStr">
+      <c r="B1034" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1034" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1034" s="4" t="inlineStr">
+      <c r="D1034" s="2" t="inlineStr">
         <is>
           <t>Material / Turnraum</t>
         </is>
       </c>
-      <c r="E1034" s="4" t="n"/>
-      <c r="F1034" s="3" t="n"/>
-      <c r="G1034" s="4" t="n"/>
-      <c r="H1034" s="4" t="n"/>
+      <c r="E1034" s="2" t="inlineStr">
+        <is>
+          <t>BIG Bobby Quad</t>
+        </is>
+      </c>
+      <c r="F1034" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1034" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1034" s="2" t="n"/>
     </row>
     <row r="1035">
-      <c r="A1035" s="4" t="inlineStr">
+      <c r="A1035" s="2" t="inlineStr">
         <is>
           <t>BA06-03</t>
         </is>
       </c>
-      <c r="B1035" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1035" s="4" t="inlineStr">
+      <c r="B1035" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1035" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1035" s="4" t="inlineStr">
+      <c r="D1035" s="2" t="inlineStr">
         <is>
           <t>Material / Turnraum</t>
         </is>
       </c>
-      <c r="E1035" s="4" t="n"/>
-      <c r="F1035" s="3" t="n"/>
-      <c r="G1035" s="4" t="n"/>
-      <c r="H1035" s="4" t="n"/>
+      <c r="E1035" s="2" t="inlineStr">
+        <is>
+          <t>Holz-Dreirad mit Kuhkopf</t>
+        </is>
+      </c>
+      <c r="F1035" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1035" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1035" s="2" t="n"/>
     </row>
     <row r="1036">
-      <c r="A1036" s="4" t="inlineStr">
+      <c r="A1036" s="2" t="inlineStr">
         <is>
           <t>BA06-04</t>
         </is>
       </c>
-      <c r="B1036" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1036" s="4" t="inlineStr">
+      <c r="B1036" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1036" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1036" s="4" t="inlineStr">
+      <c r="D1036" s="2" t="inlineStr">
         <is>
           <t>Material / Turnraum</t>
         </is>
       </c>
-      <c r="E1036" s="4" t="n"/>
-      <c r="F1036" s="3" t="n"/>
-      <c r="G1036" s="4" t="n"/>
-      <c r="H1036" s="4" t="n"/>
+      <c r="E1036" s="2" t="inlineStr">
+        <is>
+          <t>Schaukel- und Rutschtier aus Formholz</t>
+        </is>
+      </c>
+      <c r="F1036" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1036" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1036" s="2" t="n"/>
     </row>
     <row r="1037">
-      <c r="A1037" s="4" t="inlineStr">
+      <c r="A1037" s="2" t="inlineStr">
         <is>
           <t>BA06-05</t>
         </is>
       </c>
-      <c r="B1037" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1037" s="4" t="inlineStr">
+      <c r="B1037" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1037" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1037" s="4" t="inlineStr">
+      <c r="D1037" s="2" t="inlineStr">
         <is>
           <t>Material / Turnraum</t>
         </is>
       </c>
-      <c r="E1037" s="4" t="n"/>
-      <c r="F1037" s="3" t="n"/>
-      <c r="G1037" s="4" t="n"/>
-      <c r="H1037" s="4" t="n"/>
+      <c r="E1037" s="2" t="inlineStr">
+        <is>
+          <t>BIG Bobby Car Feuerwehr</t>
+        </is>
+      </c>
+      <c r="F1037" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1037" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1037" s="2" t="n"/>
     </row>
     <row r="1038">
-      <c r="A1038" s="4" t="inlineStr">
+      <c r="A1038" s="2" t="inlineStr">
         <is>
           <t>BA06-06</t>
         </is>
       </c>
-      <c r="B1038" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1038" s="4" t="inlineStr">
+      <c r="B1038" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1038" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1038" s="4" t="inlineStr">
+      <c r="D1038" s="2" t="inlineStr">
         <is>
           <t>Material / Turnraum</t>
         </is>
       </c>
-      <c r="E1038" s="4" t="n"/>
-      <c r="F1038" s="3" t="n"/>
-      <c r="G1038" s="4" t="n"/>
-      <c r="H1038" s="4" t="n"/>
+      <c r="E1038" s="2" t="inlineStr">
+        <is>
+          <t>Klettergerüst Holz</t>
+        </is>
+      </c>
+      <c r="F1038" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1038" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1038" s="2" t="n"/>
     </row>
     <row r="1039">
-      <c r="A1039" s="4" t="inlineStr">
+      <c r="A1039" s="2" t="inlineStr">
         <is>
           <t>BA06-07</t>
         </is>
       </c>
-      <c r="B1039" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1039" s="4" t="inlineStr">
+      <c r="B1039" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1039" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1039" s="4" t="inlineStr">
+      <c r="D1039" s="2" t="inlineStr">
         <is>
           <t>Material / Turnraum</t>
         </is>
       </c>
-      <c r="E1039" s="4" t="n"/>
-      <c r="F1039" s="3" t="n"/>
-      <c r="G1039" s="4" t="n"/>
-      <c r="H1039" s="4" t="n"/>
+      <c r="E1039" s="2" t="inlineStr">
+        <is>
+          <t>Klettergerüst grün mit Rutschbrett</t>
+        </is>
+      </c>
+      <c r="F1039" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1039" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1039" s="2" t="n"/>
     </row>
     <row r="1040">
-      <c r="A1040" s="4" t="inlineStr">
+      <c r="A1040" s="2" t="inlineStr">
         <is>
           <t>BA06-08</t>
         </is>
       </c>
-      <c r="B1040" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1040" s="4" t="inlineStr">
+      <c r="B1040" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1040" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1040" s="4" t="inlineStr">
+      <c r="D1040" s="2" t="inlineStr">
         <is>
           <t>Material / Turnraum</t>
         </is>
       </c>
-      <c r="E1040" s="4" t="n"/>
-      <c r="F1040" s="3" t="n"/>
-      <c r="G1040" s="4" t="n"/>
-      <c r="H1040" s="4" t="n"/>
+      <c r="E1040" s="2" t="inlineStr">
+        <is>
+          <t>Holz-Lastwagen zum Rutschen</t>
+        </is>
+      </c>
+      <c r="F1040" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1040" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1040" s="2" t="n"/>
     </row>
     <row r="1041">
-      <c r="A1041" s="4" t="inlineStr">
+      <c r="A1041" s="2" t="inlineStr">
         <is>
           <t>BA06-09</t>
         </is>
       </c>
-      <c r="B1041" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1041" s="4" t="inlineStr">
+      <c r="B1041" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1041" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1041" s="4" t="inlineStr">
+      <c r="D1041" s="2" t="inlineStr">
         <is>
           <t>Material / Turnraum</t>
         </is>
       </c>
-      <c r="E1041" s="4" t="n"/>
-      <c r="F1041" s="3" t="n"/>
-      <c r="G1041" s="4" t="n"/>
-      <c r="H1041" s="4" t="n"/>
+      <c r="E1041" s="2" t="inlineStr">
+        <is>
+          <t>Feuerwehrhaus aus Holz</t>
+        </is>
+      </c>
+      <c r="F1041" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1041" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1041" s="2" t="n"/>
     </row>
     <row r="1042">
-      <c r="A1042" s="4" t="inlineStr">
+      <c r="A1042" s="2" t="inlineStr">
         <is>
           <t>BA06-10</t>
         </is>
       </c>
-      <c r="B1042" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1042" s="4" t="inlineStr">
+      <c r="B1042" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1042" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1042" s="4" t="inlineStr">
+      <c r="D1042" s="2" t="inlineStr">
         <is>
           <t>Material / Turnraum</t>
         </is>
       </c>
-      <c r="E1042" s="4" t="n"/>
-      <c r="F1042" s="3" t="n"/>
-      <c r="G1042" s="4" t="n"/>
-      <c r="H1042" s="4" t="n"/>
+      <c r="E1042" s="2" t="inlineStr">
+        <is>
+          <t>Sitzschaukel Kunststoff mit Seilen</t>
+        </is>
+      </c>
+      <c r="F1042" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1042" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1042" s="2" t="n"/>
     </row>
     <row r="1043">
-      <c r="A1043" s="4" t="inlineStr">
+      <c r="A1043" s="2" t="inlineStr">
         <is>
           <t>BA06-11</t>
         </is>
       </c>
-      <c r="B1043" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1043" s="4" t="inlineStr">
+      <c r="B1043" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1043" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1043" s="4" t="inlineStr">
+      <c r="D1043" s="2" t="inlineStr">
         <is>
           <t>Material / Turnraum</t>
         </is>
       </c>
-      <c r="E1043" s="4" t="n"/>
-      <c r="F1043" s="3" t="n"/>
-      <c r="G1043" s="4" t="n"/>
-      <c r="H1043" s="4" t="n"/>
+      <c r="E1043" s="2" t="inlineStr">
+        <is>
+          <t>Spieltunnel grün</t>
+        </is>
+      </c>
+      <c r="F1043" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1043" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1043" s="2" t="n"/>
     </row>
     <row r="1044">
       <c r="A1044" s="4" t="inlineStr">
@@ -29579,7 +29689,7 @@
     <row r="1048">
       <c r="A1048" s="4" t="inlineStr">
         <is>
-          <t>BA07-01</t>
+          <t>BA06-16</t>
         </is>
       </c>
       <c r="B1048" s="4" t="inlineStr">
@@ -29594,7 +29704,7 @@
       </c>
       <c r="D1048" s="4" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Material / Turnraum</t>
         </is>
       </c>
       <c r="E1048" s="4" t="n"/>
@@ -29605,7 +29715,7 @@
     <row r="1049">
       <c r="A1049" s="4" t="inlineStr">
         <is>
-          <t>BA07-02</t>
+          <t>BA06-17</t>
         </is>
       </c>
       <c r="B1049" s="4" t="inlineStr">
@@ -29620,7 +29730,7 @@
       </c>
       <c r="D1049" s="4" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Material / Turnraum</t>
         </is>
       </c>
       <c r="E1049" s="4" t="n"/>
@@ -29631,7 +29741,7 @@
     <row r="1050">
       <c r="A1050" s="4" t="inlineStr">
         <is>
-          <t>BA07-03</t>
+          <t>BA06-18</t>
         </is>
       </c>
       <c r="B1050" s="4" t="inlineStr">
@@ -29646,7 +29756,7 @@
       </c>
       <c r="D1050" s="4" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Material / Turnraum</t>
         </is>
       </c>
       <c r="E1050" s="4" t="n"/>
@@ -29657,7 +29767,7 @@
     <row r="1051">
       <c r="A1051" s="4" t="inlineStr">
         <is>
-          <t>BA07-04</t>
+          <t>BA06-19</t>
         </is>
       </c>
       <c r="B1051" s="4" t="inlineStr">
@@ -29672,7 +29782,7 @@
       </c>
       <c r="D1051" s="4" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Material / Turnraum</t>
         </is>
       </c>
       <c r="E1051" s="4" t="n"/>
@@ -29683,7 +29793,7 @@
     <row r="1052">
       <c r="A1052" s="4" t="inlineStr">
         <is>
-          <t>BA07-05</t>
+          <t>BA06-20</t>
         </is>
       </c>
       <c r="B1052" s="4" t="inlineStr">
@@ -29698,7 +29808,7 @@
       </c>
       <c r="D1052" s="4" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Material / Turnraum</t>
         </is>
       </c>
       <c r="E1052" s="4" t="n"/>
@@ -29709,7 +29819,7 @@
     <row r="1053">
       <c r="A1053" s="4" t="inlineStr">
         <is>
-          <t>BA07-06</t>
+          <t>BA06-21</t>
         </is>
       </c>
       <c r="B1053" s="4" t="inlineStr">
@@ -29724,7 +29834,7 @@
       </c>
       <c r="D1053" s="4" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Material / Turnraum</t>
         </is>
       </c>
       <c r="E1053" s="4" t="n"/>
@@ -29735,7 +29845,7 @@
     <row r="1054">
       <c r="A1054" s="4" t="inlineStr">
         <is>
-          <t>BA07-07</t>
+          <t>BA07-01</t>
         </is>
       </c>
       <c r="B1054" s="4" t="inlineStr">
@@ -29761,7 +29871,7 @@
     <row r="1055">
       <c r="A1055" s="4" t="inlineStr">
         <is>
-          <t>BA07-08</t>
+          <t>BA07-02</t>
         </is>
       </c>
       <c r="B1055" s="4" t="inlineStr">
@@ -29787,7 +29897,7 @@
     <row r="1056">
       <c r="A1056" s="4" t="inlineStr">
         <is>
-          <t>BA07-09</t>
+          <t>BA07-03</t>
         </is>
       </c>
       <c r="B1056" s="4" t="inlineStr">
@@ -29813,7 +29923,7 @@
     <row r="1057">
       <c r="A1057" s="4" t="inlineStr">
         <is>
-          <t>BA07-10</t>
+          <t>BA07-04</t>
         </is>
       </c>
       <c r="B1057" s="4" t="inlineStr">
@@ -29839,7 +29949,7 @@
     <row r="1058">
       <c r="A1058" s="4" t="inlineStr">
         <is>
-          <t>BA07-11</t>
+          <t>BA07-05</t>
         </is>
       </c>
       <c r="B1058" s="4" t="inlineStr">
@@ -29865,7 +29975,7 @@
     <row r="1059">
       <c r="A1059" s="4" t="inlineStr">
         <is>
-          <t>BA07-12</t>
+          <t>BA07-06</t>
         </is>
       </c>
       <c r="B1059" s="4" t="inlineStr">
@@ -29891,7 +30001,7 @@
     <row r="1060">
       <c r="A1060" s="4" t="inlineStr">
         <is>
-          <t>BA07-13</t>
+          <t>BA07-07</t>
         </is>
       </c>
       <c r="B1060" s="4" t="inlineStr">
@@ -29917,7 +30027,7 @@
     <row r="1061">
       <c r="A1061" s="4" t="inlineStr">
         <is>
-          <t>BA07-14</t>
+          <t>BA07-08</t>
         </is>
       </c>
       <c r="B1061" s="4" t="inlineStr">
@@ -29943,7 +30053,7 @@
     <row r="1062">
       <c r="A1062" s="4" t="inlineStr">
         <is>
-          <t>BA07-15</t>
+          <t>BA07-09</t>
         </is>
       </c>
       <c r="B1062" s="4" t="inlineStr">
@@ -29967,153 +30077,113 @@
       <c r="H1062" s="4" t="n"/>
     </row>
     <row r="1063">
-      <c r="A1063" s="2" t="inlineStr">
-        <is>
-          <t>BA08-01</t>
-        </is>
-      </c>
-      <c r="B1063" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1063" s="2" t="inlineStr">
+      <c r="A1063" s="4" t="inlineStr">
+        <is>
+          <t>BA07-10</t>
+        </is>
+      </c>
+      <c r="B1063" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1063" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1063" s="2" t="inlineStr">
-        <is>
-          <t>Atelier</t>
-        </is>
-      </c>
-      <c r="E1063" s="2" t="inlineStr">
-        <is>
-          <t>Konvolut Mal- und Bastelfarben</t>
-        </is>
-      </c>
-      <c r="F1063" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1063" s="2" t="inlineStr">
-        <is>
-          <t>Konvolut</t>
-        </is>
-      </c>
-      <c r="H1063" s="2" t="n"/>
+      <c r="D1063" s="4" t="inlineStr">
+        <is>
+          <t>Klassenzimmer</t>
+        </is>
+      </c>
+      <c r="E1063" s="4" t="n"/>
+      <c r="F1063" s="3" t="n"/>
+      <c r="G1063" s="4" t="n"/>
+      <c r="H1063" s="4" t="n"/>
     </row>
     <row r="1064">
-      <c r="A1064" s="2" t="inlineStr">
-        <is>
-          <t>BA08-02</t>
-        </is>
-      </c>
-      <c r="B1064" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1064" s="2" t="inlineStr">
+      <c r="A1064" s="4" t="inlineStr">
+        <is>
+          <t>BA07-11</t>
+        </is>
+      </c>
+      <c r="B1064" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1064" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1064" s="2" t="inlineStr">
-        <is>
-          <t>Atelier</t>
-        </is>
-      </c>
-      <c r="E1064" s="2" t="inlineStr">
-        <is>
-          <t>Acrylfarben-Sortiment im Holzkasten</t>
-        </is>
-      </c>
-      <c r="F1064" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1064" s="2" t="inlineStr">
-        <is>
-          <t>Konvolut</t>
-        </is>
-      </c>
-      <c r="H1064" s="2" t="n"/>
+      <c r="D1064" s="4" t="inlineStr">
+        <is>
+          <t>Klassenzimmer</t>
+        </is>
+      </c>
+      <c r="E1064" s="4" t="n"/>
+      <c r="F1064" s="3" t="n"/>
+      <c r="G1064" s="4" t="n"/>
+      <c r="H1064" s="4" t="n"/>
     </row>
     <row r="1065">
-      <c r="A1065" s="2" t="inlineStr">
-        <is>
-          <t>BA08-03</t>
-        </is>
-      </c>
-      <c r="B1065" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1065" s="2" t="inlineStr">
+      <c r="A1065" s="4" t="inlineStr">
+        <is>
+          <t>BA07-12</t>
+        </is>
+      </c>
+      <c r="B1065" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1065" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1065" s="2" t="inlineStr">
-        <is>
-          <t>Atelier</t>
-        </is>
-      </c>
-      <c r="E1065" s="2" t="inlineStr">
-        <is>
-          <t>Konvolut Bastelmaterial</t>
-        </is>
-      </c>
-      <c r="F1065" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1065" s="2" t="inlineStr">
-        <is>
-          <t>Konvolut</t>
-        </is>
-      </c>
-      <c r="H1065" s="2" t="n"/>
+      <c r="D1065" s="4" t="inlineStr">
+        <is>
+          <t>Klassenzimmer</t>
+        </is>
+      </c>
+      <c r="E1065" s="4" t="n"/>
+      <c r="F1065" s="3" t="n"/>
+      <c r="G1065" s="4" t="n"/>
+      <c r="H1065" s="4" t="n"/>
     </row>
     <row r="1066">
-      <c r="A1066" s="2" t="inlineStr">
-        <is>
-          <t>BA08-04</t>
-        </is>
-      </c>
-      <c r="B1066" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1066" s="2" t="inlineStr">
+      <c r="A1066" s="4" t="inlineStr">
+        <is>
+          <t>BA07-13</t>
+        </is>
+      </c>
+      <c r="B1066" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1066" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1066" s="2" t="inlineStr">
-        <is>
-          <t>Atelier</t>
-        </is>
-      </c>
-      <c r="E1066" s="2" t="inlineStr">
-        <is>
-          <t>buntes Papier</t>
-        </is>
-      </c>
-      <c r="F1066" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1066" s="2" t="inlineStr">
-        <is>
-          <t>Konvolut</t>
-        </is>
-      </c>
-      <c r="H1066" s="2" t="n"/>
+      <c r="D1066" s="4" t="inlineStr">
+        <is>
+          <t>Klassenzimmer</t>
+        </is>
+      </c>
+      <c r="E1066" s="4" t="n"/>
+      <c r="F1066" s="3" t="n"/>
+      <c r="G1066" s="4" t="n"/>
+      <c r="H1066" s="4" t="n"/>
     </row>
     <row r="1067">
       <c r="A1067" s="4" t="inlineStr">
         <is>
-          <t>BA08-05</t>
+          <t>BA07-14</t>
         </is>
       </c>
       <c r="B1067" s="4" t="inlineStr">
@@ -30128,7 +30198,7 @@
       </c>
       <c r="D1067" s="4" t="inlineStr">
         <is>
-          <t>Atelier</t>
+          <t>Klassenzimmer</t>
         </is>
       </c>
       <c r="E1067" s="4" t="n"/>
@@ -30139,7 +30209,7 @@
     <row r="1068">
       <c r="A1068" s="4" t="inlineStr">
         <is>
-          <t>BA08-06</t>
+          <t>BA07-15</t>
         </is>
       </c>
       <c r="B1068" s="4" t="inlineStr">
@@ -30154,7 +30224,7 @@
       </c>
       <c r="D1068" s="4" t="inlineStr">
         <is>
-          <t>Atelier</t>
+          <t>Klassenzimmer</t>
         </is>
       </c>
       <c r="E1068" s="4" t="n"/>
@@ -30163,113 +30233,153 @@
       <c r="H1068" s="4" t="n"/>
     </row>
     <row r="1069">
-      <c r="A1069" s="4" t="inlineStr">
-        <is>
-          <t>BA08-07</t>
-        </is>
-      </c>
-      <c r="B1069" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1069" s="4" t="inlineStr">
+      <c r="A1069" s="2" t="inlineStr">
+        <is>
+          <t>BA08-01</t>
+        </is>
+      </c>
+      <c r="B1069" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1069" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1069" s="4" t="inlineStr">
+      <c r="D1069" s="2" t="inlineStr">
         <is>
           <t>Atelier</t>
         </is>
       </c>
-      <c r="E1069" s="4" t="n"/>
-      <c r="F1069" s="3" t="n"/>
-      <c r="G1069" s="4" t="n"/>
-      <c r="H1069" s="4" t="n"/>
+      <c r="E1069" s="2" t="inlineStr">
+        <is>
+          <t>Konvolut Mal- und Bastelfarben</t>
+        </is>
+      </c>
+      <c r="F1069" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1069" s="2" t="inlineStr">
+        <is>
+          <t>Konvolut</t>
+        </is>
+      </c>
+      <c r="H1069" s="2" t="n"/>
     </row>
     <row r="1070">
-      <c r="A1070" s="4" t="inlineStr">
-        <is>
-          <t>BA08-08</t>
-        </is>
-      </c>
-      <c r="B1070" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1070" s="4" t="inlineStr">
+      <c r="A1070" s="2" t="inlineStr">
+        <is>
+          <t>BA08-02</t>
+        </is>
+      </c>
+      <c r="B1070" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1070" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1070" s="4" t="inlineStr">
+      <c r="D1070" s="2" t="inlineStr">
         <is>
           <t>Atelier</t>
         </is>
       </c>
-      <c r="E1070" s="4" t="n"/>
-      <c r="F1070" s="3" t="n"/>
-      <c r="G1070" s="4" t="n"/>
-      <c r="H1070" s="4" t="n"/>
+      <c r="E1070" s="2" t="inlineStr">
+        <is>
+          <t>Acrylfarben-Sortiment im Holzkasten</t>
+        </is>
+      </c>
+      <c r="F1070" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1070" s="2" t="inlineStr">
+        <is>
+          <t>Konvolut</t>
+        </is>
+      </c>
+      <c r="H1070" s="2" t="n"/>
     </row>
     <row r="1071">
-      <c r="A1071" s="4" t="inlineStr">
-        <is>
-          <t>BA08-09</t>
-        </is>
-      </c>
-      <c r="B1071" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1071" s="4" t="inlineStr">
+      <c r="A1071" s="2" t="inlineStr">
+        <is>
+          <t>BA08-03</t>
+        </is>
+      </c>
+      <c r="B1071" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1071" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1071" s="4" t="inlineStr">
+      <c r="D1071" s="2" t="inlineStr">
         <is>
           <t>Atelier</t>
         </is>
       </c>
-      <c r="E1071" s="4" t="n"/>
-      <c r="F1071" s="3" t="n"/>
-      <c r="G1071" s="4" t="n"/>
-      <c r="H1071" s="4" t="n"/>
+      <c r="E1071" s="2" t="inlineStr">
+        <is>
+          <t>Konvolut Bastelmaterial</t>
+        </is>
+      </c>
+      <c r="F1071" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1071" s="2" t="inlineStr">
+        <is>
+          <t>Konvolut</t>
+        </is>
+      </c>
+      <c r="H1071" s="2" t="n"/>
     </row>
     <row r="1072">
-      <c r="A1072" s="4" t="inlineStr">
-        <is>
-          <t>BA08-10</t>
-        </is>
-      </c>
-      <c r="B1072" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1072" s="4" t="inlineStr">
+      <c r="A1072" s="2" t="inlineStr">
+        <is>
+          <t>BA08-04</t>
+        </is>
+      </c>
+      <c r="B1072" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1072" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1072" s="4" t="inlineStr">
+      <c r="D1072" s="2" t="inlineStr">
         <is>
           <t>Atelier</t>
         </is>
       </c>
-      <c r="E1072" s="4" t="n"/>
-      <c r="F1072" s="3" t="n"/>
-      <c r="G1072" s="4" t="n"/>
-      <c r="H1072" s="4" t="n"/>
+      <c r="E1072" s="2" t="inlineStr">
+        <is>
+          <t>buntes Papier</t>
+        </is>
+      </c>
+      <c r="F1072" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1072" s="2" t="inlineStr">
+        <is>
+          <t>Konvolut</t>
+        </is>
+      </c>
+      <c r="H1072" s="2" t="n"/>
     </row>
     <row r="1073">
       <c r="A1073" s="4" t="inlineStr">
         <is>
-          <t>BA08-11</t>
+          <t>BA08-05</t>
         </is>
       </c>
       <c r="B1073" s="4" t="inlineStr">
@@ -30295,7 +30405,7 @@
     <row r="1074">
       <c r="A1074" s="4" t="inlineStr">
         <is>
-          <t>BA08-12</t>
+          <t>BA08-06</t>
         </is>
       </c>
       <c r="B1074" s="4" t="inlineStr">
@@ -30321,7 +30431,7 @@
     <row r="1075">
       <c r="A1075" s="4" t="inlineStr">
         <is>
-          <t>BA08-13</t>
+          <t>BA08-07</t>
         </is>
       </c>
       <c r="B1075" s="4" t="inlineStr">
@@ -30347,7 +30457,7 @@
     <row r="1076">
       <c r="A1076" s="4" t="inlineStr">
         <is>
-          <t>BA08-14</t>
+          <t>BA08-08</t>
         </is>
       </c>
       <c r="B1076" s="4" t="inlineStr">
@@ -30373,7 +30483,7 @@
     <row r="1077">
       <c r="A1077" s="4" t="inlineStr">
         <is>
-          <t>BA08-15</t>
+          <t>BA08-09</t>
         </is>
       </c>
       <c r="B1077" s="4" t="inlineStr">
@@ -30399,7 +30509,7 @@
     <row r="1078">
       <c r="A1078" s="4" t="inlineStr">
         <is>
-          <t>BA08-16</t>
+          <t>BA08-10</t>
         </is>
       </c>
       <c r="B1078" s="4" t="inlineStr">
@@ -30425,7 +30535,7 @@
     <row r="1079">
       <c r="A1079" s="4" t="inlineStr">
         <is>
-          <t>BA08-17</t>
+          <t>BA08-11</t>
         </is>
       </c>
       <c r="B1079" s="4" t="inlineStr">
@@ -30451,7 +30561,7 @@
     <row r="1080">
       <c r="A1080" s="4" t="inlineStr">
         <is>
-          <t>BA08-18</t>
+          <t>BA08-12</t>
         </is>
       </c>
       <c r="B1080" s="4" t="inlineStr">
@@ -30477,7 +30587,7 @@
     <row r="1081">
       <c r="A1081" s="4" t="inlineStr">
         <is>
-          <t>BA08-19</t>
+          <t>BA08-13</t>
         </is>
       </c>
       <c r="B1081" s="4" t="inlineStr">
@@ -30503,7 +30613,7 @@
     <row r="1082">
       <c r="A1082" s="4" t="inlineStr">
         <is>
-          <t>BA08-20</t>
+          <t>BA08-14</t>
         </is>
       </c>
       <c r="B1082" s="4" t="inlineStr">
@@ -30529,7 +30639,7 @@
     <row r="1083">
       <c r="A1083" s="4" t="inlineStr">
         <is>
-          <t>BA08-21</t>
+          <t>BA08-15</t>
         </is>
       </c>
       <c r="B1083" s="4" t="inlineStr">
@@ -30555,7 +30665,7 @@
     <row r="1084">
       <c r="A1084" s="4" t="inlineStr">
         <is>
-          <t>BA08-22</t>
+          <t>BA08-16</t>
         </is>
       </c>
       <c r="B1084" s="4" t="inlineStr">
@@ -30581,7 +30691,7 @@
     <row r="1085">
       <c r="A1085" s="4" t="inlineStr">
         <is>
-          <t>BA08-23</t>
+          <t>BA08-17</t>
         </is>
       </c>
       <c r="B1085" s="4" t="inlineStr">
@@ -30607,7 +30717,7 @@
     <row r="1086">
       <c r="A1086" s="4" t="inlineStr">
         <is>
-          <t>BA08-24</t>
+          <t>BA08-18</t>
         </is>
       </c>
       <c r="B1086" s="4" t="inlineStr">
@@ -30633,7 +30743,7 @@
     <row r="1087">
       <c r="A1087" s="4" t="inlineStr">
         <is>
-          <t>BA08-25</t>
+          <t>BA08-19</t>
         </is>
       </c>
       <c r="B1087" s="4" t="inlineStr">
@@ -30657,381 +30767,381 @@
       <c r="H1087" s="4" t="n"/>
     </row>
     <row r="1088">
-      <c r="A1088" s="2" t="inlineStr">
+      <c r="A1088" s="4" t="inlineStr">
+        <is>
+          <t>BA08-20</t>
+        </is>
+      </c>
+      <c r="B1088" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1088" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1088" s="4" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="E1088" s="4" t="n"/>
+      <c r="F1088" s="3" t="n"/>
+      <c r="G1088" s="4" t="n"/>
+      <c r="H1088" s="4" t="n"/>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="4" t="inlineStr">
+        <is>
+          <t>BA08-21</t>
+        </is>
+      </c>
+      <c r="B1089" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1089" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1089" s="4" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="E1089" s="4" t="n"/>
+      <c r="F1089" s="3" t="n"/>
+      <c r="G1089" s="4" t="n"/>
+      <c r="H1089" s="4" t="n"/>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="4" t="inlineStr">
+        <is>
+          <t>BA08-22</t>
+        </is>
+      </c>
+      <c r="B1090" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1090" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1090" s="4" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="E1090" s="4" t="n"/>
+      <c r="F1090" s="3" t="n"/>
+      <c r="G1090" s="4" t="n"/>
+      <c r="H1090" s="4" t="n"/>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="4" t="inlineStr">
+        <is>
+          <t>BA08-23</t>
+        </is>
+      </c>
+      <c r="B1091" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1091" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1091" s="4" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="E1091" s="4" t="n"/>
+      <c r="F1091" s="3" t="n"/>
+      <c r="G1091" s="4" t="n"/>
+      <c r="H1091" s="4" t="n"/>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="4" t="inlineStr">
+        <is>
+          <t>BA08-24</t>
+        </is>
+      </c>
+      <c r="B1092" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1092" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1092" s="4" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="E1092" s="4" t="n"/>
+      <c r="F1092" s="3" t="n"/>
+      <c r="G1092" s="4" t="n"/>
+      <c r="H1092" s="4" t="n"/>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="4" t="inlineStr">
+        <is>
+          <t>BA08-25</t>
+        </is>
+      </c>
+      <c r="B1093" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1093" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1093" s="4" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="E1093" s="4" t="n"/>
+      <c r="F1093" s="3" t="n"/>
+      <c r="G1093" s="4" t="n"/>
+      <c r="H1093" s="4" t="n"/>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="2" t="inlineStr">
         <is>
           <t>BA09-01</t>
         </is>
       </c>
-      <c r="B1088" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1088" s="2" t="inlineStr">
+      <c r="B1094" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1094" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1088" s="2" t="inlineStr">
+      <c r="D1094" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="E1088" s="2" t="inlineStr">
+      <c r="E1094" s="2" t="inlineStr">
         <is>
           <t>Deko Metallruten mit Pompons</t>
         </is>
       </c>
-      <c r="F1088" s="3" t="n">
+      <c r="F1094" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G1088" s="2" t="inlineStr">
+      <c r="G1094" s="2" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="H1088" s="2" t="n"/>
-    </row>
-    <row r="1089">
-      <c r="A1089" s="2" t="inlineStr">
+      <c r="H1094" s="2" t="n"/>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="2" t="inlineStr">
         <is>
           <t>BA09-02</t>
         </is>
       </c>
-      <c r="B1089" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1089" s="2" t="inlineStr">
+      <c r="B1095" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1095" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1089" s="2" t="inlineStr">
+      <c r="D1095" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="E1089" s="2" t="inlineStr">
+      <c r="E1095" s="2" t="inlineStr">
         <is>
           <t>Elefantenfuß groß</t>
         </is>
       </c>
-      <c r="F1089" s="3" t="n">
+      <c r="F1095" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G1089" s="2" t="inlineStr">
+      <c r="G1095" s="2" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="H1089" s="2" t="n"/>
-    </row>
-    <row r="1090">
-      <c r="A1090" s="2" t="inlineStr">
+      <c r="H1095" s="2" t="n"/>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="2" t="inlineStr">
         <is>
           <t>BA09-03</t>
         </is>
       </c>
-      <c r="B1090" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1090" s="2" t="inlineStr">
+      <c r="B1096" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1096" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1090" s="2" t="inlineStr">
+      <c r="D1096" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="E1090" s="2" t="inlineStr">
+      <c r="E1096" s="2" t="inlineStr">
         <is>
           <t>Werte-Rad</t>
         </is>
       </c>
-      <c r="F1090" s="3" t="n">
+      <c r="F1096" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G1090" s="2" t="inlineStr">
+      <c r="G1096" s="2" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="H1090" s="2" t="n"/>
-    </row>
-    <row r="1091">
-      <c r="A1091" s="2" t="inlineStr">
+      <c r="H1096" s="2" t="n"/>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="2" t="inlineStr">
         <is>
           <t>BA09-04</t>
         </is>
       </c>
-      <c r="B1091" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1091" s="2" t="inlineStr">
+      <c r="B1097" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1097" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1091" s="2" t="inlineStr">
+      <c r="D1097" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="E1091" s="2" t="inlineStr">
+      <c r="E1097" s="2" t="inlineStr">
         <is>
           <t>USM Haller Tisch</t>
         </is>
       </c>
-      <c r="F1091" s="3" t="n">
+      <c r="F1097" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G1091" s="2" t="inlineStr">
+      <c r="G1097" s="2" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="H1091" s="2" t="n"/>
-    </row>
-    <row r="1092">
-      <c r="A1092" s="2" t="inlineStr">
+      <c r="H1097" s="2" t="n"/>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="2" t="inlineStr">
         <is>
           <t>BA09-05</t>
         </is>
       </c>
-      <c r="B1092" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1092" s="2" t="inlineStr">
+      <c r="B1098" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1098" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1092" s="2" t="inlineStr">
+      <c r="D1098" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="E1092" s="2" t="inlineStr">
+      <c r="E1098" s="2" t="inlineStr">
         <is>
           <t>Kartell Masters Stuhl</t>
         </is>
       </c>
-      <c r="F1092" s="3" t="n">
+      <c r="F1098" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G1092" s="2" t="inlineStr">
+      <c r="G1098" s="2" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="H1092" s="2" t="n"/>
-    </row>
-    <row r="1093">
-      <c r="A1093" s="2" t="inlineStr">
+      <c r="H1098" s="2" t="n"/>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="2" t="inlineStr">
         <is>
           <t>BA09-06</t>
         </is>
       </c>
-      <c r="B1093" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1093" s="2" t="inlineStr">
+      <c r="B1099" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1099" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1093" s="2" t="inlineStr">
+      <c r="D1099" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="E1093" s="2" t="inlineStr">
+      <c r="E1099" s="2" t="inlineStr">
         <is>
           <t>Sitzhocker rund, drehbar auf Rollen</t>
         </is>
       </c>
-      <c r="F1093" s="3" t="n">
+      <c r="F1099" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G1093" s="2" t="inlineStr">
+      <c r="G1099" s="2" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="H1093" s="2" t="n"/>
-    </row>
-    <row r="1094">
-      <c r="A1094" s="4" t="inlineStr">
-        <is>
-          <t>BA09-07</t>
-        </is>
-      </c>
-      <c r="B1094" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1094" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1094" s="4" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="E1094" s="4" t="n"/>
-      <c r="F1094" s="3" t="n"/>
-      <c r="G1094" s="4" t="n"/>
-      <c r="H1094" s="4" t="n"/>
-    </row>
-    <row r="1095">
-      <c r="A1095" s="4" t="inlineStr">
-        <is>
-          <t>BA09-08</t>
-        </is>
-      </c>
-      <c r="B1095" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1095" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1095" s="4" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="E1095" s="4" t="n"/>
-      <c r="F1095" s="3" t="n"/>
-      <c r="G1095" s="4" t="n"/>
-      <c r="H1095" s="4" t="n"/>
-    </row>
-    <row r="1096">
-      <c r="A1096" s="4" t="inlineStr">
-        <is>
-          <t>BA09-09</t>
-        </is>
-      </c>
-      <c r="B1096" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1096" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1096" s="4" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="E1096" s="4" t="n"/>
-      <c r="F1096" s="3" t="n"/>
-      <c r="G1096" s="4" t="n"/>
-      <c r="H1096" s="4" t="n"/>
-    </row>
-    <row r="1097">
-      <c r="A1097" s="4" t="inlineStr">
-        <is>
-          <t>BA09-10</t>
-        </is>
-      </c>
-      <c r="B1097" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1097" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1097" s="4" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="E1097" s="4" t="n"/>
-      <c r="F1097" s="3" t="n"/>
-      <c r="G1097" s="4" t="n"/>
-      <c r="H1097" s="4" t="n"/>
-    </row>
-    <row r="1098">
-      <c r="A1098" s="4" t="inlineStr">
-        <is>
-          <t>BA09-11</t>
-        </is>
-      </c>
-      <c r="B1098" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1098" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1098" s="4" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="E1098" s="4" t="n"/>
-      <c r="F1098" s="3" t="n"/>
-      <c r="G1098" s="4" t="n"/>
-      <c r="H1098" s="4" t="n"/>
-    </row>
-    <row r="1099">
-      <c r="A1099" s="4" t="inlineStr">
-        <is>
-          <t>BA09-12</t>
-        </is>
-      </c>
-      <c r="B1099" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1099" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1099" s="4" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="E1099" s="4" t="n"/>
-      <c r="F1099" s="3" t="n"/>
-      <c r="G1099" s="4" t="n"/>
-      <c r="H1099" s="4" t="n"/>
+      <c r="H1099" s="2" t="n"/>
     </row>
     <row r="1100">
       <c r="A1100" s="4" t="inlineStr">
         <is>
-          <t>BA09-13</t>
+          <t>BA09-07</t>
         </is>
       </c>
       <c r="B1100" s="4" t="inlineStr">
@@ -31057,7 +31167,7 @@
     <row r="1101">
       <c r="A1101" s="4" t="inlineStr">
         <is>
-          <t>BA09-14</t>
+          <t>BA09-08</t>
         </is>
       </c>
       <c r="B1101" s="4" t="inlineStr">
@@ -31083,7 +31193,7 @@
     <row r="1102">
       <c r="A1102" s="4" t="inlineStr">
         <is>
-          <t>BA09-15</t>
+          <t>BA09-09</t>
         </is>
       </c>
       <c r="B1102" s="4" t="inlineStr">
@@ -31109,7 +31219,7 @@
     <row r="1103">
       <c r="A1103" s="4" t="inlineStr">
         <is>
-          <t>BA09-16</t>
+          <t>BA09-10</t>
         </is>
       </c>
       <c r="B1103" s="4" t="inlineStr">
@@ -31133,225 +31243,165 @@
       <c r="H1103" s="4" t="n"/>
     </row>
     <row r="1104">
-      <c r="A1104" s="2" t="inlineStr">
-        <is>
-          <t>BA10-01</t>
-        </is>
-      </c>
-      <c r="B1104" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1104" s="2" t="inlineStr">
+      <c r="A1104" s="4" t="inlineStr">
+        <is>
+          <t>BA09-11</t>
+        </is>
+      </c>
+      <c r="B1104" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1104" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1104" s="2" t="inlineStr">
-        <is>
-          <t>Ruhe- / Schlafraum</t>
-        </is>
-      </c>
-      <c r="E1104" s="2" t="inlineStr">
-        <is>
-          <t>Glastisch rund mit Chromgestell</t>
-        </is>
-      </c>
-      <c r="F1104" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1104" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1104" s="2" t="n"/>
+      <c r="D1104" s="4" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="E1104" s="4" t="n"/>
+      <c r="F1104" s="3" t="n"/>
+      <c r="G1104" s="4" t="n"/>
+      <c r="H1104" s="4" t="n"/>
     </row>
     <row r="1105">
-      <c r="A1105" s="2" t="inlineStr">
-        <is>
-          <t>BA10-02</t>
-        </is>
-      </c>
-      <c r="B1105" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1105" s="2" t="inlineStr">
+      <c r="A1105" s="4" t="inlineStr">
+        <is>
+          <t>BA09-12</t>
+        </is>
+      </c>
+      <c r="B1105" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1105" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1105" s="2" t="inlineStr">
-        <is>
-          <t>Ruhe- / Schlafraum</t>
-        </is>
-      </c>
-      <c r="E1105" s="2" t="inlineStr">
-        <is>
-          <t>Samtsofa bordeaux, 2-Sitzer</t>
-        </is>
-      </c>
-      <c r="F1105" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1105" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1105" s="2" t="n"/>
+      <c r="D1105" s="4" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="E1105" s="4" t="n"/>
+      <c r="F1105" s="3" t="n"/>
+      <c r="G1105" s="4" t="n"/>
+      <c r="H1105" s="4" t="n"/>
     </row>
     <row r="1106">
-      <c r="A1106" s="2" t="inlineStr">
-        <is>
-          <t>BA10-03</t>
-        </is>
-      </c>
-      <c r="B1106" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1106" s="2" t="inlineStr">
+      <c r="A1106" s="4" t="inlineStr">
+        <is>
+          <t>BA09-13</t>
+        </is>
+      </c>
+      <c r="B1106" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1106" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1106" s="2" t="inlineStr">
-        <is>
-          <t>Ruhe- / Schlafraum</t>
-        </is>
-      </c>
-      <c r="E1106" s="2" t="inlineStr">
-        <is>
-          <t>Sessel mit Bezug, weiß lackiert</t>
-        </is>
-      </c>
-      <c r="F1106" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1106" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1106" s="2" t="n"/>
+      <c r="D1106" s="4" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="E1106" s="4" t="n"/>
+      <c r="F1106" s="3" t="n"/>
+      <c r="G1106" s="4" t="n"/>
+      <c r="H1106" s="4" t="n"/>
     </row>
     <row r="1107">
-      <c r="A1107" s="2" t="inlineStr">
-        <is>
-          <t>BA10-04</t>
-        </is>
-      </c>
-      <c r="B1107" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1107" s="2" t="inlineStr">
+      <c r="A1107" s="4" t="inlineStr">
+        <is>
+          <t>BA09-14</t>
+        </is>
+      </c>
+      <c r="B1107" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1107" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1107" s="2" t="inlineStr">
-        <is>
-          <t>Ruhe- / Schlafraum</t>
-        </is>
-      </c>
-      <c r="E1107" s="2" t="inlineStr">
-        <is>
-          <t>Hocker grau mit Hairpin-Beinen</t>
-        </is>
-      </c>
-      <c r="F1107" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1107" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1107" s="2" t="n"/>
+      <c r="D1107" s="4" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="E1107" s="4" t="n"/>
+      <c r="F1107" s="3" t="n"/>
+      <c r="G1107" s="4" t="n"/>
+      <c r="H1107" s="4" t="n"/>
     </row>
     <row r="1108">
-      <c r="A1108" s="2" t="inlineStr">
-        <is>
-          <t>BA10-05</t>
-        </is>
-      </c>
-      <c r="B1108" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1108" s="2" t="inlineStr">
+      <c r="A1108" s="4" t="inlineStr">
+        <is>
+          <t>BA09-15</t>
+        </is>
+      </c>
+      <c r="B1108" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1108" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1108" s="2" t="inlineStr">
-        <is>
-          <t>Ruhe- / Schlafraum</t>
-        </is>
-      </c>
-      <c r="E1108" s="2" t="inlineStr">
-        <is>
-          <t>Ohrensessel grau mit Kufengestell</t>
-        </is>
-      </c>
-      <c r="F1108" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1108" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1108" s="2" t="n"/>
+      <c r="D1108" s="4" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="E1108" s="4" t="n"/>
+      <c r="F1108" s="3" t="n"/>
+      <c r="G1108" s="4" t="n"/>
+      <c r="H1108" s="4" t="n"/>
     </row>
     <row r="1109">
-      <c r="A1109" s="2" t="inlineStr">
-        <is>
-          <t>BA10-06</t>
-        </is>
-      </c>
-      <c r="B1109" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1109" s="2" t="inlineStr">
+      <c r="A1109" s="4" t="inlineStr">
+        <is>
+          <t>BA09-16</t>
+        </is>
+      </c>
+      <c r="B1109" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1109" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1109" s="2" t="inlineStr">
-        <is>
-          <t>Ruhe- / Schlafraum</t>
-        </is>
-      </c>
-      <c r="E1109" s="2" t="inlineStr">
-        <is>
-          <t>Hocker grau, passend</t>
-        </is>
-      </c>
-      <c r="F1109" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1109" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1109" s="2" t="n"/>
+      <c r="D1109" s="4" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="E1109" s="4" t="n"/>
+      <c r="F1109" s="3" t="n"/>
+      <c r="G1109" s="4" t="n"/>
+      <c r="H1109" s="4" t="n"/>
     </row>
     <row r="1110">
       <c r="A1110" s="2" t="inlineStr">
         <is>
-          <t>BA10-07</t>
+          <t>BA10-01</t>
         </is>
       </c>
       <c r="B1110" s="2" t="inlineStr">
@@ -31371,7 +31421,7 @@
       </c>
       <c r="E1110" s="2" t="inlineStr">
         <is>
-          <t>Beistelltisch rund grau</t>
+          <t>Glastisch rund mit Chromgestell</t>
         </is>
       </c>
       <c r="F1110" s="3" t="n">
@@ -31387,7 +31437,7 @@
     <row r="1111">
       <c r="A1111" s="2" t="inlineStr">
         <is>
-          <t>BA10-08</t>
+          <t>BA10-02</t>
         </is>
       </c>
       <c r="B1111" s="2" t="inlineStr">
@@ -31407,7 +31457,7 @@
       </c>
       <c r="E1111" s="2" t="inlineStr">
         <is>
-          <t>Pendelleuchte Drahtgeflecht</t>
+          <t>Samtsofa bordeaux, 2-Sitzer</t>
         </is>
       </c>
       <c r="F1111" s="3" t="n">
@@ -31423,7 +31473,7 @@
     <row r="1112">
       <c r="A1112" s="2" t="inlineStr">
         <is>
-          <t>BA10-09</t>
+          <t>BA10-03</t>
         </is>
       </c>
       <c r="B1112" s="2" t="inlineStr">
@@ -31443,11 +31493,11 @@
       </c>
       <c r="E1112" s="2" t="inlineStr">
         <is>
-          <t>Beistelltisch rund, Tablettplatte Birke</t>
+          <t>Sessel mit Bezug, weiß lackiert</t>
         </is>
       </c>
       <c r="F1112" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1112" s="2" t="inlineStr">
         <is>
@@ -31459,7 +31509,7 @@
     <row r="1113">
       <c r="A1113" s="2" t="inlineStr">
         <is>
-          <t>BA10-10</t>
+          <t>BA10-04</t>
         </is>
       </c>
       <c r="B1113" s="2" t="inlineStr">
@@ -31479,7 +31529,7 @@
       </c>
       <c r="E1113" s="2" t="inlineStr">
         <is>
-          <t>Beistelltisch rund, Tablettplatte schwarz</t>
+          <t>Hocker grau mit Hairpin-Beinen</t>
         </is>
       </c>
       <c r="F1113" s="3" t="n">
@@ -31495,199 +31545,259 @@
     <row r="1114">
       <c r="A1114" s="2" t="inlineStr">
         <is>
+          <t>BA10-05</t>
+        </is>
+      </c>
+      <c r="B1114" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1114" s="2" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1114" s="2" t="inlineStr">
+        <is>
+          <t>Ruhe- / Schlafraum</t>
+        </is>
+      </c>
+      <c r="E1114" s="2" t="inlineStr">
+        <is>
+          <t>Ohrensessel grau mit Kufengestell</t>
+        </is>
+      </c>
+      <c r="F1114" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1114" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1114" s="2" t="n"/>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="2" t="inlineStr">
+        <is>
+          <t>BA10-06</t>
+        </is>
+      </c>
+      <c r="B1115" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1115" s="2" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1115" s="2" t="inlineStr">
+        <is>
+          <t>Ruhe- / Schlafraum</t>
+        </is>
+      </c>
+      <c r="E1115" s="2" t="inlineStr">
+        <is>
+          <t>Hocker grau, passend</t>
+        </is>
+      </c>
+      <c r="F1115" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1115" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1115" s="2" t="n"/>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="2" t="inlineStr">
+        <is>
+          <t>BA10-07</t>
+        </is>
+      </c>
+      <c r="B1116" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1116" s="2" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1116" s="2" t="inlineStr">
+        <is>
+          <t>Ruhe- / Schlafraum</t>
+        </is>
+      </c>
+      <c r="E1116" s="2" t="inlineStr">
+        <is>
+          <t>Beistelltisch rund grau</t>
+        </is>
+      </c>
+      <c r="F1116" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1116" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1116" s="2" t="n"/>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="2" t="inlineStr">
+        <is>
+          <t>BA10-08</t>
+        </is>
+      </c>
+      <c r="B1117" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1117" s="2" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1117" s="2" t="inlineStr">
+        <is>
+          <t>Ruhe- / Schlafraum</t>
+        </is>
+      </c>
+      <c r="E1117" s="2" t="inlineStr">
+        <is>
+          <t>Pendelleuchte Drahtgeflecht</t>
+        </is>
+      </c>
+      <c r="F1117" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1117" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1117" s="2" t="n"/>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="2" t="inlineStr">
+        <is>
+          <t>BA10-09</t>
+        </is>
+      </c>
+      <c r="B1118" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1118" s="2" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1118" s="2" t="inlineStr">
+        <is>
+          <t>Ruhe- / Schlafraum</t>
+        </is>
+      </c>
+      <c r="E1118" s="2" t="inlineStr">
+        <is>
+          <t>Beistelltisch rund, Tablettplatte Birke</t>
+        </is>
+      </c>
+      <c r="F1118" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1118" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1118" s="2" t="n"/>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="2" t="inlineStr">
+        <is>
+          <t>BA10-10</t>
+        </is>
+      </c>
+      <c r="B1119" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1119" s="2" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1119" s="2" t="inlineStr">
+        <is>
+          <t>Ruhe- / Schlafraum</t>
+        </is>
+      </c>
+      <c r="E1119" s="2" t="inlineStr">
+        <is>
+          <t>Beistelltisch rund, Tablettplatte schwarz</t>
+        </is>
+      </c>
+      <c r="F1119" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1119" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1119" s="2" t="n"/>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="2" t="inlineStr">
+        <is>
           <t>BA10-11</t>
         </is>
       </c>
-      <c r="B1114" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1114" s="2" t="inlineStr">
+      <c r="B1120" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1120" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1114" s="2" t="inlineStr">
+      <c r="D1120" s="2" t="inlineStr">
         <is>
           <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
-      <c r="E1114" s="2" t="inlineStr">
+      <c r="E1120" s="2" t="inlineStr">
         <is>
           <t>Tisch rund, zweiteilig, weiß</t>
         </is>
       </c>
-      <c r="F1114" s="3" t="n">
+      <c r="F1120" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G1114" s="2" t="inlineStr">
+      <c r="G1120" s="2" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="H1114" s="2" t="n"/>
-    </row>
-    <row r="1115">
-      <c r="A1115" s="4" t="inlineStr">
-        <is>
-          <t>BA10-12</t>
-        </is>
-      </c>
-      <c r="B1115" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1115" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1115" s="4" t="inlineStr">
-        <is>
-          <t>Ruhe- / Schlafraum</t>
-        </is>
-      </c>
-      <c r="E1115" s="4" t="n"/>
-      <c r="F1115" s="3" t="n"/>
-      <c r="G1115" s="4" t="n"/>
-      <c r="H1115" s="4" t="n"/>
-    </row>
-    <row r="1116">
-      <c r="A1116" s="4" t="inlineStr">
-        <is>
-          <t>BA10-13</t>
-        </is>
-      </c>
-      <c r="B1116" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1116" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1116" s="4" t="inlineStr">
-        <is>
-          <t>Ruhe- / Schlafraum</t>
-        </is>
-      </c>
-      <c r="E1116" s="4" t="n"/>
-      <c r="F1116" s="3" t="n"/>
-      <c r="G1116" s="4" t="n"/>
-      <c r="H1116" s="4" t="n"/>
-    </row>
-    <row r="1117">
-      <c r="A1117" s="4" t="inlineStr">
-        <is>
-          <t>BA10-14</t>
-        </is>
-      </c>
-      <c r="B1117" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1117" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1117" s="4" t="inlineStr">
-        <is>
-          <t>Ruhe- / Schlafraum</t>
-        </is>
-      </c>
-      <c r="E1117" s="4" t="n"/>
-      <c r="F1117" s="3" t="n"/>
-      <c r="G1117" s="4" t="n"/>
-      <c r="H1117" s="4" t="n"/>
-    </row>
-    <row r="1118">
-      <c r="A1118" s="4" t="inlineStr">
-        <is>
-          <t>BA10-15</t>
-        </is>
-      </c>
-      <c r="B1118" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1118" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1118" s="4" t="inlineStr">
-        <is>
-          <t>Ruhe- / Schlafraum</t>
-        </is>
-      </c>
-      <c r="E1118" s="4" t="n"/>
-      <c r="F1118" s="3" t="n"/>
-      <c r="G1118" s="4" t="n"/>
-      <c r="H1118" s="4" t="n"/>
-    </row>
-    <row r="1119">
-      <c r="A1119" s="4" t="inlineStr">
-        <is>
-          <t>BA10-16</t>
-        </is>
-      </c>
-      <c r="B1119" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1119" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1119" s="4" t="inlineStr">
-        <is>
-          <t>Ruhe- / Schlafraum</t>
-        </is>
-      </c>
-      <c r="E1119" s="4" t="n"/>
-      <c r="F1119" s="3" t="n"/>
-      <c r="G1119" s="4" t="n"/>
-      <c r="H1119" s="4" t="n"/>
-    </row>
-    <row r="1120">
-      <c r="A1120" s="4" t="inlineStr">
-        <is>
-          <t>BA10-17</t>
-        </is>
-      </c>
-      <c r="B1120" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1120" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1120" s="4" t="inlineStr">
-        <is>
-          <t>Ruhe- / Schlafraum</t>
-        </is>
-      </c>
-      <c r="E1120" s="4" t="n"/>
-      <c r="F1120" s="3" t="n"/>
-      <c r="G1120" s="4" t="n"/>
-      <c r="H1120" s="4" t="n"/>
+      <c r="H1120" s="2" t="n"/>
     </row>
     <row r="1121">
       <c r="A1121" s="4" t="inlineStr">
         <is>
-          <t>BA10-18</t>
+          <t>BA10-12</t>
         </is>
       </c>
       <c r="B1121" s="4" t="inlineStr">
@@ -31713,7 +31823,7 @@
     <row r="1122">
       <c r="A1122" s="4" t="inlineStr">
         <is>
-          <t>BA10-19</t>
+          <t>BA10-13</t>
         </is>
       </c>
       <c r="B1122" s="4" t="inlineStr">
@@ -31739,7 +31849,7 @@
     <row r="1123">
       <c r="A1123" s="4" t="inlineStr">
         <is>
-          <t>BA10-20</t>
+          <t>BA10-14</t>
         </is>
       </c>
       <c r="B1123" s="4" t="inlineStr">
@@ -31765,7 +31875,7 @@
     <row r="1124">
       <c r="A1124" s="4" t="inlineStr">
         <is>
-          <t>BA10-21</t>
+          <t>BA10-15</t>
         </is>
       </c>
       <c r="B1124" s="4" t="inlineStr">
@@ -31791,7 +31901,7 @@
     <row r="1125">
       <c r="A1125" s="4" t="inlineStr">
         <is>
-          <t>BA11-01</t>
+          <t>BA10-16</t>
         </is>
       </c>
       <c r="B1125" s="4" t="inlineStr">
@@ -31806,7 +31916,7 @@
       </c>
       <c r="D1125" s="4" t="inlineStr">
         <is>
-          <t>WC Kinder</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="E1125" s="4" t="n"/>
@@ -31817,7 +31927,7 @@
     <row r="1126">
       <c r="A1126" s="4" t="inlineStr">
         <is>
-          <t>BA11-02</t>
+          <t>BA10-17</t>
         </is>
       </c>
       <c r="B1126" s="4" t="inlineStr">
@@ -31832,7 +31942,7 @@
       </c>
       <c r="D1126" s="4" t="inlineStr">
         <is>
-          <t>WC Kinder</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="E1126" s="4" t="n"/>
@@ -31843,7 +31953,7 @@
     <row r="1127">
       <c r="A1127" s="4" t="inlineStr">
         <is>
-          <t>BA11-03</t>
+          <t>BA10-18</t>
         </is>
       </c>
       <c r="B1127" s="4" t="inlineStr">
@@ -31858,7 +31968,7 @@
       </c>
       <c r="D1127" s="4" t="inlineStr">
         <is>
-          <t>WC Kinder</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="E1127" s="4" t="n"/>
@@ -31869,7 +31979,7 @@
     <row r="1128">
       <c r="A1128" s="4" t="inlineStr">
         <is>
-          <t>BA11-04</t>
+          <t>BA10-19</t>
         </is>
       </c>
       <c r="B1128" s="4" t="inlineStr">
@@ -31884,7 +31994,7 @@
       </c>
       <c r="D1128" s="4" t="inlineStr">
         <is>
-          <t>WC Kinder</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="E1128" s="4" t="n"/>
@@ -31895,7 +32005,7 @@
     <row r="1129">
       <c r="A1129" s="4" t="inlineStr">
         <is>
-          <t>BA11-05</t>
+          <t>BA10-20</t>
         </is>
       </c>
       <c r="B1129" s="4" t="inlineStr">
@@ -31910,7 +32020,7 @@
       </c>
       <c r="D1129" s="4" t="inlineStr">
         <is>
-          <t>WC Kinder</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="E1129" s="4" t="n"/>
@@ -31921,7 +32031,7 @@
     <row r="1130">
       <c r="A1130" s="4" t="inlineStr">
         <is>
-          <t>BA11-06</t>
+          <t>BA10-21</t>
         </is>
       </c>
       <c r="B1130" s="4" t="inlineStr">
@@ -31936,7 +32046,7 @@
       </c>
       <c r="D1130" s="4" t="inlineStr">
         <is>
-          <t>WC Kinder</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="E1130" s="4" t="n"/>
@@ -31947,7 +32057,7 @@
     <row r="1131">
       <c r="A1131" s="4" t="inlineStr">
         <is>
-          <t>BA11-07</t>
+          <t>BA11-01</t>
         </is>
       </c>
       <c r="B1131" s="4" t="inlineStr">
@@ -31973,7 +32083,7 @@
     <row r="1132">
       <c r="A1132" s="4" t="inlineStr">
         <is>
-          <t>BA11-08</t>
+          <t>BA11-02</t>
         </is>
       </c>
       <c r="B1132" s="4" t="inlineStr">
@@ -31999,7 +32109,7 @@
     <row r="1133">
       <c r="A1133" s="4" t="inlineStr">
         <is>
-          <t>BA11-09</t>
+          <t>BA11-03</t>
         </is>
       </c>
       <c r="B1133" s="4" t="inlineStr">
@@ -32025,7 +32135,7 @@
     <row r="1134">
       <c r="A1134" s="4" t="inlineStr">
         <is>
-          <t>BA11-10</t>
+          <t>BA11-04</t>
         </is>
       </c>
       <c r="B1134" s="4" t="inlineStr">
@@ -32051,7 +32161,7 @@
     <row r="1135">
       <c r="A1135" s="4" t="inlineStr">
         <is>
-          <t>BA11-11</t>
+          <t>BA11-05</t>
         </is>
       </c>
       <c r="B1135" s="4" t="inlineStr">
@@ -32077,7 +32187,7 @@
     <row r="1136">
       <c r="A1136" s="4" t="inlineStr">
         <is>
-          <t>BA11-12</t>
+          <t>BA11-06</t>
         </is>
       </c>
       <c r="B1136" s="4" t="inlineStr">
@@ -32103,7 +32213,7 @@
     <row r="1137">
       <c r="A1137" s="4" t="inlineStr">
         <is>
-          <t>BA11-13</t>
+          <t>BA11-07</t>
         </is>
       </c>
       <c r="B1137" s="4" t="inlineStr">
@@ -32129,7 +32239,7 @@
     <row r="1138">
       <c r="A1138" s="4" t="inlineStr">
         <is>
-          <t>BA11-14</t>
+          <t>BA11-08</t>
         </is>
       </c>
       <c r="B1138" s="4" t="inlineStr">
@@ -32155,7 +32265,7 @@
     <row r="1139">
       <c r="A1139" s="4" t="inlineStr">
         <is>
-          <t>BA11-15</t>
+          <t>BA11-09</t>
         </is>
       </c>
       <c r="B1139" s="4" t="inlineStr">
@@ -32179,45 +32289,35 @@
       <c r="H1139" s="4" t="n"/>
     </row>
     <row r="1140">
-      <c r="A1140" s="2" t="inlineStr">
-        <is>
-          <t>BA12-01</t>
-        </is>
-      </c>
-      <c r="B1140" s="2" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1140" s="2" t="inlineStr">
+      <c r="A1140" s="4" t="inlineStr">
+        <is>
+          <t>BA11-10</t>
+        </is>
+      </c>
+      <c r="B1140" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1140" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1140" s="2" t="inlineStr">
-        <is>
-          <t>WC Personal</t>
-        </is>
-      </c>
-      <c r="E1140" s="2" t="inlineStr">
-        <is>
-          <t>Ast-Mobile mit Papierwaben</t>
-        </is>
-      </c>
-      <c r="F1140" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1140" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1140" s="2" t="n"/>
+      <c r="D1140" s="4" t="inlineStr">
+        <is>
+          <t>WC Kinder</t>
+        </is>
+      </c>
+      <c r="E1140" s="4" t="n"/>
+      <c r="F1140" s="3" t="n"/>
+      <c r="G1140" s="4" t="n"/>
+      <c r="H1140" s="4" t="n"/>
     </row>
     <row r="1141">
       <c r="A1141" s="4" t="inlineStr">
         <is>
-          <t>BA12-02</t>
+          <t>BA11-11</t>
         </is>
       </c>
       <c r="B1141" s="4" t="inlineStr">
@@ -32232,7 +32332,7 @@
       </c>
       <c r="D1141" s="4" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>WC Kinder</t>
         </is>
       </c>
       <c r="E1141" s="4" t="n"/>
@@ -32243,7 +32343,7 @@
     <row r="1142">
       <c r="A1142" s="4" t="inlineStr">
         <is>
-          <t>BA12-03</t>
+          <t>BA11-12</t>
         </is>
       </c>
       <c r="B1142" s="4" t="inlineStr">
@@ -32258,7 +32358,7 @@
       </c>
       <c r="D1142" s="4" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>WC Kinder</t>
         </is>
       </c>
       <c r="E1142" s="4" t="n"/>
@@ -32269,7 +32369,7 @@
     <row r="1143">
       <c r="A1143" s="4" t="inlineStr">
         <is>
-          <t>BA12-04</t>
+          <t>BA11-13</t>
         </is>
       </c>
       <c r="B1143" s="4" t="inlineStr">
@@ -32284,7 +32384,7 @@
       </c>
       <c r="D1143" s="4" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>WC Kinder</t>
         </is>
       </c>
       <c r="E1143" s="4" t="n"/>
@@ -32295,7 +32395,7 @@
     <row r="1144">
       <c r="A1144" s="4" t="inlineStr">
         <is>
-          <t>BA12-05</t>
+          <t>BA11-14</t>
         </is>
       </c>
       <c r="B1144" s="4" t="inlineStr">
@@ -32310,7 +32410,7 @@
       </c>
       <c r="D1144" s="4" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>WC Kinder</t>
         </is>
       </c>
       <c r="E1144" s="4" t="n"/>
@@ -32321,7 +32421,7 @@
     <row r="1145">
       <c r="A1145" s="4" t="inlineStr">
         <is>
-          <t>BA12-06</t>
+          <t>BA11-15</t>
         </is>
       </c>
       <c r="B1145" s="4" t="inlineStr">
@@ -32336,7 +32436,7 @@
       </c>
       <c r="D1145" s="4" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>WC Kinder</t>
         </is>
       </c>
       <c r="E1145" s="4" t="n"/>
@@ -32345,35 +32445,45 @@
       <c r="H1145" s="4" t="n"/>
     </row>
     <row r="1146">
-      <c r="A1146" s="4" t="inlineStr">
-        <is>
-          <t>BA12-07</t>
-        </is>
-      </c>
-      <c r="B1146" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1146" s="4" t="inlineStr">
+      <c r="A1146" s="2" t="inlineStr">
+        <is>
+          <t>BA12-01</t>
+        </is>
+      </c>
+      <c r="B1146" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1146" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1146" s="4" t="inlineStr">
+      <c r="D1146" s="2" t="inlineStr">
         <is>
           <t>WC Personal</t>
         </is>
       </c>
-      <c r="E1146" s="4" t="n"/>
-      <c r="F1146" s="3" t="n"/>
-      <c r="G1146" s="4" t="n"/>
-      <c r="H1146" s="4" t="n"/>
+      <c r="E1146" s="2" t="inlineStr">
+        <is>
+          <t>Ast-Mobile mit Papierwaben</t>
+        </is>
+      </c>
+      <c r="F1146" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1146" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1146" s="2" t="n"/>
     </row>
     <row r="1147">
       <c r="A1147" s="4" t="inlineStr">
         <is>
-          <t>BA12-08</t>
+          <t>BA12-02</t>
         </is>
       </c>
       <c r="B1147" s="4" t="inlineStr">
@@ -32399,7 +32509,7 @@
     <row r="1148">
       <c r="A1148" s="4" t="inlineStr">
         <is>
-          <t>BA12-09</t>
+          <t>BA12-03</t>
         </is>
       </c>
       <c r="B1148" s="4" t="inlineStr">
@@ -32425,7 +32535,7 @@
     <row r="1149">
       <c r="A1149" s="4" t="inlineStr">
         <is>
-          <t>BA12-10</t>
+          <t>BA12-04</t>
         </is>
       </c>
       <c r="B1149" s="4" t="inlineStr">
@@ -32451,7 +32561,7 @@
     <row r="1150">
       <c r="A1150" s="4" t="inlineStr">
         <is>
-          <t>BA12-11</t>
+          <t>BA12-05</t>
         </is>
       </c>
       <c r="B1150" s="4" t="inlineStr">
@@ -32477,7 +32587,7 @@
     <row r="1151">
       <c r="A1151" s="4" t="inlineStr">
         <is>
-          <t>BA13-01</t>
+          <t>BA12-06</t>
         </is>
       </c>
       <c r="B1151" s="4" t="inlineStr">
@@ -32492,7 +32602,7 @@
       </c>
       <c r="D1151" s="4" t="inlineStr">
         <is>
-          <t>Abstellraum</t>
+          <t>WC Personal</t>
         </is>
       </c>
       <c r="E1151" s="4" t="n"/>
@@ -32503,7 +32613,7 @@
     <row r="1152">
       <c r="A1152" s="4" t="inlineStr">
         <is>
-          <t>BA13-02</t>
+          <t>BA12-07</t>
         </is>
       </c>
       <c r="B1152" s="4" t="inlineStr">
@@ -32518,7 +32628,7 @@
       </c>
       <c r="D1152" s="4" t="inlineStr">
         <is>
-          <t>Abstellraum</t>
+          <t>WC Personal</t>
         </is>
       </c>
       <c r="E1152" s="4" t="n"/>
@@ -32529,7 +32639,7 @@
     <row r="1153">
       <c r="A1153" s="4" t="inlineStr">
         <is>
-          <t>BA13-03</t>
+          <t>BA12-08</t>
         </is>
       </c>
       <c r="B1153" s="4" t="inlineStr">
@@ -32544,7 +32654,7 @@
       </c>
       <c r="D1153" s="4" t="inlineStr">
         <is>
-          <t>Abstellraum</t>
+          <t>WC Personal</t>
         </is>
       </c>
       <c r="E1153" s="4" t="n"/>
@@ -32555,7 +32665,7 @@
     <row r="1154">
       <c r="A1154" s="4" t="inlineStr">
         <is>
-          <t>BA13-04</t>
+          <t>BA12-09</t>
         </is>
       </c>
       <c r="B1154" s="4" t="inlineStr">
@@ -32570,7 +32680,7 @@
       </c>
       <c r="D1154" s="4" t="inlineStr">
         <is>
-          <t>Abstellraum</t>
+          <t>WC Personal</t>
         </is>
       </c>
       <c r="E1154" s="4" t="n"/>
@@ -32581,7 +32691,7 @@
     <row r="1155">
       <c r="A1155" s="4" t="inlineStr">
         <is>
-          <t>BA13-05</t>
+          <t>BA12-10</t>
         </is>
       </c>
       <c r="B1155" s="4" t="inlineStr">
@@ -32596,7 +32706,7 @@
       </c>
       <c r="D1155" s="4" t="inlineStr">
         <is>
-          <t>Abstellraum</t>
+          <t>WC Personal</t>
         </is>
       </c>
       <c r="E1155" s="4" t="n"/>
@@ -32607,7 +32717,7 @@
     <row r="1156">
       <c r="A1156" s="4" t="inlineStr">
         <is>
-          <t>BA13-06</t>
+          <t>BA12-11</t>
         </is>
       </c>
       <c r="B1156" s="4" t="inlineStr">
@@ -32622,7 +32732,7 @@
       </c>
       <c r="D1156" s="4" t="inlineStr">
         <is>
-          <t>Abstellraum</t>
+          <t>WC Personal</t>
         </is>
       </c>
       <c r="E1156" s="4" t="n"/>
@@ -32633,7 +32743,7 @@
     <row r="1157">
       <c r="A1157" s="4" t="inlineStr">
         <is>
-          <t>BA13-07</t>
+          <t>BA13-01</t>
         </is>
       </c>
       <c r="B1157" s="4" t="inlineStr">
@@ -32659,7 +32769,7 @@
     <row r="1158">
       <c r="A1158" s="4" t="inlineStr">
         <is>
-          <t>BA13-08</t>
+          <t>BA13-02</t>
         </is>
       </c>
       <c r="B1158" s="4" t="inlineStr">
@@ -32685,7 +32795,7 @@
     <row r="1159">
       <c r="A1159" s="4" t="inlineStr">
         <is>
-          <t>BA13-09</t>
+          <t>BA13-03</t>
         </is>
       </c>
       <c r="B1159" s="4" t="inlineStr">
@@ -32711,7 +32821,7 @@
     <row r="1160">
       <c r="A1160" s="4" t="inlineStr">
         <is>
-          <t>BA13-10</t>
+          <t>BA13-04</t>
         </is>
       </c>
       <c r="B1160" s="4" t="inlineStr">
@@ -32737,7 +32847,7 @@
     <row r="1161">
       <c r="A1161" s="4" t="inlineStr">
         <is>
-          <t>BA13-11</t>
+          <t>BA13-05</t>
         </is>
       </c>
       <c r="B1161" s="4" t="inlineStr">
@@ -32763,7 +32873,7 @@
     <row r="1162">
       <c r="A1162" s="4" t="inlineStr">
         <is>
-          <t>BA13-12</t>
+          <t>BA13-06</t>
         </is>
       </c>
       <c r="B1162" s="4" t="inlineStr">
@@ -32789,7 +32899,7 @@
     <row r="1163">
       <c r="A1163" s="4" t="inlineStr">
         <is>
-          <t>BA13-13</t>
+          <t>BA13-07</t>
         </is>
       </c>
       <c r="B1163" s="4" t="inlineStr">
@@ -32815,7 +32925,7 @@
     <row r="1164">
       <c r="A1164" s="4" t="inlineStr">
         <is>
-          <t>BA13-14</t>
+          <t>BA13-08</t>
         </is>
       </c>
       <c r="B1164" s="4" t="inlineStr">
@@ -32841,7 +32951,7 @@
     <row r="1165">
       <c r="A1165" s="4" t="inlineStr">
         <is>
-          <t>BA13-15</t>
+          <t>BA13-09</t>
         </is>
       </c>
       <c r="B1165" s="4" t="inlineStr">
@@ -32865,204 +32975,154 @@
       <c r="H1165" s="4" t="n"/>
     </row>
     <row r="1166">
-      <c r="A1166" s="2" t="inlineStr">
-        <is>
-          <t>TE01-01</t>
-        </is>
-      </c>
-      <c r="B1166" s="2" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1166" s="2" t="inlineStr">
-        <is>
-          <t>ebenerdig</t>
-        </is>
-      </c>
-      <c r="D1166" s="2" t="inlineStr">
-        <is>
-          <t>Terrasse</t>
-        </is>
-      </c>
-      <c r="E1166" s="2" t="inlineStr">
-        <is>
-          <t>Biohort Freizeitbox weiß (Terrasse)</t>
-        </is>
-      </c>
-      <c r="F1166" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1166" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1166" s="2" t="n"/>
+      <c r="A1166" s="4" t="inlineStr">
+        <is>
+          <t>BA13-10</t>
+        </is>
+      </c>
+      <c r="B1166" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1166" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1166" s="4" t="inlineStr">
+        <is>
+          <t>Abstellraum</t>
+        </is>
+      </c>
+      <c r="E1166" s="4" t="n"/>
+      <c r="F1166" s="3" t="n"/>
+      <c r="G1166" s="4" t="n"/>
+      <c r="H1166" s="4" t="n"/>
     </row>
     <row r="1167">
-      <c r="A1167" s="2" t="inlineStr">
-        <is>
-          <t>TE01-02</t>
-        </is>
-      </c>
-      <c r="B1167" s="2" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1167" s="2" t="inlineStr">
-        <is>
-          <t>ebenerdig</t>
-        </is>
-      </c>
-      <c r="D1167" s="2" t="inlineStr">
-        <is>
-          <t>Terrasse</t>
-        </is>
-      </c>
-      <c r="E1167" s="2" t="inlineStr">
-        <is>
-          <t>Gartentisch mit Granitplatte inkl. Stühle und Schutzhülle</t>
-        </is>
-      </c>
-      <c r="F1167" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1167" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1167" s="2" t="n"/>
+      <c r="A1167" s="4" t="inlineStr">
+        <is>
+          <t>BA13-11</t>
+        </is>
+      </c>
+      <c r="B1167" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1167" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1167" s="4" t="inlineStr">
+        <is>
+          <t>Abstellraum</t>
+        </is>
+      </c>
+      <c r="E1167" s="4" t="n"/>
+      <c r="F1167" s="3" t="n"/>
+      <c r="G1167" s="4" t="n"/>
+      <c r="H1167" s="4" t="n"/>
     </row>
     <row r="1168">
-      <c r="A1168" s="2" t="inlineStr">
-        <is>
-          <t>TE01-03</t>
-        </is>
-      </c>
-      <c r="B1168" s="2" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1168" s="2" t="inlineStr">
-        <is>
-          <t>ebenerdig</t>
-        </is>
-      </c>
-      <c r="D1168" s="2" t="inlineStr">
-        <is>
-          <t>Terrasse</t>
-        </is>
-      </c>
-      <c r="E1168" s="2" t="inlineStr">
-        <is>
-          <t>Textilene-Stapelsessel anthrazit</t>
-        </is>
-      </c>
-      <c r="F1168" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G1168" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1168" s="2" t="n"/>
+      <c r="A1168" s="4" t="inlineStr">
+        <is>
+          <t>BA13-12</t>
+        </is>
+      </c>
+      <c r="B1168" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1168" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1168" s="4" t="inlineStr">
+        <is>
+          <t>Abstellraum</t>
+        </is>
+      </c>
+      <c r="E1168" s="4" t="n"/>
+      <c r="F1168" s="3" t="n"/>
+      <c r="G1168" s="4" t="n"/>
+      <c r="H1168" s="4" t="n"/>
     </row>
     <row r="1169">
-      <c r="A1169" s="2" t="inlineStr">
-        <is>
-          <t>TE01-04</t>
-        </is>
-      </c>
-      <c r="B1169" s="2" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1169" s="2" t="inlineStr">
-        <is>
-          <t>ebenerdig</t>
-        </is>
-      </c>
-      <c r="D1169" s="2" t="inlineStr">
-        <is>
-          <t>Terrasse</t>
-        </is>
-      </c>
-      <c r="E1169" s="2" t="inlineStr">
-        <is>
-          <t>Weber Genesis Gasgrill</t>
-        </is>
-      </c>
-      <c r="F1169" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1169" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1169" s="2" t="n"/>
+      <c r="A1169" s="4" t="inlineStr">
+        <is>
+          <t>BA13-13</t>
+        </is>
+      </c>
+      <c r="B1169" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1169" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1169" s="4" t="inlineStr">
+        <is>
+          <t>Abstellraum</t>
+        </is>
+      </c>
+      <c r="E1169" s="4" t="n"/>
+      <c r="F1169" s="3" t="n"/>
+      <c r="G1169" s="4" t="n"/>
+      <c r="H1169" s="4" t="n"/>
     </row>
     <row r="1170">
-      <c r="A1170" s="2" t="inlineStr">
-        <is>
-          <t>TE01-05</t>
-        </is>
-      </c>
-      <c r="B1170" s="2" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1170" s="2" t="inlineStr">
-        <is>
-          <t>ebenerdig</t>
-        </is>
-      </c>
-      <c r="D1170" s="2" t="inlineStr">
-        <is>
-          <t>Terrasse</t>
-        </is>
-      </c>
-      <c r="E1170" s="2" t="inlineStr">
-        <is>
-          <t>Sonnenschirm creme</t>
-        </is>
-      </c>
-      <c r="F1170" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1170" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1170" s="2" t="n"/>
+      <c r="A1170" s="4" t="inlineStr">
+        <is>
+          <t>BA13-14</t>
+        </is>
+      </c>
+      <c r="B1170" s="4" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1170" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1170" s="4" t="inlineStr">
+        <is>
+          <t>Abstellraum</t>
+        </is>
+      </c>
+      <c r="E1170" s="4" t="n"/>
+      <c r="F1170" s="3" t="n"/>
+      <c r="G1170" s="4" t="n"/>
+      <c r="H1170" s="4" t="n"/>
     </row>
     <row r="1171">
       <c r="A1171" s="4" t="inlineStr">
         <is>
-          <t>TE01-06</t>
+          <t>BA13-15</t>
         </is>
       </c>
       <c r="B1171" s="4" t="inlineStr">
         <is>
-          <t>Außen</t>
+          <t>Bestandsgebäude</t>
         </is>
       </c>
       <c r="C1171" s="4" t="inlineStr">
         <is>
-          <t>ebenerdig</t>
+          <t>Attika</t>
         </is>
       </c>
       <c r="D1171" s="4" t="inlineStr">
         <is>
-          <t>Terrasse</t>
+          <t>Abstellraum</t>
         </is>
       </c>
       <c r="E1171" s="4" t="n"/>
@@ -33071,139 +33131,189 @@
       <c r="H1171" s="4" t="n"/>
     </row>
     <row r="1172">
-      <c r="A1172" s="4" t="inlineStr">
-        <is>
-          <t>TE01-07</t>
-        </is>
-      </c>
-      <c r="B1172" s="4" t="inlineStr">
+      <c r="A1172" s="2" t="inlineStr">
+        <is>
+          <t>TE01-01</t>
+        </is>
+      </c>
+      <c r="B1172" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1172" s="4" t="inlineStr">
+      <c r="C1172" s="2" t="inlineStr">
         <is>
           <t>ebenerdig</t>
         </is>
       </c>
-      <c r="D1172" s="4" t="inlineStr">
+      <c r="D1172" s="2" t="inlineStr">
         <is>
           <t>Terrasse</t>
         </is>
       </c>
-      <c r="E1172" s="4" t="n"/>
-      <c r="F1172" s="3" t="n"/>
-      <c r="G1172" s="4" t="n"/>
-      <c r="H1172" s="4" t="n"/>
+      <c r="E1172" s="2" t="inlineStr">
+        <is>
+          <t>Biohort Freizeitbox weiß (Terrasse)</t>
+        </is>
+      </c>
+      <c r="F1172" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1172" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1172" s="2" t="n"/>
     </row>
     <row r="1173">
-      <c r="A1173" s="4" t="inlineStr">
-        <is>
-          <t>TE01-08</t>
-        </is>
-      </c>
-      <c r="B1173" s="4" t="inlineStr">
+      <c r="A1173" s="2" t="inlineStr">
+        <is>
+          <t>TE01-02</t>
+        </is>
+      </c>
+      <c r="B1173" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1173" s="4" t="inlineStr">
+      <c r="C1173" s="2" t="inlineStr">
         <is>
           <t>ebenerdig</t>
         </is>
       </c>
-      <c r="D1173" s="4" t="inlineStr">
+      <c r="D1173" s="2" t="inlineStr">
         <is>
           <t>Terrasse</t>
         </is>
       </c>
-      <c r="E1173" s="4" t="n"/>
-      <c r="F1173" s="3" t="n"/>
-      <c r="G1173" s="4" t="n"/>
-      <c r="H1173" s="4" t="n"/>
+      <c r="E1173" s="2" t="inlineStr">
+        <is>
+          <t>Gartentisch mit Granitplatte inkl. Stühle und Schutzhülle</t>
+        </is>
+      </c>
+      <c r="F1173" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1173" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1173" s="2" t="n"/>
     </row>
     <row r="1174">
-      <c r="A1174" s="4" t="inlineStr">
-        <is>
-          <t>TE01-09</t>
-        </is>
-      </c>
-      <c r="B1174" s="4" t="inlineStr">
+      <c r="A1174" s="2" t="inlineStr">
+        <is>
+          <t>TE01-03</t>
+        </is>
+      </c>
+      <c r="B1174" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1174" s="4" t="inlineStr">
+      <c r="C1174" s="2" t="inlineStr">
         <is>
           <t>ebenerdig</t>
         </is>
       </c>
-      <c r="D1174" s="4" t="inlineStr">
+      <c r="D1174" s="2" t="inlineStr">
         <is>
           <t>Terrasse</t>
         </is>
       </c>
-      <c r="E1174" s="4" t="n"/>
-      <c r="F1174" s="3" t="n"/>
-      <c r="G1174" s="4" t="n"/>
-      <c r="H1174" s="4" t="n"/>
+      <c r="E1174" s="2" t="inlineStr">
+        <is>
+          <t>Textilene-Stapelsessel anthrazit</t>
+        </is>
+      </c>
+      <c r="F1174" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1174" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1174" s="2" t="n"/>
     </row>
     <row r="1175">
-      <c r="A1175" s="4" t="inlineStr">
-        <is>
-          <t>TE01-10</t>
-        </is>
-      </c>
-      <c r="B1175" s="4" t="inlineStr">
+      <c r="A1175" s="2" t="inlineStr">
+        <is>
+          <t>TE01-04</t>
+        </is>
+      </c>
+      <c r="B1175" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1175" s="4" t="inlineStr">
+      <c r="C1175" s="2" t="inlineStr">
         <is>
           <t>ebenerdig</t>
         </is>
       </c>
-      <c r="D1175" s="4" t="inlineStr">
+      <c r="D1175" s="2" t="inlineStr">
         <is>
           <t>Terrasse</t>
         </is>
       </c>
-      <c r="E1175" s="4" t="n"/>
-      <c r="F1175" s="3" t="n"/>
-      <c r="G1175" s="4" t="n"/>
-      <c r="H1175" s="4" t="n"/>
+      <c r="E1175" s="2" t="inlineStr">
+        <is>
+          <t>Weber Genesis Gasgrill</t>
+        </is>
+      </c>
+      <c r="F1175" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1175" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1175" s="2" t="n"/>
     </row>
     <row r="1176">
-      <c r="A1176" s="4" t="inlineStr">
-        <is>
-          <t>TE01-11</t>
-        </is>
-      </c>
-      <c r="B1176" s="4" t="inlineStr">
+      <c r="A1176" s="2" t="inlineStr">
+        <is>
+          <t>TE01-05</t>
+        </is>
+      </c>
+      <c r="B1176" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1176" s="4" t="inlineStr">
+      <c r="C1176" s="2" t="inlineStr">
         <is>
           <t>ebenerdig</t>
         </is>
       </c>
-      <c r="D1176" s="4" t="inlineStr">
+      <c r="D1176" s="2" t="inlineStr">
         <is>
           <t>Terrasse</t>
         </is>
       </c>
-      <c r="E1176" s="4" t="n"/>
-      <c r="F1176" s="3" t="n"/>
-      <c r="G1176" s="4" t="n"/>
-      <c r="H1176" s="4" t="n"/>
+      <c r="E1176" s="2" t="inlineStr">
+        <is>
+          <t>Sonnenschirm creme</t>
+        </is>
+      </c>
+      <c r="F1176" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1176" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1176" s="2" t="n"/>
     </row>
     <row r="1177">
       <c r="A1177" s="4" t="inlineStr">
         <is>
-          <t>TE01-12</t>
+          <t>TE01-06</t>
         </is>
       </c>
       <c r="B1177" s="4" t="inlineStr">
@@ -33229,7 +33339,7 @@
     <row r="1178">
       <c r="A1178" s="4" t="inlineStr">
         <is>
-          <t>TE01-13</t>
+          <t>TE01-07</t>
         </is>
       </c>
       <c r="B1178" s="4" t="inlineStr">
@@ -33255,7 +33365,7 @@
     <row r="1179">
       <c r="A1179" s="4" t="inlineStr">
         <is>
-          <t>TE01-14</t>
+          <t>TE01-08</t>
         </is>
       </c>
       <c r="B1179" s="4" t="inlineStr">
@@ -33281,7 +33391,7 @@
     <row r="1180">
       <c r="A1180" s="4" t="inlineStr">
         <is>
-          <t>TE01-15</t>
+          <t>TE01-09</t>
         </is>
       </c>
       <c r="B1180" s="4" t="inlineStr">
@@ -33307,7 +33417,7 @@
     <row r="1181">
       <c r="A1181" s="4" t="inlineStr">
         <is>
-          <t>TE01-16</t>
+          <t>TE01-10</t>
         </is>
       </c>
       <c r="B1181" s="4" t="inlineStr">
@@ -33333,7 +33443,7 @@
     <row r="1182">
       <c r="A1182" s="4" t="inlineStr">
         <is>
-          <t>TE01-17</t>
+          <t>TE01-11</t>
         </is>
       </c>
       <c r="B1182" s="4" t="inlineStr">
@@ -33359,7 +33469,7 @@
     <row r="1183">
       <c r="A1183" s="4" t="inlineStr">
         <is>
-          <t>TE01-18</t>
+          <t>TE01-12</t>
         </is>
       </c>
       <c r="B1183" s="4" t="inlineStr">
@@ -33385,7 +33495,7 @@
     <row r="1184">
       <c r="A1184" s="4" t="inlineStr">
         <is>
-          <t>TE01-19</t>
+          <t>TE01-13</t>
         </is>
       </c>
       <c r="B1184" s="4" t="inlineStr">
@@ -33411,7 +33521,7 @@
     <row r="1185">
       <c r="A1185" s="4" t="inlineStr">
         <is>
-          <t>TE01-20</t>
+          <t>TE01-14</t>
         </is>
       </c>
       <c r="B1185" s="4" t="inlineStr">
@@ -33437,7 +33547,7 @@
     <row r="1186">
       <c r="A1186" s="4" t="inlineStr">
         <is>
-          <t>TE01-21</t>
+          <t>TE01-15</t>
         </is>
       </c>
       <c r="B1186" s="4" t="inlineStr">
@@ -33463,7 +33573,7 @@
     <row r="1187">
       <c r="A1187" s="4" t="inlineStr">
         <is>
-          <t>TE01-22</t>
+          <t>TE01-16</t>
         </is>
       </c>
       <c r="B1187" s="4" t="inlineStr">
@@ -33489,7 +33599,7 @@
     <row r="1188">
       <c r="A1188" s="4" t="inlineStr">
         <is>
-          <t>TE01-23</t>
+          <t>TE01-17</t>
         </is>
       </c>
       <c r="B1188" s="4" t="inlineStr">
@@ -33515,7 +33625,7 @@
     <row r="1189">
       <c r="A1189" s="4" t="inlineStr">
         <is>
-          <t>TE01-24</t>
+          <t>TE01-18</t>
         </is>
       </c>
       <c r="B1189" s="4" t="inlineStr">
@@ -33541,7 +33651,7 @@
     <row r="1190">
       <c r="A1190" s="4" t="inlineStr">
         <is>
-          <t>TE01-25</t>
+          <t>TE01-19</t>
         </is>
       </c>
       <c r="B1190" s="4" t="inlineStr">
@@ -33567,7 +33677,7 @@
     <row r="1191">
       <c r="A1191" s="4" t="inlineStr">
         <is>
-          <t>TE01-26</t>
+          <t>TE01-20</t>
         </is>
       </c>
       <c r="B1191" s="4" t="inlineStr">
@@ -33593,7 +33703,7 @@
     <row r="1192">
       <c r="A1192" s="4" t="inlineStr">
         <is>
-          <t>TE01-27</t>
+          <t>TE01-21</t>
         </is>
       </c>
       <c r="B1192" s="4" t="inlineStr">
@@ -33619,7 +33729,7 @@
     <row r="1193">
       <c r="A1193" s="4" t="inlineStr">
         <is>
-          <t>TE01-28</t>
+          <t>TE01-22</t>
         </is>
       </c>
       <c r="B1193" s="4" t="inlineStr">
@@ -33645,7 +33755,7 @@
     <row r="1194">
       <c r="A1194" s="4" t="inlineStr">
         <is>
-          <t>TE01-29</t>
+          <t>TE01-23</t>
         </is>
       </c>
       <c r="B1194" s="4" t="inlineStr">
@@ -33671,7 +33781,7 @@
     <row r="1195">
       <c r="A1195" s="4" t="inlineStr">
         <is>
-          <t>TE01-30</t>
+          <t>TE01-24</t>
         </is>
       </c>
       <c r="B1195" s="4" t="inlineStr">
@@ -33697,7 +33807,7 @@
     <row r="1196">
       <c r="A1196" s="4" t="inlineStr">
         <is>
-          <t>TE01-31</t>
+          <t>TE01-25</t>
         </is>
       </c>
       <c r="B1196" s="4" t="inlineStr">
@@ -33723,7 +33833,7 @@
     <row r="1197">
       <c r="A1197" s="4" t="inlineStr">
         <is>
-          <t>TE01-32</t>
+          <t>TE01-26</t>
         </is>
       </c>
       <c r="B1197" s="4" t="inlineStr">
@@ -33749,7 +33859,7 @@
     <row r="1198">
       <c r="A1198" s="4" t="inlineStr">
         <is>
-          <t>TE01-33</t>
+          <t>TE01-27</t>
         </is>
       </c>
       <c r="B1198" s="4" t="inlineStr">
@@ -33775,7 +33885,7 @@
     <row r="1199">
       <c r="A1199" s="4" t="inlineStr">
         <is>
-          <t>TE01-34</t>
+          <t>TE01-28</t>
         </is>
       </c>
       <c r="B1199" s="4" t="inlineStr">
@@ -33801,7 +33911,7 @@
     <row r="1200">
       <c r="A1200" s="4" t="inlineStr">
         <is>
-          <t>TE01-35</t>
+          <t>TE01-29</t>
         </is>
       </c>
       <c r="B1200" s="4" t="inlineStr">
@@ -33827,7 +33937,7 @@
     <row r="1201">
       <c r="A1201" s="4" t="inlineStr">
         <is>
-          <t>TE01-36</t>
+          <t>TE01-30</t>
         </is>
       </c>
       <c r="B1201" s="4" t="inlineStr">
@@ -33853,7 +33963,7 @@
     <row r="1202">
       <c r="A1202" s="4" t="inlineStr">
         <is>
-          <t>TE01-37</t>
+          <t>TE01-31</t>
         </is>
       </c>
       <c r="B1202" s="4" t="inlineStr">
@@ -33879,7 +33989,7 @@
     <row r="1203">
       <c r="A1203" s="4" t="inlineStr">
         <is>
-          <t>TE01-38</t>
+          <t>TE01-32</t>
         </is>
       </c>
       <c r="B1203" s="4" t="inlineStr">
@@ -33905,7 +34015,7 @@
     <row r="1204">
       <c r="A1204" s="4" t="inlineStr">
         <is>
-          <t>TE01-39</t>
+          <t>TE01-33</t>
         </is>
       </c>
       <c r="B1204" s="4" t="inlineStr">
@@ -33931,7 +34041,7 @@
     <row r="1205">
       <c r="A1205" s="4" t="inlineStr">
         <is>
-          <t>TE01-40</t>
+          <t>TE01-34</t>
         </is>
       </c>
       <c r="B1205" s="4" t="inlineStr">
@@ -33955,381 +34065,381 @@
       <c r="H1205" s="4" t="n"/>
     </row>
     <row r="1206">
-      <c r="A1206" s="2" t="inlineStr">
+      <c r="A1206" s="4" t="inlineStr">
+        <is>
+          <t>TE01-35</t>
+        </is>
+      </c>
+      <c r="B1206" s="4" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1206" s="4" t="inlineStr">
+        <is>
+          <t>ebenerdig</t>
+        </is>
+      </c>
+      <c r="D1206" s="4" t="inlineStr">
+        <is>
+          <t>Terrasse</t>
+        </is>
+      </c>
+      <c r="E1206" s="4" t="n"/>
+      <c r="F1206" s="3" t="n"/>
+      <c r="G1206" s="4" t="n"/>
+      <c r="H1206" s="4" t="n"/>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="4" t="inlineStr">
+        <is>
+          <t>TE01-36</t>
+        </is>
+      </c>
+      <c r="B1207" s="4" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1207" s="4" t="inlineStr">
+        <is>
+          <t>ebenerdig</t>
+        </is>
+      </c>
+      <c r="D1207" s="4" t="inlineStr">
+        <is>
+          <t>Terrasse</t>
+        </is>
+      </c>
+      <c r="E1207" s="4" t="n"/>
+      <c r="F1207" s="3" t="n"/>
+      <c r="G1207" s="4" t="n"/>
+      <c r="H1207" s="4" t="n"/>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="4" t="inlineStr">
+        <is>
+          <t>TE01-37</t>
+        </is>
+      </c>
+      <c r="B1208" s="4" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1208" s="4" t="inlineStr">
+        <is>
+          <t>ebenerdig</t>
+        </is>
+      </c>
+      <c r="D1208" s="4" t="inlineStr">
+        <is>
+          <t>Terrasse</t>
+        </is>
+      </c>
+      <c r="E1208" s="4" t="n"/>
+      <c r="F1208" s="3" t="n"/>
+      <c r="G1208" s="4" t="n"/>
+      <c r="H1208" s="4" t="n"/>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="4" t="inlineStr">
+        <is>
+          <t>TE01-38</t>
+        </is>
+      </c>
+      <c r="B1209" s="4" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1209" s="4" t="inlineStr">
+        <is>
+          <t>ebenerdig</t>
+        </is>
+      </c>
+      <c r="D1209" s="4" t="inlineStr">
+        <is>
+          <t>Terrasse</t>
+        </is>
+      </c>
+      <c r="E1209" s="4" t="n"/>
+      <c r="F1209" s="3" t="n"/>
+      <c r="G1209" s="4" t="n"/>
+      <c r="H1209" s="4" t="n"/>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="4" t="inlineStr">
+        <is>
+          <t>TE01-39</t>
+        </is>
+      </c>
+      <c r="B1210" s="4" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1210" s="4" t="inlineStr">
+        <is>
+          <t>ebenerdig</t>
+        </is>
+      </c>
+      <c r="D1210" s="4" t="inlineStr">
+        <is>
+          <t>Terrasse</t>
+        </is>
+      </c>
+      <c r="E1210" s="4" t="n"/>
+      <c r="F1210" s="3" t="n"/>
+      <c r="G1210" s="4" t="n"/>
+      <c r="H1210" s="4" t="n"/>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="4" t="inlineStr">
+        <is>
+          <t>TE01-40</t>
+        </is>
+      </c>
+      <c r="B1211" s="4" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1211" s="4" t="inlineStr">
+        <is>
+          <t>ebenerdig</t>
+        </is>
+      </c>
+      <c r="D1211" s="4" t="inlineStr">
+        <is>
+          <t>Terrasse</t>
+        </is>
+      </c>
+      <c r="E1211" s="4" t="n"/>
+      <c r="F1211" s="3" t="n"/>
+      <c r="G1211" s="4" t="n"/>
+      <c r="H1211" s="4" t="n"/>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="2" t="inlineStr">
         <is>
           <t>TE02-01</t>
         </is>
       </c>
-      <c r="B1206" s="2" t="inlineStr">
+      <c r="B1212" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1206" s="2" t="inlineStr">
+      <c r="C1212" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1206" s="2" t="inlineStr">
+      <c r="D1212" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1206" s="2" t="inlineStr">
+      <c r="E1212" s="2" t="inlineStr">
         <is>
           <t>Pflanzkübel Plastik weiß</t>
         </is>
       </c>
-      <c r="F1206" s="3" t="n">
+      <c r="F1212" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G1206" s="2" t="inlineStr">
+      <c r="G1212" s="2" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="H1206" s="2" t="n"/>
-    </row>
-    <row r="1207">
-      <c r="A1207" s="2" t="inlineStr">
+      <c r="H1212" s="2" t="n"/>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="2" t="inlineStr">
         <is>
           <t>TE02-02</t>
         </is>
       </c>
-      <c r="B1207" s="2" t="inlineStr">
+      <c r="B1213" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1207" s="2" t="inlineStr">
+      <c r="C1213" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1207" s="2" t="inlineStr">
+      <c r="D1213" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1207" s="2" t="inlineStr">
+      <c r="E1213" s="2" t="inlineStr">
         <is>
           <t>Gartenstuhl Kunststoff anthrazit</t>
         </is>
       </c>
-      <c r="F1207" s="3" t="n">
+      <c r="F1213" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G1207" s="2" t="inlineStr">
+      <c r="G1213" s="2" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="H1207" s="2" t="n"/>
-    </row>
-    <row r="1208">
-      <c r="A1208" s="2" t="inlineStr">
+      <c r="H1213" s="2" t="n"/>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="2" t="inlineStr">
         <is>
           <t>TE02-03</t>
         </is>
       </c>
-      <c r="B1208" s="2" t="inlineStr">
+      <c r="B1214" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1208" s="2" t="inlineStr">
+      <c r="C1214" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1208" s="2" t="inlineStr">
+      <c r="D1214" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1208" s="2" t="inlineStr">
+      <c r="E1214" s="2" t="inlineStr">
         <is>
           <t>Gartentisch anthrazit</t>
         </is>
       </c>
-      <c r="F1208" s="3" t="n">
+      <c r="F1214" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G1208" s="2" t="inlineStr">
+      <c r="G1214" s="2" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="H1208" s="2" t="n"/>
-    </row>
-    <row r="1209">
-      <c r="A1209" s="2" t="inlineStr">
+      <c r="H1214" s="2" t="n"/>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="2" t="inlineStr">
         <is>
           <t>TE02-04</t>
         </is>
       </c>
-      <c r="B1209" s="2" t="inlineStr">
+      <c r="B1215" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1209" s="2" t="inlineStr">
+      <c r="C1215" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1209" s="2" t="inlineStr">
+      <c r="D1215" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1209" s="2" t="inlineStr">
+      <c r="E1215" s="2" t="inlineStr">
         <is>
           <t>Teak-Klapptisch rund</t>
         </is>
       </c>
-      <c r="F1209" s="3" t="n">
+      <c r="F1215" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G1209" s="2" t="inlineStr">
+      <c r="G1215" s="2" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="H1209" s="2" t="n"/>
-    </row>
-    <row r="1210">
-      <c r="A1210" s="2" t="inlineStr">
+      <c r="H1215" s="2" t="n"/>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="2" t="inlineStr">
         <is>
           <t>TE02-05</t>
         </is>
       </c>
-      <c r="B1210" s="2" t="inlineStr">
+      <c r="B1216" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1210" s="2" t="inlineStr">
+      <c r="C1216" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1210" s="2" t="inlineStr">
+      <c r="D1216" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1210" s="2" t="inlineStr">
+      <c r="E1216" s="2" t="inlineStr">
         <is>
           <t>Pflanzkübel grau, groß</t>
         </is>
       </c>
-      <c r="F1210" s="3" t="n">
+      <c r="F1216" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G1210" s="2" t="inlineStr">
+      <c r="G1216" s="2" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="H1210" s="2" t="n"/>
-    </row>
-    <row r="1211">
-      <c r="A1211" s="2" t="inlineStr">
+      <c r="H1216" s="2" t="n"/>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="2" t="inlineStr">
         <is>
           <t>TE02-06</t>
         </is>
       </c>
-      <c r="B1211" s="2" t="inlineStr">
+      <c r="B1217" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1211" s="2" t="inlineStr">
+      <c r="C1217" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1211" s="2" t="inlineStr">
+      <c r="D1217" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1211" s="2" t="inlineStr">
+      <c r="E1217" s="2" t="inlineStr">
         <is>
           <t>Holzstern mit Lichterkette</t>
         </is>
       </c>
-      <c r="F1211" s="3" t="n">
+      <c r="F1217" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G1211" s="2" t="inlineStr">
+      <c r="G1217" s="2" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="H1211" s="2" t="n"/>
-    </row>
-    <row r="1212">
-      <c r="A1212" s="4" t="inlineStr">
-        <is>
-          <t>TE02-07</t>
-        </is>
-      </c>
-      <c r="B1212" s="4" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1212" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1212" s="4" t="inlineStr">
-        <is>
-          <t>Dachterrasse</t>
-        </is>
-      </c>
-      <c r="E1212" s="4" t="n"/>
-      <c r="F1212" s="3" t="n"/>
-      <c r="G1212" s="4" t="n"/>
-      <c r="H1212" s="4" t="n"/>
-    </row>
-    <row r="1213">
-      <c r="A1213" s="4" t="inlineStr">
-        <is>
-          <t>TE02-08</t>
-        </is>
-      </c>
-      <c r="B1213" s="4" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1213" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1213" s="4" t="inlineStr">
-        <is>
-          <t>Dachterrasse</t>
-        </is>
-      </c>
-      <c r="E1213" s="4" t="n"/>
-      <c r="F1213" s="3" t="n"/>
-      <c r="G1213" s="4" t="n"/>
-      <c r="H1213" s="4" t="n"/>
-    </row>
-    <row r="1214">
-      <c r="A1214" s="4" t="inlineStr">
-        <is>
-          <t>TE02-09</t>
-        </is>
-      </c>
-      <c r="B1214" s="4" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1214" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1214" s="4" t="inlineStr">
-        <is>
-          <t>Dachterrasse</t>
-        </is>
-      </c>
-      <c r="E1214" s="4" t="n"/>
-      <c r="F1214" s="3" t="n"/>
-      <c r="G1214" s="4" t="n"/>
-      <c r="H1214" s="4" t="n"/>
-    </row>
-    <row r="1215">
-      <c r="A1215" s="4" t="inlineStr">
-        <is>
-          <t>TE02-10</t>
-        </is>
-      </c>
-      <c r="B1215" s="4" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1215" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1215" s="4" t="inlineStr">
-        <is>
-          <t>Dachterrasse</t>
-        </is>
-      </c>
-      <c r="E1215" s="4" t="n"/>
-      <c r="F1215" s="3" t="n"/>
-      <c r="G1215" s="4" t="n"/>
-      <c r="H1215" s="4" t="n"/>
-    </row>
-    <row r="1216">
-      <c r="A1216" s="4" t="inlineStr">
-        <is>
-          <t>TE02-11</t>
-        </is>
-      </c>
-      <c r="B1216" s="4" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1216" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1216" s="4" t="inlineStr">
-        <is>
-          <t>Dachterrasse</t>
-        </is>
-      </c>
-      <c r="E1216" s="4" t="n"/>
-      <c r="F1216" s="3" t="n"/>
-      <c r="G1216" s="4" t="n"/>
-      <c r="H1216" s="4" t="n"/>
-    </row>
-    <row r="1217">
-      <c r="A1217" s="4" t="inlineStr">
-        <is>
-          <t>TE02-12</t>
-        </is>
-      </c>
-      <c r="B1217" s="4" t="inlineStr">
-        <is>
-          <t>Außen</t>
-        </is>
-      </c>
-      <c r="C1217" s="4" t="inlineStr">
-        <is>
-          <t>Attika</t>
-        </is>
-      </c>
-      <c r="D1217" s="4" t="inlineStr">
-        <is>
-          <t>Dachterrasse</t>
-        </is>
-      </c>
-      <c r="E1217" s="4" t="n"/>
-      <c r="F1217" s="3" t="n"/>
-      <c r="G1217" s="4" t="n"/>
-      <c r="H1217" s="4" t="n"/>
+      <c r="H1217" s="2" t="n"/>
     </row>
     <row r="1218">
       <c r="A1218" s="4" t="inlineStr">
         <is>
-          <t>TE02-13</t>
+          <t>TE02-07</t>
         </is>
       </c>
       <c r="B1218" s="4" t="inlineStr">
@@ -34355,7 +34465,7 @@
     <row r="1219">
       <c r="A1219" s="4" t="inlineStr">
         <is>
-          <t>TE02-14</t>
+          <t>TE02-08</t>
         </is>
       </c>
       <c r="B1219" s="4" t="inlineStr">
@@ -34381,7 +34491,7 @@
     <row r="1220">
       <c r="A1220" s="4" t="inlineStr">
         <is>
-          <t>TE02-15</t>
+          <t>TE02-09</t>
         </is>
       </c>
       <c r="B1220" s="4" t="inlineStr">
@@ -34407,7 +34517,7 @@
     <row r="1221">
       <c r="A1221" s="4" t="inlineStr">
         <is>
-          <t>TE02-16</t>
+          <t>TE02-10</t>
         </is>
       </c>
       <c r="B1221" s="4" t="inlineStr">
@@ -34433,7 +34543,7 @@
     <row r="1222">
       <c r="A1222" s="4" t="inlineStr">
         <is>
-          <t>TE02-17</t>
+          <t>TE02-11</t>
         </is>
       </c>
       <c r="B1222" s="4" t="inlineStr">
@@ -34459,7 +34569,7 @@
     <row r="1223">
       <c r="A1223" s="4" t="inlineStr">
         <is>
-          <t>TE02-18</t>
+          <t>TE02-12</t>
         </is>
       </c>
       <c r="B1223" s="4" t="inlineStr">
@@ -34485,7 +34595,7 @@
     <row r="1224">
       <c r="A1224" s="4" t="inlineStr">
         <is>
-          <t>TE02-19</t>
+          <t>TE02-13</t>
         </is>
       </c>
       <c r="B1224" s="4" t="inlineStr">
@@ -34511,7 +34621,7 @@
     <row r="1225">
       <c r="A1225" s="4" t="inlineStr">
         <is>
-          <t>TE02-20</t>
+          <t>TE02-14</t>
         </is>
       </c>
       <c r="B1225" s="4" t="inlineStr">
@@ -34537,7 +34647,7 @@
     <row r="1226">
       <c r="A1226" s="4" t="inlineStr">
         <is>
-          <t>TE02-21</t>
+          <t>TE02-15</t>
         </is>
       </c>
       <c r="B1226" s="4" t="inlineStr">
@@ -34563,7 +34673,7 @@
     <row r="1227">
       <c r="A1227" s="4" t="inlineStr">
         <is>
-          <t>TE02-22</t>
+          <t>TE02-16</t>
         </is>
       </c>
       <c r="B1227" s="4" t="inlineStr">
@@ -34589,7 +34699,7 @@
     <row r="1228">
       <c r="A1228" s="4" t="inlineStr">
         <is>
-          <t>TE02-23</t>
+          <t>TE02-17</t>
         </is>
       </c>
       <c r="B1228" s="4" t="inlineStr">
@@ -34615,7 +34725,7 @@
     <row r="1229">
       <c r="A1229" s="4" t="inlineStr">
         <is>
-          <t>TE02-24</t>
+          <t>TE02-18</t>
         </is>
       </c>
       <c r="B1229" s="4" t="inlineStr">
@@ -34641,7 +34751,7 @@
     <row r="1230">
       <c r="A1230" s="4" t="inlineStr">
         <is>
-          <t>TE02-25</t>
+          <t>TE02-19</t>
         </is>
       </c>
       <c r="B1230" s="4" t="inlineStr">
@@ -34667,7 +34777,7 @@
     <row r="1231">
       <c r="A1231" s="4" t="inlineStr">
         <is>
-          <t>TE02-26</t>
+          <t>TE02-20</t>
         </is>
       </c>
       <c r="B1231" s="4" t="inlineStr">
@@ -34693,7 +34803,7 @@
     <row r="1232">
       <c r="A1232" s="4" t="inlineStr">
         <is>
-          <t>TE02-27</t>
+          <t>TE02-21</t>
         </is>
       </c>
       <c r="B1232" s="4" t="inlineStr">
@@ -34719,7 +34829,7 @@
     <row r="1233">
       <c r="A1233" s="4" t="inlineStr">
         <is>
-          <t>TE02-28</t>
+          <t>TE02-22</t>
         </is>
       </c>
       <c r="B1233" s="4" t="inlineStr">
@@ -34745,7 +34855,7 @@
     <row r="1234">
       <c r="A1234" s="4" t="inlineStr">
         <is>
-          <t>TE02-29</t>
+          <t>TE02-23</t>
         </is>
       </c>
       <c r="B1234" s="4" t="inlineStr">
@@ -34771,7 +34881,7 @@
     <row r="1235">
       <c r="A1235" s="4" t="inlineStr">
         <is>
-          <t>TE02-30</t>
+          <t>TE02-24</t>
         </is>
       </c>
       <c r="B1235" s="4" t="inlineStr">
@@ -34797,7 +34907,7 @@
     <row r="1236">
       <c r="A1236" s="4" t="inlineStr">
         <is>
-          <t>TE02-31</t>
+          <t>TE02-25</t>
         </is>
       </c>
       <c r="B1236" s="4" t="inlineStr">
@@ -34823,7 +34933,7 @@
     <row r="1237">
       <c r="A1237" s="4" t="inlineStr">
         <is>
-          <t>TE02-32</t>
+          <t>TE02-26</t>
         </is>
       </c>
       <c r="B1237" s="4" t="inlineStr">
@@ -34849,7 +34959,7 @@
     <row r="1238">
       <c r="A1238" s="4" t="inlineStr">
         <is>
-          <t>TE02-33</t>
+          <t>TE02-27</t>
         </is>
       </c>
       <c r="B1238" s="4" t="inlineStr">
@@ -34875,7 +34985,7 @@
     <row r="1239">
       <c r="A1239" s="4" t="inlineStr">
         <is>
-          <t>TE02-34</t>
+          <t>TE02-28</t>
         </is>
       </c>
       <c r="B1239" s="4" t="inlineStr">
@@ -34901,7 +35011,7 @@
     <row r="1240">
       <c r="A1240" s="4" t="inlineStr">
         <is>
-          <t>TE02-35</t>
+          <t>TE02-29</t>
         </is>
       </c>
       <c r="B1240" s="4" t="inlineStr">
@@ -34927,7 +35037,7 @@
     <row r="1241">
       <c r="A1241" s="4" t="inlineStr">
         <is>
-          <t>TE02-36</t>
+          <t>TE02-30</t>
         </is>
       </c>
       <c r="B1241" s="4" t="inlineStr">
@@ -34953,7 +35063,7 @@
     <row r="1242">
       <c r="A1242" s="4" t="inlineStr">
         <is>
-          <t>TE02-37</t>
+          <t>TE02-31</t>
         </is>
       </c>
       <c r="B1242" s="4" t="inlineStr">
@@ -34979,7 +35089,7 @@
     <row r="1243">
       <c r="A1243" s="4" t="inlineStr">
         <is>
-          <t>TE02-38</t>
+          <t>TE02-32</t>
         </is>
       </c>
       <c r="B1243" s="4" t="inlineStr">
@@ -35005,7 +35115,7 @@
     <row r="1244">
       <c r="A1244" s="4" t="inlineStr">
         <is>
-          <t>TE02-39</t>
+          <t>TE02-33</t>
         </is>
       </c>
       <c r="B1244" s="4" t="inlineStr">
@@ -35031,7 +35141,7 @@
     <row r="1245">
       <c r="A1245" s="4" t="inlineStr">
         <is>
-          <t>TE02-40</t>
+          <t>TE02-34</t>
         </is>
       </c>
       <c r="B1245" s="4" t="inlineStr">
@@ -35055,41 +35165,35 @@
       <c r="H1245" s="4" t="n"/>
     </row>
     <row r="1246">
-      <c r="A1246" s="2" t="inlineStr">
-        <is>
-          <t>GA01-01</t>
-        </is>
-      </c>
-      <c r="B1246" s="2" t="inlineStr">
+      <c r="A1246" s="4" t="inlineStr">
+        <is>
+          <t>TE02-35</t>
+        </is>
+      </c>
+      <c r="B1246" s="4" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1246" s="2" t="inlineStr"/>
-      <c r="D1246" s="2" t="inlineStr">
-        <is>
-          <t>Gartenanlage</t>
-        </is>
-      </c>
-      <c r="E1246" s="2" t="inlineStr">
-        <is>
-          <t>Holz-Wellenliege, Doppelliege</t>
-        </is>
-      </c>
-      <c r="F1246" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1246" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1246" s="2" t="n"/>
+      <c r="C1246" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
+      <c r="D1246" s="4" t="inlineStr">
+        <is>
+          <t>Dachterrasse</t>
+        </is>
+      </c>
+      <c r="E1246" s="4" t="n"/>
+      <c r="F1246" s="3" t="n"/>
+      <c r="G1246" s="4" t="n"/>
+      <c r="H1246" s="4" t="n"/>
     </row>
     <row r="1247">
       <c r="A1247" s="4" t="inlineStr">
         <is>
-          <t>GA01-02</t>
+          <t>TE02-36</t>
         </is>
       </c>
       <c r="B1247" s="4" t="inlineStr">
@@ -35097,10 +35201,14 @@
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1247" s="4" t="inlineStr"/>
+      <c r="C1247" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
       <c r="D1247" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Dachterrasse</t>
         </is>
       </c>
       <c r="E1247" s="4" t="n"/>
@@ -35111,7 +35219,7 @@
     <row r="1248">
       <c r="A1248" s="4" t="inlineStr">
         <is>
-          <t>GA01-03</t>
+          <t>TE02-37</t>
         </is>
       </c>
       <c r="B1248" s="4" t="inlineStr">
@@ -35119,10 +35227,14 @@
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1248" s="4" t="inlineStr"/>
+      <c r="C1248" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
       <c r="D1248" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Dachterrasse</t>
         </is>
       </c>
       <c r="E1248" s="4" t="n"/>
@@ -35133,7 +35245,7 @@
     <row r="1249">
       <c r="A1249" s="4" t="inlineStr">
         <is>
-          <t>GA01-04</t>
+          <t>TE02-38</t>
         </is>
       </c>
       <c r="B1249" s="4" t="inlineStr">
@@ -35141,10 +35253,14 @@
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1249" s="4" t="inlineStr"/>
+      <c r="C1249" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
       <c r="D1249" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Dachterrasse</t>
         </is>
       </c>
       <c r="E1249" s="4" t="n"/>
@@ -35155,7 +35271,7 @@
     <row r="1250">
       <c r="A1250" s="4" t="inlineStr">
         <is>
-          <t>GA01-05</t>
+          <t>TE02-39</t>
         </is>
       </c>
       <c r="B1250" s="4" t="inlineStr">
@@ -35163,10 +35279,14 @@
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1250" s="4" t="inlineStr"/>
+      <c r="C1250" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
       <c r="D1250" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Dachterrasse</t>
         </is>
       </c>
       <c r="E1250" s="4" t="n"/>
@@ -35177,7 +35297,7 @@
     <row r="1251">
       <c r="A1251" s="4" t="inlineStr">
         <is>
-          <t>GA01-06</t>
+          <t>TE02-40</t>
         </is>
       </c>
       <c r="B1251" s="4" t="inlineStr">
@@ -35185,10 +35305,14 @@
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1251" s="4" t="inlineStr"/>
+      <c r="C1251" s="4" t="inlineStr">
+        <is>
+          <t>Attika</t>
+        </is>
+      </c>
       <c r="D1251" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Dachterrasse</t>
         </is>
       </c>
       <c r="E1251" s="4" t="n"/>
@@ -35197,31 +35321,41 @@
       <c r="H1251" s="4" t="n"/>
     </row>
     <row r="1252">
-      <c r="A1252" s="4" t="inlineStr">
-        <is>
-          <t>GA01-07</t>
-        </is>
-      </c>
-      <c r="B1252" s="4" t="inlineStr">
+      <c r="A1252" s="2" t="inlineStr">
+        <is>
+          <t>GA01-01</t>
+        </is>
+      </c>
+      <c r="B1252" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1252" s="4" t="inlineStr"/>
-      <c r="D1252" s="4" t="inlineStr">
+      <c r="C1252" s="2" t="inlineStr"/>
+      <c r="D1252" s="2" t="inlineStr">
         <is>
           <t>Gartenanlage</t>
         </is>
       </c>
-      <c r="E1252" s="4" t="n"/>
-      <c r="F1252" s="3" t="n"/>
-      <c r="G1252" s="4" t="n"/>
-      <c r="H1252" s="4" t="n"/>
+      <c r="E1252" s="2" t="inlineStr">
+        <is>
+          <t>Holz-Wellenliege, Doppelliege</t>
+        </is>
+      </c>
+      <c r="F1252" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1252" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1252" s="2" t="n"/>
     </row>
     <row r="1253">
       <c r="A1253" s="4" t="inlineStr">
         <is>
-          <t>GA01-08</t>
+          <t>GA01-02</t>
         </is>
       </c>
       <c r="B1253" s="4" t="inlineStr">
@@ -35243,7 +35377,7 @@
     <row r="1254">
       <c r="A1254" s="4" t="inlineStr">
         <is>
-          <t>GA01-09</t>
+          <t>GA01-03</t>
         </is>
       </c>
       <c r="B1254" s="4" t="inlineStr">
@@ -35265,7 +35399,7 @@
     <row r="1255">
       <c r="A1255" s="4" t="inlineStr">
         <is>
-          <t>GA01-10</t>
+          <t>GA01-04</t>
         </is>
       </c>
       <c r="B1255" s="4" t="inlineStr">
@@ -35287,7 +35421,7 @@
     <row r="1256">
       <c r="A1256" s="4" t="inlineStr">
         <is>
-          <t>GA01-11</t>
+          <t>GA01-05</t>
         </is>
       </c>
       <c r="B1256" s="4" t="inlineStr">
@@ -35309,7 +35443,7 @@
     <row r="1257">
       <c r="A1257" s="4" t="inlineStr">
         <is>
-          <t>GA01-12</t>
+          <t>GA01-06</t>
         </is>
       </c>
       <c r="B1257" s="4" t="inlineStr">
@@ -35331,7 +35465,7 @@
     <row r="1258">
       <c r="A1258" s="4" t="inlineStr">
         <is>
-          <t>GA01-13</t>
+          <t>GA01-07</t>
         </is>
       </c>
       <c r="B1258" s="4" t="inlineStr">
@@ -35353,7 +35487,7 @@
     <row r="1259">
       <c r="A1259" s="4" t="inlineStr">
         <is>
-          <t>GA01-14</t>
+          <t>GA01-08</t>
         </is>
       </c>
       <c r="B1259" s="4" t="inlineStr">
@@ -35375,7 +35509,7 @@
     <row r="1260">
       <c r="A1260" s="4" t="inlineStr">
         <is>
-          <t>GA01-15</t>
+          <t>GA01-09</t>
         </is>
       </c>
       <c r="B1260" s="4" t="inlineStr">
@@ -35397,7 +35531,7 @@
     <row r="1261">
       <c r="A1261" s="4" t="inlineStr">
         <is>
-          <t>GA01-16</t>
+          <t>GA01-10</t>
         </is>
       </c>
       <c r="B1261" s="4" t="inlineStr">
@@ -35419,7 +35553,7 @@
     <row r="1262">
       <c r="A1262" s="4" t="inlineStr">
         <is>
-          <t>GA01-17</t>
+          <t>GA01-11</t>
         </is>
       </c>
       <c r="B1262" s="4" t="inlineStr">
@@ -35441,7 +35575,7 @@
     <row r="1263">
       <c r="A1263" s="4" t="inlineStr">
         <is>
-          <t>GA01-18</t>
+          <t>GA01-12</t>
         </is>
       </c>
       <c r="B1263" s="4" t="inlineStr">
@@ -35463,7 +35597,7 @@
     <row r="1264">
       <c r="A1264" s="4" t="inlineStr">
         <is>
-          <t>GA01-19</t>
+          <t>GA01-13</t>
         </is>
       </c>
       <c r="B1264" s="4" t="inlineStr">
@@ -35485,7 +35619,7 @@
     <row r="1265">
       <c r="A1265" s="4" t="inlineStr">
         <is>
-          <t>GA01-20</t>
+          <t>GA01-14</t>
         </is>
       </c>
       <c r="B1265" s="4" t="inlineStr">
@@ -35507,7 +35641,7 @@
     <row r="1266">
       <c r="A1266" s="4" t="inlineStr">
         <is>
-          <t>GA01-21</t>
+          <t>GA01-15</t>
         </is>
       </c>
       <c r="B1266" s="4" t="inlineStr">
@@ -35529,7 +35663,7 @@
     <row r="1267">
       <c r="A1267" s="4" t="inlineStr">
         <is>
-          <t>GA01-22</t>
+          <t>GA01-16</t>
         </is>
       </c>
       <c r="B1267" s="4" t="inlineStr">
@@ -35551,7 +35685,7 @@
     <row r="1268">
       <c r="A1268" s="4" t="inlineStr">
         <is>
-          <t>GA01-23</t>
+          <t>GA01-17</t>
         </is>
       </c>
       <c r="B1268" s="4" t="inlineStr">
@@ -35573,7 +35707,7 @@
     <row r="1269">
       <c r="A1269" s="4" t="inlineStr">
         <is>
-          <t>GA01-24</t>
+          <t>GA01-18</t>
         </is>
       </c>
       <c r="B1269" s="4" t="inlineStr">
@@ -35595,7 +35729,7 @@
     <row r="1270">
       <c r="A1270" s="4" t="inlineStr">
         <is>
-          <t>GA01-25</t>
+          <t>GA01-19</t>
         </is>
       </c>
       <c r="B1270" s="4" t="inlineStr">
@@ -35617,7 +35751,7 @@
     <row r="1271">
       <c r="A1271" s="4" t="inlineStr">
         <is>
-          <t>GA01-26</t>
+          <t>GA01-20</t>
         </is>
       </c>
       <c r="B1271" s="4" t="inlineStr">
@@ -35639,7 +35773,7 @@
     <row r="1272">
       <c r="A1272" s="4" t="inlineStr">
         <is>
-          <t>GA01-27</t>
+          <t>GA01-21</t>
         </is>
       </c>
       <c r="B1272" s="4" t="inlineStr">
@@ -35661,7 +35795,7 @@
     <row r="1273">
       <c r="A1273" s="4" t="inlineStr">
         <is>
-          <t>GA01-28</t>
+          <t>GA01-22</t>
         </is>
       </c>
       <c r="B1273" s="4" t="inlineStr">
@@ -35683,7 +35817,7 @@
     <row r="1274">
       <c r="A1274" s="4" t="inlineStr">
         <is>
-          <t>GA01-29</t>
+          <t>GA01-23</t>
         </is>
       </c>
       <c r="B1274" s="4" t="inlineStr">
@@ -35705,7 +35839,7 @@
     <row r="1275">
       <c r="A1275" s="4" t="inlineStr">
         <is>
-          <t>GA01-30</t>
+          <t>GA01-24</t>
         </is>
       </c>
       <c r="B1275" s="4" t="inlineStr">
@@ -35727,7 +35861,7 @@
     <row r="1276">
       <c r="A1276" s="4" t="inlineStr">
         <is>
-          <t>GA01-31</t>
+          <t>GA01-25</t>
         </is>
       </c>
       <c r="B1276" s="4" t="inlineStr">
@@ -35749,7 +35883,7 @@
     <row r="1277">
       <c r="A1277" s="4" t="inlineStr">
         <is>
-          <t>GA01-32</t>
+          <t>GA01-26</t>
         </is>
       </c>
       <c r="B1277" s="4" t="inlineStr">
@@ -35771,7 +35905,7 @@
     <row r="1278">
       <c r="A1278" s="4" t="inlineStr">
         <is>
-          <t>GA01-33</t>
+          <t>GA01-27</t>
         </is>
       </c>
       <c r="B1278" s="4" t="inlineStr">
@@ -35793,7 +35927,7 @@
     <row r="1279">
       <c r="A1279" s="4" t="inlineStr">
         <is>
-          <t>GA01-34</t>
+          <t>GA01-28</t>
         </is>
       </c>
       <c r="B1279" s="4" t="inlineStr">
@@ -35815,7 +35949,7 @@
     <row r="1280">
       <c r="A1280" s="4" t="inlineStr">
         <is>
-          <t>GA01-35</t>
+          <t>GA01-29</t>
         </is>
       </c>
       <c r="B1280" s="4" t="inlineStr">
@@ -35837,7 +35971,7 @@
     <row r="1281">
       <c r="A1281" s="4" t="inlineStr">
         <is>
-          <t>GA01-36</t>
+          <t>GA01-30</t>
         </is>
       </c>
       <c r="B1281" s="4" t="inlineStr">
@@ -35859,7 +35993,7 @@
     <row r="1282">
       <c r="A1282" s="4" t="inlineStr">
         <is>
-          <t>GA01-37</t>
+          <t>GA01-31</t>
         </is>
       </c>
       <c r="B1282" s="4" t="inlineStr">
@@ -35881,7 +36015,7 @@
     <row r="1283">
       <c r="A1283" s="4" t="inlineStr">
         <is>
-          <t>GA01-38</t>
+          <t>GA01-32</t>
         </is>
       </c>
       <c r="B1283" s="4" t="inlineStr">
@@ -35903,7 +36037,7 @@
     <row r="1284">
       <c r="A1284" s="4" t="inlineStr">
         <is>
-          <t>GA01-39</t>
+          <t>GA01-33</t>
         </is>
       </c>
       <c r="B1284" s="4" t="inlineStr">
@@ -35925,7 +36059,7 @@
     <row r="1285">
       <c r="A1285" s="4" t="inlineStr">
         <is>
-          <t>GA01-40</t>
+          <t>GA01-34</t>
         </is>
       </c>
       <c r="B1285" s="4" t="inlineStr">
@@ -35944,10 +36078,142 @@
       <c r="G1285" s="4" t="n"/>
       <c r="H1285" s="4" t="n"/>
     </row>
+    <row r="1286">
+      <c r="A1286" s="4" t="inlineStr">
+        <is>
+          <t>GA01-35</t>
+        </is>
+      </c>
+      <c r="B1286" s="4" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1286" s="4" t="inlineStr"/>
+      <c r="D1286" s="4" t="inlineStr">
+        <is>
+          <t>Gartenanlage</t>
+        </is>
+      </c>
+      <c r="E1286" s="4" t="n"/>
+      <c r="F1286" s="3" t="n"/>
+      <c r="G1286" s="4" t="n"/>
+      <c r="H1286" s="4" t="n"/>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="4" t="inlineStr">
+        <is>
+          <t>GA01-36</t>
+        </is>
+      </c>
+      <c r="B1287" s="4" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1287" s="4" t="inlineStr"/>
+      <c r="D1287" s="4" t="inlineStr">
+        <is>
+          <t>Gartenanlage</t>
+        </is>
+      </c>
+      <c r="E1287" s="4" t="n"/>
+      <c r="F1287" s="3" t="n"/>
+      <c r="G1287" s="4" t="n"/>
+      <c r="H1287" s="4" t="n"/>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="4" t="inlineStr">
+        <is>
+          <t>GA01-37</t>
+        </is>
+      </c>
+      <c r="B1288" s="4" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1288" s="4" t="inlineStr"/>
+      <c r="D1288" s="4" t="inlineStr">
+        <is>
+          <t>Gartenanlage</t>
+        </is>
+      </c>
+      <c r="E1288" s="4" t="n"/>
+      <c r="F1288" s="3" t="n"/>
+      <c r="G1288" s="4" t="n"/>
+      <c r="H1288" s="4" t="n"/>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="4" t="inlineStr">
+        <is>
+          <t>GA01-38</t>
+        </is>
+      </c>
+      <c r="B1289" s="4" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1289" s="4" t="inlineStr"/>
+      <c r="D1289" s="4" t="inlineStr">
+        <is>
+          <t>Gartenanlage</t>
+        </is>
+      </c>
+      <c r="E1289" s="4" t="n"/>
+      <c r="F1289" s="3" t="n"/>
+      <c r="G1289" s="4" t="n"/>
+      <c r="H1289" s="4" t="n"/>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="4" t="inlineStr">
+        <is>
+          <t>GA01-39</t>
+        </is>
+      </c>
+      <c r="B1290" s="4" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1290" s="4" t="inlineStr"/>
+      <c r="D1290" s="4" t="inlineStr">
+        <is>
+          <t>Gartenanlage</t>
+        </is>
+      </c>
+      <c r="E1290" s="4" t="n"/>
+      <c r="F1290" s="3" t="n"/>
+      <c r="G1290" s="4" t="n"/>
+      <c r="H1290" s="4" t="n"/>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="4" t="inlineStr">
+        <is>
+          <t>GA01-40</t>
+        </is>
+      </c>
+      <c r="B1291" s="4" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="C1291" s="4" t="inlineStr"/>
+      <c r="D1291" s="4" t="inlineStr">
+        <is>
+          <t>Gartenanlage</t>
+        </is>
+      </c>
+      <c r="E1291" s="4" t="n"/>
+      <c r="F1291" s="3" t="n"/>
+      <c r="G1291" s="4" t="n"/>
+      <c r="H1291" s="4" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1285"/>
+  <autoFilter ref="A1:H1291"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F1285" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen." type="whole" operator="greaterThan">
+    <dataValidation sqref="F2:F1291" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -29569,7 +29569,7 @@
       </c>
       <c r="E1043" s="2" t="inlineStr">
         <is>
-          <t>Spieltunnel grün</t>
+          <t>Spieltunnel grün, 180 cm</t>
         </is>
       </c>
       <c r="F1043" s="3" t="n">

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -27543,7 +27543,7 @@
         </is>
       </c>
       <c r="F973" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G973" s="2" t="inlineStr">
         <is>
@@ -29843,134 +29843,184 @@
       <c r="H1053" s="4" t="n"/>
     </row>
     <row r="1054">
-      <c r="A1054" s="4" t="inlineStr">
+      <c r="A1054" s="2" t="inlineStr">
         <is>
           <t>BA07-01</t>
         </is>
       </c>
-      <c r="B1054" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1054" s="4" t="inlineStr">
+      <c r="B1054" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1054" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1054" s="4" t="inlineStr">
+      <c r="D1054" s="2" t="inlineStr">
         <is>
           <t>Klassenzimmer</t>
         </is>
       </c>
-      <c r="E1054" s="4" t="n"/>
-      <c r="F1054" s="3" t="n"/>
-      <c r="G1054" s="4" t="n"/>
-      <c r="H1054" s="4" t="n"/>
+      <c r="E1054" s="2" t="inlineStr">
+        <is>
+          <t>Kissen in Wolkenform, hellblau</t>
+        </is>
+      </c>
+      <c r="F1054" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1054" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1054" s="2" t="n"/>
     </row>
     <row r="1055">
-      <c r="A1055" s="4" t="inlineStr">
+      <c r="A1055" s="2" t="inlineStr">
         <is>
           <t>BA07-02</t>
         </is>
       </c>
-      <c r="B1055" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1055" s="4" t="inlineStr">
+      <c r="B1055" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1055" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1055" s="4" t="inlineStr">
+      <c r="D1055" s="2" t="inlineStr">
         <is>
           <t>Klassenzimmer</t>
         </is>
       </c>
-      <c r="E1055" s="4" t="n"/>
-      <c r="F1055" s="3" t="n"/>
-      <c r="G1055" s="4" t="n"/>
-      <c r="H1055" s="4" t="n"/>
+      <c r="E1055" s="2" t="inlineStr">
+        <is>
+          <t>Wandleuchte rund mit Holzrand</t>
+        </is>
+      </c>
+      <c r="F1055" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1055" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1055" s="2" t="n"/>
     </row>
     <row r="1056">
-      <c r="A1056" s="4" t="inlineStr">
+      <c r="A1056" s="2" t="inlineStr">
         <is>
           <t>BA07-03</t>
         </is>
       </c>
-      <c r="B1056" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1056" s="4" t="inlineStr">
+      <c r="B1056" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1056" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1056" s="4" t="inlineStr">
+      <c r="D1056" s="2" t="inlineStr">
         <is>
           <t>Klassenzimmer</t>
         </is>
       </c>
-      <c r="E1056" s="4" t="n"/>
-      <c r="F1056" s="3" t="n"/>
-      <c r="G1056" s="4" t="n"/>
-      <c r="H1056" s="4" t="n"/>
+      <c r="E1056" s="2" t="inlineStr">
+        <is>
+          <t>Standregal grau mit Wolkenaufsatz</t>
+        </is>
+      </c>
+      <c r="F1056" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1056" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1056" s="2" t="n"/>
     </row>
     <row r="1057">
-      <c r="A1057" s="4" t="inlineStr">
+      <c r="A1057" s="2" t="inlineStr">
         <is>
           <t>BA07-04</t>
         </is>
       </c>
-      <c r="B1057" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1057" s="4" t="inlineStr">
+      <c r="B1057" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1057" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1057" s="4" t="inlineStr">
+      <c r="D1057" s="2" t="inlineStr">
         <is>
           <t>Klassenzimmer</t>
         </is>
       </c>
-      <c r="E1057" s="4" t="n"/>
-      <c r="F1057" s="3" t="n"/>
-      <c r="G1057" s="4" t="n"/>
-      <c r="H1057" s="4" t="n"/>
+      <c r="E1057" s="2" t="inlineStr">
+        <is>
+          <t>Tisch weiß, lang, auf schwarzen Beinen</t>
+        </is>
+      </c>
+      <c r="F1057" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1057" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1057" s="2" t="n"/>
     </row>
     <row r="1058">
-      <c r="A1058" s="4" t="inlineStr">
+      <c r="A1058" s="2" t="inlineStr">
         <is>
           <t>BA07-05</t>
         </is>
       </c>
-      <c r="B1058" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1058" s="4" t="inlineStr">
+      <c r="B1058" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1058" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1058" s="4" t="inlineStr">
+      <c r="D1058" s="2" t="inlineStr">
         <is>
           <t>Klassenzimmer</t>
         </is>
       </c>
-      <c r="E1058" s="4" t="n"/>
-      <c r="F1058" s="3" t="n"/>
-      <c r="G1058" s="4" t="n"/>
-      <c r="H1058" s="4" t="n"/>
+      <c r="E1058" s="2" t="inlineStr">
+        <is>
+          <t>Regal creme, 16 Fächer, auf Metallbeinen</t>
+        </is>
+      </c>
+      <c r="F1058" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1058" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1058" s="2" t="n"/>
     </row>
     <row r="1059">
       <c r="A1059" s="4" t="inlineStr">

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -30427,212 +30427,292 @@
       <c r="H1072" s="2" t="n"/>
     </row>
     <row r="1073">
-      <c r="A1073" s="4" t="inlineStr">
+      <c r="A1073" s="2" t="inlineStr">
         <is>
           <t>BA08-05</t>
         </is>
       </c>
-      <c r="B1073" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1073" s="4" t="inlineStr">
+      <c r="B1073" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1073" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1073" s="4" t="inlineStr">
+      <c r="D1073" s="2" t="inlineStr">
         <is>
           <t>Atelier</t>
         </is>
       </c>
-      <c r="E1073" s="4" t="n"/>
-      <c r="F1073" s="3" t="n"/>
-      <c r="G1073" s="4" t="n"/>
-      <c r="H1073" s="4" t="n"/>
+      <c r="E1073" s="2" t="inlineStr">
+        <is>
+          <t>Acrylbild schwarz-weiß, Kreise mit Punkten</t>
+        </is>
+      </c>
+      <c r="F1073" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1073" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1073" s="2" t="n"/>
     </row>
     <row r="1074">
-      <c r="A1074" s="4" t="inlineStr">
+      <c r="A1074" s="2" t="inlineStr">
         <is>
           <t>BA08-06</t>
         </is>
       </c>
-      <c r="B1074" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1074" s="4" t="inlineStr">
+      <c r="B1074" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1074" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1074" s="4" t="inlineStr">
+      <c r="D1074" s="2" t="inlineStr">
         <is>
           <t>Atelier</t>
         </is>
       </c>
-      <c r="E1074" s="4" t="n"/>
-      <c r="F1074" s="3" t="n"/>
-      <c r="G1074" s="4" t="n"/>
-      <c r="H1074" s="4" t="n"/>
+      <c r="E1074" s="2" t="inlineStr">
+        <is>
+          <t>VS Schalenstuhl grau, Vierfußgestell</t>
+        </is>
+      </c>
+      <c r="F1074" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1074" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1074" s="2" t="n"/>
     </row>
     <row r="1075">
-      <c r="A1075" s="4" t="inlineStr">
+      <c r="A1075" s="2" t="inlineStr">
         <is>
           <t>BA08-07</t>
         </is>
       </c>
-      <c r="B1075" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1075" s="4" t="inlineStr">
+      <c r="B1075" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1075" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1075" s="4" t="inlineStr">
+      <c r="D1075" s="2" t="inlineStr">
         <is>
           <t>Atelier</t>
         </is>
       </c>
-      <c r="E1075" s="4" t="n"/>
-      <c r="F1075" s="3" t="n"/>
-      <c r="G1075" s="4" t="n"/>
-      <c r="H1075" s="4" t="n"/>
+      <c r="E1075" s="2" t="inlineStr">
+        <is>
+          <t>Konvolut Feinkrepp-Papier</t>
+        </is>
+      </c>
+      <c r="F1075" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1075" s="2" t="inlineStr">
+        <is>
+          <t>Konvolut</t>
+        </is>
+      </c>
+      <c r="H1075" s="2" t="n"/>
     </row>
     <row r="1076">
-      <c r="A1076" s="4" t="inlineStr">
+      <c r="A1076" s="2" t="inlineStr">
         <is>
           <t>BA08-08</t>
         </is>
       </c>
-      <c r="B1076" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1076" s="4" t="inlineStr">
+      <c r="B1076" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1076" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1076" s="4" t="inlineStr">
+      <c r="D1076" s="2" t="inlineStr">
         <is>
           <t>Atelier</t>
         </is>
       </c>
-      <c r="E1076" s="4" t="n"/>
-      <c r="F1076" s="3" t="n"/>
-      <c r="G1076" s="4" t="n"/>
-      <c r="H1076" s="4" t="n"/>
+      <c r="E1076" s="2" t="inlineStr">
+        <is>
+          <t>Deko-Pilze auf Holzfuß</t>
+        </is>
+      </c>
+      <c r="F1076" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1076" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1076" s="2" t="n"/>
     </row>
     <row r="1077">
-      <c r="A1077" s="4" t="inlineStr">
+      <c r="A1077" s="2" t="inlineStr">
         <is>
           <t>BA08-09</t>
         </is>
       </c>
-      <c r="B1077" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1077" s="4" t="inlineStr">
+      <c r="B1077" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1077" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1077" s="4" t="inlineStr">
+      <c r="D1077" s="2" t="inlineStr">
         <is>
           <t>Atelier</t>
         </is>
       </c>
-      <c r="E1077" s="4" t="n"/>
-      <c r="F1077" s="3" t="n"/>
-      <c r="G1077" s="4" t="n"/>
-      <c r="H1077" s="4" t="n"/>
+      <c r="E1077" s="2" t="inlineStr">
+        <is>
+          <t>Bastelscheren im Betzold-Holzblock</t>
+        </is>
+      </c>
+      <c r="F1077" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G1077" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1077" s="2" t="n"/>
     </row>
     <row r="1078">
-      <c r="A1078" s="4" t="inlineStr">
+      <c r="A1078" s="2" t="inlineStr">
         <is>
           <t>BA08-10</t>
         </is>
       </c>
-      <c r="B1078" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1078" s="4" t="inlineStr">
+      <c r="B1078" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1078" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1078" s="4" t="inlineStr">
+      <c r="D1078" s="2" t="inlineStr">
         <is>
           <t>Atelier</t>
         </is>
       </c>
-      <c r="E1078" s="4" t="n"/>
-      <c r="F1078" s="3" t="n"/>
-      <c r="G1078" s="4" t="n"/>
-      <c r="H1078" s="4" t="n"/>
+      <c r="E1078" s="2" t="inlineStr">
+        <is>
+          <t>Kunstpflanze Gras im weißen Topf</t>
+        </is>
+      </c>
+      <c r="F1078" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1078" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1078" s="2" t="n"/>
     </row>
     <row r="1079">
-      <c r="A1079" s="4" t="inlineStr">
+      <c r="A1079" s="2" t="inlineStr">
         <is>
           <t>BA08-11</t>
         </is>
       </c>
-      <c r="B1079" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1079" s="4" t="inlineStr">
+      <c r="B1079" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1079" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1079" s="4" t="inlineStr">
+      <c r="D1079" s="2" t="inlineStr">
         <is>
           <t>Atelier</t>
         </is>
       </c>
-      <c r="E1079" s="4" t="n"/>
-      <c r="F1079" s="3" t="n"/>
-      <c r="G1079" s="4" t="n"/>
-      <c r="H1079" s="4" t="n"/>
+      <c r="E1079" s="2" t="inlineStr">
+        <is>
+          <t>Bilderrahmen mit Zeichenwerkzeug</t>
+        </is>
+      </c>
+      <c r="F1079" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1079" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1079" s="2" t="n"/>
     </row>
     <row r="1080">
-      <c r="A1080" s="4" t="inlineStr">
+      <c r="A1080" s="2" t="inlineStr">
         <is>
           <t>BA08-12</t>
         </is>
       </c>
-      <c r="B1080" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C1080" s="4" t="inlineStr">
+      <c r="B1080" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C1080" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1080" s="4" t="inlineStr">
+      <c r="D1080" s="2" t="inlineStr">
         <is>
           <t>Atelier</t>
         </is>
       </c>
-      <c r="E1080" s="4" t="n"/>
-      <c r="F1080" s="3" t="n"/>
-      <c r="G1080" s="4" t="n"/>
-      <c r="H1080" s="4" t="n"/>
+      <c r="E1080" s="2" t="inlineStr">
+        <is>
+          <t>Wandregalbrett weiß</t>
+        </is>
+      </c>
+      <c r="F1080" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1080" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1080" s="2" t="n"/>
     </row>
     <row r="1081">
       <c r="A1081" s="4" t="inlineStr">

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="F107" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
@@ -11543,160 +11543,220 @@
       <c r="H373" s="4" t="n"/>
     </row>
     <row r="374">
-      <c r="A374" s="4" t="inlineStr">
+      <c r="A374" s="2" t="inlineStr">
         <is>
           <t>BU01-01</t>
         </is>
       </c>
-      <c r="B374" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C374" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D374" s="4" t="inlineStr">
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
         <is>
           <t>Flur 1</t>
         </is>
       </c>
-      <c r="E374" s="4" t="n"/>
-      <c r="F374" s="3" t="n"/>
-      <c r="G374" s="4" t="n"/>
-      <c r="H374" s="4" t="n"/>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>Hausbett Buche massiv</t>
+        </is>
+      </c>
+      <c r="F374" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="n"/>
     </row>
     <row r="375">
-      <c r="A375" s="4" t="inlineStr">
+      <c r="A375" s="2" t="inlineStr">
         <is>
           <t>BU01-02</t>
         </is>
       </c>
-      <c r="B375" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C375" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D375" s="4" t="inlineStr">
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
         <is>
           <t>Flur 1</t>
         </is>
       </c>
-      <c r="E375" s="4" t="n"/>
-      <c r="F375" s="3" t="n"/>
-      <c r="G375" s="4" t="n"/>
-      <c r="H375" s="4" t="n"/>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>Spielküche klein mit Mikrowelle</t>
+        </is>
+      </c>
+      <c r="F375" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="n"/>
     </row>
     <row r="376">
-      <c r="A376" s="4" t="inlineStr">
+      <c r="A376" s="2" t="inlineStr">
         <is>
           <t>BU01-03</t>
         </is>
       </c>
-      <c r="B376" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C376" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D376" s="4" t="inlineStr">
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
         <is>
           <t>Flur 1</t>
         </is>
       </c>
-      <c r="E376" s="4" t="n"/>
-      <c r="F376" s="3" t="n"/>
-      <c r="G376" s="4" t="n"/>
-      <c r="H376" s="4" t="n"/>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>Gestell Kiefer mit sechs Wannen</t>
+        </is>
+      </c>
+      <c r="F376" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H376" s="2" t="n"/>
     </row>
     <row r="377">
-      <c r="A377" s="4" t="inlineStr">
+      <c r="A377" s="2" t="inlineStr">
         <is>
           <t>BU01-04</t>
         </is>
       </c>
-      <c r="B377" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C377" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D377" s="4" t="inlineStr">
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
         <is>
           <t>Flur 1</t>
         </is>
       </c>
-      <c r="E377" s="4" t="n"/>
-      <c r="F377" s="3" t="n"/>
-      <c r="G377" s="4" t="n"/>
-      <c r="H377" s="4" t="n"/>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Småstad Kindertisch weiß</t>
+        </is>
+      </c>
+      <c r="F377" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H377" s="2" t="n"/>
     </row>
     <row r="378">
-      <c r="A378" s="4" t="inlineStr">
+      <c r="A378" s="2" t="inlineStr">
         <is>
           <t>BU01-05</t>
         </is>
       </c>
-      <c r="B378" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C378" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D378" s="4" t="inlineStr">
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
         <is>
           <t>Flur 1</t>
         </is>
       </c>
-      <c r="E378" s="4" t="n"/>
-      <c r="F378" s="3" t="n"/>
-      <c r="G378" s="4" t="n"/>
-      <c r="H378" s="4" t="n"/>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>Wanddeko Lama, Steckwand</t>
+        </is>
+      </c>
+      <c r="F378" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="n"/>
     </row>
     <row r="379">
-      <c r="A379" s="4" t="inlineStr">
+      <c r="A379" s="2" t="inlineStr">
         <is>
           <t>BU01-06</t>
         </is>
       </c>
-      <c r="B379" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C379" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D379" s="4" t="inlineStr">
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="inlineStr">
         <is>
           <t>Flur 1</t>
         </is>
       </c>
-      <c r="E379" s="4" t="n"/>
-      <c r="F379" s="3" t="n"/>
-      <c r="G379" s="4" t="n"/>
-      <c r="H379" s="4" t="n"/>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Grua Wandspiegel, schwarzer Rahmen</t>
+        </is>
+      </c>
+      <c r="F379" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H379" s="2" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="4" t="inlineStr">

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         </is>
       </c>
       <c r="F411" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
       </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
-          <t>Wanddeko Fadenbilder mit Spiegelpunkten</t>
+          <t>Kindertisch weiß, lang, zweiteilig</t>
         </is>
       </c>
       <c r="F444" s="3" t="n">
@@ -13709,212 +13709,292 @@
       <c r="H444" s="2" t="n"/>
     </row>
     <row r="445">
-      <c r="A445" s="4" t="inlineStr">
+      <c r="A445" s="2" t="inlineStr">
         <is>
           <t>BU04-06</t>
         </is>
       </c>
-      <c r="B445" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C445" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D445" s="4" t="inlineStr">
+      <c r="B445" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D445" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum</t>
         </is>
       </c>
-      <c r="E445" s="4" t="n"/>
-      <c r="F445" s="3" t="n"/>
-      <c r="G445" s="4" t="n"/>
-      <c r="H445" s="4" t="n"/>
+      <c r="E445" s="2" t="inlineStr">
+        <is>
+          <t>Gemälde Schwarzwaldfrau mit Planeten</t>
+        </is>
+      </c>
+      <c r="F445" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G445" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H445" s="2" t="n"/>
     </row>
     <row r="446">
-      <c r="A446" s="4" t="inlineStr">
+      <c r="A446" s="2" t="inlineStr">
         <is>
           <t>BU04-07</t>
         </is>
       </c>
-      <c r="B446" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C446" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D446" s="4" t="inlineStr">
+      <c r="B446" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D446" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum</t>
         </is>
       </c>
-      <c r="E446" s="4" t="n"/>
-      <c r="F446" s="3" t="n"/>
-      <c r="G446" s="4" t="n"/>
-      <c r="H446" s="4" t="n"/>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>Garderobenständer bunt, Stangenform</t>
+        </is>
+      </c>
+      <c r="F446" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G446" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H446" s="2" t="n"/>
     </row>
     <row r="447">
-      <c r="A447" s="4" t="inlineStr">
+      <c r="A447" s="2" t="inlineStr">
         <is>
           <t>BU04-08</t>
         </is>
       </c>
-      <c r="B447" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C447" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D447" s="4" t="inlineStr">
+      <c r="B447" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D447" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum</t>
         </is>
       </c>
-      <c r="E447" s="4" t="n"/>
-      <c r="F447" s="3" t="n"/>
-      <c r="G447" s="4" t="n"/>
-      <c r="H447" s="4" t="n"/>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>Kindertisch weiß aus fünf Segmenten</t>
+        </is>
+      </c>
+      <c r="F447" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G447" s="2" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="H447" s="2" t="n"/>
     </row>
     <row r="448">
-      <c r="A448" s="4" t="inlineStr">
+      <c r="A448" s="2" t="inlineStr">
         <is>
           <t>BU04-09</t>
         </is>
       </c>
-      <c r="B448" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C448" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D448" s="4" t="inlineStr">
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D448" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum</t>
         </is>
       </c>
-      <c r="E448" s="4" t="n"/>
-      <c r="F448" s="3" t="n"/>
-      <c r="G448" s="4" t="n"/>
-      <c r="H448" s="4" t="n"/>
+      <c r="E448" s="2" t="inlineStr">
+        <is>
+          <t>Regal weiß, vier Böden</t>
+        </is>
+      </c>
+      <c r="F448" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G448" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H448" s="2" t="n"/>
     </row>
     <row r="449">
-      <c r="A449" s="4" t="inlineStr">
+      <c r="A449" s="2" t="inlineStr">
         <is>
           <t>BU04-10</t>
         </is>
       </c>
-      <c r="B449" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C449" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D449" s="4" t="inlineStr">
+      <c r="B449" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D449" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum</t>
         </is>
       </c>
-      <c r="E449" s="4" t="n"/>
-      <c r="F449" s="3" t="n"/>
-      <c r="G449" s="4" t="n"/>
-      <c r="H449" s="4" t="n"/>
+      <c r="E449" s="2" t="inlineStr">
+        <is>
+          <t>Servierwagen Metall grau, drei Ebenen</t>
+        </is>
+      </c>
+      <c r="F449" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G449" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H449" s="2" t="n"/>
     </row>
     <row r="450">
-      <c r="A450" s="4" t="inlineStr">
+      <c r="A450" s="2" t="inlineStr">
         <is>
           <t>BU04-11</t>
         </is>
       </c>
-      <c r="B450" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C450" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D450" s="4" t="inlineStr">
+      <c r="B450" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D450" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum</t>
         </is>
       </c>
-      <c r="E450" s="4" t="n"/>
-      <c r="F450" s="3" t="n"/>
-      <c r="G450" s="4" t="n"/>
-      <c r="H450" s="4" t="n"/>
+      <c r="E450" s="2" t="inlineStr">
+        <is>
+          <t>Bücherregal creme mit Wolkenaufsatz</t>
+        </is>
+      </c>
+      <c r="F450" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G450" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H450" s="2" t="n"/>
     </row>
     <row r="451">
-      <c r="A451" s="4" t="inlineStr">
+      <c r="A451" s="2" t="inlineStr">
         <is>
           <t>BU04-12</t>
         </is>
       </c>
-      <c r="B451" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C451" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D451" s="4" t="inlineStr">
+      <c r="B451" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D451" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum</t>
         </is>
       </c>
-      <c r="E451" s="4" t="n"/>
-      <c r="F451" s="3" t="n"/>
-      <c r="G451" s="4" t="n"/>
-      <c r="H451" s="4" t="n"/>
+      <c r="E451" s="2" t="inlineStr">
+        <is>
+          <t>Acrylbilder Roboter, schwarz-weiß</t>
+        </is>
+      </c>
+      <c r="F451" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G451" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H451" s="2" t="n"/>
     </row>
     <row r="452">
-      <c r="A452" s="4" t="inlineStr">
+      <c r="A452" s="2" t="inlineStr">
         <is>
           <t>BU04-13</t>
         </is>
       </c>
-      <c r="B452" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C452" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D452" s="4" t="inlineStr">
+      <c r="B452" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D452" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum</t>
         </is>
       </c>
-      <c r="E452" s="4" t="n"/>
-      <c r="F452" s="3" t="n"/>
-      <c r="G452" s="4" t="n"/>
-      <c r="H452" s="4" t="n"/>
+      <c r="E452" s="2" t="inlineStr">
+        <is>
+          <t>Wanddeko Fadenbilder mit Spiegelpunkten</t>
+        </is>
+      </c>
+      <c r="F452" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G452" s="2" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="H452" s="2" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="4" t="inlineStr">
@@ -27075,7 +27155,7 @@
         </is>
       </c>
       <c r="F950" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G950" s="2" t="inlineStr">
         <is>

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -14309,238 +14309,328 @@
       <c r="H464" s="4" t="n"/>
     </row>
     <row r="465">
-      <c r="A465" s="4" t="inlineStr">
+      <c r="A465" s="2" t="inlineStr">
         <is>
           <t>BU05-01</t>
         </is>
       </c>
-      <c r="B465" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C465" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D465" s="4" t="inlineStr">
+      <c r="B465" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C465" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D465" s="2" t="inlineStr">
         <is>
           <t>Schlafraum</t>
         </is>
       </c>
-      <c r="E465" s="4" t="n"/>
-      <c r="F465" s="3" t="n"/>
-      <c r="G465" s="4" t="n"/>
-      <c r="H465" s="4" t="n"/>
+      <c r="E465" s="2" t="inlineStr">
+        <is>
+          <t>Spielhaus weiß mit Hochebene und Bett</t>
+        </is>
+      </c>
+      <c r="F465" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G465" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H465" s="2" t="n"/>
     </row>
     <row r="466">
-      <c r="A466" s="4" t="inlineStr">
+      <c r="A466" s="2" t="inlineStr">
         <is>
           <t>BU05-02</t>
         </is>
       </c>
-      <c r="B466" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C466" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D466" s="4" t="inlineStr">
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D466" s="2" t="inlineStr">
         <is>
           <t>Schlafraum</t>
         </is>
       </c>
-      <c r="E466" s="4" t="n"/>
-      <c r="F466" s="3" t="n"/>
-      <c r="G466" s="4" t="n"/>
-      <c r="H466" s="4" t="n"/>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>Wesco Spielküche, vier Module mit Mikrowelle</t>
+        </is>
+      </c>
+      <c r="F466" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="H466" s="2" t="n"/>
     </row>
     <row r="467">
-      <c r="A467" s="4" t="inlineStr">
+      <c r="A467" s="2" t="inlineStr">
         <is>
           <t>BU05-03</t>
         </is>
       </c>
-      <c r="B467" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C467" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D467" s="4" t="inlineStr">
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D467" s="2" t="inlineStr">
         <is>
           <t>Schlafraum</t>
         </is>
       </c>
-      <c r="E467" s="4" t="n"/>
-      <c r="F467" s="3" t="n"/>
-      <c r="G467" s="4" t="n"/>
-      <c r="H467" s="4" t="n"/>
+      <c r="E467" s="2" t="inlineStr">
+        <is>
+          <t>Treppenregal weiß mit Wannen</t>
+        </is>
+      </c>
+      <c r="F467" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G467" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H467" s="2" t="n"/>
     </row>
     <row r="468">
-      <c r="A468" s="4" t="inlineStr">
+      <c r="A468" s="2" t="inlineStr">
         <is>
           <t>BU05-04</t>
         </is>
       </c>
-      <c r="B468" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C468" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D468" s="4" t="inlineStr">
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D468" s="2" t="inlineStr">
         <is>
           <t>Schlafraum</t>
         </is>
       </c>
-      <c r="E468" s="4" t="n"/>
-      <c r="F468" s="3" t="n"/>
-      <c r="G468" s="4" t="n"/>
-      <c r="H468" s="4" t="n"/>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>Schaukeltier Storch</t>
+        </is>
+      </c>
+      <c r="F468" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G468" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H468" s="2" t="n"/>
     </row>
     <row r="469">
-      <c r="A469" s="4" t="inlineStr">
+      <c r="A469" s="2" t="inlineStr">
         <is>
           <t>BU05-05</t>
         </is>
       </c>
-      <c r="B469" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C469" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D469" s="4" t="inlineStr">
+      <c r="B469" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D469" s="2" t="inlineStr">
         <is>
           <t>Schlafraum</t>
         </is>
       </c>
-      <c r="E469" s="4" t="n"/>
-      <c r="F469" s="3" t="n"/>
-      <c r="G469" s="4" t="n"/>
-      <c r="H469" s="4" t="n"/>
+      <c r="E469" s="2" t="inlineStr">
+        <is>
+          <t>Kindersessel Teddyfell beige</t>
+        </is>
+      </c>
+      <c r="F469" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G469" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H469" s="2" t="n"/>
     </row>
     <row r="470">
-      <c r="A470" s="4" t="inlineStr">
+      <c r="A470" s="2" t="inlineStr">
         <is>
           <t>BU05-06</t>
         </is>
       </c>
-      <c r="B470" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C470" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D470" s="4" t="inlineStr">
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D470" s="2" t="inlineStr">
         <is>
           <t>Schlafraum</t>
         </is>
       </c>
-      <c r="E470" s="4" t="n"/>
-      <c r="F470" s="3" t="n"/>
-      <c r="G470" s="4" t="n"/>
-      <c r="H470" s="4" t="n"/>
+      <c r="E470" s="2" t="inlineStr">
+        <is>
+          <t>Sitzbank gepolstert, hellgrau</t>
+        </is>
+      </c>
+      <c r="F470" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G470" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H470" s="2" t="n"/>
     </row>
     <row r="471">
-      <c r="A471" s="4" t="inlineStr">
+      <c r="A471" s="2" t="inlineStr">
         <is>
           <t>BU05-07</t>
         </is>
       </c>
-      <c r="B471" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C471" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D471" s="4" t="inlineStr">
+      <c r="B471" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C471" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D471" s="2" t="inlineStr">
         <is>
           <t>Schlafraum</t>
         </is>
       </c>
-      <c r="E471" s="4" t="n"/>
-      <c r="F471" s="3" t="n"/>
-      <c r="G471" s="4" t="n"/>
-      <c r="H471" s="4" t="n"/>
+      <c r="E471" s="2" t="inlineStr">
+        <is>
+          <t>Puppenwagen rosa mit Tragetasche</t>
+        </is>
+      </c>
+      <c r="F471" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G471" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H471" s="2" t="n"/>
     </row>
     <row r="472">
-      <c r="A472" s="4" t="inlineStr">
+      <c r="A472" s="2" t="inlineStr">
         <is>
           <t>BU05-08</t>
         </is>
       </c>
-      <c r="B472" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C472" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D472" s="4" t="inlineStr">
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D472" s="2" t="inlineStr">
         <is>
           <t>Schlafraum</t>
         </is>
       </c>
-      <c r="E472" s="4" t="n"/>
-      <c r="F472" s="3" t="n"/>
-      <c r="G472" s="4" t="n"/>
-      <c r="H472" s="4" t="n"/>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>Puppenwagen Holz mit Gummirädern</t>
+        </is>
+      </c>
+      <c r="F472" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G472" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H472" s="2" t="n"/>
     </row>
     <row r="473">
-      <c r="A473" s="4" t="inlineStr">
+      <c r="A473" s="2" t="inlineStr">
         <is>
           <t>BU05-09</t>
         </is>
       </c>
-      <c r="B473" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C473" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D473" s="4" t="inlineStr">
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D473" s="2" t="inlineStr">
         <is>
           <t>Schlafraum</t>
         </is>
       </c>
-      <c r="E473" s="4" t="n"/>
-      <c r="F473" s="3" t="n"/>
-      <c r="G473" s="4" t="n"/>
-      <c r="H473" s="4" t="n"/>
+      <c r="E473" s="2" t="inlineStr">
+        <is>
+          <t>Wesco Rutschfahrzeug mit Spielelementen</t>
+        </is>
+      </c>
+      <c r="F473" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G473" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H473" s="2" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="4" t="inlineStr">
@@ -31125,7 +31215,7 @@
         </is>
       </c>
       <c r="F1085" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G1085" s="2" t="inlineStr">
         <is>

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="F116" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
@@ -8243,238 +8243,328 @@
       <c r="H248" s="4" t="n"/>
     </row>
     <row r="249">
-      <c r="A249" s="4" t="inlineStr">
+      <c r="A249" s="2" t="inlineStr">
         <is>
           <t>NE03-01</t>
         </is>
       </c>
-      <c r="B249" s="4" t="inlineStr">
+      <c r="B249" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C249" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D249" s="4" t="inlineStr">
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 2</t>
         </is>
       </c>
-      <c r="E249" s="4" t="n"/>
-      <c r="F249" s="3" t="n"/>
-      <c r="G249" s="4" t="n"/>
-      <c r="H249" s="4" t="n"/>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>Wandregale in Wolkenform</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="n"/>
     </row>
     <row r="250">
-      <c r="A250" s="4" t="inlineStr">
+      <c r="A250" s="2" t="inlineStr">
         <is>
           <t>NE03-02</t>
         </is>
       </c>
-      <c r="B250" s="4" t="inlineStr">
+      <c r="B250" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C250" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D250" s="4" t="inlineStr">
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 2</t>
         </is>
       </c>
-      <c r="E250" s="4" t="n"/>
-      <c r="F250" s="3" t="n"/>
-      <c r="G250" s="4" t="n"/>
-      <c r="H250" s="4" t="n"/>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>Wesco Gitterbett Kunststoff, grau</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="n"/>
     </row>
     <row r="251">
-      <c r="A251" s="4" t="inlineStr">
+      <c r="A251" s="2" t="inlineStr">
         <is>
           <t>NE03-03</t>
         </is>
       </c>
-      <c r="B251" s="4" t="inlineStr">
+      <c r="B251" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C251" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D251" s="4" t="inlineStr">
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 2</t>
         </is>
       </c>
-      <c r="E251" s="4" t="n"/>
-      <c r="F251" s="3" t="n"/>
-      <c r="G251" s="4" t="n"/>
-      <c r="H251" s="4" t="n"/>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>Gitterbett Holz weiß</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="n"/>
     </row>
     <row r="252">
-      <c r="A252" s="4" t="inlineStr">
+      <c r="A252" s="2" t="inlineStr">
         <is>
           <t>NE03-04</t>
         </is>
       </c>
-      <c r="B252" s="4" t="inlineStr">
+      <c r="B252" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C252" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D252" s="4" t="inlineStr">
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 2</t>
         </is>
       </c>
-      <c r="E252" s="4" t="n"/>
-      <c r="F252" s="3" t="n"/>
-      <c r="G252" s="4" t="n"/>
-      <c r="H252" s="4" t="n"/>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>Hauck Kinderwagen schwarz</t>
+        </is>
+      </c>
+      <c r="F252" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="n"/>
     </row>
     <row r="253">
-      <c r="A253" s="4" t="inlineStr">
+      <c r="A253" s="2" t="inlineStr">
         <is>
           <t>NE03-05</t>
         </is>
       </c>
-      <c r="B253" s="4" t="inlineStr">
+      <c r="B253" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C253" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D253" s="4" t="inlineStr">
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 2</t>
         </is>
       </c>
-      <c r="E253" s="4" t="n"/>
-      <c r="F253" s="3" t="n"/>
-      <c r="G253" s="4" t="n"/>
-      <c r="H253" s="4" t="n"/>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>Leuchtobjekt Elefant, Metall</t>
+        </is>
+      </c>
+      <c r="F253" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="n"/>
     </row>
     <row r="254">
-      <c r="A254" s="4" t="inlineStr">
+      <c r="A254" s="2" t="inlineStr">
         <is>
           <t>NE03-06</t>
         </is>
       </c>
-      <c r="B254" s="4" t="inlineStr">
+      <c r="B254" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C254" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D254" s="4" t="inlineStr">
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 2</t>
         </is>
       </c>
-      <c r="E254" s="4" t="n"/>
-      <c r="F254" s="3" t="n"/>
-      <c r="G254" s="4" t="n"/>
-      <c r="H254" s="4" t="n"/>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Kleiderschrank anthrazit mit drei Böden</t>
+        </is>
+      </c>
+      <c r="F254" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="n"/>
     </row>
     <row r="255">
-      <c r="A255" s="4" t="inlineStr">
+      <c r="A255" s="2" t="inlineStr">
         <is>
           <t>NE03-07</t>
         </is>
       </c>
-      <c r="B255" s="4" t="inlineStr">
+      <c r="B255" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C255" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D255" s="4" t="inlineStr">
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 2</t>
         </is>
       </c>
-      <c r="E255" s="4" t="n"/>
-      <c r="F255" s="3" t="n"/>
-      <c r="G255" s="4" t="n"/>
-      <c r="H255" s="4" t="n"/>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Schrank weiß mit Drahtkörben</t>
+        </is>
+      </c>
+      <c r="F255" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="n"/>
     </row>
     <row r="256">
-      <c r="A256" s="4" t="inlineStr">
+      <c r="A256" s="2" t="inlineStr">
         <is>
           <t>NE03-08</t>
         </is>
       </c>
-      <c r="B256" s="4" t="inlineStr">
+      <c r="B256" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C256" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D256" s="4" t="inlineStr">
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 2</t>
         </is>
       </c>
-      <c r="E256" s="4" t="n"/>
-      <c r="F256" s="3" t="n"/>
-      <c r="G256" s="4" t="n"/>
-      <c r="H256" s="4" t="n"/>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>Plüsch-Elefanten, zwei Stück</t>
+        </is>
+      </c>
+      <c r="F256" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="n"/>
     </row>
     <row r="257">
-      <c r="A257" s="4" t="inlineStr">
+      <c r="A257" s="2" t="inlineStr">
         <is>
           <t>NE03-09</t>
         </is>
       </c>
-      <c r="B257" s="4" t="inlineStr">
+      <c r="B257" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C257" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D257" s="4" t="inlineStr">
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 2</t>
         </is>
       </c>
-      <c r="E257" s="4" t="n"/>
-      <c r="F257" s="3" t="n"/>
-      <c r="G257" s="4" t="n"/>
-      <c r="H257" s="4" t="n"/>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>Wolken-Mobile Stoff, weiß</t>
+        </is>
+      </c>
+      <c r="F257" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="4" t="inlineStr">

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="F251" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         </is>
       </c>
       <c r="F257" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
@@ -8983,316 +8983,436 @@
       <c r="H273" s="4" t="n"/>
     </row>
     <row r="274">
-      <c r="A274" s="4" t="inlineStr">
+      <c r="A274" s="2" t="inlineStr">
         <is>
           <t>NE04-01</t>
         </is>
       </c>
-      <c r="B274" s="4" t="inlineStr">
+      <c r="B274" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C274" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D274" s="4" t="inlineStr">
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 3</t>
         </is>
       </c>
-      <c r="E274" s="4" t="n"/>
-      <c r="F274" s="3" t="n"/>
-      <c r="G274" s="4" t="n"/>
-      <c r="H274" s="4" t="n"/>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>Wanddekoration Wolken schwarz</t>
+        </is>
+      </c>
+      <c r="F274" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="n"/>
     </row>
     <row r="275">
-      <c r="A275" s="4" t="inlineStr">
+      <c r="A275" s="2" t="inlineStr">
         <is>
           <t>NE04-02</t>
         </is>
       </c>
-      <c r="B275" s="4" t="inlineStr">
+      <c r="B275" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C275" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D275" s="4" t="inlineStr">
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 3</t>
         </is>
       </c>
-      <c r="E275" s="4" t="n"/>
-      <c r="F275" s="3" t="n"/>
-      <c r="G275" s="4" t="n"/>
-      <c r="H275" s="4" t="n"/>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>Schrank weiß mit zwei Türen und zwei Schubladen</t>
+        </is>
+      </c>
+      <c r="F275" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="n"/>
     </row>
     <row r="276">
-      <c r="A276" s="4" t="inlineStr">
+      <c r="A276" s="2" t="inlineStr">
         <is>
           <t>NE04-03</t>
         </is>
       </c>
-      <c r="B276" s="4" t="inlineStr">
+      <c r="B276" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C276" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D276" s="4" t="inlineStr">
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 3</t>
         </is>
       </c>
-      <c r="E276" s="4" t="n"/>
-      <c r="F276" s="3" t="n"/>
-      <c r="G276" s="4" t="n"/>
-      <c r="H276" s="4" t="n"/>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>Wandspiegel in Wolkenform, weiß</t>
+        </is>
+      </c>
+      <c r="F276" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="n"/>
     </row>
     <row r="277">
-      <c r="A277" s="4" t="inlineStr">
+      <c r="A277" s="2" t="inlineStr">
         <is>
           <t>NE04-04</t>
         </is>
       </c>
-      <c r="B277" s="4" t="inlineStr">
+      <c r="B277" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C277" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D277" s="4" t="inlineStr">
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 3</t>
         </is>
       </c>
-      <c r="E277" s="4" t="n"/>
-      <c r="F277" s="3" t="n"/>
-      <c r="G277" s="4" t="n"/>
-      <c r="H277" s="4" t="n"/>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>Wesco Wickelauflage beige</t>
+        </is>
+      </c>
+      <c r="F277" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="n"/>
     </row>
     <row r="278">
-      <c r="A278" s="4" t="inlineStr">
+      <c r="A278" s="2" t="inlineStr">
         <is>
           <t>NE04-05</t>
         </is>
       </c>
-      <c r="B278" s="4" t="inlineStr">
+      <c r="B278" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C278" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D278" s="4" t="inlineStr">
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 3</t>
         </is>
       </c>
-      <c r="E278" s="4" t="n"/>
-      <c r="F278" s="3" t="n"/>
-      <c r="G278" s="4" t="n"/>
-      <c r="H278" s="4" t="n"/>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>Wickelkommode Buche mit zehn Wannen</t>
+        </is>
+      </c>
+      <c r="F278" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="n"/>
     </row>
     <row r="279">
-      <c r="A279" s="4" t="inlineStr">
+      <c r="A279" s="2" t="inlineStr">
         <is>
           <t>NE04-06</t>
         </is>
       </c>
-      <c r="B279" s="4" t="inlineStr">
+      <c r="B279" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C279" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D279" s="4" t="inlineStr">
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 3</t>
         </is>
       </c>
-      <c r="E279" s="4" t="n"/>
-      <c r="F279" s="3" t="n"/>
-      <c r="G279" s="4" t="n"/>
-      <c r="H279" s="4" t="n"/>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>Wickelkommode Buche groß mit Treppe</t>
+        </is>
+      </c>
+      <c r="F279" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="n"/>
     </row>
     <row r="280">
-      <c r="A280" s="4" t="inlineStr">
+      <c r="A280" s="2" t="inlineStr">
         <is>
           <t>NE04-07</t>
         </is>
       </c>
-      <c r="B280" s="4" t="inlineStr">
+      <c r="B280" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C280" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D280" s="4" t="inlineStr">
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 3</t>
         </is>
       </c>
-      <c r="E280" s="4" t="n"/>
-      <c r="F280" s="3" t="n"/>
-      <c r="G280" s="4" t="n"/>
-      <c r="H280" s="4" t="n"/>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>Wickelkommode mit Türen und Fachböden</t>
+        </is>
+      </c>
+      <c r="F280" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="n"/>
     </row>
     <row r="281">
-      <c r="A281" s="4" t="inlineStr">
+      <c r="A281" s="2" t="inlineStr">
         <is>
           <t>NE04-08</t>
         </is>
       </c>
-      <c r="B281" s="4" t="inlineStr">
+      <c r="B281" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C281" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D281" s="4" t="inlineStr">
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 3</t>
         </is>
       </c>
-      <c r="E281" s="4" t="n"/>
-      <c r="F281" s="3" t="n"/>
-      <c r="G281" s="4" t="n"/>
-      <c r="H281" s="4" t="n"/>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>Baby Jogger City Select Kinderwagen, rot</t>
+        </is>
+      </c>
+      <c r="F281" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="n"/>
     </row>
     <row r="282">
-      <c r="A282" s="4" t="inlineStr">
+      <c r="A282" s="2" t="inlineStr">
         <is>
           <t>NE04-09</t>
         </is>
       </c>
-      <c r="B282" s="4" t="inlineStr">
+      <c r="B282" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C282" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D282" s="4" t="inlineStr">
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 3</t>
         </is>
       </c>
-      <c r="E282" s="4" t="n"/>
-      <c r="F282" s="3" t="n"/>
-      <c r="G282" s="4" t="n"/>
-      <c r="H282" s="4" t="n"/>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>Hochflorteppich rund, rot-orange</t>
+        </is>
+      </c>
+      <c r="F282" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="n"/>
     </row>
     <row r="283">
-      <c r="A283" s="4" t="inlineStr">
+      <c r="A283" s="2" t="inlineStr">
         <is>
           <t>NE04-10</t>
         </is>
       </c>
-      <c r="B283" s="4" t="inlineStr">
+      <c r="B283" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C283" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D283" s="4" t="inlineStr">
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 3</t>
         </is>
       </c>
-      <c r="E283" s="4" t="n"/>
-      <c r="F283" s="3" t="n"/>
-      <c r="G283" s="4" t="n"/>
-      <c r="H283" s="4" t="n"/>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>Windeleimer weiß mit Deckel</t>
+        </is>
+      </c>
+      <c r="F283" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="n"/>
     </row>
     <row r="284">
-      <c r="A284" s="4" t="inlineStr">
+      <c r="A284" s="2" t="inlineStr">
         <is>
           <t>NE04-11</t>
         </is>
       </c>
-      <c r="B284" s="4" t="inlineStr">
+      <c r="B284" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C284" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D284" s="4" t="inlineStr">
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 3</t>
         </is>
       </c>
-      <c r="E284" s="4" t="n"/>
-      <c r="F284" s="3" t="n"/>
-      <c r="G284" s="4" t="n"/>
-      <c r="H284" s="4" t="n"/>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>Wandregal in Bergform, Holz</t>
+        </is>
+      </c>
+      <c r="F284" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="n"/>
     </row>
     <row r="285">
-      <c r="A285" s="4" t="inlineStr">
+      <c r="A285" s="2" t="inlineStr">
         <is>
           <t>NE04-12</t>
         </is>
       </c>
-      <c r="B285" s="4" t="inlineStr">
+      <c r="B285" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C285" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D285" s="4" t="inlineStr">
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
         <is>
           <t>Schlafraum 3</t>
         </is>
       </c>
-      <c r="E285" s="4" t="n"/>
-      <c r="F285" s="3" t="n"/>
-      <c r="G285" s="4" t="n"/>
-      <c r="H285" s="4" t="n"/>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>Mobile Holzbogen mit Filzkugeln</t>
+        </is>
+      </c>
+      <c r="F285" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="4" t="inlineStr">

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="F110" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         </is>
       </c>
       <c r="F299" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         </is>
       </c>
       <c r="F300" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
@@ -9861,290 +9861,400 @@
       <c r="H301" s="2" t="n"/>
     </row>
     <row r="302">
-      <c r="A302" s="4" t="inlineStr">
+      <c r="A302" s="2" t="inlineStr">
         <is>
           <t>NE05-04</t>
         </is>
       </c>
-      <c r="B302" s="4" t="inlineStr">
+      <c r="B302" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C302" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D302" s="4" t="inlineStr">
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
         <is>
           <t>Speisesaal</t>
         </is>
       </c>
-      <c r="E302" s="4" t="n"/>
-      <c r="F302" s="3" t="n"/>
-      <c r="G302" s="4" t="n"/>
-      <c r="H302" s="4" t="n"/>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>Freischwinger rot, Erwachsenengröße</t>
+        </is>
+      </c>
+      <c r="F302" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="n"/>
     </row>
     <row r="303">
-      <c r="A303" s="4" t="inlineStr">
+      <c r="A303" s="2" t="inlineStr">
         <is>
           <t>NE05-05</t>
         </is>
       </c>
-      <c r="B303" s="4" t="inlineStr">
+      <c r="B303" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C303" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D303" s="4" t="inlineStr">
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
         <is>
           <t>Speisesaal</t>
         </is>
       </c>
-      <c r="E303" s="4" t="n"/>
-      <c r="F303" s="3" t="n"/>
-      <c r="G303" s="4" t="n"/>
-      <c r="H303" s="4" t="n"/>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>Freischwinger rot, Kindergröße</t>
+        </is>
+      </c>
+      <c r="F303" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="n"/>
     </row>
     <row r="304">
-      <c r="A304" s="4" t="inlineStr">
+      <c r="A304" s="2" t="inlineStr">
         <is>
           <t>NE05-06</t>
         </is>
       </c>
-      <c r="B304" s="4" t="inlineStr">
+      <c r="B304" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C304" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D304" s="4" t="inlineStr">
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
         <is>
           <t>Speisesaal</t>
         </is>
       </c>
-      <c r="E304" s="4" t="n"/>
-      <c r="F304" s="3" t="n"/>
-      <c r="G304" s="4" t="n"/>
-      <c r="H304" s="4" t="n"/>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>Treppenhochstuhl schwarz</t>
+        </is>
+      </c>
+      <c r="F304" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="n"/>
     </row>
     <row r="305">
-      <c r="A305" s="4" t="inlineStr">
+      <c r="A305" s="2" t="inlineStr">
         <is>
           <t>NE05-07</t>
         </is>
       </c>
-      <c r="B305" s="4" t="inlineStr">
+      <c r="B305" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C305" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D305" s="4" t="inlineStr">
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
         <is>
           <t>Speisesaal</t>
         </is>
       </c>
-      <c r="E305" s="4" t="n"/>
-      <c r="F305" s="3" t="n"/>
-      <c r="G305" s="4" t="n"/>
-      <c r="H305" s="4" t="n"/>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>Treppenhochstuhl schwarz-weiß</t>
+        </is>
+      </c>
+      <c r="F305" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="n"/>
     </row>
     <row r="306">
-      <c r="A306" s="4" t="inlineStr">
+      <c r="A306" s="2" t="inlineStr">
         <is>
           <t>NE05-08</t>
         </is>
       </c>
-      <c r="B306" s="4" t="inlineStr">
+      <c r="B306" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C306" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D306" s="4" t="inlineStr">
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
         <is>
           <t>Speisesaal</t>
         </is>
       </c>
-      <c r="E306" s="4" t="n"/>
-      <c r="F306" s="3" t="n"/>
-      <c r="G306" s="4" t="n"/>
-      <c r="H306" s="4" t="n"/>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>Treppenhochstuhl grau mit Buchengestell</t>
+        </is>
+      </c>
+      <c r="F306" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="n"/>
     </row>
     <row r="307">
-      <c r="A307" s="4" t="inlineStr">
+      <c r="A307" s="2" t="inlineStr">
         <is>
           <t>NE05-09</t>
         </is>
       </c>
-      <c r="B307" s="4" t="inlineStr">
+      <c r="B307" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C307" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D307" s="4" t="inlineStr">
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
         <is>
           <t>Speisesaal</t>
         </is>
       </c>
-      <c r="E307" s="4" t="n"/>
-      <c r="F307" s="3" t="n"/>
-      <c r="G307" s="4" t="n"/>
-      <c r="H307" s="4" t="n"/>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Ingolf Kinderhochstuhl weiß</t>
+        </is>
+      </c>
+      <c r="F307" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="n"/>
     </row>
     <row r="308">
-      <c r="A308" s="4" t="inlineStr">
+      <c r="A308" s="2" t="inlineStr">
         <is>
           <t>NE05-10</t>
         </is>
       </c>
-      <c r="B308" s="4" t="inlineStr">
+      <c r="B308" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C308" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D308" s="4" t="inlineStr">
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
         <is>
           <t>Speisesaal</t>
         </is>
       </c>
-      <c r="E308" s="4" t="n"/>
-      <c r="F308" s="3" t="n"/>
-      <c r="G308" s="4" t="n"/>
-      <c r="H308" s="4" t="n"/>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>Rollwagen schwarz mit Holzplatte</t>
+        </is>
+      </c>
+      <c r="F308" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="n"/>
     </row>
     <row r="309">
-      <c r="A309" s="4" t="inlineStr">
+      <c r="A309" s="2" t="inlineStr">
         <is>
           <t>NE05-11</t>
         </is>
       </c>
-      <c r="B309" s="4" t="inlineStr">
+      <c r="B309" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C309" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D309" s="4" t="inlineStr">
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
         <is>
           <t>Speisesaal</t>
         </is>
       </c>
-      <c r="E309" s="4" t="n"/>
-      <c r="F309" s="3" t="n"/>
-      <c r="G309" s="4" t="n"/>
-      <c r="H309" s="4" t="n"/>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>Glas-Magnettafel weiß, großformatig</t>
+        </is>
+      </c>
+      <c r="F309" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="n"/>
     </row>
     <row r="310">
-      <c r="A310" s="4" t="inlineStr">
+      <c r="A310" s="2" t="inlineStr">
         <is>
           <t>NE05-12</t>
         </is>
       </c>
-      <c r="B310" s="4" t="inlineStr">
+      <c r="B310" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C310" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D310" s="4" t="inlineStr">
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
         <is>
           <t>Speisesaal</t>
         </is>
       </c>
-      <c r="E310" s="4" t="n"/>
-      <c r="F310" s="3" t="n"/>
-      <c r="G310" s="4" t="n"/>
-      <c r="H310" s="4" t="n"/>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>Wandleuchte Rehkitz schwarz</t>
+        </is>
+      </c>
+      <c r="F310" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="n"/>
     </row>
     <row r="311">
-      <c r="A311" s="4" t="inlineStr">
+      <c r="A311" s="2" t="inlineStr">
         <is>
           <t>NE05-13</t>
         </is>
       </c>
-      <c r="B311" s="4" t="inlineStr">
+      <c r="B311" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C311" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D311" s="4" t="inlineStr">
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
         <is>
           <t>Speisesaal</t>
         </is>
       </c>
-      <c r="E311" s="4" t="n"/>
-      <c r="F311" s="3" t="n"/>
-      <c r="G311" s="4" t="n"/>
-      <c r="H311" s="4" t="n"/>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>Deko-Stern Holz</t>
+        </is>
+      </c>
+      <c r="F311" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="n"/>
     </row>
     <row r="312">
-      <c r="A312" s="4" t="inlineStr">
+      <c r="A312" s="2" t="inlineStr">
         <is>
           <t>NE05-14</t>
         </is>
       </c>
-      <c r="B312" s="4" t="inlineStr">
+      <c r="B312" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C312" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D312" s="4" t="inlineStr">
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
         <is>
           <t>Speisesaal</t>
         </is>
       </c>
-      <c r="E312" s="4" t="n"/>
-      <c r="F312" s="3" t="n"/>
-      <c r="G312" s="4" t="n"/>
-      <c r="H312" s="4" t="n"/>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>Wandhaken in Stuhlform, schwarz</t>
+        </is>
+      </c>
+      <c r="F312" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="4" t="inlineStr">

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -10099,11 +10099,11 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>Rollwagen schwarz mit Holzplatte</t>
+          <t>Freischwinger weiß, Kindergröße</t>
         </is>
       </c>
       <c r="F308" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
@@ -10135,11 +10135,11 @@
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>Glas-Magnettafel weiß, großformatig</t>
+          <t>Rollwagen schwarz mit Holzplatte</t>
         </is>
       </c>
       <c r="F309" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
@@ -10171,11 +10171,11 @@
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>Wandleuchte Rehkitz schwarz</t>
+          <t>Glas-Magnettafel weiß, großformatig</t>
         </is>
       </c>
       <c r="F310" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
@@ -10207,11 +10207,11 @@
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>Deko-Stern Holz</t>
+          <t>Wandleuchte Rehkitz schwarz</t>
         </is>
       </c>
       <c r="F311" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
@@ -10243,44 +10243,54 @@
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
+          <t>Deko-Stern Holz</t>
+        </is>
+      </c>
+      <c r="F312" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>NE05-15</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>Neubau</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>Speisesaal</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
           <t>Wandhaken in Stuhlform, schwarz</t>
         </is>
       </c>
-      <c r="F312" s="3" t="n">
+      <c r="F313" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G312" s="2" t="inlineStr">
+      <c r="G313" s="2" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="H312" s="2" t="n"/>
-    </row>
-    <row r="313">
-      <c r="A313" s="4" t="inlineStr">
-        <is>
-          <t>NE05-15</t>
-        </is>
-      </c>
-      <c r="B313" s="4" t="inlineStr">
-        <is>
-          <t>Neubau</t>
-        </is>
-      </c>
-      <c r="C313" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D313" s="4" t="inlineStr">
-        <is>
-          <t>Speisesaal</t>
-        </is>
-      </c>
-      <c r="E313" s="4" t="n"/>
-      <c r="F313" s="3" t="n"/>
-      <c r="G313" s="4" t="n"/>
-      <c r="H313" s="4" t="n"/>
+      <c r="H313" s="2" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="4" t="inlineStr">

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -2155,11 +2155,11 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Sitztier Elefant, weiß und schwarz</t>
+          <t>Vitra Eames Elephant, große Ausführung</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
@@ -2385,30 +2385,40 @@
       <c r="H55" s="2" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>NU02-23</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Neubau</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="E56" s="4" t="n"/>
-      <c r="F56" s="3" t="n"/>
-      <c r="G56" s="4" t="n"/>
-      <c r="H56" s="4" t="n"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Vitra Eames Elephant, kleine Ausführung, schwarz</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -4641,7 +4651,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Mitwachsender Treppenhochstuhl, weiß</t>
+          <t>Stokke Steps Treppenhochstuhl, weiß mit Buchengestell</t>
         </is>
       </c>
       <c r="F130" s="3" t="n">
@@ -9883,7 +9893,7 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>Freischwinger rot, Erwachsenengröße</t>
+          <t>Vitra Panton Chair rot, Erwachsenengröße</t>
         </is>
       </c>
       <c r="F302" s="3" t="n">
@@ -9919,7 +9929,7 @@
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>Freischwinger rot, Kindergröße</t>
+          <t>Vitra Panton Chair Junior rot, Kindergröße</t>
         </is>
       </c>
       <c r="F303" s="3" t="n">
@@ -9955,7 +9965,7 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>Treppenhochstuhl schwarz</t>
+          <t>Stokke Steps Treppenhochstuhl, schwarz</t>
         </is>
       </c>
       <c r="F304" s="3" t="n">
@@ -9991,7 +10001,7 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>Treppenhochstuhl schwarz-weiß</t>
+          <t>Stokke Steps Treppenhochstuhl, weiß mit schwarzem Gestell</t>
         </is>
       </c>
       <c r="F305" s="3" t="n">
@@ -10027,7 +10037,7 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>Treppenhochstuhl grau mit Buchengestell</t>
+          <t>Stokke Steps Treppenhochstuhl, grau mit Buchengestell</t>
         </is>
       </c>
       <c r="F306" s="3" t="n">
@@ -10099,7 +10109,7 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>Freischwinger weiß, Kindergröße</t>
+          <t>Vitra Panton Chair Junior weiß, Kindergröße</t>
         </is>
       </c>
       <c r="F308" s="3" t="n">

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -4283,7 +4283,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Freischwinger schwarz, Kunststoff</t>
+          <t>Vitra Panton Chair schwarz, Erwachsenengröße</t>
         </is>
       </c>
       <c r="F117" s="3" t="n">
@@ -19377,108 +19377,148 @@
       <c r="H637" s="2" t="n"/>
     </row>
     <row r="638">
-      <c r="A638" s="4" t="inlineStr">
+      <c r="A638" s="2" t="inlineStr">
         <is>
           <t>BE01-04</t>
         </is>
       </c>
-      <c r="B638" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C638" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D638" s="4" t="inlineStr">
+      <c r="B638" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C638" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D638" s="2" t="inlineStr">
         <is>
           <t>Flur 1</t>
         </is>
       </c>
-      <c r="E638" s="4" t="n"/>
-      <c r="F638" s="3" t="n"/>
-      <c r="G638" s="4" t="n"/>
-      <c r="H638" s="4" t="n"/>
+      <c r="E638" s="2" t="inlineStr">
+        <is>
+          <t>Beistelltisch rund, Drahtgestell schwarz</t>
+        </is>
+      </c>
+      <c r="F638" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G638" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H638" s="2" t="n"/>
     </row>
     <row r="639">
-      <c r="A639" s="4" t="inlineStr">
+      <c r="A639" s="2" t="inlineStr">
         <is>
           <t>BE01-05</t>
         </is>
       </c>
-      <c r="B639" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C639" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D639" s="4" t="inlineStr">
+      <c r="B639" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C639" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D639" s="2" t="inlineStr">
         <is>
           <t>Flur 1</t>
         </is>
       </c>
-      <c r="E639" s="4" t="n"/>
-      <c r="F639" s="3" t="n"/>
-      <c r="G639" s="4" t="n"/>
-      <c r="H639" s="4" t="n"/>
+      <c r="E639" s="2" t="inlineStr">
+        <is>
+          <t>Wandhängeregal weiß, drei Fächer</t>
+        </is>
+      </c>
+      <c r="F639" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G639" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H639" s="2" t="n"/>
     </row>
     <row r="640">
-      <c r="A640" s="4" t="inlineStr">
+      <c r="A640" s="2" t="inlineStr">
         <is>
           <t>BE01-06</t>
         </is>
       </c>
-      <c r="B640" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C640" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D640" s="4" t="inlineStr">
+      <c r="B640" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C640" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D640" s="2" t="inlineStr">
         <is>
           <t>Flur 1</t>
         </is>
       </c>
-      <c r="E640" s="4" t="n"/>
-      <c r="F640" s="3" t="n"/>
-      <c r="G640" s="4" t="n"/>
-      <c r="H640" s="4" t="n"/>
+      <c r="E640" s="2" t="inlineStr">
+        <is>
+          <t>Wandregal in Hausform, Holz</t>
+        </is>
+      </c>
+      <c r="F640" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G640" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H640" s="2" t="n"/>
     </row>
     <row r="641">
-      <c r="A641" s="4" t="inlineStr">
+      <c r="A641" s="2" t="inlineStr">
         <is>
           <t>BE01-07</t>
         </is>
       </c>
-      <c r="B641" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C641" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D641" s="4" t="inlineStr">
+      <c r="B641" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C641" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D641" s="2" t="inlineStr">
         <is>
           <t>Flur 1</t>
         </is>
       </c>
-      <c r="E641" s="4" t="n"/>
-      <c r="F641" s="3" t="n"/>
-      <c r="G641" s="4" t="n"/>
-      <c r="H641" s="4" t="n"/>
+      <c r="E641" s="2" t="inlineStr">
+        <is>
+          <t>Wanddeko Hirschkopf mit Holzgeweih</t>
+        </is>
+      </c>
+      <c r="F641" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G641" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H641" s="2" t="n"/>
     </row>
     <row r="642">
       <c r="A642" s="4" t="inlineStr">
@@ -24155,7 +24195,7 @@
         </is>
       </c>
       <c r="F820" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G820" s="2" t="inlineStr">
         <is>
@@ -24273,108 +24313,148 @@
       <c r="H823" s="2" t="n"/>
     </row>
     <row r="824">
-      <c r="A824" s="4" t="inlineStr">
+      <c r="A824" s="2" t="inlineStr">
         <is>
           <t>BE10-05</t>
         </is>
       </c>
-      <c r="B824" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C824" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D824" s="4" t="inlineStr">
+      <c r="B824" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C824" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D824" s="2" t="inlineStr">
         <is>
           <t>Büro / Besprechung</t>
         </is>
       </c>
-      <c r="E824" s="4" t="n"/>
-      <c r="F824" s="3" t="n"/>
-      <c r="G824" s="4" t="n"/>
-      <c r="H824" s="4" t="n"/>
+      <c r="E824" s="2" t="inlineStr">
+        <is>
+          <t>Schalenstuhl weiß mit Holzbeinen</t>
+        </is>
+      </c>
+      <c r="F824" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G824" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H824" s="2" t="n"/>
     </row>
     <row r="825">
-      <c r="A825" s="4" t="inlineStr">
+      <c r="A825" s="2" t="inlineStr">
         <is>
           <t>BE10-06</t>
         </is>
       </c>
-      <c r="B825" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C825" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D825" s="4" t="inlineStr">
+      <c r="B825" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C825" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D825" s="2" t="inlineStr">
         <is>
           <t>Büro / Besprechung</t>
         </is>
       </c>
-      <c r="E825" s="4" t="n"/>
-      <c r="F825" s="3" t="n"/>
-      <c r="G825" s="4" t="n"/>
-      <c r="H825" s="4" t="n"/>
+      <c r="E825" s="2" t="inlineStr">
+        <is>
+          <t>Acrylbild abstrakt, schwarz-weiß-beige, großformatig</t>
+        </is>
+      </c>
+      <c r="F825" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G825" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H825" s="2" t="n"/>
     </row>
     <row r="826">
-      <c r="A826" s="4" t="inlineStr">
+      <c r="A826" s="2" t="inlineStr">
         <is>
           <t>BE10-07</t>
         </is>
       </c>
-      <c r="B826" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C826" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D826" s="4" t="inlineStr">
+      <c r="B826" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C826" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D826" s="2" t="inlineStr">
         <is>
           <t>Büro / Besprechung</t>
         </is>
       </c>
-      <c r="E826" s="4" t="n"/>
-      <c r="F826" s="3" t="n"/>
-      <c r="G826" s="4" t="n"/>
-      <c r="H826" s="4" t="n"/>
+      <c r="E826" s="2" t="inlineStr">
+        <is>
+          <t>Flipchart fahrbar mit Papierrolle</t>
+        </is>
+      </c>
+      <c r="F826" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G826" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H826" s="2" t="n"/>
     </row>
     <row r="827">
-      <c r="A827" s="4" t="inlineStr">
+      <c r="A827" s="2" t="inlineStr">
         <is>
           <t>BE10-08</t>
         </is>
       </c>
-      <c r="B827" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C827" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D827" s="4" t="inlineStr">
+      <c r="B827" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C827" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D827" s="2" t="inlineStr">
         <is>
           <t>Büro / Besprechung</t>
         </is>
       </c>
-      <c r="E827" s="4" t="n"/>
-      <c r="F827" s="3" t="n"/>
-      <c r="G827" s="4" t="n"/>
-      <c r="H827" s="4" t="n"/>
+      <c r="E827" s="2" t="inlineStr">
+        <is>
+          <t>Eckschreibtisch weiß</t>
+        </is>
+      </c>
+      <c r="F827" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G827" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H827" s="2" t="n"/>
     </row>
     <row r="828">
       <c r="A828" s="4" t="inlineStr">
@@ -28707,7 +28787,7 @@
       </c>
       <c r="E986" s="2" t="inlineStr">
         <is>
-          <t>Stapelstuhl Kunststoff weiß, Erwachsenengröße</t>
+          <t>IKEA Urban Stapelstuhl weiß, Erwachsenengröße</t>
         </is>
       </c>
       <c r="F986" s="3" t="n">

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -24457,108 +24457,148 @@
       <c r="H827" s="2" t="n"/>
     </row>
     <row r="828">
-      <c r="A828" s="4" t="inlineStr">
+      <c r="A828" s="2" t="inlineStr">
         <is>
           <t>BE10-09</t>
         </is>
       </c>
-      <c r="B828" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C828" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D828" s="4" t="inlineStr">
+      <c r="B828" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C828" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D828" s="2" t="inlineStr">
         <is>
           <t>Büro / Besprechung</t>
         </is>
       </c>
-      <c r="E828" s="4" t="n"/>
-      <c r="F828" s="3" t="n"/>
-      <c r="G828" s="4" t="n"/>
-      <c r="H828" s="4" t="n"/>
+      <c r="E828" s="2" t="inlineStr">
+        <is>
+          <t>Konsolentisch schwarz mit Glasablagen</t>
+        </is>
+      </c>
+      <c r="F828" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G828" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H828" s="2" t="n"/>
     </row>
     <row r="829">
-      <c r="A829" s="4" t="inlineStr">
+      <c r="A829" s="2" t="inlineStr">
         <is>
           <t>BE10-10</t>
         </is>
       </c>
-      <c r="B829" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C829" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D829" s="4" t="inlineStr">
+      <c r="B829" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C829" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D829" s="2" t="inlineStr">
         <is>
           <t>Büro / Besprechung</t>
         </is>
       </c>
-      <c r="E829" s="4" t="n"/>
-      <c r="F829" s="3" t="n"/>
-      <c r="G829" s="4" t="n"/>
-      <c r="H829" s="4" t="n"/>
+      <c r="E829" s="2" t="inlineStr">
+        <is>
+          <t>Kommode Holz, antik</t>
+        </is>
+      </c>
+      <c r="F829" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G829" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H829" s="2" t="n"/>
     </row>
     <row r="830">
-      <c r="A830" s="4" t="inlineStr">
+      <c r="A830" s="2" t="inlineStr">
         <is>
           <t>BE10-11</t>
         </is>
       </c>
-      <c r="B830" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C830" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D830" s="4" t="inlineStr">
+      <c r="B830" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C830" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D830" s="2" t="inlineStr">
         <is>
           <t>Büro / Besprechung</t>
         </is>
       </c>
-      <c r="E830" s="4" t="n"/>
-      <c r="F830" s="3" t="n"/>
-      <c r="G830" s="4" t="n"/>
-      <c r="H830" s="4" t="n"/>
+      <c r="E830" s="2" t="inlineStr">
+        <is>
+          <t>Bürodrehstuhl weiß</t>
+        </is>
+      </c>
+      <c r="F830" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G830" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H830" s="2" t="n"/>
     </row>
     <row r="831">
-      <c r="A831" s="4" t="inlineStr">
+      <c r="A831" s="2" t="inlineStr">
         <is>
           <t>BE10-12</t>
         </is>
       </c>
-      <c r="B831" s="4" t="inlineStr">
-        <is>
-          <t>Bestandsgebäude</t>
-        </is>
-      </c>
-      <c r="C831" s="4" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D831" s="4" t="inlineStr">
+      <c r="B831" s="2" t="inlineStr">
+        <is>
+          <t>Bestandsgebäude</t>
+        </is>
+      </c>
+      <c r="C831" s="2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D831" s="2" t="inlineStr">
         <is>
           <t>Büro / Besprechung</t>
         </is>
       </c>
-      <c r="E831" s="4" t="n"/>
-      <c r="F831" s="3" t="n"/>
-      <c r="G831" s="4" t="n"/>
-      <c r="H831" s="4" t="n"/>
+      <c r="E831" s="2" t="inlineStr">
+        <is>
+          <t>Aktenschrank weiß</t>
+        </is>
+      </c>
+      <c r="F831" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G831" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H831" s="2" t="n"/>
     </row>
     <row r="832">
       <c r="A832" s="4" t="inlineStr">

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -35963,316 +35963,436 @@
       <c r="H1233" s="2" t="n"/>
     </row>
     <row r="1234">
-      <c r="A1234" s="4" t="inlineStr">
+      <c r="A1234" s="2" t="inlineStr">
         <is>
           <t>TE02-07</t>
         </is>
       </c>
-      <c r="B1234" s="4" t="inlineStr">
+      <c r="B1234" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1234" s="4" t="inlineStr">
+      <c r="C1234" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1234" s="4" t="inlineStr">
+      <c r="D1234" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1234" s="4" t="n"/>
-      <c r="F1234" s="3" t="n"/>
-      <c r="G1234" s="4" t="n"/>
-      <c r="H1234" s="4" t="n"/>
+      <c r="E1234" s="2" t="inlineStr">
+        <is>
+          <t>KidKraft Kinder-Strandliege mit Sonnendach</t>
+        </is>
+      </c>
+      <c r="F1234" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1234" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1234" s="2" t="n"/>
     </row>
     <row r="1235">
-      <c r="A1235" s="4" t="inlineStr">
+      <c r="A1235" s="2" t="inlineStr">
         <is>
           <t>TE02-08</t>
         </is>
       </c>
-      <c r="B1235" s="4" t="inlineStr">
+      <c r="B1235" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1235" s="4" t="inlineStr">
+      <c r="C1235" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1235" s="4" t="inlineStr">
+      <c r="D1235" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1235" s="4" t="n"/>
-      <c r="F1235" s="3" t="n"/>
-      <c r="G1235" s="4" t="n"/>
-      <c r="H1235" s="4" t="n"/>
+      <c r="E1235" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Skarpö Sessel weiß</t>
+        </is>
+      </c>
+      <c r="F1235" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1235" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1235" s="2" t="n"/>
     </row>
     <row r="1236">
-      <c r="A1236" s="4" t="inlineStr">
+      <c r="A1236" s="2" t="inlineStr">
         <is>
           <t>TE02-09</t>
         </is>
       </c>
-      <c r="B1236" s="4" t="inlineStr">
+      <c r="B1236" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1236" s="4" t="inlineStr">
+      <c r="C1236" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1236" s="4" t="inlineStr">
+      <c r="D1236" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1236" s="4" t="n"/>
-      <c r="F1236" s="3" t="n"/>
-      <c r="G1236" s="4" t="n"/>
-      <c r="H1236" s="4" t="n"/>
+      <c r="E1236" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Mammut Kinderstuhl rot</t>
+        </is>
+      </c>
+      <c r="F1236" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1236" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1236" s="2" t="n"/>
     </row>
     <row r="1237">
-      <c r="A1237" s="4" t="inlineStr">
+      <c r="A1237" s="2" t="inlineStr">
         <is>
           <t>TE02-10</t>
         </is>
       </c>
-      <c r="B1237" s="4" t="inlineStr">
+      <c r="B1237" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1237" s="4" t="inlineStr">
+      <c r="C1237" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1237" s="4" t="inlineStr">
+      <c r="D1237" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1237" s="4" t="n"/>
-      <c r="F1237" s="3" t="n"/>
-      <c r="G1237" s="4" t="n"/>
-      <c r="H1237" s="4" t="n"/>
+      <c r="E1237" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Mammut Kinderstuhl grün</t>
+        </is>
+      </c>
+      <c r="F1237" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G1237" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1237" s="2" t="n"/>
     </row>
     <row r="1238">
-      <c r="A1238" s="4" t="inlineStr">
+      <c r="A1238" s="2" t="inlineStr">
         <is>
           <t>TE02-11</t>
         </is>
       </c>
-      <c r="B1238" s="4" t="inlineStr">
+      <c r="B1238" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1238" s="4" t="inlineStr">
+      <c r="C1238" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1238" s="4" t="inlineStr">
+      <c r="D1238" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1238" s="4" t="n"/>
-      <c r="F1238" s="3" t="n"/>
-      <c r="G1238" s="4" t="n"/>
-      <c r="H1238" s="4" t="n"/>
+      <c r="E1238" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Mammut Kindertisch grün, rund</t>
+        </is>
+      </c>
+      <c r="F1238" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1238" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1238" s="2" t="n"/>
     </row>
     <row r="1239">
-      <c r="A1239" s="4" t="inlineStr">
+      <c r="A1239" s="2" t="inlineStr">
         <is>
           <t>TE02-12</t>
         </is>
       </c>
-      <c r="B1239" s="4" t="inlineStr">
+      <c r="B1239" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1239" s="4" t="inlineStr">
+      <c r="C1239" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1239" s="4" t="inlineStr">
+      <c r="D1239" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1239" s="4" t="n"/>
-      <c r="F1239" s="3" t="n"/>
-      <c r="G1239" s="4" t="n"/>
-      <c r="H1239" s="4" t="n"/>
+      <c r="E1239" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Mammut Kindertisch grün, rund, stark verwittert</t>
+        </is>
+      </c>
+      <c r="F1239" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1239" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1239" s="2" t="n"/>
     </row>
     <row r="1240">
-      <c r="A1240" s="4" t="inlineStr">
+      <c r="A1240" s="2" t="inlineStr">
         <is>
           <t>TE02-13</t>
         </is>
       </c>
-      <c r="B1240" s="4" t="inlineStr">
+      <c r="B1240" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1240" s="4" t="inlineStr">
+      <c r="C1240" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1240" s="4" t="inlineStr">
+      <c r="D1240" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1240" s="4" t="n"/>
-      <c r="F1240" s="3" t="n"/>
-      <c r="G1240" s="4" t="n"/>
-      <c r="H1240" s="4" t="n"/>
+      <c r="E1240" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Mammut Kinderstuhl weiß</t>
+        </is>
+      </c>
+      <c r="F1240" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1240" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1240" s="2" t="n"/>
     </row>
     <row r="1241">
-      <c r="A1241" s="4" t="inlineStr">
+      <c r="A1241" s="2" t="inlineStr">
         <is>
           <t>TE02-14</t>
         </is>
       </c>
-      <c r="B1241" s="4" t="inlineStr">
+      <c r="B1241" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1241" s="4" t="inlineStr">
+      <c r="C1241" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1241" s="4" t="inlineStr">
+      <c r="D1241" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1241" s="4" t="n"/>
-      <c r="F1241" s="3" t="n"/>
-      <c r="G1241" s="4" t="n"/>
-      <c r="H1241" s="4" t="n"/>
+      <c r="E1241" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Mammut Kinderstuhl rosa</t>
+        </is>
+      </c>
+      <c r="F1241" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1241" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1241" s="2" t="n"/>
     </row>
     <row r="1242">
-      <c r="A1242" s="4" t="inlineStr">
+      <c r="A1242" s="2" t="inlineStr">
         <is>
           <t>TE02-15</t>
         </is>
       </c>
-      <c r="B1242" s="4" t="inlineStr">
+      <c r="B1242" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1242" s="4" t="inlineStr">
+      <c r="C1242" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1242" s="4" t="inlineStr">
+      <c r="D1242" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1242" s="4" t="n"/>
-      <c r="F1242" s="3" t="n"/>
-      <c r="G1242" s="4" t="n"/>
-      <c r="H1242" s="4" t="n"/>
+      <c r="E1242" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Mammut Kindertisch rot</t>
+        </is>
+      </c>
+      <c r="F1242" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1242" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1242" s="2" t="n"/>
     </row>
     <row r="1243">
-      <c r="A1243" s="4" t="inlineStr">
+      <c r="A1243" s="2" t="inlineStr">
         <is>
           <t>TE02-16</t>
         </is>
       </c>
-      <c r="B1243" s="4" t="inlineStr">
+      <c r="B1243" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1243" s="4" t="inlineStr">
+      <c r="C1243" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1243" s="4" t="inlineStr">
+      <c r="D1243" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1243" s="4" t="n"/>
-      <c r="F1243" s="3" t="n"/>
-      <c r="G1243" s="4" t="n"/>
-      <c r="H1243" s="4" t="n"/>
+      <c r="E1243" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Mammut Stuhl rot</t>
+        </is>
+      </c>
+      <c r="F1243" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1243" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1243" s="2" t="n"/>
     </row>
     <row r="1244">
-      <c r="A1244" s="4" t="inlineStr">
+      <c r="A1244" s="2" t="inlineStr">
         <is>
           <t>TE02-17</t>
         </is>
       </c>
-      <c r="B1244" s="4" t="inlineStr">
+      <c r="B1244" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1244" s="4" t="inlineStr">
+      <c r="C1244" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1244" s="4" t="inlineStr">
+      <c r="D1244" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1244" s="4" t="n"/>
-      <c r="F1244" s="3" t="n"/>
-      <c r="G1244" s="4" t="n"/>
-      <c r="H1244" s="4" t="n"/>
+      <c r="E1244" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Mammut Kindertisch weiß</t>
+        </is>
+      </c>
+      <c r="F1244" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1244" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1244" s="2" t="n"/>
     </row>
     <row r="1245">
-      <c r="A1245" s="4" t="inlineStr">
+      <c r="A1245" s="2" t="inlineStr">
         <is>
           <t>TE02-18</t>
         </is>
       </c>
-      <c r="B1245" s="4" t="inlineStr">
+      <c r="B1245" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1245" s="4" t="inlineStr">
+      <c r="C1245" s="2" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1245" s="4" t="inlineStr">
+      <c r="D1245" s="2" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1245" s="4" t="n"/>
-      <c r="F1245" s="3" t="n"/>
-      <c r="G1245" s="4" t="n"/>
-      <c r="H1245" s="4" t="n"/>
+      <c r="E1245" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Mammut Stuhl weiß</t>
+        </is>
+      </c>
+      <c r="F1245" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1245" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1245" s="2" t="n"/>
     </row>
     <row r="1246">
       <c r="A1246" s="4" t="inlineStr">

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -34683,7 +34683,7 @@
         </is>
       </c>
       <c r="F1188" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1188" s="2" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         </is>
       </c>
       <c r="F1236" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G1236" s="2" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         </is>
       </c>
       <c r="F1240" s="3" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G1240" s="2" t="inlineStr">
         <is>
@@ -36309,11 +36309,11 @@
       </c>
       <c r="E1243" s="2" t="inlineStr">
         <is>
-          <t>IKEA Mammut Stuhl rot</t>
+          <t>IKEA Mammut Kindertisch weiß</t>
         </is>
       </c>
       <c r="F1243" s="3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G1243" s="2" t="inlineStr">
         <is>
@@ -36323,76 +36323,56 @@
       <c r="H1243" s="2" t="n"/>
     </row>
     <row r="1244">
-      <c r="A1244" s="2" t="inlineStr">
+      <c r="A1244" s="4" t="inlineStr">
         <is>
           <t>TE02-17</t>
         </is>
       </c>
-      <c r="B1244" s="2" t="inlineStr">
+      <c r="B1244" s="4" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1244" s="2" t="inlineStr">
+      <c r="C1244" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1244" s="2" t="inlineStr">
+      <c r="D1244" s="4" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1244" s="2" t="inlineStr">
-        <is>
-          <t>IKEA Mammut Kindertisch weiß</t>
-        </is>
-      </c>
-      <c r="F1244" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G1244" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1244" s="2" t="n"/>
+      <c r="E1244" s="4" t="n"/>
+      <c r="F1244" s="3" t="n"/>
+      <c r="G1244" s="4" t="n"/>
+      <c r="H1244" s="4" t="n"/>
     </row>
     <row r="1245">
-      <c r="A1245" s="2" t="inlineStr">
+      <c r="A1245" s="4" t="inlineStr">
         <is>
           <t>TE02-18</t>
         </is>
       </c>
-      <c r="B1245" s="2" t="inlineStr">
+      <c r="B1245" s="4" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1245" s="2" t="inlineStr">
+      <c r="C1245" s="4" t="inlineStr">
         <is>
           <t>Attika</t>
         </is>
       </c>
-      <c r="D1245" s="2" t="inlineStr">
+      <c r="D1245" s="4" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="E1245" s="2" t="inlineStr">
-        <is>
-          <t>IKEA Mammut Stuhl weiß</t>
-        </is>
-      </c>
-      <c r="F1245" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="G1245" s="2" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="H1245" s="2" t="n"/>
+      <c r="E1245" s="4" t="n"/>
+      <c r="F1245" s="3" t="n"/>
+      <c r="G1245" s="4" t="n"/>
+      <c r="H1245" s="4" t="n"/>
     </row>
     <row r="1246">
       <c r="A1246" s="4" t="inlineStr">

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -36979,334 +36979,484 @@
       <c r="H1268" s="2" t="n"/>
     </row>
     <row r="1269">
-      <c r="A1269" s="4" t="inlineStr">
+      <c r="A1269" s="2" t="inlineStr">
         <is>
           <t>GA01-02</t>
         </is>
       </c>
-      <c r="B1269" s="4" t="inlineStr">
+      <c r="B1269" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1269" s="4" t="inlineStr"/>
-      <c r="D1269" s="4" t="inlineStr">
+      <c r="C1269" s="2" t="inlineStr"/>
+      <c r="D1269" s="2" t="inlineStr">
         <is>
           <t>Gartenanlage</t>
         </is>
       </c>
-      <c r="E1269" s="4" t="n"/>
-      <c r="F1269" s="3" t="n"/>
-      <c r="G1269" s="4" t="n"/>
-      <c r="H1269" s="4" t="n"/>
+      <c r="E1269" s="2" t="inlineStr">
+        <is>
+          <t>Smoby Kinderrutsche</t>
+        </is>
+      </c>
+      <c r="F1269" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1269" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1269" s="2" t="n"/>
     </row>
     <row r="1270">
-      <c r="A1270" s="4" t="inlineStr">
+      <c r="A1270" s="2" t="inlineStr">
         <is>
           <t>GA01-03</t>
         </is>
       </c>
-      <c r="B1270" s="4" t="inlineStr">
+      <c r="B1270" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1270" s="4" t="inlineStr"/>
-      <c r="D1270" s="4" t="inlineStr">
+      <c r="C1270" s="2" t="inlineStr"/>
+      <c r="D1270" s="2" t="inlineStr">
         <is>
           <t>Gartenanlage</t>
         </is>
       </c>
-      <c r="E1270" s="4" t="n"/>
-      <c r="F1270" s="3" t="n"/>
-      <c r="G1270" s="4" t="n"/>
-      <c r="H1270" s="4" t="n"/>
+      <c r="E1270" s="2" t="inlineStr">
+        <is>
+          <t>Schaukelanlage Holz mit Leiter und Hängehöhle</t>
+        </is>
+      </c>
+      <c r="F1270" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1270" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1270" s="2" t="n"/>
     </row>
     <row r="1271">
-      <c r="A1271" s="4" t="inlineStr">
+      <c r="A1271" s="2" t="inlineStr">
         <is>
           <t>GA01-04</t>
         </is>
       </c>
-      <c r="B1271" s="4" t="inlineStr">
+      <c r="B1271" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1271" s="4" t="inlineStr"/>
-      <c r="D1271" s="4" t="inlineStr">
+      <c r="C1271" s="2" t="inlineStr"/>
+      <c r="D1271" s="2" t="inlineStr">
         <is>
           <t>Gartenanlage</t>
         </is>
       </c>
-      <c r="E1271" s="4" t="n"/>
-      <c r="F1271" s="3" t="n"/>
-      <c r="G1271" s="4" t="n"/>
-      <c r="H1271" s="4" t="n"/>
+      <c r="E1271" s="2" t="inlineStr">
+        <is>
+          <t>Schaukelanlage Holz mit Rutsche und Strickleiter</t>
+        </is>
+      </c>
+      <c r="F1271" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1271" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1271" s="2" t="n"/>
     </row>
     <row r="1272">
-      <c r="A1272" s="4" t="inlineStr">
+      <c r="A1272" s="2" t="inlineStr">
         <is>
           <t>GA01-05</t>
         </is>
       </c>
-      <c r="B1272" s="4" t="inlineStr">
+      <c r="B1272" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1272" s="4" t="inlineStr"/>
-      <c r="D1272" s="4" t="inlineStr">
+      <c r="C1272" s="2" t="inlineStr"/>
+      <c r="D1272" s="2" t="inlineStr">
         <is>
           <t>Gartenanlage</t>
         </is>
       </c>
-      <c r="E1272" s="4" t="n"/>
-      <c r="F1272" s="3" t="n"/>
-      <c r="G1272" s="4" t="n"/>
-      <c r="H1272" s="4" t="n"/>
+      <c r="E1272" s="2" t="inlineStr">
+        <is>
+          <t>Smoby Kindertisch mit zwei Stühlen</t>
+        </is>
+      </c>
+      <c r="F1272" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1272" s="2" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="H1272" s="2" t="n"/>
     </row>
     <row r="1273">
-      <c r="A1273" s="4" t="inlineStr">
+      <c r="A1273" s="2" t="inlineStr">
         <is>
           <t>GA01-06</t>
         </is>
       </c>
-      <c r="B1273" s="4" t="inlineStr">
+      <c r="B1273" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1273" s="4" t="inlineStr"/>
-      <c r="D1273" s="4" t="inlineStr">
+      <c r="C1273" s="2" t="inlineStr"/>
+      <c r="D1273" s="2" t="inlineStr">
         <is>
           <t>Gartenanlage</t>
         </is>
       </c>
-      <c r="E1273" s="4" t="n"/>
-      <c r="F1273" s="3" t="n"/>
-      <c r="G1273" s="4" t="n"/>
-      <c r="H1273" s="4" t="n"/>
+      <c r="E1273" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Mammut Kinderstuhl weiß</t>
+        </is>
+      </c>
+      <c r="F1273" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1273" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1273" s="2" t="n"/>
     </row>
     <row r="1274">
-      <c r="A1274" s="4" t="inlineStr">
+      <c r="A1274" s="2" t="inlineStr">
         <is>
           <t>GA01-07</t>
         </is>
       </c>
-      <c r="B1274" s="4" t="inlineStr">
+      <c r="B1274" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1274" s="4" t="inlineStr"/>
-      <c r="D1274" s="4" t="inlineStr">
+      <c r="C1274" s="2" t="inlineStr"/>
+      <c r="D1274" s="2" t="inlineStr">
         <is>
           <t>Gartenanlage</t>
         </is>
       </c>
-      <c r="E1274" s="4" t="n"/>
-      <c r="F1274" s="3" t="n"/>
-      <c r="G1274" s="4" t="n"/>
-      <c r="H1274" s="4" t="n"/>
+      <c r="E1274" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Mammut Kinderstuhl blau</t>
+        </is>
+      </c>
+      <c r="F1274" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1274" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1274" s="2" t="n"/>
     </row>
     <row r="1275">
-      <c r="A1275" s="4" t="inlineStr">
+      <c r="A1275" s="2" t="inlineStr">
         <is>
           <t>GA01-08</t>
         </is>
       </c>
-      <c r="B1275" s="4" t="inlineStr">
+      <c r="B1275" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1275" s="4" t="inlineStr"/>
-      <c r="D1275" s="4" t="inlineStr">
+      <c r="C1275" s="2" t="inlineStr"/>
+      <c r="D1275" s="2" t="inlineStr">
         <is>
           <t>Gartenanlage</t>
         </is>
       </c>
-      <c r="E1275" s="4" t="n"/>
-      <c r="F1275" s="3" t="n"/>
-      <c r="G1275" s="4" t="n"/>
-      <c r="H1275" s="4" t="n"/>
+      <c r="E1275" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Mammut Kinderstuhl rosa</t>
+        </is>
+      </c>
+      <c r="F1275" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1275" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1275" s="2" t="n"/>
     </row>
     <row r="1276">
-      <c r="A1276" s="4" t="inlineStr">
+      <c r="A1276" s="2" t="inlineStr">
         <is>
           <t>GA01-09</t>
         </is>
       </c>
-      <c r="B1276" s="4" t="inlineStr">
+      <c r="B1276" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1276" s="4" t="inlineStr"/>
-      <c r="D1276" s="4" t="inlineStr">
+      <c r="C1276" s="2" t="inlineStr"/>
+      <c r="D1276" s="2" t="inlineStr">
         <is>
           <t>Gartenanlage</t>
         </is>
       </c>
-      <c r="E1276" s="4" t="n"/>
-      <c r="F1276" s="3" t="n"/>
-      <c r="G1276" s="4" t="n"/>
-      <c r="H1276" s="4" t="n"/>
+      <c r="E1276" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Mammut Kindertisch weiß</t>
+        </is>
+      </c>
+      <c r="F1276" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1276" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1276" s="2" t="n"/>
     </row>
     <row r="1277">
-      <c r="A1277" s="4" t="inlineStr">
+      <c r="A1277" s="2" t="inlineStr">
         <is>
           <t>GA01-10</t>
         </is>
       </c>
-      <c r="B1277" s="4" t="inlineStr">
+      <c r="B1277" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1277" s="4" t="inlineStr"/>
-      <c r="D1277" s="4" t="inlineStr">
+      <c r="C1277" s="2" t="inlineStr"/>
+      <c r="D1277" s="2" t="inlineStr">
         <is>
           <t>Gartenanlage</t>
         </is>
       </c>
-      <c r="E1277" s="4" t="n"/>
-      <c r="F1277" s="3" t="n"/>
-      <c r="G1277" s="4" t="n"/>
-      <c r="H1277" s="4" t="n"/>
+      <c r="E1277" s="2" t="inlineStr">
+        <is>
+          <t>IKEA Mammut Kindertisch rot</t>
+        </is>
+      </c>
+      <c r="F1277" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1277" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1277" s="2" t="n"/>
     </row>
     <row r="1278">
-      <c r="A1278" s="4" t="inlineStr">
+      <c r="A1278" s="2" t="inlineStr">
         <is>
           <t>GA01-11</t>
         </is>
       </c>
-      <c r="B1278" s="4" t="inlineStr">
+      <c r="B1278" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1278" s="4" t="inlineStr"/>
-      <c r="D1278" s="4" t="inlineStr">
+      <c r="C1278" s="2" t="inlineStr"/>
+      <c r="D1278" s="2" t="inlineStr">
         <is>
           <t>Gartenanlage</t>
         </is>
       </c>
-      <c r="E1278" s="4" t="n"/>
-      <c r="F1278" s="3" t="n"/>
-      <c r="G1278" s="4" t="n"/>
-      <c r="H1278" s="4" t="n"/>
+      <c r="E1278" s="2" t="inlineStr">
+        <is>
+          <t>Fenwick Trettraktor Gabelstapler</t>
+        </is>
+      </c>
+      <c r="F1278" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1278" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1278" s="2" t="n"/>
     </row>
     <row r="1279">
-      <c r="A1279" s="4" t="inlineStr">
+      <c r="A1279" s="2" t="inlineStr">
         <is>
           <t>GA01-12</t>
         </is>
       </c>
-      <c r="B1279" s="4" t="inlineStr">
+      <c r="B1279" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1279" s="4" t="inlineStr"/>
-      <c r="D1279" s="4" t="inlineStr">
+      <c r="C1279" s="2" t="inlineStr"/>
+      <c r="D1279" s="2" t="inlineStr">
         <is>
           <t>Gartenanlage</t>
         </is>
       </c>
-      <c r="E1279" s="4" t="n"/>
-      <c r="F1279" s="3" t="n"/>
-      <c r="G1279" s="4" t="n"/>
-      <c r="H1279" s="4" t="n"/>
+      <c r="E1279" s="2" t="inlineStr">
+        <is>
+          <t>Claas Axos 340 Trettraktor</t>
+        </is>
+      </c>
+      <c r="F1279" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1279" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1279" s="2" t="n"/>
     </row>
     <row r="1280">
-      <c r="A1280" s="4" t="inlineStr">
+      <c r="A1280" s="2" t="inlineStr">
         <is>
           <t>GA01-13</t>
         </is>
       </c>
-      <c r="B1280" s="4" t="inlineStr">
+      <c r="B1280" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1280" s="4" t="inlineStr"/>
-      <c r="D1280" s="4" t="inlineStr">
+      <c r="C1280" s="2" t="inlineStr"/>
+      <c r="D1280" s="2" t="inlineStr">
         <is>
           <t>Gartenanlage</t>
         </is>
       </c>
-      <c r="E1280" s="4" t="n"/>
-      <c r="F1280" s="3" t="n"/>
-      <c r="G1280" s="4" t="n"/>
-      <c r="H1280" s="4" t="n"/>
+      <c r="E1280" s="2" t="inlineStr">
+        <is>
+          <t>Kinder-Liege Kunststoff orange</t>
+        </is>
+      </c>
+      <c r="F1280" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1280" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1280" s="2" t="n"/>
     </row>
     <row r="1281">
-      <c r="A1281" s="4" t="inlineStr">
+      <c r="A1281" s="2" t="inlineStr">
         <is>
           <t>GA01-14</t>
         </is>
       </c>
-      <c r="B1281" s="4" t="inlineStr">
+      <c r="B1281" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1281" s="4" t="inlineStr"/>
-      <c r="D1281" s="4" t="inlineStr">
+      <c r="C1281" s="2" t="inlineStr"/>
+      <c r="D1281" s="2" t="inlineStr">
         <is>
           <t>Gartenanlage</t>
         </is>
       </c>
-      <c r="E1281" s="4" t="n"/>
-      <c r="F1281" s="3" t="n"/>
-      <c r="G1281" s="4" t="n"/>
-      <c r="H1281" s="4" t="n"/>
+      <c r="E1281" s="2" t="inlineStr">
+        <is>
+          <t>Wehrfritz Spielanlage Burg mit zwei Rutschen</t>
+        </is>
+      </c>
+      <c r="F1281" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1281" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1281" s="2" t="n"/>
     </row>
     <row r="1282">
-      <c r="A1282" s="4" t="inlineStr">
+      <c r="A1282" s="2" t="inlineStr">
         <is>
           <t>GA01-15</t>
         </is>
       </c>
-      <c r="B1282" s="4" t="inlineStr">
+      <c r="B1282" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1282" s="4" t="inlineStr"/>
-      <c r="D1282" s="4" t="inlineStr">
+      <c r="C1282" s="2" t="inlineStr"/>
+      <c r="D1282" s="2" t="inlineStr">
         <is>
           <t>Gartenanlage</t>
         </is>
       </c>
-      <c r="E1282" s="4" t="n"/>
-      <c r="F1282" s="3" t="n"/>
-      <c r="G1282" s="4" t="n"/>
-      <c r="H1282" s="4" t="n"/>
+      <c r="E1282" s="2" t="inlineStr">
+        <is>
+          <t>Sitzgruppe Holz, sechseckig</t>
+        </is>
+      </c>
+      <c r="F1282" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1282" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1282" s="2" t="n"/>
     </row>
     <row r="1283">
-      <c r="A1283" s="4" t="inlineStr">
+      <c r="A1283" s="2" t="inlineStr">
         <is>
           <t>GA01-16</t>
         </is>
       </c>
-      <c r="B1283" s="4" t="inlineStr">
+      <c r="B1283" s="2" t="inlineStr">
         <is>
           <t>Außen</t>
         </is>
       </c>
-      <c r="C1283" s="4" t="inlineStr"/>
-      <c r="D1283" s="4" t="inlineStr">
+      <c r="C1283" s="2" t="inlineStr"/>
+      <c r="D1283" s="2" t="inlineStr">
         <is>
           <t>Gartenanlage</t>
         </is>
       </c>
-      <c r="E1283" s="4" t="n"/>
-      <c r="F1283" s="3" t="n"/>
-      <c r="G1283" s="4" t="n"/>
-      <c r="H1283" s="4" t="n"/>
+      <c r="E1283" s="2" t="inlineStr">
+        <is>
+          <t>Pinolino Kindersitzgarnitur mit Tisch</t>
+        </is>
+      </c>
+      <c r="F1283" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1283" s="2" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="H1283" s="2" t="n"/>
     </row>
     <row r="1284">
       <c r="A1284" s="4" t="inlineStr">

--- a/ausgabe/T3_Erfassungsliste.xlsx
+++ b/ausgabe/T3_Erfassungsliste.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E24" s="4" t="n"/>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E25" s="4" t="n"/>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E26" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E27" s="4" t="n"/>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E28" s="4" t="n"/>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E29" s="4" t="n"/>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E30" s="4" t="n"/>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E31" s="4" t="n"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E32" s="4" t="n"/>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Flur</t>
+          <t>Eingang und Elternlounge</t>
         </is>
       </c>
       <c r="E33" s="4" t="n"/>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E57" s="4" t="n"/>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E58" s="4" t="n"/>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E59" s="4" t="n"/>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E60" s="4" t="n"/>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E61" s="4" t="n"/>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E62" s="4" t="n"/>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E63" s="4" t="n"/>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E64" s="4" t="n"/>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E65" s="4" t="n"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E66" s="4" t="n"/>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E67" s="4" t="n"/>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E68" s="4" t="n"/>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E69" s="4" t="n"/>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E70" s="4" t="n"/>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E71" s="4" t="n"/>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E72" s="4" t="n"/>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E73" s="4" t="n"/>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E84" s="4" t="n"/>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E85" s="4" t="n"/>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E86" s="4" t="n"/>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E87" s="4" t="n"/>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E88" s="4" t="n"/>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E89" s="4" t="n"/>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E90" s="4" t="n"/>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E91" s="4" t="n"/>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E92" s="4" t="n"/>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E93" s="4" t="n"/>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E94" s="4" t="n"/>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E95" s="4" t="n"/>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E96" s="4" t="n"/>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E97" s="4" t="n"/>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E98" s="4" t="n"/>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E120" s="4" t="n"/>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E121" s="4" t="n"/>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E122" s="4" t="n"/>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E123" s="4" t="n"/>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E124" s="4" t="n"/>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E125" s="4" t="n"/>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E126" s="4" t="n"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E127" s="4" t="n"/>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E128" s="4" t="n"/>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="E129" s="4" t="n"/>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Treppenaufgang</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Treppenaufgang</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Treppenaufgang</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Treppenaufgang</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Treppenaufgang</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Treppenaufgang</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Treppenaufgang</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Treppenaufgang</t>
         </is>
       </c>
       <c r="E137" s="4" t="n"/>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Treppenaufgang</t>
         </is>
       </c>
       <c r="E138" s="4" t="n"/>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Treppenaufgang</t>
         </is>
       </c>
       <c r="E139" s="4" t="n"/>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Treppenaufgang</t>
         </is>
       </c>
       <c r="E140" s="4" t="n"/>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Treppenaufgang</t>
         </is>
       </c>
       <c r="E141" s="4" t="n"/>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Treppenaufgang</t>
         </is>
       </c>
       <c r="E142" s="4" t="n"/>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Treppenaufgang</t>
         </is>
       </c>
       <c r="E143" s="4" t="n"/>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Treppenaufgang</t>
         </is>
       </c>
       <c r="E144" s="4" t="n"/>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Treppenaufgang</t>
         </is>
       </c>
       <c r="E145" s="4" t="n"/>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Treppenaufgang</t>
         </is>
       </c>
       <c r="E146" s="4" t="n"/>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Matschraum</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Matschraum</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Matschraum</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Matschraum</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Matschraum</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Matschraum</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Matschraum</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Matschraum</t>
         </is>
       </c>
       <c r="E154" s="4" t="n"/>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Matschraum</t>
         </is>
       </c>
       <c r="E155" s="4" t="n"/>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Matschraum</t>
         </is>
       </c>
       <c r="E156" s="4" t="n"/>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Matschraum</t>
         </is>
       </c>
       <c r="E157" s="4" t="n"/>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Matschraum</t>
         </is>
       </c>
       <c r="E158" s="4" t="n"/>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Matschraum</t>
         </is>
       </c>
       <c r="E159" s="4" t="n"/>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Matschraum</t>
         </is>
       </c>
       <c r="E160" s="4" t="n"/>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Matschraum</t>
         </is>
       </c>
       <c r="E161" s="4" t="n"/>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Matschraum</t>
         </is>
       </c>
       <c r="E162" s="4" t="n"/>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Matschraum</t>
         </is>
       </c>
       <c r="E163" s="4" t="n"/>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E171" s="4" t="n"/>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E172" s="4" t="n"/>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E173" s="4" t="n"/>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E174" s="4" t="n"/>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E175" s="4" t="n"/>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E176" s="4" t="n"/>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E177" s="4" t="n"/>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E178" s="4" t="n"/>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E179" s="4" t="n"/>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E180" s="4" t="n"/>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E181" s="4" t="n"/>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E182" s="4" t="n"/>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E183" s="4" t="n"/>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E184" s="4" t="n"/>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E185" s="4" t="n"/>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E186" s="4" t="n"/>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E187" s="4" t="n"/>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E188" s="4" t="n"/>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -8342,7 +8342,7 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -8450,7 +8450,7 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="D258" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E258" s="4" t="n"/>
@@ -8620,7 +8620,7 @@
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E259" s="4" t="n"/>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E260" s="4" t="n"/>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E261" s="4" t="n"/>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E262" s="4" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="D263" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E263" s="4" t="n"/>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="D264" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E264" s="4" t="n"/>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E265" s="4" t="n"/>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E266" s="4" t="n"/>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E267" s="4" t="n"/>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E268" s="4" t="n"/>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E269" s="4" t="n"/>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E270" s="4" t="n"/>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E271" s="4" t="n"/>
@@ -8958,7 +8958,7 @@
       </c>
       <c r="D272" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E272" s="4" t="n"/>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 2</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E273" s="4" t="n"/>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E286" s="4" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E287" s="4" t="n"/>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E288" s="4" t="n"/>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E289" s="4" t="n"/>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E290" s="4" t="n"/>
@@ -9572,7 +9572,7 @@
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E291" s="4" t="n"/>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E292" s="4" t="n"/>
@@ -9624,7 +9624,7 @@
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E293" s="4" t="n"/>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E294" s="4" t="n"/>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E295" s="4" t="n"/>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E296" s="4" t="n"/>
@@ -9728,7 +9728,7 @@
       </c>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E297" s="4" t="n"/>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>Schlafraum 3</t>
+          <t>Krippenschlafraum</t>
         </is>
       </c>
       <c r="E298" s="4" t="n"/>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
@@ -12024,7 +12024,7 @@
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
@@ -12096,7 +12096,7 @@
       </c>
       <c r="D380" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E380" s="4" t="n"/>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="D381" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E381" s="4" t="n"/>
@@ -12148,7 +12148,7 @@
       </c>
       <c r="D382" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E382" s="4" t="n"/>
@@ -12174,7 +12174,7 @@
       </c>
       <c r="D383" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E383" s="4" t="n"/>
@@ -12200,7 +12200,7 @@
       </c>
       <c r="D384" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E384" s="4" t="n"/>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="D385" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E385" s="4" t="n"/>
@@ -12252,7 +12252,7 @@
       </c>
       <c r="D386" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E386" s="4" t="n"/>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="D387" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E387" s="4" t="n"/>
@@ -12304,7 +12304,7 @@
       </c>
       <c r="D388" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E388" s="4" t="n"/>
@@ -12330,7 +12330,7 @@
       </c>
       <c r="D389" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E389" s="4" t="n"/>
@@ -12356,7 +12356,7 @@
       </c>
       <c r="D390" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E390" s="4" t="n"/>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="D391" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E391" s="4" t="n"/>
@@ -12408,7 +12408,7 @@
       </c>
       <c r="D392" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E392" s="4" t="n"/>
@@ -12434,7 +12434,7 @@
       </c>
       <c r="D393" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E393" s="4" t="n"/>
@@ -12460,7 +12460,7 @@
       </c>
       <c r="D394" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E394" s="4" t="n"/>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="D395" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E395" s="4" t="n"/>
@@ -12512,7 +12512,7 @@
       </c>
       <c r="D396" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E396" s="4" t="n"/>
@@ -12538,7 +12538,7 @@
       </c>
       <c r="D397" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E397" s="4" t="n"/>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="D398" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E398" s="4" t="n"/>
@@ -12590,7 +12590,7 @@
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
@@ -12662,7 +12662,7 @@
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
@@ -12842,7 +12842,7 @@
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
@@ -12950,7 +12950,7 @@
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
@@ -12986,7 +12986,7 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
@@ -13022,7 +13022,7 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="D412" s="4" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E412" s="4" t="n"/>
@@ -13084,7 +13084,7 @@
       </c>
       <c r="D413" s="4" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E413" s="4" t="n"/>
@@ -13110,7 +13110,7 @@
       </c>
       <c r="D414" s="4" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E414" s="4" t="n"/>
@@ -13136,7 +13136,7 @@
       </c>
       <c r="D415" s="4" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E415" s="4" t="n"/>
@@ -13162,7 +13162,7 @@
       </c>
       <c r="D416" s="4" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E416" s="4" t="n"/>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="D417" s="4" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E417" s="4" t="n"/>
@@ -13214,7 +13214,7 @@
       </c>
       <c r="D418" s="4" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E418" s="4" t="n"/>
@@ -13240,7 +13240,7 @@
       </c>
       <c r="D419" s="4" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E419" s="4" t="n"/>
@@ -13266,7 +13266,7 @@
       </c>
       <c r="D420" s="4" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E420" s="4" t="n"/>
@@ -13292,7 +13292,7 @@
       </c>
       <c r="D421" s="4" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E421" s="4" t="n"/>
@@ -13318,7 +13318,7 @@
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>Flur 3</t>
+          <t>Garderobenflur</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>Flur 3</t>
+          <t>Garderobenflur</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>Flur 3</t>
+          <t>Garderobenflur</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
@@ -13426,7 +13426,7 @@
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>Flur 3</t>
+          <t>Garderobenflur</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
@@ -13462,7 +13462,7 @@
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>Flur 3</t>
+          <t>Garderobenflur</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>Flur 3</t>
+          <t>Garderobenflur</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
@@ -13534,7 +13534,7 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>Flur 3</t>
+          <t>Garderobenflur</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>Flur 3</t>
+          <t>Garderobenflur</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
@@ -13606,7 +13606,7 @@
       </c>
       <c r="D430" s="4" t="inlineStr">
         <is>
-          <t>Flur 3</t>
+          <t>Garderobenflur</t>
         </is>
       </c>
       <c r="E430" s="4" t="n"/>
@@ -13632,7 +13632,7 @@
       </c>
       <c r="D431" s="4" t="inlineStr">
         <is>
-          <t>Flur 3</t>
+          <t>Garderobenflur</t>
         </is>
       </c>
       <c r="E431" s="4" t="n"/>
@@ -13658,7 +13658,7 @@
       </c>
       <c r="D432" s="4" t="inlineStr">
         <is>
-          <t>Flur 3</t>
+          <t>Garderobenflur</t>
         </is>
       </c>
       <c r="E432" s="4" t="n"/>
@@ -13684,7 +13684,7 @@
       </c>
       <c r="D433" s="4" t="inlineStr">
         <is>
-          <t>Flur 3</t>
+          <t>Garderobenflur</t>
         </is>
       </c>
       <c r="E433" s="4" t="n"/>
@@ -13710,7 +13710,7 @@
       </c>
       <c r="D434" s="4" t="inlineStr">
         <is>
-          <t>Flur 3</t>
+          <t>Garderobenflur</t>
         </is>
       </c>
       <c r="E434" s="4" t="n"/>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="D435" s="4" t="inlineStr">
         <is>
-          <t>Flur 3</t>
+          <t>Garderobenflur</t>
         </is>
       </c>
       <c r="E435" s="4" t="n"/>
@@ -13762,7 +13762,7 @@
       </c>
       <c r="D436" s="4" t="inlineStr">
         <is>
-          <t>Flur 3</t>
+          <t>Garderobenflur</t>
         </is>
       </c>
       <c r="E436" s="4" t="n"/>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="D437" s="4" t="inlineStr">
         <is>
-          <t>Flur 3</t>
+          <t>Garderobenflur</t>
         </is>
       </c>
       <c r="E437" s="4" t="n"/>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="D438" s="4" t="inlineStr">
         <is>
-          <t>Flur 3</t>
+          <t>Garderobenflur</t>
         </is>
       </c>
       <c r="E438" s="4" t="n"/>
@@ -13840,7 +13840,7 @@
       </c>
       <c r="D439" s="4" t="inlineStr">
         <is>
-          <t>Flur 3</t>
+          <t>Garderobenflur</t>
         </is>
       </c>
       <c r="E439" s="4" t="n"/>
@@ -15386,7 +15386,7 @@
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>Küche / Essen</t>
+          <t>Küche und Essbereich</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>Küche / Essen</t>
+          <t>Küche und Essbereich</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>Küche / Essen</t>
+          <t>Küche und Essbereich</t>
         </is>
       </c>
       <c r="E492" s="2" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>Küche / Essen</t>
+          <t>Küche und Essbereich</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">
@@ -15530,7 +15530,7 @@
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>Küche / Essen</t>
+          <t>Küche und Essbereich</t>
         </is>
       </c>
       <c r="E494" s="2" t="inlineStr">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>Küche / Essen</t>
+          <t>Küche und Essbereich</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr">
@@ -15602,7 +15602,7 @@
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>Küche / Essen</t>
+          <t>Küche und Essbereich</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr">
@@ -15638,7 +15638,7 @@
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>Küche / Essen</t>
+          <t>Küche und Essbereich</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
@@ -15674,7 +15674,7 @@
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>Küche / Essen</t>
+          <t>Küche und Essbereich</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
@@ -15710,7 +15710,7 @@
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>Küche / Essen</t>
+          <t>Küche und Essbereich</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="D500" s="4" t="inlineStr">
         <is>
-          <t>Küche / Essen</t>
+          <t>Küche und Essbereich</t>
         </is>
       </c>
       <c r="E500" s="4" t="n"/>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="D501" s="4" t="inlineStr">
         <is>
-          <t>Küche / Essen</t>
+          <t>Küche und Essbereich</t>
         </is>
       </c>
       <c r="E501" s="4" t="n"/>
@@ -15798,7 +15798,7 @@
       </c>
       <c r="D502" s="4" t="inlineStr">
         <is>
-          <t>Küche / Essen</t>
+          <t>Küche und Essbereich</t>
         </is>
       </c>
       <c r="E502" s="4" t="n"/>
@@ -15824,7 +15824,7 @@
       </c>
       <c r="D503" s="4" t="inlineStr">
         <is>
-          <t>Küche / Essen</t>
+          <t>Küche und Essbereich</t>
         </is>
       </c>
       <c r="E503" s="4" t="n"/>
@@ -15850,7 +15850,7 @@
       </c>
       <c r="D504" s="4" t="inlineStr">
         <is>
-          <t>Küche / Essen</t>
+          <t>Küche und Essbereich</t>
         </is>
       </c>
       <c r="E504" s="4" t="n"/>
@@ -15876,7 +15876,7 @@
       </c>
       <c r="D505" s="4" t="inlineStr">
         <is>
-          <t>Küche / Essen</t>
+          <t>Küche und Essbereich</t>
         </is>
       </c>
       <c r="E505" s="4" t="n"/>
@@ -15902,7 +15902,7 @@
       </c>
       <c r="D506" s="4" t="inlineStr">
         <is>
-          <t>Küche / Essen</t>
+          <t>Küche und Essbereich</t>
         </is>
       </c>
       <c r="E506" s="4" t="n"/>
@@ -15928,7 +15928,7 @@
       </c>
       <c r="D507" s="4" t="inlineStr">
         <is>
-          <t>Küche / Essen</t>
+          <t>Küche und Essbereich</t>
         </is>
       </c>
       <c r="E507" s="4" t="n"/>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="D508" s="4" t="inlineStr">
         <is>
-          <t>Küche / Essen</t>
+          <t>Küche und Essbereich</t>
         </is>
       </c>
       <c r="E508" s="4" t="n"/>
@@ -15980,7 +15980,7 @@
       </c>
       <c r="D509" s="4" t="inlineStr">
         <is>
-          <t>Küche / Essen</t>
+          <t>Küche und Essbereich</t>
         </is>
       </c>
       <c r="E509" s="4" t="n"/>
@@ -19286,7 +19286,7 @@
       </c>
       <c r="D635" s="2" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E635" s="2" t="inlineStr">
@@ -19322,7 +19322,7 @@
       </c>
       <c r="D636" s="2" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E636" s="2" t="inlineStr">
@@ -19358,7 +19358,7 @@
       </c>
       <c r="D637" s="2" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E637" s="2" t="inlineStr">
@@ -19394,7 +19394,7 @@
       </c>
       <c r="D638" s="2" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E638" s="2" t="inlineStr">
@@ -19430,7 +19430,7 @@
       </c>
       <c r="D639" s="2" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E639" s="2" t="inlineStr">
@@ -19466,7 +19466,7 @@
       </c>
       <c r="D640" s="2" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E640" s="2" t="inlineStr">
@@ -19502,7 +19502,7 @@
       </c>
       <c r="D641" s="2" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E641" s="2" t="inlineStr">
@@ -19538,7 +19538,7 @@
       </c>
       <c r="D642" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E642" s="4" t="n"/>
@@ -19564,7 +19564,7 @@
       </c>
       <c r="D643" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E643" s="4" t="n"/>
@@ -19590,7 +19590,7 @@
       </c>
       <c r="D644" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E644" s="4" t="n"/>
@@ -19616,7 +19616,7 @@
       </c>
       <c r="D645" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E645" s="4" t="n"/>
@@ -19642,7 +19642,7 @@
       </c>
       <c r="D646" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E646" s="4" t="n"/>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="D647" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E647" s="4" t="n"/>
@@ -19694,7 +19694,7 @@
       </c>
       <c r="D648" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E648" s="4" t="n"/>
@@ -19720,7 +19720,7 @@
       </c>
       <c r="D649" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E649" s="4" t="n"/>
@@ -19746,7 +19746,7 @@
       </c>
       <c r="D650" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E650" s="4" t="n"/>
@@ -19772,7 +19772,7 @@
       </c>
       <c r="D651" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E651" s="4" t="n"/>
@@ -19798,7 +19798,7 @@
       </c>
       <c r="D652" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E652" s="4" t="n"/>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="D653" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E653" s="4" t="n"/>
@@ -19850,7 +19850,7 @@
       </c>
       <c r="D654" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E654" s="4" t="n"/>
@@ -19876,7 +19876,7 @@
       </c>
       <c r="D655" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E655" s="4" t="n"/>
@@ -19902,7 +19902,7 @@
       </c>
       <c r="D656" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E656" s="4" t="n"/>
@@ -19928,7 +19928,7 @@
       </c>
       <c r="D657" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E657" s="4" t="n"/>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="D658" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E658" s="4" t="n"/>
@@ -19980,7 +19980,7 @@
       </c>
       <c r="D659" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E659" s="4" t="n"/>
@@ -21826,7 +21826,7 @@
       </c>
       <c r="D730" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E730" s="2" t="inlineStr">
@@ -21862,7 +21862,7 @@
       </c>
       <c r="D731" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E731" s="2" t="inlineStr">
@@ -21898,7 +21898,7 @@
       </c>
       <c r="D732" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E732" s="4" t="n"/>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="D733" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E733" s="4" t="n"/>
@@ -21950,7 +21950,7 @@
       </c>
       <c r="D734" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E734" s="4" t="n"/>
@@ -21976,7 +21976,7 @@
       </c>
       <c r="D735" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E735" s="4" t="n"/>
@@ -22002,7 +22002,7 @@
       </c>
       <c r="D736" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E736" s="4" t="n"/>
@@ -22028,7 +22028,7 @@
       </c>
       <c r="D737" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E737" s="4" t="n"/>
@@ -22054,7 +22054,7 @@
       </c>
       <c r="D738" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E738" s="4" t="n"/>
@@ -22080,7 +22080,7 @@
       </c>
       <c r="D739" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E739" s="4" t="n"/>
@@ -22106,7 +22106,7 @@
       </c>
       <c r="D740" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E740" s="4" t="n"/>
@@ -22132,7 +22132,7 @@
       </c>
       <c r="D741" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E741" s="4" t="n"/>
@@ -22158,7 +22158,7 @@
       </c>
       <c r="D742" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E742" s="4" t="n"/>
@@ -22184,7 +22184,7 @@
       </c>
       <c r="D743" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E743" s="4" t="n"/>
@@ -22210,7 +22210,7 @@
       </c>
       <c r="D744" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E744" s="4" t="n"/>
@@ -22236,7 +22236,7 @@
       </c>
       <c r="D745" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E745" s="4" t="n"/>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="D746" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E746" s="4" t="n"/>
@@ -22288,7 +22288,7 @@
       </c>
       <c r="D747" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E747" s="4" t="n"/>
@@ -22314,7 +22314,7 @@
       </c>
       <c r="D748" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E748" s="4" t="n"/>
@@ -22340,7 +22340,7 @@
       </c>
       <c r="D749" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E749" s="4" t="n"/>
@@ -22366,7 +22366,7 @@
       </c>
       <c r="D750" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E750" s="4" t="n"/>
@@ -22392,7 +22392,7 @@
       </c>
       <c r="D751" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E751" s="4" t="n"/>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="D752" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E752" s="4" t="n"/>
@@ -22444,7 +22444,7 @@
       </c>
       <c r="D753" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E753" s="4" t="n"/>
@@ -22470,7 +22470,7 @@
       </c>
       <c r="D754" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E754" s="4" t="n"/>
@@ -24186,7 +24186,7 @@
       </c>
       <c r="D820" s="2" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E820" s="2" t="inlineStr">
@@ -24222,7 +24222,7 @@
       </c>
       <c r="D821" s="2" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E821" s="2" t="inlineStr">
@@ -24258,7 +24258,7 @@
       </c>
       <c r="D822" s="2" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E822" s="2" t="inlineStr">
@@ -24294,7 +24294,7 @@
       </c>
       <c r="D823" s="2" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E823" s="2" t="inlineStr">
@@ -24330,7 +24330,7 @@
       </c>
       <c r="D824" s="2" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E824" s="2" t="inlineStr">
@@ -24366,7 +24366,7 @@
       </c>
       <c r="D825" s="2" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E825" s="2" t="inlineStr">
@@ -24402,7 +24402,7 @@
       </c>
       <c r="D826" s="2" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E826" s="2" t="inlineStr">
@@ -24438,7 +24438,7 @@
       </c>
       <c r="D827" s="2" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E827" s="2" t="inlineStr">
@@ -24474,7 +24474,7 @@
       </c>
       <c r="D828" s="2" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E828" s="2" t="inlineStr">
@@ -24510,7 +24510,7 @@
       </c>
       <c r="D829" s="2" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E829" s="2" t="inlineStr">
@@ -24546,7 +24546,7 @@
       </c>
       <c r="D830" s="2" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E830" s="2" t="inlineStr">
@@ -24582,7 +24582,7 @@
       </c>
       <c r="D831" s="2" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E831" s="2" t="inlineStr">
@@ -24618,7 +24618,7 @@
       </c>
       <c r="D832" s="4" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E832" s="4" t="n"/>
@@ -24644,7 +24644,7 @@
       </c>
       <c r="D833" s="4" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E833" s="4" t="n"/>
@@ -24670,7 +24670,7 @@
       </c>
       <c r="D834" s="4" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E834" s="4" t="n"/>
@@ -24696,7 +24696,7 @@
       </c>
       <c r="D835" s="4" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E835" s="4" t="n"/>
@@ -24722,7 +24722,7 @@
       </c>
       <c r="D836" s="4" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E836" s="4" t="n"/>
@@ -24748,7 +24748,7 @@
       </c>
       <c r="D837" s="4" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E837" s="4" t="n"/>
@@ -24774,7 +24774,7 @@
       </c>
       <c r="D838" s="4" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E838" s="4" t="n"/>
@@ -24800,7 +24800,7 @@
       </c>
       <c r="D839" s="4" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E839" s="4" t="n"/>
@@ -24826,7 +24826,7 @@
       </c>
       <c r="D840" s="4" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E840" s="4" t="n"/>
@@ -24852,7 +24852,7 @@
       </c>
       <c r="D841" s="4" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E841" s="4" t="n"/>
@@ -24878,7 +24878,7 @@
       </c>
       <c r="D842" s="4" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E842" s="4" t="n"/>
@@ -24904,7 +24904,7 @@
       </c>
       <c r="D843" s="4" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E843" s="4" t="n"/>
@@ -24930,7 +24930,7 @@
       </c>
       <c r="D844" s="4" t="inlineStr">
         <is>
-          <t>Büro / Besprechung</t>
+          <t>Büro und Besprechung</t>
         </is>
       </c>
       <c r="E844" s="4" t="n"/>
@@ -27296,7 +27296,7 @@
       </c>
       <c r="D935" s="2" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E935" s="2" t="inlineStr">
@@ -27332,7 +27332,7 @@
       </c>
       <c r="D936" s="2" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E936" s="2" t="inlineStr">
@@ -27368,7 +27368,7 @@
       </c>
       <c r="D937" s="2" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E937" s="2" t="inlineStr">
@@ -27404,7 +27404,7 @@
       </c>
       <c r="D938" s="2" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E938" s="2" t="inlineStr">
@@ -27440,7 +27440,7 @@
       </c>
       <c r="D939" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E939" s="4" t="n"/>
@@ -27466,7 +27466,7 @@
       </c>
       <c r="D940" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E940" s="4" t="n"/>
@@ -27492,7 +27492,7 @@
       </c>
       <c r="D941" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E941" s="4" t="n"/>
@@ -27518,7 +27518,7 @@
       </c>
       <c r="D942" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E942" s="4" t="n"/>
@@ -27544,7 +27544,7 @@
       </c>
       <c r="D943" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E943" s="4" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="D944" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E944" s="4" t="n"/>
@@ -27596,7 +27596,7 @@
       </c>
       <c r="D945" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E945" s="4" t="n"/>
@@ -27622,7 +27622,7 @@
       </c>
       <c r="D946" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E946" s="4" t="n"/>
@@ -27648,7 +27648,7 @@
       </c>
       <c r="D947" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E947" s="4" t="n"/>
@@ -27674,7 +27674,7 @@
       </c>
       <c r="D948" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E948" s="4" t="n"/>
@@ -27700,7 +27700,7 @@
       </c>
       <c r="D949" s="4" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E949" s="4" t="n"/>
@@ -27726,7 +27726,7 @@
       </c>
       <c r="D950" s="2" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E950" s="2" t="inlineStr">
@@ -27762,7 +27762,7 @@
       </c>
       <c r="D951" s="2" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E951" s="2" t="inlineStr">
@@ -27798,7 +27798,7 @@
       </c>
       <c r="D952" s="2" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E952" s="2" t="inlineStr">
@@ -27834,7 +27834,7 @@
       </c>
       <c r="D953" s="2" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E953" s="2" t="inlineStr">
@@ -27870,7 +27870,7 @@
       </c>
       <c r="D954" s="2" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E954" s="2" t="inlineStr">
@@ -27906,7 +27906,7 @@
       </c>
       <c r="D955" s="2" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E955" s="2" t="inlineStr">
@@ -27942,7 +27942,7 @@
       </c>
       <c r="D956" s="2" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E956" s="2" t="inlineStr">
@@ -27978,7 +27978,7 @@
       </c>
       <c r="D957" s="4" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E957" s="4" t="n"/>
@@ -28004,7 +28004,7 @@
       </c>
       <c r="D958" s="4" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E958" s="4" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="D959" s="4" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E959" s="4" t="n"/>
@@ -28056,7 +28056,7 @@
       </c>
       <c r="D960" s="4" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E960" s="4" t="n"/>
@@ -28082,7 +28082,7 @@
       </c>
       <c r="D961" s="4" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E961" s="4" t="n"/>
@@ -28108,7 +28108,7 @@
       </c>
       <c r="D962" s="4" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E962" s="4" t="n"/>
@@ -28134,7 +28134,7 @@
       </c>
       <c r="D963" s="4" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E963" s="4" t="n"/>
@@ -28160,7 +28160,7 @@
       </c>
       <c r="D964" s="4" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E964" s="4" t="n"/>
@@ -28186,7 +28186,7 @@
       </c>
       <c r="D965" s="4" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E965" s="4" t="n"/>
@@ -28212,7 +28212,7 @@
       </c>
       <c r="D966" s="4" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur</t>
         </is>
       </c>
       <c r="E966" s="4" t="n"/>
@@ -28750,7 +28750,7 @@
       </c>
       <c r="D984" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E984" s="2" t="inlineStr">
@@ -28786,7 +28786,7 @@
       </c>
       <c r="D985" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E985" s="2" t="inlineStr">
@@ -28822,7 +28822,7 @@
       </c>
       <c r="D986" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E986" s="2" t="inlineStr">
@@ -28858,7 +28858,7 @@
       </c>
       <c r="D987" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E987" s="2" t="inlineStr">
@@ -28894,7 +28894,7 @@
       </c>
       <c r="D988" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E988" s="2" t="inlineStr">
@@ -28930,7 +28930,7 @@
       </c>
       <c r="D989" s="2" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E989" s="2" t="inlineStr">
@@ -28966,7 +28966,7 @@
       </c>
       <c r="D990" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E990" s="4" t="n"/>
@@ -28992,7 +28992,7 @@
       </c>
       <c r="D991" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E991" s="4" t="n"/>
@@ -29018,7 +29018,7 @@
       </c>
       <c r="D992" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E992" s="4" t="n"/>
@@ -29044,7 +29044,7 @@
       </c>
       <c r="D993" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E993" s="4" t="n"/>
@@ -29070,7 +29070,7 @@
       </c>
       <c r="D994" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E994" s="4" t="n"/>
@@ -29096,7 +29096,7 @@
       </c>
       <c r="D995" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E995" s="4" t="n"/>
@@ -29122,7 +29122,7 @@
       </c>
       <c r="D996" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E996" s="4" t="n"/>
@@ -29148,7 +29148,7 @@
       </c>
       <c r="D997" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E997" s="4" t="n"/>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="D998" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E998" s="4" t="n"/>
@@ -29200,7 +29200,7 @@
       </c>
       <c r="D999" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E999" s="4" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="D1000" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E1000" s="4" t="n"/>
@@ -29252,7 +29252,7 @@
       </c>
       <c r="D1001" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E1001" s="4" t="n"/>
@@ -29278,7 +29278,7 @@
       </c>
       <c r="D1002" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E1002" s="4" t="n"/>
@@ -29304,7 +29304,7 @@
       </c>
       <c r="D1003" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E1003" s="4" t="n"/>
@@ -29330,7 +29330,7 @@
       </c>
       <c r="D1004" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E1004" s="4" t="n"/>
@@ -29356,7 +29356,7 @@
       </c>
       <c r="D1005" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E1005" s="4" t="n"/>
@@ -29382,7 +29382,7 @@
       </c>
       <c r="D1006" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E1006" s="4" t="n"/>
@@ -29408,7 +29408,7 @@
       </c>
       <c r="D1007" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E1007" s="4" t="n"/>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="D1008" s="4" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="E1008" s="4" t="n"/>
@@ -30600,7 +30600,7 @@
       </c>
       <c r="D1049" s="2" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Materialraum</t>
         </is>
       </c>
       <c r="E1049" s="2" t="inlineStr">
@@ -30636,7 +30636,7 @@
       </c>
       <c r="D1050" s="2" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Materialraum</t>
         </is>
       </c>
       <c r="E1050" s="2" t="inlineStr">
@@ -30672,7 +30672,7 @@
       </c>
       <c r="D1051" s="2" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Materialraum</t>
         </is>
       </c>
       <c r="E1051" s="2" t="inlineStr">
@@ -30708,7 +30708,7 @@
       </c>
       <c r="D1052" s="2" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Materialraum</t>
         </is>
       </c>
       <c r="E1052" s="2" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="D1053" s="2" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Materialraum</t>
         </is>
       </c>
       <c r="E1053" s="2" t="inlineStr">
@@ -30780,7 +30780,7 @@
       </c>
       <c r="D1054" s="2" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Materialraum</t>
         </is>
       </c>
       <c r="E1054" s="2" t="inlineStr">
@@ -30816,7 +30816,7 @@
       </c>
       <c r="D1055" s="2" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Materialraum</t>
         </is>
       </c>
       <c r="E1055" s="2" t="inlineStr">
@@ -30852,7 +30852,7 @@
       </c>
       <c r="D1056" s="2" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Materialraum</t>
         </is>
       </c>
       <c r="E1056" s="2" t="inlineStr">
@@ -30888,7 +30888,7 @@
       </c>
       <c r="D1057" s="2" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Materialraum</t>
         </is>
       </c>
       <c r="E1057" s="2" t="inlineStr">
@@ -30924,7 +30924,7 @@
       </c>
       <c r="D1058" s="2" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Materialraum</t>
         </is>
       </c>
       <c r="E1058" s="2" t="inlineStr">
@@ -30960,7 +30960,7 @@
       </c>
       <c r="D1059" s="2" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Materialraum</t>
         </is>
       </c>
       <c r="E1059" s="2" t="inlineStr">
@@ -30996,7 +30996,7 @@
       </c>
       <c r="D1060" s="4" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Materialraum</t>
         </is>
       </c>
       <c r="E1060" s="4" t="n"/>
@@ -31022,7 +31022,7 @@
       </c>
       <c r="D1061" s="4" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Materialraum</t>
         </is>
       </c>
       <c r="E1061" s="4" t="n"/>
@@ -31048,7 +31048,7 @@
       </c>
       <c r="D1062" s="4" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Materialraum</t>
         </is>
       </c>
       <c r="E1062" s="4" t="n"/>
@@ -31074,7 +31074,7 @@
       </c>
       <c r="D1063" s="4" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Materialraum</t>
         </is>
       </c>
       <c r="E1063" s="4" t="n"/>
@@ -31100,7 +31100,7 @@
       </c>
       <c r="D1064" s="4" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Materialraum</t>
         </is>
       </c>
       <c r="E1064" s="4" t="n"/>
@@ -31126,7 +31126,7 @@
       </c>
       <c r="D1065" s="4" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Materialraum</t>
         </is>
       </c>
       <c r="E1065" s="4" t="n"/>
@@ -31152,7 +31152,7 @@
       </c>
       <c r="D1066" s="4" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Materialraum</t>
         </is>
       </c>
       <c r="E1066" s="4" t="n"/>
@@ -31178,7 +31178,7 @@
       </c>
       <c r="D1067" s="4" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Materialraum</t>
         </is>
       </c>
       <c r="E1067" s="4" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="D1068" s="4" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Materialraum</t>
         </is>
       </c>
       <c r="E1068" s="4" t="n"/>
@@ -31230,7 +31230,7 @@
       </c>
       <c r="D1069" s="4" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Materialraum</t>
         </is>
       </c>
       <c r="E1069" s="4" t="n"/>
@@ -31256,7 +31256,7 @@
       </c>
       <c r="D1070" s="2" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Lernraum</t>
         </is>
       </c>
       <c r="E1070" s="2" t="inlineStr">
@@ -31292,7 +31292,7 @@
       </c>
       <c r="D1071" s="2" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Lernraum</t>
         </is>
       </c>
       <c r="E1071" s="2" t="inlineStr">
@@ -31328,7 +31328,7 @@
       </c>
       <c r="D1072" s="2" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Lernraum</t>
         </is>
       </c>
       <c r="E1072" s="2" t="inlineStr">
@@ -31364,7 +31364,7 @@
       </c>
       <c r="D1073" s="2" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Lernraum</t>
         </is>
       </c>
       <c r="E1073" s="2" t="inlineStr">
@@ -31400,7 +31400,7 @@
       </c>
       <c r="D1074" s="2" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Lernraum</t>
         </is>
       </c>
       <c r="E1074" s="2" t="inlineStr">
@@ -31436,7 +31436,7 @@
       </c>
       <c r="D1075" s="4" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Lernraum</t>
         </is>
       </c>
       <c r="E1075" s="4" t="n"/>
@@ -31462,7 +31462,7 @@
       </c>
       <c r="D1076" s="4" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Lernraum</t>
         </is>
       </c>
       <c r="E1076" s="4" t="n"/>
@@ -31488,7 +31488,7 @@
       </c>
       <c r="D1077" s="4" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Lernraum</t>
         </is>
       </c>
       <c r="E1077" s="4" t="n"/>
@@ -31514,7 +31514,7 @@
       </c>
       <c r="D1078" s="4" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Lernraum</t>
         </is>
       </c>
       <c r="E1078" s="4" t="n"/>
@@ -31540,7 +31540,7 @@
       </c>
       <c r="D1079" s="4" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Lernraum</t>
         </is>
       </c>
       <c r="E1079" s="4" t="n"/>
@@ -31566,7 +31566,7 @@
       </c>
       <c r="D1080" s="4" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Lernraum</t>
         </is>
       </c>
       <c r="E1080" s="4" t="n"/>
@@ -31592,7 +31592,7 @@
       </c>
       <c r="D1081" s="4" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Lernraum</t>
         </is>
       </c>
       <c r="E1081" s="4" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="D1082" s="4" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Lernraum</t>
         </is>
       </c>
       <c r="E1082" s="4" t="n"/>
@@ -31644,7 +31644,7 @@
       </c>
       <c r="D1083" s="4" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Lernraum</t>
         </is>
       </c>
       <c r="E1083" s="4" t="n"/>
@@ -31670,7 +31670,7 @@
       </c>
       <c r="D1084" s="4" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Lernraum</t>
         </is>
       </c>
       <c r="E1084" s="4" t="n"/>
@@ -32466,7 +32466,7 @@
       </c>
       <c r="D1110" s="2" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Personalraum</t>
         </is>
       </c>
       <c r="E1110" s="2" t="inlineStr">
@@ -32502,7 +32502,7 @@
       </c>
       <c r="D1111" s="2" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Personalraum</t>
         </is>
       </c>
       <c r="E1111" s="2" t="inlineStr">
@@ -32538,7 +32538,7 @@
       </c>
       <c r="D1112" s="2" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Personalraum</t>
         </is>
       </c>
       <c r="E1112" s="2" t="inlineStr">
@@ -32574,7 +32574,7 @@
       </c>
       <c r="D1113" s="2" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Personalraum</t>
         </is>
       </c>
       <c r="E1113" s="2" t="inlineStr">
@@ -32610,7 +32610,7 @@
       </c>
       <c r="D1114" s="2" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Personalraum</t>
         </is>
       </c>
       <c r="E1114" s="2" t="inlineStr">
@@ -32646,7 +32646,7 @@
       </c>
       <c r="D1115" s="2" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Personalraum</t>
         </is>
       </c>
       <c r="E1115" s="2" t="inlineStr">
@@ -32682,7 +32682,7 @@
       </c>
       <c r="D1116" s="4" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Personalraum</t>
         </is>
       </c>
       <c r="E1116" s="4" t="n"/>
@@ -32708,7 +32708,7 @@
       </c>
       <c r="D1117" s="4" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Personalraum</t>
         </is>
       </c>
       <c r="E1117" s="4" t="n"/>
@@ -32734,7 +32734,7 @@
       </c>
       <c r="D1118" s="4" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Personalraum</t>
         </is>
       </c>
       <c r="E1118" s="4" t="n"/>
@@ -32760,7 +32760,7 @@
       </c>
       <c r="D1119" s="4" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Personalraum</t>
         </is>
       </c>
       <c r="E1119" s="4" t="n"/>
@@ -32786,7 +32786,7 @@
       </c>
       <c r="D1120" s="4" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Personalraum</t>
         </is>
       </c>
       <c r="E1120" s="4" t="n"/>
@@ -32812,7 +32812,7 @@
       </c>
       <c r="D1121" s="4" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Personalraum</t>
         </is>
       </c>
       <c r="E1121" s="4" t="n"/>
@@ -32838,7 +32838,7 @@
       </c>
       <c r="D1122" s="4" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Personalraum</t>
         </is>
       </c>
       <c r="E1122" s="4" t="n"/>
@@ -32864,7 +32864,7 @@
       </c>
       <c r="D1123" s="4" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Personalraum</t>
         </is>
       </c>
       <c r="E1123" s="4" t="n"/>
@@ -32890,7 +32890,7 @@
       </c>
       <c r="D1124" s="4" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Personalraum</t>
         </is>
       </c>
       <c r="E1124" s="4" t="n"/>
@@ -32916,7 +32916,7 @@
       </c>
       <c r="D1125" s="4" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Personalraum</t>
         </is>
       </c>
       <c r="E1125" s="4" t="n"/>
@@ -32942,7 +32942,7 @@
       </c>
       <c r="D1126" s="2" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Ruheraum</t>
         </is>
       </c>
       <c r="E1126" s="2" t="inlineStr">
@@ -32978,7 +32978,7 @@
       </c>
       <c r="D1127" s="2" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Ruheraum</t>
         </is>
       </c>
       <c r="E1127" s="2" t="inlineStr">
@@ -33014,7 +33014,7 @@
       </c>
       <c r="D1128" s="2" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Ruheraum</t>
         </is>
       </c>
       <c r="E1128" s="2" t="inlineStr">
@@ -33050,7 +33050,7 @@
       </c>
       <c r="D1129" s="2" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Ruheraum</t>
         </is>
       </c>
       <c r="E1129" s="2" t="inlineStr">
@@ -33086,7 +33086,7 @@
       </c>
       <c r="D1130" s="2" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Ruheraum</t>
         </is>
       </c>
       <c r="E1130" s="2" t="inlineStr">
@@ -33122,7 +33122,7 @@
       </c>
       <c r="D1131" s="2" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Ruheraum</t>
         </is>
       </c>
       <c r="E1131" s="2" t="inlineStr">
@@ -33158,7 +33158,7 @@
       </c>
       <c r="D1132" s="2" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Ruheraum</t>
         </is>
       </c>
       <c r="E1132" s="2" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="D1133" s="2" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Ruheraum</t>
         </is>
       </c>
       <c r="E1133" s="2" t="inlineStr">
@@ -33230,7 +33230,7 @@
       </c>
       <c r="D1134" s="2" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Ruheraum</t>
         </is>
       </c>
       <c r="E1134" s="2" t="inlineStr">
@@ -33266,7 +33266,7 @@
       </c>
       <c r="D1135" s="2" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Ruheraum</t>
         </is>
       </c>
       <c r="E1135" s="2" t="inlineStr">
@@ -33302,7 +33302,7 @@
       </c>
       <c r="D1136" s="2" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Ruheraum</t>
         </is>
       </c>
       <c r="E1136" s="2" t="inlineStr">
@@ -33338,7 +33338,7 @@
       </c>
       <c r="D1137" s="4" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Ruheraum</t>
         </is>
       </c>
       <c r="E1137" s="4" t="n"/>
@@ -33364,7 +33364,7 @@
       </c>
       <c r="D1138" s="4" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Ruheraum</t>
         </is>
       </c>
       <c r="E1138" s="4" t="n"/>
@@ -33390,7 +33390,7 @@
       </c>
       <c r="D1139" s="4" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Ruheraum</t>
         </is>
       </c>
       <c r="E1139" s="4" t="n"/>
@@ -33416,7 +33416,7 @@
       </c>
       <c r="D1140" s="4" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Ruheraum</t>
         </is>
       </c>
       <c r="E1140" s="4" t="n"/>
@@ -33442,7 +33442,7 @@
       </c>
       <c r="D1141" s="4" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Ruheraum</t>
         </is>
       </c>
       <c r="E1141" s="4" t="n"/>
@@ -33468,7 +33468,7 @@
       </c>
       <c r="D1142" s="4" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Ruheraum</t>
         </is>
       </c>
       <c r="E1142" s="4" t="n"/>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="D1143" s="4" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Ruheraum</t>
         </is>
       </c>
       <c r="E1143" s="4" t="n"/>
@@ -33520,7 +33520,7 @@
       </c>
       <c r="D1144" s="4" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Ruheraum</t>
         </is>
       </c>
       <c r="E1144" s="4" t="n"/>
@@ -33546,7 +33546,7 @@
       </c>
       <c r="D1145" s="4" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Ruheraum</t>
         </is>
       </c>
       <c r="E1145" s="4" t="n"/>
@@ -33572,7 +33572,7 @@
       </c>
       <c r="D1146" s="4" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Ruheraum</t>
         </is>
       </c>
       <c r="E1146" s="4" t="n"/>
@@ -33988,7 +33988,7 @@
       </c>
       <c r="D1162" s="2" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>Personal-WC</t>
         </is>
       </c>
       <c r="E1162" s="2" t="inlineStr">
@@ -34024,7 +34024,7 @@
       </c>
       <c r="D1163" s="4" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>Personal-WC</t>
         </is>
       </c>
       <c r="E1163" s="4" t="n"/>
@@ -34050,7 +34050,7 @@
       </c>
       <c r="D1164" s="4" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>Personal-WC</t>
         </is>
       </c>
       <c r="E1164" s="4" t="n"/>
@@ -34076,7 +34076,7 @@
       </c>
       <c r="D1165" s="4" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>Personal-WC</t>
         </is>
       </c>
       <c r="E1165" s="4" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="D1166" s="4" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>Personal-WC</t>
         </is>
       </c>
       <c r="E1166" s="4" t="n"/>
@@ -34128,7 +34128,7 @@
       </c>
       <c r="D1167" s="4" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>Personal-WC</t>
         </is>
       </c>
       <c r="E1167" s="4" t="n"/>
@@ -34154,7 +34154,7 @@
       </c>
       <c r="D1168" s="4" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>Personal-WC</t>
         </is>
       </c>
       <c r="E1168" s="4" t="n"/>
@@ -34180,7 +34180,7 @@
       </c>
       <c r="D1169" s="4" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>Personal-WC</t>
         </is>
       </c>
       <c r="E1169" s="4" t="n"/>
@@ -34206,7 +34206,7 @@
       </c>
       <c r="D1170" s="4" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>Personal-WC</t>
         </is>
       </c>
       <c r="E1170" s="4" t="n"/>
@@ -34232,7 +34232,7 @@
       </c>
       <c r="D1171" s="4" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>Personal-WC</t>
         </is>
       </c>
       <c r="E1171" s="4" t="n"/>
@@ -34258,7 +34258,7 @@
       </c>
       <c r="D1172" s="4" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>Personal-WC</t>
         </is>
       </c>
       <c r="E1172" s="4" t="n"/>
@@ -36960,7 +36960,7 @@
       <c r="C1268" s="2" t="inlineStr"/>
       <c r="D1268" s="2" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1268" s="2" t="inlineStr">
@@ -36992,7 +36992,7 @@
       <c r="C1269" s="2" t="inlineStr"/>
       <c r="D1269" s="2" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1269" s="2" t="inlineStr">
@@ -37024,7 +37024,7 @@
       <c r="C1270" s="2" t="inlineStr"/>
       <c r="D1270" s="2" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1270" s="2" t="inlineStr">
@@ -37056,7 +37056,7 @@
       <c r="C1271" s="2" t="inlineStr"/>
       <c r="D1271" s="2" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1271" s="2" t="inlineStr">
@@ -37088,7 +37088,7 @@
       <c r="C1272" s="2" t="inlineStr"/>
       <c r="D1272" s="2" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1272" s="2" t="inlineStr">
@@ -37120,7 +37120,7 @@
       <c r="C1273" s="2" t="inlineStr"/>
       <c r="D1273" s="2" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1273" s="2" t="inlineStr">
@@ -37152,7 +37152,7 @@
       <c r="C1274" s="2" t="inlineStr"/>
       <c r="D1274" s="2" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1274" s="2" t="inlineStr">
@@ -37184,7 +37184,7 @@
       <c r="C1275" s="2" t="inlineStr"/>
       <c r="D1275" s="2" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1275" s="2" t="inlineStr">
@@ -37216,7 +37216,7 @@
       <c r="C1276" s="2" t="inlineStr"/>
       <c r="D1276" s="2" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1276" s="2" t="inlineStr">
@@ -37248,7 +37248,7 @@
       <c r="C1277" s="2" t="inlineStr"/>
       <c r="D1277" s="2" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1277" s="2" t="inlineStr">
@@ -37280,7 +37280,7 @@
       <c r="C1278" s="2" t="inlineStr"/>
       <c r="D1278" s="2" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1278" s="2" t="inlineStr">
@@ -37312,7 +37312,7 @@
       <c r="C1279" s="2" t="inlineStr"/>
       <c r="D1279" s="2" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1279" s="2" t="inlineStr">
@@ -37344,7 +37344,7 @@
       <c r="C1280" s="2" t="inlineStr"/>
       <c r="D1280" s="2" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1280" s="2" t="inlineStr">
@@ -37376,7 +37376,7 @@
       <c r="C1281" s="2" t="inlineStr"/>
       <c r="D1281" s="2" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1281" s="2" t="inlineStr">
@@ -37408,7 +37408,7 @@
       <c r="C1282" s="2" t="inlineStr"/>
       <c r="D1282" s="2" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1282" s="2" t="inlineStr">
@@ -37440,7 +37440,7 @@
       <c r="C1283" s="2" t="inlineStr"/>
       <c r="D1283" s="2" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1283" s="2" t="inlineStr">
@@ -37472,7 +37472,7 @@
       <c r="C1284" s="4" t="inlineStr"/>
       <c r="D1284" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1284" s="4" t="n"/>
@@ -37494,7 +37494,7 @@
       <c r="C1285" s="4" t="inlineStr"/>
       <c r="D1285" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1285" s="4" t="n"/>
@@ -37516,7 +37516,7 @@
       <c r="C1286" s="4" t="inlineStr"/>
       <c r="D1286" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1286" s="4" t="n"/>
@@ -37538,7 +37538,7 @@
       <c r="C1287" s="4" t="inlineStr"/>
       <c r="D1287" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1287" s="4" t="n"/>
@@ -37560,7 +37560,7 @@
       <c r="C1288" s="4" t="inlineStr"/>
       <c r="D1288" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1288" s="4" t="n"/>
@@ -37582,7 +37582,7 @@
       <c r="C1289" s="4" t="inlineStr"/>
       <c r="D1289" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1289" s="4" t="n"/>
@@ -37604,7 +37604,7 @@
       <c r="C1290" s="4" t="inlineStr"/>
       <c r="D1290" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1290" s="4" t="n"/>
@@ -37626,7 +37626,7 @@
       <c r="C1291" s="4" t="inlineStr"/>
       <c r="D1291" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1291" s="4" t="n"/>
@@ -37648,7 +37648,7 @@
       <c r="C1292" s="4" t="inlineStr"/>
       <c r="D1292" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1292" s="4" t="n"/>
@@ -37670,7 +37670,7 @@
       <c r="C1293" s="4" t="inlineStr"/>
       <c r="D1293" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1293" s="4" t="n"/>
@@ -37692,7 +37692,7 @@
       <c r="C1294" s="4" t="inlineStr"/>
       <c r="D1294" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1294" s="4" t="n"/>
@@ -37714,7 +37714,7 @@
       <c r="C1295" s="4" t="inlineStr"/>
       <c r="D1295" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1295" s="4" t="n"/>
@@ -37736,7 +37736,7 @@
       <c r="C1296" s="4" t="inlineStr"/>
       <c r="D1296" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1296" s="4" t="n"/>
@@ -37758,7 +37758,7 @@
       <c r="C1297" s="4" t="inlineStr"/>
       <c r="D1297" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1297" s="4" t="n"/>
@@ -37780,7 +37780,7 @@
       <c r="C1298" s="4" t="inlineStr"/>
       <c r="D1298" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1298" s="4" t="n"/>
@@ -37802,7 +37802,7 @@
       <c r="C1299" s="4" t="inlineStr"/>
       <c r="D1299" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1299" s="4" t="n"/>
@@ -37824,7 +37824,7 @@
       <c r="C1300" s="4" t="inlineStr"/>
       <c r="D1300" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1300" s="4" t="n"/>
@@ -37846,7 +37846,7 @@
       <c r="C1301" s="4" t="inlineStr"/>
       <c r="D1301" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1301" s="4" t="n"/>
@@ -37868,7 +37868,7 @@
       <c r="C1302" s="4" t="inlineStr"/>
       <c r="D1302" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1302" s="4" t="n"/>
@@ -37890,7 +37890,7 @@
       <c r="C1303" s="4" t="inlineStr"/>
       <c r="D1303" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1303" s="4" t="n"/>
@@ -37912,7 +37912,7 @@
       <c r="C1304" s="4" t="inlineStr"/>
       <c r="D1304" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1304" s="4" t="n"/>
@@ -37934,7 +37934,7 @@
       <c r="C1305" s="4" t="inlineStr"/>
       <c r="D1305" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1305" s="4" t="n"/>
@@ -37956,7 +37956,7 @@
       <c r="C1306" s="4" t="inlineStr"/>
       <c r="D1306" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1306" s="4" t="n"/>
@@ -37978,7 +37978,7 @@
       <c r="C1307" s="4" t="inlineStr"/>
       <c r="D1307" s="4" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garten</t>
         </is>
       </c>
       <c r="E1307" s="4" t="n"/>
